--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4143D07C-BA0B-4ADD-97DF-BE9BFB2F5ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4478D3-12B2-47F3-A8EC-438404F07569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="371">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1564,10 +1564,6 @@
   </si>
   <si>
     <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target Buy Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3466,10 +3462,10 @@
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="306" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F1" s="307" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -3498,13 +3494,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C5" s="49" t="s">
+        <v>322</v>
+      </c>
+      <c r="D5" s="50" t="s">
         <v>323</v>
-      </c>
-      <c r="D5" s="50" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3534,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
@@ -3546,7 +3542,7 @@
       <c r="C9" s="51">
         <v>1.06</v>
       </c>
-      <c r="D9" s="49" t="str">
+      <c r="D9" s="33" t="str">
         <f>IF(C8=D6,D6,C8&amp;"/"&amp;D6)</f>
         <v>CNY/HKD</v>
       </c>
@@ -3554,7 +3550,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C10" s="300">
         <v>6</v>
@@ -3593,7 +3589,7 @@
     </row>
     <row r="14" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="308" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C14" s="308"/>
       <c r="D14" s="308"/>
@@ -3602,14 +3598,14 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="46" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C16" s="47"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C17" s="33" t="e">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3622,13 +3618,13 @@
         <v>61</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C19" s="265">
         <v>0.2</v>
@@ -3636,15 +3632,16 @@
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B20" s="2" t="s">
-        <v>296</v>
+      <c r="B20" s="2" t="str">
+        <f>"Target Buy Price ("&amp;Market_currency&amp;") :"</f>
+        <v>Target Buy Price (HKD) :</v>
       </c>
       <c r="C20" s="268" t="e">
         <f>C121</f>
         <v>#VALUE!</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E20" s="302">
         <f>Scenarios!C76</f>
@@ -3653,16 +3650,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C21" s="301" t="e">
         <f ca="1">Scenarios!C87</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D21" s="5" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
+      <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3897,7 +3891,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="48" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C53" s="200" t="str">
         <f>Normalized_FCF!G19</f>
@@ -3923,7 +3917,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B55" s="271" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C55" s="101" t="e">
         <f>Normalized_FCF!C120</f>
@@ -3932,7 +3926,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="271" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C56" s="101" t="e">
         <f>Normalized_FCF!C92</f>
@@ -3941,7 +3935,7 @@
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A58" s="263" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B58" s="37"/>
       <c r="C58" s="37"/>
@@ -3955,7 +3949,7 @@
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
       <c r="B60" s="310" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C60" s="310"/>
       <c r="D60" s="310"/>
@@ -3978,7 +3972,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C64" s="282">
         <v>0.08</v>
@@ -3986,26 +3980,26 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C65" s="282">
         <f>IF(D65="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C66" s="282">
         <f>IF(D66="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -4022,7 +4016,7 @@
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="308" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C69" s="308"/>
       <c r="D69" s="308"/>
@@ -4048,7 +4042,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B73" s="48" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C73" s="264" t="e">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4106,7 +4100,7 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="48" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C82" s="264">
         <f>C81*C28*Exchange_Rate/Common_Shares</f>
@@ -4150,7 +4144,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="48" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C87" s="264">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4181,7 +4175,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="48" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C91" s="264">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
@@ -4203,7 +4197,7 @@
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="48" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C95" s="264" t="e">
         <f>Valuation_Model!C12</f>
@@ -4226,7 +4220,7 @@
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B99" s="308" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C99" s="308"/>
       <c r="D99" s="308"/>
@@ -4375,7 +4369,7 @@
     </row>
     <row r="110" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A110" s="263" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B110" s="37"/>
       <c r="C110" s="37"/>
@@ -4408,7 +4402,7 @@
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B115" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C115" s="266">
         <f>C19</f>
@@ -6660,7 +6654,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10238,7 +10232,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C92" s="24" t="e">
         <f>C89/Market_Price</f>
@@ -11315,7 +11309,7 @@
     <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="10"/>
       <c r="B120" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C120" s="84" t="e">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -12820,13 +12814,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C45" s="279" t="s">
         <v>148</v>
       </c>
       <c r="D45" s="218" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F45" s="110" t="s">
         <v>64</v>
@@ -12834,7 +12828,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C46" s="200">
         <f>G29</f>
@@ -12987,7 +12981,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="170" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C61" s="280" t="s">
         <v>149</v>
@@ -13010,7 +13004,7 @@
         <v>1.3197490690642218E-3</v>
       </c>
       <c r="F62" s="305" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -13032,7 +13026,7 @@
         <v>148</v>
       </c>
       <c r="D65" s="285" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="66" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -13164,7 +13158,7 @@
     </row>
     <row r="78" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="88" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C78" s="38"/>
       <c r="D78" s="38"/>
@@ -13175,15 +13169,15 @@
     </row>
     <row r="79" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="D79" s="290" t="s">
         <v>338</v>
-      </c>
-      <c r="D79" s="290" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="80" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="287" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C80" s="200">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -13200,7 +13194,7 @@
     </row>
     <row r="81" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="287" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C81" s="200">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -13234,7 +13228,7 @@
     </row>
     <row r="83" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B83" s="89" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C83" s="199">
         <f>SUM(C80:C82)</f>
@@ -14736,7 +14730,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="168" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C80" s="168" t="s">
         <v>117</v>
@@ -14808,7 +14802,7 @@
       <c r="E2" s="38"/>
       <c r="F2" s="38"/>
       <c r="H2" s="298" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I2" s="299"/>
     </row>
@@ -14862,7 +14856,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="111" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F6" s="111"/>
       <c r="H6" s="297">
@@ -14875,7 +14869,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="111" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" s="126" t="str">
         <f>Normalized_FCF!G8</f>
@@ -14955,7 +14949,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="172" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E11" s="315"/>
       <c r="F11" s="315"/>
@@ -15041,12 +15035,12 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="172" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="111" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C21" s="173">
         <f>Market_Price</f>
@@ -15059,7 +15053,7 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="111" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C22" s="173" t="e">
         <f>Valuation_Model!C12</f>
@@ -15347,7 +15341,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="172" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E54" s="172" t="s">
         <v>161</v>
@@ -15416,7 +15410,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="111" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F60" s="294">
         <v>3</v>
@@ -15424,7 +15418,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="37" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C62" s="38"/>
       <c r="D62" s="38"/>
@@ -15433,10 +15427,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="120" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E63" s="304" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -15448,7 +15442,7 @@
       </c>
       <c r="D64" s="162"/>
       <c r="E64" s="303" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -15460,7 +15454,7 @@
       </c>
       <c r="D65" s="163"/>
       <c r="E65" s="303" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -15476,20 +15470,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="303" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="120" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E68" s="304" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="111" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C69" s="293" t="e">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -15499,19 +15493,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="111" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C70" s="293" t="e">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E70" s="303" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="111" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C71" s="293" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -15521,7 +15515,7 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="111" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C72" s="292" t="e">
         <f>IF(E72&gt;50%,"Y","N")</f>
@@ -15550,7 +15544,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C76" s="295">
         <f>F60</f>
@@ -15575,12 +15569,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="120" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="160" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C80" s="180">
         <f>Thesis!C115</f>
@@ -15634,12 +15628,12 @@
     </row>
     <row r="85" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="120" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="160" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C86" s="286">
         <f>Market_Price</f>
@@ -15652,7 +15646,7 @@
     </row>
     <row r="87" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="111" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C87" s="284" t="e">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEC5372-AD18-4B20-8E5C-403B2FABDF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49B8AA9-874A-4663-95BF-4180CC8D4B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="386">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -118,10 +118,6 @@
   </si>
   <si>
     <t>Total Liabilities</t>
-  </si>
-  <si>
-    <t>Capitalization:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ST AR</t>
@@ -1564,10 +1560,6 @@
   </si>
   <si>
     <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target Buy Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3322,20 +3314,35 @@
     <xf numFmtId="187" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3346,22 +3353,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3653,22 +3645,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C1" s="44">
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="293" t="s">
+        <v>362</v>
+      </c>
+      <c r="F1" s="294" t="s">
         <v>364</v>
-      </c>
-      <c r="F1" s="294" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="254" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3692,24 +3684,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="50">
         <v>7.9</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -3725,7 +3717,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C8" s="287">
         <v>6</v>
@@ -3735,7 +3727,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3745,17 +3737,15 @@
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="4" t="s">
-        <v>25</v>
+      <c r="B10" s="4" t="str">
+        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
+        <v>Capitalization (HKD):</v>
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
         <v>64557.851494399998</v>
       </c>
-      <c r="D10" s="32" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
+      <c r="D10" s="32"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -3763,24 +3753,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="325" t="s">
-        <v>300</v>
-      </c>
-      <c r="C12" s="325"/>
-      <c r="D12" s="325"/>
-      <c r="E12" s="325"/>
-      <c r="F12" s="325"/>
+      <c r="B12" s="330" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12" s="330"/>
+      <c r="D12" s="330"/>
+      <c r="E12" s="330"/>
+      <c r="F12" s="330"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3793,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -3813,16 +3803,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C19" s="256">
         <v>0.2</v>
@@ -3830,15 +3820,16 @@
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B20" s="2" t="s">
-        <v>296</v>
+      <c r="B20" s="2" t="str">
+        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
+        <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="259">
         <f>C123</f>
         <v>7.4179368510878518</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E20" s="289">
         <f>Scenarios!C76</f>
@@ -3847,16 +3838,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
         <v>0.17349059186547722</v>
       </c>
-      <c r="D21" s="5" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
+      <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3865,7 +3853,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="254" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -3874,26 +3862,26 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="325" t="s">
-        <v>244</v>
-      </c>
-      <c r="C25" s="325"/>
-      <c r="D25" s="325"/>
-      <c r="E25" s="325"/>
-      <c r="F25" s="325"/>
+      <c r="B25" s="330" t="s">
+        <v>243</v>
+      </c>
+      <c r="C25" s="330"/>
+      <c r="D25" s="330"/>
+      <c r="E25" s="330"/>
+      <c r="F25" s="330"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="329" t="s">
-        <v>265</v>
-      </c>
-      <c r="C26" s="329"/>
-      <c r="D26" s="329"/>
-      <c r="E26" s="329"/>
-      <c r="F26" s="329"/>
+      <c r="B26" s="331" t="s">
+        <v>264</v>
+      </c>
+      <c r="C26" s="331"/>
+      <c r="D26" s="331"/>
+      <c r="E26" s="331"/>
+      <c r="F26" s="331"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
@@ -3901,17 +3889,17 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="327" t="s">
-        <v>246</v>
-      </c>
-      <c r="C29" s="327"/>
-      <c r="D29" s="327"/>
-      <c r="E29" s="327"/>
-      <c r="F29" s="327"/>
+      <c r="B29" s="329" t="s">
+        <v>245</v>
+      </c>
+      <c r="C29" s="329"/>
+      <c r="D29" s="329"/>
+      <c r="E29" s="329"/>
+      <c r="F29" s="329"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C30" s="192">
         <f>Normalized_FCF!C8</f>
@@ -3927,17 +3915,17 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="327" t="s">
-        <v>248</v>
-      </c>
-      <c r="C32" s="327"/>
-      <c r="D32" s="327"/>
-      <c r="E32" s="327"/>
-      <c r="F32" s="327"/>
+      <c r="B32" s="329" t="s">
+        <v>247</v>
+      </c>
+      <c r="C32" s="329"/>
+      <c r="D32" s="329"/>
+      <c r="E32" s="329"/>
+      <c r="F32" s="329"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C33" s="192">
         <f>Normalized_FCF!C9</f>
@@ -3950,7 +3938,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C34" s="192">
         <f>Normalized_FCF!C10</f>
@@ -3962,17 +3950,17 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="327" t="s">
-        <v>251</v>
-      </c>
-      <c r="C36" s="327"/>
-      <c r="D36" s="327"/>
-      <c r="E36" s="327"/>
-      <c r="F36" s="327"/>
+      <c r="B36" s="329" t="s">
+        <v>250</v>
+      </c>
+      <c r="C36" s="329"/>
+      <c r="D36" s="329"/>
+      <c r="E36" s="329"/>
+      <c r="F36" s="329"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C37" s="192">
         <f>Normalized_FCF!C11</f>
@@ -3984,17 +3972,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="327" t="s">
-        <v>255</v>
-      </c>
-      <c r="C39" s="327"/>
-      <c r="D39" s="327"/>
-      <c r="E39" s="327"/>
-      <c r="F39" s="327"/>
+      <c r="B39" s="329" t="s">
+        <v>254</v>
+      </c>
+      <c r="C39" s="329"/>
+      <c r="D39" s="329"/>
+      <c r="E39" s="329"/>
+      <c r="F39" s="329"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C40" s="192">
         <f>Normalized_FCF!C12</f>
@@ -4007,12 +3995,12 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="47" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C43" s="192">
         <f>Normalized_FCF!C15</f>
@@ -4024,17 +4012,17 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="327" t="s">
-        <v>256</v>
-      </c>
-      <c r="C45" s="327"/>
-      <c r="D45" s="327"/>
-      <c r="E45" s="327"/>
-      <c r="F45" s="327"/>
+      <c r="B45" s="329" t="s">
+        <v>255</v>
+      </c>
+      <c r="C45" s="329"/>
+      <c r="D45" s="329"/>
+      <c r="E45" s="329"/>
+      <c r="F45" s="329"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C46" s="192">
         <f>Normalized_FCF!C14</f>
@@ -4046,17 +4034,17 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="327" t="s">
-        <v>259</v>
-      </c>
-      <c r="C48" s="328"/>
-      <c r="D48" s="328"/>
-      <c r="E48" s="328"/>
-      <c r="F48" s="328"/>
+      <c r="B48" s="329" t="s">
+        <v>258</v>
+      </c>
+      <c r="C48" s="333"/>
+      <c r="D48" s="333"/>
+      <c r="E48" s="333"/>
+      <c r="F48" s="333"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C49" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4069,7 +4057,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="47" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C50" s="1">
         <f>Normalized_FCF!C18</f>
@@ -4081,17 +4069,17 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="325" t="s">
-        <v>281</v>
-      </c>
-      <c r="C52" s="325"/>
-      <c r="D52" s="325"/>
-      <c r="E52" s="325"/>
-      <c r="F52" s="325"/>
+      <c r="B52" s="330" t="s">
+        <v>280</v>
+      </c>
+      <c r="C52" s="330"/>
+      <c r="D52" s="330"/>
+      <c r="E52" s="330"/>
+      <c r="F52" s="330"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C53" s="192">
         <f>Normalized_FCF!G19</f>
@@ -4104,7 +4092,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B54" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C54" s="192">
         <f>Normalized_FCF!C19</f>
@@ -4117,7 +4105,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B55" s="261" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
@@ -4126,7 +4114,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="261" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
@@ -4135,7 +4123,7 @@
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A58" s="254" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B58" s="36"/>
       <c r="C58" s="36"/>
@@ -4148,31 +4136,31 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="327" t="s">
-        <v>317</v>
-      </c>
-      <c r="C60" s="327"/>
-      <c r="D60" s="327"/>
-      <c r="E60" s="327"/>
-      <c r="F60" s="327"/>
+      <c r="B60" s="329" t="s">
+        <v>315</v>
+      </c>
+      <c r="C60" s="329"/>
+      <c r="D60" s="329"/>
+      <c r="E60" s="329"/>
+      <c r="F60" s="329"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="329" t="s">
-        <v>272</v>
-      </c>
-      <c r="C61" s="329"/>
-      <c r="D61" s="329"/>
-      <c r="E61" s="329"/>
-      <c r="F61" s="329"/>
+      <c r="B61" s="331" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="331"/>
+      <c r="D61" s="331"/>
+      <c r="E61" s="331"/>
+      <c r="F61" s="331"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C64" s="322">
         <v>0.08</v>
@@ -4180,31 +4168,31 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C65" s="271">
         <f>IF(D65="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D65" s="296" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C66" s="271">
         <f>IF(D66="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D66" s="296" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="82" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C67" s="271">
         <f>SUM(C64:C66)</f>
@@ -4215,26 +4203,26 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="325" t="s">
-        <v>325</v>
-      </c>
-      <c r="C69" s="325"/>
-      <c r="D69" s="325"/>
-      <c r="E69" s="325"/>
-      <c r="F69" s="325"/>
+      <c r="B69" s="330" t="s">
+        <v>323</v>
+      </c>
+      <c r="C69" s="330"/>
+      <c r="D69" s="330"/>
+      <c r="E69" s="330"/>
+      <c r="F69" s="330"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="325" t="s">
-        <v>271</v>
-      </c>
-      <c r="C70" s="325"/>
-      <c r="D70" s="325"/>
-      <c r="E70" s="325"/>
-      <c r="F70" s="325"/>
+      <c r="B70" s="330" t="s">
+        <v>270</v>
+      </c>
+      <c r="C70" s="330"/>
+      <c r="D70" s="330"/>
+      <c r="E70" s="330"/>
+      <c r="F70" s="330"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C71" s="271">
         <v>0</v>
@@ -4242,7 +4230,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B73" s="47" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C73" s="255">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4255,7 +4243,7 @@
     </row>
     <row r="75" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A75" s="254" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B75" s="36"/>
       <c r="C75" s="36"/>
@@ -4267,27 +4255,27 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="325" t="s">
-        <v>274</v>
-      </c>
-      <c r="C77" s="325"/>
-      <c r="D77" s="325"/>
-      <c r="E77" s="325"/>
-      <c r="F77" s="325"/>
+      <c r="B77" s="330" t="s">
+        <v>273</v>
+      </c>
+      <c r="C77" s="330"/>
+      <c r="D77" s="330"/>
+      <c r="E77" s="330"/>
+      <c r="F77" s="330"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B80" s="241" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="47" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C81" s="192">
         <f>Valuation_Model!C7</f>
@@ -4300,7 +4288,7 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="47" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C82" s="255">
         <f>C81*C28*Exchange_Rate/Common_Shares</f>
@@ -4313,12 +4301,12 @@
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C85" s="192">
         <f>BS!C66</f>
@@ -4331,7 +4319,7 @@
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C86" s="192">
         <f>Valuation_Model!C8</f>
@@ -4344,7 +4332,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C87" s="255">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4357,12 +4345,12 @@
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C90" s="192">
         <f>Valuation_Model!C9</f>
@@ -4375,7 +4363,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C91" s="255">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
@@ -4387,17 +4375,17 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="325" t="s">
-        <v>280</v>
-      </c>
-      <c r="C93" s="325"/>
-      <c r="D93" s="325"/>
-      <c r="E93" s="325"/>
-      <c r="F93" s="325"/>
+      <c r="B93" s="330" t="s">
+        <v>279</v>
+      </c>
+      <c r="C93" s="330"/>
+      <c r="D93" s="330"/>
+      <c r="E93" s="330"/>
+      <c r="F93" s="330"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C95" s="255">
         <f>Valuation_Model!C12</f>
@@ -4410,7 +4398,7 @@
     </row>
     <row r="97" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A97" s="254" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B97" s="36"/>
       <c r="C97" s="36"/>
@@ -4419,29 +4407,29 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="327" t="s">
-        <v>386</v>
-      </c>
-      <c r="C99" s="327"/>
-      <c r="D99" s="327"/>
-      <c r="E99" s="327"/>
-      <c r="F99" s="327"/>
+      <c r="B99" s="329" t="s">
+        <v>384</v>
+      </c>
+      <c r="C99" s="329"/>
+      <c r="D99" s="329"/>
+      <c r="E99" s="329"/>
+      <c r="F99" s="329"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C101" s="267" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D101" s="267" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E101" s="267" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F101" s="267" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
@@ -4556,7 +4544,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B108" s="242" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C108" s="248">
         <f>Scenarios!C60</f>
@@ -4568,17 +4556,17 @@
       </c>
     </row>
     <row r="110" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B110" s="338" t="s">
-        <v>387</v>
-      </c>
-      <c r="C110" s="338"/>
-      <c r="D110" s="338"/>
-      <c r="E110" s="338"/>
-      <c r="F110" s="338"/>
+      <c r="B110" s="334" t="s">
+        <v>385</v>
+      </c>
+      <c r="C110" s="334"/>
+      <c r="D110" s="334"/>
+      <c r="E110" s="334"/>
+      <c r="F110" s="334"/>
     </row>
     <row r="112" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A112" s="254" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B112" s="36"/>
       <c r="C112" s="36"/>
@@ -4587,22 +4575,22 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="326" t="s">
-        <v>288</v>
-      </c>
-      <c r="C114" s="326"/>
-      <c r="D114" s="326"/>
-      <c r="E114" s="326"/>
-      <c r="F114" s="326"/>
+      <c r="B114" s="332" t="s">
+        <v>287</v>
+      </c>
+      <c r="C114" s="332"/>
+      <c r="D114" s="332"/>
+      <c r="E114" s="332"/>
+      <c r="F114" s="332"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B116" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C116" s="258">
         <f>E20</f>
@@ -4611,7 +4599,7 @@
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B117" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C117" s="257">
         <f>C19</f>
@@ -4620,7 +4608,7 @@
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B118" s="243" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C118" s="244">
         <f>Scenarios!C77</f>
@@ -4633,7 +4621,7 @@
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B120" s="241" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.35">
@@ -4658,7 +4646,7 @@
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B123" s="82" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C123" s="246">
         <f>Scenarios!C83</f>
@@ -4671,7 +4659,7 @@
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B124" s="245" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C124" s="158">
         <f>Scenarios!F83</f>
@@ -4680,12 +4668,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4699,6 +4681,12 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4782,7 +4770,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -4798,7 +4786,7 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="109">
         <v>1000000</v>
@@ -4832,7 +4820,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="194">
         <v>5344</v>
@@ -4858,7 +4846,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="194">
         <v>1084</v>
@@ -4882,7 +4870,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="195"/>
       <c r="D7" s="193"/>
@@ -4898,7 +4886,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="194"/>
       <c r="D8" s="185"/>
@@ -4914,7 +4902,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C9" s="194">
         <v>639</v>
@@ -4934,7 +4922,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C10" s="194"/>
       <c r="D10" s="185"/>
@@ -4950,7 +4938,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C11" s="194"/>
       <c r="D11" s="185"/>
@@ -4966,7 +4954,7 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="194">
         <v>43</v>
@@ -4990,7 +4978,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C13" s="194">
         <v>2340</v>
@@ -5014,7 +5002,7 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" s="194">
         <v>519</v>
@@ -5038,7 +5026,7 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="196">
         <v>4251</v>
@@ -5062,7 +5050,7 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="194">
         <v>-151</v>
@@ -5082,13 +5070,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="185">
         <v>160</v>
@@ -5112,7 +5100,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" s="185">
         <v>69</v>
@@ -5132,7 +5120,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C21" s="185">
         <v>910</v>
@@ -5177,13 +5165,13 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="187"/>
       <c r="D25" s="185">
@@ -5201,7 +5189,7 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="187"/>
       <c r="D26" s="185">
@@ -5219,7 +5207,7 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="186">
         <v>14028</v>
@@ -5239,7 +5227,7 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="186">
         <v>166316</v>
@@ -5259,7 +5247,7 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C29" s="185"/>
       <c r="D29" s="185"/>
@@ -5275,13 +5263,13 @@
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C31" s="9"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="185"/>
       <c r="D32" s="185"/>
@@ -5297,7 +5285,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -5313,7 +5301,7 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.35">
@@ -5367,7 +5355,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C37" s="187">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -5416,7 +5404,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C38" s="188">
         <f>IF(C36="","",C36+C37)</f>
@@ -5465,7 +5453,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" s="187">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -5514,7 +5502,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C40" s="189">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -5563,7 +5551,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C41" s="189">
         <f>IF(C$4="","",C39-C40)</f>
@@ -5612,7 +5600,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="187">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -5661,7 +5649,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="43" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C43" s="190">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -5710,7 +5698,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="43" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C44" s="191">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -5759,7 +5747,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C45" s="192">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -5808,7 +5796,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="187">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -5857,7 +5845,7 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="190">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -5906,7 +5894,7 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C48" s="187">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -5955,12 +5943,12 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C51" s="187">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -6009,7 +5997,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" s="187">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6058,12 +6046,12 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="179" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C55" s="192">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6112,7 +6100,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="40" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C56" s="192">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6161,7 +6149,7 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C57" s="192">
         <f>IF(C$4="","",C11)</f>
@@ -6210,7 +6198,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C58" s="192">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -6259,13 +6247,13 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C61" s="187">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
@@ -6314,7 +6302,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C62" s="187">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
@@ -6363,7 +6351,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C63" s="187">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
@@ -6412,7 +6400,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C64" s="75">
         <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C22)</f>
@@ -6461,7 +6449,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="93" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -6716,7 +6704,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
@@ -6732,7 +6720,7 @@
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B74" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C74" s="9"/>
     </row>
@@ -6787,7 +6775,7 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
@@ -6821,7 +6809,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C77" s="74">
         <f t="shared" si="39"/>
@@ -6855,7 +6843,7 @@
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B78" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C78" s="58">
         <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
@@ -6904,7 +6892,7 @@
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C79" s="58">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C28)</f>
@@ -6996,7 +6984,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C1" s="102">
         <v>45473</v>
@@ -7012,7 +7000,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7023,27 +7011,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="210" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="211" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="C3" s="210" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" s="211" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>197</v>
-      </c>
       <c r="G3" s="210" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="19">
         <v>8029</v>
@@ -7053,7 +7041,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G4" s="19">
         <v>45665</v>
@@ -7064,7 +7052,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -7074,7 +7062,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="19">
         <v>2014</v>
@@ -7095,7 +7083,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G6" s="19">
         <v>156</v>
@@ -7106,7 +7094,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" s="19">
         <v>5466</v>
@@ -7116,7 +7104,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -7127,7 +7115,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -7137,7 +7125,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -7148,7 +7136,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="19">
         <v>0</v>
@@ -7158,7 +7146,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -7193,7 +7181,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
@@ -7204,7 +7192,7 @@
         <v>13028</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
@@ -7222,27 +7210,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C14" s="210" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D14" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G14" s="210" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H14" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="19">
         <v>2757</v>
@@ -7251,7 +7239,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -7262,7 +7250,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -7271,7 +7259,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G16" s="19">
         <v>1373</v>
@@ -7282,7 +7270,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" s="19">
         <v>67668</v>
@@ -7291,7 +7279,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G17" s="19">
         <v>13024</v>
@@ -7302,7 +7290,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -7311,7 +7299,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G18" s="19">
         <v>23696</v>
@@ -7322,7 +7310,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="19">
         <v>1284</v>
@@ -7331,7 +7319,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -7351,7 +7339,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -7371,7 +7359,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -7406,7 +7394,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
@@ -7417,7 +7405,7 @@
         <v>41841</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
@@ -7430,19 +7418,19 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C26" s="210" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F26" s="212" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G26" s="213" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H26" s="214" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7453,7 +7441,7 @@
         <v>967</v>
       </c>
       <c r="F27" s="215" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
@@ -7472,7 +7460,7 @@
         <v>37</v>
       </c>
       <c r="F28" s="217" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G28" s="185">
         <v>519</v>
@@ -7487,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="218" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -7516,14 +7504,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
         <v>1004</v>
       </c>
       <c r="F31" s="218" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G31" s="219">
         <f>C31+C40</f>
@@ -7540,7 +7528,7 @@
         <v>8048</v>
       </c>
       <c r="F32" s="220" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G32" s="221">
         <f>G35+G40</f>
@@ -7566,24 +7554,24 @@
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="224" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G34" s="225" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H34" s="226" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C35" s="210" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F35" s="227" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G35" s="221">
         <f>C12+C24</f>
@@ -7602,7 +7590,7 @@
         <v>832</v>
       </c>
       <c r="F36" s="218" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G36" s="219">
         <f>C4+C15</f>
@@ -7618,7 +7606,7 @@
         <v>27</v>
       </c>
       <c r="F37" s="218" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G37" s="219">
         <f>C6</f>
@@ -7634,7 +7622,7 @@
         <v>1230</v>
       </c>
       <c r="F38" s="218" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G38" s="219">
         <f>C7+C17</f>
@@ -7650,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="218" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G39" s="219">
         <f>C7+C17+C19+C20</f>
@@ -7663,14 +7651,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
         <v>2089</v>
       </c>
       <c r="F40" s="227" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G40" s="221">
         <f>G12+G24</f>
@@ -7690,7 +7678,7 @@
         <v>2748</v>
       </c>
       <c r="F41" s="218" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G41" s="219">
         <f>C70</f>
@@ -7709,7 +7697,7 @@
         <v>4837</v>
       </c>
       <c r="F42" s="229" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G42" s="230">
         <f>C82</f>
@@ -7722,7 +7710,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="81" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -7733,21 +7721,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C45" s="268" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D45" s="210" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F45" s="297" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C46" s="192">
         <f>G29</f>
@@ -7779,20 +7767,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="162" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C49" s="269" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D49" s="225" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="292"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
@@ -7806,7 +7794,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C51" s="209"/>
       <c r="D51" s="94">
@@ -7820,19 +7808,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="162" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C53" s="269" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D53" s="225" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F53" s="292"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
@@ -7846,7 +7834,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
@@ -7863,19 +7851,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="162" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C57" s="269" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D57" s="225" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F57" s="292"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C58" s="101"/>
       <c r="D58" s="23">
@@ -7886,7 +7874,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C59" s="101"/>
       <c r="D59" s="94">
@@ -7900,19 +7888,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="162" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C61" s="269" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D61" s="225" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F61" s="292"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -7923,12 +7911,12 @@
         <v>3.1154705020769802E-3</v>
       </c>
       <c r="F62" s="292" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="81" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -7939,21 +7927,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C65" s="268" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D65" s="211" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F65" s="297" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="108" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -7964,12 +7952,12 @@
         <v>45106.841774682267</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="108" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -7979,7 +7967,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -7989,7 +7977,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -7999,7 +7987,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
@@ -8012,19 +8000,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="295" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C72" s="268" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D72" s="210" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F72" s="292"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C73" s="192">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
@@ -8037,7 +8025,7 @@
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="298" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C74" s="299">
         <f>-$C$66/C73</f>
@@ -8048,12 +8036,12 @@
         <v>92.682867505381196</v>
       </c>
       <c r="F74" s="292" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C75" s="304"/>
       <c r="D75" s="303">
@@ -8061,12 +8049,12 @@
         <v>-2572.1582253177344</v>
       </c>
       <c r="F75" s="292" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="300" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C76" s="301"/>
       <c r="D76" s="302">
@@ -8074,7 +8062,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="292" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8082,19 +8070,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C78" s="268" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D78" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F78" s="292"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8108,7 +8096,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8122,7 +8110,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8136,7 +8124,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
@@ -8150,7 +8138,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8161,15 +8149,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D85" s="278" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="275" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C86" s="192">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8186,7 +8174,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="275" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C87" s="192">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8203,7 +8191,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="276" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C88" s="192">
         <f>Valuation_Model!C9*Exchange_Rate</f>
@@ -8220,7 +8208,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C89" s="191">
         <f>SUM(C86:C88)</f>
@@ -8268,7 +8256,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -8321,12 +8309,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -8344,7 +8332,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
@@ -8415,7 +8403,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="198">
         <f>C25</f>
@@ -8470,7 +8458,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="188">
         <f>C4+C5</f>
@@ -8525,7 +8513,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="198">
         <f>C35</f>
@@ -8580,7 +8568,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C8" s="199">
         <f>C6+C7</f>
@@ -8637,7 +8625,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="198">
         <f>BS!$G$39*BS!D58</f>
@@ -8692,7 +8680,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10" s="198">
         <f>-C4*C77</f>
@@ -8747,7 +8735,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C11" s="200">
         <f>C62</f>
@@ -8804,7 +8792,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="198">
         <f>C49</f>
@@ -8859,7 +8847,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="71" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C13" s="188">
         <f>SUM(C8:C12)</f>
@@ -8914,7 +8902,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" s="198">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -8969,7 +8957,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C15" s="198">
         <f>-C4*C82</f>
@@ -9026,7 +9014,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C16" s="201">
         <f>SUM(C13:C15)</f>
@@ -9083,7 +9071,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" s="198">
         <f>-C4*C84</f>
@@ -9091,7 +9079,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="312" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="202"/>
@@ -9109,7 +9097,7 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C18" s="198">
         <f>-C4*C85</f>
@@ -9117,7 +9105,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="312" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="203"/>
@@ -9135,7 +9123,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C19" s="188">
         <f>SUM(C16:C18)</f>
@@ -9211,12 +9199,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9234,7 +9222,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="65" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
@@ -9255,7 +9243,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="204">
         <f>-C4*C28</f>
@@ -9312,7 +9300,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C24" s="198">
         <f>-C4*C29</f>
@@ -9369,7 +9357,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="188">
         <f>C23+C24</f>
@@ -9430,14 +9418,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E27" s="313"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:H28)</f>
@@ -9445,7 +9433,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="311" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9505,7 +9493,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="311" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9556,7 +9544,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
@@ -9615,21 +9603,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" s="313"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C33" s="205">
         <f>AVERAGE(G33:H33)</f>
         <v>-1106.5</v>
       </c>
       <c r="E33" s="311" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G33" s="198">
         <f>Data!C41</f>
@@ -9679,7 +9667,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" s="205">
         <f>AVERAGE(G34:J34)</f>
@@ -9687,7 +9675,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="311" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="187">
@@ -9738,7 +9726,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" s="188">
         <f>C33+C34</f>
@@ -9799,7 +9787,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E37" s="313"/>
     </row>
@@ -9922,7 +9910,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
@@ -9981,21 +9969,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E42" s="313"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C43" s="307">
         <v>0.24</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="310" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10049,12 +10037,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10072,14 +10060,14 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E46" s="313"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C47" s="198">
         <f>-BS!G31*Normalized_FCF!C53</f>
@@ -10134,7 +10122,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C48" s="198">
         <f>BS!$C$66*C52</f>
@@ -10189,7 +10177,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C49" s="188">
         <f>C47+C48</f>
@@ -10248,23 +10236,23 @@
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
       <c r="B51" s="73" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E51" s="313"/>
       <c r="G51" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C52" s="89">
         <v>0.03</v>
       </c>
       <c r="E52" s="310" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G52" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G48/BS!$C$66)</f>
@@ -10284,14 +10272,14 @@
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C53" s="84">
         <f>G53</f>
         <v>1.3902360168121564E-2</v>
       </c>
       <c r="E53" s="310" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G53" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10311,7 +10299,7 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C54" s="42">
         <f>-C8/C47</f>
@@ -10370,17 +10358,17 @@
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
       <c r="B56" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E56" s="313"/>
       <c r="G56" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="40" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C57" s="198">
         <f>BS!$C79*C65</f>
@@ -10435,7 +10423,7 @@
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C58" s="198">
         <f>BS!$C68*C66</f>
@@ -10490,7 +10478,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C59" s="198">
         <f>BS!$C81*C67</f>
@@ -10545,7 +10533,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C60" s="188">
         <f>SUM(C57:C59)</f>
@@ -10600,13 +10588,13 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C61" s="308">
         <v>0</v>
       </c>
       <c r="E61" s="311" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G61" s="198">
         <f>Data!C58</f>
@@ -10656,7 +10644,7 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C62" s="188">
         <f>C60+C61</f>
@@ -10715,17 +10703,17 @@
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
       <c r="B64" s="99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E64" s="313"/>
       <c r="G64" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="40" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C65" s="181">
         <f>G65</f>
@@ -10750,7 +10738,7 @@
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="108" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C66" s="181">
         <f>G66</f>
@@ -10775,7 +10763,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C67" s="181">
         <f>G67</f>
@@ -10800,7 +10788,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C68" s="72">
         <f>C60/BS!C70</f>
@@ -10830,12 +10818,12 @@
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A70" s="10"/>
       <c r="B70" s="54" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C70" s="54"/>
       <c r="D70" s="56"/>
       <c r="E70" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F70" s="56"/>
       <c r="G70" s="37"/>
@@ -10853,7 +10841,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="10"/>
       <c r="B71" s="73" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C71" s="63"/>
       <c r="D71" s="27"/>
@@ -10874,7 +10862,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C72" s="79">
         <f>ABS(C5/C$4)</f>
@@ -10931,7 +10919,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C73" s="80">
         <f>ABS(C6/C$4)</f>
@@ -10988,7 +10976,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C74" s="79">
         <f>ABS(C7/C$4)</f>
@@ -11045,7 +11033,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C75" s="80">
         <f>ABS(C8/C$4)</f>
@@ -11102,7 +11090,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C76" s="79">
         <f>ABS(C9/C$4)</f>
@@ -11159,7 +11147,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C77" s="90">
         <f>MAX(AVERAGE(G77:J77),C76)</f>
@@ -11167,7 +11155,7 @@
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="311" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
@@ -11218,7 +11206,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="31" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C78" s="80">
         <f>ABS(C11/C$4)</f>
@@ -11275,7 +11263,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C79" s="79">
         <f>ABS(C12/C$4)</f>
@@ -11332,7 +11320,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
       <c r="B80" s="71" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C80" s="80">
         <f>C13/C4</f>
@@ -11389,7 +11377,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C81" s="79">
         <f>ABS(C14/C$4)</f>
@@ -11504,7 +11492,7 @@
     <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="10"/>
       <c r="B83" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C83" s="80">
         <f>ABS(C16/C$4)</f>
@@ -11561,7 +11549,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10"/>
       <c r="B84" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C84" s="309">
         <v>0</v>
@@ -11587,7 +11575,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10"/>
       <c r="B85" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C85" s="309">
         <v>0</v>
@@ -11611,7 +11599,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
       <c r="B86" s="31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C86" s="80">
         <f>ABS(C19/C$4)</f>
@@ -11672,7 +11660,7 @@
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
       <c r="B88" s="65" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E88" s="313"/>
     </row>
@@ -11791,7 +11779,7 @@
     <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C91" s="23">
         <f>C89/(C19*$C$3/Common_Shares)</f>
@@ -11846,7 +11834,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
@@ -11905,7 +11893,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
       <c r="B94" s="162" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C94" s="63"/>
       <c r="D94" s="27"/>
@@ -11926,7 +11914,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
       <c r="B95" s="27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C95" s="79">
         <f>C4/G4-1</f>
@@ -11983,7 +11971,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
       <c r="B96" s="71" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C96" s="79">
         <f>C13/G13-1</f>
@@ -12043,12 +12031,12 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A98" s="3"/>
       <c r="B98" s="54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C98" s="54"/>
       <c r="D98" s="56"/>
       <c r="E98" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F98" s="56"/>
       <c r="G98" s="37"/>
@@ -12066,11 +12054,11 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="10"/>
       <c r="B99" s="65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E99" s="313"/>
       <c r="G99" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12133,7 +12121,7 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="10"/>
       <c r="B101" s="95" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C101" s="207">
         <f>BS!C4</f>
@@ -12190,7 +12178,7 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="95" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C102" s="207">
         <f>BS!C6+BS!C7</f>
@@ -12247,7 +12235,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
       <c r="B103" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C103" s="206">
         <f>BS!G30</f>
@@ -12304,7 +12292,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C104" s="206">
         <f>BS!G27</f>
@@ -12365,14 +12353,14 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
       <c r="B106" s="93" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C106" s="26"/>
       <c r="D106" s="26"/>
       <c r="E106" s="314"/>
       <c r="F106" s="26"/>
       <c r="G106" s="100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
@@ -12388,7 +12376,7 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
       <c r="B107" s="26" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C107" s="97">
         <f>C101/C$4</f>
@@ -12445,7 +12433,7 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
@@ -12502,7 +12490,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C109" s="97">
         <f>BS!$G$38/C$4</f>
@@ -12533,7 +12521,7 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
       <c r="B111" s="93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C111" s="55"/>
       <c r="D111" s="55"/>
@@ -12587,7 +12575,7 @@
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
       <c r="B112" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C112" s="23">
         <f>C80</f>
@@ -12641,7 +12629,7 @@
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B113" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C113" s="42">
         <f>C4/C100</f>
@@ -12695,7 +12683,7 @@
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C114" s="15">
         <f>C100/C104</f>
@@ -12752,7 +12740,7 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="10"/>
       <c r="B115" s="71" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C115" s="105">
         <f>C8/C104</f>
@@ -12828,12 +12816,12 @@
     <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A117" s="10"/>
       <c r="B117" s="54" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C117" s="54"/>
       <c r="D117" s="56"/>
       <c r="E117" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F117" s="56"/>
       <c r="G117" s="37"/>
@@ -12851,7 +12839,7 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="10"/>
       <c r="B118" s="183" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C118" s="184"/>
       <c r="D118" s="27"/>
@@ -12930,7 +12918,7 @@
     <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="10"/>
       <c r="B120" s="27" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13699,32 +13687,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="134" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="112" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="124"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="103" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
@@ -13735,7 +13723,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F4" s="138">
         <f>Thesis!C71</f>
@@ -13745,7 +13733,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="234" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C5" s="235">
         <f>Thesis!C67</f>
@@ -13756,7 +13744,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="153" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C6" s="239">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -13766,15 +13754,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="330" t="s">
-        <v>268</v>
-      </c>
-      <c r="F6" s="330"/>
+      <c r="E6" s="335" t="s">
+        <v>267</v>
+      </c>
+      <c r="F6" s="335"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C7" s="233">
         <f>BS!G31</f>
@@ -13784,13 +13772,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="330"/>
-      <c r="F7" s="330"/>
+      <c r="E7" s="335"/>
+      <c r="F7" s="335"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C8" s="208">
         <f>BS!D66</f>
@@ -13800,13 +13788,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="330"/>
-      <c r="F8" s="330"/>
+      <c r="E8" s="335"/>
+      <c r="F8" s="335"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="234" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C9" s="236">
         <f>BS!H42</f>
@@ -13816,13 +13804,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="330"/>
-      <c r="F9" s="330"/>
+      <c r="E9" s="335"/>
+      <c r="F9" s="335"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C10" s="239">
         <f>C6-C7+C8+C9</f>
@@ -13836,7 +13824,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="237" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C11" s="238">
         <f>Exchange_Rate</f>
@@ -13850,7 +13838,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
@@ -13867,7 +13855,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B14" s="36" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -13877,13 +13865,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B15" s="123" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="156" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C16" s="166">
         <f>Scenarios!C65</f>
@@ -13893,7 +13881,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C17" s="167">
         <f>Scenarios!C64</f>
@@ -13903,7 +13891,7 @@
     </row>
     <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="157" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
@@ -13920,19 +13908,19 @@
     </row>
     <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="132" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="132" t="s">
         <v>119</v>
       </c>
-      <c r="C20" s="132" t="s">
+      <c r="D20" s="132" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="132" t="s">
         <v>120</v>
       </c>
-      <c r="D20" s="132" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20" s="132" t="s">
+      <c r="F20" s="133" t="s">
         <v>121</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>122</v>
       </c>
       <c r="H20" s="124"/>
     </row>
@@ -14598,7 +14586,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B51" s="130" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -14621,7 +14609,7 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C52" s="118"/>
       <c r="E52" s="131" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
@@ -14635,7 +14623,7 @@
     </row>
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B54" s="123" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C54" s="140"/>
       <c r="D54" s="140"/>
@@ -14806,7 +14794,7 @@
     </row>
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B63" s="123" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C63" s="118"/>
       <c r="D63" s="118"/>
@@ -15025,19 +15013,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="176" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C73" s="176" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D73" s="176" t="s">
+        <v>123</v>
+      </c>
+      <c r="E73" s="177" t="s">
         <v>124</v>
       </c>
-      <c r="E73" s="177" t="s">
-        <v>125</v>
-      </c>
       <c r="F73" s="177" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -15162,20 +15150,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="160" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C80" s="160" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81" s="160" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82" s="160" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.35">
@@ -15227,20 +15215,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="285" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="I2" s="286"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="164" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H3" s="284">
         <v>0</v>
@@ -15252,14 +15240,14 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="156" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C4" s="124">
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="160" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F4" s="160"/>
       <c r="H4" s="284">
@@ -15281,14 +15269,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="164" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="284">
@@ -15301,7 +15289,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15311,11 +15299,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="332" t="str">
+      <c r="E7" s="337" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="332"/>
+      <c r="F7" s="337"/>
       <c r="H7" s="284">
         <v>4</v>
       </c>
@@ -15326,7 +15314,7 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
@@ -15336,8 +15324,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="332"/>
-      <c r="F8" s="332"/>
+      <c r="E8" s="337"/>
+      <c r="F8" s="337"/>
       <c r="H8" s="284">
         <v>5</v>
       </c>
@@ -15348,7 +15336,7 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="103" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" s="208">
         <f>Normalized_FCF!C19</f>
@@ -15358,8 +15346,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="332"/>
-      <c r="F9" s="332"/>
+      <c r="E9" s="337"/>
+      <c r="F9" s="337"/>
       <c r="H9" s="284">
         <v>6</v>
       </c>
@@ -15369,8 +15357,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="332"/>
-      <c r="F10" s="332"/>
+      <c r="E10" s="337"/>
+      <c r="F10" s="337"/>
       <c r="H10" s="284">
         <v>7</v>
       </c>
@@ -15381,10 +15369,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="164" t="s">
-        <v>309</v>
-      </c>
-      <c r="E11" s="332"/>
-      <c r="F11" s="332"/>
+        <v>307</v>
+      </c>
+      <c r="E11" s="337"/>
+      <c r="F11" s="337"/>
       <c r="H11" s="284">
         <v>8</v>
       </c>
@@ -15395,15 +15383,15 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="163">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.28945840615733698</v>
       </c>
       <c r="D12" s="163"/>
-      <c r="E12" s="332"/>
-      <c r="F12" s="332"/>
+      <c r="E12" s="337"/>
+      <c r="F12" s="337"/>
       <c r="H12" s="284">
         <v>9</v>
       </c>
@@ -15414,14 +15402,14 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="152" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="163">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.42686307479092267</v>
       </c>
-      <c r="E13" s="332"/>
-      <c r="F13" s="332"/>
+      <c r="E13" s="337"/>
+      <c r="F13" s="337"/>
       <c r="H13" s="284">
         <v>10</v>
       </c>
@@ -15432,18 +15420,18 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="163">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.22869925060693375</v>
       </c>
-      <c r="E14" s="332"/>
-      <c r="F14" s="332"/>
+      <c r="E14" s="337"/>
+      <c r="F14" s="337"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -15452,38 +15440,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="112" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E17" s="164" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="156" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="332" t="s">
-        <v>385</v>
-      </c>
-      <c r="F18" s="337"/>
+      <c r="E18" s="337" t="s">
+        <v>383</v>
+      </c>
+      <c r="F18" s="338"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="337"/>
-      <c r="F19" s="337"/>
+      <c r="E19" s="338"/>
+      <c r="F19" s="338"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="164" t="s">
-        <v>347</v>
-      </c>
-      <c r="E20" s="337"/>
-      <c r="F20" s="337"/>
+        <v>345</v>
+      </c>
+      <c r="E20" s="338"/>
+      <c r="F20" s="338"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
@@ -15493,12 +15481,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="337"/>
-      <c r="F21" s="337"/>
+      <c r="E21" s="338"/>
+      <c r="F21" s="338"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C22" s="165">
         <f>Valuation_Model!C12</f>
@@ -15508,44 +15496,44 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="337"/>
-      <c r="F22" s="337"/>
+      <c r="E22" s="338"/>
+      <c r="F22" s="338"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="164" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E24" s="164" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F24" s="164"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C25" s="171">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D25" s="168"/>
-      <c r="E25" s="331"/>
-      <c r="F25" s="331"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C26" s="169">
         <v>0</v>
       </c>
       <c r="D26" s="169"/>
-      <c r="E26" s="331"/>
-      <c r="F26" s="331"/>
+      <c r="E26" s="336"/>
+      <c r="F26" s="336"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C27" s="165">
         <f>Valuation_Model!E76</f>
@@ -15555,55 +15543,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="331"/>
-      <c r="F27" s="331"/>
+      <c r="E27" s="336"/>
+      <c r="F27" s="336"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C28" s="170">
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="170"/>
-      <c r="E28" s="331"/>
-      <c r="F28" s="331"/>
+      <c r="E28" s="336"/>
+      <c r="F28" s="336"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="164" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E30" s="164" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F30" s="164"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C31" s="171">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D31" s="168"/>
-      <c r="E31" s="331"/>
-      <c r="F31" s="331"/>
+      <c r="E31" s="336"/>
+      <c r="F31" s="336"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C32" s="169">
         <v>-0.05</v>
       </c>
       <c r="D32" s="169"/>
-      <c r="E32" s="331"/>
-      <c r="F32" s="331"/>
+      <c r="E32" s="336"/>
+      <c r="F32" s="336"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C33" s="165">
         <f>Valuation_Model!E77</f>
@@ -15613,55 +15601,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="331"/>
-      <c r="F33" s="331"/>
+      <c r="E33" s="336"/>
+      <c r="F33" s="336"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C34" s="170">
         <v>0.2</v>
       </c>
       <c r="D34" s="170"/>
-      <c r="E34" s="331"/>
-      <c r="F34" s="331"/>
+      <c r="E34" s="336"/>
+      <c r="F34" s="336"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="164" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E36" s="164" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F36" s="164"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C37" s="171">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D37" s="168"/>
-      <c r="E37" s="331"/>
-      <c r="F37" s="331"/>
+      <c r="E37" s="336"/>
+      <c r="F37" s="336"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C38" s="169">
         <v>0.02</v>
       </c>
       <c r="D38" s="169"/>
-      <c r="E38" s="331"/>
-      <c r="F38" s="331"/>
+      <c r="E38" s="336"/>
+      <c r="F38" s="336"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C39" s="165">
         <f>Valuation_Model!E75</f>
@@ -15671,24 +15659,24 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="331"/>
-      <c r="F39" s="331"/>
+      <c r="E39" s="336"/>
+      <c r="F39" s="336"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C40" s="172">
         <f>1-C28-C34</f>
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="170"/>
-      <c r="E40" s="331"/>
-      <c r="F40" s="331"/>
+      <c r="E40" s="336"/>
+      <c r="F40" s="336"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C42" s="159">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -15701,7 +15689,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B44" s="36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -15710,12 +15698,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B45" s="112" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="156" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C46" s="154">
         <v>15</v>
@@ -15730,39 +15718,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B48" s="164" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E48" s="164" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F48" s="164"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C49" s="171">
         <f>C46</f>
         <v>15</v>
       </c>
       <c r="D49" s="168"/>
-      <c r="E49" s="331"/>
-      <c r="F49" s="331"/>
+      <c r="E49" s="336"/>
+      <c r="F49" s="336"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C50" s="169">
         <v>-0.3</v>
       </c>
       <c r="D50" s="169"/>
-      <c r="E50" s="331"/>
-      <c r="F50" s="331"/>
+      <c r="E50" s="336"/>
+      <c r="F50" s="336"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C51" s="165">
         <f>Valuation_Model!E78</f>
@@ -15772,55 +15760,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="331"/>
-      <c r="F51" s="331"/>
+      <c r="E51" s="336"/>
+      <c r="F51" s="336"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C52" s="170">
         <v>0.05</v>
       </c>
       <c r="D52" s="170"/>
-      <c r="E52" s="331"/>
-      <c r="F52" s="331"/>
+      <c r="E52" s="336"/>
+      <c r="F52" s="336"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="164" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E54" s="164" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F54" s="164"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C55" s="171">
         <f>C46</f>
         <v>15</v>
       </c>
       <c r="D55" s="168"/>
-      <c r="E55" s="331"/>
-      <c r="F55" s="331"/>
+      <c r="E55" s="336"/>
+      <c r="F55" s="336"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C56" s="169">
         <v>0.05</v>
       </c>
       <c r="D56" s="169"/>
-      <c r="E56" s="331"/>
-      <c r="F56" s="331"/>
+      <c r="E56" s="336"/>
+      <c r="F56" s="336"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C57" s="165">
         <f>Valuation_Model!E74</f>
@@ -15830,23 +15818,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="331"/>
-      <c r="F57" s="331"/>
+      <c r="E57" s="336"/>
+      <c r="F57" s="336"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C58" s="170">
         <v>0.05</v>
       </c>
       <c r="D58" s="170"/>
-      <c r="E58" s="331"/>
-      <c r="F58" s="331"/>
+      <c r="E58" s="336"/>
+      <c r="F58" s="336"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C60" s="159">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -15857,7 +15845,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F60" s="324">
         <v>3</v>
@@ -15865,7 +15853,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -15874,39 +15862,39 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E63" s="291" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="156" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C64" s="171">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="290" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C65" s="155">
         <v>-8.7951517171891112E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="290" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="103" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C66" s="165">
         <f>Valuation_Model!C18</f>
@@ -15917,20 +15905,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="290" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E68" s="291" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C69" s="281" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -15940,19 +15928,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C70" s="281" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="290" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C71" s="281" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -15962,7 +15950,7 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C72" s="280" t="str">
         <f>IF(E72&gt;50%,"Y","N")</f>
@@ -15975,7 +15963,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B74" s="36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -15984,32 +15972,32 @@
     </row>
     <row r="75" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B75" s="112" t="s">
-        <v>137</v>
-      </c>
-      <c r="E75" s="333" t="s">
-        <v>379</v>
+        <v>136</v>
+      </c>
+      <c r="E75" s="325" t="s">
+        <v>377</v>
       </c>
       <c r="F75" s="323"/>
     </row>
     <row r="76" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B76" s="283" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C76" s="282">
         <f>F60</f>
         <v>3</v>
       </c>
       <c r="D76" s="138"/>
-      <c r="E76" s="334" t="s">
-        <v>380</v>
+      <c r="E76" s="326" t="s">
+        <v>378</v>
       </c>
       <c r="F76" s="323" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B77" s="103" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C77" s="178">
         <f>Normalized_FCF!C89</f>
@@ -16019,29 +16007,29 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E77" s="335" t="s">
+      <c r="E77" s="327" t="s">
+        <v>378</v>
+      </c>
+      <c r="F77" s="323" t="s">
         <v>380</v>
       </c>
-      <c r="F77" s="323" t="s">
-        <v>382</v>
-      </c>
     </row>
     <row r="78" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E78" s="336" t="s">
-        <v>380</v>
+      <c r="E78" s="328" t="s">
+        <v>378</v>
       </c>
       <c r="F78" s="323" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C80" s="172">
         <f>Thesis!C117</f>
@@ -16050,7 +16038,7 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -16062,7 +16050,7 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
@@ -16072,7 +16060,7 @@
     </row>
     <row r="83" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
@@ -16083,7 +16071,7 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="150" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F83" s="270">
         <f>(C83/C60-1)</f>
@@ -16095,12 +16083,12 @@
     </row>
     <row r="85" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
@@ -16113,7 +16101,7 @@
     </row>
     <row r="87" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49B8AA9-874A-4663-95BF-4180CC8D4B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1FA9C1-CCCD-4CBC-909F-BB02DA26D622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3326,20 +3326,20 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="5"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3753,13 +3753,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="330" t="s">
+      <c r="B12" s="329" t="s">
         <v>298</v>
       </c>
-      <c r="C12" s="330"/>
-      <c r="D12" s="330"/>
-      <c r="E12" s="330"/>
-      <c r="F12" s="330"/>
+      <c r="C12" s="329"/>
+      <c r="D12" s="329"/>
+      <c r="E12" s="329"/>
+      <c r="F12" s="329"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="C20" s="259">
         <f>C123</f>
-        <v>7.4179368510878518</v>
+        <v>7.3815066170863481</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>352</v>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17349059186547722</v>
+        <v>0.17143601630956429</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3862,22 +3862,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="330" t="s">
+      <c r="B25" s="329" t="s">
         <v>243</v>
       </c>
-      <c r="C25" s="330"/>
-      <c r="D25" s="330"/>
-      <c r="E25" s="330"/>
-      <c r="F25" s="330"/>
+      <c r="C25" s="329"/>
+      <c r="D25" s="329"/>
+      <c r="E25" s="329"/>
+      <c r="F25" s="329"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="331" t="s">
+      <c r="B26" s="333" t="s">
         <v>264</v>
       </c>
-      <c r="C26" s="331"/>
-      <c r="D26" s="331"/>
-      <c r="E26" s="331"/>
-      <c r="F26" s="331"/>
+      <c r="C26" s="333"/>
+      <c r="D26" s="333"/>
+      <c r="E26" s="333"/>
+      <c r="F26" s="333"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3889,13 +3889,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="329" t="s">
+      <c r="B29" s="331" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="329"/>
-      <c r="D29" s="329"/>
-      <c r="E29" s="329"/>
-      <c r="F29" s="329"/>
+      <c r="C29" s="331"/>
+      <c r="D29" s="331"/>
+      <c r="E29" s="331"/>
+      <c r="F29" s="331"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3915,13 +3915,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="329" t="s">
+      <c r="B32" s="331" t="s">
         <v>247</v>
       </c>
-      <c r="C32" s="329"/>
-      <c r="D32" s="329"/>
-      <c r="E32" s="329"/>
-      <c r="F32" s="329"/>
+      <c r="C32" s="331"/>
+      <c r="D32" s="331"/>
+      <c r="E32" s="331"/>
+      <c r="F32" s="331"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3950,13 +3950,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="329" t="s">
+      <c r="B36" s="331" t="s">
         <v>250</v>
       </c>
-      <c r="C36" s="329"/>
-      <c r="D36" s="329"/>
-      <c r="E36" s="329"/>
-      <c r="F36" s="329"/>
+      <c r="C36" s="331"/>
+      <c r="D36" s="331"/>
+      <c r="E36" s="331"/>
+      <c r="F36" s="331"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3972,13 +3972,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="329" t="s">
+      <c r="B39" s="331" t="s">
         <v>254</v>
       </c>
-      <c r="C39" s="329"/>
-      <c r="D39" s="329"/>
-      <c r="E39" s="329"/>
-      <c r="F39" s="329"/>
+      <c r="C39" s="331"/>
+      <c r="D39" s="331"/>
+      <c r="E39" s="331"/>
+      <c r="F39" s="331"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4012,13 +4012,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="329" t="s">
+      <c r="B45" s="331" t="s">
         <v>255</v>
       </c>
-      <c r="C45" s="329"/>
-      <c r="D45" s="329"/>
-      <c r="E45" s="329"/>
-      <c r="F45" s="329"/>
+      <c r="C45" s="331"/>
+      <c r="D45" s="331"/>
+      <c r="E45" s="331"/>
+      <c r="F45" s="331"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4034,13 +4034,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="329" t="s">
+      <c r="B48" s="331" t="s">
         <v>258</v>
       </c>
-      <c r="C48" s="333"/>
-      <c r="D48" s="333"/>
-      <c r="E48" s="333"/>
-      <c r="F48" s="333"/>
+      <c r="C48" s="332"/>
+      <c r="D48" s="332"/>
+      <c r="E48" s="332"/>
+      <c r="F48" s="332"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4069,13 +4069,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="330" t="s">
+      <c r="B52" s="329" t="s">
         <v>280</v>
       </c>
-      <c r="C52" s="330"/>
-      <c r="D52" s="330"/>
-      <c r="E52" s="330"/>
-      <c r="F52" s="330"/>
+      <c r="C52" s="329"/>
+      <c r="D52" s="329"/>
+      <c r="E52" s="329"/>
+      <c r="F52" s="329"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4136,22 +4136,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="329" t="s">
+      <c r="B60" s="331" t="s">
         <v>315</v>
       </c>
-      <c r="C60" s="329"/>
-      <c r="D60" s="329"/>
-      <c r="E60" s="329"/>
-      <c r="F60" s="329"/>
+      <c r="C60" s="331"/>
+      <c r="D60" s="331"/>
+      <c r="E60" s="331"/>
+      <c r="F60" s="331"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="331" t="s">
+      <c r="B61" s="333" t="s">
         <v>271</v>
       </c>
-      <c r="C61" s="331"/>
-      <c r="D61" s="331"/>
-      <c r="E61" s="331"/>
-      <c r="F61" s="331"/>
+      <c r="C61" s="333"/>
+      <c r="D61" s="333"/>
+      <c r="E61" s="333"/>
+      <c r="F61" s="333"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4203,22 +4203,22 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="330" t="s">
+      <c r="B69" s="329" t="s">
         <v>323</v>
       </c>
-      <c r="C69" s="330"/>
-      <c r="D69" s="330"/>
-      <c r="E69" s="330"/>
-      <c r="F69" s="330"/>
+      <c r="C69" s="329"/>
+      <c r="D69" s="329"/>
+      <c r="E69" s="329"/>
+      <c r="F69" s="329"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="330" t="s">
+      <c r="B70" s="329" t="s">
         <v>270</v>
       </c>
-      <c r="C70" s="330"/>
-      <c r="D70" s="330"/>
-      <c r="E70" s="330"/>
-      <c r="F70" s="330"/>
+      <c r="C70" s="329"/>
+      <c r="D70" s="329"/>
+      <c r="E70" s="329"/>
+      <c r="F70" s="329"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4255,13 +4255,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="330" t="s">
+      <c r="B77" s="329" t="s">
         <v>273</v>
       </c>
-      <c r="C77" s="330"/>
-      <c r="D77" s="330"/>
-      <c r="E77" s="330"/>
-      <c r="F77" s="330"/>
+      <c r="C77" s="329"/>
+      <c r="D77" s="329"/>
+      <c r="E77" s="329"/>
+      <c r="F77" s="329"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="C86" s="192">
         <f>Valuation_Model!C8</f>
-        <v>45106.841774682267</v>
+        <v>44592.410129618722</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="C87" s="255">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>5.5197631546164541</v>
+        <v>5.4568117102618574</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4375,13 +4375,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="330" t="s">
+      <c r="B93" s="329" t="s">
         <v>279</v>
       </c>
-      <c r="C93" s="330"/>
-      <c r="D93" s="330"/>
-      <c r="E93" s="330"/>
-      <c r="F93" s="330"/>
+      <c r="C93" s="329"/>
+      <c r="D93" s="329"/>
+      <c r="E93" s="329"/>
+      <c r="F93" s="329"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="C95" s="255">
         <f>Valuation_Model!C12</f>
-        <v>10.838654713529085</v>
+        <v>10.775703269174489</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4407,13 +4407,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="329" t="s">
+      <c r="B99" s="331" t="s">
         <v>384</v>
       </c>
-      <c r="C99" s="329"/>
-      <c r="D99" s="329"/>
-      <c r="E99" s="329"/>
-      <c r="F99" s="329"/>
+      <c r="C99" s="331"/>
+      <c r="D99" s="331"/>
+      <c r="E99" s="331"/>
+      <c r="F99" s="331"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="E102" s="265" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>12.27 HKD</v>
+        <v>12.21 HKD</v>
       </c>
       <c r="F102" s="266">
         <f>Valuation_Model!F74</f>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="E103" s="252" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>11.16 HKD</v>
+        <v>11.09 HKD</v>
       </c>
       <c r="F103" s="253">
         <f>Valuation_Model!F75</f>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="E104" s="252" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>10.84 HKD</v>
+        <v>10.78 HKD</v>
       </c>
       <c r="F104" s="253">
         <f>Valuation_Model!F76</f>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="E105" s="252" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>10.16 HKD</v>
+        <v>10.1 HKD</v>
       </c>
       <c r="F105" s="253">
         <f>Valuation_Model!F77</f>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="E106" s="252" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>7.77 HKD</v>
+        <v>7.71 HKD</v>
       </c>
       <c r="F106" s="253">
         <f>Valuation_Model!F78</f>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C108" s="248">
         <f>Scenarios!C60</f>
-        <v>10.706994878679808</v>
+        <v>10.64404343432521</v>
       </c>
       <c r="D108" s="243" t="str">
         <f>Market_currency</f>
@@ -4575,13 +4575,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="332" t="s">
+      <c r="B114" s="330" t="s">
         <v>287</v>
       </c>
-      <c r="C114" s="332"/>
-      <c r="D114" s="332"/>
-      <c r="E114" s="332"/>
-      <c r="F114" s="332"/>
+      <c r="C114" s="330"/>
+      <c r="D114" s="330"/>
+      <c r="E114" s="330"/>
+      <c r="F114" s="330"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="C122" s="247">
         <f>Scenarios!C82</f>
-        <v>6.1961775918285928</v>
+        <v>6.1597473578270892</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="C123" s="246">
         <f>Scenarios!C83</f>
-        <v>7.4179368510878518</v>
+        <v>7.3815066170863481</v>
       </c>
       <c r="D123" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4663,11 +4663,17 @@
       </c>
       <c r="C124" s="158">
         <f>Scenarios!F83</f>
-        <v>-0.30718778376753109</v>
+        <v>-0.30651291845707263</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4681,12 +4687,6 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="D66" s="192">
         <f>C66+D75</f>
-        <v>45106.841774682267</v>
+        <v>44592.410129618722</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>238</v>
@@ -8046,7 +8046,7 @@
       <c r="C75" s="304"/>
       <c r="D75" s="303">
         <f>MIN(D73*D76,-G5)</f>
-        <v>-2572.1582253177344</v>
+        <v>-3086.5898703812809</v>
       </c>
       <c r="F75" s="292" t="s">
         <v>371</v>
@@ -8058,8 +8058,8 @@
       </c>
       <c r="C76" s="301"/>
       <c r="D76" s="302">
-        <f>IF(D74&lt;=3,1,IF(D74&gt;10,5,2))</f>
-        <v>5</v>
+        <f>IF(D74&lt;=3,1,IF(D74&gt;12,6,2))</f>
+        <v>6</v>
       </c>
       <c r="F76" s="292" t="s">
         <v>376</v>
@@ -8178,11 +8178,11 @@
       </c>
       <c r="C87" s="192">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>45106.841774682267</v>
+        <v>44592.410129618722</v>
       </c>
       <c r="D87" s="255">
         <f>C87*$H$1/Common_Shares</f>
-        <v>5.5197631546164541</v>
+        <v>5.4568117102618574</v>
       </c>
       <c r="E87" s="277" t="str">
         <f>Market_currency</f>
@@ -8212,11 +8212,11 @@
       </c>
       <c r="C89" s="191">
         <f>SUM(C86:C88)</f>
-        <v>49828.241774682268</v>
+        <v>49313.810129618723</v>
       </c>
       <c r="D89" s="279">
         <f>SUM(D86:D88)</f>
-        <v>6.0975249471264705</v>
+        <v>6.0345735027718739</v>
       </c>
       <c r="E89" s="277" t="str">
         <f>Market_currency</f>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="C8" s="208">
         <f>BS!D66</f>
-        <v>45106.841774682267</v>
+        <v>44592.410129618722</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="C10" s="239">
         <f>C6-C7+C8+C9</f>
-        <v>88572.184986720153</v>
+        <v>88057.753341656615</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -13842,7 +13842,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>10.838654713529085</v>
+        <v>10.775703269174489</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -13895,7 +13895,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>10.708213341286156</v>
+        <v>10.645261896931558</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14831,23 +14831,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>10.838654713529085</v>
+        <v>10.775703269174489</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>10.838654713529085</v>
+        <v>10.775703269174489</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>10.838654713529085</v>
+        <v>10.775703269174489</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>10.838654713529085</v>
+        <v>10.775703269174489</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>10.838654713529085</v>
+        <v>10.775703269174489</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -14858,23 +14858,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>8.9367265403465179</v>
+        <v>8.8737750959919204</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>10.464191416631589</v>
+        <v>10.401239972276992</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>10.838654713529085</v>
+        <v>10.775703269174487</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>10.996571841845507</v>
+        <v>10.933620397490911</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>11.242812160570372</v>
+        <v>11.179860716215776</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -14885,23 +14885,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>8.2561544066991601</v>
+        <v>8.1932029623445626</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>10.163266547548384</v>
+        <v>10.100315103193786</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>10.838654713529081</v>
+        <v>10.775703269174485</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>11.156364901945436</v>
+        <v>11.09341345759084</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>11.694349144231008</v>
+        <v>11.631397699876411</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -14912,23 +14912,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>7.7735358606357119</v>
+        <v>7.7105844162811144</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>9.861261440865567</v>
+        <v>9.7983099965109712</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>10.838654713529081</v>
+        <v>10.775703269174485</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>11.345457459822585</v>
+        <v>11.282506015467989</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>12.272278419093899</v>
+        <v>12.209326974739303</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -14939,23 +14939,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>7.4554655168012136</v>
+        <v>7.3925140724466178</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>9.6114574364644501</v>
+        <v>9.5485059921098543</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>10.838654713529081</v>
+        <v>10.775703269174485</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>11.529519480109208</v>
+        <v>11.466568035754612</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>12.883852077820981</v>
+        <v>12.820900633466385</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -14966,23 +14966,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>7.2482608345624957</v>
+        <v>7.185309390207899</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>9.4221858163511669</v>
+        <v>9.3592343719965729</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>10.838654713529079</v>
+        <v>10.775703269174485</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>11.693037626525086</v>
+        <v>11.630086182170489</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>13.477060144941481</v>
+        <v>13.414108700586887</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14992,23 +14992,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>7.1135394903821911</v>
+        <v>7.0505880460275954</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>9.2856359928419838</v>
+        <v>9.2226845484873881</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>10.838654713529079</v>
+        <v>10.775703269174485</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>11.83080797822601</v>
+        <v>11.767856533871415</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>14.024959466862017</v>
+        <v>13.962008022507421</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>12.272278419093899</v>
+        <v>12.209326974739303</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>11.156364901945436</v>
+        <v>11.09341345759084</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>10.838654713529081</v>
+        <v>10.775703269174485</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15111,7 +15111,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>10.163266547548384</v>
+        <v>10.100315103193786</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.7735358606357119</v>
+        <v>7.7105844162811144</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="I6" s="272">
         <f t="shared" si="0"/>
-        <v>11.286994878679808</v>
+        <v>11.22404343432521</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="C22" s="165">
         <f>Valuation_Model!C12</f>
-        <v>10.838654713529085</v>
+        <v>10.775703269174489</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="C27" s="165">
         <f>Valuation_Model!E76</f>
-        <v>10.838654713529081</v>
+        <v>10.775703269174485</v>
       </c>
       <c r="D27" s="165" t="str">
         <f>Market_currency</f>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="C33" s="165">
         <f>Valuation_Model!E77</f>
-        <v>10.163266547548384</v>
+        <v>10.100315103193786</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="C39" s="165">
         <f>Valuation_Model!E75</f>
-        <v>11.156364901945436</v>
+        <v>11.09341345759084</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="C42" s="159">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>10.78300462743703</v>
+        <v>10.720053183082435</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="C51" s="165">
         <f>Valuation_Model!E78</f>
-        <v>7.7735358606357119</v>
+        <v>7.7105844162811144</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="C57" s="165">
         <f>Valuation_Model!E74</f>
-        <v>12.272278419093899</v>
+        <v>12.209326974739303</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -15838,7 +15838,7 @@
       </c>
       <c r="C60" s="159">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>10.706994878679808</v>
+        <v>10.64404343432521</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -15898,7 +15898,7 @@
       </c>
       <c r="C66" s="165">
         <f>Valuation_Model!C18</f>
-        <v>10.708213341286156</v>
+        <v>10.645261896931558</v>
       </c>
       <c r="D66" s="165" t="str">
         <f>Market_currency</f>
@@ -16054,7 +16054,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>6.1961775918285928</v>
+        <v>6.1597473578270892</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16064,7 +16064,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>7.4179368510878518</v>
+        <v>7.3815066170863481</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16075,7 +16075,7 @@
       </c>
       <c r="F83" s="270">
         <f>(C83/C60-1)</f>
-        <v>-0.30718778376753109</v>
+        <v>-0.30651291845707263</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.35">
@@ -16105,7 +16105,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17349059186547722</v>
+        <v>0.17143601630956429</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.35">

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1FA9C1-CCCD-4CBC-909F-BB02DA26D622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B927457-BE0A-4A0B-B7AA-F3B7FD9C5F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -1992,7 +1992,7 @@
     <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="192" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="58" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2416,13 +2416,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF00B050"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <i/>
       <u/>
       <sz val="10"/>
@@ -2638,7 +2632,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="339">
+  <cellXfs count="342">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3240,9 +3234,6 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3310,36 +3301,20 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3355,6 +3330,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3651,10 +3648,10 @@
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="293" t="s">
+      <c r="E1" s="292" t="s">
         <v>362</v>
       </c>
-      <c r="F1" s="294" t="s">
+      <c r="F1" s="293" t="s">
         <v>364</v>
       </c>
     </row>
@@ -3753,13 +3750,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="329" t="s">
+      <c r="B12" s="323" t="s">
         <v>298</v>
       </c>
-      <c r="C12" s="329"/>
-      <c r="D12" s="329"/>
-      <c r="E12" s="329"/>
-      <c r="F12" s="329"/>
+      <c r="C12" s="323"/>
+      <c r="D12" s="323"/>
+      <c r="E12" s="323"/>
+      <c r="F12" s="323"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3831,8 +3828,7 @@
       <c r="D20" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="E20" s="289">
-        <f>Scenarios!C76</f>
+      <c r="E20" s="333">
         <v>3</v>
       </c>
     </row>
@@ -3862,22 +3858,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="329" t="s">
+      <c r="B25" s="323" t="s">
         <v>243</v>
       </c>
-      <c r="C25" s="329"/>
-      <c r="D25" s="329"/>
-      <c r="E25" s="329"/>
-      <c r="F25" s="329"/>
+      <c r="C25" s="323"/>
+      <c r="D25" s="323"/>
+      <c r="E25" s="323"/>
+      <c r="F25" s="323"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="333" t="s">
+      <c r="B26" s="324" t="s">
         <v>264</v>
       </c>
-      <c r="C26" s="333"/>
-      <c r="D26" s="333"/>
-      <c r="E26" s="333"/>
-      <c r="F26" s="333"/>
+      <c r="C26" s="324"/>
+      <c r="D26" s="324"/>
+      <c r="E26" s="324"/>
+      <c r="F26" s="324"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3889,13 +3885,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="331" t="s">
+      <c r="B29" s="322" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="331"/>
-      <c r="D29" s="331"/>
-      <c r="E29" s="331"/>
-      <c r="F29" s="331"/>
+      <c r="C29" s="322"/>
+      <c r="D29" s="322"/>
+      <c r="E29" s="322"/>
+      <c r="F29" s="322"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3915,13 +3911,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="331" t="s">
+      <c r="B32" s="322" t="s">
         <v>247</v>
       </c>
-      <c r="C32" s="331"/>
-      <c r="D32" s="331"/>
-      <c r="E32" s="331"/>
-      <c r="F32" s="331"/>
+      <c r="C32" s="322"/>
+      <c r="D32" s="322"/>
+      <c r="E32" s="322"/>
+      <c r="F32" s="322"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3950,13 +3946,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="331" t="s">
+      <c r="B36" s="322" t="s">
         <v>250</v>
       </c>
-      <c r="C36" s="331"/>
-      <c r="D36" s="331"/>
-      <c r="E36" s="331"/>
-      <c r="F36" s="331"/>
+      <c r="C36" s="322"/>
+      <c r="D36" s="322"/>
+      <c r="E36" s="322"/>
+      <c r="F36" s="322"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3972,13 +3968,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="331" t="s">
+      <c r="B39" s="322" t="s">
         <v>254</v>
       </c>
-      <c r="C39" s="331"/>
-      <c r="D39" s="331"/>
-      <c r="E39" s="331"/>
-      <c r="F39" s="331"/>
+      <c r="C39" s="322"/>
+      <c r="D39" s="322"/>
+      <c r="E39" s="322"/>
+      <c r="F39" s="322"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4012,13 +4008,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="331" t="s">
+      <c r="B45" s="322" t="s">
         <v>255</v>
       </c>
-      <c r="C45" s="331"/>
-      <c r="D45" s="331"/>
-      <c r="E45" s="331"/>
-      <c r="F45" s="331"/>
+      <c r="C45" s="322"/>
+      <c r="D45" s="322"/>
+      <c r="E45" s="322"/>
+      <c r="F45" s="322"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4034,13 +4030,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="331" t="s">
+      <c r="B48" s="322" t="s">
         <v>258</v>
       </c>
-      <c r="C48" s="332"/>
-      <c r="D48" s="332"/>
-      <c r="E48" s="332"/>
-      <c r="F48" s="332"/>
+      <c r="C48" s="326"/>
+      <c r="D48" s="326"/>
+      <c r="E48" s="326"/>
+      <c r="F48" s="326"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4069,13 +4065,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="329" t="s">
+      <c r="B52" s="323" t="s">
         <v>280</v>
       </c>
-      <c r="C52" s="329"/>
-      <c r="D52" s="329"/>
-      <c r="E52" s="329"/>
-      <c r="F52" s="329"/>
+      <c r="C52" s="323"/>
+      <c r="D52" s="323"/>
+      <c r="E52" s="323"/>
+      <c r="F52" s="323"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4136,22 +4132,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="331" t="s">
+      <c r="B60" s="322" t="s">
         <v>315</v>
       </c>
-      <c r="C60" s="331"/>
-      <c r="D60" s="331"/>
-      <c r="E60" s="331"/>
-      <c r="F60" s="331"/>
+      <c r="C60" s="322"/>
+      <c r="D60" s="322"/>
+      <c r="E60" s="322"/>
+      <c r="F60" s="322"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="333" t="s">
+      <c r="B61" s="324" t="s">
         <v>271</v>
       </c>
-      <c r="C61" s="333"/>
-      <c r="D61" s="333"/>
-      <c r="E61" s="333"/>
-      <c r="F61" s="333"/>
+      <c r="C61" s="324"/>
+      <c r="D61" s="324"/>
+      <c r="E61" s="324"/>
+      <c r="F61" s="324"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4162,7 +4158,7 @@
       <c r="B64" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C64" s="322">
+      <c r="C64" s="321">
         <v>0.08</v>
       </c>
     </row>
@@ -4174,7 +4170,7 @@
         <f>IF(D65="Y",1%,0)</f>
         <v>0.01</v>
       </c>
-      <c r="D65" s="296" t="s">
+      <c r="D65" s="295" t="s">
         <v>319</v>
       </c>
     </row>
@@ -4186,7 +4182,7 @@
         <f>IF(D66="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D66" s="296" t="s">
+      <c r="D66" s="295" t="s">
         <v>370</v>
       </c>
     </row>
@@ -4203,22 +4199,22 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="329" t="s">
+      <c r="B69" s="323" t="s">
         <v>323</v>
       </c>
-      <c r="C69" s="329"/>
-      <c r="D69" s="329"/>
-      <c r="E69" s="329"/>
-      <c r="F69" s="329"/>
+      <c r="C69" s="323"/>
+      <c r="D69" s="323"/>
+      <c r="E69" s="323"/>
+      <c r="F69" s="323"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="329" t="s">
+      <c r="B70" s="323" t="s">
         <v>270</v>
       </c>
-      <c r="C70" s="329"/>
-      <c r="D70" s="329"/>
-      <c r="E70" s="329"/>
-      <c r="F70" s="329"/>
+      <c r="C70" s="323"/>
+      <c r="D70" s="323"/>
+      <c r="E70" s="323"/>
+      <c r="F70" s="323"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4255,13 +4251,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="329" t="s">
+      <c r="B77" s="323" t="s">
         <v>273</v>
       </c>
-      <c r="C77" s="329"/>
-      <c r="D77" s="329"/>
-      <c r="E77" s="329"/>
-      <c r="F77" s="329"/>
+      <c r="C77" s="323"/>
+      <c r="D77" s="323"/>
+      <c r="E77" s="323"/>
+      <c r="F77" s="323"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4375,13 +4371,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="329" t="s">
+      <c r="B93" s="323" t="s">
         <v>279</v>
       </c>
-      <c r="C93" s="329"/>
-      <c r="D93" s="329"/>
-      <c r="E93" s="329"/>
-      <c r="F93" s="329"/>
+      <c r="C93" s="323"/>
+      <c r="D93" s="323"/>
+      <c r="E93" s="323"/>
+      <c r="F93" s="323"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4407,13 +4403,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="322" t="s">
         <v>384</v>
       </c>
-      <c r="C99" s="331"/>
-      <c r="D99" s="331"/>
-      <c r="E99" s="331"/>
-      <c r="F99" s="331"/>
+      <c r="C99" s="322"/>
+      <c r="D99" s="322"/>
+      <c r="E99" s="322"/>
+      <c r="F99" s="322"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4556,13 +4552,13 @@
       </c>
     </row>
     <row r="110" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B110" s="334" t="s">
+      <c r="B110" s="327" t="s">
         <v>385</v>
       </c>
-      <c r="C110" s="334"/>
-      <c r="D110" s="334"/>
-      <c r="E110" s="334"/>
-      <c r="F110" s="334"/>
+      <c r="C110" s="327"/>
+      <c r="D110" s="327"/>
+      <c r="E110" s="327"/>
+      <c r="F110" s="327"/>
     </row>
     <row r="112" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A112" s="254" t="s">
@@ -4575,13 +4571,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="330" t="s">
+      <c r="B114" s="325" t="s">
         <v>287</v>
       </c>
-      <c r="C114" s="330"/>
-      <c r="D114" s="330"/>
-      <c r="E114" s="330"/>
-      <c r="F114" s="330"/>
+      <c r="C114" s="325"/>
+      <c r="D114" s="325"/>
+      <c r="E114" s="325"/>
+      <c r="F114" s="325"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -4668,12 +4664,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4687,6 +4677,12 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -7036,7 +7032,7 @@
       <c r="C4" s="19">
         <v>8029</v>
       </c>
-      <c r="D4" s="305">
+      <c r="D4" s="304">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -7046,7 +7042,7 @@
       <c r="G4" s="19">
         <v>45665</v>
       </c>
-      <c r="H4" s="305">
+      <c r="H4" s="304">
         <v>0.9</v>
       </c>
     </row>
@@ -7057,7 +7053,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="305">
+      <c r="D5" s="304">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -7067,7 +7063,7 @@
       <c r="G5" s="19">
         <v>2014</v>
       </c>
-      <c r="H5" s="305">
+      <c r="H5" s="304">
         <v>0.7</v>
       </c>
     </row>
@@ -7078,7 +7074,7 @@
       <c r="C6" s="19">
         <v>9844</v>
       </c>
-      <c r="D6" s="305">
+      <c r="D6" s="304">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -7088,7 +7084,7 @@
       <c r="G6" s="19">
         <v>156</v>
       </c>
-      <c r="H6" s="305">
+      <c r="H6" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7099,7 +7095,7 @@
       <c r="C7" s="19">
         <v>5466</v>
       </c>
-      <c r="D7" s="305">
+      <c r="D7" s="304">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -7109,7 +7105,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="305">
+      <c r="H7" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7120,7 +7116,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="305">
+      <c r="D8" s="304">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -7130,7 +7126,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="305">
+      <c r="H8" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7141,7 +7137,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="305">
+      <c r="D9" s="304">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -7151,7 +7147,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="305">
+      <c r="H9" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7162,10 +7158,10 @@
       <c r="C10" s="19">
         <v>10</v>
       </c>
-      <c r="D10" s="305">
+      <c r="D10" s="304">
         <v>0.9</v>
       </c>
-      <c r="H10" s="306"/>
+      <c r="H10" s="305"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
@@ -7174,10 +7170,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="305">
+      <c r="D11" s="304">
         <v>0.05</v>
       </c>
-      <c r="H11" s="306"/>
+      <c r="H11" s="305"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
@@ -7235,7 +7231,7 @@
       <c r="C15" s="19">
         <v>2757</v>
       </c>
-      <c r="D15" s="305">
+      <c r="D15" s="304">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -7244,7 +7240,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="305">
+      <c r="H15" s="304">
         <v>0.8</v>
       </c>
     </row>
@@ -7255,7 +7251,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="305">
+      <c r="D16" s="304">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -7264,7 +7260,7 @@
       <c r="G16" s="19">
         <v>1373</v>
       </c>
-      <c r="H16" s="305">
+      <c r="H16" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7275,7 +7271,7 @@
       <c r="C17" s="19">
         <v>67668</v>
       </c>
-      <c r="D17" s="305">
+      <c r="D17" s="304">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -7284,7 +7280,7 @@
       <c r="G17" s="19">
         <v>13024</v>
       </c>
-      <c r="H17" s="305">
+      <c r="H17" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7295,7 +7291,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="305">
+      <c r="D18" s="304">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -7304,7 +7300,7 @@
       <c r="G18" s="19">
         <v>23696</v>
       </c>
-      <c r="H18" s="305">
+      <c r="H18" s="304">
         <v>0.1</v>
       </c>
     </row>
@@ -7315,7 +7311,7 @@
       <c r="C19" s="19">
         <v>1284</v>
       </c>
-      <c r="D19" s="305">
+      <c r="D19" s="304">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -7324,7 +7320,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="305">
+      <c r="H19" s="304">
         <v>0.1</v>
       </c>
     </row>
@@ -7335,7 +7331,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="305">
+      <c r="D20" s="304">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -7344,7 +7340,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="305">
+      <c r="H20" s="304">
         <v>0.2</v>
       </c>
     </row>
@@ -7355,7 +7351,7 @@
       <c r="C21" s="19">
         <v>0</v>
       </c>
-      <c r="D21" s="305">
+      <c r="D21" s="304">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -7364,7 +7360,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="305">
+      <c r="H21" s="304">
         <v>0.1</v>
       </c>
     </row>
@@ -7375,10 +7371,10 @@
       <c r="C22" s="19">
         <v>10</v>
       </c>
-      <c r="D22" s="305">
+      <c r="D22" s="304">
         <v>0.9</v>
       </c>
-      <c r="H22" s="306"/>
+      <c r="H22" s="305"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
@@ -7387,10 +7383,10 @@
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="305">
-        <v>0</v>
-      </c>
-      <c r="H23" s="306"/>
+      <c r="D23" s="304">
+        <v>0</v>
+      </c>
+      <c r="H23" s="305"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
@@ -7729,7 +7725,7 @@
       <c r="D45" s="210" t="s">
         <v>300</v>
       </c>
-      <c r="F45" s="297" t="s">
+      <c r="F45" s="296" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7745,7 +7741,7 @@
         <f>H29</f>
         <v>94070.7</v>
       </c>
-      <c r="F46" s="292"/>
+      <c r="F46" s="291"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="str">
@@ -7760,10 +7756,10 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>11.511512740854835</v>
       </c>
-      <c r="F47" s="292"/>
+      <c r="F47" s="291"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F48" s="292"/>
+      <c r="F48" s="291"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="162" t="s">
@@ -7776,7 +7772,7 @@
         <v>105</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="292"/>
+      <c r="F49" s="291"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
@@ -7790,7 +7786,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>1.3234916559691912</v>
       </c>
-      <c r="F50" s="292"/>
+      <c r="F50" s="291"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
@@ -7801,10 +7797,10 @@
         <f>G29/G32</f>
         <v>0.92039603085151056</v>
       </c>
-      <c r="F51" s="292"/>
+      <c r="F51" s="291"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F52" s="292"/>
+      <c r="F52" s="291"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="162" t="s">
@@ -7816,7 +7812,7 @@
       <c r="D53" s="225" t="s">
         <v>105</v>
       </c>
-      <c r="F53" s="292"/>
+      <c r="F53" s="291"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
@@ -7830,7 +7826,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>2.4582404173854506E-2</v>
       </c>
-      <c r="F54" s="292"/>
+      <c r="F54" s="291"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
@@ -7844,10 +7840,10 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>7.4364584303137507E-3</v>
       </c>
-      <c r="F55" s="292"/>
+      <c r="F55" s="291"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F56" s="292"/>
+      <c r="F56" s="291"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="162" t="s">
@@ -7859,7 +7855,7 @@
       <c r="D57" s="225" t="s">
         <v>105</v>
       </c>
-      <c r="F57" s="292"/>
+      <c r="F57" s="291"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
@@ -7881,10 +7877,10 @@
         <f>G39/G32</f>
         <v>0.41115825764105285</v>
       </c>
-      <c r="F59" s="292"/>
+      <c r="F59" s="291"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F60" s="292"/>
+      <c r="F60" s="291"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="162" t="s">
@@ -7896,7 +7892,7 @@
       <c r="D61" s="225" t="s">
         <v>105</v>
       </c>
-      <c r="F61" s="292"/>
+      <c r="F61" s="291"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
@@ -7910,7 +7906,7 @@
         <f>G28/G29</f>
         <v>3.1154705020769802E-3</v>
       </c>
-      <c r="F62" s="292" t="s">
+      <c r="F62" s="291" t="s">
         <v>301</v>
       </c>
     </row>
@@ -7935,7 +7931,7 @@
       <c r="D65" s="211" t="s">
         <v>326</v>
       </c>
-      <c r="F65" s="297" t="s">
+      <c r="F65" s="296" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7963,7 +7959,7 @@
         <f>G6+G16</f>
         <v>1529</v>
       </c>
-      <c r="F67" s="292"/>
+      <c r="F67" s="291"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
@@ -7973,7 +7969,7 @@
         <f>G18</f>
         <v>23696</v>
       </c>
-      <c r="F68" s="292"/>
+      <c r="F68" s="291"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
@@ -7983,7 +7979,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="292"/>
+      <c r="F69" s="291"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
@@ -7993,13 +7989,13 @@
         <f>SUM(C66:C69)</f>
         <v>72904</v>
       </c>
-      <c r="F70" s="292"/>
+      <c r="F70" s="291"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F71" s="292"/>
+      <c r="F71" s="291"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="295" t="s">
+      <c r="B72" s="294" t="s">
         <v>367</v>
       </c>
       <c r="C72" s="268" t="s">
@@ -8008,7 +8004,7 @@
       <c r="D72" s="210" t="s">
         <v>61</v>
       </c>
-      <c r="F72" s="292"/>
+      <c r="F72" s="291"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
@@ -8024,18 +8020,18 @@
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="298" t="s">
+      <c r="B74" s="297" t="s">
         <v>374</v>
       </c>
-      <c r="C74" s="299">
+      <c r="C74" s="298">
         <f>-$C$66/C73</f>
         <v>89.008711885500944</v>
       </c>
-      <c r="D74" s="299">
+      <c r="D74" s="298">
         <f>-$C$66/D73</f>
         <v>92.682867505381196</v>
       </c>
-      <c r="F74" s="292" t="s">
+      <c r="F74" s="291" t="s">
         <v>368</v>
       </c>
     </row>
@@ -8043,30 +8039,30 @@
       <c r="B75" s="82" t="s">
         <v>369</v>
       </c>
-      <c r="C75" s="304"/>
-      <c r="D75" s="303">
+      <c r="C75" s="303"/>
+      <c r="D75" s="302">
         <f>MIN(D73*D76,-G5)</f>
         <v>-3086.5898703812809</v>
       </c>
-      <c r="F75" s="292" t="s">
+      <c r="F75" s="291" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="300" t="s">
+      <c r="B76" s="299" t="s">
         <v>375</v>
       </c>
-      <c r="C76" s="301"/>
-      <c r="D76" s="302">
+      <c r="C76" s="300"/>
+      <c r="D76" s="301">
         <f>IF(D74&lt;=3,1,IF(D74&gt;12,6,2))</f>
         <v>6</v>
       </c>
-      <c r="F76" s="292" t="s">
+      <c r="F76" s="291" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F77" s="292"/>
+      <c r="F77" s="291"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
@@ -8078,7 +8074,7 @@
       <c r="D78" s="211" t="s">
         <v>36</v>
       </c>
-      <c r="F78" s="292"/>
+      <c r="F78" s="291"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
@@ -8092,7 +8088,7 @@
         <f>G7*H7+G17*H17</f>
         <v>7814.4</v>
       </c>
-      <c r="F79" s="292"/>
+      <c r="F79" s="291"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
@@ -8106,7 +8102,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="292"/>
+      <c r="F80" s="291"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
@@ -8120,7 +8116,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="292"/>
+      <c r="F81" s="291"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
@@ -8134,7 +8130,7 @@
         <f>SUM(D79:D81)</f>
         <v>7814.4</v>
       </c>
-      <c r="F82" s="292"/>
+      <c r="F82" s="291"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
@@ -8339,7 +8335,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="313"/>
+      <c r="E3" s="312"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -8353,7 +8349,7 @@
         <v>8765</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="311"/>
+      <c r="E4" s="310"/>
       <c r="F4" s="57"/>
       <c r="G4" s="187">
         <f>Data!C36</f>
@@ -8409,7 +8405,7 @@
         <f>C25</f>
         <v>-5066.6797407625618</v>
       </c>
-      <c r="E5" s="313"/>
+      <c r="E5" s="312"/>
       <c r="G5" s="187">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-5344</v>
@@ -8464,7 +8460,7 @@
         <f>C4+C5</f>
         <v>3698.3202592374382</v>
       </c>
-      <c r="E6" s="313"/>
+      <c r="E6" s="312"/>
       <c r="G6" s="188">
         <f>IF(G4="","",G4+G5)</f>
         <v>3421</v>
@@ -8519,7 +8515,7 @@
         <f>C35</f>
         <v>-1106.5</v>
       </c>
-      <c r="E7" s="313"/>
+      <c r="E7" s="312"/>
       <c r="G7" s="198">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-1084</v>
@@ -8575,7 +8571,7 @@
         <v>2591.8202592374382</v>
       </c>
       <c r="D8" s="60"/>
-      <c r="E8" s="319"/>
+      <c r="E8" s="318"/>
       <c r="F8" s="60"/>
       <c r="G8" s="188">
         <f>IF(G$4="","",G6+G7)</f>
@@ -8631,7 +8627,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>159.99999999999997</v>
       </c>
-      <c r="E9" s="313"/>
+      <c r="E9" s="312"/>
       <c r="G9" s="198">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>160</v>
@@ -8686,7 +8682,7 @@
         <f>-C4*C77</f>
         <v>-159.99999999999997</v>
       </c>
-      <c r="E10" s="313"/>
+      <c r="E10" s="312"/>
       <c r="G10" s="198">
         <f>Data!C62</f>
         <v>-69</v>
@@ -8742,7 +8738,7 @@
         <v>639</v>
       </c>
       <c r="D11" s="173"/>
-      <c r="E11" s="312"/>
+      <c r="E11" s="311"/>
       <c r="F11" s="173"/>
       <c r="G11" s="190">
         <f>G60</f>
@@ -8798,7 +8794,7 @@
         <f>C49</f>
         <v>1387.37</v>
       </c>
-      <c r="E12" s="313"/>
+      <c r="E12" s="312"/>
       <c r="G12" s="198">
         <f t="shared" ref="G12:Q12" si="6">G49</f>
         <v>2297</v>
@@ -8853,7 +8849,7 @@
         <f>SUM(C8:C12)</f>
         <v>4618.1902592374381</v>
       </c>
-      <c r="E13" s="313"/>
+      <c r="E13" s="312"/>
       <c r="G13" s="188">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>5364</v>
@@ -8908,7 +8904,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-1108.3656622169851</v>
       </c>
-      <c r="E14" s="313"/>
+      <c r="E14" s="312"/>
       <c r="G14" s="198">
         <f>Data!C46</f>
         <v>-519</v>
@@ -8964,7 +8960,7 @@
         <v>-22.869707937042335</v>
       </c>
       <c r="D15" s="61"/>
-      <c r="E15" s="320"/>
+      <c r="E15" s="319"/>
       <c r="F15" s="61"/>
       <c r="G15" s="187">
         <f>Data!C48</f>
@@ -9021,7 +9017,7 @@
         <v>3486.9548890834108</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="321"/>
+      <c r="E16" s="320"/>
       <c r="F16" s="62"/>
       <c r="G16" s="188">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -9078,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="59"/>
-      <c r="E17" s="312" t="s">
+      <c r="E17" s="311" t="s">
         <v>259</v>
       </c>
       <c r="F17" s="59"/>
@@ -9104,7 +9100,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
-      <c r="E18" s="312" t="s">
+      <c r="E18" s="311" t="s">
         <v>108</v>
       </c>
       <c r="F18" s="59"/>
@@ -9130,7 +9126,7 @@
         <v>3486.9548890834108</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="310"/>
+      <c r="E19" s="309"/>
       <c r="F19" s="27"/>
       <c r="G19" s="190">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",SUM(G16:G18))</f>
@@ -9226,7 +9222,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="310"/>
+      <c r="E22" s="309"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -9250,7 +9246,7 @@
         <v>-5066.6797407625618</v>
       </c>
       <c r="D23" s="59"/>
-      <c r="E23" s="312"/>
+      <c r="E23" s="311"/>
       <c r="F23" s="59"/>
       <c r="G23" s="187">
         <f>Data!C37</f>
@@ -9307,7 +9303,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="310"/>
+      <c r="E24" s="309"/>
       <c r="F24" s="27"/>
       <c r="G24" s="187">
         <f>Data!C40</f>
@@ -9364,7 +9360,7 @@
         <v>-5066.6797407625618</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="318"/>
+      <c r="E25" s="317"/>
       <c r="F25" s="9"/>
       <c r="G25" s="188">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -9413,14 +9409,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
-      <c r="E26" s="313"/>
+      <c r="E26" s="312"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
         <v>218</v>
       </c>
-      <c r="E27" s="313"/>
+      <c r="E27" s="312"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
@@ -9432,7 +9428,7 @@
         <v>0.57805815639048053</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="311" t="s">
+      <c r="E28" s="310" t="s">
         <v>89</v>
       </c>
       <c r="F28" s="26"/>
@@ -9492,7 +9488,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="311" t="s">
+      <c r="E29" s="310" t="s">
         <v>89</v>
       </c>
       <c r="F29" s="26"/>
@@ -9550,7 +9546,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.57805815639048053</v>
       </c>
-      <c r="E30" s="313"/>
+      <c r="E30" s="312"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.60969766115231028</v>
@@ -9598,14 +9594,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
-      <c r="E31" s="313"/>
+      <c r="E31" s="312"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="313"/>
+      <c r="E32" s="312"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
@@ -9616,7 +9612,7 @@
         <f>AVERAGE(G33:H33)</f>
         <v>-1106.5</v>
       </c>
-      <c r="E33" s="311" t="s">
+      <c r="E33" s="310" t="s">
         <v>89</v>
       </c>
       <c r="G33" s="198">
@@ -9674,7 +9670,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="59"/>
-      <c r="E34" s="311" t="s">
+      <c r="E34" s="310" t="s">
         <v>89</v>
       </c>
       <c r="F34" s="59"/>
@@ -9733,7 +9729,7 @@
         <v>-1106.5</v>
       </c>
       <c r="D35" s="59"/>
-      <c r="E35" s="312"/>
+      <c r="E35" s="311"/>
       <c r="F35" s="59"/>
       <c r="G35" s="188">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -9782,14 +9778,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
-      <c r="E36" s="313"/>
+      <c r="E36" s="312"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="E37" s="313"/>
+      <c r="E37" s="312"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
@@ -9802,7 +9798,7 @@
         <v>0.1262407301768397</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="310"/>
+      <c r="E38" s="309"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -9860,7 +9856,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="310"/>
+      <c r="E39" s="309"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -9916,7 +9912,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.1262407301768397</v>
       </c>
-      <c r="E40" s="313"/>
+      <c r="E40" s="312"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.12367370222475756</v>
@@ -9964,25 +9960,25 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10"/>
-      <c r="E41" s="313"/>
+      <c r="E41" s="312"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="E42" s="313"/>
+      <c r="E42" s="312"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="C43" s="307">
+      <c r="C43" s="306">
         <v>0.24</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="310" t="s">
+      <c r="E43" s="309" t="s">
         <v>82</v>
       </c>
       <c r="F43" s="27"/>
@@ -10062,7 +10058,7 @@
       <c r="B46" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="313"/>
+      <c r="E46" s="312"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
@@ -10073,7 +10069,7 @@
         <f>-BS!G31*Normalized_FCF!C53</f>
         <v>-43</v>
       </c>
-      <c r="E47" s="313"/>
+      <c r="E47" s="312"/>
       <c r="G47" s="198">
         <f>Data!C51</f>
         <v>-43</v>
@@ -10128,7 +10124,7 @@
         <f>BS!$C$66*C52</f>
         <v>1430.37</v>
       </c>
-      <c r="E48" s="313"/>
+      <c r="E48" s="312"/>
       <c r="G48" s="198">
         <f>Data!C52</f>
         <v>2340</v>
@@ -10183,7 +10179,7 @@
         <f>C47+C48</f>
         <v>1387.37</v>
       </c>
-      <c r="E49" s="313"/>
+      <c r="E49" s="312"/>
       <c r="G49" s="188">
         <f t="shared" ref="G49:Q49" si="19">IF(G4="","",G47+G48)</f>
         <v>2297</v>
@@ -10231,14 +10227,14 @@
     </row>
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10"/>
-      <c r="E50" s="313"/>
+      <c r="E50" s="312"/>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
       <c r="B51" s="73" t="s">
         <v>166</v>
       </c>
-      <c r="E51" s="313"/>
+      <c r="E51" s="312"/>
       <c r="G51" s="100" t="s">
         <v>231</v>
       </c>
@@ -10251,7 +10247,7 @@
       <c r="C52" s="89">
         <v>0.03</v>
       </c>
-      <c r="E52" s="310" t="s">
+      <c r="E52" s="309" t="s">
         <v>86</v>
       </c>
       <c r="G52" s="6">
@@ -10278,7 +10274,7 @@
         <f>G53</f>
         <v>1.3902360168121564E-2</v>
       </c>
-      <c r="E53" s="310" t="s">
+      <c r="E53" s="309" t="s">
         <v>85</v>
       </c>
       <c r="G53" s="23">
@@ -10305,7 +10301,7 @@
         <f>-C8/C47</f>
         <v>60.274889749707867</v>
       </c>
-      <c r="E54" s="313"/>
+      <c r="E54" s="312"/>
       <c r="G54" s="42">
         <f>IF(G4="","",-G8/G47)</f>
         <v>54.348837209302324</v>
@@ -10353,14 +10349,14 @@
     </row>
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
-      <c r="E55" s="313"/>
+      <c r="E55" s="312"/>
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
       <c r="B56" s="65" t="s">
         <v>179</v>
       </c>
-      <c r="E56" s="313"/>
+      <c r="E56" s="312"/>
       <c r="G56" s="100" t="s">
         <v>231</v>
       </c>
@@ -10374,7 +10370,7 @@
         <f>BS!$C79*C65</f>
         <v>0</v>
       </c>
-      <c r="E57" s="313"/>
+      <c r="E57" s="312"/>
       <c r="G57" s="198">
         <f>Data!C56</f>
         <v>0</v>
@@ -10429,7 +10425,7 @@
         <f>BS!$C68*C66</f>
         <v>639</v>
       </c>
-      <c r="E58" s="313"/>
+      <c r="E58" s="312"/>
       <c r="G58" s="198">
         <f>Data!C55</f>
         <v>639</v>
@@ -10484,7 +10480,7 @@
         <f>BS!$C81*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="313"/>
+      <c r="E59" s="312"/>
       <c r="G59" s="198">
         <f>Data!C57</f>
         <v>0</v>
@@ -10539,7 +10535,7 @@
         <f>SUM(C57:C59)</f>
         <v>639</v>
       </c>
-      <c r="E60" s="313"/>
+      <c r="E60" s="312"/>
       <c r="G60" s="188">
         <f t="shared" ref="G60:Q60" si="21">IF(G4="","",SUM(G57:G59))</f>
         <v>639</v>
@@ -10590,10 +10586,10 @@
       <c r="B61" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="C61" s="308">
-        <v>0</v>
-      </c>
-      <c r="E61" s="311" t="s">
+      <c r="C61" s="307">
+        <v>0</v>
+      </c>
+      <c r="E61" s="310" t="s">
         <v>206</v>
       </c>
       <c r="G61" s="198">
@@ -10650,7 +10646,7 @@
         <f>C60+C61</f>
         <v>639</v>
       </c>
-      <c r="E62" s="313"/>
+      <c r="E62" s="312"/>
       <c r="G62" s="188">
         <f t="shared" ref="G62:Q62" si="22">IF(G4="","",G60+G61)</f>
         <v>136</v>
@@ -10698,14 +10694,14 @@
     </row>
     <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10"/>
-      <c r="E63" s="313"/>
+      <c r="E63" s="312"/>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
       <c r="B64" s="99" t="s">
         <v>180</v>
       </c>
-      <c r="E64" s="313"/>
+      <c r="E64" s="312"/>
       <c r="G64" s="100" t="s">
         <v>231</v>
       </c>
@@ -10719,7 +10715,7 @@
         <f>G65</f>
         <v>0</v>
       </c>
-      <c r="E65" s="313"/>
+      <c r="E65" s="312"/>
       <c r="G65" s="23">
         <f>IFERROR(G57/BS!$C$67,0)</f>
         <v>0</v>
@@ -10744,7 +10740,7 @@
         <f>G66</f>
         <v>2.6966576637407157E-2</v>
       </c>
-      <c r="E66" s="313"/>
+      <c r="E66" s="312"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$68,0)</f>
         <v>2.6966576637407157E-2</v>
@@ -10769,7 +10765,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="313"/>
+      <c r="E67" s="312"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$81,0)</f>
         <v>0</v>
@@ -10795,7 +10791,7 @@
         <v>8.7649511686601553E-3</v>
       </c>
       <c r="D68" s="9"/>
-      <c r="E68" s="318"/>
+      <c r="E68" s="317"/>
       <c r="F68" s="9"/>
       <c r="G68" s="72">
         <f>G60/BS!C70</f>
@@ -10845,7 +10841,7 @@
       </c>
       <c r="C71" s="63"/>
       <c r="D71" s="27"/>
-      <c r="E71" s="310"/>
+      <c r="E71" s="309"/>
       <c r="F71" s="27"/>
       <c r="G71" s="100"/>
       <c r="H71" s="12"/>
@@ -10869,7 +10865,7 @@
         <v>0.57805815639048053</v>
       </c>
       <c r="D72" s="27"/>
-      <c r="E72" s="310"/>
+      <c r="E72" s="309"/>
       <c r="F72" s="27"/>
       <c r="G72" s="6">
         <f t="shared" ref="G72:Q72" si="23">IF(G$4="","",ABS(G5/G$4))</f>
@@ -10926,7 +10922,7 @@
         <v>0.42194184360951947</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="310"/>
+      <c r="E73" s="309"/>
       <c r="F73" s="27"/>
       <c r="G73" s="66">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G6/G$4))</f>
@@ -10983,7 +10979,7 @@
         <v>0.1262407301768397</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="310"/>
+      <c r="E74" s="309"/>
       <c r="F74" s="27"/>
       <c r="G74" s="6">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G7/G$4))</f>
@@ -11040,7 +11036,7 @@
         <v>0.2957011134326798</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="310"/>
+      <c r="E75" s="309"/>
       <c r="F75" s="27"/>
       <c r="G75" s="66">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G8/G$4))</f>
@@ -11097,7 +11093,7 @@
         <v>1.8254420992584137E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="310"/>
+      <c r="E76" s="309"/>
       <c r="F76" s="27"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",G9/G$4)</f>
@@ -11154,7 +11150,7 @@
         <v>1.8254420992584137E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="311" t="s">
+      <c r="E77" s="310" t="s">
         <v>88</v>
       </c>
       <c r="F77" s="27"/>
@@ -11213,7 +11209,7 @@
         <v>7.2903593839132919E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="310"/>
+      <c r="E78" s="309"/>
       <c r="F78" s="27"/>
       <c r="G78" s="66">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",G11/G$4)</f>
@@ -11270,7 +11266,7 @@
         <v>0.15828522532800912</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="310"/>
+      <c r="E79" s="309"/>
       <c r="F79" s="27"/>
       <c r="G79" s="6">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",ABS(G12/G$4))</f>
@@ -11327,7 +11323,7 @@
         <v>0.52688993259982175</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="310"/>
+      <c r="E80" s="309"/>
       <c r="F80" s="27"/>
       <c r="G80" s="66">
         <f>IF(G$4="","",G13/G$4)</f>
@@ -11384,7 +11380,7 @@
         <v>0.12645358382395724</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="310"/>
+      <c r="E81" s="309"/>
       <c r="F81" s="27"/>
       <c r="G81" s="6">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",ABS(G14/G$4))</f>
@@ -11437,12 +11433,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C82" s="309">
+      <c r="C82" s="308">
         <f>MIN(BS!C62,MAX(G82:K82))</f>
         <v>2.6092079791263361E-3</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="310"/>
+      <c r="E82" s="309"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",-G15/G$4)</f>
@@ -11499,7 +11495,7 @@
         <v>0.39782714079673825</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="310"/>
+      <c r="E83" s="309"/>
       <c r="F83" s="27"/>
       <c r="G83" s="66">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",ABS(G16/G$4))</f>
@@ -11551,11 +11547,11 @@
       <c r="B84" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C84" s="309">
+      <c r="C84" s="308">
         <v>0</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="312" t="str">
+      <c r="E84" s="311" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
@@ -11577,10 +11573,10 @@
       <c r="B85" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C85" s="309">
-        <v>0</v>
-      </c>
-      <c r="E85" s="312" t="str">
+      <c r="C85" s="308">
+        <v>0</v>
+      </c>
+      <c r="E85" s="311" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -11606,7 +11602,7 @@
         <v>0.39782714079673825</v>
       </c>
       <c r="D86" s="77"/>
-      <c r="E86" s="310"/>
+      <c r="E86" s="309"/>
       <c r="F86" s="77"/>
       <c r="G86" s="66">
         <f t="shared" ref="G86:Q86" si="35">IF(G$4="","",ABS(G19/G$4))</f>
@@ -11655,14 +11651,14 @@
     </row>
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
-      <c r="E87" s="313"/>
+      <c r="E87" s="312"/>
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
       <c r="B88" s="65" t="s">
         <v>226</v>
       </c>
-      <c r="E88" s="313"/>
+      <c r="E88" s="312"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
@@ -11674,7 +11670,7 @@
         <f>G89</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="E89" s="313"/>
+      <c r="E89" s="312"/>
       <c r="G89" s="116">
         <f>Data!C64</f>
         <v>0.57999999999999996</v>
@@ -11730,7 +11726,7 @@
         <f>C89*Common_Shares/$C$3</f>
         <v>4739.6903628800001</v>
       </c>
-      <c r="E90" s="313"/>
+      <c r="E90" s="312"/>
       <c r="G90" s="76">
         <f t="shared" ref="G90:Q90" si="36">IF(G$4="","",G89*Common_Shares/$C$3)</f>
         <v>4739.6903628800001</v>
@@ -11785,7 +11781,7 @@
         <f>C89/(C19*$C$3/Common_Shares)</f>
         <v>1.3592634587039025</v>
       </c>
-      <c r="E91" s="313"/>
+      <c r="E91" s="312"/>
       <c r="G91" s="175">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G89/(G19*$C$3/Common_Shares))</f>
         <v>0.97826426478431361</v>
@@ -11840,7 +11836,7 @@
         <f>C89/Market_Price</f>
         <v>7.3417721518987331E-2</v>
       </c>
-      <c r="E92" s="313"/>
+      <c r="E92" s="312"/>
       <c r="G92" s="23">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G89/Market_Price)</f>
         <v>7.3417721518987331E-2</v>
@@ -11888,7 +11884,7 @@
     </row>
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
-      <c r="E93" s="313"/>
+      <c r="E93" s="312"/>
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
@@ -11897,7 +11893,7 @@
       </c>
       <c r="C94" s="63"/>
       <c r="D94" s="27"/>
-      <c r="E94" s="310"/>
+      <c r="E94" s="309"/>
       <c r="F94" s="27"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12"/>
@@ -11921,7 +11917,7 @@
         <v>0</v>
       </c>
       <c r="D95" s="27"/>
-      <c r="E95" s="310"/>
+      <c r="E95" s="309"/>
       <c r="F95" s="27"/>
       <c r="G95" s="6">
         <f t="shared" ref="G95:Q95" si="39">IF(H4="","",G4/H4-1)</f>
@@ -11978,7 +11974,7 @@
         <v>-0.13903984727117114</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="310"/>
+      <c r="E96" s="309"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G13/H13-1)</f>
@@ -12056,7 +12052,7 @@
       <c r="B99" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="E99" s="313"/>
+      <c r="E99" s="312"/>
       <c r="G99" s="100" t="s">
         <v>231</v>
       </c>
@@ -12071,7 +12067,7 @@
         <v>180996</v>
       </c>
       <c r="D100" s="26"/>
-      <c r="E100" s="314"/>
+      <c r="E100" s="313"/>
       <c r="F100" s="26"/>
       <c r="G100" s="187">
         <f t="shared" ref="G100:Q100" si="41">IF(G$4="","",G104+G103)</f>
@@ -12128,7 +12124,7 @@
         <v>8029</v>
       </c>
       <c r="D101" s="91"/>
-      <c r="E101" s="315"/>
+      <c r="E101" s="314"/>
       <c r="F101" s="91"/>
       <c r="G101" s="189">
         <f>IF(G$4="","",Data!D76)</f>
@@ -12185,7 +12181,7 @@
         <v>15310</v>
       </c>
       <c r="D102" s="91"/>
-      <c r="E102" s="315"/>
+      <c r="E102" s="314"/>
       <c r="F102" s="91"/>
       <c r="G102" s="189">
         <f>IF(G$4="","",Data!D77)</f>
@@ -12242,7 +12238,7 @@
         <v>13889</v>
       </c>
       <c r="D103" s="26"/>
-      <c r="E103" s="314"/>
+      <c r="E103" s="313"/>
       <c r="F103" s="26"/>
       <c r="G103" s="187">
         <f>Data!C78</f>
@@ -12299,7 +12295,7 @@
         <v>167107</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="314"/>
+      <c r="E104" s="313"/>
       <c r="F104" s="26"/>
       <c r="G104" s="187">
         <f>Data!C79</f>
@@ -12348,7 +12344,7 @@
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="10"/>
-      <c r="E105" s="313"/>
+      <c r="E105" s="312"/>
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
@@ -12357,7 +12353,7 @@
       </c>
       <c r="C106" s="26"/>
       <c r="D106" s="26"/>
-      <c r="E106" s="314"/>
+      <c r="E106" s="313"/>
       <c r="F106" s="26"/>
       <c r="G106" s="100" t="s">
         <v>231</v>
@@ -12383,7 +12379,7 @@
         <v>0.91602966343411296</v>
       </c>
       <c r="D107" s="26"/>
-      <c r="E107" s="314"/>
+      <c r="E107" s="313"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97">
         <f t="shared" ref="G107:Q107" si="42">IF(G$4="","",G101/G$4)</f>
@@ -12440,7 +12436,7 @@
         <v>1.7467199087278951</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="314"/>
+      <c r="E108" s="313"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -12497,7 +12493,7 @@
         <v>8.343867655447804</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="314"/>
+      <c r="E109" s="313"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f>BS!$G$38/G$4</f>
@@ -12516,7 +12512,7 @@
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10"/>
-      <c r="E110" s="313"/>
+      <c r="E110" s="312"/>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
@@ -12525,7 +12521,7 @@
       </c>
       <c r="C111" s="55"/>
       <c r="D111" s="55"/>
-      <c r="E111" s="316"/>
+      <c r="E111" s="315"/>
       <c r="F111" s="55"/>
       <c r="G111" s="23" t="str">
         <f>IFERROR(IF(#REF!*G113*(1/#REF!)=G115,"","Error"),"")</f>
@@ -12581,7 +12577,7 @@
         <f>C80</f>
         <v>0.52688993259982175</v>
       </c>
-      <c r="E112" s="313"/>
+      <c r="E112" s="312"/>
       <c r="G112" s="23">
         <f t="shared" ref="G112:Q112" si="44">G80</f>
         <v>0.61197946377638335</v>
@@ -12635,7 +12631,7 @@
         <f>C4/C100</f>
         <v>4.8426484563194767E-2</v>
       </c>
-      <c r="E113" s="313"/>
+      <c r="E113" s="312"/>
       <c r="G113" s="42">
         <f t="shared" ref="G113:Q113" si="45">IF(G4="","",G4/G100)</f>
         <v>4.8601561460320276E-2</v>
@@ -12690,7 +12686,7 @@
         <v>1.0831144117242246</v>
       </c>
       <c r="D114" s="11"/>
-      <c r="E114" s="317"/>
+      <c r="E114" s="316"/>
       <c r="F114" s="11"/>
       <c r="G114" s="15">
         <f t="shared" ref="G114:Q114" si="46">IF(G$4="","",G100/G104)</f>
@@ -12747,7 +12743,7 @@
         <v>1.5509944282629921E-2</v>
       </c>
       <c r="D115" s="106"/>
-      <c r="E115" s="316"/>
+      <c r="E115" s="315"/>
       <c r="F115" s="106"/>
       <c r="G115" s="105">
         <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G8/G104)</f>
@@ -12843,7 +12839,7 @@
       </c>
       <c r="C118" s="184"/>
       <c r="D118" s="27"/>
-      <c r="E118" s="310"/>
+      <c r="E118" s="309"/>
       <c r="F118" s="27"/>
       <c r="G118" s="12"/>
       <c r="H118" s="12"/>
@@ -12868,7 +12864,7 @@
         <v>0.42670167897623534</v>
       </c>
       <c r="D119" s="27"/>
-      <c r="E119" s="310"/>
+      <c r="E119" s="309"/>
       <c r="F119" s="27"/>
       <c r="G119" s="182">
         <f t="shared" ref="G119:Q119" si="48">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -12925,7 +12921,7 @@
         <v>5.401287075648549E-2</v>
       </c>
       <c r="D120" s="27"/>
-      <c r="E120" s="310"/>
+      <c r="E120" s="309"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
@@ -13754,10 +13750,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="335" t="s">
+      <c r="E6" s="328" t="s">
         <v>267</v>
       </c>
-      <c r="F6" s="335"/>
+      <c r="F6" s="328"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -13772,8 +13768,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="335"/>
-      <c r="F7" s="335"/>
+      <c r="E7" s="328"/>
+      <c r="F7" s="328"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -13788,8 +13784,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="335"/>
-      <c r="F8" s="335"/>
+      <c r="E8" s="328"/>
+      <c r="F8" s="328"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -13804,8 +13800,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="335"/>
-      <c r="F9" s="335"/>
+      <c r="E9" s="328"/>
+      <c r="F9" s="328"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15202,7 +15198,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I90"/>
+  <dimension ref="B2:I92"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -15254,7 +15250,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="272">
-        <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.57999999999999996</v>
       </c>
     </row>
@@ -15263,7 +15259,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="272">
-        <f t="shared" si="0"/>
+        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.57999999999999996</v>
       </c>
     </row>
@@ -15283,7 +15279,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="272">
-        <f t="shared" si="0"/>
+        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>11.22404343432521</v>
       </c>
     </row>
@@ -15299,16 +15295,16 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="337" t="str">
+      <c r="E7" s="330" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="337"/>
+      <c r="F7" s="330"/>
       <c r="H7" s="284">
         <v>4</v>
       </c>
       <c r="I7" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v/>
       </c>
     </row>
@@ -15324,13 +15320,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="337"/>
-      <c r="F8" s="337"/>
+      <c r="E8" s="330"/>
+      <c r="F8" s="330"/>
       <c r="H8" s="284">
         <v>5</v>
       </c>
       <c r="I8" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v/>
       </c>
     </row>
@@ -15346,24 +15342,24 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="337"/>
-      <c r="F9" s="337"/>
+      <c r="E9" s="330"/>
+      <c r="F9" s="330"/>
       <c r="H9" s="284">
         <v>6</v>
       </c>
       <c r="I9" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="337"/>
-      <c r="F10" s="337"/>
+      <c r="E10" s="330"/>
+      <c r="F10" s="330"/>
       <c r="H10" s="284">
         <v>7</v>
       </c>
       <c r="I10" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v/>
       </c>
     </row>
@@ -15371,13 +15367,13 @@
       <c r="B11" s="164" t="s">
         <v>307</v>
       </c>
-      <c r="E11" s="337"/>
-      <c r="F11" s="337"/>
+      <c r="E11" s="330"/>
+      <c r="F11" s="330"/>
       <c r="H11" s="284">
         <v>8</v>
       </c>
       <c r="I11" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v/>
       </c>
     </row>
@@ -15390,13 +15386,13 @@
         <v>-0.28945840615733698</v>
       </c>
       <c r="D12" s="163"/>
-      <c r="E12" s="337"/>
-      <c r="F12" s="337"/>
+      <c r="E12" s="330"/>
+      <c r="F12" s="330"/>
       <c r="H12" s="284">
         <v>9</v>
       </c>
       <c r="I12" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v/>
       </c>
     </row>
@@ -15408,13 +15404,13 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.42686307479092267</v>
       </c>
-      <c r="E13" s="337"/>
-      <c r="F13" s="337"/>
+      <c r="E13" s="330"/>
+      <c r="F13" s="330"/>
       <c r="H13" s="284">
         <v>10</v>
       </c>
       <c r="I13" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v/>
       </c>
     </row>
@@ -15426,8 +15422,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.22869925060693375</v>
       </c>
-      <c r="E14" s="337"/>
-      <c r="F14" s="337"/>
+      <c r="E14" s="330"/>
+      <c r="F14" s="330"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15453,21 +15449,21 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="337" t="s">
+      <c r="E18" s="330" t="s">
         <v>383</v>
       </c>
-      <c r="F18" s="338"/>
+      <c r="F18" s="331"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="338"/>
-      <c r="F19" s="338"/>
+      <c r="E19" s="331"/>
+      <c r="F19" s="331"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="164" t="s">
         <v>345</v>
       </c>
-      <c r="E20" s="338"/>
-      <c r="F20" s="338"/>
+      <c r="E20" s="331"/>
+      <c r="F20" s="331"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -15481,8 +15477,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="338"/>
-      <c r="F21" s="338"/>
+      <c r="E21" s="331"/>
+      <c r="F21" s="331"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -15496,8 +15492,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="338"/>
-      <c r="F22" s="338"/>
+      <c r="E22" s="331"/>
+      <c r="F22" s="331"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="164" t="s">
@@ -15517,8 +15513,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="168"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="E25" s="329"/>
+      <c r="F25" s="329"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -15528,8 +15524,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="169"/>
-      <c r="E26" s="336"/>
-      <c r="F26" s="336"/>
+      <c r="E26" s="329"/>
+      <c r="F26" s="329"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -15543,8 +15539,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="336"/>
-      <c r="F27" s="336"/>
+      <c r="E27" s="329"/>
+      <c r="F27" s="329"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -15554,8 +15550,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="170"/>
-      <c r="E28" s="336"/>
-      <c r="F28" s="336"/>
+      <c r="E28" s="329"/>
+      <c r="F28" s="329"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="164" t="s">
@@ -15575,8 +15571,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="168"/>
-      <c r="E31" s="336"/>
-      <c r="F31" s="336"/>
+      <c r="E31" s="329"/>
+      <c r="F31" s="329"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -15586,8 +15582,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="169"/>
-      <c r="E32" s="336"/>
-      <c r="F32" s="336"/>
+      <c r="E32" s="329"/>
+      <c r="F32" s="329"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -15601,8 +15597,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="336"/>
-      <c r="F33" s="336"/>
+      <c r="E33" s="329"/>
+      <c r="F33" s="329"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -15612,8 +15608,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="170"/>
-      <c r="E34" s="336"/>
-      <c r="F34" s="336"/>
+      <c r="E34" s="329"/>
+      <c r="F34" s="329"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="164" t="s">
@@ -15633,8 +15629,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="168"/>
-      <c r="E37" s="336"/>
-      <c r="F37" s="336"/>
+      <c r="E37" s="329"/>
+      <c r="F37" s="329"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -15644,8 +15640,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="169"/>
-      <c r="E38" s="336"/>
-      <c r="F38" s="336"/>
+      <c r="E38" s="329"/>
+      <c r="F38" s="329"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -15659,8 +15655,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="336"/>
-      <c r="F39" s="336"/>
+      <c r="E39" s="329"/>
+      <c r="F39" s="329"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -15671,8 +15667,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="170"/>
-      <c r="E40" s="336"/>
-      <c r="F40" s="336"/>
+      <c r="E40" s="329"/>
+      <c r="F40" s="329"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -15734,8 +15730,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="168"/>
-      <c r="E49" s="336"/>
-      <c r="F49" s="336"/>
+      <c r="E49" s="329"/>
+      <c r="F49" s="329"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -15745,8 +15741,8 @@
         <v>-0.3</v>
       </c>
       <c r="D50" s="169"/>
-      <c r="E50" s="336"/>
-      <c r="F50" s="336"/>
+      <c r="E50" s="329"/>
+      <c r="F50" s="329"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -15760,8 +15756,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="336"/>
-      <c r="F51" s="336"/>
+      <c r="E51" s="329"/>
+      <c r="F51" s="329"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -15771,8 +15767,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="170"/>
-      <c r="E52" s="336"/>
-      <c r="F52" s="336"/>
+      <c r="E52" s="329"/>
+      <c r="F52" s="329"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="164" t="s">
@@ -15792,8 +15788,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="168"/>
-      <c r="E55" s="336"/>
-      <c r="F55" s="336"/>
+      <c r="E55" s="329"/>
+      <c r="F55" s="329"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -15803,8 +15799,8 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="169"/>
-      <c r="E56" s="336"/>
-      <c r="F56" s="336"/>
+      <c r="E56" s="329"/>
+      <c r="F56" s="329"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -15818,8 +15814,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="336"/>
-      <c r="F57" s="336"/>
+      <c r="E57" s="329"/>
+      <c r="F57" s="329"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -15829,8 +15825,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="170"/>
-      <c r="E58" s="336"/>
-      <c r="F58" s="336"/>
+      <c r="E58" s="329"/>
+      <c r="F58" s="329"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -15847,7 +15843,8 @@
       <c r="E60" s="103" t="s">
         <v>338</v>
       </c>
-      <c r="F60" s="324">
+      <c r="F60" s="332">
+        <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
@@ -15864,7 +15861,7 @@
       <c r="B63" s="112" t="s">
         <v>346</v>
       </c>
-      <c r="E63" s="291" t="s">
+      <c r="E63" s="290" t="s">
         <v>356</v>
       </c>
     </row>
@@ -15876,7 +15873,7 @@
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
-      <c r="E64" s="290" t="s">
+      <c r="E64" s="289" t="s">
         <v>357</v>
       </c>
     </row>
@@ -15888,7 +15885,7 @@
         <v>-8.7951517171891112E-3</v>
       </c>
       <c r="D65" s="155"/>
-      <c r="E65" s="290" t="s">
+      <c r="E65" s="289" t="s">
         <v>358</v>
       </c>
     </row>
@@ -15904,7 +15901,7 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="290" t="s">
+      <c r="E66" s="289" t="s">
         <v>359</v>
       </c>
     </row>
@@ -15912,7 +15909,7 @@
       <c r="B68" s="112" t="s">
         <v>333</v>
       </c>
-      <c r="E68" s="291" t="s">
+      <c r="E68" s="290" t="s">
         <v>360</v>
       </c>
     </row>
@@ -15934,7 +15931,7 @@
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
-      <c r="E70" s="290" t="s">
+      <c r="E70" s="289" t="s">
         <v>336</v>
       </c>
     </row>
@@ -15946,7 +15943,7 @@
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="290"/>
+      <c r="E71" s="289"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
@@ -15970,16 +15967,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B75" s="112" t="s">
         <v>136</v>
       </c>
-      <c r="E75" s="325" t="s">
-        <v>377</v>
-      </c>
-      <c r="F75" s="323"/>
-    </row>
-    <row r="76" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="283" t="s">
         <v>339</v>
       </c>
@@ -15988,14 +15981,8 @@
         <v>3</v>
       </c>
       <c r="D76" s="138"/>
-      <c r="E76" s="326" t="s">
-        <v>378</v>
-      </c>
-      <c r="F76" s="323" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="103" t="s">
         <v>122</v>
       </c>
@@ -16007,20 +15994,6 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E77" s="327" t="s">
-        <v>378</v>
-      </c>
-      <c r="F77" s="323" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="78" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E78" s="328" t="s">
-        <v>378</v>
-      </c>
-      <c r="F78" s="323" t="s">
-        <v>381</v>
-      </c>
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
@@ -16036,7 +16009,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
         <v>132</v>
       </c>
@@ -16048,7 +16021,7 @@
       <c r="E81" s="103"/>
       <c r="F81" s="103"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
         <v>133</v>
       </c>
@@ -16058,7 +16031,7 @@
       </c>
       <c r="D82" s="120"/>
     </row>
-    <row r="83" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
         <v>112</v>
       </c>
@@ -16078,15 +16051,15 @@
         <v>-0.30651291845707263</v>
       </c>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E84" s="124"/>
     </row>
-    <row r="85" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
         <v>342</v>
       </c>
@@ -16099,7 +16072,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
         <v>340</v>
       </c>
@@ -16108,11 +16081,46 @@
         <v>0.17143601630956429</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="103"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C90" s="121"/>
+    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E89" s="341" t="s">
+        <v>377</v>
+      </c>
+      <c r="F89" s="338"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="337"/>
+    </row>
+    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E90" s="334" t="s">
+        <v>378</v>
+      </c>
+      <c r="F90" s="339" t="s">
+        <v>379</v>
+      </c>
+      <c r="G90" s="2"/>
+      <c r="H90" s="337"/>
+    </row>
+    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E91" s="335" t="s">
+        <v>378</v>
+      </c>
+      <c r="F91" s="339" t="s">
+        <v>380</v>
+      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="337"/>
+    </row>
+    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E92" s="336" t="s">
+        <v>378</v>
+      </c>
+      <c r="F92" s="340" t="s">
+        <v>381</v>
+      </c>
+      <c r="G92" s="2"/>
+      <c r="H92" s="337"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B927457-BE0A-4A0B-B7AA-F3B7FD9C5F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88949521-9C60-419A-BFB1-5F7225EF1E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3301,36 +3301,6 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3352,6 +3322,36 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3645,7 +3645,7 @@
         <v>44</v>
       </c>
       <c r="C1" s="44">
-        <v>45730</v>
+        <v>1</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="292" t="s">
@@ -3750,13 +3750,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="323" t="s">
+      <c r="B12" s="333" t="s">
         <v>298</v>
       </c>
-      <c r="C12" s="323"/>
-      <c r="D12" s="323"/>
-      <c r="E12" s="323"/>
-      <c r="F12" s="323"/>
+      <c r="C12" s="333"/>
+      <c r="D12" s="333"/>
+      <c r="E12" s="333"/>
+      <c r="F12" s="333"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3828,7 +3828,7 @@
       <c r="D20" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="E20" s="333">
+      <c r="E20" s="323">
         <v>3</v>
       </c>
     </row>
@@ -3858,22 +3858,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="323" t="s">
+      <c r="B25" s="333" t="s">
         <v>243</v>
       </c>
-      <c r="C25" s="323"/>
-      <c r="D25" s="323"/>
-      <c r="E25" s="323"/>
-      <c r="F25" s="323"/>
+      <c r="C25" s="333"/>
+      <c r="D25" s="333"/>
+      <c r="E25" s="333"/>
+      <c r="F25" s="333"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="324" t="s">
+      <c r="B26" s="334" t="s">
         <v>264</v>
       </c>
-      <c r="C26" s="324"/>
-      <c r="D26" s="324"/>
-      <c r="E26" s="324"/>
-      <c r="F26" s="324"/>
+      <c r="C26" s="334"/>
+      <c r="D26" s="334"/>
+      <c r="E26" s="334"/>
+      <c r="F26" s="334"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3885,13 +3885,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="322" t="s">
+      <c r="B29" s="332" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="322"/>
-      <c r="D29" s="322"/>
-      <c r="E29" s="322"/>
-      <c r="F29" s="322"/>
+      <c r="C29" s="332"/>
+      <c r="D29" s="332"/>
+      <c r="E29" s="332"/>
+      <c r="F29" s="332"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3911,13 +3911,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="322" t="s">
+      <c r="B32" s="332" t="s">
         <v>247</v>
       </c>
-      <c r="C32" s="322"/>
-      <c r="D32" s="322"/>
-      <c r="E32" s="322"/>
-      <c r="F32" s="322"/>
+      <c r="C32" s="332"/>
+      <c r="D32" s="332"/>
+      <c r="E32" s="332"/>
+      <c r="F32" s="332"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3946,13 +3946,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="322" t="s">
+      <c r="B36" s="332" t="s">
         <v>250</v>
       </c>
-      <c r="C36" s="322"/>
-      <c r="D36" s="322"/>
-      <c r="E36" s="322"/>
-      <c r="F36" s="322"/>
+      <c r="C36" s="332"/>
+      <c r="D36" s="332"/>
+      <c r="E36" s="332"/>
+      <c r="F36" s="332"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3968,13 +3968,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="322" t="s">
+      <c r="B39" s="332" t="s">
         <v>254</v>
       </c>
-      <c r="C39" s="322"/>
-      <c r="D39" s="322"/>
-      <c r="E39" s="322"/>
-      <c r="F39" s="322"/>
+      <c r="C39" s="332"/>
+      <c r="D39" s="332"/>
+      <c r="E39" s="332"/>
+      <c r="F39" s="332"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4008,13 +4008,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="322" t="s">
+      <c r="B45" s="332" t="s">
         <v>255</v>
       </c>
-      <c r="C45" s="322"/>
-      <c r="D45" s="322"/>
-      <c r="E45" s="322"/>
-      <c r="F45" s="322"/>
+      <c r="C45" s="332"/>
+      <c r="D45" s="332"/>
+      <c r="E45" s="332"/>
+      <c r="F45" s="332"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4030,13 +4030,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="322" t="s">
+      <c r="B48" s="332" t="s">
         <v>258</v>
       </c>
-      <c r="C48" s="326"/>
-      <c r="D48" s="326"/>
-      <c r="E48" s="326"/>
-      <c r="F48" s="326"/>
+      <c r="C48" s="336"/>
+      <c r="D48" s="336"/>
+      <c r="E48" s="336"/>
+      <c r="F48" s="336"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4065,13 +4065,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="323" t="s">
+      <c r="B52" s="333" t="s">
         <v>280</v>
       </c>
-      <c r="C52" s="323"/>
-      <c r="D52" s="323"/>
-      <c r="E52" s="323"/>
-      <c r="F52" s="323"/>
+      <c r="C52" s="333"/>
+      <c r="D52" s="333"/>
+      <c r="E52" s="333"/>
+      <c r="F52" s="333"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4132,22 +4132,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="322" t="s">
+      <c r="B60" s="332" t="s">
         <v>315</v>
       </c>
-      <c r="C60" s="322"/>
-      <c r="D60" s="322"/>
-      <c r="E60" s="322"/>
-      <c r="F60" s="322"/>
+      <c r="C60" s="332"/>
+      <c r="D60" s="332"/>
+      <c r="E60" s="332"/>
+      <c r="F60" s="332"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="324" t="s">
+      <c r="B61" s="334" t="s">
         <v>271</v>
       </c>
-      <c r="C61" s="324"/>
-      <c r="D61" s="324"/>
-      <c r="E61" s="324"/>
-      <c r="F61" s="324"/>
+      <c r="C61" s="334"/>
+      <c r="D61" s="334"/>
+      <c r="E61" s="334"/>
+      <c r="F61" s="334"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4199,22 +4199,22 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="323" t="s">
+      <c r="B69" s="333" t="s">
         <v>323</v>
       </c>
-      <c r="C69" s="323"/>
-      <c r="D69" s="323"/>
-      <c r="E69" s="323"/>
-      <c r="F69" s="323"/>
+      <c r="C69" s="333"/>
+      <c r="D69" s="333"/>
+      <c r="E69" s="333"/>
+      <c r="F69" s="333"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="323" t="s">
+      <c r="B70" s="333" t="s">
         <v>270</v>
       </c>
-      <c r="C70" s="323"/>
-      <c r="D70" s="323"/>
-      <c r="E70" s="323"/>
-      <c r="F70" s="323"/>
+      <c r="C70" s="333"/>
+      <c r="D70" s="333"/>
+      <c r="E70" s="333"/>
+      <c r="F70" s="333"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4251,13 +4251,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="323" t="s">
+      <c r="B77" s="333" t="s">
         <v>273</v>
       </c>
-      <c r="C77" s="323"/>
-      <c r="D77" s="323"/>
-      <c r="E77" s="323"/>
-      <c r="F77" s="323"/>
+      <c r="C77" s="333"/>
+      <c r="D77" s="333"/>
+      <c r="E77" s="333"/>
+      <c r="F77" s="333"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4371,13 +4371,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="323" t="s">
+      <c r="B93" s="333" t="s">
         <v>279</v>
       </c>
-      <c r="C93" s="323"/>
-      <c r="D93" s="323"/>
-      <c r="E93" s="323"/>
-      <c r="F93" s="323"/>
+      <c r="C93" s="333"/>
+      <c r="D93" s="333"/>
+      <c r="E93" s="333"/>
+      <c r="F93" s="333"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4403,13 +4403,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="322" t="s">
+      <c r="B99" s="332" t="s">
         <v>384</v>
       </c>
-      <c r="C99" s="322"/>
-      <c r="D99" s="322"/>
-      <c r="E99" s="322"/>
-      <c r="F99" s="322"/>
+      <c r="C99" s="332"/>
+      <c r="D99" s="332"/>
+      <c r="E99" s="332"/>
+      <c r="F99" s="332"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4552,13 +4552,13 @@
       </c>
     </row>
     <row r="110" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B110" s="327" t="s">
+      <c r="B110" s="337" t="s">
         <v>385</v>
       </c>
-      <c r="C110" s="327"/>
-      <c r="D110" s="327"/>
-      <c r="E110" s="327"/>
-      <c r="F110" s="327"/>
+      <c r="C110" s="337"/>
+      <c r="D110" s="337"/>
+      <c r="E110" s="337"/>
+      <c r="F110" s="337"/>
     </row>
     <row r="112" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A112" s="254" t="s">
@@ -4571,13 +4571,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="325" t="s">
+      <c r="B114" s="335" t="s">
         <v>287</v>
       </c>
-      <c r="C114" s="325"/>
-      <c r="D114" s="325"/>
-      <c r="E114" s="325"/>
-      <c r="F114" s="325"/>
+      <c r="C114" s="335"/>
+      <c r="D114" s="335"/>
+      <c r="E114" s="335"/>
+      <c r="F114" s="335"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -5150,9 +5150,7 @@
       </c>
       <c r="F22" s="39"/>
       <c r="G22" s="39"/>
-      <c r="H22" s="39">
-        <v>1.1499999999999999</v>
-      </c>
+      <c r="H22" s="39"/>
       <c r="I22" s="39"/>
       <c r="J22" s="39"/>
       <c r="K22" s="39"/>
@@ -13750,10 +13748,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="328" t="s">
+      <c r="E6" s="338" t="s">
         <v>267</v>
       </c>
-      <c r="F6" s="328"/>
+      <c r="F6" s="338"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -13768,8 +13766,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="328"/>
-      <c r="F7" s="328"/>
+      <c r="E7" s="338"/>
+      <c r="F7" s="338"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -13784,8 +13782,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="328"/>
-      <c r="F8" s="328"/>
+      <c r="E8" s="338"/>
+      <c r="F8" s="338"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -13800,8 +13798,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="328"/>
-      <c r="F9" s="328"/>
+      <c r="E9" s="338"/>
+      <c r="F9" s="338"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15250,7 +15248,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="272">
-        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.57999999999999996</v>
       </c>
     </row>
@@ -15259,7 +15257,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="272">
-        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <f t="shared" si="0"/>
         <v>0.57999999999999996</v>
       </c>
     </row>
@@ -15279,7 +15277,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="272">
-        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <f t="shared" si="0"/>
         <v>11.22404343432521</v>
       </c>
     </row>
@@ -15295,16 +15293,16 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="330" t="str">
+      <c r="E7" s="340" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="330"/>
+      <c r="F7" s="340"/>
       <c r="H7" s="284">
         <v>4</v>
       </c>
       <c r="I7" s="272" t="str">
-        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15320,13 +15318,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="330"/>
-      <c r="F8" s="330"/>
+      <c r="E8" s="340"/>
+      <c r="F8" s="340"/>
       <c r="H8" s="284">
         <v>5</v>
       </c>
       <c r="I8" s="272" t="str">
-        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15342,24 +15340,24 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="330"/>
-      <c r="F9" s="330"/>
+      <c r="E9" s="340"/>
+      <c r="F9" s="340"/>
       <c r="H9" s="284">
         <v>6</v>
       </c>
       <c r="I9" s="272" t="str">
-        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="330"/>
-      <c r="F10" s="330"/>
+      <c r="E10" s="340"/>
+      <c r="F10" s="340"/>
       <c r="H10" s="284">
         <v>7</v>
       </c>
       <c r="I10" s="272" t="str">
-        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15367,13 +15365,13 @@
       <c r="B11" s="164" t="s">
         <v>307</v>
       </c>
-      <c r="E11" s="330"/>
-      <c r="F11" s="330"/>
+      <c r="E11" s="340"/>
+      <c r="F11" s="340"/>
       <c r="H11" s="284">
         <v>8</v>
       </c>
       <c r="I11" s="272" t="str">
-        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15386,13 +15384,13 @@
         <v>-0.28945840615733698</v>
       </c>
       <c r="D12" s="163"/>
-      <c r="E12" s="330"/>
-      <c r="F12" s="330"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
       <c r="H12" s="284">
         <v>9</v>
       </c>
       <c r="I12" s="272" t="str">
-        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15404,13 +15402,13 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.42686307479092267</v>
       </c>
-      <c r="E13" s="330"/>
-      <c r="F13" s="330"/>
+      <c r="E13" s="340"/>
+      <c r="F13" s="340"/>
       <c r="H13" s="284">
         <v>10</v>
       </c>
       <c r="I13" s="272" t="str">
-        <f>IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15422,8 +15420,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.22869925060693375</v>
       </c>
-      <c r="E14" s="330"/>
-      <c r="F14" s="330"/>
+      <c r="E14" s="340"/>
+      <c r="F14" s="340"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15449,21 +15447,21 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="330" t="s">
+      <c r="E18" s="340" t="s">
         <v>383</v>
       </c>
-      <c r="F18" s="331"/>
+      <c r="F18" s="341"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="331"/>
-      <c r="F19" s="331"/>
+      <c r="E19" s="341"/>
+      <c r="F19" s="341"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="164" t="s">
         <v>345</v>
       </c>
-      <c r="E20" s="331"/>
-      <c r="F20" s="331"/>
+      <c r="E20" s="341"/>
+      <c r="F20" s="341"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -15477,8 +15475,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="331"/>
-      <c r="F21" s="331"/>
+      <c r="E21" s="341"/>
+      <c r="F21" s="341"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -15492,8 +15490,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="331"/>
-      <c r="F22" s="331"/>
+      <c r="E22" s="341"/>
+      <c r="F22" s="341"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="164" t="s">
@@ -15513,8 +15511,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="168"/>
-      <c r="E25" s="329"/>
-      <c r="F25" s="329"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -15524,8 +15522,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="169"/>
-      <c r="E26" s="329"/>
-      <c r="F26" s="329"/>
+      <c r="E26" s="339"/>
+      <c r="F26" s="339"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -15539,8 +15537,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="329"/>
-      <c r="F27" s="329"/>
+      <c r="E27" s="339"/>
+      <c r="F27" s="339"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -15550,8 +15548,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="170"/>
-      <c r="E28" s="329"/>
-      <c r="F28" s="329"/>
+      <c r="E28" s="339"/>
+      <c r="F28" s="339"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="164" t="s">
@@ -15571,8 +15569,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="168"/>
-      <c r="E31" s="329"/>
-      <c r="F31" s="329"/>
+      <c r="E31" s="339"/>
+      <c r="F31" s="339"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -15582,8 +15580,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="169"/>
-      <c r="E32" s="329"/>
-      <c r="F32" s="329"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -15597,8 +15595,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="329"/>
-      <c r="F33" s="329"/>
+      <c r="E33" s="339"/>
+      <c r="F33" s="339"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -15608,8 +15606,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="170"/>
-      <c r="E34" s="329"/>
-      <c r="F34" s="329"/>
+      <c r="E34" s="339"/>
+      <c r="F34" s="339"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="164" t="s">
@@ -15629,8 +15627,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="168"/>
-      <c r="E37" s="329"/>
-      <c r="F37" s="329"/>
+      <c r="E37" s="339"/>
+      <c r="F37" s="339"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -15640,8 +15638,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="169"/>
-      <c r="E38" s="329"/>
-      <c r="F38" s="329"/>
+      <c r="E38" s="339"/>
+      <c r="F38" s="339"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -15655,8 +15653,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="329"/>
-      <c r="F39" s="329"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -15667,8 +15665,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="170"/>
-      <c r="E40" s="329"/>
-      <c r="F40" s="329"/>
+      <c r="E40" s="339"/>
+      <c r="F40" s="339"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -15730,8 +15728,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="168"/>
-      <c r="E49" s="329"/>
-      <c r="F49" s="329"/>
+      <c r="E49" s="339"/>
+      <c r="F49" s="339"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -15741,8 +15739,8 @@
         <v>-0.3</v>
       </c>
       <c r="D50" s="169"/>
-      <c r="E50" s="329"/>
-      <c r="F50" s="329"/>
+      <c r="E50" s="339"/>
+      <c r="F50" s="339"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -15756,8 +15754,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="329"/>
-      <c r="F51" s="329"/>
+      <c r="E51" s="339"/>
+      <c r="F51" s="339"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -15767,8 +15765,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="170"/>
-      <c r="E52" s="329"/>
-      <c r="F52" s="329"/>
+      <c r="E52" s="339"/>
+      <c r="F52" s="339"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="164" t="s">
@@ -15788,8 +15786,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="168"/>
-      <c r="E55" s="329"/>
-      <c r="F55" s="329"/>
+      <c r="E55" s="339"/>
+      <c r="F55" s="339"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -15799,8 +15797,8 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="169"/>
-      <c r="E56" s="329"/>
-      <c r="F56" s="329"/>
+      <c r="E56" s="339"/>
+      <c r="F56" s="339"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -15814,8 +15812,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="329"/>
-      <c r="F57" s="329"/>
+      <c r="E57" s="339"/>
+      <c r="F57" s="339"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -15825,8 +15823,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="170"/>
-      <c r="E58" s="329"/>
-      <c r="F58" s="329"/>
+      <c r="E58" s="339"/>
+      <c r="F58" s="339"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -15843,7 +15841,7 @@
       <c r="E60" s="103" t="s">
         <v>338</v>
       </c>
-      <c r="F60" s="332">
+      <c r="F60" s="322">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
@@ -16085,42 +16083,42 @@
       <c r="B88" s="103"/>
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="341" t="s">
+      <c r="E89" s="331" t="s">
         <v>377</v>
       </c>
-      <c r="F89" s="338"/>
+      <c r="F89" s="328"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="337"/>
+      <c r="H89" s="327"/>
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="334" t="s">
+      <c r="E90" s="324" t="s">
         <v>378</v>
       </c>
-      <c r="F90" s="339" t="s">
+      <c r="F90" s="329" t="s">
         <v>379</v>
       </c>
       <c r="G90" s="2"/>
-      <c r="H90" s="337"/>
+      <c r="H90" s="327"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="335" t="s">
+      <c r="E91" s="325" t="s">
         <v>378</v>
       </c>
-      <c r="F91" s="339" t="s">
+      <c r="F91" s="329" t="s">
         <v>380</v>
       </c>
       <c r="G91" s="2"/>
-      <c r="H91" s="337"/>
+      <c r="H91" s="327"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="336" t="s">
+      <c r="E92" s="326" t="s">
         <v>378</v>
       </c>
-      <c r="F92" s="340" t="s">
+      <c r="F92" s="330" t="s">
         <v>381</v>
       </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="337"/>
+      <c r="H92" s="327"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88949521-9C60-419A-BFB1-5F7225EF1E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2654A4E1-EDC1-4558-97C5-03A2B7E268B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -105,9 +105,6 @@
     <t>Biological assets</t>
   </si>
   <si>
-    <t>Intangible assets</t>
-  </si>
-  <si>
     <t>LT DTA</t>
   </si>
   <si>
@@ -125,10 +122,6 @@
   </si>
   <si>
     <t>Prepayments and Contract Assets</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PP&amp;E &amp; Right of Use Assets</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1966,6 +1959,14 @@
   </si>
   <si>
     <t>Note that this model prioritizes fundamental analysis when combined with supplementary market signal analysis. While market signal analysis predicts future trends, fundamental analysis interprets these trends and identifies relevant factors and possibilities.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PP&amp;E &amp; Other fixed assets related Items</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Intellectual assets</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3323,20 +3324,20 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3642,22 +3643,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C1" s="44">
         <v>1</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="292" t="s">
+        <v>360</v>
+      </c>
+      <c r="F1" s="293" t="s">
         <v>362</v>
-      </c>
-      <c r="F1" s="293" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="254" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3681,24 +3682,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C6" s="50">
         <v>7.9</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -3714,7 +3715,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C8" s="287">
         <v>6</v>
@@ -3724,7 +3725,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3750,28 +3751,28 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="333" t="s">
-        <v>298</v>
-      </c>
-      <c r="C12" s="333"/>
-      <c r="D12" s="333"/>
-      <c r="E12" s="333"/>
-      <c r="F12" s="333"/>
+      <c r="B12" s="332" t="s">
+        <v>296</v>
+      </c>
+      <c r="C12" s="332"/>
+      <c r="D12" s="332"/>
+      <c r="E12" s="332"/>
+      <c r="F12" s="332"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C15" s="32" t="str">
+        <v>346</v>
+      </c>
+      <c r="C15" s="32" t="e">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
-        <v>Negative Growth Asset Play</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E15" s="5"/>
     </row>
@@ -3780,7 +3781,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -3800,16 +3801,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C19" s="256">
         <v>0.2</v>
@@ -3821,12 +3822,12 @@
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="259">
+      <c r="C20" s="259" t="e">
         <f>C123</f>
-        <v>7.3815066170863481</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E20" s="323">
         <v>3</v>
@@ -3834,11 +3835,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C21" s="288">
+        <v>349</v>
+      </c>
+      <c r="C21" s="288" t="e">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17143601630956429</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3849,7 +3850,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="254" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -3858,26 +3859,26 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="333" t="s">
-        <v>243</v>
-      </c>
-      <c r="C25" s="333"/>
-      <c r="D25" s="333"/>
-      <c r="E25" s="333"/>
-      <c r="F25" s="333"/>
+      <c r="B25" s="332" t="s">
+        <v>241</v>
+      </c>
+      <c r="C25" s="332"/>
+      <c r="D25" s="332"/>
+      <c r="E25" s="332"/>
+      <c r="F25" s="332"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="334" t="s">
-        <v>264</v>
-      </c>
-      <c r="C26" s="334"/>
-      <c r="D26" s="334"/>
-      <c r="E26" s="334"/>
-      <c r="F26" s="334"/>
+      <c r="B26" s="336" t="s">
+        <v>262</v>
+      </c>
+      <c r="C26" s="336"/>
+      <c r="D26" s="336"/>
+      <c r="E26" s="336"/>
+      <c r="F26" s="336"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
@@ -3885,17 +3886,17 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="332" t="s">
-        <v>245</v>
-      </c>
-      <c r="C29" s="332"/>
-      <c r="D29" s="332"/>
-      <c r="E29" s="332"/>
-      <c r="F29" s="332"/>
+      <c r="B29" s="334" t="s">
+        <v>243</v>
+      </c>
+      <c r="C29" s="334"/>
+      <c r="D29" s="334"/>
+      <c r="E29" s="334"/>
+      <c r="F29" s="334"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C30" s="192">
         <f>Normalized_FCF!C8</f>
@@ -3911,21 +3912,21 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="332" t="s">
-        <v>247</v>
-      </c>
-      <c r="C32" s="332"/>
-      <c r="D32" s="332"/>
-      <c r="E32" s="332"/>
-      <c r="F32" s="332"/>
+      <c r="B32" s="334" t="s">
+        <v>245</v>
+      </c>
+      <c r="C32" s="334"/>
+      <c r="D32" s="334"/>
+      <c r="E32" s="334"/>
+      <c r="F32" s="334"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>248</v>
-      </c>
-      <c r="C33" s="192">
+        <v>246</v>
+      </c>
+      <c r="C33" s="192" t="e">
         <f>Normalized_FCF!C9</f>
-        <v>159.99999999999997</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>Reporting_currency</f>
@@ -3934,11 +3935,11 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>249</v>
-      </c>
-      <c r="C34" s="192">
+        <v>247</v>
+      </c>
+      <c r="C34" s="192" t="e">
         <f>Normalized_FCF!C10</f>
-        <v>-159.99999999999997</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
@@ -3946,21 +3947,21 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="332" t="s">
-        <v>250</v>
-      </c>
-      <c r="C36" s="332"/>
-      <c r="D36" s="332"/>
-      <c r="E36" s="332"/>
-      <c r="F36" s="332"/>
+      <c r="B36" s="334" t="s">
+        <v>248</v>
+      </c>
+      <c r="C36" s="334"/>
+      <c r="D36" s="334"/>
+      <c r="E36" s="334"/>
+      <c r="F36" s="334"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C37" s="192">
         <f>Normalized_FCF!C11</f>
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="D37" s="1" t="str">
         <f>Reporting_currency</f>
@@ -3968,21 +3969,21 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="332" t="s">
-        <v>254</v>
-      </c>
-      <c r="C39" s="332"/>
-      <c r="D39" s="332"/>
-      <c r="E39" s="332"/>
-      <c r="F39" s="332"/>
+      <c r="B39" s="334" t="s">
+        <v>252</v>
+      </c>
+      <c r="C39" s="334"/>
+      <c r="D39" s="334"/>
+      <c r="E39" s="334"/>
+      <c r="F39" s="334"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C40" s="192">
         <f>Normalized_FCF!C12</f>
-        <v>1387.37</v>
+        <v>0</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -3991,16 +3992,16 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C43" s="192">
         <f>Normalized_FCF!C15</f>
-        <v>-22.869707937042335</v>
+        <v>0</v>
       </c>
       <c r="D43" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4008,21 +4009,21 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="332" t="s">
-        <v>255</v>
-      </c>
-      <c r="C45" s="332"/>
-      <c r="D45" s="332"/>
-      <c r="E45" s="332"/>
-      <c r="F45" s="332"/>
+      <c r="B45" s="334" t="s">
+        <v>253</v>
+      </c>
+      <c r="C45" s="334"/>
+      <c r="D45" s="334"/>
+      <c r="E45" s="334"/>
+      <c r="F45" s="334"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C46" s="192">
         <f>Normalized_FCF!C14</f>
-        <v>-1108.3656622169851</v>
+        <v>-622.03686221698513</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4030,17 +4031,17 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="332" t="s">
-        <v>258</v>
-      </c>
-      <c r="C48" s="336"/>
-      <c r="D48" s="336"/>
-      <c r="E48" s="336"/>
-      <c r="F48" s="336"/>
+      <c r="B48" s="334" t="s">
+        <v>256</v>
+      </c>
+      <c r="C48" s="335"/>
+      <c r="D48" s="335"/>
+      <c r="E48" s="335"/>
+      <c r="F48" s="335"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C49" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4053,7 +4054,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="47" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C50" s="1">
         <f>Normalized_FCF!C18</f>
@@ -4065,17 +4066,17 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="333" t="s">
-        <v>280</v>
-      </c>
-      <c r="C52" s="333"/>
-      <c r="D52" s="333"/>
-      <c r="E52" s="333"/>
-      <c r="F52" s="333"/>
+      <c r="B52" s="332" t="s">
+        <v>278</v>
+      </c>
+      <c r="C52" s="332"/>
+      <c r="D52" s="332"/>
+      <c r="E52" s="332"/>
+      <c r="F52" s="332"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C53" s="192">
         <f>Normalized_FCF!G19</f>
@@ -4088,11 +4089,11 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B54" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C54" s="192">
+        <v>264</v>
+      </c>
+      <c r="C54" s="192" t="e">
         <f>Normalized_FCF!C19</f>
-        <v>3486.9548890834108</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D54" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4101,16 +4102,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B55" s="261" t="s">
-        <v>296</v>
-      </c>
-      <c r="C55" s="94">
+        <v>294</v>
+      </c>
+      <c r="C55" s="94" t="e">
         <f>Normalized_FCF!C120</f>
-        <v>5.401287075648549E-2</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="261" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
@@ -4119,7 +4120,7 @@
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A58" s="254" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B58" s="36"/>
       <c r="C58" s="36"/>
@@ -4132,31 +4133,31 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="332" t="s">
-        <v>315</v>
-      </c>
-      <c r="C60" s="332"/>
-      <c r="D60" s="332"/>
-      <c r="E60" s="332"/>
-      <c r="F60" s="332"/>
+      <c r="B60" s="334" t="s">
+        <v>313</v>
+      </c>
+      <c r="C60" s="334"/>
+      <c r="D60" s="334"/>
+      <c r="E60" s="334"/>
+      <c r="F60" s="334"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="334" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="334"/>
-      <c r="D61" s="334"/>
-      <c r="E61" s="334"/>
-      <c r="F61" s="334"/>
+      <c r="B61" s="336" t="s">
+        <v>269</v>
+      </c>
+      <c r="C61" s="336"/>
+      <c r="D61" s="336"/>
+      <c r="E61" s="336"/>
+      <c r="F61" s="336"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C64" s="321">
         <v>0.08</v>
@@ -4164,31 +4165,31 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C65" s="271">
         <f>IF(D65="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D65" s="295" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C66" s="271">
         <f>IF(D66="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D66" s="295" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="82" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C67" s="271">
         <f>SUM(C64:C66)</f>
@@ -4199,26 +4200,26 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="333" t="s">
-        <v>323</v>
-      </c>
-      <c r="C69" s="333"/>
-      <c r="D69" s="333"/>
-      <c r="E69" s="333"/>
-      <c r="F69" s="333"/>
+      <c r="B69" s="332" t="s">
+        <v>321</v>
+      </c>
+      <c r="C69" s="332"/>
+      <c r="D69" s="332"/>
+      <c r="E69" s="332"/>
+      <c r="F69" s="332"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="333" t="s">
-        <v>270</v>
-      </c>
-      <c r="C70" s="333"/>
-      <c r="D70" s="333"/>
-      <c r="E70" s="333"/>
-      <c r="F70" s="333"/>
+      <c r="B70" s="332" t="s">
+        <v>268</v>
+      </c>
+      <c r="C70" s="332"/>
+      <c r="D70" s="332"/>
+      <c r="E70" s="332"/>
+      <c r="F70" s="332"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C71" s="271">
         <v>0</v>
@@ -4226,11 +4227,11 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B73" s="47" t="s">
-        <v>313</v>
-      </c>
-      <c r="C73" s="255">
+        <v>311</v>
+      </c>
+      <c r="C73" s="255" t="e">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>4.7411297664026151</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D73" s="1" t="str">
         <f>Market_currency</f>
@@ -4239,7 +4240,7 @@
     </row>
     <row r="75" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A75" s="254" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B75" s="36"/>
       <c r="C75" s="36"/>
@@ -4251,31 +4252,31 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="333" t="s">
-        <v>273</v>
-      </c>
-      <c r="C77" s="333"/>
-      <c r="D77" s="333"/>
-      <c r="E77" s="333"/>
-      <c r="F77" s="333"/>
+      <c r="B77" s="332" t="s">
+        <v>271</v>
+      </c>
+      <c r="C77" s="332"/>
+      <c r="D77" s="332"/>
+      <c r="E77" s="332"/>
+      <c r="F77" s="332"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B80" s="241" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="47" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C81" s="192">
         <f>Valuation_Model!C7</f>
-        <v>3093</v>
+        <v>0</v>
       </c>
       <c r="D81" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4284,11 +4285,11 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="47" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C82" s="255">
         <f>C81*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.37849307922088393</v>
+        <v>0</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4297,16 +4298,16 @@
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C85" s="192">
         <f>BS!C66</f>
-        <v>47679</v>
+        <v>0</v>
       </c>
       <c r="D85" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4315,11 +4316,11 @@
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C86" s="192">
         <f>Valuation_Model!C8</f>
-        <v>44592.410129618722</v>
+        <v>-514.43164506354685</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4328,11 +4329,11 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C87" s="255">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>5.4568117102618574</v>
+        <v>-6.2951444354596403E-2</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4341,16 +4342,16 @@
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C90" s="192">
         <f>Valuation_Model!C9</f>
-        <v>7814.4</v>
+        <v>0</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4359,11 +4360,11 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C91" s="255">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.95625487173090062</v>
+        <v>0</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Market_currency</f>
@@ -4371,21 +4372,21 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="333" t="s">
-        <v>279</v>
-      </c>
-      <c r="C93" s="333"/>
-      <c r="D93" s="333"/>
-      <c r="E93" s="333"/>
-      <c r="F93" s="333"/>
+      <c r="B93" s="332" t="s">
+        <v>277</v>
+      </c>
+      <c r="C93" s="332"/>
+      <c r="D93" s="332"/>
+      <c r="E93" s="332"/>
+      <c r="F93" s="332"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
-        <v>312</v>
-      </c>
-      <c r="C95" s="255">
+        <v>310</v>
+      </c>
+      <c r="C95" s="255" t="e">
         <f>Valuation_Model!C12</f>
-        <v>10.775703269174489</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4394,7 +4395,7 @@
     </row>
     <row r="97" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A97" s="254" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B97" s="36"/>
       <c r="C97" s="36"/>
@@ -4403,29 +4404,29 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="332" t="s">
-        <v>384</v>
-      </c>
-      <c r="C99" s="332"/>
-      <c r="D99" s="332"/>
-      <c r="E99" s="332"/>
-      <c r="F99" s="332"/>
+      <c r="B99" s="334" t="s">
+        <v>382</v>
+      </c>
+      <c r="C99" s="334"/>
+      <c r="D99" s="334"/>
+      <c r="E99" s="334"/>
+      <c r="F99" s="334"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C101" s="267" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D101" s="267" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E101" s="267" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F101" s="267" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
@@ -4441,9 +4442,9 @@
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E102" s="265" t="str">
+      <c r="E102" s="265" t="e">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>12.21 HKD</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F102" s="266">
         <f>Valuation_Model!F74</f>
@@ -4463,9 +4464,9 @@
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E103" s="252" t="str">
+      <c r="E103" s="252" t="e">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>11.09 HKD</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F103" s="253">
         <f>Valuation_Model!F75</f>
@@ -4485,9 +4486,9 @@
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E104" s="252" t="str">
+      <c r="E104" s="252" t="e">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>10.78 HKD</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F104" s="253">
         <f>Valuation_Model!F76</f>
@@ -4507,9 +4508,9 @@
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E105" s="252" t="str">
+      <c r="E105" s="252" t="e">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>10.1 HKD</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F105" s="253">
         <f>Valuation_Model!F77</f>
@@ -4529,9 +4530,9 @@
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E106" s="252" t="str">
+      <c r="E106" s="252" t="e">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>7.71 HKD</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F106" s="253">
         <f>Valuation_Model!F78</f>
@@ -4540,11 +4541,11 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B108" s="242" t="s">
-        <v>281</v>
-      </c>
-      <c r="C108" s="248">
+        <v>279</v>
+      </c>
+      <c r="C108" s="248" t="e">
         <f>Scenarios!C60</f>
-        <v>10.64404343432521</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D108" s="243" t="str">
         <f>Market_currency</f>
@@ -4553,7 +4554,7 @@
     </row>
     <row r="110" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B110" s="337" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C110" s="337"/>
       <c r="D110" s="337"/>
@@ -4562,7 +4563,7 @@
     </row>
     <row r="112" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A112" s="254" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B112" s="36"/>
       <c r="C112" s="36"/>
@@ -4571,22 +4572,22 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="335" t="s">
-        <v>287</v>
-      </c>
-      <c r="C114" s="335"/>
-      <c r="D114" s="335"/>
-      <c r="E114" s="335"/>
-      <c r="F114" s="335"/>
+      <c r="B114" s="333" t="s">
+        <v>285</v>
+      </c>
+      <c r="C114" s="333"/>
+      <c r="D114" s="333"/>
+      <c r="E114" s="333"/>
+      <c r="F114" s="333"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B116" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C116" s="258">
         <f>E20</f>
@@ -4595,7 +4596,7 @@
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B117" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C117" s="257">
         <f>C19</f>
@@ -4604,7 +4605,7 @@
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B118" s="243" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C118" s="244">
         <f>Scenarios!C77</f>
@@ -4617,7 +4618,7 @@
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B120" s="241" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.35">
@@ -4635,18 +4636,18 @@
         <f>"+ PV(Equity Value realized at year "&amp;C116&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C122" s="247">
+      <c r="C122" s="247" t="e">
         <f>Scenarios!C82</f>
-        <v>6.1597473578270892</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B123" s="82" t="s">
-        <v>283</v>
-      </c>
-      <c r="C123" s="246">
+        <v>281</v>
+      </c>
+      <c r="C123" s="246" t="e">
         <f>Scenarios!C83</f>
-        <v>7.3815066170863481</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D123" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4655,15 +4656,21 @@
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B124" s="245" t="s">
-        <v>285</v>
-      </c>
-      <c r="C124" s="158">
+        <v>283</v>
+      </c>
+      <c r="C124" s="158" t="e">
         <f>Scenarios!F83</f>
-        <v>-0.30651291845707263</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4677,12 +4684,6 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4766,7 +4767,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -4782,7 +4783,7 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" s="109">
         <v>1000000</v>
@@ -4816,7 +4817,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="194">
         <v>5344</v>
@@ -4842,7 +4843,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C6" s="194">
         <v>1084</v>
@@ -4866,7 +4867,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C7" s="195"/>
       <c r="D7" s="193"/>
@@ -4882,7 +4883,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" s="194"/>
       <c r="D8" s="185"/>
@@ -4898,7 +4899,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C9" s="194">
         <v>639</v>
@@ -4918,7 +4919,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C10" s="194"/>
       <c r="D10" s="185"/>
@@ -4934,7 +4935,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C11" s="194"/>
       <c r="D11" s="185"/>
@@ -4950,7 +4951,7 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" s="194">
         <v>43</v>
@@ -4974,7 +4975,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13" s="194">
         <v>2340</v>
@@ -4998,7 +4999,7 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C14" s="194">
         <v>519</v>
@@ -5022,7 +5023,7 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C15" s="196">
         <v>4251</v>
@@ -5046,7 +5047,7 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C16" s="194">
         <v>-151</v>
@@ -5066,13 +5067,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C19" s="185">
         <v>160</v>
@@ -5096,7 +5097,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C20" s="185">
         <v>69</v>
@@ -5116,7 +5117,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C21" s="185">
         <v>910</v>
@@ -5159,13 +5160,13 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="187"/>
       <c r="D25" s="185">
@@ -5183,7 +5184,7 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C26" s="187"/>
       <c r="D26" s="185">
@@ -5201,7 +5202,7 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" s="186">
         <v>14028</v>
@@ -5221,7 +5222,7 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28" s="186">
         <v>166316</v>
@@ -5241,7 +5242,7 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C29" s="185"/>
       <c r="D29" s="185"/>
@@ -5257,13 +5258,13 @@
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C31" s="9"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C32" s="185"/>
       <c r="D32" s="185"/>
@@ -5279,7 +5280,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -5295,7 +5296,7 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.35">
@@ -5349,7 +5350,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C37" s="187">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -5398,7 +5399,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="31" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C38" s="188">
         <f>IF(C36="","",C36+C37)</f>
@@ -5447,7 +5448,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C39" s="187">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -5496,7 +5497,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="70" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C40" s="189">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -5545,7 +5546,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="70" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C41" s="189">
         <f>IF(C$4="","",C39-C40)</f>
@@ -5594,7 +5595,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C42" s="187">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -5643,7 +5644,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="43" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C43" s="190">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -5692,7 +5693,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="43" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C44" s="191">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -5741,7 +5742,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="40" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C45" s="192">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -5790,7 +5791,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C46" s="187">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -5839,7 +5840,7 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C47" s="190">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -5888,7 +5889,7 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C48" s="187">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -5937,12 +5938,12 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C51" s="187">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -5991,7 +5992,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="40" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C52" s="187">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6040,12 +6041,12 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="179" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="40" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C55" s="192">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6094,7 +6095,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C56" s="192">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6143,7 +6144,7 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C57" s="192">
         <f>IF(C$4="","",C11)</f>
@@ -6192,7 +6193,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C58" s="192">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -6241,13 +6242,13 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C61" s="187">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
@@ -6296,7 +6297,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C62" s="187">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
@@ -6345,7 +6346,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C63" s="187">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
@@ -6394,7 +6395,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C64" s="75">
         <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C22)</f>
@@ -6443,7 +6444,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="93" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -6698,7 +6699,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="36" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
@@ -6714,7 +6715,7 @@
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B74" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C74" s="9"/>
     </row>
@@ -6769,7 +6770,7 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="95" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
@@ -6803,7 +6804,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C77" s="74">
         <f t="shared" si="39"/>
@@ -6837,7 +6838,7 @@
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B78" s="26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C78" s="58">
         <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
@@ -6886,7 +6887,7 @@
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C79" s="58">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C28)</f>
@@ -6978,7 +6979,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C1" s="102">
         <v>45473</v>
@@ -6994,7 +6995,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7005,40 +7006,40 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C3" s="210" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D3" s="211" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G3" s="210" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H3" s="211" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="19">
-        <v>8029</v>
+        <v>0</v>
       </c>
       <c r="D4" s="304">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G4" s="19">
-        <v>45665</v>
+        <v>0</v>
       </c>
       <c r="H4" s="304">
         <v>0.9</v>
@@ -7046,7 +7047,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -7056,10 +7057,10 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G5" s="19">
-        <v>2014</v>
+        <v>0</v>
       </c>
       <c r="H5" s="304">
         <v>0.7</v>
@@ -7070,17 +7071,17 @@
         <v>11</v>
       </c>
       <c r="C6" s="19">
-        <v>9844</v>
+        <v>0</v>
       </c>
       <c r="D6" s="304">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G6" s="19">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H6" s="304">
         <v>0.6</v>
@@ -7088,17 +7089,17 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" s="19">
-        <v>5466</v>
+        <v>0</v>
       </c>
       <c r="D7" s="304">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -7109,7 +7110,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -7119,7 +7120,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -7130,7 +7131,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="19">
         <v>0</v>
@@ -7140,7 +7141,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -7175,26 +7176,26 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
-        <v>23349</v>
+        <v>10</v>
       </c>
       <c r="D12" s="20">
         <f>C4*D4+C5*D5+C9*D9+C6*D6+C8*D8+C7*D7+C10*D10+C11*D11</f>
-        <v>13028</v>
+        <v>9</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
-        <v>47835</v>
+        <v>0</v>
       </c>
       <c r="H12" s="20">
         <f>G4*H4+G5*H5+G6*H6+G7*H7+G8*H8+G9*H9</f>
-        <v>42601.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7204,36 +7205,36 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C14" s="210" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D14" s="211" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G14" s="210" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H14" s="211" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C15" s="19">
-        <v>2757</v>
+        <v>0</v>
       </c>
       <c r="D15" s="304">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -7244,7 +7245,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -7253,10 +7254,10 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G16" s="19">
-        <v>1373</v>
+        <v>0</v>
       </c>
       <c r="H16" s="304">
         <v>0.6</v>
@@ -7264,19 +7265,19 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C17" s="19">
-        <v>67668</v>
+        <v>0</v>
       </c>
       <c r="D17" s="304">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G17" s="19">
-        <v>13024</v>
+        <v>0</v>
       </c>
       <c r="H17" s="304">
         <v>0.6</v>
@@ -7284,7 +7285,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -7293,10 +7294,10 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G18" s="19">
-        <v>23696</v>
+        <v>0</v>
       </c>
       <c r="H18" s="304">
         <v>0.1</v>
@@ -7304,16 +7305,16 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
-        <v>27</v>
+        <v>384</v>
       </c>
       <c r="C19" s="19">
-        <v>1284</v>
+        <v>0</v>
       </c>
       <c r="D19" s="304">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -7333,7 +7334,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -7344,7 +7345,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
-        <v>20</v>
+        <v>385</v>
       </c>
       <c r="C21" s="19">
         <v>0</v>
@@ -7353,7 +7354,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -7364,10 +7365,10 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" s="19">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D22" s="304">
         <v>0.9</v>
@@ -7376,7 +7377,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" s="19">
         <v>0</v>
@@ -7388,43 +7389,43 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
-        <v>71719</v>
+        <v>0</v>
       </c>
       <c r="D24" s="20">
         <f>C15*D15+C16*D16+C18*D18+C17*D17+C19*D19+C20*D20+C21*D21+C22*D22+C23*D23</f>
-        <v>41841</v>
+        <v>0</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
-        <v>38093</v>
+        <v>0</v>
       </c>
       <c r="H24" s="20">
         <f>G15*H15+G16*H16+G17*H17+G18*H18+G19*H19+G20*H20+G21*H21</f>
-        <v>11007.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C26" s="210" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F26" s="212" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G26" s="213" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H26" s="214" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7432,18 +7433,18 @@
         <v>6</v>
       </c>
       <c r="C27" s="19">
-        <v>967</v>
+        <v>0</v>
       </c>
       <c r="F27" s="215" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
-        <v>167107</v>
+        <v>10</v>
       </c>
       <c r="H27" s="216">
         <f>H32-G30</f>
-        <v>94589.7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7451,13 +7452,13 @@
         <v>7</v>
       </c>
       <c r="C28" s="19">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F28" s="217" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G28" s="185">
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="H28" s="216"/>
     </row>
@@ -7469,15 +7470,15 @@
         <v>0</v>
       </c>
       <c r="F29" s="218" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
-        <v>166588</v>
+        <v>10</v>
       </c>
       <c r="H29" s="216">
         <f>H27-G28</f>
-        <v>94070.7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7488,28 +7489,28 @@
         <v>0</v>
       </c>
       <c r="F30" s="215" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
-        <v>13889</v>
+        <v>0</v>
       </c>
       <c r="H30" s="216"/>
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
-        <v>1004</v>
+        <v>0</v>
       </c>
       <c r="F31" s="218" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G31" s="219">
         <f>C31+C40</f>
-        <v>3093</v>
+        <v>0</v>
       </c>
       <c r="H31" s="216"/>
     </row>
@@ -7519,18 +7520,18 @@
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
-        <v>8048</v>
+        <v>0</v>
       </c>
       <c r="F32" s="220" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G32" s="221">
         <f>G35+G40</f>
-        <v>180996</v>
+        <v>10</v>
       </c>
       <c r="H32" s="216">
         <f>H35+H40</f>
-        <v>108478.7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7538,7 +7539,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="86">
-        <v>9052</v>
+        <v>0</v>
       </c>
       <c r="F33" s="222"/>
       <c r="G33" s="2"/>
@@ -7548,32 +7549,32 @@
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="224" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G34" s="225" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H34" s="226" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C35" s="210" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F35" s="227" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G35" s="221">
         <f>C12+C24</f>
-        <v>95068</v>
+        <v>10</v>
       </c>
       <c r="H35" s="228">
         <f>D12+D24</f>
-        <v>54869</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7581,14 +7582,14 @@
         <v>14</v>
       </c>
       <c r="C36" s="19">
-        <v>832</v>
+        <v>0</v>
       </c>
       <c r="F36" s="218" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G36" s="219">
         <f>C4+C15</f>
-        <v>10786</v>
+        <v>0</v>
       </c>
       <c r="H36" s="223"/>
     </row>
@@ -7597,14 +7598,14 @@
         <v>15</v>
       </c>
       <c r="C37" s="19">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F37" s="218" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G37" s="219">
         <f>C6</f>
-        <v>9844</v>
+        <v>0</v>
       </c>
       <c r="H37" s="223"/>
     </row>
@@ -7613,14 +7614,14 @@
         <v>16</v>
       </c>
       <c r="C38" s="19">
-        <v>1230</v>
+        <v>0</v>
       </c>
       <c r="F38" s="218" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G38" s="219">
         <f>C7+C17</f>
-        <v>73134</v>
+        <v>0</v>
       </c>
       <c r="H38" s="223"/>
     </row>
@@ -7632,35 +7633,35 @@
         <v>0</v>
       </c>
       <c r="F39" s="218" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G39" s="219">
         <f>C7+C17+C19+C20</f>
-        <v>74418</v>
+        <v>0</v>
       </c>
       <c r="H39" s="216">
         <f>C7*D7+C17*D17+C19*D19+C20*D20</f>
-        <v>44008.799999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
-        <v>2089</v>
+        <v>0</v>
       </c>
       <c r="F40" s="227" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G40" s="221">
         <f>G12+G24</f>
-        <v>85928</v>
+        <v>0</v>
       </c>
       <c r="H40" s="228">
         <f>H12+H24</f>
-        <v>53609.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7669,42 +7670,42 @@
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
-        <v>2748</v>
+        <v>0</v>
       </c>
       <c r="F41" s="218" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G41" s="219">
         <f>C70</f>
-        <v>72904</v>
+        <v>0</v>
       </c>
       <c r="H41" s="228">
         <f>H40-H42</f>
-        <v>45795.299999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="86">
-        <v>4837</v>
+        <v>0</v>
       </c>
       <c r="F42" s="229" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G42" s="230">
         <f>C82</f>
-        <v>13024</v>
+        <v>0</v>
       </c>
       <c r="H42" s="231">
         <f>D82</f>
-        <v>7814.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="81" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -7715,29 +7716,29 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C45" s="268" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D45" s="210" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F45" s="296" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C46" s="192">
         <f>G29</f>
-        <v>166588</v>
+        <v>10</v>
       </c>
       <c r="D46" s="192">
         <f>H29</f>
-        <v>94070.7</v>
+        <v>9</v>
       </c>
       <c r="F46" s="291"/>
     </row>
@@ -7748,11 +7749,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>20.385517323391081</v>
+        <v>1.2237086298767666E-3</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.511512740854835</v>
+        <v>1.10133776688909E-3</v>
       </c>
       <c r="F47" s="291"/>
     </row>
@@ -7761,39 +7762,39 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="162" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C49" s="269" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D49" s="225" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="291"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
-        <v>1.1933697905849452</v>
+        <v>0</v>
       </c>
       <c r="D50" s="98">
         <f>G31/Normalized_FCF!G8</f>
-        <v>1.3234916559691912</v>
+        <v>0</v>
       </c>
       <c r="F50" s="291"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C51" s="209"/>
       <c r="D51" s="94">
         <f>G29/G32</f>
-        <v>0.92039603085151056</v>
+        <v>1</v>
       </c>
       <c r="F51" s="291"/>
     </row>
@@ -7802,41 +7803,41 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="162" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C53" s="269" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D53" s="225" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F53" s="291"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
-        <v>2.7262804090098017E-2</v>
+        <v>259.18202592374382</v>
       </c>
       <c r="D54" s="94">
         <f>Normalized_FCF!G8/G35</f>
-        <v>2.4582404173854506E-2</v>
+        <v>233.7</v>
       </c>
       <c r="F54" s="291"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C55" s="94">
+        <v>150</v>
+      </c>
+      <c r="C55" s="94" t="e">
         <f>Normalized_FCF!C11/G40</f>
-        <v>7.4364584303137507E-3</v>
-      </c>
-      <c r="D55" s="94">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D55" s="94" t="e">
         <f>Normalized_FCF!G11/G40</f>
-        <v>7.4364584303137507E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F55" s="291"/>
     </row>
@@ -7845,35 +7846,35 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="162" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C57" s="269" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D57" s="225" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F57" s="291"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C58" s="101"/>
-      <c r="D58" s="23">
+      <c r="D58" s="23" t="e">
         <f>Normalized_FCF!G9/BS!$G$39</f>
-        <v>2.1500174688919346E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F58" s="5"/>
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C59" s="101"/>
       <c r="D59" s="94">
         <f>G39/G32</f>
-        <v>0.41115825764105285</v>
+        <v>0</v>
       </c>
       <c r="F59" s="291"/>
     </row>
@@ -7882,35 +7883,35 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="162" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C61" s="269" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D61" s="225" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F61" s="291"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
-        <v>3.1154705020769802E-3</v>
+        <v>0</v>
       </c>
       <c r="D62" s="94">
         <f>G28/G29</f>
-        <v>3.1154705020769802E-3</v>
+        <v>0</v>
       </c>
       <c r="F62" s="291" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="81" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -7921,57 +7922,57 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C65" s="268" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D65" s="211" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F65" s="296" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="108" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
-        <v>47679</v>
+        <v>0</v>
       </c>
       <c r="D66" s="192">
         <f>C66+D75</f>
-        <v>44592.410129618722</v>
+        <v>-514.43164506354685</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="108" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
-        <v>1529</v>
+        <v>0</v>
       </c>
       <c r="F67" s="291"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
-        <v>23696</v>
+        <v>0</v>
       </c>
       <c r="F68" s="291"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -7981,11 +7982,11 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
-        <v>72904</v>
+        <v>0</v>
       </c>
       <c r="F70" s="291"/>
     </row>
@@ -7994,19 +7995,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="294" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C72" s="268" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D72" s="210" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F72" s="291"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C73" s="192">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
@@ -8019,44 +8020,44 @@
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="297" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C74" s="298">
         <f>-$C$66/C73</f>
-        <v>89.008711885500944</v>
+        <v>0</v>
       </c>
       <c r="D74" s="298">
         <f>-$C$66/D73</f>
-        <v>92.682867505381196</v>
+        <v>0</v>
       </c>
       <c r="F74" s="291" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C75" s="303"/>
       <c r="D75" s="302">
         <f>MIN(D73*D76,-G5)</f>
-        <v>-3086.5898703812809</v>
+        <v>-514.43164506354685</v>
       </c>
       <c r="F75" s="291" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="299" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C76" s="300"/>
       <c r="D76" s="301">
         <f>IF(D74&lt;=3,1,IF(D74&gt;12,6,2))</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F76" s="291" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8064,33 +8065,33 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C78" s="268" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D78" s="211" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F78" s="291"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
-        <v>13024</v>
+        <v>0</v>
       </c>
       <c r="D79" s="192">
         <f>G7*H7+G17*H17</f>
-        <v>7814.4</v>
+        <v>0</v>
       </c>
       <c r="F79" s="291"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8104,7 +8105,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8118,21 +8119,21 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
-        <v>13024</v>
+        <v>0</v>
       </c>
       <c r="D82" s="83">
         <f>SUM(D79:D81)</f>
-        <v>7814.4</v>
+        <v>0</v>
       </c>
       <c r="F82" s="291"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8143,23 +8144,23 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D85" s="278" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="275" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C86" s="192">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-3093</v>
+        <v>0</v>
       </c>
       <c r="D86" s="255">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-0.37849307922088393</v>
+        <v>0</v>
       </c>
       <c r="E86" s="277" t="str">
         <f>Market_currency</f>
@@ -8168,15 +8169,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="275" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C87" s="192">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>44592.410129618722</v>
+        <v>-514.43164506354685</v>
       </c>
       <c r="D87" s="255">
         <f>C87*$H$1/Common_Shares</f>
-        <v>5.4568117102618574</v>
+        <v>-6.2951444354596403E-2</v>
       </c>
       <c r="E87" s="277" t="str">
         <f>Market_currency</f>
@@ -8185,15 +8186,15 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="276" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C88" s="192">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>7814.4</v>
+        <v>0</v>
       </c>
       <c r="D88" s="255">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.95625487173090062</v>
+        <v>0</v>
       </c>
       <c r="E88" s="277" t="str">
         <f>Market_currency</f>
@@ -8202,15 +8203,15 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C89" s="191">
         <f>SUM(C86:C88)</f>
-        <v>49313.810129618723</v>
+        <v>-514.43164506354685</v>
       </c>
       <c r="D89" s="279">
         <f>SUM(D86:D88)</f>
-        <v>6.0345735027718739</v>
+        <v>-6.2951444354596403E-2</v>
       </c>
       <c r="E89" s="277" t="str">
         <f>Market_currency</f>
@@ -8250,7 +8251,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -8303,12 +8304,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="67" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -8326,7 +8327,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
@@ -8397,7 +8398,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5" s="198">
         <f>C25</f>
@@ -8452,7 +8453,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6" s="188">
         <f>C4+C5</f>
@@ -8507,7 +8508,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C7" s="198">
         <f>C35</f>
@@ -8562,7 +8563,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C8" s="199">
         <f>C6+C7</f>
@@ -8619,11 +8620,11 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="198">
+        <v>67</v>
+      </c>
+      <c r="C9" s="198" t="e">
         <f>BS!$G$39*BS!D58</f>
-        <v>159.99999999999997</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E9" s="312"/>
       <c r="G9" s="198">
@@ -8674,11 +8675,11 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="198">
+        <v>88</v>
+      </c>
+      <c r="C10" s="198" t="e">
         <f>-C4*C77</f>
-        <v>-159.99999999999997</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E10" s="312"/>
       <c r="G10" s="198">
@@ -8729,11 +8730,11 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C11" s="200">
         <f>C62</f>
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="D11" s="173"/>
       <c r="E11" s="311"/>
@@ -8786,11 +8787,11 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" s="198">
         <f>C49</f>
-        <v>1387.37</v>
+        <v>0</v>
       </c>
       <c r="E12" s="312"/>
       <c r="G12" s="198">
@@ -8841,11 +8842,11 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="71" t="s">
-        <v>175</v>
-      </c>
-      <c r="C13" s="188">
+        <v>173</v>
+      </c>
+      <c r="C13" s="188" t="e">
         <f>SUM(C8:C12)</f>
-        <v>4618.1902592374381</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E13" s="312"/>
       <c r="G13" s="188">
@@ -8896,11 +8897,11 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C14" s="198">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1108.3656622169851</v>
+        <v>-622.03686221698513</v>
       </c>
       <c r="E14" s="312"/>
       <c r="G14" s="198">
@@ -8951,11 +8952,11 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C15" s="198">
         <f>-C4*C82</f>
-        <v>-22.869707937042335</v>
+        <v>0</v>
       </c>
       <c r="D15" s="61"/>
       <c r="E15" s="319"/>
@@ -9008,11 +9009,11 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="C16" s="201">
+        <v>163</v>
+      </c>
+      <c r="C16" s="201" t="e">
         <f>SUM(C13:C15)</f>
-        <v>3486.9548890834108</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D16" s="62"/>
       <c r="E16" s="320"/>
@@ -9065,7 +9066,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C17" s="198">
         <f>-C4*C84</f>
@@ -9073,7 +9074,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="311" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="202"/>
@@ -9091,7 +9092,7 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C18" s="198">
         <f>-C4*C85</f>
@@ -9099,7 +9100,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="311" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="203"/>
@@ -9117,11 +9118,11 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="188">
+        <v>68</v>
+      </c>
+      <c r="C19" s="188" t="e">
         <f>SUM(C16:C18)</f>
-        <v>3486.9548890834108</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="309"/>
@@ -9193,12 +9194,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="67" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9216,7 +9217,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="65" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
@@ -9237,7 +9238,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C23" s="204">
         <f>-C4*C28</f>
@@ -9294,7 +9295,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="69" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C24" s="198">
         <f>-C4*C29</f>
@@ -9351,7 +9352,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="71" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C25" s="188">
         <f>C23+C24</f>
@@ -9412,14 +9413,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E27" s="312"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:H28)</f>
@@ -9427,7 +9428,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="310" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9487,7 +9488,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="310" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9538,7 +9539,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="71" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
@@ -9597,21 +9598,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E32" s="312"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C33" s="205">
         <f>AVERAGE(G33:H33)</f>
         <v>-1106.5</v>
       </c>
       <c r="E33" s="310" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G33" s="198">
         <f>Data!C41</f>
@@ -9661,7 +9662,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C34" s="205">
         <f>AVERAGE(G34:J34)</f>
@@ -9669,7 +9670,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="310" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="187">
@@ -9720,7 +9721,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="71" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C35" s="188">
         <f>C33+C34</f>
@@ -9781,7 +9782,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E37" s="312"/>
     </row>
@@ -9904,7 +9905,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="71" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
@@ -9963,21 +9964,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E42" s="312"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C43" s="306">
         <v>0.24</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="309" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10031,12 +10032,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="67" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10054,18 +10055,18 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="65" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E46" s="312"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C47" s="198">
         <f>-BS!G31*Normalized_FCF!C53</f>
-        <v>-43</v>
+        <v>0</v>
       </c>
       <c r="E47" s="312"/>
       <c r="G47" s="198">
@@ -10116,11 +10117,11 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C48" s="198">
         <f>BS!$C$66*C52</f>
-        <v>1430.37</v>
+        <v>0</v>
       </c>
       <c r="E48" s="312"/>
       <c r="G48" s="198">
@@ -10171,11 +10172,11 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="71" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C49" s="188">
         <f>C47+C48</f>
-        <v>1387.37</v>
+        <v>0</v>
       </c>
       <c r="E49" s="312"/>
       <c r="G49" s="188">
@@ -10230,27 +10231,27 @@
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
       <c r="B51" s="73" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E51" s="312"/>
       <c r="G51" s="100" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C52" s="89">
         <v>0.03</v>
       </c>
       <c r="E52" s="309" t="s">
-        <v>86</v>
-      </c>
-      <c r="G52" s="6">
+        <v>84</v>
+      </c>
+      <c r="G52" s="6" t="e">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G48/BS!$C$66)</f>
-        <v>4.907821053293903E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H52" s="174"/>
       <c r="I52" s="174"/>
@@ -10266,18 +10267,18 @@
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C53" s="84">
         <f>G53</f>
-        <v>1.3902360168121564E-2</v>
+        <v>0</v>
       </c>
       <c r="E53" s="309" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G53" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
-        <v>1.3902360168121564E-2</v>
+        <v>0</v>
       </c>
       <c r="H53" s="174"/>
       <c r="I53" s="174"/>
@@ -10293,11 +10294,11 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="C54" s="42">
+        <v>98</v>
+      </c>
+      <c r="C54" s="42" t="e">
         <f>-C8/C47</f>
-        <v>60.274889749707867</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E54" s="312"/>
       <c r="G54" s="42">
@@ -10352,17 +10353,17 @@
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
       <c r="B56" s="65" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E56" s="312"/>
       <c r="G56" s="100" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C57" s="198">
         <f>BS!$C79*C65</f>
@@ -10417,11 +10418,11 @@
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C58" s="198">
         <f>BS!$C68*C66</f>
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="E58" s="312"/>
       <c r="G58" s="198">
@@ -10472,7 +10473,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C59" s="198">
         <f>BS!$C81*C67</f>
@@ -10527,11 +10528,11 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="31" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C60" s="188">
         <f>SUM(C57:C59)</f>
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="E60" s="312"/>
       <c r="G60" s="188">
@@ -10582,13 +10583,13 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C61" s="307">
         <v>0</v>
       </c>
       <c r="E61" s="310" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G61" s="198">
         <f>Data!C58</f>
@@ -10638,11 +10639,11 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="31" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C62" s="188">
         <f>C60+C61</f>
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="E62" s="312"/>
       <c r="G62" s="188">
@@ -10697,17 +10698,17 @@
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
       <c r="B64" s="99" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E64" s="312"/>
       <c r="G64" s="100" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C65" s="181">
         <f>G65</f>
@@ -10732,16 +10733,16 @@
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="108" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C66" s="181">
         <f>G66</f>
-        <v>2.6966576637407157E-2</v>
+        <v>0</v>
       </c>
       <c r="E66" s="312"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$68,0)</f>
-        <v>2.6966576637407157E-2</v>
+        <v>0</v>
       </c>
       <c r="H66" s="180"/>
       <c r="I66" s="180"/>
@@ -10757,7 +10758,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C67" s="181">
         <f>G67</f>
@@ -10782,18 +10783,18 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="C68" s="72">
+        <v>203</v>
+      </c>
+      <c r="C68" s="72" t="e">
         <f>C60/BS!C70</f>
-        <v>8.7649511686601553E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D68" s="9"/>
       <c r="E68" s="317"/>
       <c r="F68" s="9"/>
-      <c r="G68" s="72">
+      <c r="G68" s="72" t="e">
         <f>G60/BS!C70</f>
-        <v>8.7649511686601553E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H68" s="180"/>
       <c r="I68" s="180"/>
@@ -10812,12 +10813,12 @@
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A70" s="10"/>
       <c r="B70" s="54" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C70" s="54"/>
       <c r="D70" s="56"/>
       <c r="E70" s="67" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F70" s="56"/>
       <c r="G70" s="37"/>
@@ -10835,7 +10836,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="10"/>
       <c r="B71" s="73" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C71" s="63"/>
       <c r="D71" s="27"/>
@@ -10856,7 +10857,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C72" s="79">
         <f>ABS(C5/C$4)</f>
@@ -10913,7 +10914,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C73" s="80">
         <f>ABS(C6/C$4)</f>
@@ -10970,7 +10971,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C74" s="79">
         <f>ABS(C7/C$4)</f>
@@ -11027,7 +11028,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="29" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C75" s="80">
         <f>ABS(C8/C$4)</f>
@@ -11084,11 +11085,11 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C76" s="79">
+        <v>67</v>
+      </c>
+      <c r="C76" s="79" t="e">
         <f>ABS(C9/C$4)</f>
-        <v>1.8254420992584137E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="309"/>
@@ -11141,15 +11142,15 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C77" s="90">
+        <v>88</v>
+      </c>
+      <c r="C77" s="90" t="e">
         <f>MAX(AVERAGE(G77:J77),C76)</f>
-        <v>1.8254420992584137E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="310" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
@@ -11200,11 +11201,11 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="31" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C78" s="80">
         <f>ABS(C11/C$4)</f>
-        <v>7.2903593839132919E-2</v>
+        <v>0</v>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="309"/>
@@ -11257,11 +11258,11 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C79" s="79">
         <f>ABS(C12/C$4)</f>
-        <v>0.15828522532800912</v>
+        <v>0</v>
       </c>
       <c r="D79" s="27"/>
       <c r="E79" s="309"/>
@@ -11314,11 +11315,11 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
       <c r="B80" s="71" t="s">
-        <v>175</v>
-      </c>
-      <c r="C80" s="80">
+        <v>173</v>
+      </c>
+      <c r="C80" s="80" t="e">
         <f>C13/C4</f>
-        <v>0.52688993259982175</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="309"/>
@@ -11371,11 +11372,11 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C81" s="79">
         <f>ABS(C14/C$4)</f>
-        <v>0.12645358382395724</v>
+        <v>7.096826722384314E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="309"/>
@@ -11433,7 +11434,7 @@
       </c>
       <c r="C82" s="308">
         <f>MIN(BS!C62,MAX(G82:K82))</f>
-        <v>2.6092079791263361E-3</v>
+        <v>0</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="309"/>
@@ -11486,11 +11487,11 @@
     <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="10"/>
       <c r="B83" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="C83" s="80">
+        <v>163</v>
+      </c>
+      <c r="C83" s="80" t="e">
         <f>ABS(C16/C$4)</f>
-        <v>0.39782714079673825</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="309"/>
@@ -11543,7 +11544,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10"/>
       <c r="B84" s="27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C84" s="308">
         <v>0</v>
@@ -11569,7 +11570,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10"/>
       <c r="B85" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C85" s="308">
         <v>0</v>
@@ -11593,11 +11594,11 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
       <c r="B86" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="C86" s="80">
+        <v>149</v>
+      </c>
+      <c r="C86" s="80" t="e">
         <f>ABS(C19/C$4)</f>
-        <v>0.39782714079673825</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D86" s="77"/>
       <c r="E86" s="309"/>
@@ -11654,7 +11655,7 @@
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
       <c r="B88" s="65" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E88" s="312"/>
     </row>
@@ -11773,11 +11774,11 @@
     <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C91" s="23">
+        <v>223</v>
+      </c>
+      <c r="C91" s="23" t="e">
         <f>C89/(C19*$C$3/Common_Shares)</f>
-        <v>1.3592634587039025</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E91" s="312"/>
       <c r="G91" s="175">
@@ -11828,7 +11829,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
@@ -11887,7 +11888,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
       <c r="B94" s="162" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C94" s="63"/>
       <c r="D94" s="27"/>
@@ -11908,7 +11909,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
       <c r="B95" s="27" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C95" s="79">
         <f>C4/G4-1</f>
@@ -11965,11 +11966,11 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
       <c r="B96" s="71" t="s">
-        <v>175</v>
-      </c>
-      <c r="C96" s="79">
+        <v>173</v>
+      </c>
+      <c r="C96" s="79" t="e">
         <f>C13/G13-1</f>
-        <v>-0.13903984727117114</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D96" s="27"/>
       <c r="E96" s="309"/>
@@ -12025,12 +12026,12 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A98" s="3"/>
       <c r="B98" s="54" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C98" s="54"/>
       <c r="D98" s="56"/>
       <c r="E98" s="67" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F98" s="56"/>
       <c r="G98" s="37"/>
@@ -12048,11 +12049,11 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="10"/>
       <c r="B99" s="65" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E99" s="312"/>
       <c r="G99" s="100" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12062,7 +12063,7 @@
       </c>
       <c r="C100" s="206">
         <f>BS!G32</f>
-        <v>180996</v>
+        <v>10</v>
       </c>
       <c r="D100" s="26"/>
       <c r="E100" s="313"/>
@@ -12115,11 +12116,11 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="10"/>
       <c r="B101" s="95" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C101" s="207">
         <f>BS!C4</f>
-        <v>8029</v>
+        <v>0</v>
       </c>
       <c r="D101" s="91"/>
       <c r="E101" s="314"/>
@@ -12172,11 +12173,11 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="95" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C102" s="207">
         <f>BS!C6+BS!C7</f>
-        <v>15310</v>
+        <v>0</v>
       </c>
       <c r="D102" s="91"/>
       <c r="E102" s="314"/>
@@ -12229,11 +12230,11 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
       <c r="B103" s="26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C103" s="206">
         <f>BS!G30</f>
-        <v>13889</v>
+        <v>0</v>
       </c>
       <c r="D103" s="26"/>
       <c r="E103" s="313"/>
@@ -12286,11 +12287,11 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C104" s="206">
         <f>BS!G27</f>
-        <v>167107</v>
+        <v>10</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="313"/>
@@ -12347,14 +12348,14 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
       <c r="B106" s="93" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C106" s="26"/>
       <c r="D106" s="26"/>
       <c r="E106" s="313"/>
       <c r="F106" s="26"/>
       <c r="G106" s="100" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
@@ -12370,11 +12371,11 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
       <c r="B107" s="26" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C107" s="97">
         <f>C101/C$4</f>
-        <v>0.91602966343411296</v>
+        <v>0</v>
       </c>
       <c r="D107" s="26"/>
       <c r="E107" s="313"/>
@@ -12427,11 +12428,11 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
-        <v>1.7467199087278951</v>
+        <v>0</v>
       </c>
       <c r="D108" s="26"/>
       <c r="E108" s="313"/>
@@ -12484,18 +12485,18 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C109" s="97">
         <f>BS!$G$38/C$4</f>
-        <v>8.343867655447804</v>
+        <v>0</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="313"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f>BS!$G$38/G$4</f>
-        <v>8.343867655447804</v>
+        <v>0</v>
       </c>
       <c r="H109" s="232"/>
       <c r="I109" s="232"/>
@@ -12515,7 +12516,7 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
       <c r="B111" s="93" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C111" s="55"/>
       <c r="D111" s="55"/>
@@ -12569,11 +12570,11 @@
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
       <c r="B112" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C112" s="23">
+        <v>231</v>
+      </c>
+      <c r="C112" s="23" t="e">
         <f>C80</f>
-        <v>0.52688993259982175</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E112" s="312"/>
       <c r="G112" s="23">
@@ -12623,11 +12624,11 @@
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B113" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C113" s="42">
         <f>C4/C100</f>
-        <v>4.8426484563194767E-2</v>
+        <v>876.5</v>
       </c>
       <c r="E113" s="312"/>
       <c r="G113" s="42">
@@ -12677,11 +12678,11 @@
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C114" s="15">
         <f>C100/C104</f>
-        <v>1.0831144117242246</v>
+        <v>1</v>
       </c>
       <c r="D114" s="11"/>
       <c r="E114" s="316"/>
@@ -12734,11 +12735,11 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="10"/>
       <c r="B115" s="71" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C115" s="105">
         <f>C8/C104</f>
-        <v>1.5509944282629921E-2</v>
+        <v>259.18202592374382</v>
       </c>
       <c r="D115" s="106"/>
       <c r="E115" s="315"/>
@@ -12810,12 +12811,12 @@
     <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A117" s="10"/>
       <c r="B117" s="54" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C117" s="54"/>
       <c r="D117" s="56"/>
       <c r="E117" s="67" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F117" s="56"/>
       <c r="G117" s="37"/>
@@ -12833,7 +12834,7 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="10"/>
       <c r="B118" s="183" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C118" s="184"/>
       <c r="D118" s="27"/>
@@ -12857,9 +12858,9 @@
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
         <v>FCFE per share (HKD)</v>
       </c>
-      <c r="C119" s="182">
+      <c r="C119" s="182" t="e">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.42670167897623534</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D119" s="27"/>
       <c r="E119" s="309"/>
@@ -12912,11 +12913,11 @@
     <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="10"/>
       <c r="B120" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="C120" s="79">
+        <v>293</v>
+      </c>
+      <c r="C120" s="79" t="e">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.401287075648549E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="309"/>
@@ -13681,43 +13682,43 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="134" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="112" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H3" s="124"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="103" t="s">
-        <v>139</v>
-      </c>
-      <c r="C4" s="113">
+        <v>137</v>
+      </c>
+      <c r="C4" s="113" t="e">
         <f>Normalized_FCF!C19</f>
-        <v>3486.9548890834108</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F4" s="138">
         <f>Thesis!C71</f>
@@ -13727,7 +13728,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="234" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C5" s="235">
         <f>Thesis!C67</f>
@@ -13738,29 +13739,29 @@
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="153" t="s">
-        <v>240</v>
-      </c>
-      <c r="C6" s="239">
+        <v>238</v>
+      </c>
+      <c r="C6" s="239" t="e">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>38743.943212037899</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
       <c r="E6" s="338" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F6" s="338"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C7" s="233">
         <f>BS!G31</f>
-        <v>3093</v>
+        <v>0</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
@@ -13772,11 +13773,11 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C8" s="208">
         <f>BS!D66</f>
-        <v>44592.410129618722</v>
+        <v>-514.43164506354685</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -13788,11 +13789,11 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="234" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C9" s="236">
         <f>BS!H42</f>
-        <v>7814.4</v>
+        <v>0</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -13804,11 +13805,11 @@
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
-        <v>239</v>
-      </c>
-      <c r="C10" s="239">
+        <v>237</v>
+      </c>
+      <c r="C10" s="239" t="e">
         <f>C6-C7+C8+C9</f>
-        <v>88057.753341656615</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -13818,7 +13819,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="237" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C11" s="238">
         <f>Exchange_Rate</f>
@@ -13832,11 +13833,11 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="115">
+        <v>111</v>
+      </c>
+      <c r="C12" s="115" t="e">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>10.775703269174489</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -13849,7 +13850,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B14" s="36" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -13859,13 +13860,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B15" s="123" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="156" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C16" s="166">
         <f>Scenarios!C65</f>
@@ -13875,7 +13876,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="122" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C17" s="167">
         <f>Scenarios!C64</f>
@@ -13885,11 +13886,11 @@
     </row>
     <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="157" t="s">
-        <v>117</v>
-      </c>
-      <c r="C18" s="144">
+        <v>115</v>
+      </c>
+      <c r="C18" s="144" t="e">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>10.645261896931558</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -13902,19 +13903,19 @@
     </row>
     <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="132" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="132" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="132" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="132" t="s">
         <v>118</v>
       </c>
-      <c r="C20" s="132" t="s">
+      <c r="F20" s="133" t="s">
         <v>119</v>
-      </c>
-      <c r="D20" s="132" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" s="132" t="s">
-        <v>120</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>121</v>
       </c>
       <c r="H20" s="124"/>
     </row>
@@ -13922,9 +13923,9 @@
       <c r="B21" s="126">
         <v>1</v>
       </c>
-      <c r="C21" s="127">
+      <c r="C21" s="127" t="e">
         <f>C4*(1+D21)</f>
-        <v>3456.2865918029279</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D21" s="142">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -13934,9 +13935,9 @@
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
         <v>0.9174311926605504</v>
       </c>
-      <c r="F21" s="129">
+      <c r="F21" s="129" t="e">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>3170.9051300944288</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -13944,9 +13945,9 @@
       <c r="B22" s="126">
         <v>2</v>
       </c>
-      <c r="C22" s="127">
+      <c r="C22" s="127" t="e">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3425.8880268499347</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D22" s="142">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -13956,9 +13957,9 @@
         <f t="shared" si="0"/>
         <v>0.84167999326655996</v>
       </c>
-      <c r="F22" s="129">
+      <c r="F22" s="129" t="e">
         <f t="shared" si="1"/>
-        <v>2883.5014113710413</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -13966,9 +13967,9 @@
       <c r="B23" s="126">
         <v>3</v>
       </c>
-      <c r="C23" s="127">
+      <c r="C23" s="127" t="e">
         <f t="shared" si="2"/>
-        <v>3395.7568218876877</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D23" s="142">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -13978,9 +13979,9 @@
         <f t="shared" si="0"/>
         <v>0.77218348006106419</v>
       </c>
-      <c r="F23" s="129">
+      <c r="F23" s="129" t="e">
         <f t="shared" si="1"/>
-        <v>2622.1473201663339</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -13988,9 +13989,9 @@
       <c r="B24" s="126">
         <v>4</v>
       </c>
-      <c r="C24" s="127">
+      <c r="C24" s="127" t="e">
         <f t="shared" si="2"/>
-        <v>3365.8906254445051</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D24" s="142">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14000,9 +14001,9 @@
         <f t="shared" si="0"/>
         <v>0.7084252110651964</v>
       </c>
-      <c r="F24" s="129">
+      <c r="F24" s="129" t="e">
         <f t="shared" si="1"/>
-        <v>2384.4817767528893</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -14010,9 +14011,9 @@
       <c r="B25" s="126">
         <v>5</v>
       </c>
-      <c r="C25" s="127">
+      <c r="C25" s="127" t="e">
         <f t="shared" si="2"/>
-        <v>3336.2871067302563</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D25" s="142">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14022,9 +14023,9 @@
         <f t="shared" si="0"/>
         <v>0.64993138629834524</v>
       </c>
-      <c r="F25" s="129">
+      <c r="F25" s="129" t="e">
         <f t="shared" si="1"/>
-        <v>2168.3577043664909</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -14032,9 +14033,9 @@
       <c r="B26" s="126">
         <v>6</v>
       </c>
-      <c r="C26" s="127">
+      <c r="C26" s="127" t="e">
         <f t="shared" si="2"/>
-        <v>3306.9439554544615</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D26" s="142">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14044,9 +14045,9 @@
         <f t="shared" si="0"/>
         <v>0.5962673268792158</v>
       </c>
-      <c r="F26" s="129">
+      <c r="F26" s="129" t="e">
         <f t="shared" si="1"/>
-        <v>1971.8226324582122</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -14054,9 +14055,9 @@
       <c r="B27" s="126">
         <v>7</v>
       </c>
-      <c r="C27" s="127">
+      <c r="C27" s="127" t="e">
         <f t="shared" si="2"/>
-        <v>3277.8588816459983</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D27" s="142">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -14066,9 +14067,9 @@
         <f t="shared" si="0"/>
         <v>0.54703424484331731</v>
       </c>
-      <c r="F27" s="129">
+      <c r="F27" s="129" t="e">
         <f t="shared" si="1"/>
-        <v>1793.1010580241793</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -14076,9 +14077,9 @@
       <c r="B28" s="126">
         <v>8</v>
       </c>
-      <c r="C28" s="127">
+      <c r="C28" s="127" t="e">
         <f t="shared" si="2"/>
-        <v>3249.0296154743855</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D28" s="142">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -14088,9 +14089,9 @@
         <f t="shared" si="0"/>
         <v>0.50186627967276809</v>
       </c>
-      <c r="F28" s="129">
+      <c r="F28" s="129" t="e">
         <f t="shared" si="1"/>
-        <v>1630.5784056647742</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -14098,9 +14099,9 @@
       <c r="B29" s="126">
         <v>9</v>
       </c>
-      <c r="C29" s="127">
+      <c r="C29" s="127" t="e">
         <f t="shared" si="2"/>
-        <v>3220.4539070726478</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D29" s="142">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -14110,9 +14111,9 @@
         <f t="shared" si="0"/>
         <v>0.46042777951630098</v>
       </c>
-      <c r="F29" s="129">
+      <c r="F29" s="129" t="e">
         <f t="shared" si="1"/>
-        <v>1482.786441468055</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -14120,9 +14121,9 @@
       <c r="B30" s="126">
         <v>10</v>
       </c>
-      <c r="C30" s="127">
+      <c r="C30" s="127" t="e">
         <f t="shared" si="2"/>
-        <v>3192.1295263617289</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D30" s="142">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -14132,9 +14133,9 @@
         <f t="shared" si="0"/>
         <v>0.42241080689568894</v>
       </c>
-      <c r="F30" s="129">
+      <c r="F30" s="129" t="e">
         <f t="shared" si="1"/>
-        <v>1348.3900089460112</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -14580,11 +14581,11 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B51" s="130" t="s">
-        <v>142</v>
-      </c>
-      <c r="C51" s="127">
+        <v>140</v>
+      </c>
+      <c r="C51" s="127" t="e">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38403.184353365868</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -14594,20 +14595,20 @@
         <f>1/(1+Equity_Cost)^C17</f>
         <v>0.42241080689568894</v>
       </c>
-      <c r="F51" s="129">
+      <c r="F51" s="129" t="e">
         <f t="shared" si="1"/>
-        <v>16221.920090069172</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H51" s="124"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C52" s="118"/>
       <c r="E52" s="131" t="s">
-        <v>111</v>
-      </c>
-      <c r="F52" s="141">
+        <v>109</v>
+      </c>
+      <c r="F52" s="141" t="e">
         <f>SUM(F21:F51)</f>
-        <v>37677.991979381593</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -14617,7 +14618,7 @@
     </row>
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B54" s="123" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C54" s="140"/>
       <c r="D54" s="140"/>
@@ -14626,9 +14627,9 @@
       <c r="H54" s="124"/>
     </row>
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="A55" s="137">
+      <c r="A55" s="137" t="e">
         <f>F52</f>
-        <v>37677.991979381593</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
@@ -14656,21 +14657,21 @@
       <c r="A56" s="147">
         <v>5</v>
       </c>
-      <c r="B56" s="127">
+      <c r="B56" s="127" t="e">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>23201.614533894139</v>
-      </c>
-      <c r="C56" s="127">
-        <v>35683.87410935283</v>
-      </c>
-      <c r="D56" s="127">
-        <v>38743.943212037884</v>
-      </c>
-      <c r="E56" s="127">
-        <v>40034.423024477604</v>
-      </c>
-      <c r="F56" s="127">
-        <v>42046.669344499569</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C56" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D56" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E56" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F56" s="127" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -14678,20 +14679,20 @@
       <c r="A57" s="147">
         <v>10</v>
       </c>
-      <c r="B57" s="127">
-        <v>17640.060769940577</v>
-      </c>
-      <c r="C57" s="127">
-        <v>33224.752209448372</v>
-      </c>
-      <c r="D57" s="127">
-        <v>38743.943212037877</v>
-      </c>
-      <c r="E57" s="127">
-        <v>41340.23272622026</v>
-      </c>
-      <c r="F57" s="127">
-        <v>45736.575361637872</v>
+      <c r="B57" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C57" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D57" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E57" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F57" s="127" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -14699,20 +14700,20 @@
       <c r="A58" s="147">
         <v>15</v>
       </c>
-      <c r="B58" s="127">
-        <v>13696.159956623198</v>
-      </c>
-      <c r="C58" s="127">
-        <v>30756.80273757752</v>
-      </c>
-      <c r="D58" s="127">
-        <v>38743.943212037877</v>
-      </c>
-      <c r="E58" s="127">
-        <v>42885.474405983456</v>
-      </c>
-      <c r="F58" s="127">
-        <v>50459.344007316962</v>
+      <c r="B58" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C58" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D58" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E58" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F58" s="127" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -14720,20 +14721,20 @@
       <c r="A59" s="148">
         <v>20</v>
       </c>
-      <c r="B59" s="127">
-        <v>11096.927295605441</v>
-      </c>
-      <c r="C59" s="127">
-        <v>28715.43440607957</v>
-      </c>
-      <c r="D59" s="127">
-        <v>38743.943212037877</v>
-      </c>
-      <c r="E59" s="127">
-        <v>44389.607136543338</v>
-      </c>
-      <c r="F59" s="127">
-        <v>55457.050518454918</v>
+      <c r="B59" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C59" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D59" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E59" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F59" s="127" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -14741,20 +14742,20 @@
       <c r="A60" s="148">
         <v>25</v>
       </c>
-      <c r="B60" s="127">
-        <v>9403.6755101736071</v>
-      </c>
-      <c r="C60" s="127">
-        <v>27168.729451221632</v>
-      </c>
-      <c r="D60" s="127">
-        <v>38743.943212037862</v>
-      </c>
-      <c r="E60" s="127">
-        <v>45725.857796411146</v>
-      </c>
-      <c r="F60" s="127">
-        <v>60304.675620030292</v>
+      <c r="B60" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C60" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D60" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E60" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F60" s="127" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -14762,20 +14763,20 @@
       <c r="A61" s="148">
         <v>30</v>
       </c>
-      <c r="B61" s="127">
-        <v>8302.7488607156283</v>
-      </c>
-      <c r="C61" s="127">
-        <v>26052.860688222594</v>
-      </c>
-      <c r="D61" s="127">
-        <v>38743.943212037862</v>
-      </c>
-      <c r="E61" s="127">
-        <v>46851.700569251603</v>
-      </c>
-      <c r="F61" s="127">
-        <v>64782.043095780697</v>
+      <c r="B61" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C61" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D61" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E61" s="127" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F61" s="127" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -14788,7 +14789,7 @@
     </row>
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B63" s="123" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C63" s="118"/>
       <c r="D63" s="118"/>
@@ -14823,25 +14824,25 @@
       <c r="A65" s="147">
         <v>0</v>
       </c>
-      <c r="B65" s="128">
+      <c r="B65" s="128" t="e">
         <f>C12</f>
-        <v>10.775703269174489</v>
-      </c>
-      <c r="C65" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C65" s="128" t="e">
         <f>C12</f>
-        <v>10.775703269174489</v>
-      </c>
-      <c r="D65" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D65" s="128" t="e">
         <f>C12</f>
-        <v>10.775703269174489</v>
-      </c>
-      <c r="E65" s="145">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E65" s="145" t="e">
         <f>C12</f>
-        <v>10.775703269174489</v>
-      </c>
-      <c r="F65" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F65" s="128" t="e">
         <f>C12</f>
-        <v>10.775703269174489</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -14850,25 +14851,25 @@
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
       </c>
-      <c r="B66" s="128">
+      <c r="B66" s="128" t="e">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>8.8737750959919204</v>
-      </c>
-      <c r="C66" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C66" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>10.401239972276992</v>
-      </c>
-      <c r="D66" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D66" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>10.775703269174487</v>
-      </c>
-      <c r="E66" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E66" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>10.933620397490911</v>
-      </c>
-      <c r="F66" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F66" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>11.179860716215776</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -14877,25 +14878,25 @@
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="B67" s="128">
+      <c r="B67" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>8.1932029623445626</v>
-      </c>
-      <c r="C67" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C67" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>10.100315103193786</v>
-      </c>
-      <c r="D67" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D67" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>10.775703269174485</v>
-      </c>
-      <c r="E67" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E67" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>11.09341345759084</v>
-      </c>
-      <c r="F67" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F67" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>11.631397699876411</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -14904,25 +14905,25 @@
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="B68" s="128">
+      <c r="B68" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>7.7105844162811144</v>
-      </c>
-      <c r="C68" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C68" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>9.7983099965109712</v>
-      </c>
-      <c r="D68" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D68" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>10.775703269174485</v>
-      </c>
-      <c r="E68" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E68" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>11.282506015467989</v>
-      </c>
-      <c r="F68" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F68" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>12.209326974739303</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -14931,25 +14932,25 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="B69" s="128">
+      <c r="B69" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>7.3925140724466178</v>
-      </c>
-      <c r="C69" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C69" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>9.5485059921098543</v>
-      </c>
-      <c r="D69" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D69" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>10.775703269174485</v>
-      </c>
-      <c r="E69" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E69" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>11.466568035754612</v>
-      </c>
-      <c r="F69" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F69" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>12.820900633466385</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -14958,25 +14959,25 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="B70" s="128">
+      <c r="B70" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>7.185309390207899</v>
-      </c>
-      <c r="C70" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C70" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>9.3592343719965729</v>
-      </c>
-      <c r="D70" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D70" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>10.775703269174485</v>
-      </c>
-      <c r="E70" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E70" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>11.630086182170489</v>
-      </c>
-      <c r="F70" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F70" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>13.414108700586887</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14984,42 +14985,42 @@
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="B71" s="128">
+      <c r="B71" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>7.0505880460275954</v>
-      </c>
-      <c r="C71" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C71" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>9.2226845484873881</v>
-      </c>
-      <c r="D71" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D71" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>10.775703269174485</v>
-      </c>
-      <c r="E71" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E71" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>11.767856533871415</v>
-      </c>
-      <c r="F71" s="128">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F71" s="128" t="e">
         <f t="shared" si="4"/>
-        <v>13.962008022507421</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="176" t="s">
+        <v>126</v>
+      </c>
+      <c r="C73" s="176" t="s">
+        <v>141</v>
+      </c>
+      <c r="D73" s="176" t="s">
+        <v>121</v>
+      </c>
+      <c r="E73" s="177" t="s">
+        <v>122</v>
+      </c>
+      <c r="F73" s="177" t="s">
         <v>128</v>
-      </c>
-      <c r="C73" s="176" t="s">
-        <v>143</v>
-      </c>
-      <c r="D73" s="176" t="s">
-        <v>123</v>
-      </c>
-      <c r="E73" s="177" t="s">
-        <v>124</v>
-      </c>
-      <c r="F73" s="177" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -15035,9 +15036,9 @@
         <f>Scenarios!C55</f>
         <v>15</v>
       </c>
-      <c r="E74" s="139">
+      <c r="E74" s="139" t="e">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>12.209326974739303</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15057,9 +15058,9 @@
         <f>Scenarios!C37</f>
         <v>10</v>
       </c>
-      <c r="E75" s="139">
+      <c r="E75" s="139" t="e">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>11.09341345759084</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15080,9 +15081,9 @@
         <f>Scenarios!C25</f>
         <v>10</v>
       </c>
-      <c r="E76" s="139">
+      <c r="E76" s="139" t="e">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>10.775703269174485</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15103,9 +15104,9 @@
         <f>Scenarios!C31</f>
         <v>10</v>
       </c>
-      <c r="E77" s="139">
+      <c r="E77" s="139" t="e">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>10.100315103193786</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15126,9 +15127,9 @@
         <f>Scenarios!C49</f>
         <v>15</v>
       </c>
-      <c r="E78" s="139">
+      <c r="E78" s="139" t="e">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.7105844162811144</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15144,20 +15145,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="160" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C80" s="160" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81" s="160" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82" s="160" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.35">
@@ -15209,20 +15210,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="285" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="I2" s="286"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="164" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H3" s="284">
         <v>0</v>
@@ -15234,14 +15235,14 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="156" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C4" s="124">
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="160" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F4" s="160"/>
       <c r="H4" s="284">
@@ -15263,27 +15264,27 @@
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="164" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="284">
         <v>3</v>
       </c>
-      <c r="I6" s="272">
+      <c r="I6" s="272" t="e">
         <f t="shared" si="0"/>
-        <v>11.22404343432521</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15308,7 +15309,7 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="103" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
@@ -15330,11 +15331,11 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="103" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="208">
+        <v>59</v>
+      </c>
+      <c r="C9" s="208" t="e">
         <f>Normalized_FCF!C19</f>
-        <v>3486.9548890834108</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -15363,7 +15364,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="164" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E11" s="340"/>
       <c r="F11" s="340"/>
@@ -15377,7 +15378,7 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C12" s="163">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15396,7 +15397,7 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="152" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C13" s="163">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15414,7 +15415,7 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="103" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C14" s="163">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15425,7 +15426,7 @@
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -15434,21 +15435,21 @@
     </row>
     <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="112" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E17" s="164" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="156" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C18" s="154">
         <v>10</v>
       </c>
       <c r="E18" s="340" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F18" s="341"/>
     </row>
@@ -15458,14 +15459,14 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="164" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E20" s="341"/>
       <c r="F20" s="341"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
@@ -15480,11 +15481,11 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>309</v>
-      </c>
-      <c r="C22" s="165">
+        <v>307</v>
+      </c>
+      <c r="C22" s="165" t="e">
         <f>Valuation_Model!C12</f>
-        <v>10.775703269174489</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15495,16 +15496,16 @@
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="164" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E24" s="164" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F24" s="164"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C25" s="171">
         <f>C18</f>
@@ -15516,7 +15517,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C26" s="169">
         <v>0</v>
@@ -15527,11 +15528,11 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
-        <v>124</v>
-      </c>
-      <c r="C27" s="165">
+        <v>122</v>
+      </c>
+      <c r="C27" s="165" t="e">
         <f>Valuation_Model!E76</f>
-        <v>10.775703269174485</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D27" s="165" t="str">
         <f>Market_currency</f>
@@ -15542,7 +15543,7 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C28" s="170">
         <v>0.55000000000000004</v>
@@ -15553,16 +15554,16 @@
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="164" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E30" s="164" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F30" s="164"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C31" s="171">
         <f>C18</f>
@@ -15574,7 +15575,7 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C32" s="169">
         <v>-0.05</v>
@@ -15585,11 +15586,11 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
-        <v>124</v>
-      </c>
-      <c r="C33" s="165">
+        <v>122</v>
+      </c>
+      <c r="C33" s="165" t="e">
         <f>Valuation_Model!E77</f>
-        <v>10.100315103193786</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15600,7 +15601,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C34" s="170">
         <v>0.2</v>
@@ -15611,16 +15612,16 @@
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="164" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E36" s="164" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F36" s="164"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C37" s="171">
         <f>C18</f>
@@ -15632,7 +15633,7 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C38" s="169">
         <v>0.02</v>
@@ -15643,11 +15644,11 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
-        <v>124</v>
-      </c>
-      <c r="C39" s="165">
+        <v>122</v>
+      </c>
+      <c r="C39" s="165" t="e">
         <f>Valuation_Model!E75</f>
-        <v>11.09341345759084</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15658,7 +15659,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C40" s="172">
         <f>1-C28-C34</f>
@@ -15670,11 +15671,11 @@
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
-        <v>131</v>
-      </c>
-      <c r="C42" s="159">
+        <v>129</v>
+      </c>
+      <c r="C42" s="159" t="e">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>10.720053183082435</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15683,7 +15684,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B44" s="36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -15692,12 +15693,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B45" s="112" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="156" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C46" s="154">
         <v>15</v>
@@ -15712,16 +15713,16 @@
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B48" s="164" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E48" s="164" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F48" s="164"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C49" s="171">
         <f>C46</f>
@@ -15733,7 +15734,7 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C50" s="169">
         <v>-0.3</v>
@@ -15744,11 +15745,11 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
-        <v>124</v>
-      </c>
-      <c r="C51" s="165">
+        <v>122</v>
+      </c>
+      <c r="C51" s="165" t="e">
         <f>Valuation_Model!E78</f>
-        <v>7.7105844162811144</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -15759,7 +15760,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C52" s="170">
         <v>0.05</v>
@@ -15770,16 +15771,16 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="164" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E54" s="164" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F54" s="164"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C55" s="171">
         <f>C46</f>
@@ -15791,7 +15792,7 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C56" s="169">
         <v>0.05</v>
@@ -15802,11 +15803,11 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
-        <v>124</v>
-      </c>
-      <c r="C57" s="165">
+        <v>122</v>
+      </c>
+      <c r="C57" s="165" t="e">
         <f>Valuation_Model!E74</f>
-        <v>12.209326974739303</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -15817,7 +15818,7 @@
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C58" s="170">
         <v>0.05</v>
@@ -15828,18 +15829,18 @@
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
-        <v>131</v>
-      </c>
-      <c r="C60" s="159">
+        <v>129</v>
+      </c>
+      <c r="C60" s="159" t="e">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>10.64404343432521</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F60" s="322">
         <f>Thesis!E20</f>
@@ -15848,7 +15849,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -15857,85 +15858,85 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E63" s="290" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="156" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C64" s="171">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="289" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="122" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C65" s="155">
         <v>-8.7951517171891112E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="289" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="103" t="s">
-        <v>113</v>
-      </c>
-      <c r="C66" s="165">
+        <v>111</v>
+      </c>
+      <c r="C66" s="165" t="e">
         <f>Valuation_Model!C18</f>
-        <v>10.645261896931558</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D66" s="165" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="289" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E68" s="290" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>347</v>
-      </c>
-      <c r="C69" s="281" t="str">
+        <v>345</v>
+      </c>
+      <c r="C69" s="281" t="e">
         <f>IF(C60&lt;C22,"Y","N")</f>
-        <v>Y</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E69" s="138"/>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>335</v>
-      </c>
-      <c r="C70" s="281" t="str">
+        <v>333</v>
+      </c>
+      <c r="C70" s="281" t="e">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
-        <v>N</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E70" s="289" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C71" s="281" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -15945,20 +15946,20 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>325</v>
-      </c>
-      <c r="C72" s="280" t="str">
+        <v>323</v>
+      </c>
+      <c r="C72" s="280" t="e">
         <f>IF(E72&gt;50%,"Y","N")</f>
-        <v>Y</v>
-      </c>
-      <c r="E72" s="138" t="str">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E72" s="138" t="e">
         <f>"Non-FCF Value is "&amp;ROUND(BS!D89/C60*100,0)&amp;"% of the Expected Equity Value"</f>
-        <v>Non-FCF Value is 57% of the Expected Equity Value</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B74" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -15967,12 +15968,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B75" s="112" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="283" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C76" s="282">
         <f>F60</f>
@@ -15982,7 +15983,7 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="103" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C77" s="178">
         <f>Normalized_FCF!C89</f>
@@ -15995,12 +15996,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C80" s="172">
         <f>Thesis!C117</f>
@@ -16009,7 +16010,7 @@
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -16021,32 +16022,32 @@
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
-        <v>133</v>
-      </c>
-      <c r="C82" s="120">
+        <v>131</v>
+      </c>
+      <c r="C82" s="120" t="e">
         <f>C60/(1+C80)^C76</f>
-        <v>6.1597473578270892</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D82" s="120"/>
     </row>
     <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
-        <v>112</v>
-      </c>
-      <c r="C83" s="115">
+        <v>110</v>
+      </c>
+      <c r="C83" s="115" t="e">
         <f>C81+C82</f>
-        <v>7.3815066170863481</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E83" s="150" t="s">
-        <v>137</v>
-      </c>
-      <c r="F83" s="270">
+        <v>135</v>
+      </c>
+      <c r="F83" s="270" t="e">
         <f>(C83/C60-1)</f>
-        <v>-0.30651291845707263</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16054,12 +16055,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
@@ -16072,11 +16073,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>340</v>
-      </c>
-      <c r="C87" s="273">
+        <v>338</v>
+      </c>
+      <c r="C87" s="273" t="e">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17143601630956429</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
@@ -16084,7 +16085,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="331" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F89" s="328"/>
       <c r="G89" s="2"/>
@@ -16092,30 +16093,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="324" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F90" s="329" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="327"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="325" t="s">
+        <v>376</v>
+      </c>
+      <c r="F91" s="329" t="s">
         <v>378</v>
-      </c>
-      <c r="F91" s="329" t="s">
-        <v>380</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="327"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="326" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F92" s="330" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="327"/>

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50ACA129-107D-40D7-B8CF-A534B0B6D6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01ECF68-34A5-476C-BB47-1B2D9EB84220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="392">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2000,6 +2000,14 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Operating Interest Income</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Non-FCF Value is of the Expected Value, at</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2025,7 +2033,7 @@
     <numFmt numFmtId="192" formatCode="0.0\x"/>
     <numFmt numFmtId="193" formatCode="0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="58" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2458,13 +2466,6 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3368,15 +3369,14 @@
     <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="193" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3406,6 +3406,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3804,13 +3807,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="341" t="s">
+      <c r="B12" s="340" t="s">
         <v>286</v>
       </c>
-      <c r="C12" s="341"/>
-      <c r="D12" s="341"/>
-      <c r="E12" s="341"/>
-      <c r="F12" s="341"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3912,22 +3915,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="341" t="s">
+      <c r="B25" s="340" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="341"/>
-      <c r="D25" s="341"/>
-      <c r="E25" s="341"/>
-      <c r="F25" s="341"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="341" t="s">
         <v>382</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3939,13 +3942,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="339" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3965,13 +3968,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="339" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4000,13 +4003,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="339" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4022,13 +4025,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="339" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4092,13 +4095,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="339" t="s">
         <v>248</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4114,13 +4117,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
+      <c r="B50" s="339" t="s">
         <v>381</v>
       </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
+      <c r="C50" s="343"/>
+      <c r="D50" s="343"/>
+      <c r="E50" s="343"/>
+      <c r="F50" s="343"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4136,22 +4139,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="341" t="s">
+      <c r="B53" s="340" t="s">
         <v>386</v>
       </c>
-      <c r="C53" s="341"/>
-      <c r="D53" s="341"/>
-      <c r="E53" s="341"/>
-      <c r="F53" s="341"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="341" t="s">
+      <c r="B54" s="340" t="s">
         <v>268</v>
       </c>
-      <c r="C54" s="341"/>
-      <c r="D54" s="341"/>
-      <c r="E54" s="341"/>
-      <c r="F54" s="341"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4159,7 +4162,7 @@
       </c>
       <c r="C56" s="192">
         <f>Normalized_FCF!G19</f>
-        <v>2548</v>
+        <v>2807.968614974819</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4212,22 +4215,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="339" t="s">
         <v>303</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="341" t="s">
         <v>259</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="241" t="s">
@@ -4279,22 +4282,22 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="341" t="s">
+      <c r="B72" s="340" t="s">
         <v>387</v>
       </c>
-      <c r="C72" s="341"/>
-      <c r="D72" s="341"/>
-      <c r="E72" s="341"/>
-      <c r="F72" s="341"/>
+      <c r="C72" s="340"/>
+      <c r="D72" s="340"/>
+      <c r="E72" s="340"/>
+      <c r="F72" s="340"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="341" t="s">
+      <c r="B73" s="340" t="s">
         <v>388</v>
       </c>
-      <c r="C73" s="341"/>
-      <c r="D73" s="341"/>
-      <c r="E73" s="341"/>
-      <c r="F73" s="341"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
@@ -4331,13 +4334,13 @@
       <c r="A79" s="240"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="341" t="s">
+      <c r="B80" s="340" t="s">
         <v>261</v>
       </c>
-      <c r="C80" s="341"/>
-      <c r="D80" s="341"/>
-      <c r="E80" s="341"/>
-      <c r="F80" s="341"/>
+      <c r="C80" s="340"/>
+      <c r="D80" s="340"/>
+      <c r="E80" s="340"/>
+      <c r="F80" s="340"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4350,13 +4353,13 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="341" t="s">
+      <c r="B84" s="340" t="s">
         <v>389</v>
       </c>
-      <c r="C84" s="341"/>
-      <c r="D84" s="341"/>
-      <c r="E84" s="341"/>
-      <c r="F84" s="341"/>
+      <c r="C84" s="340"/>
+      <c r="D84" s="340"/>
+      <c r="E84" s="340"/>
+      <c r="F84" s="340"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
@@ -4460,13 +4463,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="341" t="s">
+      <c r="B97" s="340" t="s">
         <v>267</v>
       </c>
-      <c r="C97" s="341"/>
-      <c r="D97" s="341"/>
-      <c r="E97" s="341"/>
-      <c r="F97" s="341"/>
+      <c r="C97" s="340"/>
+      <c r="D97" s="340"/>
+      <c r="E97" s="340"/>
+      <c r="F97" s="340"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
@@ -4492,13 +4495,13 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="340" t="s">
+      <c r="B103" s="339" t="s">
         <v>369</v>
       </c>
-      <c r="C103" s="340"/>
-      <c r="D103" s="340"/>
-      <c r="E103" s="340"/>
-      <c r="F103" s="340"/>
+      <c r="C103" s="339"/>
+      <c r="D103" s="339"/>
+      <c r="E103" s="339"/>
+      <c r="F103" s="339"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="267" t="s">
@@ -4641,13 +4644,13 @@
       </c>
     </row>
     <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="345" t="s">
+      <c r="B114" s="344" t="s">
         <v>370</v>
       </c>
-      <c r="C114" s="345"/>
-      <c r="D114" s="345"/>
-      <c r="E114" s="345"/>
-      <c r="F114" s="345"/>
+      <c r="C114" s="344"/>
+      <c r="D114" s="344"/>
+      <c r="E114" s="344"/>
+      <c r="F114" s="344"/>
     </row>
     <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A116" s="254" t="s">
@@ -4660,13 +4663,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="343" t="s">
+      <c r="B118" s="342" t="s">
         <v>275</v>
       </c>
-      <c r="C118" s="343"/>
-      <c r="D118" s="343"/>
-      <c r="E118" s="343"/>
-      <c r="F118" s="343"/>
+      <c r="C118" s="342"/>
+      <c r="D118" s="342"/>
+      <c r="E118" s="342"/>
+      <c r="F118" s="342"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="241" t="s">
@@ -4889,15 +4892,9 @@
       <c r="D4" s="185">
         <v>11881</v>
       </c>
-      <c r="E4" s="185">
-        <v>15650.563377</v>
-      </c>
-      <c r="F4" s="185">
-        <v>24433.371759000001</v>
-      </c>
-      <c r="G4" s="185">
-        <v>5887</v>
-      </c>
+      <c r="E4" s="185"/>
+      <c r="F4" s="185"/>
+      <c r="G4" s="185"/>
       <c r="H4" s="185"/>
       <c r="I4" s="185"/>
       <c r="J4" s="185"/>
@@ -4915,15 +4912,9 @@
       <c r="D5" s="185">
         <v>6492</v>
       </c>
-      <c r="E5" s="185">
-        <v>7482.8818240000001</v>
-      </c>
-      <c r="F5" s="185">
-        <v>11196.89644</v>
-      </c>
-      <c r="G5" s="185">
-        <v>2437</v>
-      </c>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
       <c r="H5" s="185"/>
       <c r="I5" s="185"/>
       <c r="J5" s="185"/>
@@ -4941,12 +4932,8 @@
       <c r="D6" s="185">
         <v>1129</v>
       </c>
-      <c r="E6" s="185">
-        <v>867.48327900000004</v>
-      </c>
-      <c r="F6" s="185">
-        <v>823.28128300000003</v>
-      </c>
+      <c r="E6" s="185"/>
+      <c r="F6" s="185"/>
       <c r="G6" s="185"/>
       <c r="H6" s="185"/>
       <c r="I6" s="185"/>
@@ -5049,12 +5036,8 @@
       <c r="D12" s="185">
         <v>40.775368</v>
       </c>
-      <c r="E12" s="185">
-        <v>49.197794000000002</v>
-      </c>
-      <c r="F12" s="185">
-        <v>81.763175000000004</v>
-      </c>
+      <c r="E12" s="185"/>
+      <c r="F12" s="185"/>
       <c r="G12" s="185"/>
       <c r="H12" s="185"/>
       <c r="I12" s="185"/>
@@ -5073,12 +5056,8 @@
       <c r="D13" s="185">
         <v>1390.845307</v>
       </c>
-      <c r="E13" s="185">
-        <v>337.25969199999997</v>
-      </c>
-      <c r="F13" s="185">
-        <v>572.18514300000004</v>
-      </c>
+      <c r="E13" s="185"/>
+      <c r="F13" s="185"/>
       <c r="G13" s="185"/>
       <c r="H13" s="185"/>
       <c r="I13" s="185"/>
@@ -5097,12 +5076,8 @@
       <c r="D14" s="185">
         <v>860.83482800000002</v>
       </c>
-      <c r="E14" s="185">
-        <v>1349.107495</v>
-      </c>
-      <c r="F14" s="185">
-        <v>2530.7695309999999</v>
-      </c>
+      <c r="E14" s="185"/>
+      <c r="F14" s="185"/>
       <c r="G14" s="185"/>
       <c r="H14" s="185"/>
       <c r="I14" s="185"/>
@@ -5121,12 +5096,8 @@
       <c r="D15" s="186">
         <v>5880</v>
       </c>
-      <c r="E15" s="186">
-        <v>5735.3965490000001</v>
-      </c>
-      <c r="F15" s="186">
-        <v>9646.0369900000005</v>
-      </c>
+      <c r="E15" s="186"/>
+      <c r="F15" s="186"/>
       <c r="G15" s="186"/>
       <c r="H15" s="186"/>
       <c r="I15" s="186"/>
@@ -5171,12 +5142,8 @@
       <c r="D19" s="185">
         <v>198</v>
       </c>
-      <c r="E19" s="185">
-        <v>181.018</v>
-      </c>
-      <c r="F19" s="185">
-        <v>186.14699999999999</v>
-      </c>
+      <c r="E19" s="185"/>
+      <c r="F19" s="185"/>
       <c r="G19" s="185"/>
       <c r="H19" s="185"/>
       <c r="I19" s="185"/>
@@ -5236,9 +5203,7 @@
       <c r="D22" s="39">
         <v>0.57999999999999996</v>
       </c>
-      <c r="E22" s="39">
-        <v>0.56999999999999995</v>
-      </c>
+      <c r="E22" s="39"/>
       <c r="F22" s="39"/>
       <c r="G22" s="39"/>
       <c r="H22" s="39"/>
@@ -5401,17 +5366,17 @@
         <f t="shared" si="1"/>
         <v>11881</v>
       </c>
-      <c r="E36" s="187">
+      <c r="E36" s="187" t="str">
         <f t="shared" si="1"/>
-        <v>15650.563377</v>
-      </c>
-      <c r="F36" s="187">
+        <v/>
+      </c>
+      <c r="F36" s="187" t="str">
         <f t="shared" si="1"/>
-        <v>24433.371759000001</v>
-      </c>
-      <c r="G36" s="187">
+        <v/>
+      </c>
+      <c r="G36" s="187" t="str">
         <f t="shared" si="1"/>
-        <v>5887</v>
+        <v/>
       </c>
       <c r="H36" s="187" t="str">
         <f t="shared" si="1"/>
@@ -5450,17 +5415,17 @@
         <f t="shared" si="2"/>
         <v>-6492</v>
       </c>
-      <c r="E37" s="187">
+      <c r="E37" s="187" t="str">
         <f t="shared" si="2"/>
-        <v>-7482.8818240000001</v>
-      </c>
-      <c r="F37" s="187">
+        <v/>
+      </c>
+      <c r="F37" s="187" t="str">
         <f t="shared" si="2"/>
-        <v>-11196.89644</v>
-      </c>
-      <c r="G37" s="187">
+        <v/>
+      </c>
+      <c r="G37" s="187" t="str">
         <f t="shared" si="2"/>
-        <v>-2437</v>
+        <v/>
       </c>
       <c r="H37" s="187" t="str">
         <f t="shared" si="2"/>
@@ -5499,17 +5464,17 @@
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>5389</v>
       </c>
-      <c r="E38" s="188">
+      <c r="E38" s="188" t="str">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
-        <v>8167.6815530000003</v>
-      </c>
-      <c r="F38" s="188">
+        <v/>
+      </c>
+      <c r="F38" s="188" t="str">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
-        <v>13236.475319000001</v>
-      </c>
-      <c r="G38" s="188">
+        <v/>
+      </c>
+      <c r="G38" s="188" t="str">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
-        <v>3450</v>
+        <v/>
       </c>
       <c r="H38" s="188" t="str">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
@@ -5548,17 +5513,17 @@
         <f t="shared" si="13"/>
         <v>-1129</v>
       </c>
-      <c r="E39" s="187">
+      <c r="E39" s="187" t="str">
         <f t="shared" si="13"/>
-        <v>-867.48327900000004</v>
-      </c>
-      <c r="F39" s="187">
+        <v/>
+      </c>
+      <c r="F39" s="187" t="str">
         <f t="shared" si="13"/>
-        <v>-823.28128300000003</v>
-      </c>
-      <c r="G39" s="187">
+        <v/>
+      </c>
+      <c r="G39" s="187" t="str">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H39" s="187" t="str">
         <f t="shared" si="13"/>
@@ -5597,17 +5562,17 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="E40" s="189">
+      <c r="E40" s="189" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="189">
+        <v/>
+      </c>
+      <c r="F40" s="189" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="189">
+        <v/>
+      </c>
+      <c r="G40" s="189" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H40" s="189" t="str">
         <f t="shared" si="14"/>
@@ -5646,17 +5611,17 @@
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-1129</v>
       </c>
-      <c r="E41" s="189">
+      <c r="E41" s="189" t="str">
         <f t="shared" si="15"/>
-        <v>-867.48327900000004</v>
-      </c>
-      <c r="F41" s="189">
+        <v/>
+      </c>
+      <c r="F41" s="189" t="str">
         <f t="shared" si="15"/>
-        <v>-823.28128300000003</v>
-      </c>
-      <c r="G41" s="189">
+        <v/>
+      </c>
+      <c r="G41" s="189" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H41" s="189" t="str">
         <f t="shared" si="15"/>
@@ -5695,17 +5660,17 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E42" s="187">
+      <c r="E42" s="187" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="F42" s="187">
+        <v/>
+      </c>
+      <c r="F42" s="187" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="G42" s="187">
+        <v/>
+      </c>
+      <c r="G42" s="187" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H42" s="187" t="str">
         <f t="shared" si="16"/>
@@ -5744,17 +5709,17 @@
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>4260</v>
       </c>
-      <c r="E43" s="190">
+      <c r="E43" s="190" t="str">
         <f t="shared" si="17"/>
-        <v>7300.1982740000003</v>
-      </c>
-      <c r="F43" s="190">
+        <v/>
+      </c>
+      <c r="F43" s="190" t="str">
         <f t="shared" si="17"/>
-        <v>12413.194036000001</v>
-      </c>
-      <c r="G43" s="190">
+        <v/>
+      </c>
+      <c r="G43" s="190" t="str">
         <f t="shared" si="17"/>
-        <v>3450</v>
+        <v/>
       </c>
       <c r="H43" s="190" t="str">
         <f t="shared" si="17"/>
@@ -5793,17 +5758,17 @@
         <f t="shared" si="18"/>
         <v>1130.764889</v>
       </c>
-      <c r="E44" s="191">
+      <c r="E44" s="191" t="str">
         <f t="shared" si="18"/>
-        <v>-503.75612799999999</v>
-      </c>
-      <c r="F44" s="191">
+        <v/>
+      </c>
+      <c r="F44" s="191" t="str">
         <f t="shared" si="18"/>
-        <v>-726.80948300000091</v>
-      </c>
-      <c r="G44" s="191">
+        <v/>
+      </c>
+      <c r="G44" s="191" t="str">
         <f t="shared" si="18"/>
-        <v>-3450</v>
+        <v/>
       </c>
       <c r="H44" s="191" t="str">
         <f t="shared" si="18"/>
@@ -5842,17 +5807,17 @@
         <f t="shared" si="19"/>
         <v>1350.069939</v>
       </c>
-      <c r="E45" s="192">
+      <c r="E45" s="192" t="str">
         <f t="shared" si="19"/>
-        <v>288.06189799999999</v>
-      </c>
-      <c r="F45" s="192">
+        <v/>
+      </c>
+      <c r="F45" s="192" t="str">
         <f t="shared" si="19"/>
-        <v>490.42196800000005</v>
-      </c>
-      <c r="G45" s="192">
+        <v/>
+      </c>
+      <c r="G45" s="192" t="str">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H45" s="192" t="str">
         <f t="shared" si="19"/>
@@ -5891,17 +5856,17 @@
         <f t="shared" si="20"/>
         <v>-860.83482800000002</v>
       </c>
-      <c r="E46" s="187">
+      <c r="E46" s="187" t="str">
         <f t="shared" si="20"/>
-        <v>-1349.107495</v>
-      </c>
-      <c r="F46" s="187">
+        <v/>
+      </c>
+      <c r="F46" s="187" t="str">
         <f t="shared" si="20"/>
-        <v>-2530.7695309999999</v>
-      </c>
-      <c r="G46" s="187">
+        <v/>
+      </c>
+      <c r="G46" s="187" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H46" s="187" t="str">
         <f t="shared" si="20"/>
@@ -5940,17 +5905,17 @@
         <f t="shared" si="21"/>
         <v>5880</v>
       </c>
-      <c r="E47" s="190">
+      <c r="E47" s="190" t="str">
         <f t="shared" si="21"/>
-        <v>5735.3965490000001</v>
-      </c>
-      <c r="F47" s="190">
+        <v/>
+      </c>
+      <c r="F47" s="190" t="str">
         <f t="shared" si="21"/>
-        <v>9646.0369900000005</v>
-      </c>
-      <c r="G47" s="190">
+        <v/>
+      </c>
+      <c r="G47" s="190" t="str">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H47" s="190" t="str">
         <f t="shared" si="21"/>
@@ -5989,17 +5954,17 @@
         <f t="shared" si="22"/>
         <v>-31</v>
       </c>
-      <c r="E48" s="187">
+      <c r="E48" s="187" t="str">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="187">
+        <v/>
+      </c>
+      <c r="F48" s="187" t="str">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="G48" s="187">
+        <v/>
+      </c>
+      <c r="G48" s="187" t="str">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H48" s="187" t="str">
         <f t="shared" si="22"/>
@@ -6043,17 +6008,17 @@
         <f t="shared" si="23"/>
         <v>-40.775368</v>
       </c>
-      <c r="E51" s="187">
+      <c r="E51" s="187" t="str">
         <f t="shared" si="23"/>
-        <v>-49.197794000000002</v>
-      </c>
-      <c r="F51" s="187">
+        <v/>
+      </c>
+      <c r="F51" s="187" t="str">
         <f t="shared" si="23"/>
-        <v>-81.763175000000004</v>
-      </c>
-      <c r="G51" s="187">
+        <v/>
+      </c>
+      <c r="G51" s="187" t="str">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H51" s="187" t="str">
         <f t="shared" si="23"/>
@@ -6092,17 +6057,17 @@
         <f t="shared" si="24"/>
         <v>1390.845307</v>
       </c>
-      <c r="E52" s="187">
+      <c r="E52" s="187" t="str">
         <f t="shared" si="24"/>
-        <v>337.25969199999997</v>
-      </c>
-      <c r="F52" s="187">
+        <v/>
+      </c>
+      <c r="F52" s="187" t="str">
         <f t="shared" si="24"/>
-        <v>572.18514300000004</v>
-      </c>
-      <c r="G52" s="187">
+        <v/>
+      </c>
+      <c r="G52" s="187" t="str">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H52" s="187" t="str">
         <f t="shared" si="24"/>
@@ -6146,17 +6111,17 @@
         <f t="shared" si="25"/>
         <v>927</v>
       </c>
-      <c r="E55" s="192">
+      <c r="E55" s="192" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="F55" s="192">
+        <v/>
+      </c>
+      <c r="F55" s="192" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="G55" s="192">
+        <v/>
+      </c>
+      <c r="G55" s="192" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H55" s="192" t="str">
         <f t="shared" si="25"/>
@@ -6195,17 +6160,17 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E56" s="192">
+      <c r="E56" s="192" t="str">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="F56" s="192">
+        <v/>
+      </c>
+      <c r="F56" s="192" t="str">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="G56" s="192">
+        <v/>
+      </c>
+      <c r="G56" s="192" t="str">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H56" s="192" t="str">
         <f t="shared" si="26"/>
@@ -6244,17 +6209,17 @@
         <f t="shared" ref="D57:M57" si="27">IF(D$4="","",D11)</f>
         <v>0</v>
       </c>
-      <c r="E57" s="192">
+      <c r="E57" s="192" t="str">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="F57" s="192">
+        <v/>
+      </c>
+      <c r="F57" s="192" t="str">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="G57" s="192">
+        <v/>
+      </c>
+      <c r="G57" s="192" t="str">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H57" s="192" t="str">
         <f t="shared" si="27"/>
@@ -6293,17 +6258,17 @@
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
         <v>203.76488900000004</v>
       </c>
-      <c r="E58" s="192">
+      <c r="E58" s="192" t="str">
         <f t="shared" si="28"/>
-        <v>-503.75612799999999</v>
-      </c>
-      <c r="F58" s="192">
+        <v/>
+      </c>
+      <c r="F58" s="192" t="str">
         <f t="shared" si="28"/>
-        <v>-726.80948300000091</v>
-      </c>
-      <c r="G58" s="192">
+        <v/>
+      </c>
+      <c r="G58" s="192" t="str">
         <f t="shared" si="28"/>
-        <v>-3450</v>
+        <v/>
       </c>
       <c r="H58" s="192" t="str">
         <f t="shared" si="28"/>
@@ -6348,17 +6313,17 @@
         <f t="shared" si="29"/>
         <v>-198</v>
       </c>
-      <c r="E61" s="187">
+      <c r="E61" s="187" t="str">
         <f t="shared" si="29"/>
-        <v>-181.018</v>
-      </c>
-      <c r="F61" s="187">
+        <v/>
+      </c>
+      <c r="F61" s="187" t="str">
         <f t="shared" si="29"/>
-        <v>-186.14699999999999</v>
-      </c>
-      <c r="G61" s="187">
+        <v/>
+      </c>
+      <c r="G61" s="187" t="str">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H61" s="187" t="str">
         <f t="shared" si="29"/>
@@ -6397,17 +6362,17 @@
         <f t="shared" si="30"/>
         <v>-108</v>
       </c>
-      <c r="E62" s="187">
+      <c r="E62" s="187" t="str">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="F62" s="187">
+        <v/>
+      </c>
+      <c r="F62" s="187" t="str">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G62" s="187">
+        <v/>
+      </c>
+      <c r="G62" s="187" t="str">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H62" s="187" t="str">
         <f t="shared" si="30"/>
@@ -6446,17 +6411,17 @@
         <f t="shared" si="31"/>
         <v>-2541</v>
       </c>
-      <c r="E63" s="187">
+      <c r="E63" s="187" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="F63" s="187">
+        <v/>
+      </c>
+      <c r="F63" s="187" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="G63" s="187">
+        <v/>
+      </c>
+      <c r="G63" s="187" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H63" s="187" t="str">
         <f t="shared" si="31"/>
@@ -6495,17 +6460,17 @@
         <f t="shared" si="32"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="E64" s="75">
+      <c r="E64" s="75" t="str">
         <f t="shared" si="32"/>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="F64" s="75">
+        <v/>
+      </c>
+      <c r="F64" s="75" t="str">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="G64" s="75">
+        <v/>
+      </c>
+      <c r="G64" s="75" t="str">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H64" s="75" t="str">
         <f t="shared" si="32"/>
@@ -6546,17 +6511,17 @@
         <f t="shared" ref="C67:M67" si="33">IF(D$36="","",C36/D36-1)</f>
         <v>-0.26226748590186011</v>
       </c>
-      <c r="D67" s="94">
+      <c r="D67" s="94" t="str">
         <f t="shared" si="33"/>
-        <v>-0.2408579989228844</v>
-      </c>
-      <c r="E67" s="94">
+        <v/>
+      </c>
+      <c r="E67" s="94" t="str">
         <f t="shared" si="33"/>
-        <v>-0.35945953217712834</v>
-      </c>
-      <c r="F67" s="94">
+        <v/>
+      </c>
+      <c r="F67" s="94" t="str">
         <f t="shared" si="33"/>
-        <v>3.150394387463904</v>
+        <v/>
       </c>
       <c r="G67" s="94" t="str">
         <f t="shared" si="33"/>
@@ -6596,17 +6561,17 @@
         <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C37/D37-1)</f>
         <v>-0.17683302526186073</v>
       </c>
-      <c r="D68" s="104">
+      <c r="D68" s="104" t="str">
         <f t="shared" si="34"/>
-        <v>-0.13241981462568664</v>
-      </c>
-      <c r="E68" s="104">
+        <v/>
+      </c>
+      <c r="E68" s="104" t="str">
         <f t="shared" si="34"/>
-        <v>-0.33170036321243324</v>
-      </c>
-      <c r="F68" s="104">
+        <v/>
+      </c>
+      <c r="F68" s="104" t="str">
         <f t="shared" si="34"/>
-        <v>3.5945410094378332</v>
+        <v/>
       </c>
       <c r="G68" s="104" t="str">
         <f t="shared" si="34"/>
@@ -6646,17 +6611,17 @@
         <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C38/D38-1)</f>
         <v>-0.36518834663202826</v>
       </c>
-      <c r="D69" s="94">
+      <c r="D69" s="94" t="str">
         <f t="shared" si="35"/>
-        <v>-0.34020444295840435</v>
-      </c>
-      <c r="E69" s="94">
+        <v/>
+      </c>
+      <c r="E69" s="94" t="str">
         <f t="shared" si="35"/>
-        <v>-0.38294135287844455</v>
-      </c>
-      <c r="F69" s="94">
+        <v/>
+      </c>
+      <c r="F69" s="94" t="str">
         <f t="shared" si="35"/>
-        <v>2.8366595127536236</v>
+        <v/>
       </c>
       <c r="G69" s="94" t="str">
         <f t="shared" si="35"/>
@@ -6696,17 +6661,17 @@
         <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C39/D39-1)</f>
         <v>-3.9858281665190454E-2</v>
       </c>
-      <c r="D70" s="104">
+      <c r="D70" s="104" t="str">
         <f t="shared" si="36"/>
-        <v>0.30146600785373745</v>
-      </c>
-      <c r="E70" s="104">
+        <v/>
+      </c>
+      <c r="E70" s="104" t="str">
         <f t="shared" si="36"/>
-        <v>5.3690029049281884E-2</v>
-      </c>
-      <c r="F70" s="104" t="e">
+        <v/>
+      </c>
+      <c r="F70" s="104" t="str">
         <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
+        <v/>
       </c>
       <c r="G70" s="104" t="str">
         <f t="shared" si="36"/>
@@ -6746,17 +6711,17 @@
         <f>IF(D$36="","",C64/D64-1)</f>
         <v>0</v>
       </c>
-      <c r="D71" s="94">
+      <c r="D71" s="94" t="str">
         <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D64/E64-1)</f>
-        <v>1.7543859649122862E-2</v>
-      </c>
-      <c r="E71" s="94" t="e">
+        <v/>
+      </c>
+      <c r="E71" s="94" t="str">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F71" s="94" t="e">
+        <v/>
+      </c>
+      <c r="F71" s="94" t="str">
         <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
+        <v/>
       </c>
       <c r="G71" s="94" t="str">
         <f t="shared" si="37"/>
@@ -6821,17 +6786,17 @@
         <f t="shared" ref="D75:M75" si="38">IF(D$4="","",D78+D79)</f>
         <v>174007</v>
       </c>
-      <c r="E75" s="78">
+      <c r="E75" s="78" t="str">
         <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="F75" s="78">
+        <v/>
+      </c>
+      <c r="F75" s="78" t="str">
         <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="G75" s="78">
+        <v/>
+      </c>
+      <c r="G75" s="78" t="str">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H75" s="78" t="str">
         <f t="shared" si="38"/>
@@ -6870,17 +6835,17 @@
         <f t="shared" si="39"/>
         <v>7251</v>
       </c>
-      <c r="E76" s="74">
+      <c r="E76" s="74" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="F76" s="74">
+        <v/>
+      </c>
+      <c r="F76" s="74" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="G76" s="74">
+        <v/>
+      </c>
+      <c r="G76" s="74" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H76" s="74" t="str">
         <f t="shared" si="39"/>
@@ -6904,17 +6869,17 @@
         <f t="shared" si="39"/>
         <v>16389</v>
       </c>
-      <c r="E77" s="74">
+      <c r="E77" s="74" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="F77" s="74">
+        <v/>
+      </c>
+      <c r="F77" s="74" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="G77" s="74">
+        <v/>
+      </c>
+      <c r="G77" s="74" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H77" s="74" t="str">
         <f t="shared" si="39"/>
@@ -6938,17 +6903,17 @@
         <f t="shared" si="40"/>
         <v>10902</v>
       </c>
-      <c r="E78" s="58">
+      <c r="E78" s="58" t="str">
         <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="F78" s="58">
+        <v/>
+      </c>
+      <c r="F78" s="58" t="str">
         <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="G78" s="58">
+        <v/>
+      </c>
+      <c r="G78" s="58" t="str">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H78" s="58" t="str">
         <f t="shared" si="40"/>
@@ -6987,17 +6952,17 @@
         <f t="shared" si="41"/>
         <v>163105</v>
       </c>
-      <c r="E79" s="58">
+      <c r="E79" s="58" t="str">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="F79" s="58">
+        <v/>
+      </c>
+      <c r="F79" s="58" t="str">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="G79" s="58">
+        <v/>
+      </c>
+      <c r="G79" s="58" t="str">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H79" s="58" t="str">
         <f t="shared" si="41"/>
@@ -8142,7 +8107,7 @@
         <v>360</v>
       </c>
       <c r="C76" s="300"/>
-      <c r="D76" s="339">
+      <c r="D76" s="337">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,IF(D74&gt;36,12,6),2))</f>
         <v>12</v>
       </c>
@@ -8448,17 +8413,17 @@
         <f>Data!D36</f>
         <v>11881</v>
       </c>
-      <c r="I4" s="187">
+      <c r="I4" s="187" t="str">
         <f>Data!E36</f>
-        <v>15650.563377</v>
-      </c>
-      <c r="J4" s="187">
+        <v/>
+      </c>
+      <c r="J4" s="187" t="str">
         <f>Data!F36</f>
-        <v>24433.371759000001</v>
-      </c>
-      <c r="K4" s="187">
+        <v/>
+      </c>
+      <c r="K4" s="187" t="str">
         <f>Data!G36</f>
-        <v>5887</v>
+        <v/>
       </c>
       <c r="L4" s="187" t="str">
         <f>Data!H36</f>
@@ -8503,17 +8468,17 @@
         <f t="shared" si="1"/>
         <v>-6492</v>
       </c>
-      <c r="I5" s="187">
+      <c r="I5" s="187" t="str">
         <f t="shared" si="1"/>
-        <v>-7482.8818240000001</v>
-      </c>
-      <c r="J5" s="187">
+        <v/>
+      </c>
+      <c r="J5" s="187" t="str">
         <f t="shared" si="1"/>
-        <v>-11196.89644</v>
-      </c>
-      <c r="K5" s="187">
+        <v/>
+      </c>
+      <c r="K5" s="187" t="str">
         <f t="shared" si="1"/>
-        <v>-2437</v>
+        <v/>
       </c>
       <c r="L5" s="187" t="str">
         <f t="shared" si="1"/>
@@ -8558,17 +8523,17 @@
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>5389</v>
       </c>
-      <c r="I6" s="188">
+      <c r="I6" s="188" t="str">
         <f t="shared" si="2"/>
-        <v>8167.6815530000003</v>
-      </c>
-      <c r="J6" s="188">
+        <v/>
+      </c>
+      <c r="J6" s="188" t="str">
         <f t="shared" si="2"/>
-        <v>13236.475319000001</v>
-      </c>
-      <c r="K6" s="188">
+        <v/>
+      </c>
+      <c r="K6" s="188" t="str">
         <f t="shared" si="2"/>
-        <v>3450</v>
+        <v/>
       </c>
       <c r="L6" s="188" t="str">
         <f t="shared" si="2"/>
@@ -8613,17 +8578,17 @@
         <f t="shared" si="3"/>
         <v>-1129</v>
       </c>
-      <c r="I7" s="198">
+      <c r="I7" s="198" t="str">
         <f t="shared" si="3"/>
-        <v>-867.48327900000004</v>
-      </c>
-      <c r="J7" s="198">
+        <v/>
+      </c>
+      <c r="J7" s="198" t="str">
         <f t="shared" si="3"/>
-        <v>-823.28128300000003</v>
-      </c>
-      <c r="K7" s="198">
+        <v/>
+      </c>
+      <c r="K7" s="198" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L7" s="198" t="str">
         <f t="shared" si="3"/>
@@ -8670,17 +8635,17 @@
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>4260</v>
       </c>
-      <c r="I8" s="188">
+      <c r="I8" s="188" t="str">
         <f t="shared" si="4"/>
-        <v>7300.1982740000003</v>
-      </c>
-      <c r="J8" s="188">
+        <v/>
+      </c>
+      <c r="J8" s="188" t="str">
         <f t="shared" si="4"/>
-        <v>12413.194036000001</v>
-      </c>
-      <c r="K8" s="188">
+        <v/>
+      </c>
+      <c r="K8" s="188" t="str">
         <f t="shared" si="4"/>
-        <v>3450</v>
+        <v/>
       </c>
       <c r="L8" s="188" t="str">
         <f t="shared" si="4"/>
@@ -8725,17 +8690,17 @@
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>198</v>
       </c>
-      <c r="I9" s="198">
+      <c r="I9" s="198" t="str">
         <f>IF(Data!E61="","",-Data!E61)</f>
-        <v>181.018</v>
-      </c>
-      <c r="J9" s="198">
+        <v/>
+      </c>
+      <c r="J9" s="198" t="str">
         <f>IF(Data!F61="","",-Data!F61)</f>
-        <v>186.14699999999999</v>
-      </c>
-      <c r="K9" s="198">
+        <v/>
+      </c>
+      <c r="K9" s="198" t="str">
         <f>IF(Data!G61="","",-Data!G61)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L9" s="198" t="str">
         <f>IF(Data!H61="","",-Data!H61)</f>
@@ -8780,17 +8745,17 @@
         <f>Data!D62</f>
         <v>-108</v>
       </c>
-      <c r="I10" s="198">
+      <c r="I10" s="198" t="str">
         <f>Data!E62</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="198">
+        <v/>
+      </c>
+      <c r="J10" s="198" t="str">
         <f>Data!F62</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="198">
+        <v/>
+      </c>
+      <c r="K10" s="198" t="str">
         <f>Data!G62</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L10" s="198" t="str">
         <f>Data!H62</f>
@@ -8837,17 +8802,17 @@
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>927</v>
       </c>
-      <c r="I11" s="190">
+      <c r="I11" s="190" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="190">
+        <v/>
+      </c>
+      <c r="J11" s="190" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="190">
+        <v/>
+      </c>
+      <c r="K11" s="190" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L11" s="190" t="str">
         <f t="shared" si="5"/>
@@ -8885,48 +8850,48 @@
       </c>
       <c r="E12" s="311"/>
       <c r="G12" s="198">
-        <f t="shared" ref="G12:Q12" si="6">G50</f>
-        <v>0</v>
+        <f>G50</f>
+        <v>259.96861497481899</v>
       </c>
       <c r="H12" s="198">
+        <f t="shared" ref="H12:Q12" si="6">H50</f>
+        <v>139.30261332735768</v>
+      </c>
+      <c r="I12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="198">
+        <v/>
+      </c>
+      <c r="J12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="198">
+        <v/>
+      </c>
+      <c r="K12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="198">
+        <v/>
+      </c>
+      <c r="L12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="198">
+        <v/>
+      </c>
+      <c r="M12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="198">
+        <v/>
+      </c>
+      <c r="N12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="198">
+        <v/>
+      </c>
+      <c r="O12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="198">
+        <v/>
+      </c>
+      <c r="P12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="198">
+        <v/>
+      </c>
+      <c r="Q12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="198">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8941,23 +8906,23 @@
       <c r="E13" s="311"/>
       <c r="G13" s="188">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3067</v>
+        <v>3326.968614974819</v>
       </c>
       <c r="H13" s="188">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>5277</v>
-      </c>
-      <c r="I13" s="188">
+        <v>5416.3026133273579</v>
+      </c>
+      <c r="I13" s="188" t="str">
         <f t="shared" si="7"/>
-        <v>7481.2162740000003</v>
-      </c>
-      <c r="J13" s="188">
+        <v/>
+      </c>
+      <c r="J13" s="188" t="str">
         <f t="shared" si="7"/>
-        <v>12599.341036000002</v>
-      </c>
-      <c r="K13" s="188">
+        <v/>
+      </c>
+      <c r="K13" s="188" t="str">
         <f t="shared" si="7"/>
-        <v>3450</v>
+        <v/>
       </c>
       <c r="L13" s="188" t="str">
         <f t="shared" si="7"/>
@@ -9002,17 +8967,17 @@
         <f>Data!D46</f>
         <v>-860.83482800000002</v>
       </c>
-      <c r="I14" s="198">
+      <c r="I14" s="198" t="str">
         <f>Data!E46</f>
-        <v>-1349.107495</v>
-      </c>
-      <c r="J14" s="198">
+        <v/>
+      </c>
+      <c r="J14" s="198" t="str">
         <f>Data!F46</f>
-        <v>-2530.7695309999999</v>
-      </c>
-      <c r="K14" s="198">
+        <v/>
+      </c>
+      <c r="K14" s="198" t="str">
         <f>Data!G46</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L14" s="198" t="str">
         <f>Data!H46</f>
@@ -9059,17 +9024,17 @@
         <f>Data!D48</f>
         <v>-31</v>
       </c>
-      <c r="I15" s="187">
+      <c r="I15" s="187" t="str">
         <f>Data!E48</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="187">
+        <v/>
+      </c>
+      <c r="J15" s="187" t="str">
         <f>Data!F48</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="187">
+        <v/>
+      </c>
+      <c r="K15" s="187" t="str">
         <f>Data!G48</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L15" s="187" t="str">
         <f>Data!H48</f>
@@ -9110,23 +9075,23 @@
       <c r="F16" s="62"/>
       <c r="G16" s="188">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2548</v>
+        <v>2807.968614974819</v>
       </c>
       <c r="H16" s="188">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>4385.165172</v>
-      </c>
-      <c r="I16" s="188">
+        <v>4524.4677853273579</v>
+      </c>
+      <c r="I16" s="188" t="str">
         <f t="shared" si="8"/>
-        <v>6132.1087790000001</v>
-      </c>
-      <c r="J16" s="188">
+        <v/>
+      </c>
+      <c r="J16" s="188" t="str">
         <f t="shared" si="8"/>
-        <v>10068.571505000002</v>
-      </c>
-      <c r="K16" s="188">
+        <v/>
+      </c>
+      <c r="K16" s="188" t="str">
         <f t="shared" si="8"/>
-        <v>3450</v>
+        <v/>
       </c>
       <c r="L16" s="188" t="str">
         <f t="shared" si="8"/>
@@ -9218,23 +9183,23 @@
       <c r="F19" s="27"/>
       <c r="G19" s="190">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2548</v>
+        <v>2807.968614974819</v>
       </c>
       <c r="H19" s="190">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>4385.165172</v>
-      </c>
-      <c r="I19" s="190">
+        <v>4524.4677853273579</v>
+      </c>
+      <c r="I19" s="190" t="str">
         <f t="shared" si="9"/>
-        <v>6132.1087790000001</v>
-      </c>
-      <c r="J19" s="190">
+        <v/>
+      </c>
+      <c r="J19" s="190" t="str">
         <f t="shared" si="9"/>
-        <v>10068.571505000002</v>
-      </c>
-      <c r="K19" s="190">
+        <v/>
+      </c>
+      <c r="K19" s="190" t="str">
         <f t="shared" si="9"/>
-        <v>3450</v>
+        <v/>
       </c>
       <c r="L19" s="190" t="str">
         <f t="shared" si="9"/>
@@ -9344,17 +9309,17 @@
         <f>Data!D37</f>
         <v>-6492</v>
       </c>
-      <c r="I23" s="187">
+      <c r="I23" s="187" t="str">
         <f>Data!E37</f>
-        <v>-7482.8818240000001</v>
-      </c>
-      <c r="J23" s="187">
+        <v/>
+      </c>
+      <c r="J23" s="187" t="str">
         <f>Data!F37</f>
-        <v>-11196.89644</v>
-      </c>
-      <c r="K23" s="187">
+        <v/>
+      </c>
+      <c r="K23" s="187" t="str">
         <f>Data!G37</f>
-        <v>-2437</v>
+        <v/>
       </c>
       <c r="L23" s="187" t="str">
         <f>Data!H37</f>
@@ -9401,17 +9366,17 @@
         <f>Data!D40</f>
         <v>0</v>
       </c>
-      <c r="I24" s="187">
+      <c r="I24" s="187" t="str">
         <f>Data!E40</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="187">
+        <v/>
+      </c>
+      <c r="J24" s="187" t="str">
         <f>Data!F40</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="187">
+        <v/>
+      </c>
+      <c r="K24" s="187" t="str">
         <f>Data!G40</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L24" s="187" t="str">
         <f>Data!H40</f>
@@ -9458,17 +9423,17 @@
         <f t="shared" si="10"/>
         <v>-6492</v>
       </c>
-      <c r="I25" s="188">
+      <c r="I25" s="188" t="str">
         <f t="shared" si="10"/>
-        <v>-7482.8818240000001</v>
-      </c>
-      <c r="J25" s="188">
+        <v/>
+      </c>
+      <c r="J25" s="188" t="str">
         <f t="shared" si="10"/>
-        <v>-11196.89644</v>
-      </c>
-      <c r="K25" s="188">
+        <v/>
+      </c>
+      <c r="K25" s="188" t="str">
         <f t="shared" si="10"/>
-        <v>-2437</v>
+        <v/>
       </c>
       <c r="L25" s="188" t="str">
         <f t="shared" si="10"/>
@@ -9528,17 +9493,17 @@
         <f t="shared" si="11"/>
         <v>0.54641865162865078</v>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="13" t="str">
         <f t="shared" si="11"/>
-        <v>0.47812220197752181</v>
-      </c>
-      <c r="J28" s="13">
+        <v/>
+      </c>
+      <c r="J28" s="13" t="str">
         <f t="shared" si="11"/>
-        <v>0.45826243510069942</v>
-      </c>
-      <c r="K28" s="13">
+        <v/>
+      </c>
+      <c r="K28" s="13" t="str">
         <f t="shared" si="11"/>
-        <v>0.4139629692542891</v>
+        <v/>
       </c>
       <c r="L28" s="13" t="str">
         <f t="shared" si="11"/>
@@ -9588,17 +9553,17 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="13" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="13">
+        <v/>
+      </c>
+      <c r="J29" s="13" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="13">
+        <v/>
+      </c>
+      <c r="K29" s="13" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L29" s="13" t="str">
         <f t="shared" si="12"/>
@@ -9643,17 +9608,17 @@
         <f t="shared" si="13"/>
         <v>0.54641865162865078</v>
       </c>
-      <c r="I30" s="30">
+      <c r="I30" s="30" t="str">
         <f t="shared" si="13"/>
-        <v>0.47812220197752181</v>
-      </c>
-      <c r="J30" s="30">
+        <v/>
+      </c>
+      <c r="J30" s="30" t="str">
         <f t="shared" si="13"/>
-        <v>0.45826243510069942</v>
-      </c>
-      <c r="K30" s="30">
+        <v/>
+      </c>
+      <c r="K30" s="30" t="str">
         <f t="shared" si="13"/>
-        <v>0.4139629692542891</v>
+        <v/>
       </c>
       <c r="L30" s="30" t="str">
         <f t="shared" si="13"/>
@@ -9711,17 +9676,17 @@
         <f>Data!D41</f>
         <v>-1129</v>
       </c>
-      <c r="I33" s="198">
+      <c r="I33" s="198" t="str">
         <f>Data!E41</f>
-        <v>-867.48327900000004</v>
-      </c>
-      <c r="J33" s="198">
+        <v/>
+      </c>
+      <c r="J33" s="198" t="str">
         <f>Data!F41</f>
-        <v>-823.28128300000003</v>
-      </c>
-      <c r="K33" s="198">
+        <v/>
+      </c>
+      <c r="K33" s="198" t="str">
         <f>Data!G41</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L33" s="198" t="str">
         <f>Data!H41</f>
@@ -9770,17 +9735,17 @@
         <f>Data!D42</f>
         <v>0</v>
       </c>
-      <c r="I34" s="187">
+      <c r="I34" s="187" t="str">
         <f>Data!E42</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="187">
+        <v/>
+      </c>
+      <c r="J34" s="187" t="str">
         <f>Data!F42</f>
-        <v>0</v>
-      </c>
-      <c r="K34" s="187">
+        <v/>
+      </c>
+      <c r="K34" s="187" t="str">
         <f>Data!G42</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L34" s="187" t="str">
         <f>Data!H42</f>
@@ -9827,17 +9792,17 @@
         <f t="shared" si="14"/>
         <v>-1129</v>
       </c>
-      <c r="I35" s="188">
+      <c r="I35" s="188" t="str">
         <f t="shared" si="14"/>
-        <v>-867.48327900000004</v>
-      </c>
-      <c r="J35" s="188">
+        <v/>
+      </c>
+      <c r="J35" s="188" t="str">
         <f t="shared" si="14"/>
-        <v>-823.28128300000003</v>
-      </c>
-      <c r="K35" s="188">
+        <v/>
+      </c>
+      <c r="K35" s="188" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L35" s="188" t="str">
         <f t="shared" si="14"/>
@@ -9896,17 +9861,17 @@
         <f t="shared" si="15"/>
         <v>9.5025671239794635E-2</v>
       </c>
-      <c r="I38" s="13">
+      <c r="I38" s="13" t="str">
         <f t="shared" si="15"/>
-        <v>5.5428246134247773E-2</v>
-      </c>
-      <c r="J38" s="13">
+        <v/>
+      </c>
+      <c r="J38" s="13" t="str">
         <f t="shared" si="15"/>
-        <v>3.3694951770082464E-2</v>
-      </c>
-      <c r="K38" s="13">
+        <v/>
+      </c>
+      <c r="K38" s="13" t="str">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L38" s="13" t="str">
         <f t="shared" si="15"/>
@@ -9954,17 +9919,17 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I39" s="13">
+      <c r="I39" s="13" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="J39" s="13">
+        <v/>
+      </c>
+      <c r="J39" s="13" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K39" s="13">
+        <v/>
+      </c>
+      <c r="K39" s="13" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L39" s="13" t="str">
         <f t="shared" si="16"/>
@@ -10009,17 +9974,17 @@
         <f t="shared" si="17"/>
         <v>9.5025671239794635E-2</v>
       </c>
-      <c r="I40" s="30">
+      <c r="I40" s="30" t="str">
         <f t="shared" si="17"/>
-        <v>5.5428246134247773E-2</v>
-      </c>
-      <c r="J40" s="30">
+        <v/>
+      </c>
+      <c r="J40" s="30" t="str">
         <f t="shared" si="17"/>
-        <v>3.3694951770082464E-2</v>
-      </c>
-      <c r="K40" s="30">
+        <v/>
+      </c>
+      <c r="K40" s="30" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L40" s="30" t="str">
         <f t="shared" si="17"/>
@@ -10072,23 +10037,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.17439516129032259</v>
+        <v>0.16038474464748129</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.16596005937921729</v>
-      </c>
-      <c r="I43" s="6">
+        <v>0.16161958688679046</v>
+      </c>
+      <c r="I43" s="6" t="str">
         <f t="shared" si="18"/>
-        <v>0.18480422645572653</v>
-      </c>
-      <c r="J43" s="6">
+        <v/>
+      </c>
+      <c r="J43" s="6" t="str">
         <f t="shared" si="18"/>
-        <v>0.2038773843106306</v>
-      </c>
-      <c r="K43" s="6">
+        <v/>
+      </c>
+      <c r="K43" s="6" t="str">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10166,17 +10131,17 @@
         <f>Data!D51</f>
         <v>-40.775368</v>
       </c>
-      <c r="I47" s="198">
+      <c r="I47" s="198" t="str">
         <f>Data!E51</f>
-        <v>-49.197794000000002</v>
-      </c>
-      <c r="J47" s="198">
+        <v/>
+      </c>
+      <c r="J47" s="198" t="str">
         <f>Data!F51</f>
-        <v>-81.763175000000004</v>
-      </c>
-      <c r="K47" s="198">
+        <v/>
+      </c>
+      <c r="K47" s="198" t="str">
         <f>Data!G51</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L47" s="198" t="str">
         <f>Data!H51</f>
@@ -10206,78 +10171,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>71</v>
+        <v>390</v>
       </c>
       <c r="C48" s="198">
         <f>BS!D75*C53</f>
         <v>185.19539222287685</v>
       </c>
       <c r="E48" s="311"/>
-      <c r="G48" s="333"/>
-      <c r="H48" s="333"/>
-      <c r="I48" s="333"/>
-      <c r="J48" s="333"/>
-      <c r="K48" s="333"/>
-      <c r="L48" s="333"/>
-      <c r="M48" s="333"/>
-      <c r="N48" s="333"/>
-      <c r="O48" s="333"/>
-      <c r="P48" s="333"/>
-      <c r="Q48" s="333"/>
+      <c r="G48" s="338">
+        <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
+        <v>302.96861497481899</v>
+      </c>
+      <c r="H48" s="338">
+        <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
+        <v>180.07798132735766</v>
+      </c>
+      <c r="I48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="J48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="K48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="L48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="M48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="N48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="O48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="P48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="Q48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
-      <c r="B49" s="334" t="s">
+      <c r="B49" s="333" t="s">
         <v>385</v>
       </c>
-      <c r="C49" s="335">
+      <c r="C49" s="334">
         <f>BS!$C$66*C53</f>
         <v>1430.37</v>
       </c>
-      <c r="D49" s="336"/>
-      <c r="E49" s="337"/>
-      <c r="F49" s="336"/>
-      <c r="G49" s="335">
+      <c r="D49" s="335"/>
+      <c r="E49" s="336"/>
+      <c r="F49" s="335"/>
+      <c r="G49" s="334">
         <f>Data!C52</f>
         <v>2340</v>
       </c>
-      <c r="H49" s="335">
+      <c r="H49" s="334">
         <f>Data!D52</f>
         <v>1390.845307</v>
       </c>
-      <c r="I49" s="335">
+      <c r="I49" s="334" t="str">
         <f>Data!E52</f>
-        <v>337.25969199999997</v>
-      </c>
-      <c r="J49" s="335">
+        <v/>
+      </c>
+      <c r="J49" s="334" t="str">
         <f>Data!F52</f>
-        <v>572.18514300000004</v>
-      </c>
-      <c r="K49" s="335">
+        <v/>
+      </c>
+      <c r="K49" s="334" t="str">
         <f>Data!G52</f>
-        <v>0</v>
-      </c>
-      <c r="L49" s="335" t="str">
+        <v/>
+      </c>
+      <c r="L49" s="334" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="335" t="str">
+      <c r="M49" s="334" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="335" t="str">
+      <c r="N49" s="334" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="335" t="str">
+      <c r="O49" s="334" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="335" t="str">
+      <c r="P49" s="334" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="335" t="str">
+      <c r="Q49" s="334" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -10292,17 +10290,50 @@
         <v>142.19539222287685</v>
       </c>
       <c r="E50" s="311"/>
-      <c r="G50" s="338"/>
-      <c r="H50" s="338"/>
-      <c r="I50" s="338"/>
-      <c r="J50" s="338"/>
-      <c r="K50" s="338"/>
-      <c r="L50" s="338"/>
-      <c r="M50" s="338"/>
-      <c r="N50" s="338"/>
-      <c r="O50" s="338"/>
-      <c r="P50" s="338"/>
-      <c r="Q50" s="338"/>
+      <c r="G50" s="188">
+        <f>IF(G$4="","",(G47+G48))</f>
+        <v>259.96861497481899</v>
+      </c>
+      <c r="H50" s="188">
+        <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
+        <v>139.30261332735768</v>
+      </c>
+      <c r="I50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="J50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="K50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="L50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="M50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="N50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="O50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="P50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="Q50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
@@ -10382,47 +10413,47 @@
       </c>
       <c r="E55" s="311"/>
       <c r="G55" s="42">
-        <f t="shared" ref="G55:Q55" si="19">IF(G4="","",-G8/G47)</f>
+        <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>54.348837209302324</v>
       </c>
       <c r="H55" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>104.47483882916765</v>
       </c>
-      <c r="I55" s="42">
-        <f t="shared" si="19"/>
-        <v>148.38466688160855</v>
-      </c>
-      <c r="J55" s="42">
-        <f t="shared" si="19"/>
-        <v>151.81888467516092</v>
-      </c>
-      <c r="K55" s="42" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+      <c r="I55" s="42" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="J55" s="42" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="K55" s="42" t="str">
+        <f t="shared" si="21"/>
+        <v/>
       </c>
       <c r="L55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="M55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="O55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Q55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -10458,17 +10489,17 @@
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="198">
+      <c r="I58" s="198" t="str">
         <f>Data!E56</f>
-        <v>0</v>
-      </c>
-      <c r="J58" s="198">
+        <v/>
+      </c>
+      <c r="J58" s="198" t="str">
         <f>Data!F56</f>
-        <v>0</v>
-      </c>
-      <c r="K58" s="198">
+        <v/>
+      </c>
+      <c r="K58" s="198" t="str">
         <f>Data!G56</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L58" s="198" t="str">
         <f>Data!H56</f>
@@ -10513,17 +10544,17 @@
         <f>Data!D55</f>
         <v>927</v>
       </c>
-      <c r="I59" s="198">
+      <c r="I59" s="198" t="str">
         <f>Data!E55</f>
-        <v>0</v>
-      </c>
-      <c r="J59" s="198">
+        <v/>
+      </c>
+      <c r="J59" s="198" t="str">
         <f>Data!F55</f>
-        <v>0</v>
-      </c>
-      <c r="K59" s="198">
+        <v/>
+      </c>
+      <c r="K59" s="198" t="str">
         <f>Data!G55</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L59" s="198" t="str">
         <f>Data!H55</f>
@@ -10568,17 +10599,17 @@
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="198">
+      <c r="I60" s="198" t="str">
         <f>Data!E57</f>
-        <v>0</v>
-      </c>
-      <c r="J60" s="198">
+        <v/>
+      </c>
+      <c r="J60" s="198" t="str">
         <f>Data!F57</f>
-        <v>0</v>
-      </c>
-      <c r="K60" s="198">
+        <v/>
+      </c>
+      <c r="K60" s="198" t="str">
         <f>Data!G57</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L60" s="198" t="str">
         <f>Data!H57</f>
@@ -10616,47 +10647,47 @@
       </c>
       <c r="E61" s="311"/>
       <c r="G61" s="188">
-        <f t="shared" ref="G61:Q61" si="20">IF(G4="","",SUM(G58:G60))</f>
+        <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>639</v>
       </c>
       <c r="H61" s="188">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>927</v>
       </c>
-      <c r="I61" s="188">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="188">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K61" s="188">
-        <f t="shared" si="20"/>
-        <v>0</v>
+      <c r="I61" s="188" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="J61" s="188" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="K61" s="188" t="str">
+        <f t="shared" si="22"/>
+        <v/>
       </c>
       <c r="L61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="M61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="N61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="O61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="P61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -10679,17 +10710,17 @@
         <f>Data!D58</f>
         <v>203.76488900000004</v>
       </c>
-      <c r="I62" s="198">
+      <c r="I62" s="198" t="str">
         <f>Data!E58</f>
-        <v>-503.75612799999999</v>
-      </c>
-      <c r="J62" s="198">
+        <v/>
+      </c>
+      <c r="J62" s="198" t="str">
         <f>Data!F58</f>
-        <v>-726.80948300000091</v>
-      </c>
-      <c r="K62" s="198">
+        <v/>
+      </c>
+      <c r="K62" s="198" t="str">
         <f>Data!G58</f>
-        <v>-3450</v>
+        <v/>
       </c>
       <c r="L62" s="198" t="str">
         <f>Data!H58</f>
@@ -10727,47 +10758,47 @@
       </c>
       <c r="E63" s="311"/>
       <c r="G63" s="188">
-        <f t="shared" ref="G63:Q63" si="21">IF(G4="","",G61+G62)</f>
+        <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>136</v>
       </c>
       <c r="H63" s="188">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1130.764889</v>
       </c>
-      <c r="I63" s="188">
-        <f t="shared" si="21"/>
-        <v>-503.75612799999999</v>
-      </c>
-      <c r="J63" s="188">
-        <f t="shared" si="21"/>
-        <v>-726.80948300000091</v>
-      </c>
-      <c r="K63" s="188">
-        <f t="shared" si="21"/>
-        <v>-3450</v>
+      <c r="I63" s="188" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="J63" s="188" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="K63" s="188" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="L63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="N63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="O63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="P63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Q63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -10947,47 +10978,47 @@
       <c r="E73" s="308"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
-        <f t="shared" ref="G73:Q73" si="22">IF(G$4="","",ABS(G5/G$4))</f>
+        <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
         <v>0.60969766115231028</v>
       </c>
       <c r="H73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.54641865162865078</v>
       </c>
-      <c r="I73" s="6">
-        <f t="shared" si="22"/>
-        <v>0.47812220197752181</v>
-      </c>
-      <c r="J73" s="6">
-        <f t="shared" si="22"/>
-        <v>0.45826243510069942</v>
-      </c>
-      <c r="K73" s="6">
-        <f t="shared" si="22"/>
-        <v>0.4139629692542891</v>
+      <c r="I73" s="6" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="J73" s="6" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="K73" s="6" t="str">
+        <f t="shared" si="24"/>
+        <v/>
       </c>
       <c r="L73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="M73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="P73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="Q73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -11004,47 +11035,47 @@
       <c r="E74" s="308"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
-        <f t="shared" ref="G74:Q74" si="23">IF(G$4="","",ABS(G6/G$4))</f>
+        <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
         <v>0.39030233884768967</v>
       </c>
       <c r="H74" s="66">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.45358134837134922</v>
       </c>
-      <c r="I74" s="66">
-        <f t="shared" si="23"/>
-        <v>0.52187779802247813</v>
-      </c>
-      <c r="J74" s="66">
-        <f t="shared" si="23"/>
-        <v>0.54173756489930058</v>
-      </c>
-      <c r="K74" s="66">
-        <f t="shared" si="23"/>
-        <v>0.5860370307457109</v>
+      <c r="I74" s="66" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="J74" s="66" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="K74" s="66" t="str">
+        <f t="shared" si="25"/>
+        <v/>
       </c>
       <c r="L74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="N74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="P74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -11061,47 +11092,47 @@
       <c r="E75" s="308"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
-        <f t="shared" ref="G75:Q75" si="24">IF(G$4="","",ABS(G7/G$4))</f>
+        <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
         <v>0.12367370222475756</v>
       </c>
       <c r="H75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>9.5025671239794635E-2</v>
       </c>
-      <c r="I75" s="6">
-        <f t="shared" si="24"/>
-        <v>5.5428246134247773E-2</v>
-      </c>
-      <c r="J75" s="6">
-        <f t="shared" si="24"/>
-        <v>3.3694951770082464E-2</v>
-      </c>
-      <c r="K75" s="6">
-        <f t="shared" si="24"/>
-        <v>0</v>
+      <c r="I75" s="6" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="J75" s="6" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="K75" s="6" t="str">
+        <f t="shared" si="26"/>
+        <v/>
       </c>
       <c r="L75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="M75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="O75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Q75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -11118,47 +11149,47 @@
       <c r="E76" s="308"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
-        <f t="shared" ref="G76:Q76" si="25">IF(G$4="","",ABS(G8/G$4))</f>
+        <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
         <v>0.26662863662293212</v>
       </c>
       <c r="H76" s="66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.35855567713155456</v>
       </c>
-      <c r="I76" s="66">
-        <f t="shared" si="25"/>
-        <v>0.4664495518882304</v>
-      </c>
-      <c r="J76" s="66">
-        <f t="shared" si="25"/>
-        <v>0.50804261312921806</v>
-      </c>
-      <c r="K76" s="66">
-        <f t="shared" si="25"/>
-        <v>0.5860370307457109</v>
+      <c r="I76" s="66" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="J76" s="66" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="K76" s="66" t="str">
+        <f t="shared" si="27"/>
+        <v/>
       </c>
       <c r="L76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="M76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="N76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="P76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
     </row>
@@ -11175,47 +11206,47 @@
       <c r="E77" s="308"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
-        <f t="shared" ref="G77:Q77" si="26">IF(G$4="","",G9/G$4)</f>
+        <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
         <v>1.825442099258414E-2</v>
       </c>
       <c r="H77" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.6665263866677889E-2</v>
       </c>
-      <c r="I77" s="6">
-        <f t="shared" si="26"/>
-        <v>1.1566229000166427E-2</v>
-      </c>
-      <c r="J77" s="6">
-        <f t="shared" si="26"/>
-        <v>7.6185555491919766E-3</v>
-      </c>
-      <c r="K77" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
+      <c r="I77" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="J77" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="K77" s="6" t="str">
+        <f t="shared" si="28"/>
+        <v/>
       </c>
       <c r="L77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="M77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="N77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="O77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="Q77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -11234,47 +11265,47 @@
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
-        <f t="shared" ref="G78:Q78" si="27">IF(G$4="","",-G10/G$4)</f>
+        <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
         <v>7.8722190530519116E-3</v>
       </c>
       <c r="H78" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>9.0901439272788494E-3</v>
       </c>
-      <c r="I78" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J78" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="K78" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
+      <c r="I78" s="6" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="J78" s="6" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="K78" s="6" t="str">
+        <f t="shared" si="29"/>
+        <v/>
       </c>
       <c r="L78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="M78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="O78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="P78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11291,47 +11322,47 @@
       <c r="E79" s="308"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
-        <f t="shared" ref="G79:Q79" si="28">IF(G$4="","",G11/G$4)</f>
+        <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
         <v>7.2903593839132919E-2</v>
       </c>
       <c r="H79" s="66">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7.8023735375810116E-2</v>
       </c>
-      <c r="I79" s="66">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="J79" s="66">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K79" s="66">
-        <f t="shared" si="28"/>
-        <v>0</v>
+      <c r="I79" s="66" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="J79" s="66" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="K79" s="66" t="str">
+        <f t="shared" si="30"/>
+        <v/>
       </c>
       <c r="L79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="M79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="N79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="O79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="P79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -11348,47 +11379,47 @@
       <c r="E80" s="308"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
-        <f t="shared" ref="G80:Q80" si="29">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>0</v>
+        <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
+        <v>2.9659853391308499E-2</v>
       </c>
       <c r="H80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="I80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="J80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="K80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>1.1724822264738463E-2</v>
+      </c>
+      <c r="I80" s="6" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="J80" s="6" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="K80" s="6" t="str">
+        <f t="shared" si="31"/>
+        <v/>
       </c>
       <c r="L80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="M80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="O80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="P80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="Q80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -11405,47 +11436,47 @@
       <c r="E81" s="308"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
-        <f t="shared" ref="G81:Q81" si="30">IF(G$4="","",G13/G$4)</f>
-        <v>0.34991443240159725</v>
+        <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
+        <v>0.37957428579290575</v>
       </c>
       <c r="H81" s="66">
-        <f t="shared" si="30"/>
-        <v>0.44415453244676373</v>
-      </c>
-      <c r="I81" s="66">
-        <f t="shared" si="30"/>
-        <v>0.47801578088839686</v>
-      </c>
-      <c r="J81" s="66">
-        <f t="shared" si="30"/>
-        <v>0.51566116867841005</v>
-      </c>
-      <c r="K81" s="66">
-        <f t="shared" si="30"/>
-        <v>0.5860370307457109</v>
+        <f t="shared" si="32"/>
+        <v>0.4558793547115022</v>
+      </c>
+      <c r="I81" s="66" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="J81" s="66" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="K81" s="66" t="str">
+        <f t="shared" si="32"/>
+        <v/>
       </c>
       <c r="L81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="N81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="O81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="P81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="Q81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11462,47 +11493,47 @@
       <c r="E82" s="308"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
-        <f t="shared" ref="G82:Q82" si="31">IF(G$4="","",ABS(G14/G$4))</f>
+        <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
         <v>5.9212778094694808E-2</v>
       </c>
       <c r="H82" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>7.2454745223466038E-2</v>
       </c>
-      <c r="I82" s="6">
-        <f t="shared" si="31"/>
-        <v>8.6201848617324689E-2</v>
-      </c>
-      <c r="J82" s="6">
-        <f t="shared" si="31"/>
-        <v>0.10357839908312262</v>
-      </c>
-      <c r="K82" s="6">
-        <f t="shared" si="31"/>
-        <v>0</v>
+      <c r="I82" s="6" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="J82" s="6" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="K82" s="6" t="str">
+        <f t="shared" si="33"/>
+        <v/>
       </c>
       <c r="L82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="N82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="P82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Q82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
     </row>
@@ -11520,47 +11551,47 @@
       <c r="E83" s="308"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
-        <f t="shared" ref="G83:Q83" si="32">IF(G$4="","",-G15/G$4)</f>
+        <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
         <v>0</v>
       </c>
       <c r="H83" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>2.6092079791263361E-3</v>
       </c>
-      <c r="I83" s="6">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J83" s="6">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="K83" s="6">
-        <f t="shared" si="32"/>
-        <v>0</v>
+      <c r="I83" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="J83" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="K83" s="6" t="str">
+        <f t="shared" si="34"/>
+        <v/>
       </c>
       <c r="L83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="P83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
     </row>
@@ -11577,47 +11608,47 @@
       <c r="E84" s="308"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
-        <f t="shared" ref="G84:Q84" si="33">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.29070165430690248</v>
+        <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
+        <v>0.32036150769821098</v>
       </c>
       <c r="H84" s="66">
-        <f t="shared" si="33"/>
-        <v>0.36909057924417138</v>
-      </c>
-      <c r="I84" s="66">
-        <f t="shared" si="33"/>
-        <v>0.39181393227107214</v>
-      </c>
-      <c r="J84" s="66">
-        <f t="shared" si="33"/>
-        <v>0.4120827695952875</v>
-      </c>
-      <c r="K84" s="66">
-        <f t="shared" si="33"/>
-        <v>0.5860370307457109</v>
+        <f t="shared" si="35"/>
+        <v>0.38081540150890986</v>
+      </c>
+      <c r="I84" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="J84" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="K84" s="66" t="str">
+        <f t="shared" si="35"/>
+        <v/>
       </c>
       <c r="L84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="M84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="P84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
     </row>
@@ -11684,47 +11715,47 @@
       <c r="E87" s="308"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
-        <f t="shared" ref="G87:Q87" si="34">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.29070165430690248</v>
+        <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
+        <v>0.32036150769821098</v>
       </c>
       <c r="H87" s="66">
-        <f t="shared" si="34"/>
-        <v>0.36909057924417138</v>
-      </c>
-      <c r="I87" s="66">
-        <f t="shared" si="34"/>
-        <v>0.39181393227107214</v>
-      </c>
-      <c r="J87" s="66">
-        <f t="shared" si="34"/>
-        <v>0.4120827695952875</v>
-      </c>
-      <c r="K87" s="66">
-        <f t="shared" si="34"/>
-        <v>0.5860370307457109</v>
+        <f t="shared" si="36"/>
+        <v>0.38081540150890986</v>
+      </c>
+      <c r="I87" s="66" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="J87" s="66" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="K87" s="66" t="str">
+        <f t="shared" si="36"/>
+        <v/>
       </c>
       <c r="L87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="M87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="N87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="O87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="P87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -11758,17 +11789,17 @@
         <f>Data!D64</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="I90" s="116">
+      <c r="I90" s="116" t="str">
         <f>Data!E64</f>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="J90" s="116">
+        <v/>
+      </c>
+      <c r="J90" s="116" t="str">
         <f>Data!F64</f>
-        <v>0</v>
-      </c>
-      <c r="K90" s="116">
+        <v/>
+      </c>
+      <c r="K90" s="116" t="str">
         <f>Data!G64</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L90" s="116" t="str">
         <f>Data!H64</f>
@@ -11807,47 +11838,47 @@
       </c>
       <c r="E91" s="311"/>
       <c r="G91" s="76">
-        <f t="shared" ref="G91:Q91" si="35">IF(G$4="","",G90*Common_Shares/$C$3)</f>
+        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
         <v>4739.6903628800001</v>
       </c>
       <c r="H91" s="76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4739.6903628800001</v>
       </c>
-      <c r="I91" s="76">
-        <f t="shared" si="35"/>
-        <v>4657.9715635199991</v>
-      </c>
-      <c r="J91" s="76">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="K91" s="76">
-        <f t="shared" si="35"/>
-        <v>0</v>
+      <c r="I91" s="76" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="J91" s="76" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="K91" s="76" t="str">
+        <f t="shared" si="37"/>
+        <v/>
       </c>
       <c r="L91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="M91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="O91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="P91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="Q91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -11862,47 +11893,47 @@
       </c>
       <c r="E92" s="311"/>
       <c r="G92" s="175">
-        <f t="shared" ref="G92:Q92" si="36">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>1.8601610529356356</v>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
+        <v>1.6879427845465798</v>
       </c>
       <c r="H92" s="175">
-        <f t="shared" si="36"/>
-        <v>1.0808464851321227</v>
-      </c>
-      <c r="I92" s="175">
-        <f t="shared" si="36"/>
-        <v>0.75960354445630085</v>
-      </c>
-      <c r="J92" s="175">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="K92" s="175">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>1.0475685954159291</v>
+      </c>
+      <c r="I92" s="175" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="J92" s="175" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="K92" s="175" t="str">
+        <f t="shared" si="38"/>
+        <v/>
       </c>
       <c r="L92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="M92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="N92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="P92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="Q92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -11917,47 +11948,47 @@
       </c>
       <c r="E93" s="311"/>
       <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="37">IF(G$4="","",G90/Market_Price)</f>
+        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>7.3417721518987331E-2</v>
       </c>
       <c r="H93" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>7.3417721518987331E-2</v>
       </c>
-      <c r="I93" s="23">
-        <f t="shared" si="37"/>
-        <v>7.2151898734177211E-2</v>
-      </c>
-      <c r="J93" s="23">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K93" s="23">
-        <f t="shared" si="37"/>
-        <v>0</v>
+      <c r="I93" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="J93" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K93" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
       </c>
       <c r="L93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="M93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="O93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Q93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -11999,47 +12030,47 @@
       <c r="E96" s="308"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="38">IF(H4="","",G4/H4-1)</f>
+        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
         <v>-0.26226748590186011</v>
       </c>
-      <c r="H96" s="6">
-        <f t="shared" si="38"/>
-        <v>-0.2408579989228844</v>
-      </c>
-      <c r="I96" s="6">
-        <f t="shared" si="38"/>
-        <v>-0.35945953217712834</v>
-      </c>
-      <c r="J96" s="6">
-        <f t="shared" si="38"/>
-        <v>3.150394387463904</v>
+      <c r="H96" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="I96" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="J96" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
       </c>
       <c r="K96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="L96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="M96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="N96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="O96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="P96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="Q96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -12050,53 +12081,53 @@
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>9.9776867121067703E-2</v>
+        <v>1.3840538284081383E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="308"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="39">IF(H5="","",G13/H13-1)</f>
-        <v>-0.41879855978775815</v>
-      </c>
-      <c r="H97" s="6">
-        <f t="shared" si="39"/>
-        <v>-0.29463341163661705</v>
-      </c>
-      <c r="I97" s="6">
-        <f t="shared" si="39"/>
-        <v>-0.40622162281154406</v>
-      </c>
-      <c r="J97" s="6">
-        <f t="shared" si="39"/>
-        <v>2.6519829089855076</v>
+        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <v>-0.38574912583568022</v>
+      </c>
+      <c r="H97" s="6" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="I97" s="6" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="J97" s="6" t="str">
+        <f t="shared" si="41"/>
+        <v/>
       </c>
       <c r="K97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="L97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="M97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="N97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="O97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="P97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="Q97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
@@ -12149,47 +12180,47 @@
       <c r="E101" s="312"/>
       <c r="F101" s="26"/>
       <c r="G101" s="187">
-        <f t="shared" ref="G101:Q101" si="40">IF(G$4="","",G105+G104)</f>
+        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>180344</v>
       </c>
       <c r="H101" s="187">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>174007</v>
       </c>
-      <c r="I101" s="187">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="J101" s="187">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="K101" s="187">
-        <f t="shared" si="40"/>
-        <v>0</v>
+      <c r="I101" s="187" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="J101" s="187" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="K101" s="187" t="str">
+        <f t="shared" si="42"/>
+        <v/>
       </c>
       <c r="L101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="M101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="N101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="O101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="P101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="Q101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
@@ -12209,17 +12240,17 @@
         <f>IF(G$4="","",Data!D76)</f>
         <v>7251</v>
       </c>
-      <c r="H102" s="189">
+      <c r="H102" s="189" t="str">
         <f>IF(H$4="","",Data!E76)</f>
-        <v>0</v>
-      </c>
-      <c r="I102" s="189">
+        <v/>
+      </c>
+      <c r="I102" s="189" t="str">
         <f>IF(I$4="","",Data!F76)</f>
-        <v>0</v>
-      </c>
-      <c r="J102" s="189">
+        <v/>
+      </c>
+      <c r="J102" s="189" t="str">
         <f>IF(J$4="","",Data!G76)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K102" s="189" t="str">
         <f>IF(K$4="","",Data!H76)</f>
@@ -12266,17 +12297,17 @@
         <f>IF(G$4="","",Data!D77)</f>
         <v>16389</v>
       </c>
-      <c r="H103" s="189">
+      <c r="H103" s="189" t="str">
         <f>IF(H$4="","",Data!E77)</f>
-        <v>0</v>
-      </c>
-      <c r="I103" s="189">
+        <v/>
+      </c>
+      <c r="I103" s="189" t="str">
         <f>IF(I$4="","",Data!F77)</f>
-        <v>0</v>
-      </c>
-      <c r="J103" s="189">
+        <v/>
+      </c>
+      <c r="J103" s="189" t="str">
         <f>IF(J$4="","",Data!G77)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K103" s="189" t="str">
         <f>IF(K$4="","",Data!H77)</f>
@@ -12327,17 +12358,17 @@
         <f>Data!D78</f>
         <v>10902</v>
       </c>
-      <c r="I104" s="187">
+      <c r="I104" s="187" t="str">
         <f>Data!E78</f>
-        <v>0</v>
-      </c>
-      <c r="J104" s="187">
+        <v/>
+      </c>
+      <c r="J104" s="187" t="str">
         <f>Data!F78</f>
-        <v>0</v>
-      </c>
-      <c r="K104" s="187">
+        <v/>
+      </c>
+      <c r="K104" s="187" t="str">
         <f>Data!G78</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L104" s="187" t="str">
         <f>Data!H78</f>
@@ -12384,17 +12415,17 @@
         <f>Data!D79</f>
         <v>163105</v>
       </c>
-      <c r="I105" s="187">
+      <c r="I105" s="187" t="str">
         <f>Data!E79</f>
-        <v>0</v>
-      </c>
-      <c r="J105" s="187">
+        <v/>
+      </c>
+      <c r="J105" s="187" t="str">
         <f>Data!F79</f>
-        <v>0</v>
-      </c>
-      <c r="K105" s="187">
+        <v/>
+      </c>
+      <c r="K105" s="187" t="str">
         <f>Data!G79</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L105" s="187" t="str">
         <f>Data!H79</f>
@@ -12461,47 +12492,47 @@
       <c r="E108" s="312"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
-        <f t="shared" ref="G108:Q108" si="41">IF(G$4="","",G102/G$4)</f>
+        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
         <v>0.82726754135767255</v>
       </c>
-      <c r="H108" s="97">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="I108" s="97">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="J108" s="97">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="K108" s="97" t="e">
-        <f t="shared" si="41"/>
+      <c r="H108" s="97" t="e">
+        <f t="shared" si="43"/>
         <v>#VALUE!</v>
       </c>
+      <c r="I108" s="97" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="J108" s="97" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="K108" s="97" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
       <c r="L108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="M108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="N108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="O108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="P108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Q108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -12518,47 +12549,47 @@
       <c r="E109" s="312"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
-        <f t="shared" ref="G109:Q109" si="42">IF(G$4="","",G103/G$4)</f>
+        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
         <v>1.8698231602966344</v>
       </c>
-      <c r="H109" s="97">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="I109" s="97">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="J109" s="97">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="K109" s="97" t="e">
-        <f t="shared" si="42"/>
+      <c r="H109" s="97" t="e">
+        <f t="shared" si="44"/>
         <v>#VALUE!</v>
       </c>
+      <c r="I109" s="97" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="J109" s="97" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="K109" s="97" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
       <c r="L109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="M109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="N109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="O109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="P109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="Q109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
@@ -12658,47 +12689,47 @@
       </c>
       <c r="E113" s="311"/>
       <c r="G113" s="23">
-        <f t="shared" ref="G113:Q113" si="43">G81</f>
-        <v>0.34991443240159725</v>
+        <f t="shared" ref="G113:Q113" si="45">G81</f>
+        <v>0.37957428579290575</v>
       </c>
       <c r="H113" s="23">
-        <f t="shared" si="43"/>
-        <v>0.44415453244676373</v>
-      </c>
-      <c r="I113" s="23">
-        <f t="shared" si="43"/>
-        <v>0.47801578088839686</v>
-      </c>
-      <c r="J113" s="23">
-        <f t="shared" si="43"/>
-        <v>0.51566116867841005</v>
-      </c>
-      <c r="K113" s="23">
-        <f t="shared" si="43"/>
-        <v>0.5860370307457109</v>
+        <f t="shared" si="45"/>
+        <v>0.4558793547115022</v>
+      </c>
+      <c r="I113" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="J113" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="K113" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
       </c>
       <c r="L113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="M113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="N113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="O113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="P113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Q113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
@@ -12712,47 +12743,47 @@
       </c>
       <c r="E114" s="311"/>
       <c r="G114" s="42">
-        <f t="shared" ref="G114:Q114" si="44">IF(G4="","",G4/G101)</f>
+        <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
         <v>4.8601561460320276E-2</v>
       </c>
       <c r="H114" s="42">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>6.8278862344618316E-2</v>
       </c>
-      <c r="I114" s="42" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J114" s="42" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K114" s="42" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
+      <c r="I114" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="J114" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="K114" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
       </c>
       <c r="L114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="M114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="N114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="O114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="P114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="Q114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
@@ -12768,47 +12799,47 @@
       <c r="E115" s="315"/>
       <c r="F115" s="11"/>
       <c r="G115" s="15">
-        <f t="shared" ref="G115:Q115" si="45">IF(G$4="","",G101/G105)</f>
+        <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
         <v>1.0843454628538445</v>
       </c>
       <c r="H115" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1.0668403788970295</v>
       </c>
-      <c r="I115" s="15" t="e">
-        <f t="shared" si="45"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J115" s="15" t="e">
-        <f t="shared" si="45"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K115" s="15" t="e">
-        <f t="shared" si="45"/>
-        <v>#DIV/0!</v>
+      <c r="I115" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="J115" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="K115" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
       </c>
       <c r="L115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="M115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="N115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="O115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="P115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="Q115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
@@ -12825,47 +12856,47 @@
       <c r="E116" s="314"/>
       <c r="F116" s="106"/>
       <c r="G116" s="105">
-        <f t="shared" ref="G116:Q116" si="46">IF(G$4="","",G8/G105)</f>
+        <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
         <v>1.4051564491690517E-2</v>
       </c>
       <c r="H116" s="105">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>2.6118144753379726E-2</v>
       </c>
-      <c r="I116" s="105" t="e">
-        <f t="shared" si="46"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J116" s="105" t="e">
-        <f t="shared" si="46"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K116" s="105" t="e">
-        <f t="shared" si="46"/>
-        <v>#DIV/0!</v>
+      <c r="I116" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="J116" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="K116" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
       </c>
       <c r="L116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="M116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="N116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="O116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="P116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="Q116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
@@ -12946,47 +12977,47 @@
       <c r="E120" s="308"/>
       <c r="F120" s="27"/>
       <c r="G120" s="182">
-        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.31180095889260018</v>
+        <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>0.34361354265677985</v>
       </c>
       <c r="H120" s="182">
-        <f t="shared" si="47"/>
-        <v>0.53661644644114359</v>
-      </c>
-      <c r="I120" s="182">
-        <f t="shared" si="47"/>
-        <v>0.7503914432205383</v>
-      </c>
-      <c r="J120" s="182">
-        <f t="shared" si="47"/>
-        <v>1.2320997841199808</v>
-      </c>
-      <c r="K120" s="182">
-        <f t="shared" si="47"/>
-        <v>0.42217947730748451</v>
+        <f t="shared" si="49"/>
+        <v>0.55366302745045104</v>
+      </c>
+      <c r="I120" s="182" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="J120" s="182" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="K120" s="182" t="str">
+        <f t="shared" si="49"/>
+        <v/>
       </c>
       <c r="L120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="M120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="N120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="O120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="P120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="Q120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
@@ -13003,47 +13034,47 @@
       <c r="E121" s="308"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
-        <f t="shared" ref="G121" si="48">IF(G$4="","",G120/Market_Price)</f>
-        <v>3.9468475809189892E-2</v>
+        <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
+        <v>4.3495385146427826E-2</v>
       </c>
       <c r="H121" s="79">
-        <f t="shared" ref="H121" si="49">IF(H$4="","",H120/Market_Price)</f>
-        <v>6.7926132460904246E-2</v>
-      </c>
-      <c r="I121" s="79">
-        <f t="shared" ref="I121" si="50">IF(I$4="","",I120/Market_Price)</f>
-        <v>9.4986258635511175E-2</v>
-      </c>
-      <c r="J121" s="79">
-        <f t="shared" ref="J121" si="51">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.15596199798987098</v>
-      </c>
-      <c r="K121" s="79">
-        <f t="shared" ref="K121" si="52">IF(K$4="","",K120/Market_Price)</f>
-        <v>5.3440440165504366E-2</v>
+        <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
+        <v>7.0083927525373541E-2</v>
+      </c>
+      <c r="I121" s="79" t="str">
+        <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="J121" s="79" t="str">
+        <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="K121" s="79" t="str">
+        <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
+        <v/>
       </c>
       <c r="L121" s="79" t="str">
-        <f t="shared" ref="L121" si="53">IF(L$4="","",L120/Market_Price)</f>
+        <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
         <v/>
       </c>
       <c r="M121" s="79" t="str">
-        <f t="shared" ref="M121" si="54">IF(M$4="","",M120/Market_Price)</f>
+        <f t="shared" ref="M121" si="56">IF(M$4="","",M120/Market_Price)</f>
         <v/>
       </c>
       <c r="N121" s="79" t="str">
-        <f t="shared" ref="N121" si="55">IF(N$4="","",N120/Market_Price)</f>
+        <f t="shared" ref="N121" si="57">IF(N$4="","",N120/Market_Price)</f>
         <v/>
       </c>
       <c r="O121" s="79" t="str">
-        <f t="shared" ref="O121" si="56">IF(O$4="","",O120/Market_Price)</f>
+        <f t="shared" ref="O121" si="58">IF(O$4="","",O120/Market_Price)</f>
         <v/>
       </c>
       <c r="P121" s="79" t="str">
-        <f t="shared" ref="P121" si="57">IF(P$4="","",P120/Market_Price)</f>
+        <f t="shared" ref="P121" si="59">IF(P$4="","",P120/Market_Price)</f>
         <v/>
       </c>
       <c r="Q121" s="79" t="str">
-        <f t="shared" ref="Q121" si="58">IF(Q$4="","",Q120/Market_Price)</f>
+        <f t="shared" ref="Q121" si="60">IF(Q$4="","",Q120/Market_Price)</f>
         <v/>
       </c>
     </row>
@@ -13829,10 +13860,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="346" t="s">
+      <c r="E6" s="345" t="s">
         <v>256</v>
       </c>
-      <c r="F6" s="346"/>
+      <c r="F6" s="345"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -13847,8 +13878,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="346"/>
-      <c r="F7" s="346"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -13863,8 +13894,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -13879,8 +13910,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15374,11 +15405,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="348" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="348"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="284">
         <v>4</v>
       </c>
@@ -15393,14 +15424,14 @@
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>2548</v>
+        <v>2807.968614974819</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="284">
         <v>5</v>
       </c>
@@ -15421,8 +15452,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="284">
         <v>6</v>
       </c>
@@ -15432,8 +15463,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="348"/>
-      <c r="F10" s="348"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="284">
         <v>7</v>
       </c>
@@ -15446,8 +15477,8 @@
       <c r="B11" s="164" t="s">
         <v>295</v>
       </c>
-      <c r="E11" s="348"/>
-      <c r="F11" s="348"/>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="284">
         <v>8</v>
       </c>
@@ -15460,13 +15491,13 @@
       <c r="B12" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="C12" s="163">
+      <c r="C12" s="163" t="e">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.28945840615733698</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D12" s="163"/>
-      <c r="E12" s="348"/>
-      <c r="F12" s="348"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="284">
         <v>9</v>
       </c>
@@ -15479,12 +15510,12 @@
       <c r="B13" s="152" t="s">
         <v>157</v>
       </c>
-      <c r="C13" s="163">
+      <c r="C13" s="163" t="e">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.42686307479092267</v>
-      </c>
-      <c r="E13" s="348"/>
-      <c r="F13" s="348"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="284">
         <v>10</v>
       </c>
@@ -15497,12 +15528,12 @@
       <c r="B14" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="163">
+      <c r="C14" s="163" t="e">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.36747573837633207</v>
-      </c>
-      <c r="E14" s="348"/>
-      <c r="F14" s="348"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15528,21 +15559,21 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="348" t="s">
+      <c r="E18" s="347" t="s">
         <v>368</v>
       </c>
-      <c r="F18" s="349"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="349"/>
-      <c r="F19" s="349"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="164" t="s">
         <v>332</v>
       </c>
-      <c r="E20" s="349"/>
-      <c r="F20" s="349"/>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -15556,8 +15587,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="349"/>
-      <c r="F21" s="349"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -15571,8 +15602,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="349"/>
-      <c r="F22" s="349"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="164" t="s">
@@ -15592,8 +15623,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="168"/>
-      <c r="E25" s="347"/>
-      <c r="F25" s="347"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -15603,8 +15634,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="169"/>
-      <c r="E26" s="347"/>
-      <c r="F26" s="347"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -15618,8 +15649,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="347"/>
-      <c r="F27" s="347"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -15629,8 +15660,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="170"/>
-      <c r="E28" s="347"/>
-      <c r="F28" s="347"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="164" t="s">
@@ -15650,8 +15681,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="168"/>
-      <c r="E31" s="347"/>
-      <c r="F31" s="347"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -15661,8 +15692,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="169"/>
-      <c r="E32" s="347"/>
-      <c r="F32" s="347"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -15676,8 +15707,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="347"/>
-      <c r="F33" s="347"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -15687,8 +15718,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="170"/>
-      <c r="E34" s="347"/>
-      <c r="F34" s="347"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="164" t="s">
@@ -15708,8 +15739,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="168"/>
-      <c r="E37" s="347"/>
-      <c r="F37" s="347"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -15719,8 +15750,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="169"/>
-      <c r="E38" s="347"/>
-      <c r="F38" s="347"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -15734,8 +15765,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="347"/>
-      <c r="F39" s="347"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -15746,8 +15777,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="170"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -15809,8 +15840,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="168"/>
-      <c r="E49" s="347"/>
-      <c r="F49" s="347"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -15820,8 +15851,8 @@
         <v>-0.2</v>
       </c>
       <c r="D50" s="169"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -15835,8 +15866,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="347"/>
-      <c r="F51" s="347"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -15846,8 +15877,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="170"/>
-      <c r="E52" s="347"/>
-      <c r="F52" s="347"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="164" t="s">
@@ -15867,8 +15898,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="168"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -15878,8 +15909,8 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="169"/>
-      <c r="E56" s="347"/>
-      <c r="F56" s="347"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -15893,8 +15924,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="347"/>
-      <c r="F57" s="347"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -15904,8 +15935,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="170"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -16029,12 +16060,15 @@
         <v>312</v>
       </c>
       <c r="C72" s="280" t="str">
-        <f>IF(E72&gt;50%,"Y","N")</f>
+        <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="E72" s="138" t="str">
-        <f>"Non-FCF Value is "&amp;ROUND(BS!D89/C60*100,0)&amp;"% of the Expected Equity Value"</f>
-        <v>Non-FCF Value is 63% of the Expected Equity Value</v>
+      <c r="E72" s="138" t="s">
+        <v>391</v>
+      </c>
+      <c r="F72" s="349">
+        <f>BS!D89/C60</f>
+        <v>0.62612608991135499</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01ECF68-34A5-476C-BB47-1B2D9EB84220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184A39BD-C96D-4D89-903D-B691DEBEED7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2673,7 +2673,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="350">
+  <cellXfs count="348">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3016,7 +3016,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3238,9 +3237,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="190" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3377,22 +3373,25 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="193" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -3406,9 +3405,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3705,15 +3701,15 @@
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="292" t="s">
+      <c r="E1" s="290" t="s">
         <v>349</v>
       </c>
-      <c r="F1" s="293" t="s">
+      <c r="F1" s="291" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A2" s="254" t="s">
+      <c r="A2" s="253" t="s">
         <v>281</v>
       </c>
       <c r="B2" s="36"/>
@@ -3773,7 +3769,7 @@
       <c r="B8" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C8" s="287">
+      <c r="C8" s="285">
         <v>6</v>
       </c>
       <c r="D8" s="5"/>
@@ -3807,13 +3803,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="338" t="s">
         <v>286</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3868,7 +3864,7 @@
       <c r="B19" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C19" s="256">
+      <c r="C19" s="255">
         <v>0.2</v>
       </c>
       <c r="E19" s="5"/>
@@ -3878,14 +3874,14 @@
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="259">
+      <c r="C20" s="258">
         <f>C127</f>
         <v>6.4501768017717804</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="E20" s="322">
+      <c r="E20" s="320">
         <v>3</v>
       </c>
     </row>
@@ -3893,7 +3889,7 @@
       <c r="B21" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C21" s="288">
+      <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
         <v>0.11614149089878545</v>
       </c>
@@ -3905,7 +3901,7 @@
       <c r="E22" s="5"/>
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A23" s="254" t="s">
+      <c r="A23" s="253" t="s">
         <v>235</v>
       </c>
       <c r="B23" s="36"/>
@@ -3915,25 +3911,25 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="338" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="342" t="s">
         <v>382</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B28" s="241" t="s">
+      <c r="B28" s="240" t="s">
         <v>237</v>
       </c>
       <c r="C28" s="111">
@@ -3942,19 +3938,19 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="340" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C30" s="192">
+      <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
         <v>2591.8202592374382</v>
       </c>
@@ -3968,19 +3964,19 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="340" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="192">
+      <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
         <v>159.99999999999997</v>
       </c>
@@ -3993,7 +3989,7 @@
       <c r="B34" s="52" t="s">
         <v>242</v>
       </c>
-      <c r="C34" s="192">
+      <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
         <v>-159.99999999999997</v>
       </c>
@@ -4003,19 +3999,19 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="340" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
         <v>244</v>
       </c>
-      <c r="C37" s="192">
+      <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
         <v>639</v>
       </c>
@@ -4025,19 +4021,19 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="340" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
         <v>383</v>
       </c>
-      <c r="C40" s="332">
+      <c r="C40" s="330">
         <f>Normalized_FCF!C48</f>
         <v>185.19539222287685</v>
       </c>
@@ -4045,14 +4041,14 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E40" s="331"/>
-      <c r="F40" s="331"/>
+      <c r="E40" s="329"/>
+      <c r="F40" s="329"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
         <v>384</v>
       </c>
-      <c r="C41" s="332">
+      <c r="C41" s="330">
         <f>Normalized_FCF!C47</f>
         <v>-43</v>
       </c>
@@ -4060,14 +4056,14 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E41" s="331"/>
-      <c r="F41" s="331"/>
+      <c r="E41" s="329"/>
+      <c r="F41" s="329"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
         <v>245</v>
       </c>
-      <c r="C42" s="192">
+      <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
         <v>142.19539222287685</v>
       </c>
@@ -4085,7 +4081,7 @@
       <c r="B45" s="47" t="s">
         <v>279</v>
       </c>
-      <c r="C45" s="192">
+      <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
         <v>-22.869707937042335</v>
       </c>
@@ -4095,19 +4091,19 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="340" t="s">
         <v>248</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
         <v>246</v>
       </c>
-      <c r="C48" s="192">
+      <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
         <v>-809.52375635047554</v>
       </c>
@@ -4117,13 +4113,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="340" t="s">
         <v>381</v>
       </c>
-      <c r="C50" s="343"/>
-      <c r="D50" s="343"/>
-      <c r="E50" s="343"/>
-      <c r="F50" s="343"/>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4139,28 +4135,28 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="338" t="s">
         <v>386</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="338" t="s">
         <v>268</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C56" s="192">
+      <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
         <v>2807.968614974819</v>
       </c>
@@ -4173,7 +4169,7 @@
       <c r="B57" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="C57" s="192">
+      <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
         <v>2540.6221871727971</v>
       </c>
@@ -4183,7 +4179,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B58" s="261" t="s">
+      <c r="B58" s="260" t="s">
         <v>284</v>
       </c>
       <c r="C58" s="94">
@@ -4192,7 +4188,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B59" s="261" t="s">
+      <c r="B59" s="260" t="s">
         <v>340</v>
       </c>
       <c r="C59" s="94">
@@ -4201,7 +4197,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A61" s="254" t="s">
+      <c r="A61" s="253" t="s">
         <v>302</v>
       </c>
       <c r="B61" s="36"/>
@@ -4211,29 +4207,29 @@
       <c r="F61" s="36"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="240"/>
+      <c r="A62" s="239"/>
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
+      <c r="B63" s="340" t="s">
         <v>303</v>
       </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="342" t="s">
         <v>259</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B66" s="241" t="s">
+      <c r="B66" s="240" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4241,7 +4237,7 @@
       <c r="B67" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C67" s="320">
+      <c r="C67" s="318">
         <v>0.08</v>
       </c>
     </row>
@@ -4249,11 +4245,11 @@
       <c r="B68" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C68" s="271">
+      <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0.01</v>
       </c>
-      <c r="D68" s="295" t="s">
+      <c r="D68" s="293" t="s">
         <v>307</v>
       </c>
     </row>
@@ -4261,11 +4257,11 @@
       <c r="B69" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C69" s="271">
+      <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D69" s="295" t="s">
+      <c r="D69" s="293" t="s">
         <v>357</v>
       </c>
     </row>
@@ -4273,7 +4269,7 @@
       <c r="B70" s="82" t="s">
         <v>254</v>
       </c>
-      <c r="C70" s="271">
+      <c r="C70" s="269">
         <f>SUM(C67:C69)</f>
         <v>0.09</v>
       </c>
@@ -4282,28 +4278,28 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="340" t="s">
+      <c r="B72" s="338" t="s">
         <v>387</v>
       </c>
-      <c r="C72" s="340"/>
-      <c r="D72" s="340"/>
-      <c r="E72" s="340"/>
-      <c r="F72" s="340"/>
+      <c r="C72" s="338"/>
+      <c r="D72" s="338"/>
+      <c r="E72" s="338"/>
+      <c r="F72" s="338"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="338" t="s">
         <v>388</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C75" s="271">
+      <c r="C75" s="269">
         <v>0</v>
       </c>
     </row>
@@ -4311,7 +4307,7 @@
       <c r="B76" s="47" t="s">
         <v>301</v>
       </c>
-      <c r="C76" s="255">
+      <c r="C76" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
         <v>3.4544236618885975</v>
       </c>
@@ -4321,7 +4317,7 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A78" s="254" t="s">
+      <c r="A78" s="253" t="s">
         <v>260</v>
       </c>
       <c r="B78" s="36"/>
@@ -4331,16 +4327,16 @@
       <c r="F78" s="36"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="240"/>
+      <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="340" t="s">
+      <c r="B80" s="338" t="s">
         <v>261</v>
       </c>
-      <c r="C80" s="340"/>
-      <c r="D80" s="340"/>
-      <c r="E80" s="340"/>
-      <c r="F80" s="340"/>
+      <c r="C80" s="338"/>
+      <c r="D80" s="338"/>
+      <c r="E80" s="338"/>
+      <c r="F80" s="338"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4348,24 +4344,24 @@
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B83" s="241" t="s">
+      <c r="B83" s="240" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="340" t="s">
+      <c r="B84" s="338" t="s">
         <v>389</v>
       </c>
-      <c r="C84" s="340"/>
-      <c r="D84" s="340"/>
-      <c r="E84" s="340"/>
-      <c r="F84" s="340"/>
+      <c r="C84" s="338"/>
+      <c r="D84" s="338"/>
+      <c r="E84" s="338"/>
+      <c r="F84" s="338"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="C85" s="192">
+      <c r="C85" s="191">
         <f>Valuation_Model!C7</f>
         <v>3093</v>
       </c>
@@ -4378,7 +4374,7 @@
       <c r="B86" s="47" t="s">
         <v>304</v>
       </c>
-      <c r="C86" s="255">
+      <c r="C86" s="254">
         <f>C85*C28*Exchange_Rate/Common_Shares</f>
         <v>0.37849307922088393</v>
       </c>
@@ -4396,7 +4392,7 @@
       <c r="B89" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="C89" s="192">
+      <c r="C89" s="191">
         <f>BS!C66</f>
         <v>47679</v>
       </c>
@@ -4409,7 +4405,7 @@
       <c r="B90" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="C90" s="192">
+      <c r="C90" s="191">
         <f>Valuation_Model!C8</f>
         <v>41505.820259237436</v>
       </c>
@@ -4422,7 +4418,7 @@
       <c r="B91" s="47" t="s">
         <v>305</v>
       </c>
-      <c r="C91" s="255">
+      <c r="C91" s="254">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
         <v>5.0791030441342784</v>
       </c>
@@ -4440,7 +4436,7 @@
       <c r="B94" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C94" s="192">
+      <c r="C94" s="191">
         <f>Valuation_Model!C9</f>
         <v>7814.4</v>
       </c>
@@ -4453,7 +4449,7 @@
       <c r="B95" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="C95" s="255">
+      <c r="C95" s="254">
         <f>C94*C28*Exchange_Rate/Common_Shares</f>
         <v>0.95625487173090062</v>
       </c>
@@ -4463,19 +4459,19 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="340" t="s">
+      <c r="B97" s="338" t="s">
         <v>267</v>
       </c>
-      <c r="C97" s="340"/>
-      <c r="D97" s="340"/>
-      <c r="E97" s="340"/>
-      <c r="F97" s="340"/>
+      <c r="C97" s="338"/>
+      <c r="D97" s="338"/>
+      <c r="E97" s="338"/>
+      <c r="F97" s="338"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
         <v>300</v>
       </c>
-      <c r="C99" s="255">
+      <c r="C99" s="254">
         <f>Valuation_Model!C12</f>
         <v>9.111288498532895</v>
       </c>
@@ -4485,7 +4481,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A101" s="254" t="s">
+      <c r="A101" s="253" t="s">
         <v>277</v>
       </c>
       <c r="B101" s="36"/>
@@ -4495,165 +4491,165 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="339" t="s">
+      <c r="B103" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C103" s="339"/>
-      <c r="D103" s="339"/>
-      <c r="E103" s="339"/>
-      <c r="F103" s="339"/>
+      <c r="C103" s="340"/>
+      <c r="D103" s="340"/>
+      <c r="E103" s="340"/>
+      <c r="F103" s="340"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B105" s="267" t="s">
+      <c r="B105" s="266" t="s">
         <v>122</v>
       </c>
-      <c r="C105" s="267" t="s">
+      <c r="C105" s="266" t="s">
         <v>137</v>
       </c>
-      <c r="D105" s="267" t="s">
+      <c r="D105" s="266" t="s">
         <v>117</v>
       </c>
-      <c r="E105" s="267" t="s">
+      <c r="E105" s="266" t="s">
         <v>270</v>
       </c>
-      <c r="F105" s="267" t="s">
+      <c r="F105" s="266" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B106" s="262" t="str">
+      <c r="B106" s="261" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C106" s="263">
+      <c r="C106" s="262">
         <f>Valuation_Model!C74</f>
         <v>0.05</v>
       </c>
-      <c r="D106" s="264">
+      <c r="D106" s="263">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E106" s="265" t="str">
+      <c r="E106" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>10.16 HKD</v>
       </c>
-      <c r="F106" s="266">
+      <c r="F106" s="265">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="249" t="str">
+      <c r="B107" s="248" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C107" s="250">
+      <c r="C107" s="249">
         <f>Valuation_Model!C75</f>
         <v>0.02</v>
       </c>
-      <c r="D107" s="251">
+      <c r="D107" s="250">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E107" s="252" t="str">
+      <c r="E107" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>9.34 HKD</v>
       </c>
-      <c r="F107" s="253">
+      <c r="F107" s="252">
         <f>Valuation_Model!F75</f>
         <v>0.22499999999999992</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="249" t="str">
+      <c r="B108" s="248" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C108" s="250">
+      <c r="C108" s="249">
         <f>Valuation_Model!C76</f>
         <v>0</v>
       </c>
-      <c r="D108" s="251">
+      <c r="D108" s="250">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E108" s="252" t="str">
+      <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>9.11 HKD</v>
       </c>
-      <c r="F108" s="253">
+      <c r="F108" s="252">
         <f>Valuation_Model!F76</f>
         <v>0.495</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="249" t="str">
+      <c r="B109" s="248" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C109" s="250">
+      <c r="C109" s="249">
         <f>Valuation_Model!C77</f>
         <v>-0.05</v>
       </c>
-      <c r="D109" s="251">
+      <c r="D109" s="250">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E109" s="252" t="str">
+      <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>8.62 HKD</v>
       </c>
-      <c r="F109" s="253">
+      <c r="F109" s="252">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="249" t="str">
+      <c r="B110" s="248" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C110" s="250">
+      <c r="C110" s="249">
         <f>Valuation_Model!C78</f>
         <v>-0.2</v>
       </c>
-      <c r="D110" s="251">
+      <c r="D110" s="250">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E110" s="252" t="str">
+      <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>7.26 HKD</v>
       </c>
-      <c r="F110" s="253">
+      <c r="F110" s="252">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B112" s="242" t="s">
+      <c r="B112" s="241" t="s">
         <v>269</v>
       </c>
-      <c r="C112" s="248">
+      <c r="C112" s="247">
         <f>Scenarios!C60</f>
         <v>9.0347055134616365</v>
       </c>
-      <c r="D112" s="243" t="str">
+      <c r="D112" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="344" t="s">
+      <c r="B114" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C114" s="344"/>
-      <c r="D114" s="344"/>
-      <c r="E114" s="344"/>
-      <c r="F114" s="344"/>
+      <c r="C114" s="343"/>
+      <c r="D114" s="343"/>
+      <c r="E114" s="343"/>
+      <c r="F114" s="343"/>
     </row>
     <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A116" s="254" t="s">
+      <c r="A116" s="253" t="s">
         <v>299</v>
       </c>
       <c r="B116" s="36"/>
@@ -4663,16 +4659,16 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="342" t="s">
+      <c r="B118" s="339" t="s">
         <v>275</v>
       </c>
-      <c r="C118" s="342"/>
-      <c r="D118" s="342"/>
-      <c r="E118" s="342"/>
-      <c r="F118" s="342"/>
+      <c r="C118" s="339"/>
+      <c r="D118" s="339"/>
+      <c r="E118" s="339"/>
+      <c r="F118" s="339"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="241" t="s">
+      <c r="B119" s="240" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4680,7 +4676,7 @@
       <c r="B120" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C120" s="258">
+      <c r="C120" s="257">
         <f>E20</f>
         <v>3</v>
       </c>
@@ -4689,45 +4685,45 @@
       <c r="B121" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C121" s="257">
+      <c r="C121" s="256">
         <f>C19</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="243" t="s">
+      <c r="B122" s="242" t="s">
         <v>272</v>
       </c>
-      <c r="C122" s="244">
+      <c r="C122" s="243">
         <f>Scenarios!C77</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="D122" s="243" t="str">
+      <c r="D122" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="241" t="s">
+      <c r="B124" s="240" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B125" s="243" t="str">
+      <c r="B125" s="242" t="str">
         <f>"PV("&amp;C120&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C125" s="247">
+      <c r="C125" s="246">
         <f>Scenarios!C81</f>
         <v>1.2217592592592592</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="243" t="str">
+      <c r="B126" s="242" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C120&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C126" s="247">
+      <c r="C126" s="246">
         <f>Scenarios!C82</f>
         <v>5.2284175425125214</v>
       </c>
@@ -4736,7 +4732,7 @@
       <c r="B127" s="82" t="s">
         <v>271</v>
       </c>
-      <c r="C127" s="246">
+      <c r="C127" s="245">
         <f>Scenarios!C83</f>
         <v>6.4501768017717804</v>
       </c>
@@ -4746,16 +4742,22 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="245" t="s">
+      <c r="B128" s="244" t="s">
         <v>273</v>
       </c>
-      <c r="C128" s="158">
+      <c r="C128" s="94">
         <f>Scenarios!F83</f>
-        <v>-0.28606673541699057</v>
+        <v>0.28606673541699057</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4771,12 +4773,6 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4886,245 +4882,245 @@
       <c r="B4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="194">
+      <c r="C4" s="193">
         <v>8765</v>
       </c>
-      <c r="D4" s="185">
+      <c r="D4" s="184">
         <v>11881</v>
       </c>
-      <c r="E4" s="185"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="185"/>
-      <c r="H4" s="185"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="185"/>
-      <c r="K4" s="185"/>
-      <c r="L4" s="185"/>
-      <c r="M4" s="185"/>
+      <c r="E4" s="184"/>
+      <c r="F4" s="184"/>
+      <c r="G4" s="184"/>
+      <c r="H4" s="184"/>
+      <c r="I4" s="184"/>
+      <c r="J4" s="184"/>
+      <c r="K4" s="184"/>
+      <c r="L4" s="184"/>
+      <c r="M4" s="184"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="194">
+      <c r="C5" s="193">
         <v>5344</v>
       </c>
-      <c r="D5" s="185">
+      <c r="D5" s="184">
         <v>6492</v>
       </c>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="185"/>
-      <c r="I5" s="185"/>
-      <c r="J5" s="185"/>
-      <c r="K5" s="185"/>
-      <c r="L5" s="185"/>
-      <c r="M5" s="185"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="184"/>
+      <c r="K5" s="184"/>
+      <c r="L5" s="184"/>
+      <c r="M5" s="184"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="194">
+      <c r="C6" s="193">
         <v>1084</v>
       </c>
-      <c r="D6" s="185">
+      <c r="D6" s="184">
         <v>1129</v>
       </c>
-      <c r="E6" s="185"/>
-      <c r="F6" s="185"/>
-      <c r="G6" s="185"/>
-      <c r="H6" s="185"/>
-      <c r="I6" s="185"/>
-      <c r="J6" s="185"/>
-      <c r="K6" s="185"/>
-      <c r="L6" s="185"/>
-      <c r="M6" s="185"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="184"/>
+      <c r="H6" s="184"/>
+      <c r="I6" s="184"/>
+      <c r="J6" s="184"/>
+      <c r="K6" s="184"/>
+      <c r="L6" s="184"/>
+      <c r="M6" s="184"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="195"/>
-      <c r="D7" s="193"/>
-      <c r="E7" s="193"/>
-      <c r="F7" s="193"/>
-      <c r="G7" s="193"/>
-      <c r="H7" s="193"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
-      <c r="L7" s="193"/>
-      <c r="M7" s="193"/>
+      <c r="C7" s="194"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
+      <c r="I7" s="192"/>
+      <c r="J7" s="192"/>
+      <c r="K7" s="192"/>
+      <c r="L7" s="192"/>
+      <c r="M7" s="192"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="194"/>
-      <c r="D8" s="185"/>
-      <c r="E8" s="185"/>
-      <c r="F8" s="185"/>
-      <c r="G8" s="185"/>
-      <c r="H8" s="185"/>
-      <c r="I8" s="185"/>
-      <c r="J8" s="185"/>
-      <c r="K8" s="185"/>
-      <c r="L8" s="185"/>
-      <c r="M8" s="185"/>
+      <c r="C8" s="193"/>
+      <c r="D8" s="184"/>
+      <c r="E8" s="184"/>
+      <c r="F8" s="184"/>
+      <c r="G8" s="184"/>
+      <c r="H8" s="184"/>
+      <c r="I8" s="184"/>
+      <c r="J8" s="184"/>
+      <c r="K8" s="184"/>
+      <c r="L8" s="184"/>
+      <c r="M8" s="184"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="194">
+      <c r="C9" s="193">
         <v>639</v>
       </c>
-      <c r="D9" s="185">
+      <c r="D9" s="184">
         <v>927</v>
       </c>
-      <c r="E9" s="185"/>
-      <c r="F9" s="185"/>
-      <c r="G9" s="185"/>
-      <c r="H9" s="185"/>
-      <c r="I9" s="185"/>
-      <c r="J9" s="185"/>
-      <c r="K9" s="185"/>
-      <c r="L9" s="185"/>
-      <c r="M9" s="185"/>
+      <c r="E9" s="184"/>
+      <c r="F9" s="184"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="184"/>
+      <c r="I9" s="184"/>
+      <c r="J9" s="184"/>
+      <c r="K9" s="184"/>
+      <c r="L9" s="184"/>
+      <c r="M9" s="184"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C10" s="194"/>
-      <c r="D10" s="185"/>
-      <c r="E10" s="185"/>
-      <c r="F10" s="185"/>
-      <c r="G10" s="185"/>
-      <c r="H10" s="185"/>
-      <c r="I10" s="185"/>
-      <c r="J10" s="185"/>
-      <c r="K10" s="185"/>
-      <c r="L10" s="185"/>
-      <c r="M10" s="185"/>
+      <c r="C10" s="193"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="184"/>
+      <c r="F10" s="184"/>
+      <c r="G10" s="184"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="184"/>
+      <c r="J10" s="184"/>
+      <c r="K10" s="184"/>
+      <c r="L10" s="184"/>
+      <c r="M10" s="184"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="194"/>
-      <c r="D11" s="185"/>
-      <c r="E11" s="185"/>
-      <c r="F11" s="185"/>
-      <c r="G11" s="185"/>
-      <c r="H11" s="185"/>
-      <c r="I11" s="185"/>
-      <c r="J11" s="185"/>
-      <c r="K11" s="185"/>
-      <c r="L11" s="185"/>
-      <c r="M11" s="185"/>
+      <c r="C11" s="193"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="184"/>
+      <c r="J11" s="184"/>
+      <c r="K11" s="184"/>
+      <c r="L11" s="184"/>
+      <c r="M11" s="184"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="194">
+      <c r="C12" s="193">
         <v>43</v>
       </c>
-      <c r="D12" s="185">
+      <c r="D12" s="184">
         <v>40.775368</v>
       </c>
-      <c r="E12" s="185"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="185"/>
-      <c r="L12" s="185"/>
-      <c r="M12" s="185"/>
+      <c r="E12" s="184"/>
+      <c r="F12" s="184"/>
+      <c r="G12" s="184"/>
+      <c r="H12" s="184"/>
+      <c r="I12" s="184"/>
+      <c r="J12" s="184"/>
+      <c r="K12" s="184"/>
+      <c r="L12" s="184"/>
+      <c r="M12" s="184"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="194">
+      <c r="C13" s="193">
         <v>2340</v>
       </c>
-      <c r="D13" s="185">
+      <c r="D13" s="184">
         <v>1390.845307</v>
       </c>
-      <c r="E13" s="185"/>
-      <c r="F13" s="185"/>
-      <c r="G13" s="185"/>
-      <c r="H13" s="185"/>
-      <c r="I13" s="185"/>
-      <c r="J13" s="185"/>
-      <c r="K13" s="185"/>
-      <c r="L13" s="185"/>
-      <c r="M13" s="185"/>
+      <c r="E13" s="184"/>
+      <c r="F13" s="184"/>
+      <c r="G13" s="184"/>
+      <c r="H13" s="184"/>
+      <c r="I13" s="184"/>
+      <c r="J13" s="184"/>
+      <c r="K13" s="184"/>
+      <c r="L13" s="184"/>
+      <c r="M13" s="184"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="194">
+      <c r="C14" s="193">
         <v>519</v>
       </c>
-      <c r="D14" s="185">
+      <c r="D14" s="184">
         <v>860.83482800000002</v>
       </c>
-      <c r="E14" s="185"/>
-      <c r="F14" s="185"/>
-      <c r="G14" s="185"/>
-      <c r="H14" s="185"/>
-      <c r="I14" s="185"/>
-      <c r="J14" s="185"/>
-      <c r="K14" s="185"/>
-      <c r="L14" s="185"/>
-      <c r="M14" s="185"/>
+      <c r="E14" s="184"/>
+      <c r="F14" s="184"/>
+      <c r="G14" s="184"/>
+      <c r="H14" s="184"/>
+      <c r="I14" s="184"/>
+      <c r="J14" s="184"/>
+      <c r="K14" s="184"/>
+      <c r="L14" s="184"/>
+      <c r="M14" s="184"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="196">
+      <c r="C15" s="195">
         <v>4251</v>
       </c>
-      <c r="D15" s="186">
+      <c r="D15" s="185">
         <v>5880</v>
       </c>
-      <c r="E15" s="186"/>
-      <c r="F15" s="186"/>
-      <c r="G15" s="186"/>
-      <c r="H15" s="186"/>
-      <c r="I15" s="186"/>
-      <c r="J15" s="186"/>
-      <c r="K15" s="186"/>
-      <c r="L15" s="186"/>
-      <c r="M15" s="186"/>
+      <c r="E15" s="185"/>
+      <c r="F15" s="185"/>
+      <c r="G15" s="185"/>
+      <c r="H15" s="185"/>
+      <c r="I15" s="185"/>
+      <c r="J15" s="185"/>
+      <c r="K15" s="185"/>
+      <c r="L15" s="185"/>
+      <c r="M15" s="185"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="194">
+      <c r="C16" s="193">
         <v>-151</v>
       </c>
-      <c r="D16" s="185">
+      <c r="D16" s="184">
         <v>31</v>
       </c>
-      <c r="E16" s="185"/>
-      <c r="F16" s="185"/>
-      <c r="G16" s="185"/>
-      <c r="H16" s="185"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="185"/>
-      <c r="K16" s="185"/>
-      <c r="L16" s="185"/>
-      <c r="M16" s="185"/>
+      <c r="E16" s="184"/>
+      <c r="F16" s="184"/>
+      <c r="G16" s="184"/>
+      <c r="H16" s="184"/>
+      <c r="I16" s="184"/>
+      <c r="J16" s="184"/>
+      <c r="K16" s="184"/>
+      <c r="L16" s="184"/>
+      <c r="M16" s="184"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
@@ -5136,61 +5132,61 @@
       <c r="B19" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="185">
+      <c r="C19" s="184">
         <v>160</v>
       </c>
-      <c r="D19" s="185">
+      <c r="D19" s="184">
         <v>198</v>
       </c>
-      <c r="E19" s="185"/>
-      <c r="F19" s="185"/>
-      <c r="G19" s="185"/>
-      <c r="H19" s="185"/>
-      <c r="I19" s="185"/>
-      <c r="J19" s="185"/>
-      <c r="K19" s="185"/>
-      <c r="L19" s="185"/>
-      <c r="M19" s="185"/>
+      <c r="E19" s="184"/>
+      <c r="F19" s="184"/>
+      <c r="G19" s="184"/>
+      <c r="H19" s="184"/>
+      <c r="I19" s="184"/>
+      <c r="J19" s="184"/>
+      <c r="K19" s="184"/>
+      <c r="L19" s="184"/>
+      <c r="M19" s="184"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="185">
+      <c r="C20" s="184">
         <v>69</v>
       </c>
-      <c r="D20" s="185">
+      <c r="D20" s="184">
         <v>108</v>
       </c>
-      <c r="E20" s="185"/>
-      <c r="F20" s="185"/>
-      <c r="G20" s="185"/>
-      <c r="H20" s="185"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="185"/>
-      <c r="K20" s="185"/>
-      <c r="L20" s="185"/>
-      <c r="M20" s="185"/>
+      <c r="E20" s="184"/>
+      <c r="F20" s="184"/>
+      <c r="G20" s="184"/>
+      <c r="H20" s="184"/>
+      <c r="I20" s="184"/>
+      <c r="J20" s="184"/>
+      <c r="K20" s="184"/>
+      <c r="L20" s="184"/>
+      <c r="M20" s="184"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="185">
+      <c r="C21" s="184">
         <v>910</v>
       </c>
-      <c r="D21" s="185">
+      <c r="D21" s="184">
         <v>2541</v>
       </c>
-      <c r="E21" s="185"/>
-      <c r="F21" s="185"/>
-      <c r="G21" s="185"/>
-      <c r="H21" s="185"/>
-      <c r="I21" s="185"/>
-      <c r="J21" s="185"/>
-      <c r="K21" s="185"/>
-      <c r="L21" s="185"/>
-      <c r="M21" s="185"/>
+      <c r="E21" s="184"/>
+      <c r="F21" s="184"/>
+      <c r="G21" s="184"/>
+      <c r="H21" s="184"/>
+      <c r="I21" s="184"/>
+      <c r="J21" s="184"/>
+      <c r="K21" s="184"/>
+      <c r="L21" s="184"/>
+      <c r="M21" s="184"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="24" t="str">
@@ -5223,93 +5219,93 @@
       <c r="B25" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="187"/>
-      <c r="D25" s="185">
+      <c r="C25" s="186"/>
+      <c r="D25" s="184">
         <v>7251</v>
       </c>
-      <c r="E25" s="185"/>
-      <c r="F25" s="185"/>
-      <c r="G25" s="185"/>
-      <c r="H25" s="185"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="185"/>
-      <c r="K25" s="185"/>
-      <c r="L25" s="185"/>
-      <c r="M25" s="185"/>
+      <c r="E25" s="184"/>
+      <c r="F25" s="184"/>
+      <c r="G25" s="184"/>
+      <c r="H25" s="184"/>
+      <c r="I25" s="184"/>
+      <c r="J25" s="184"/>
+      <c r="K25" s="184"/>
+      <c r="L25" s="184"/>
+      <c r="M25" s="184"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="187"/>
-      <c r="D26" s="185">
+      <c r="C26" s="186"/>
+      <c r="D26" s="184">
         <v>16389</v>
       </c>
-      <c r="E26" s="185"/>
-      <c r="F26" s="185"/>
-      <c r="G26" s="185"/>
-      <c r="H26" s="185"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="185"/>
-      <c r="K26" s="185"/>
-      <c r="L26" s="185"/>
-      <c r="M26" s="185"/>
+      <c r="E26" s="184"/>
+      <c r="F26" s="184"/>
+      <c r="G26" s="184"/>
+      <c r="H26" s="184"/>
+      <c r="I26" s="184"/>
+      <c r="J26" s="184"/>
+      <c r="K26" s="184"/>
+      <c r="L26" s="184"/>
+      <c r="M26" s="184"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="186">
+      <c r="C27" s="185">
         <v>14028</v>
       </c>
-      <c r="D27" s="186">
+      <c r="D27" s="185">
         <v>10902</v>
       </c>
-      <c r="E27" s="186"/>
-      <c r="F27" s="186"/>
-      <c r="G27" s="186"/>
-      <c r="H27" s="186"/>
-      <c r="I27" s="186"/>
-      <c r="J27" s="186"/>
-      <c r="K27" s="186"/>
-      <c r="L27" s="186"/>
-      <c r="M27" s="186"/>
+      <c r="E27" s="185"/>
+      <c r="F27" s="185"/>
+      <c r="G27" s="185"/>
+      <c r="H27" s="185"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="185"/>
+      <c r="K27" s="185"/>
+      <c r="L27" s="185"/>
+      <c r="M27" s="185"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="186">
+      <c r="C28" s="185">
         <v>166316</v>
       </c>
-      <c r="D28" s="186">
+      <c r="D28" s="185">
         <v>163105</v>
       </c>
-      <c r="E28" s="186"/>
-      <c r="F28" s="186"/>
-      <c r="G28" s="186"/>
-      <c r="H28" s="186"/>
-      <c r="I28" s="186"/>
-      <c r="J28" s="186"/>
-      <c r="K28" s="186"/>
-      <c r="L28" s="186"/>
-      <c r="M28" s="186"/>
+      <c r="E28" s="185"/>
+      <c r="F28" s="185"/>
+      <c r="G28" s="185"/>
+      <c r="H28" s="185"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="185"/>
+      <c r="K28" s="185"/>
+      <c r="L28" s="185"/>
+      <c r="M28" s="185"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="C29" s="185"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="185"/>
-      <c r="F29" s="185"/>
-      <c r="G29" s="186"/>
-      <c r="H29" s="186"/>
-      <c r="I29" s="186"/>
-      <c r="J29" s="186"/>
-      <c r="K29" s="186"/>
-      <c r="L29" s="186"/>
-      <c r="M29" s="186"/>
+      <c r="C29" s="184"/>
+      <c r="D29" s="184"/>
+      <c r="E29" s="184"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="185"/>
+      <c r="H29" s="185"/>
+      <c r="I29" s="185"/>
+      <c r="J29" s="185"/>
+      <c r="K29" s="185"/>
+      <c r="L29" s="185"/>
+      <c r="M29" s="185"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
@@ -5321,17 +5317,17 @@
       <c r="B32" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="185"/>
-      <c r="D32" s="185"/>
-      <c r="E32" s="185"/>
-      <c r="F32" s="185"/>
-      <c r="G32" s="185"/>
-      <c r="H32" s="185"/>
-      <c r="I32" s="185"/>
-      <c r="J32" s="185"/>
-      <c r="K32" s="185"/>
-      <c r="L32" s="185"/>
-      <c r="M32" s="185"/>
+      <c r="C32" s="184"/>
+      <c r="D32" s="184"/>
+      <c r="E32" s="184"/>
+      <c r="F32" s="184"/>
+      <c r="G32" s="184"/>
+      <c r="H32" s="184"/>
+      <c r="I32" s="184"/>
+      <c r="J32" s="184"/>
+      <c r="K32" s="184"/>
+      <c r="L32" s="184"/>
+      <c r="M32" s="184"/>
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
@@ -5358,47 +5354,47 @@
       <c r="B36" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="187">
+      <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>8765</v>
       </c>
-      <c r="D36" s="187">
+      <c r="D36" s="186">
         <f t="shared" si="1"/>
         <v>11881</v>
       </c>
-      <c r="E36" s="187" t="str">
+      <c r="E36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F36" s="187" t="str">
+      <c r="F36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G36" s="187" t="str">
+      <c r="G36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H36" s="187" t="str">
+      <c r="H36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I36" s="187" t="str">
+      <c r="I36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J36" s="187" t="str">
+      <c r="J36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="187" t="str">
+      <c r="K36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L36" s="187" t="str">
+      <c r="L36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="M36" s="187" t="str">
+      <c r="M36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5407,47 +5403,47 @@
       <c r="B37" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="187">
+      <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-5344</v>
       </c>
-      <c r="D37" s="187">
+      <c r="D37" s="186">
         <f t="shared" si="2"/>
         <v>-6492</v>
       </c>
-      <c r="E37" s="187" t="str">
+      <c r="E37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F37" s="187" t="str">
+      <c r="F37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G37" s="187" t="str">
+      <c r="G37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H37" s="187" t="str">
+      <c r="H37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I37" s="187" t="str">
+      <c r="I37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J37" s="187" t="str">
+      <c r="J37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K37" s="187" t="str">
+      <c r="K37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L37" s="187" t="str">
+      <c r="L37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M37" s="187" t="str">
+      <c r="M37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -5456,47 +5452,47 @@
       <c r="B38" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
         <v>3421</v>
       </c>
-      <c r="D38" s="188">
+      <c r="D38" s="187">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>5389</v>
       </c>
-      <c r="E38" s="188" t="str">
+      <c r="E38" s="187" t="str">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v/>
       </c>
-      <c r="F38" s="188" t="str">
+      <c r="F38" s="187" t="str">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v/>
       </c>
-      <c r="G38" s="188" t="str">
+      <c r="G38" s="187" t="str">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v/>
       </c>
-      <c r="H38" s="188" t="str">
+      <c r="H38" s="187" t="str">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v/>
       </c>
-      <c r="I38" s="188" t="str">
+      <c r="I38" s="187" t="str">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v/>
       </c>
-      <c r="J38" s="188" t="str">
+      <c r="J38" s="187" t="str">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v/>
       </c>
-      <c r="K38" s="188" t="str">
+      <c r="K38" s="187" t="str">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v/>
       </c>
-      <c r="L38" s="188" t="str">
+      <c r="L38" s="187" t="str">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v/>
       </c>
-      <c r="M38" s="188" t="str">
+      <c r="M38" s="187" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -5505,47 +5501,47 @@
       <c r="B39" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="187">
+      <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-1084</v>
       </c>
-      <c r="D39" s="187">
+      <c r="D39" s="186">
         <f t="shared" si="13"/>
         <v>-1129</v>
       </c>
-      <c r="E39" s="187" t="str">
+      <c r="E39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="F39" s="187" t="str">
+      <c r="F39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="G39" s="187" t="str">
+      <c r="G39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="H39" s="187" t="str">
+      <c r="H39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="I39" s="187" t="str">
+      <c r="I39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="J39" s="187" t="str">
+      <c r="J39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="K39" s="187" t="str">
+      <c r="K39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="L39" s="187" t="str">
+      <c r="L39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="M39" s="187" t="str">
+      <c r="M39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -5554,47 +5550,47 @@
       <c r="B40" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="189">
+      <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>0</v>
       </c>
-      <c r="D40" s="189">
+      <c r="D40" s="188">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="E40" s="189" t="str">
+      <c r="E40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="F40" s="189" t="str">
+      <c r="F40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="G40" s="189" t="str">
+      <c r="G40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="H40" s="189" t="str">
+      <c r="H40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="I40" s="189" t="str">
+      <c r="I40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="J40" s="189" t="str">
+      <c r="J40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="K40" s="189" t="str">
+      <c r="K40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L40" s="189" t="str">
+      <c r="L40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M40" s="189" t="str">
+      <c r="M40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -5603,47 +5599,47 @@
       <c r="B41" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C41" s="189">
+      <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-1084</v>
       </c>
-      <c r="D41" s="189">
+      <c r="D41" s="188">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-1129</v>
       </c>
-      <c r="E41" s="189" t="str">
+      <c r="E41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="F41" s="189" t="str">
+      <c r="F41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="G41" s="189" t="str">
+      <c r="G41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="H41" s="189" t="str">
+      <c r="H41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I41" s="189" t="str">
+      <c r="I41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J41" s="189" t="str">
+      <c r="J41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K41" s="189" t="str">
+      <c r="K41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="L41" s="189" t="str">
+      <c r="L41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="M41" s="189" t="str">
+      <c r="M41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -5652,47 +5648,47 @@
       <c r="B42" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="187">
+      <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="187">
+      <c r="D42" s="186">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E42" s="187" t="str">
+      <c r="E42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="F42" s="187" t="str">
+      <c r="F42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="G42" s="187" t="str">
+      <c r="G42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="H42" s="187" t="str">
+      <c r="H42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="I42" s="187" t="str">
+      <c r="I42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="J42" s="187" t="str">
+      <c r="J42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="K42" s="187" t="str">
+      <c r="K42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="L42" s="187" t="str">
+      <c r="L42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="M42" s="187" t="str">
+      <c r="M42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -5701,47 +5697,47 @@
       <c r="B43" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="C43" s="190">
+      <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>2337</v>
       </c>
-      <c r="D43" s="190">
+      <c r="D43" s="189">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>4260</v>
       </c>
-      <c r="E43" s="190" t="str">
+      <c r="E43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="F43" s="190" t="str">
+      <c r="F43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="G43" s="190" t="str">
+      <c r="G43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="H43" s="190" t="str">
+      <c r="H43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="I43" s="190" t="str">
+      <c r="I43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="J43" s="190" t="str">
+      <c r="J43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="K43" s="190" t="str">
+      <c r="K43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="L43" s="190" t="str">
+      <c r="L43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="M43" s="190" t="str">
+      <c r="M43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -5750,47 +5746,47 @@
       <c r="B44" s="43" t="s">
         <v>173</v>
       </c>
-      <c r="C44" s="191">
+      <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
         <v>136</v>
       </c>
-      <c r="D44" s="191">
+      <c r="D44" s="190">
         <f t="shared" si="18"/>
         <v>1130.764889</v>
       </c>
-      <c r="E44" s="191" t="str">
+      <c r="E44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="F44" s="191" t="str">
+      <c r="F44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="G44" s="191" t="str">
+      <c r="G44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="H44" s="191" t="str">
+      <c r="H44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="I44" s="191" t="str">
+      <c r="I44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="J44" s="191" t="str">
+      <c r="J44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="K44" s="191" t="str">
+      <c r="K44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L44" s="191" t="str">
+      <c r="L44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="M44" s="191" t="str">
+      <c r="M44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
@@ -5799,47 +5795,47 @@
       <c r="B45" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="192">
+      <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
         <v>2297</v>
       </c>
-      <c r="D45" s="192">
+      <c r="D45" s="191">
         <f t="shared" si="19"/>
         <v>1350.069939</v>
       </c>
-      <c r="E45" s="192" t="str">
+      <c r="E45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="F45" s="192" t="str">
+      <c r="F45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="G45" s="192" t="str">
+      <c r="G45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="H45" s="192" t="str">
+      <c r="H45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I45" s="192" t="str">
+      <c r="I45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J45" s="192" t="str">
+      <c r="J45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="K45" s="192" t="str">
+      <c r="K45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="L45" s="192" t="str">
+      <c r="L45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M45" s="192" t="str">
+      <c r="M45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -5848,47 +5844,47 @@
       <c r="B46" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="187">
+      <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-519</v>
       </c>
-      <c r="D46" s="187">
+      <c r="D46" s="186">
         <f t="shared" si="20"/>
         <v>-860.83482800000002</v>
       </c>
-      <c r="E46" s="187" t="str">
+      <c r="E46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="F46" s="187" t="str">
+      <c r="F46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="G46" s="187" t="str">
+      <c r="G46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="H46" s="187" t="str">
+      <c r="H46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="I46" s="187" t="str">
+      <c r="I46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="J46" s="187" t="str">
+      <c r="J46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="K46" s="187" t="str">
+      <c r="K46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="L46" s="187" t="str">
+      <c r="L46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M46" s="187" t="str">
+      <c r="M46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -5897,47 +5893,47 @@
       <c r="B47" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="190">
+      <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>4251</v>
       </c>
-      <c r="D47" s="190">
+      <c r="D47" s="189">
         <f t="shared" si="21"/>
         <v>5880</v>
       </c>
-      <c r="E47" s="190" t="str">
+      <c r="E47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="F47" s="190" t="str">
+      <c r="F47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="G47" s="190" t="str">
+      <c r="G47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="H47" s="190" t="str">
+      <c r="H47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="I47" s="190" t="str">
+      <c r="I47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="J47" s="190" t="str">
+      <c r="J47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="K47" s="190" t="str">
+      <c r="K47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="L47" s="190" t="str">
+      <c r="L47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="M47" s="190" t="str">
+      <c r="M47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -5946,47 +5942,47 @@
       <c r="B48" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="187">
+      <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>0</v>
       </c>
-      <c r="D48" s="187">
+      <c r="D48" s="186">
         <f t="shared" si="22"/>
         <v>-31</v>
       </c>
-      <c r="E48" s="187" t="str">
+      <c r="E48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="F48" s="187" t="str">
+      <c r="F48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="G48" s="187" t="str">
+      <c r="G48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="H48" s="187" t="str">
+      <c r="H48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="I48" s="187" t="str">
+      <c r="I48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="J48" s="187" t="str">
+      <c r="J48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="K48" s="187" t="str">
+      <c r="K48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L48" s="187" t="str">
+      <c r="L48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="M48" s="187" t="str">
+      <c r="M48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -6000,47 +5996,47 @@
       <c r="B51" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="187">
+      <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-43</v>
       </c>
-      <c r="D51" s="187">
+      <c r="D51" s="186">
         <f t="shared" si="23"/>
         <v>-40.775368</v>
       </c>
-      <c r="E51" s="187" t="str">
+      <c r="E51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="F51" s="187" t="str">
+      <c r="F51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="G51" s="187" t="str">
+      <c r="G51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="H51" s="187" t="str">
+      <c r="H51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="I51" s="187" t="str">
+      <c r="I51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="J51" s="187" t="str">
+      <c r="J51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K51" s="187" t="str">
+      <c r="K51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="L51" s="187" t="str">
+      <c r="L51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="M51" s="187" t="str">
+      <c r="M51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -6049,53 +6045,53 @@
       <c r="B52" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C52" s="187">
+      <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>2340</v>
       </c>
-      <c r="D52" s="187">
+      <c r="D52" s="186">
         <f t="shared" si="24"/>
         <v>1390.845307</v>
       </c>
-      <c r="E52" s="187" t="str">
+      <c r="E52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="F52" s="187" t="str">
+      <c r="F52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="G52" s="187" t="str">
+      <c r="G52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="H52" s="187" t="str">
+      <c r="H52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="I52" s="187" t="str">
+      <c r="I52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="J52" s="187" t="str">
+      <c r="J52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="K52" s="187" t="str">
+      <c r="K52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="L52" s="187" t="str">
+      <c r="L52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="M52" s="187" t="str">
+      <c r="M52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B54" s="179" t="s">
+      <c r="B54" s="178" t="s">
         <v>173</v>
       </c>
     </row>
@@ -6103,47 +6099,47 @@
       <c r="B55" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C55" s="192">
+      <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
         <v>639</v>
       </c>
-      <c r="D55" s="192">
+      <c r="D55" s="191">
         <f t="shared" si="25"/>
         <v>927</v>
       </c>
-      <c r="E55" s="192" t="str">
+      <c r="E55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="F55" s="192" t="str">
+      <c r="F55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="G55" s="192" t="str">
+      <c r="G55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="H55" s="192" t="str">
+      <c r="H55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I55" s="192" t="str">
+      <c r="I55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="J55" s="192" t="str">
+      <c r="J55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="K55" s="192" t="str">
+      <c r="K55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="L55" s="192" t="str">
+      <c r="L55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="M55" s="192" t="str">
+      <c r="M55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
@@ -6152,47 +6148,47 @@
       <c r="B56" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C56" s="192">
+      <c r="C56" s="191">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
         <v>0</v>
       </c>
-      <c r="D56" s="192">
+      <c r="D56" s="191">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E56" s="192" t="str">
+      <c r="E56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="F56" s="192" t="str">
+      <c r="F56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="G56" s="192" t="str">
+      <c r="G56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="H56" s="192" t="str">
+      <c r="H56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="I56" s="192" t="str">
+      <c r="I56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="J56" s="192" t="str">
+      <c r="J56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="K56" s="192" t="str">
+      <c r="K56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="L56" s="192" t="str">
+      <c r="L56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="M56" s="192" t="str">
+      <c r="M56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
@@ -6201,47 +6197,47 @@
       <c r="B57" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C57" s="192">
+      <c r="C57" s="191">
         <f>IF(C$4="","",C11)</f>
         <v>0</v>
       </c>
-      <c r="D57" s="192">
+      <c r="D57" s="191">
         <f t="shared" ref="D57:M57" si="27">IF(D$4="","",D11)</f>
         <v>0</v>
       </c>
-      <c r="E57" s="192" t="str">
+      <c r="E57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="F57" s="192" t="str">
+      <c r="F57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="G57" s="192" t="str">
+      <c r="G57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="H57" s="192" t="str">
+      <c r="H57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="I57" s="192" t="str">
+      <c r="I57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="J57" s="192" t="str">
+      <c r="J57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="K57" s="192" t="str">
+      <c r="K57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="L57" s="192" t="str">
+      <c r="L57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="M57" s="192" t="str">
+      <c r="M57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -6250,47 +6246,47 @@
       <c r="B58" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C58" s="192">
+      <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
         <v>-503</v>
       </c>
-      <c r="D58" s="192">
+      <c r="D58" s="191">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
         <v>203.76488900000004</v>
       </c>
-      <c r="E58" s="192" t="str">
+      <c r="E58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="F58" s="192" t="str">
+      <c r="F58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="G58" s="192" t="str">
+      <c r="G58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="H58" s="192" t="str">
+      <c r="H58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="I58" s="192" t="str">
+      <c r="I58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="J58" s="192" t="str">
+      <c r="J58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="K58" s="192" t="str">
+      <c r="K58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="L58" s="192" t="str">
+      <c r="L58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="M58" s="192" t="str">
+      <c r="M58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
@@ -6305,47 +6301,47 @@
       <c r="B61" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C61" s="187">
+      <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
         <v>-160</v>
       </c>
-      <c r="D61" s="187">
+      <c r="D61" s="186">
         <f t="shared" si="29"/>
         <v>-198</v>
       </c>
-      <c r="E61" s="187" t="str">
+      <c r="E61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="F61" s="187" t="str">
+      <c r="F61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="G61" s="187" t="str">
+      <c r="G61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="H61" s="187" t="str">
+      <c r="H61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="I61" s="187" t="str">
+      <c r="I61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="J61" s="187" t="str">
+      <c r="J61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="K61" s="187" t="str">
+      <c r="K61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="L61" s="187" t="str">
+      <c r="L61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="M61" s="187" t="str">
+      <c r="M61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -6354,47 +6350,47 @@
       <c r="B62" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C62" s="187">
+      <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
         <v>-69</v>
       </c>
-      <c r="D62" s="187">
+      <c r="D62" s="186">
         <f t="shared" si="30"/>
         <v>-108</v>
       </c>
-      <c r="E62" s="187" t="str">
+      <c r="E62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="F62" s="187" t="str">
+      <c r="F62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="G62" s="187" t="str">
+      <c r="G62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="H62" s="187" t="str">
+      <c r="H62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="I62" s="187" t="str">
+      <c r="I62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="J62" s="187" t="str">
+      <c r="J62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="K62" s="187" t="str">
+      <c r="K62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="L62" s="187" t="str">
+      <c r="L62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="M62" s="187" t="str">
+      <c r="M62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -6403,47 +6399,47 @@
       <c r="B63" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C63" s="187">
+      <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
         <v>-910</v>
       </c>
-      <c r="D63" s="187">
+      <c r="D63" s="186">
         <f t="shared" si="31"/>
         <v>-2541</v>
       </c>
-      <c r="E63" s="187" t="str">
+      <c r="E63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="F63" s="187" t="str">
+      <c r="F63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="G63" s="187" t="str">
+      <c r="G63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="H63" s="187" t="str">
+      <c r="H63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="I63" s="187" t="str">
+      <c r="I63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="J63" s="187" t="str">
+      <c r="J63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="K63" s="187" t="str">
+      <c r="K63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="L63" s="187" t="str">
+      <c r="L63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="M63" s="187" t="str">
+      <c r="M63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7063,19 +7059,19 @@
       <c r="B3" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="210" t="s">
+      <c r="C3" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="211" t="s">
+      <c r="D3" s="210" t="s">
         <v>36</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="G3" s="210" t="s">
+      <c r="G3" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="H3" s="211" t="s">
+      <c r="H3" s="210" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7086,7 +7082,7 @@
       <c r="C4" s="19">
         <v>8029</v>
       </c>
-      <c r="D4" s="303">
+      <c r="D4" s="301">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -7096,7 +7092,7 @@
       <c r="G4" s="19">
         <v>45665</v>
       </c>
-      <c r="H4" s="303">
+      <c r="H4" s="301">
         <v>0.9</v>
       </c>
     </row>
@@ -7107,7 +7103,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="303">
+      <c r="D5" s="301">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -7117,7 +7113,7 @@
       <c r="G5" s="19">
         <v>2014</v>
       </c>
-      <c r="H5" s="303">
+      <c r="H5" s="301">
         <v>0.7</v>
       </c>
     </row>
@@ -7128,7 +7124,7 @@
       <c r="C6" s="19">
         <v>9844</v>
       </c>
-      <c r="D6" s="303">
+      <c r="D6" s="301">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -7138,7 +7134,7 @@
       <c r="G6" s="19">
         <v>156</v>
       </c>
-      <c r="H6" s="303">
+      <c r="H6" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7149,7 +7145,7 @@
       <c r="C7" s="19">
         <v>5466</v>
       </c>
-      <c r="D7" s="303">
+      <c r="D7" s="301">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -7159,7 +7155,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="303">
+      <c r="H7" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7170,7 +7166,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="303">
+      <c r="D8" s="301">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -7180,7 +7176,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="303">
+      <c r="H8" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7191,7 +7187,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="303">
+      <c r="D9" s="301">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -7201,7 +7197,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="303">
+      <c r="H9" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7212,10 +7208,10 @@
       <c r="C10" s="19">
         <v>10</v>
       </c>
-      <c r="D10" s="303">
+      <c r="D10" s="301">
         <v>0.9</v>
       </c>
-      <c r="H10" s="304"/>
+      <c r="H10" s="302"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
@@ -7224,10 +7220,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="303">
+      <c r="D11" s="301">
         <v>0.05</v>
       </c>
-      <c r="H11" s="304"/>
+      <c r="H11" s="302"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
@@ -7262,19 +7258,19 @@
       <c r="B14" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="C14" s="210" t="s">
+      <c r="C14" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="211" t="s">
+      <c r="D14" s="210" t="s">
         <v>36</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="G14" s="210" t="s">
+      <c r="G14" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="H14" s="211" t="s">
+      <c r="H14" s="210" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7285,7 +7281,7 @@
       <c r="C15" s="19">
         <v>2757</v>
       </c>
-      <c r="D15" s="303">
+      <c r="D15" s="301">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -7294,7 +7290,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="303">
+      <c r="H15" s="301">
         <v>0.8</v>
       </c>
     </row>
@@ -7305,7 +7301,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="303">
+      <c r="D16" s="301">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -7314,7 +7310,7 @@
       <c r="G16" s="19">
         <v>1373</v>
       </c>
-      <c r="H16" s="303">
+      <c r="H16" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7325,7 +7321,7 @@
       <c r="C17" s="19">
         <v>67668</v>
       </c>
-      <c r="D17" s="303">
+      <c r="D17" s="301">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -7334,7 +7330,7 @@
       <c r="G17" s="19">
         <v>13024</v>
       </c>
-      <c r="H17" s="303">
+      <c r="H17" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7345,7 +7341,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="303">
+      <c r="D18" s="301">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -7354,7 +7350,7 @@
       <c r="G18" s="19">
         <v>23696</v>
       </c>
-      <c r="H18" s="303">
+      <c r="H18" s="301">
         <v>0.1</v>
       </c>
     </row>
@@ -7365,7 +7361,7 @@
       <c r="C19" s="19">
         <v>1284</v>
       </c>
-      <c r="D19" s="303">
+      <c r="D19" s="301">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -7374,7 +7370,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="303">
+      <c r="H19" s="301">
         <v>0.1</v>
       </c>
     </row>
@@ -7385,7 +7381,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="303">
+      <c r="D20" s="301">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -7394,7 +7390,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="303">
+      <c r="H20" s="301">
         <v>0.2</v>
       </c>
     </row>
@@ -7405,7 +7401,7 @@
       <c r="C21" s="19">
         <v>0</v>
       </c>
-      <c r="D21" s="303">
+      <c r="D21" s="301">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -7414,7 +7410,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="303">
+      <c r="H21" s="301">
         <v>0.1</v>
       </c>
     </row>
@@ -7425,10 +7421,10 @@
       <c r="C22" s="19">
         <v>10</v>
       </c>
-      <c r="D22" s="303">
+      <c r="D22" s="301">
         <v>0.9</v>
       </c>
-      <c r="H22" s="304"/>
+      <c r="H22" s="302"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
@@ -7437,10 +7433,10 @@
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="303">
+      <c r="D23" s="301">
         <v>0</v>
       </c>
-      <c r="H23" s="304"/>
+      <c r="H23" s="302"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
@@ -7470,16 +7466,16 @@
       <c r="B26" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="C26" s="210" t="s">
+      <c r="C26" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="F26" s="212" t="s">
+      <c r="F26" s="211" t="s">
         <v>201</v>
       </c>
-      <c r="G26" s="213" t="s">
+      <c r="G26" s="212" t="s">
         <v>141</v>
       </c>
-      <c r="H26" s="214" t="s">
+      <c r="H26" s="213" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7490,14 +7486,14 @@
       <c r="C27" s="19">
         <v>967</v>
       </c>
-      <c r="F27" s="215" t="s">
+      <c r="F27" s="214" t="s">
         <v>31</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
         <v>167107</v>
       </c>
-      <c r="H27" s="216">
+      <c r="H27" s="215">
         <f>H32-G30</f>
         <v>94589.7</v>
       </c>
@@ -7509,13 +7505,13 @@
       <c r="C28" s="19">
         <v>37</v>
       </c>
-      <c r="F28" s="217" t="s">
+      <c r="F28" s="216" t="s">
         <v>251</v>
       </c>
-      <c r="G28" s="185">
+      <c r="G28" s="184">
         <v>519</v>
       </c>
-      <c r="H28" s="216"/>
+      <c r="H28" s="215"/>
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="4" t="s">
@@ -7524,14 +7520,14 @@
       <c r="C29" s="19">
         <v>0</v>
       </c>
-      <c r="F29" s="218" t="s">
+      <c r="F29" s="217" t="s">
         <v>80</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
         <v>166588</v>
       </c>
-      <c r="H29" s="216">
+      <c r="H29" s="215">
         <f>H27-G28</f>
         <v>94070.7</v>
       </c>
@@ -7543,14 +7539,14 @@
       <c r="C30" s="19">
         <v>0</v>
       </c>
-      <c r="F30" s="215" t="s">
+      <c r="F30" s="214" t="s">
         <v>24</v>
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
         <v>13889</v>
       </c>
-      <c r="H30" s="216"/>
+      <c r="H30" s="215"/>
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
@@ -7560,14 +7556,14 @@
         <f>SUM(C27:C30)</f>
         <v>1004</v>
       </c>
-      <c r="F31" s="218" t="s">
+      <c r="F31" s="217" t="s">
         <v>81</v>
       </c>
-      <c r="G31" s="219">
+      <c r="G31" s="218">
         <f>C31+C40</f>
         <v>3093</v>
       </c>
-      <c r="H31" s="216"/>
+      <c r="H31" s="215"/>
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
@@ -7577,14 +7573,14 @@
         <f>C33-C31</f>
         <v>8048</v>
       </c>
-      <c r="F32" s="220" t="s">
+      <c r="F32" s="219" t="s">
         <v>79</v>
       </c>
-      <c r="G32" s="221">
+      <c r="G32" s="220">
         <f>G35+G40</f>
         <v>180996</v>
       </c>
-      <c r="H32" s="216">
+      <c r="H32" s="215">
         <f>H35+H40</f>
         <v>108478.7</v>
       </c>
@@ -7596,20 +7592,20 @@
       <c r="C33" s="86">
         <v>9052</v>
       </c>
-      <c r="F33" s="222"/>
+      <c r="F33" s="221"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="223"/>
+      <c r="H33" s="222"/>
     </row>
     <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
-      <c r="F34" s="224" t="s">
+      <c r="F34" s="223" t="s">
         <v>207</v>
       </c>
-      <c r="G34" s="225" t="s">
+      <c r="G34" s="224" t="s">
         <v>141</v>
       </c>
-      <c r="H34" s="226" t="s">
+      <c r="H34" s="225" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7617,17 +7613,17 @@
       <c r="B35" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="C35" s="210" t="s">
+      <c r="C35" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="F35" s="227" t="s">
+      <c r="F35" s="226" t="s">
         <v>32</v>
       </c>
-      <c r="G35" s="221">
+      <c r="G35" s="220">
         <f>C12+C24</f>
         <v>95068</v>
       </c>
-      <c r="H35" s="228">
+      <c r="H35" s="227">
         <f>D12+D24</f>
         <v>54869</v>
       </c>
@@ -7639,14 +7635,14 @@
       <c r="C36" s="19">
         <v>832</v>
       </c>
-      <c r="F36" s="218" t="s">
+      <c r="F36" s="217" t="s">
         <v>202</v>
       </c>
-      <c r="G36" s="219">
+      <c r="G36" s="218">
         <f>C4+C15</f>
         <v>10786</v>
       </c>
-      <c r="H36" s="223"/>
+      <c r="H36" s="222"/>
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="4" t="s">
@@ -7655,14 +7651,14 @@
       <c r="C37" s="19">
         <v>27</v>
       </c>
-      <c r="F37" s="218" t="s">
+      <c r="F37" s="217" t="s">
         <v>203</v>
       </c>
-      <c r="G37" s="219">
+      <c r="G37" s="218">
         <f>C6</f>
         <v>9844</v>
       </c>
-      <c r="H37" s="223"/>
+      <c r="H37" s="222"/>
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="4" t="s">
@@ -7671,14 +7667,14 @@
       <c r="C38" s="19">
         <v>1230</v>
       </c>
-      <c r="F38" s="218" t="s">
+      <c r="F38" s="217" t="s">
         <v>204</v>
       </c>
-      <c r="G38" s="219">
+      <c r="G38" s="218">
         <f>C7+C17</f>
         <v>73134</v>
       </c>
-      <c r="H38" s="223"/>
+      <c r="H38" s="222"/>
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="2" t="s">
@@ -7687,14 +7683,14 @@
       <c r="C39" s="19">
         <v>0</v>
       </c>
-      <c r="F39" s="218" t="s">
+      <c r="F39" s="217" t="s">
         <v>84</v>
       </c>
-      <c r="G39" s="219">
+      <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
         <v>74418</v>
       </c>
-      <c r="H39" s="216">
+      <c r="H39" s="215">
         <f>C7*D7+C17*D17+C19*D19+C20*D20</f>
         <v>44008.799999999996</v>
       </c>
@@ -7707,14 +7703,14 @@
         <f>SUM(C36:C39)</f>
         <v>2089</v>
       </c>
-      <c r="F40" s="227" t="s">
+      <c r="F40" s="226" t="s">
         <v>143</v>
       </c>
-      <c r="G40" s="221">
+      <c r="G40" s="220">
         <f>G12+G24</f>
         <v>85928</v>
       </c>
-      <c r="H40" s="228">
+      <c r="H40" s="227">
         <f>H12+H24</f>
         <v>53609.7</v>
       </c>
@@ -7727,14 +7723,14 @@
         <f>C42-C40</f>
         <v>2748</v>
       </c>
-      <c r="F41" s="218" t="s">
+      <c r="F41" s="217" t="s">
         <v>196</v>
       </c>
-      <c r="G41" s="219">
+      <c r="G41" s="218">
         <f>C70</f>
         <v>72904</v>
       </c>
-      <c r="H41" s="228">
+      <c r="H41" s="227">
         <f>H40-H42</f>
         <v>45795.299999999996</v>
       </c>
@@ -7746,14 +7742,14 @@
       <c r="C42" s="86">
         <v>4837</v>
       </c>
-      <c r="F42" s="229" t="s">
+      <c r="F42" s="228" t="s">
         <v>197</v>
       </c>
-      <c r="G42" s="230">
+      <c r="G42" s="229">
         <f>C82</f>
         <v>13024</v>
       </c>
-      <c r="H42" s="231">
+      <c r="H42" s="230">
         <f>D82</f>
         <v>7814.4</v>
       </c>
@@ -7773,13 +7769,13 @@
       <c r="B45" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="C45" s="268" t="s">
+      <c r="C45" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D45" s="210" t="s">
+      <c r="D45" s="209" t="s">
         <v>288</v>
       </c>
-      <c r="F45" s="296" t="s">
+      <c r="F45" s="294" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7787,15 +7783,15 @@
       <c r="B46" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C46" s="192">
+      <c r="C46" s="191">
         <f>G29</f>
         <v>166588</v>
       </c>
-      <c r="D46" s="192">
+      <c r="D46" s="191">
         <f>H29</f>
         <v>94070.7</v>
       </c>
-      <c r="F46" s="291"/>
+      <c r="F46" s="289"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="str">
@@ -7810,23 +7806,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>11.511512740854835</v>
       </c>
-      <c r="F47" s="291"/>
+      <c r="F47" s="289"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F48" s="291"/>
+      <c r="F48" s="289"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="162" t="s">
+      <c r="B49" s="161" t="s">
         <v>148</v>
       </c>
-      <c r="C49" s="269" t="s">
+      <c r="C49" s="268" t="s">
         <v>61</v>
       </c>
-      <c r="D49" s="225" t="s">
+      <c r="D49" s="224" t="s">
         <v>100</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="291"/>
+      <c r="F49" s="289"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
@@ -7840,33 +7836,33 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>1.3234916559691912</v>
       </c>
-      <c r="F50" s="291"/>
+      <c r="F50" s="289"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C51" s="209"/>
+      <c r="C51" s="208"/>
       <c r="D51" s="94">
         <f>G29/G32</f>
         <v>0.92039603085151056</v>
       </c>
-      <c r="F51" s="291"/>
+      <c r="F51" s="289"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F52" s="291"/>
+      <c r="F52" s="289"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="162" t="s">
+      <c r="B53" s="161" t="s">
         <v>147</v>
       </c>
-      <c r="C53" s="269" t="s">
+      <c r="C53" s="268" t="s">
         <v>61</v>
       </c>
-      <c r="D53" s="225" t="s">
+      <c r="D53" s="224" t="s">
         <v>100</v>
       </c>
-      <c r="F53" s="291"/>
+      <c r="F53" s="289"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
@@ -7880,7 +7876,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>2.4582404173854506E-2</v>
       </c>
-      <c r="F54" s="291"/>
+      <c r="F54" s="289"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
@@ -7894,22 +7890,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>7.4364584303137507E-3</v>
       </c>
-      <c r="F55" s="291"/>
+      <c r="F55" s="289"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F56" s="291"/>
+      <c r="F56" s="289"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="162" t="s">
+      <c r="B57" s="161" t="s">
         <v>180</v>
       </c>
-      <c r="C57" s="269" t="s">
+      <c r="C57" s="268" t="s">
         <v>61</v>
       </c>
-      <c r="D57" s="225" t="s">
+      <c r="D57" s="224" t="s">
         <v>100</v>
       </c>
-      <c r="F57" s="291"/>
+      <c r="F57" s="289"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
@@ -7931,22 +7927,22 @@
         <f>G39/G32</f>
         <v>0.41115825764105285</v>
       </c>
-      <c r="F59" s="291"/>
+      <c r="F59" s="289"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F60" s="291"/>
+      <c r="F60" s="289"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="162" t="s">
+      <c r="B61" s="161" t="s">
         <v>291</v>
       </c>
-      <c r="C61" s="269" t="s">
+      <c r="C61" s="268" t="s">
         <v>142</v>
       </c>
-      <c r="D61" s="225" t="s">
+      <c r="D61" s="224" t="s">
         <v>100</v>
       </c>
-      <c r="F61" s="291"/>
+      <c r="F61" s="289"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
@@ -7960,7 +7956,7 @@
         <f>G28/G29</f>
         <v>3.1154705020769802E-3</v>
       </c>
-      <c r="F62" s="291" t="s">
+      <c r="F62" s="289" t="s">
         <v>289</v>
       </c>
     </row>
@@ -7979,13 +7975,13 @@
       <c r="B65" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="C65" s="268" t="s">
+      <c r="C65" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D65" s="211" t="s">
+      <c r="D65" s="210" t="s">
         <v>313</v>
       </c>
-      <c r="F65" s="296" t="s">
+      <c r="F65" s="294" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7997,7 +7993,7 @@
         <f>G4+G5+G15</f>
         <v>47679</v>
       </c>
-      <c r="D66" s="192">
+      <c r="D66" s="191">
         <f>C66-D75</f>
         <v>41505.820259237436</v>
       </c>
@@ -8013,7 +8009,7 @@
         <f>G6+G16</f>
         <v>1529</v>
       </c>
-      <c r="F67" s="291"/>
+      <c r="F67" s="289"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
@@ -8023,7 +8019,7 @@
         <f>G18</f>
         <v>23696</v>
       </c>
-      <c r="F68" s="291"/>
+      <c r="F68" s="289"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
@@ -8033,7 +8029,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="291"/>
+      <c r="F69" s="289"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
@@ -8043,49 +8039,49 @@
         <f>SUM(C66:C69)</f>
         <v>72904</v>
       </c>
-      <c r="F70" s="291"/>
+      <c r="F70" s="289"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F71" s="291"/>
+      <c r="F71" s="289"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="294" t="s">
+      <c r="B72" s="292" t="s">
         <v>354</v>
       </c>
-      <c r="C72" s="268" t="s">
+      <c r="C72" s="267" t="s">
         <v>100</v>
       </c>
-      <c r="D72" s="210" t="s">
+      <c r="D72" s="209" t="s">
         <v>61</v>
       </c>
-      <c r="F72" s="291"/>
+      <c r="F72" s="289"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
         <v>353</v>
       </c>
-      <c r="C73" s="192">
+      <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
         <v>-535.66666666666663</v>
       </c>
-      <c r="D73" s="192">
+      <c r="D73" s="191">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35)/12</f>
         <v>-514.43164506354685</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="297" t="s">
+      <c r="B74" s="295" t="s">
         <v>359</v>
       </c>
-      <c r="C74" s="298">
+      <c r="C74" s="296">
         <f>-$C$66/C73</f>
         <v>89.008711885500944</v>
       </c>
-      <c r="D74" s="298">
+      <c r="D74" s="296">
         <f>-$C$66/D73</f>
         <v>92.682867505381196</v>
       </c>
-      <c r="F74" s="291" t="s">
+      <c r="F74" s="289" t="s">
         <v>355</v>
       </c>
     </row>
@@ -8093,42 +8089,42 @@
       <c r="B75" s="82" t="s">
         <v>356</v>
       </c>
-      <c r="C75" s="302"/>
-      <c r="D75" s="301">
+      <c r="C75" s="300"/>
+      <c r="D75" s="299">
         <f>MAX(-D73*D76,G5)</f>
         <v>6173.1797407625618</v>
       </c>
-      <c r="F75" s="291" t="s">
+      <c r="F75" s="289" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="299" t="s">
+      <c r="B76" s="297" t="s">
         <v>360</v>
       </c>
-      <c r="C76" s="300"/>
-      <c r="D76" s="337">
+      <c r="C76" s="298"/>
+      <c r="D76" s="335">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,IF(D74&gt;36,12,6),2))</f>
         <v>12</v>
       </c>
-      <c r="F76" s="291" t="s">
+      <c r="F76" s="289" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F77" s="291"/>
+      <c r="F77" s="289"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D78" s="211" t="s">
+      <c r="D78" s="210" t="s">
         <v>36</v>
       </c>
-      <c r="F78" s="291"/>
+      <c r="F78" s="289"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
@@ -8138,11 +8134,11 @@
         <f>G7+G17</f>
         <v>13024</v>
       </c>
-      <c r="D79" s="192">
+      <c r="D79" s="191">
         <f>G7*H7+G17*H17</f>
         <v>7814.4</v>
       </c>
-      <c r="F79" s="291"/>
+      <c r="F79" s="289"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
@@ -8152,11 +8148,11 @@
         <f>G19</f>
         <v>0</v>
       </c>
-      <c r="D80" s="192">
+      <c r="D80" s="191">
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="291"/>
+      <c r="F80" s="289"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
@@ -8166,11 +8162,11 @@
         <f>G9+G21</f>
         <v>0</v>
       </c>
-      <c r="D81" s="192">
+      <c r="D81" s="191">
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="291"/>
+      <c r="F81" s="289"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
@@ -8184,7 +8180,7 @@
         <f>SUM(D79:D81)</f>
         <v>7814.4</v>
       </c>
-      <c r="F82" s="291"/>
+      <c r="F82" s="289"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
@@ -8201,57 +8197,57 @@
       <c r="B85" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="D85" s="278" t="s">
+      <c r="D85" s="276" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="275" t="s">
+      <c r="B86" s="273" t="s">
         <v>314</v>
       </c>
-      <c r="C86" s="192">
+      <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
         <v>-3093</v>
       </c>
-      <c r="D86" s="255">
+      <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
         <v>-0.37849307922088393</v>
       </c>
-      <c r="E86" s="277" t="str">
+      <c r="E86" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="275" t="s">
+      <c r="B87" s="273" t="s">
         <v>315</v>
       </c>
-      <c r="C87" s="192">
+      <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
         <v>41505.820259237436</v>
       </c>
-      <c r="D87" s="255">
+      <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
         <v>5.0791030441342784</v>
       </c>
-      <c r="E87" s="277" t="str">
+      <c r="E87" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="276" t="s">
+      <c r="B88" s="274" t="s">
         <v>194</v>
       </c>
-      <c r="C88" s="192">
+      <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
         <v>7814.4</v>
       </c>
-      <c r="D88" s="255">
+      <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
         <v>0.95625487173090062</v>
       </c>
-      <c r="E88" s="277" t="str">
+      <c r="E88" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -8260,15 +8256,15 @@
       <c r="B89" s="82" t="s">
         <v>319</v>
       </c>
-      <c r="C89" s="191">
+      <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
         <v>46227.220259237438</v>
       </c>
-      <c r="D89" s="279">
+      <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
         <v>5.6568648366442948</v>
       </c>
-      <c r="E89" s="277" t="str">
+      <c r="E89" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -8389,7 +8385,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="311"/>
+      <c r="E3" s="309"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -8398,54 +8394,54 @@
       <c r="B4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="197">
+      <c r="C4" s="196">
         <f>G4</f>
         <v>8765</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="309"/>
+      <c r="E4" s="307"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="187">
+      <c r="G4" s="186">
         <f>Data!C36</f>
         <v>8765</v>
       </c>
-      <c r="H4" s="187">
+      <c r="H4" s="186">
         <f>Data!D36</f>
         <v>11881</v>
       </c>
-      <c r="I4" s="187" t="str">
+      <c r="I4" s="186" t="str">
         <f>Data!E36</f>
         <v/>
       </c>
-      <c r="J4" s="187" t="str">
+      <c r="J4" s="186" t="str">
         <f>Data!F36</f>
         <v/>
       </c>
-      <c r="K4" s="187" t="str">
+      <c r="K4" s="186" t="str">
         <f>Data!G36</f>
         <v/>
       </c>
-      <c r="L4" s="187" t="str">
+      <c r="L4" s="186" t="str">
         <f>Data!H36</f>
         <v/>
       </c>
-      <c r="M4" s="187" t="str">
+      <c r="M4" s="186" t="str">
         <f>Data!I36</f>
         <v/>
       </c>
-      <c r="N4" s="187" t="str">
+      <c r="N4" s="186" t="str">
         <f>Data!J36</f>
         <v/>
       </c>
-      <c r="O4" s="187" t="str">
+      <c r="O4" s="186" t="str">
         <f>Data!K36</f>
         <v/>
       </c>
-      <c r="P4" s="187" t="str">
+      <c r="P4" s="186" t="str">
         <f>Data!L36</f>
         <v/>
       </c>
-      <c r="Q4" s="187" t="str">
+      <c r="Q4" s="186" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -8455,52 +8451,52 @@
       <c r="B5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="198">
+      <c r="C5" s="197">
         <f>C25</f>
         <v>-5066.6797407625618</v>
       </c>
-      <c r="E5" s="311"/>
-      <c r="G5" s="187">
+      <c r="E5" s="309"/>
+      <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-5344</v>
       </c>
-      <c r="H5" s="187">
+      <c r="H5" s="186">
         <f t="shared" si="1"/>
         <v>-6492</v>
       </c>
-      <c r="I5" s="187" t="str">
+      <c r="I5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J5" s="187" t="str">
+      <c r="J5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K5" s="187" t="str">
+      <c r="K5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L5" s="187" t="str">
+      <c r="L5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="M5" s="187" t="str">
+      <c r="M5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N5" s="187" t="str">
+      <c r="N5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="O5" s="187" t="str">
+      <c r="O5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P5" s="187" t="str">
+      <c r="P5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q5" s="187" t="str">
+      <c r="Q5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8510,52 +8506,52 @@
       <c r="B6" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="188">
+      <c r="C6" s="187">
         <f>C4+C5</f>
         <v>3698.3202592374382</v>
       </c>
-      <c r="E6" s="311"/>
-      <c r="G6" s="188">
+      <c r="E6" s="309"/>
+      <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
         <v>3421</v>
       </c>
-      <c r="H6" s="188">
+      <c r="H6" s="187">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>5389</v>
       </c>
-      <c r="I6" s="188" t="str">
+      <c r="I6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J6" s="188" t="str">
+      <c r="J6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K6" s="188" t="str">
+      <c r="K6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L6" s="188" t="str">
+      <c r="L6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M6" s="188" t="str">
+      <c r="M6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="N6" s="188" t="str">
+      <c r="N6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O6" s="188" t="str">
+      <c r="O6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P6" s="188" t="str">
+      <c r="P6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Q6" s="188" t="str">
+      <c r="Q6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -8565,52 +8561,52 @@
       <c r="B7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="198">
+      <c r="C7" s="197">
         <f>C35</f>
         <v>-1106.5</v>
       </c>
-      <c r="E7" s="311"/>
-      <c r="G7" s="198">
+      <c r="E7" s="309"/>
+      <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-1084</v>
       </c>
-      <c r="H7" s="198">
+      <c r="H7" s="197">
         <f t="shared" si="3"/>
         <v>-1129</v>
       </c>
-      <c r="I7" s="198" t="str">
+      <c r="I7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J7" s="198" t="str">
+      <c r="J7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K7" s="198" t="str">
+      <c r="K7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L7" s="198" t="str">
+      <c r="L7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M7" s="198" t="str">
+      <c r="M7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="N7" s="198" t="str">
+      <c r="N7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O7" s="198" t="str">
+      <c r="O7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P7" s="198" t="str">
+      <c r="P7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q7" s="198" t="str">
+      <c r="Q7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -8620,54 +8616,54 @@
       <c r="B8" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="199">
+      <c r="C8" s="198">
         <f>C6+C7</f>
         <v>2591.8202592374382</v>
       </c>
       <c r="D8" s="60"/>
-      <c r="E8" s="317"/>
+      <c r="E8" s="315"/>
       <c r="F8" s="60"/>
-      <c r="G8" s="188">
+      <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
         <v>2337</v>
       </c>
-      <c r="H8" s="188">
+      <c r="H8" s="187">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>4260</v>
       </c>
-      <c r="I8" s="188" t="str">
+      <c r="I8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J8" s="188" t="str">
+      <c r="J8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K8" s="188" t="str">
+      <c r="K8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="L8" s="188" t="str">
+      <c r="L8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M8" s="188" t="str">
+      <c r="M8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N8" s="188" t="str">
+      <c r="N8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O8" s="188" t="str">
+      <c r="O8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P8" s="188" t="str">
+      <c r="P8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Q8" s="188" t="str">
+      <c r="Q8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -8677,52 +8673,52 @@
       <c r="B9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="198">
+      <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
         <v>159.99999999999997</v>
       </c>
-      <c r="E9" s="311"/>
-      <c r="G9" s="198">
+      <c r="E9" s="309"/>
+      <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>160</v>
       </c>
-      <c r="H9" s="198">
+      <c r="H9" s="197">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>198</v>
       </c>
-      <c r="I9" s="198" t="str">
+      <c r="I9" s="197" t="str">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v/>
       </c>
-      <c r="J9" s="198" t="str">
+      <c r="J9" s="197" t="str">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v/>
       </c>
-      <c r="K9" s="198" t="str">
+      <c r="K9" s="197" t="str">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v/>
       </c>
-      <c r="L9" s="198" t="str">
+      <c r="L9" s="197" t="str">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v/>
       </c>
-      <c r="M9" s="198" t="str">
+      <c r="M9" s="197" t="str">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v/>
       </c>
-      <c r="N9" s="198" t="str">
+      <c r="N9" s="197" t="str">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v/>
       </c>
-      <c r="O9" s="198" t="str">
+      <c r="O9" s="197" t="str">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v/>
       </c>
-      <c r="P9" s="198" t="str">
+      <c r="P9" s="197" t="str">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v/>
       </c>
-      <c r="Q9" s="198" t="str">
+      <c r="Q9" s="197" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -8732,52 +8728,52 @@
       <c r="B10" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="198">
+      <c r="C10" s="197">
         <f>-C4*C78</f>
         <v>-159.99999999999997</v>
       </c>
-      <c r="E10" s="311"/>
-      <c r="G10" s="198">
+      <c r="E10" s="309"/>
+      <c r="G10" s="197">
         <f>Data!C62</f>
         <v>-69</v>
       </c>
-      <c r="H10" s="198">
+      <c r="H10" s="197">
         <f>Data!D62</f>
         <v>-108</v>
       </c>
-      <c r="I10" s="198" t="str">
+      <c r="I10" s="197" t="str">
         <f>Data!E62</f>
         <v/>
       </c>
-      <c r="J10" s="198" t="str">
+      <c r="J10" s="197" t="str">
         <f>Data!F62</f>
         <v/>
       </c>
-      <c r="K10" s="198" t="str">
+      <c r="K10" s="197" t="str">
         <f>Data!G62</f>
         <v/>
       </c>
-      <c r="L10" s="198" t="str">
+      <c r="L10" s="197" t="str">
         <f>Data!H62</f>
         <v/>
       </c>
-      <c r="M10" s="198" t="str">
+      <c r="M10" s="197" t="str">
         <f>Data!I62</f>
         <v/>
       </c>
-      <c r="N10" s="198" t="str">
+      <c r="N10" s="197" t="str">
         <f>Data!J62</f>
         <v/>
       </c>
-      <c r="O10" s="198" t="str">
+      <c r="O10" s="197" t="str">
         <f>Data!K62</f>
         <v/>
       </c>
-      <c r="P10" s="198" t="str">
+      <c r="P10" s="197" t="str">
         <f>Data!L62</f>
         <v/>
       </c>
-      <c r="Q10" s="198" t="str">
+      <c r="Q10" s="197" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -8787,54 +8783,54 @@
       <c r="B11" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="C11" s="200">
+      <c r="C11" s="199">
         <f>C63</f>
         <v>639</v>
       </c>
-      <c r="D11" s="173"/>
-      <c r="E11" s="310"/>
-      <c r="F11" s="173"/>
-      <c r="G11" s="190">
+      <c r="D11" s="172"/>
+      <c r="E11" s="308"/>
+      <c r="F11" s="172"/>
+      <c r="G11" s="189">
         <f>G61</f>
         <v>639</v>
       </c>
-      <c r="H11" s="190">
+      <c r="H11" s="189">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>927</v>
       </c>
-      <c r="I11" s="190" t="str">
+      <c r="I11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J11" s="190" t="str">
+      <c r="J11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="K11" s="190" t="str">
+      <c r="K11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="L11" s="190" t="str">
+      <c r="L11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="M11" s="190" t="str">
+      <c r="M11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N11" s="190" t="str">
+      <c r="N11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="O11" s="190" t="str">
+      <c r="O11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="P11" s="190" t="str">
+      <c r="P11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q11" s="190" t="str">
+      <c r="Q11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -8844,52 +8840,52 @@
       <c r="B12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="198">
+      <c r="C12" s="197">
         <f>C50</f>
         <v>142.19539222287685</v>
       </c>
-      <c r="E12" s="311"/>
-      <c r="G12" s="198">
+      <c r="E12" s="309"/>
+      <c r="G12" s="197">
         <f>G50</f>
         <v>259.96861497481899</v>
       </c>
-      <c r="H12" s="198">
+      <c r="H12" s="197">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>139.30261332735768</v>
       </c>
-      <c r="I12" s="198" t="str">
+      <c r="I12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="J12" s="198" t="str">
+      <c r="J12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="K12" s="198" t="str">
+      <c r="K12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="L12" s="198" t="str">
+      <c r="L12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="M12" s="198" t="str">
+      <c r="M12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="N12" s="198" t="str">
+      <c r="N12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O12" s="198" t="str">
+      <c r="O12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P12" s="198" t="str">
+      <c r="P12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q12" s="198" t="str">
+      <c r="Q12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -8899,52 +8895,52 @@
       <c r="B13" s="71" t="s">
         <v>169</v>
       </c>
-      <c r="C13" s="188">
+      <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
         <v>3373.015651460315</v>
       </c>
-      <c r="E13" s="311"/>
-      <c r="G13" s="188">
+      <c r="E13" s="309"/>
+      <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>3326.968614974819</v>
       </c>
-      <c r="H13" s="188">
+      <c r="H13" s="187">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>5416.3026133273579</v>
       </c>
-      <c r="I13" s="188" t="str">
+      <c r="I13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J13" s="188" t="str">
+      <c r="J13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K13" s="188" t="str">
+      <c r="K13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="L13" s="188" t="str">
+      <c r="L13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M13" s="188" t="str">
+      <c r="M13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N13" s="188" t="str">
+      <c r="N13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="O13" s="188" t="str">
+      <c r="O13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P13" s="188" t="str">
+      <c r="P13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q13" s="188" t="str">
+      <c r="Q13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -8954,52 +8950,52 @@
       <c r="B14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="198">
+      <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-809.52375635047554</v>
       </c>
-      <c r="E14" s="311"/>
-      <c r="G14" s="198">
+      <c r="E14" s="309"/>
+      <c r="G14" s="197">
         <f>Data!C46</f>
         <v>-519</v>
       </c>
-      <c r="H14" s="198">
+      <c r="H14" s="197">
         <f>Data!D46</f>
         <v>-860.83482800000002</v>
       </c>
-      <c r="I14" s="198" t="str">
+      <c r="I14" s="197" t="str">
         <f>Data!E46</f>
         <v/>
       </c>
-      <c r="J14" s="198" t="str">
+      <c r="J14" s="197" t="str">
         <f>Data!F46</f>
         <v/>
       </c>
-      <c r="K14" s="198" t="str">
+      <c r="K14" s="197" t="str">
         <f>Data!G46</f>
         <v/>
       </c>
-      <c r="L14" s="198" t="str">
+      <c r="L14" s="197" t="str">
         <f>Data!H46</f>
         <v/>
       </c>
-      <c r="M14" s="198" t="str">
+      <c r="M14" s="197" t="str">
         <f>Data!I46</f>
         <v/>
       </c>
-      <c r="N14" s="198" t="str">
+      <c r="N14" s="197" t="str">
         <f>Data!J46</f>
         <v/>
       </c>
-      <c r="O14" s="198" t="str">
+      <c r="O14" s="197" t="str">
         <f>Data!K46</f>
         <v/>
       </c>
-      <c r="P14" s="198" t="str">
+      <c r="P14" s="197" t="str">
         <f>Data!L46</f>
         <v/>
       </c>
-      <c r="Q14" s="198" t="str">
+      <c r="Q14" s="197" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -9009,54 +9005,54 @@
       <c r="B15" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="C15" s="198">
+      <c r="C15" s="197">
         <f>-C4*C83</f>
         <v>-22.869707937042335</v>
       </c>
       <c r="D15" s="61"/>
-      <c r="E15" s="318"/>
+      <c r="E15" s="316"/>
       <c r="F15" s="61"/>
-      <c r="G15" s="187">
+      <c r="G15" s="186">
         <f>Data!C48</f>
         <v>0</v>
       </c>
-      <c r="H15" s="187">
+      <c r="H15" s="186">
         <f>Data!D48</f>
         <v>-31</v>
       </c>
-      <c r="I15" s="187" t="str">
+      <c r="I15" s="186" t="str">
         <f>Data!E48</f>
         <v/>
       </c>
-      <c r="J15" s="187" t="str">
+      <c r="J15" s="186" t="str">
         <f>Data!F48</f>
         <v/>
       </c>
-      <c r="K15" s="187" t="str">
+      <c r="K15" s="186" t="str">
         <f>Data!G48</f>
         <v/>
       </c>
-      <c r="L15" s="187" t="str">
+      <c r="L15" s="186" t="str">
         <f>Data!H48</f>
         <v/>
       </c>
-      <c r="M15" s="187" t="str">
+      <c r="M15" s="186" t="str">
         <f>Data!I48</f>
         <v/>
       </c>
-      <c r="N15" s="187" t="str">
+      <c r="N15" s="186" t="str">
         <f>Data!J48</f>
         <v/>
       </c>
-      <c r="O15" s="187" t="str">
+      <c r="O15" s="186" t="str">
         <f>Data!K48</f>
         <v/>
       </c>
-      <c r="P15" s="187" t="str">
+      <c r="P15" s="186" t="str">
         <f>Data!L48</f>
         <v/>
       </c>
-      <c r="Q15" s="187" t="str">
+      <c r="Q15" s="186" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -9066,54 +9062,54 @@
       <c r="B16" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="201">
+      <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
         <v>2540.6221871727971</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="319"/>
+      <c r="E16" s="317"/>
       <c r="F16" s="62"/>
-      <c r="G16" s="188">
+      <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>2807.968614974819</v>
       </c>
-      <c r="H16" s="188">
+      <c r="H16" s="187">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>4524.4677853273579</v>
       </c>
-      <c r="I16" s="188" t="str">
+      <c r="I16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J16" s="188" t="str">
+      <c r="J16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="K16" s="188" t="str">
+      <c r="K16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="L16" s="188" t="str">
+      <c r="L16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M16" s="188" t="str">
+      <c r="M16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N16" s="188" t="str">
+      <c r="N16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="O16" s="188" t="str">
+      <c r="O16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P16" s="188" t="str">
+      <c r="P16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="Q16" s="188" t="str">
+      <c r="Q16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -9123,105 +9119,105 @@
       <c r="B17" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="198">
+      <c r="C17" s="197">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
       <c r="D17" s="59"/>
-      <c r="E17" s="310" t="s">
+      <c r="E17" s="308" t="s">
         <v>373</v>
       </c>
       <c r="F17" s="59"/>
-      <c r="G17" s="202"/>
-      <c r="H17" s="202"/>
-      <c r="I17" s="202"/>
-      <c r="J17" s="202"/>
-      <c r="K17" s="202"/>
-      <c r="L17" s="202"/>
-      <c r="M17" s="202"/>
-      <c r="N17" s="202"/>
-      <c r="O17" s="202"/>
-      <c r="P17" s="202"/>
-      <c r="Q17" s="202"/>
+      <c r="G17" s="201"/>
+      <c r="H17" s="201"/>
+      <c r="I17" s="201"/>
+      <c r="J17" s="201"/>
+      <c r="K17" s="201"/>
+      <c r="L17" s="201"/>
+      <c r="M17" s="201"/>
+      <c r="N17" s="201"/>
+      <c r="O17" s="201"/>
+      <c r="P17" s="201"/>
+      <c r="Q17" s="201"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="198">
+      <c r="C18" s="197">
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
-      <c r="E18" s="310" t="s">
+      <c r="E18" s="308" t="s">
         <v>374</v>
       </c>
       <c r="F18" s="59"/>
-      <c r="G18" s="203"/>
-      <c r="H18" s="203"/>
-      <c r="I18" s="203"/>
-      <c r="J18" s="203"/>
-      <c r="K18" s="203"/>
-      <c r="L18" s="203"/>
-      <c r="M18" s="203"/>
-      <c r="N18" s="203"/>
-      <c r="O18" s="203"/>
-      <c r="P18" s="203"/>
-      <c r="Q18" s="203"/>
+      <c r="G18" s="202"/>
+      <c r="H18" s="202"/>
+      <c r="I18" s="202"/>
+      <c r="J18" s="202"/>
+      <c r="K18" s="202"/>
+      <c r="L18" s="202"/>
+      <c r="M18" s="202"/>
+      <c r="N18" s="202"/>
+      <c r="O18" s="202"/>
+      <c r="P18" s="202"/>
+      <c r="Q18" s="202"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="188">
+      <c r="C19" s="187">
         <f>C16+C17</f>
         <v>2540.6221871727971</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="308"/>
+      <c r="E19" s="306"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="190">
+      <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
         <v>2807.968614974819</v>
       </c>
-      <c r="H19" s="190">
+      <c r="H19" s="189">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>4524.4677853273579</v>
       </c>
-      <c r="I19" s="190" t="str">
+      <c r="I19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J19" s="190" t="str">
+      <c r="J19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K19" s="190" t="str">
+      <c r="K19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="L19" s="190" t="str">
+      <c r="L19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M19" s="190" t="str">
+      <c r="M19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="N19" s="190" t="str">
+      <c r="N19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O19" s="190" t="str">
+      <c r="O19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="P19" s="190" t="str">
+      <c r="P19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q19" s="190" t="str">
+      <c r="Q19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -9275,7 +9271,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="308"/>
+      <c r="E22" s="306"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -9294,54 +9290,54 @@
       <c r="B23" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="204">
+      <c r="C23" s="203">
         <f>-C4*C28</f>
         <v>-5066.6797407625618</v>
       </c>
       <c r="D23" s="59"/>
-      <c r="E23" s="310"/>
+      <c r="E23" s="308"/>
       <c r="F23" s="59"/>
-      <c r="G23" s="187">
+      <c r="G23" s="186">
         <f>Data!C37</f>
         <v>-5344</v>
       </c>
-      <c r="H23" s="187">
+      <c r="H23" s="186">
         <f>Data!D37</f>
         <v>-6492</v>
       </c>
-      <c r="I23" s="187" t="str">
+      <c r="I23" s="186" t="str">
         <f>Data!E37</f>
         <v/>
       </c>
-      <c r="J23" s="187" t="str">
+      <c r="J23" s="186" t="str">
         <f>Data!F37</f>
         <v/>
       </c>
-      <c r="K23" s="187" t="str">
+      <c r="K23" s="186" t="str">
         <f>Data!G37</f>
         <v/>
       </c>
-      <c r="L23" s="187" t="str">
+      <c r="L23" s="186" t="str">
         <f>Data!H37</f>
         <v/>
       </c>
-      <c r="M23" s="187" t="str">
+      <c r="M23" s="186" t="str">
         <f>Data!I37</f>
         <v/>
       </c>
-      <c r="N23" s="187" t="str">
+      <c r="N23" s="186" t="str">
         <f>Data!J37</f>
         <v/>
       </c>
-      <c r="O23" s="187" t="str">
+      <c r="O23" s="186" t="str">
         <f>Data!K37</f>
         <v/>
       </c>
-      <c r="P23" s="187" t="str">
+      <c r="P23" s="186" t="str">
         <f>Data!L37</f>
         <v/>
       </c>
-      <c r="Q23" s="187" t="str">
+      <c r="Q23" s="186" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -9351,54 +9347,54 @@
       <c r="B24" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="198">
+      <c r="C24" s="197">
         <f>-C4*C29</f>
         <v>0</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="308"/>
+      <c r="E24" s="306"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="187">
+      <c r="G24" s="186">
         <f>Data!C40</f>
         <v>0</v>
       </c>
-      <c r="H24" s="187">
+      <c r="H24" s="186">
         <f>Data!D40</f>
         <v>0</v>
       </c>
-      <c r="I24" s="187" t="str">
+      <c r="I24" s="186" t="str">
         <f>Data!E40</f>
         <v/>
       </c>
-      <c r="J24" s="187" t="str">
+      <c r="J24" s="186" t="str">
         <f>Data!F40</f>
         <v/>
       </c>
-      <c r="K24" s="187" t="str">
+      <c r="K24" s="186" t="str">
         <f>Data!G40</f>
         <v/>
       </c>
-      <c r="L24" s="187" t="str">
+      <c r="L24" s="186" t="str">
         <f>Data!H40</f>
         <v/>
       </c>
-      <c r="M24" s="187" t="str">
+      <c r="M24" s="186" t="str">
         <f>Data!I40</f>
         <v/>
       </c>
-      <c r="N24" s="187" t="str">
+      <c r="N24" s="186" t="str">
         <f>Data!J40</f>
         <v/>
       </c>
-      <c r="O24" s="187" t="str">
+      <c r="O24" s="186" t="str">
         <f>Data!K40</f>
         <v/>
       </c>
-      <c r="P24" s="187" t="str">
+      <c r="P24" s="186" t="str">
         <f>Data!L40</f>
         <v/>
       </c>
-      <c r="Q24" s="187" t="str">
+      <c r="Q24" s="186" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -9408,68 +9404,68 @@
       <c r="B25" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="188">
+      <c r="C25" s="187">
         <f>C23+C24</f>
         <v>-5066.6797407625618</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="316"/>
+      <c r="E25" s="314"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="188">
+      <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-5344</v>
       </c>
-      <c r="H25" s="188">
+      <c r="H25" s="187">
         <f t="shared" si="10"/>
         <v>-6492</v>
       </c>
-      <c r="I25" s="188" t="str">
+      <c r="I25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="J25" s="188" t="str">
+      <c r="J25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="K25" s="188" t="str">
+      <c r="K25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="L25" s="188" t="str">
+      <c r="L25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="M25" s="188" t="str">
+      <c r="M25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="N25" s="188" t="str">
+      <c r="N25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O25" s="188" t="str">
+      <c r="O25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="P25" s="188" t="str">
+      <c r="P25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Q25" s="188" t="str">
+      <c r="Q25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
-      <c r="E26" s="311"/>
+      <c r="E26" s="309"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="311"/>
+      <c r="E27" s="309"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
@@ -9481,7 +9477,7 @@
         <v>0.57805815639048053</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="309" t="s">
+      <c r="E28" s="307" t="s">
         <v>375</v>
       </c>
       <c r="F28" s="26"/>
@@ -9541,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="309" t="s">
+      <c r="E29" s="307" t="s">
         <v>375</v>
       </c>
       <c r="F29" s="26"/>
@@ -9599,7 +9595,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.57805815639048053</v>
       </c>
-      <c r="E30" s="311"/>
+      <c r="E30" s="309"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.60969766115231028</v>
@@ -9647,68 +9643,68 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
-      <c r="E31" s="311"/>
+      <c r="E31" s="309"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="311"/>
+      <c r="E32" s="309"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C33" s="205">
+      <c r="C33" s="204">
         <f>AVERAGE(G33:H33)</f>
         <v>-1106.5</v>
       </c>
-      <c r="E33" s="309" t="s">
+      <c r="E33" s="307" t="s">
         <v>375</v>
       </c>
-      <c r="G33" s="198">
+      <c r="G33" s="197">
         <f>Data!C41</f>
         <v>-1084</v>
       </c>
-      <c r="H33" s="198">
+      <c r="H33" s="197">
         <f>Data!D41</f>
         <v>-1129</v>
       </c>
-      <c r="I33" s="198" t="str">
+      <c r="I33" s="197" t="str">
         <f>Data!E41</f>
         <v/>
       </c>
-      <c r="J33" s="198" t="str">
+      <c r="J33" s="197" t="str">
         <f>Data!F41</f>
         <v/>
       </c>
-      <c r="K33" s="198" t="str">
+      <c r="K33" s="197" t="str">
         <f>Data!G41</f>
         <v/>
       </c>
-      <c r="L33" s="198" t="str">
+      <c r="L33" s="197" t="str">
         <f>Data!H41</f>
         <v/>
       </c>
-      <c r="M33" s="198" t="str">
+      <c r="M33" s="197" t="str">
         <f>Data!I41</f>
         <v/>
       </c>
-      <c r="N33" s="198" t="str">
+      <c r="N33" s="197" t="str">
         <f>Data!J41</f>
         <v/>
       </c>
-      <c r="O33" s="198" t="str">
+      <c r="O33" s="197" t="str">
         <f>Data!K41</f>
         <v/>
       </c>
-      <c r="P33" s="198" t="str">
+      <c r="P33" s="197" t="str">
         <f>Data!L41</f>
         <v/>
       </c>
-      <c r="Q33" s="198" t="str">
+      <c r="Q33" s="197" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -9718,56 +9714,56 @@
       <c r="B34" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="205">
+      <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
       <c r="D34" s="59"/>
-      <c r="E34" s="309" t="s">
+      <c r="E34" s="307" t="s">
         <v>375</v>
       </c>
       <c r="F34" s="59"/>
-      <c r="G34" s="187">
+      <c r="G34" s="186">
         <f>Data!C42</f>
         <v>0</v>
       </c>
-      <c r="H34" s="187">
+      <c r="H34" s="186">
         <f>Data!D42</f>
         <v>0</v>
       </c>
-      <c r="I34" s="187" t="str">
+      <c r="I34" s="186" t="str">
         <f>Data!E42</f>
         <v/>
       </c>
-      <c r="J34" s="187" t="str">
+      <c r="J34" s="186" t="str">
         <f>Data!F42</f>
         <v/>
       </c>
-      <c r="K34" s="187" t="str">
+      <c r="K34" s="186" t="str">
         <f>Data!G42</f>
         <v/>
       </c>
-      <c r="L34" s="187" t="str">
+      <c r="L34" s="186" t="str">
         <f>Data!H42</f>
         <v/>
       </c>
-      <c r="M34" s="187" t="str">
+      <c r="M34" s="186" t="str">
         <f>Data!I42</f>
         <v/>
       </c>
-      <c r="N34" s="187" t="str">
+      <c r="N34" s="186" t="str">
         <f>Data!J42</f>
         <v/>
       </c>
-      <c r="O34" s="187" t="str">
+      <c r="O34" s="186" t="str">
         <f>Data!K42</f>
         <v/>
       </c>
-      <c r="P34" s="187" t="str">
+      <c r="P34" s="186" t="str">
         <f>Data!L42</f>
         <v/>
       </c>
-      <c r="Q34" s="187" t="str">
+      <c r="Q34" s="186" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -9777,68 +9773,68 @@
       <c r="B35" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C35" s="187">
         <f>C33+C34</f>
         <v>-1106.5</v>
       </c>
       <c r="D35" s="59"/>
-      <c r="E35" s="310"/>
+      <c r="E35" s="308"/>
       <c r="F35" s="59"/>
-      <c r="G35" s="188">
+      <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-1084</v>
       </c>
-      <c r="H35" s="188">
+      <c r="H35" s="187">
         <f t="shared" si="14"/>
         <v>-1129</v>
       </c>
-      <c r="I35" s="188" t="str">
+      <c r="I35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="J35" s="188" t="str">
+      <c r="J35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="K35" s="188" t="str">
+      <c r="K35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L35" s="188" t="str">
+      <c r="L35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M35" s="188" t="str">
+      <c r="M35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="N35" s="188" t="str">
+      <c r="N35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="O35" s="188" t="str">
+      <c r="O35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="P35" s="188" t="str">
+      <c r="P35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q35" s="188" t="str">
+      <c r="Q35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
-      <c r="E36" s="311"/>
+      <c r="E36" s="309"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="E37" s="311"/>
+      <c r="E37" s="309"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
@@ -9851,7 +9847,7 @@
         <v>0.1262407301768397</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="308"/>
+      <c r="E38" s="306"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -9909,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="308"/>
+      <c r="E39" s="306"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -9965,7 +9961,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.1262407301768397</v>
       </c>
-      <c r="E40" s="311"/>
+      <c r="E40" s="309"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.12367370222475756</v>
@@ -10013,25 +10009,25 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10"/>
-      <c r="E41" s="311"/>
+      <c r="E41" s="309"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="311"/>
+      <c r="E42" s="309"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="305">
+      <c r="C43" s="303">
         <v>0.24</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="308" t="s">
+      <c r="E43" s="306" t="s">
         <v>376</v>
       </c>
       <c r="F43" s="27"/>
@@ -10111,59 +10107,59 @@
       <c r="B46" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="311"/>
+      <c r="E46" s="309"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C47" s="198">
+      <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-43</v>
       </c>
-      <c r="E47" s="311"/>
-      <c r="G47" s="198">
+      <c r="E47" s="309"/>
+      <c r="G47" s="197">
         <f>Data!C51</f>
         <v>-43</v>
       </c>
-      <c r="H47" s="198">
+      <c r="H47" s="197">
         <f>Data!D51</f>
         <v>-40.775368</v>
       </c>
-      <c r="I47" s="198" t="str">
+      <c r="I47" s="197" t="str">
         <f>Data!E51</f>
         <v/>
       </c>
-      <c r="J47" s="198" t="str">
+      <c r="J47" s="197" t="str">
         <f>Data!F51</f>
         <v/>
       </c>
-      <c r="K47" s="198" t="str">
+      <c r="K47" s="197" t="str">
         <f>Data!G51</f>
         <v/>
       </c>
-      <c r="L47" s="198" t="str">
+      <c r="L47" s="197" t="str">
         <f>Data!H51</f>
         <v/>
       </c>
-      <c r="M47" s="198" t="str">
+      <c r="M47" s="197" t="str">
         <f>Data!I51</f>
         <v/>
       </c>
-      <c r="N47" s="198" t="str">
+      <c r="N47" s="197" t="str">
         <f>Data!J51</f>
         <v/>
       </c>
-      <c r="O47" s="198" t="str">
+      <c r="O47" s="197" t="str">
         <f>Data!K51</f>
         <v/>
       </c>
-      <c r="P47" s="198" t="str">
+      <c r="P47" s="197" t="str">
         <f>Data!L51</f>
         <v/>
       </c>
-      <c r="Q47" s="198" t="str">
+      <c r="Q47" s="197" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -10173,109 +10169,109 @@
       <c r="B48" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C48" s="198">
+      <c r="C48" s="197">
         <f>BS!D75*C53</f>
         <v>185.19539222287685</v>
       </c>
-      <c r="E48" s="311"/>
-      <c r="G48" s="338">
+      <c r="E48" s="309"/>
+      <c r="G48" s="336">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
         <v>302.96861497481899</v>
       </c>
-      <c r="H48" s="338">
+      <c r="H48" s="336">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
         <v>180.07798132735766</v>
       </c>
-      <c r="I48" s="338" t="str">
+      <c r="I48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J48" s="338" t="str">
+      <c r="J48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="K48" s="338" t="str">
+      <c r="K48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="L48" s="338" t="str">
+      <c r="L48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="338" t="str">
+      <c r="M48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="338" t="str">
+      <c r="N48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="338" t="str">
+      <c r="O48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="338" t="str">
+      <c r="P48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="338" t="str">
+      <c r="Q48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
-      <c r="B49" s="333" t="s">
+      <c r="B49" s="331" t="s">
         <v>385</v>
       </c>
-      <c r="C49" s="334">
+      <c r="C49" s="332">
         <f>BS!$C$66*C53</f>
         <v>1430.37</v>
       </c>
-      <c r="D49" s="335"/>
-      <c r="E49" s="336"/>
-      <c r="F49" s="335"/>
-      <c r="G49" s="334">
+      <c r="D49" s="333"/>
+      <c r="E49" s="334"/>
+      <c r="F49" s="333"/>
+      <c r="G49" s="332">
         <f>Data!C52</f>
         <v>2340</v>
       </c>
-      <c r="H49" s="334">
+      <c r="H49" s="332">
         <f>Data!D52</f>
         <v>1390.845307</v>
       </c>
-      <c r="I49" s="334" t="str">
+      <c r="I49" s="332" t="str">
         <f>Data!E52</f>
         <v/>
       </c>
-      <c r="J49" s="334" t="str">
+      <c r="J49" s="332" t="str">
         <f>Data!F52</f>
         <v/>
       </c>
-      <c r="K49" s="334" t="str">
+      <c r="K49" s="332" t="str">
         <f>Data!G52</f>
         <v/>
       </c>
-      <c r="L49" s="334" t="str">
+      <c r="L49" s="332" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="334" t="str">
+      <c r="M49" s="332" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="334" t="str">
+      <c r="N49" s="332" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="334" t="str">
+      <c r="O49" s="332" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="334" t="str">
+      <c r="P49" s="332" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="334" t="str">
+      <c r="Q49" s="332" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -10285,66 +10281,66 @@
       <c r="B50" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="188">
+      <c r="C50" s="187">
         <f>C47+C48</f>
         <v>142.19539222287685</v>
       </c>
-      <c r="E50" s="311"/>
-      <c r="G50" s="188">
+      <c r="E50" s="309"/>
+      <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>259.96861497481899</v>
       </c>
-      <c r="H50" s="188">
+      <c r="H50" s="187">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>139.30261332735768</v>
       </c>
-      <c r="I50" s="188" t="str">
+      <c r="I50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="J50" s="188" t="str">
+      <c r="J50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="K50" s="188" t="str">
+      <c r="K50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="L50" s="188" t="str">
+      <c r="L50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M50" s="188" t="str">
+      <c r="M50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="N50" s="188" t="str">
+      <c r="N50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="O50" s="188" t="str">
+      <c r="O50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="P50" s="188" t="str">
+      <c r="P50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="Q50" s="188" t="str">
+      <c r="Q50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
-      <c r="E51" s="311"/>
+      <c r="E51" s="309"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="E52" s="311"/>
+      <c r="E52" s="309"/>
       <c r="G52" s="100" t="s">
         <v>224</v>
       </c>
@@ -10357,23 +10353,23 @@
       <c r="C53" s="89">
         <v>0.03</v>
       </c>
-      <c r="E53" s="308" t="s">
+      <c r="E53" s="306" t="s">
         <v>377</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
         <v>4.907821053293903E-2</v>
       </c>
-      <c r="H53" s="174"/>
-      <c r="I53" s="174"/>
-      <c r="J53" s="174"/>
-      <c r="K53" s="174"/>
-      <c r="L53" s="174"/>
-      <c r="M53" s="174"/>
-      <c r="N53" s="174"/>
-      <c r="O53" s="174"/>
-      <c r="P53" s="174"/>
-      <c r="Q53" s="174"/>
+      <c r="H53" s="173"/>
+      <c r="I53" s="173"/>
+      <c r="J53" s="173"/>
+      <c r="K53" s="173"/>
+      <c r="L53" s="173"/>
+      <c r="M53" s="173"/>
+      <c r="N53" s="173"/>
+      <c r="O53" s="173"/>
+      <c r="P53" s="173"/>
+      <c r="Q53" s="173"/>
     </row>
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
@@ -10384,23 +10380,23 @@
         <f>G54</f>
         <v>1.3902360168121564E-2</v>
       </c>
-      <c r="E54" s="308" t="s">
+      <c r="E54" s="306" t="s">
         <v>378</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
         <v>1.3902360168121564E-2</v>
       </c>
-      <c r="H54" s="174"/>
-      <c r="I54" s="174"/>
-      <c r="J54" s="174"/>
-      <c r="K54" s="174"/>
-      <c r="L54" s="174"/>
-      <c r="M54" s="174"/>
-      <c r="N54" s="174"/>
-      <c r="O54" s="174"/>
-      <c r="P54" s="174"/>
-      <c r="Q54" s="174"/>
+      <c r="H54" s="173"/>
+      <c r="I54" s="173"/>
+      <c r="J54" s="173"/>
+      <c r="K54" s="173"/>
+      <c r="L54" s="173"/>
+      <c r="M54" s="173"/>
+      <c r="N54" s="173"/>
+      <c r="O54" s="173"/>
+      <c r="P54" s="173"/>
+      <c r="Q54" s="173"/>
     </row>
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
@@ -10411,7 +10407,7 @@
         <f>-C8/C47</f>
         <v>60.274889749707867</v>
       </c>
-      <c r="E55" s="311"/>
+      <c r="E55" s="309"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>54.348837209302324</v>
@@ -10459,14 +10455,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
-      <c r="E56" s="311"/>
+      <c r="E56" s="309"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="E57" s="311"/>
+      <c r="E57" s="309"/>
       <c r="G57" s="100" t="s">
         <v>224</v>
       </c>
@@ -10476,52 +10472,52 @@
       <c r="B58" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C58" s="198">
+      <c r="C58" s="197">
         <f>BS!$C79*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="311"/>
-      <c r="G58" s="198">
+      <c r="E58" s="309"/>
+      <c r="G58" s="197">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="198">
+      <c r="H58" s="197">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="198" t="str">
+      <c r="I58" s="197" t="str">
         <f>Data!E56</f>
         <v/>
       </c>
-      <c r="J58" s="198" t="str">
+      <c r="J58" s="197" t="str">
         <f>Data!F56</f>
         <v/>
       </c>
-      <c r="K58" s="198" t="str">
+      <c r="K58" s="197" t="str">
         <f>Data!G56</f>
         <v/>
       </c>
-      <c r="L58" s="198" t="str">
+      <c r="L58" s="197" t="str">
         <f>Data!H56</f>
         <v/>
       </c>
-      <c r="M58" s="198" t="str">
+      <c r="M58" s="197" t="str">
         <f>Data!I56</f>
         <v/>
       </c>
-      <c r="N58" s="198" t="str">
+      <c r="N58" s="197" t="str">
         <f>Data!J56</f>
         <v/>
       </c>
-      <c r="O58" s="198" t="str">
+      <c r="O58" s="197" t="str">
         <f>Data!K56</f>
         <v/>
       </c>
-      <c r="P58" s="198" t="str">
+      <c r="P58" s="197" t="str">
         <f>Data!L56</f>
         <v/>
       </c>
-      <c r="Q58" s="198" t="str">
+      <c r="Q58" s="197" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -10531,52 +10527,52 @@
       <c r="B59" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C59" s="198">
+      <c r="C59" s="197">
         <f>BS!$C68*C67</f>
         <v>639</v>
       </c>
-      <c r="E59" s="311"/>
-      <c r="G59" s="198">
+      <c r="E59" s="309"/>
+      <c r="G59" s="197">
         <f>Data!C55</f>
         <v>639</v>
       </c>
-      <c r="H59" s="198">
+      <c r="H59" s="197">
         <f>Data!D55</f>
         <v>927</v>
       </c>
-      <c r="I59" s="198" t="str">
+      <c r="I59" s="197" t="str">
         <f>Data!E55</f>
         <v/>
       </c>
-      <c r="J59" s="198" t="str">
+      <c r="J59" s="197" t="str">
         <f>Data!F55</f>
         <v/>
       </c>
-      <c r="K59" s="198" t="str">
+      <c r="K59" s="197" t="str">
         <f>Data!G55</f>
         <v/>
       </c>
-      <c r="L59" s="198" t="str">
+      <c r="L59" s="197" t="str">
         <f>Data!H55</f>
         <v/>
       </c>
-      <c r="M59" s="198" t="str">
+      <c r="M59" s="197" t="str">
         <f>Data!I55</f>
         <v/>
       </c>
-      <c r="N59" s="198" t="str">
+      <c r="N59" s="197" t="str">
         <f>Data!J55</f>
         <v/>
       </c>
-      <c r="O59" s="198" t="str">
+      <c r="O59" s="197" t="str">
         <f>Data!K55</f>
         <v/>
       </c>
-      <c r="P59" s="198" t="str">
+      <c r="P59" s="197" t="str">
         <f>Data!L55</f>
         <v/>
       </c>
-      <c r="Q59" s="198" t="str">
+      <c r="Q59" s="197" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -10586,52 +10582,52 @@
       <c r="B60" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C60" s="198">
+      <c r="C60" s="197">
         <f>BS!$C81*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="311"/>
-      <c r="G60" s="198">
+      <c r="E60" s="309"/>
+      <c r="G60" s="197">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="198">
+      <c r="H60" s="197">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="198" t="str">
+      <c r="I60" s="197" t="str">
         <f>Data!E57</f>
         <v/>
       </c>
-      <c r="J60" s="198" t="str">
+      <c r="J60" s="197" t="str">
         <f>Data!F57</f>
         <v/>
       </c>
-      <c r="K60" s="198" t="str">
+      <c r="K60" s="197" t="str">
         <f>Data!G57</f>
         <v/>
       </c>
-      <c r="L60" s="198" t="str">
+      <c r="L60" s="197" t="str">
         <f>Data!H57</f>
         <v/>
       </c>
-      <c r="M60" s="198" t="str">
+      <c r="M60" s="197" t="str">
         <f>Data!I57</f>
         <v/>
       </c>
-      <c r="N60" s="198" t="str">
+      <c r="N60" s="197" t="str">
         <f>Data!J57</f>
         <v/>
       </c>
-      <c r="O60" s="198" t="str">
+      <c r="O60" s="197" t="str">
         <f>Data!K57</f>
         <v/>
       </c>
-      <c r="P60" s="198" t="str">
+      <c r="P60" s="197" t="str">
         <f>Data!L57</f>
         <v/>
       </c>
-      <c r="Q60" s="198" t="str">
+      <c r="Q60" s="197" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -10641,52 +10637,52 @@
       <c r="B61" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="C61" s="188">
+      <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
         <v>639</v>
       </c>
-      <c r="E61" s="311"/>
-      <c r="G61" s="188">
+      <c r="E61" s="309"/>
+      <c r="G61" s="187">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>639</v>
       </c>
-      <c r="H61" s="188">
+      <c r="H61" s="187">
         <f t="shared" si="22"/>
         <v>927</v>
       </c>
-      <c r="I61" s="188" t="str">
+      <c r="I61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="J61" s="188" t="str">
+      <c r="J61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="K61" s="188" t="str">
+      <c r="K61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L61" s="188" t="str">
+      <c r="L61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="M61" s="188" t="str">
+      <c r="M61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="N61" s="188" t="str">
+      <c r="N61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="O61" s="188" t="str">
+      <c r="O61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="P61" s="188" t="str">
+      <c r="P61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Q61" s="188" t="str">
+      <c r="Q61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -10696,53 +10692,53 @@
       <c r="B62" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C62" s="306">
+      <c r="C62" s="304">
         <v>0</v>
       </c>
-      <c r="E62" s="309" t="s">
+      <c r="E62" s="307" t="s">
         <v>379</v>
       </c>
-      <c r="G62" s="198">
+      <c r="G62" s="197">
         <f>Data!C58</f>
         <v>-503</v>
       </c>
-      <c r="H62" s="198">
+      <c r="H62" s="197">
         <f>Data!D58</f>
         <v>203.76488900000004</v>
       </c>
-      <c r="I62" s="198" t="str">
+      <c r="I62" s="197" t="str">
         <f>Data!E58</f>
         <v/>
       </c>
-      <c r="J62" s="198" t="str">
+      <c r="J62" s="197" t="str">
         <f>Data!F58</f>
         <v/>
       </c>
-      <c r="K62" s="198" t="str">
+      <c r="K62" s="197" t="str">
         <f>Data!G58</f>
         <v/>
       </c>
-      <c r="L62" s="198" t="str">
+      <c r="L62" s="197" t="str">
         <f>Data!H58</f>
         <v/>
       </c>
-      <c r="M62" s="198" t="str">
+      <c r="M62" s="197" t="str">
         <f>Data!I58</f>
         <v/>
       </c>
-      <c r="N62" s="198" t="str">
+      <c r="N62" s="197" t="str">
         <f>Data!J58</f>
         <v/>
       </c>
-      <c r="O62" s="198" t="str">
+      <c r="O62" s="197" t="str">
         <f>Data!K58</f>
         <v/>
       </c>
-      <c r="P62" s="198" t="str">
+      <c r="P62" s="197" t="str">
         <f>Data!L58</f>
         <v/>
       </c>
-      <c r="Q62" s="198" t="str">
+      <c r="Q62" s="197" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -10752,66 +10748,66 @@
       <c r="B63" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="C63" s="188">
+      <c r="C63" s="187">
         <f>C61+C62</f>
         <v>639</v>
       </c>
-      <c r="E63" s="311"/>
-      <c r="G63" s="188">
+      <c r="E63" s="309"/>
+      <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>136</v>
       </c>
-      <c r="H63" s="188">
+      <c r="H63" s="187">
         <f t="shared" si="23"/>
         <v>1130.764889</v>
       </c>
-      <c r="I63" s="188" t="str">
+      <c r="I63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="J63" s="188" t="str">
+      <c r="J63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K63" s="188" t="str">
+      <c r="K63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="L63" s="188" t="str">
+      <c r="L63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="M63" s="188" t="str">
+      <c r="M63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="N63" s="188" t="str">
+      <c r="N63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="O63" s="188" t="str">
+      <c r="O63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="P63" s="188" t="str">
+      <c r="P63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Q63" s="188" t="str">
+      <c r="Q63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
-      <c r="E64" s="311"/>
+      <c r="E64" s="309"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="99" t="s">
         <v>174</v>
       </c>
-      <c r="E65" s="311"/>
+      <c r="E65" s="309"/>
       <c r="G65" s="100" t="s">
         <v>224</v>
       </c>
@@ -10821,75 +10817,75 @@
       <c r="B66" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C66" s="181">
+      <c r="C66" s="180">
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="311"/>
+      <c r="E66" s="309"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
       </c>
-      <c r="H66" s="180"/>
-      <c r="I66" s="180"/>
-      <c r="J66" s="180"/>
-      <c r="K66" s="180"/>
-      <c r="L66" s="180"/>
-      <c r="M66" s="180"/>
-      <c r="N66" s="180"/>
-      <c r="O66" s="180"/>
-      <c r="P66" s="180"/>
-      <c r="Q66" s="180"/>
+      <c r="H66" s="179"/>
+      <c r="I66" s="179"/>
+      <c r="J66" s="179"/>
+      <c r="K66" s="179"/>
+      <c r="L66" s="179"/>
+      <c r="M66" s="179"/>
+      <c r="N66" s="179"/>
+      <c r="O66" s="179"/>
+      <c r="P66" s="179"/>
+      <c r="Q66" s="179"/>
     </row>
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
         <v>162</v>
       </c>
-      <c r="C67" s="181">
+      <c r="C67" s="180">
         <f>G67</f>
         <v>2.6966576637407157E-2</v>
       </c>
-      <c r="E67" s="311"/>
+      <c r="E67" s="309"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>2.6966576637407157E-2</v>
       </c>
-      <c r="H67" s="180"/>
-      <c r="I67" s="180"/>
-      <c r="J67" s="180"/>
-      <c r="K67" s="180"/>
-      <c r="L67" s="180"/>
-      <c r="M67" s="180"/>
-      <c r="N67" s="180"/>
-      <c r="O67" s="180"/>
-      <c r="P67" s="180"/>
-      <c r="Q67" s="180"/>
+      <c r="H67" s="179"/>
+      <c r="I67" s="179"/>
+      <c r="J67" s="179"/>
+      <c r="K67" s="179"/>
+      <c r="L67" s="179"/>
+      <c r="M67" s="179"/>
+      <c r="N67" s="179"/>
+      <c r="O67" s="179"/>
+      <c r="P67" s="179"/>
+      <c r="Q67" s="179"/>
     </row>
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="108" t="s">
         <v>163</v>
       </c>
-      <c r="C68" s="181">
+      <c r="C68" s="180">
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="311"/>
+      <c r="E68" s="309"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$81,0)</f>
         <v>0</v>
       </c>
-      <c r="H68" s="180"/>
-      <c r="I68" s="180"/>
-      <c r="J68" s="180"/>
-      <c r="K68" s="180"/>
-      <c r="L68" s="180"/>
-      <c r="M68" s="180"/>
-      <c r="N68" s="180"/>
-      <c r="O68" s="180"/>
-      <c r="P68" s="180"/>
-      <c r="Q68" s="180"/>
+      <c r="H68" s="179"/>
+      <c r="I68" s="179"/>
+      <c r="J68" s="179"/>
+      <c r="K68" s="179"/>
+      <c r="L68" s="179"/>
+      <c r="M68" s="179"/>
+      <c r="N68" s="179"/>
+      <c r="O68" s="179"/>
+      <c r="P68" s="179"/>
+      <c r="Q68" s="179"/>
     </row>
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10"/>
@@ -10901,22 +10897,22 @@
         <v>8.7649511686601553E-3</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="316"/>
+      <c r="E69" s="314"/>
       <c r="F69" s="9"/>
       <c r="G69" s="72">
         <f>G61/BS!C70</f>
         <v>8.7649511686601553E-3</v>
       </c>
-      <c r="H69" s="180"/>
-      <c r="I69" s="180"/>
-      <c r="J69" s="180"/>
-      <c r="K69" s="180"/>
-      <c r="L69" s="180"/>
-      <c r="M69" s="180"/>
-      <c r="N69" s="180"/>
-      <c r="O69" s="180"/>
-      <c r="P69" s="180"/>
-      <c r="Q69" s="180"/>
+      <c r="H69" s="179"/>
+      <c r="I69" s="179"/>
+      <c r="J69" s="179"/>
+      <c r="K69" s="179"/>
+      <c r="L69" s="179"/>
+      <c r="M69" s="179"/>
+      <c r="N69" s="179"/>
+      <c r="O69" s="179"/>
+      <c r="P69" s="179"/>
+      <c r="Q69" s="179"/>
     </row>
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="10"/>
@@ -10951,7 +10947,7 @@
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="308"/>
+      <c r="E72" s="306"/>
       <c r="F72" s="27"/>
       <c r="G72" s="100"/>
       <c r="H72" s="12"/>
@@ -10975,7 +10971,7 @@
         <v>0.57805815639048053</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="308"/>
+      <c r="E73" s="306"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -11032,7 +11028,7 @@
         <v>0.42194184360951947</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="308"/>
+      <c r="E74" s="306"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -11089,7 +11085,7 @@
         <v>0.1262407301768397</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="308"/>
+      <c r="E75" s="306"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -11146,7 +11142,7 @@
         <v>0.2957011134326798</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="308"/>
+      <c r="E76" s="306"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -11203,7 +11199,7 @@
         <v>1.8254420992584137E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="308"/>
+      <c r="E77" s="306"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -11260,7 +11256,7 @@
         <v>1.8254420992584137E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="309" t="s">
+      <c r="E78" s="307" t="s">
         <v>380</v>
       </c>
       <c r="F78" s="27"/>
@@ -11319,7 +11315,7 @@
         <v>7.2903593839132919E-2</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="308"/>
+      <c r="E79" s="306"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -11376,7 +11372,7 @@
         <v>1.6223090955262618E-2</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="308"/>
+      <c r="E80" s="306"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -11433,7 +11429,7 @@
         <v>0.3848277982270753</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="308"/>
+      <c r="E81" s="306"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -11490,7 +11486,7 @@
         <v>9.2358671574498064E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="308"/>
+      <c r="E82" s="306"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -11543,12 +11539,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="307">
+      <c r="C83" s="305">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>2.6092079791263361E-3</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="308"/>
+      <c r="E83" s="306"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -11605,7 +11601,7 @@
         <v>0.2898599186734509</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="308"/>
+      <c r="E84" s="306"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -11657,26 +11653,26 @@
       <c r="B85" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C85" s="307">
+      <c r="C85" s="305">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="310" t="str">
+      <c r="E85" s="308" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="260"/>
-      <c r="H85" s="260"/>
-      <c r="I85" s="260"/>
-      <c r="J85" s="260"/>
-      <c r="K85" s="260"/>
-      <c r="L85" s="260"/>
-      <c r="M85" s="260"/>
-      <c r="N85" s="260"/>
-      <c r="O85" s="260"/>
-      <c r="P85" s="260"/>
-      <c r="Q85" s="260"/>
+      <c r="G85" s="259"/>
+      <c r="H85" s="259"/>
+      <c r="I85" s="259"/>
+      <c r="J85" s="259"/>
+      <c r="K85" s="259"/>
+      <c r="L85" s="259"/>
+      <c r="M85" s="259"/>
+      <c r="N85" s="259"/>
+      <c r="O85" s="259"/>
+      <c r="P85" s="259"/>
+      <c r="Q85" s="259"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
@@ -11686,21 +11682,21 @@
       <c r="C86" s="79">
         <v>0</v>
       </c>
-      <c r="E86" s="310" t="str">
+      <c r="E86" s="308" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
-      <c r="G86" s="174"/>
-      <c r="H86" s="174"/>
-      <c r="I86" s="174"/>
-      <c r="J86" s="174"/>
-      <c r="K86" s="174"/>
-      <c r="L86" s="174"/>
-      <c r="M86" s="174"/>
-      <c r="N86" s="174"/>
-      <c r="O86" s="174"/>
-      <c r="P86" s="174"/>
-      <c r="Q86" s="174"/>
+      <c r="G86" s="173"/>
+      <c r="H86" s="173"/>
+      <c r="I86" s="173"/>
+      <c r="J86" s="173"/>
+      <c r="K86" s="173"/>
+      <c r="L86" s="173"/>
+      <c r="M86" s="173"/>
+      <c r="N86" s="173"/>
+      <c r="O86" s="173"/>
+      <c r="P86" s="173"/>
+      <c r="Q86" s="173"/>
     </row>
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
@@ -11712,7 +11708,7 @@
         <v>0.2898599186734509</v>
       </c>
       <c r="D87" s="77"/>
-      <c r="E87" s="308"/>
+      <c r="E87" s="306"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -11761,14 +11757,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
-      <c r="E88" s="311"/>
+      <c r="E88" s="309"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
       <c r="B89" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="E89" s="311"/>
+      <c r="E89" s="309"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="10"/>
@@ -11780,7 +11776,7 @@
         <f>G90</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="E90" s="311"/>
+      <c r="E90" s="309"/>
       <c r="G90" s="116">
         <f>Data!C64</f>
         <v>0.57999999999999996</v>
@@ -11836,7 +11832,7 @@
         <f>C90*Common_Shares/$C$3</f>
         <v>4739.6903628800001</v>
       </c>
-      <c r="E91" s="311"/>
+      <c r="E91" s="309"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
         <v>4739.6903628800001</v>
@@ -11891,48 +11887,48 @@
         <f>C90/(C19*$C$3/Common_Shares)</f>
         <v>1.8655628478763795</v>
       </c>
-      <c r="E92" s="311"/>
-      <c r="G92" s="175">
+      <c r="E92" s="309"/>
+      <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
         <v>1.6879427845465798</v>
       </c>
-      <c r="H92" s="175">
+      <c r="H92" s="174">
         <f t="shared" si="38"/>
         <v>1.0475685954159291</v>
       </c>
-      <c r="I92" s="175" t="str">
+      <c r="I92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="J92" s="175" t="str">
+      <c r="J92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="K92" s="175" t="str">
+      <c r="K92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="L92" s="175" t="str">
+      <c r="L92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="M92" s="175" t="str">
+      <c r="M92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="N92" s="175" t="str">
+      <c r="N92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="O92" s="175" t="str">
+      <c r="O92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="P92" s="175" t="str">
+      <c r="P92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="Q92" s="175" t="str">
+      <c r="Q92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
@@ -11946,7 +11942,7 @@
         <f>C90/Market_Price</f>
         <v>7.3417721518987331E-2</v>
       </c>
-      <c r="E93" s="311"/>
+      <c r="E93" s="309"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>7.3417721518987331E-2</v>
@@ -11994,16 +11990,16 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
-      <c r="E94" s="311"/>
+      <c r="E94" s="309"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
-      <c r="B95" s="162" t="s">
+      <c r="B95" s="161" t="s">
         <v>89</v>
       </c>
       <c r="C95" s="63"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="308"/>
+      <c r="E95" s="306"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -12027,7 +12023,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="308"/>
+      <c r="E96" s="306"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -12084,7 +12080,7 @@
         <v>1.3840538284081383E-2</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="308"/>
+      <c r="E97" s="306"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -12162,7 +12158,7 @@
       <c r="B100" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="E100" s="311"/>
+      <c r="E100" s="309"/>
       <c r="G100" s="100" t="s">
         <v>224</v>
       </c>
@@ -12172,54 +12168,54 @@
       <c r="B101" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C101" s="206">
+      <c r="C101" s="205">
         <f>BS!G32</f>
         <v>180996</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="312"/>
+      <c r="E101" s="310"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="187">
+      <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>180344</v>
       </c>
-      <c r="H101" s="187">
+      <c r="H101" s="186">
         <f t="shared" si="42"/>
         <v>174007</v>
       </c>
-      <c r="I101" s="187" t="str">
+      <c r="I101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="J101" s="187" t="str">
+      <c r="J101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="K101" s="187" t="str">
+      <c r="K101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="L101" s="187" t="str">
+      <c r="L101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="M101" s="187" t="str">
+      <c r="M101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="N101" s="187" t="str">
+      <c r="N101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="O101" s="187" t="str">
+      <c r="O101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="P101" s="187" t="str">
+      <c r="P101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="Q101" s="187" t="str">
+      <c r="Q101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -12229,54 +12225,54 @@
       <c r="B102" s="95" t="s">
         <v>215</v>
       </c>
-      <c r="C102" s="207">
+      <c r="C102" s="206">
         <f>BS!C4</f>
         <v>8029</v>
       </c>
       <c r="D102" s="91"/>
-      <c r="E102" s="313"/>
+      <c r="E102" s="311"/>
       <c r="F102" s="91"/>
-      <c r="G102" s="189">
+      <c r="G102" s="188">
         <f>IF(G$4="","",Data!D76)</f>
         <v>7251</v>
       </c>
-      <c r="H102" s="189" t="str">
+      <c r="H102" s="188" t="str">
         <f>IF(H$4="","",Data!E76)</f>
         <v/>
       </c>
-      <c r="I102" s="189" t="str">
+      <c r="I102" s="188" t="str">
         <f>IF(I$4="","",Data!F76)</f>
         <v/>
       </c>
-      <c r="J102" s="189" t="str">
+      <c r="J102" s="188" t="str">
         <f>IF(J$4="","",Data!G76)</f>
         <v/>
       </c>
-      <c r="K102" s="189" t="str">
+      <c r="K102" s="188" t="str">
         <f>IF(K$4="","",Data!H76)</f>
         <v/>
       </c>
-      <c r="L102" s="189" t="str">
+      <c r="L102" s="188" t="str">
         <f>IF(L$4="","",Data!I76)</f>
         <v/>
       </c>
-      <c r="M102" s="189" t="str">
+      <c r="M102" s="188" t="str">
         <f>IF(M$4="","",Data!J76)</f>
         <v/>
       </c>
-      <c r="N102" s="189" t="str">
+      <c r="N102" s="188" t="str">
         <f>IF(N$4="","",Data!K76)</f>
         <v/>
       </c>
-      <c r="O102" s="189" t="str">
+      <c r="O102" s="188" t="str">
         <f>IF(O$4="","",Data!L76)</f>
         <v/>
       </c>
-      <c r="P102" s="189" t="str">
+      <c r="P102" s="188" t="str">
         <f>IF(P$4="","",Data!M76)</f>
         <v/>
       </c>
-      <c r="Q102" s="189" t="str">
+      <c r="Q102" s="188" t="str">
         <f>IF(Q$4="","",Data!N76)</f>
         <v/>
       </c>
@@ -12286,54 +12282,54 @@
       <c r="B103" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="C103" s="207">
+      <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
         <v>15310</v>
       </c>
       <c r="D103" s="91"/>
-      <c r="E103" s="313"/>
+      <c r="E103" s="311"/>
       <c r="F103" s="91"/>
-      <c r="G103" s="189">
+      <c r="G103" s="188">
         <f>IF(G$4="","",Data!D77)</f>
         <v>16389</v>
       </c>
-      <c r="H103" s="189" t="str">
+      <c r="H103" s="188" t="str">
         <f>IF(H$4="","",Data!E77)</f>
         <v/>
       </c>
-      <c r="I103" s="189" t="str">
+      <c r="I103" s="188" t="str">
         <f>IF(I$4="","",Data!F77)</f>
         <v/>
       </c>
-      <c r="J103" s="189" t="str">
+      <c r="J103" s="188" t="str">
         <f>IF(J$4="","",Data!G77)</f>
         <v/>
       </c>
-      <c r="K103" s="189" t="str">
+      <c r="K103" s="188" t="str">
         <f>IF(K$4="","",Data!H77)</f>
         <v/>
       </c>
-      <c r="L103" s="189" t="str">
+      <c r="L103" s="188" t="str">
         <f>IF(L$4="","",Data!I77)</f>
         <v/>
       </c>
-      <c r="M103" s="189" t="str">
+      <c r="M103" s="188" t="str">
         <f>IF(M$4="","",Data!J77)</f>
         <v/>
       </c>
-      <c r="N103" s="189" t="str">
+      <c r="N103" s="188" t="str">
         <f>IF(N$4="","",Data!K77)</f>
         <v/>
       </c>
-      <c r="O103" s="189" t="str">
+      <c r="O103" s="188" t="str">
         <f>IF(O$4="","",Data!L77)</f>
         <v/>
       </c>
-      <c r="P103" s="189" t="str">
+      <c r="P103" s="188" t="str">
         <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
-      <c r="Q103" s="189" t="str">
+      <c r="Q103" s="188" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -12343,54 +12339,54 @@
       <c r="B104" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C104" s="206">
+      <c r="C104" s="205">
         <f>BS!G30</f>
         <v>13889</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="312"/>
+      <c r="E104" s="310"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="187">
+      <c r="G104" s="186">
         <f>Data!C78</f>
         <v>14028</v>
       </c>
-      <c r="H104" s="187">
+      <c r="H104" s="186">
         <f>Data!D78</f>
         <v>10902</v>
       </c>
-      <c r="I104" s="187" t="str">
+      <c r="I104" s="186" t="str">
         <f>Data!E78</f>
         <v/>
       </c>
-      <c r="J104" s="187" t="str">
+      <c r="J104" s="186" t="str">
         <f>Data!F78</f>
         <v/>
       </c>
-      <c r="K104" s="187" t="str">
+      <c r="K104" s="186" t="str">
         <f>Data!G78</f>
         <v/>
       </c>
-      <c r="L104" s="187" t="str">
+      <c r="L104" s="186" t="str">
         <f>Data!H78</f>
         <v/>
       </c>
-      <c r="M104" s="187" t="str">
+      <c r="M104" s="186" t="str">
         <f>Data!I78</f>
         <v/>
       </c>
-      <c r="N104" s="187" t="str">
+      <c r="N104" s="186" t="str">
         <f>Data!J78</f>
         <v/>
       </c>
-      <c r="O104" s="187" t="str">
+      <c r="O104" s="186" t="str">
         <f>Data!K78</f>
         <v/>
       </c>
-      <c r="P104" s="187" t="str">
+      <c r="P104" s="186" t="str">
         <f>Data!L78</f>
         <v/>
       </c>
-      <c r="Q104" s="187" t="str">
+      <c r="Q104" s="186" t="str">
         <f>Data!M78</f>
         <v/>
       </c>
@@ -12400,61 +12396,61 @@
       <c r="B105" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C105" s="206">
+      <c r="C105" s="205">
         <f>BS!G27</f>
         <v>167107</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="312"/>
+      <c r="E105" s="310"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="187">
+      <c r="G105" s="186">
         <f>Data!C79</f>
         <v>166316</v>
       </c>
-      <c r="H105" s="187">
+      <c r="H105" s="186">
         <f>Data!D79</f>
         <v>163105</v>
       </c>
-      <c r="I105" s="187" t="str">
+      <c r="I105" s="186" t="str">
         <f>Data!E79</f>
         <v/>
       </c>
-      <c r="J105" s="187" t="str">
+      <c r="J105" s="186" t="str">
         <f>Data!F79</f>
         <v/>
       </c>
-      <c r="K105" s="187" t="str">
+      <c r="K105" s="186" t="str">
         <f>Data!G79</f>
         <v/>
       </c>
-      <c r="L105" s="187" t="str">
+      <c r="L105" s="186" t="str">
         <f>Data!H79</f>
         <v/>
       </c>
-      <c r="M105" s="187" t="str">
+      <c r="M105" s="186" t="str">
         <f>Data!I79</f>
         <v/>
       </c>
-      <c r="N105" s="187" t="str">
+      <c r="N105" s="186" t="str">
         <f>Data!J79</f>
         <v/>
       </c>
-      <c r="O105" s="187" t="str">
+      <c r="O105" s="186" t="str">
         <f>Data!K79</f>
         <v/>
       </c>
-      <c r="P105" s="187" t="str">
+      <c r="P105" s="186" t="str">
         <f>Data!L79</f>
         <v/>
       </c>
-      <c r="Q105" s="187" t="str">
+      <c r="Q105" s="186" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
-      <c r="E106" s="311"/>
+      <c r="E106" s="309"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
@@ -12463,7 +12459,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="312"/>
+      <c r="E107" s="310"/>
       <c r="F107" s="26"/>
       <c r="G107" s="100" t="s">
         <v>224</v>
@@ -12489,7 +12485,7 @@
         <v>0.91602966343411296</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="312"/>
+      <c r="E108" s="310"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -12546,7 +12542,7 @@
         <v>1.7467199087278951</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="312"/>
+      <c r="E109" s="310"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -12603,26 +12599,26 @@
         <v>8.343867655447804</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="312"/>
+      <c r="E110" s="310"/>
       <c r="F110" s="26"/>
       <c r="G110" s="97">
         <f>BS!$G$38/G$4</f>
         <v>8.343867655447804</v>
       </c>
-      <c r="H110" s="232"/>
-      <c r="I110" s="232"/>
-      <c r="J110" s="232"/>
-      <c r="K110" s="232"/>
-      <c r="L110" s="232"/>
-      <c r="M110" s="232"/>
-      <c r="N110" s="232"/>
-      <c r="O110" s="232"/>
-      <c r="P110" s="232"/>
-      <c r="Q110" s="232"/>
+      <c r="H110" s="231"/>
+      <c r="I110" s="231"/>
+      <c r="J110" s="231"/>
+      <c r="K110" s="231"/>
+      <c r="L110" s="231"/>
+      <c r="M110" s="231"/>
+      <c r="N110" s="231"/>
+      <c r="O110" s="231"/>
+      <c r="P110" s="231"/>
+      <c r="Q110" s="231"/>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
-      <c r="E111" s="311"/>
+      <c r="E111" s="309"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
@@ -12631,7 +12627,7 @@
       </c>
       <c r="C112" s="55"/>
       <c r="D112" s="55"/>
-      <c r="E112" s="314"/>
+      <c r="E112" s="312"/>
       <c r="F112" s="55"/>
       <c r="G112" s="23" t="str">
         <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
@@ -12687,7 +12683,7 @@
         <f>C81</f>
         <v>0.3848277982270753</v>
       </c>
-      <c r="E113" s="311"/>
+      <c r="E113" s="309"/>
       <c r="G113" s="23">
         <f t="shared" ref="G113:Q113" si="45">G81</f>
         <v>0.37957428579290575</v>
@@ -12741,7 +12737,7 @@
         <f>C4/C101</f>
         <v>4.8426484563194767E-2</v>
       </c>
-      <c r="E114" s="311"/>
+      <c r="E114" s="309"/>
       <c r="G114" s="42">
         <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
         <v>4.8601561460320276E-2</v>
@@ -12796,7 +12792,7 @@
         <v>1.0831144117242246</v>
       </c>
       <c r="D115" s="11"/>
-      <c r="E115" s="315"/>
+      <c r="E115" s="313"/>
       <c r="F115" s="11"/>
       <c r="G115" s="15">
         <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
@@ -12853,7 +12849,7 @@
         <v>1.5509944282629921E-2</v>
       </c>
       <c r="D116" s="106"/>
-      <c r="E116" s="314"/>
+      <c r="E116" s="312"/>
       <c r="F116" s="106"/>
       <c r="G116" s="105">
         <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
@@ -12944,12 +12940,12 @@
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10"/>
-      <c r="B119" s="183" t="s">
+      <c r="B119" s="182" t="s">
         <v>175</v>
       </c>
-      <c r="C119" s="184"/>
+      <c r="C119" s="183"/>
       <c r="D119" s="27"/>
-      <c r="E119" s="308"/>
+      <c r="E119" s="306"/>
       <c r="F119" s="27"/>
       <c r="G119" s="12"/>
       <c r="H119" s="12"/>
@@ -12969,54 +12965,54 @@
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
         <v>FCFE per share (HKD)</v>
       </c>
-      <c r="C120" s="182">
+      <c r="C120" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
         <v>0.31089812956997381</v>
       </c>
       <c r="D120" s="27"/>
-      <c r="E120" s="308"/>
+      <c r="E120" s="306"/>
       <c r="F120" s="27"/>
-      <c r="G120" s="182">
+      <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
         <v>0.34361354265677985</v>
       </c>
-      <c r="H120" s="182">
+      <c r="H120" s="181">
         <f t="shared" si="49"/>
         <v>0.55366302745045104</v>
       </c>
-      <c r="I120" s="182" t="str">
+      <c r="I120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="J120" s="182" t="str">
+      <c r="J120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="K120" s="182" t="str">
+      <c r="K120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="L120" s="182" t="str">
+      <c r="L120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="M120" s="182" t="str">
+      <c r="M120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="N120" s="182" t="str">
+      <c r="N120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="O120" s="182" t="str">
+      <c r="O120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="P120" s="182" t="str">
+      <c r="P120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="Q120" s="182" t="str">
+      <c r="Q120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
@@ -13031,7 +13027,7 @@
         <v>3.9354193616452378E-2</v>
       </c>
       <c r="D121" s="27"/>
-      <c r="E121" s="308"/>
+      <c r="E121" s="306"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
@@ -13838,10 +13834,10 @@
       <c r="H4" s="124"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B5" s="234" t="s">
+      <c r="B5" s="233" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="235">
+      <c r="C5" s="234">
         <f>Thesis!C70</f>
         <v>0.09</v>
       </c>
@@ -13852,7 +13848,7 @@
       <c r="B6" s="153" t="s">
         <v>233</v>
       </c>
-      <c r="C6" s="239">
+      <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>28229.135413031079</v>
       </c>
@@ -13860,17 +13856,17 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="344" t="s">
         <v>256</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="344"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
         <v>229</v>
       </c>
-      <c r="C7" s="233">
+      <c r="C7" s="232">
         <f>BS!G31</f>
         <v>3093</v>
       </c>
@@ -13878,15 +13874,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="344"/>
+      <c r="F7" s="344"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
         <v>230</v>
       </c>
-      <c r="C8" s="208">
+      <c r="C8" s="207">
         <f>BS!D66</f>
         <v>41505.820259237436</v>
       </c>
@@ -13894,15 +13890,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="344"/>
+      <c r="F8" s="344"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B9" s="234" t="s">
+      <c r="B9" s="233" t="s">
         <v>195</v>
       </c>
-      <c r="C9" s="236">
+      <c r="C9" s="235">
         <f>BS!H42</f>
         <v>7814.4</v>
       </c>
@@ -13910,15 +13906,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="344"/>
+      <c r="F9" s="344"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
         <v>232</v>
       </c>
-      <c r="C10" s="239">
+      <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
         <v>74456.355672268517</v>
       </c>
@@ -13929,10 +13925,10 @@
       <c r="H10" s="124"/>
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="237" t="s">
+      <c r="B11" s="236" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="238">
+      <c r="C11" s="237">
         <f>Exchange_Rate</f>
         <v>1</v>
       </c>
@@ -13979,7 +13975,7 @@
       <c r="B16" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="166">
+      <c r="C16" s="165">
         <f>Scenarios!C65</f>
         <v>-7.3000000000000001E-3</v>
       </c>
@@ -13989,7 +13985,7 @@
       <c r="B17" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="167">
+      <c r="C17" s="166">
         <f>Scenarios!C64</f>
         <v>10</v>
       </c>
@@ -15118,19 +15114,19 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B73" s="176" t="s">
+      <c r="B73" s="175" t="s">
         <v>122</v>
       </c>
-      <c r="C73" s="176" t="s">
+      <c r="C73" s="175" t="s">
         <v>137</v>
       </c>
-      <c r="D73" s="176" t="s">
+      <c r="D73" s="175" t="s">
         <v>117</v>
       </c>
-      <c r="E73" s="177" t="s">
+      <c r="E73" s="176" t="s">
         <v>118</v>
       </c>
-      <c r="F73" s="177" t="s">
+      <c r="F73" s="176" t="s">
         <v>124</v>
       </c>
     </row>
@@ -15248,27 +15244,27 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B79" s="160"/>
-      <c r="C79" s="160"/>
-      <c r="D79" s="160"/>
-      <c r="E79" s="160"/>
-      <c r="F79" s="161"/>
+      <c r="B79" s="159"/>
+      <c r="C79" s="159"/>
+      <c r="D79" s="159"/>
+      <c r="E79" s="159"/>
+      <c r="F79" s="160"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B80" s="160" t="s">
+      <c r="B80" s="159" t="s">
         <v>342</v>
       </c>
-      <c r="C80" s="160" t="s">
+      <c r="C80" s="159" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C81" s="160" t="s">
+      <c r="C81" s="159" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C82" s="160" t="s">
+      <c r="C82" s="159" t="s">
         <v>108</v>
       </c>
     </row>
@@ -15327,19 +15323,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="285" t="s">
+      <c r="H2" s="283" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="286"/>
+      <c r="I2" s="284"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="163" t="s">
         <v>153</v>
       </c>
-      <c r="H3" s="284">
+      <c r="H3" s="282">
         <v>0</v>
       </c>
-      <c r="I3" s="272">
+      <c r="I3" s="270">
         <f>-Market_Price</f>
         <v>-7.9</v>
       </c>
@@ -15352,29 +15348,29 @@
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
-      <c r="E4" s="160" t="s">
+      <c r="E4" s="159" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="160"/>
-      <c r="H4" s="284">
+      <c r="F4" s="159"/>
+      <c r="H4" s="282">
         <v>1</v>
       </c>
-      <c r="I4" s="272">
+      <c r="I4" s="270">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="H5" s="284">
+      <c r="H5" s="282">
         <v>2</v>
       </c>
-      <c r="I5" s="272">
+      <c r="I5" s="270">
         <f t="shared" si="0"/>
         <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B6" s="164" t="s">
+      <c r="B6" s="163" t="s">
         <v>100</v>
       </c>
       <c r="C6" s="110">
@@ -15385,10 +15381,10 @@
         <v>298</v>
       </c>
       <c r="F6" s="103"/>
-      <c r="H6" s="284">
+      <c r="H6" s="282">
         <v>3</v>
       </c>
-      <c r="I6" s="272">
+      <c r="I6" s="270">
         <f t="shared" si="0"/>
         <v>9.6147055134616366</v>
       </c>
@@ -15405,15 +15401,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="346" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
-      <c r="H7" s="284">
+      <c r="F7" s="346"/>
+      <c r="H7" s="282">
         <v>4</v>
       </c>
-      <c r="I7" s="272" t="str">
+      <c r="I7" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15430,12 +15426,12 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
-      <c r="H8" s="284">
+      <c r="E8" s="346"/>
+      <c r="F8" s="346"/>
+      <c r="H8" s="282">
         <v>5</v>
       </c>
-      <c r="I8" s="272" t="str">
+      <c r="I8" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15444,7 +15440,7 @@
       <c r="B9" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="208">
+      <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
         <v>2540.6221871727971</v>
       </c>
@@ -15452,37 +15448,37 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
-      <c r="H9" s="284">
+      <c r="E9" s="346"/>
+      <c r="F9" s="346"/>
+      <c r="H9" s="282">
         <v>6</v>
       </c>
-      <c r="I9" s="272" t="str">
+      <c r="I9" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
-      <c r="H10" s="284">
+      <c r="E10" s="346"/>
+      <c r="F10" s="346"/>
+      <c r="H10" s="282">
         <v>7</v>
       </c>
-      <c r="I10" s="272" t="str">
+      <c r="I10" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B11" s="164" t="s">
+      <c r="B11" s="163" t="s">
         <v>295</v>
       </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
-      <c r="H11" s="284">
+      <c r="E11" s="346"/>
+      <c r="F11" s="346"/>
+      <c r="H11" s="282">
         <v>8</v>
       </c>
-      <c r="I11" s="272" t="str">
+      <c r="I11" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15491,17 +15487,17 @@
       <c r="B12" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="C12" s="163" t="e">
+      <c r="C12" s="162" t="e">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D12" s="163"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
-      <c r="H12" s="284">
+      <c r="D12" s="162"/>
+      <c r="E12" s="346"/>
+      <c r="F12" s="346"/>
+      <c r="H12" s="282">
         <v>9</v>
       </c>
-      <c r="I12" s="272" t="str">
+      <c r="I12" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15510,16 +15506,16 @@
       <c r="B13" s="152" t="s">
         <v>157</v>
       </c>
-      <c r="C13" s="163" t="e">
+      <c r="C13" s="162" t="e">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
-      <c r="H13" s="284">
+      <c r="E13" s="346"/>
+      <c r="F13" s="346"/>
+      <c r="H13" s="282">
         <v>10</v>
       </c>
-      <c r="I13" s="272" t="str">
+      <c r="I13" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15528,12 +15524,12 @@
       <c r="B14" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="163" t="e">
+      <c r="C14" s="162" t="e">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="346"/>
+      <c r="F14" s="346"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15548,7 +15544,7 @@
       <c r="B17" s="112" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="164" t="s">
+      <c r="E17" s="163" t="s">
         <v>367</v>
       </c>
     </row>
@@ -15559,27 +15555,27 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="347" t="s">
+      <c r="E18" s="346" t="s">
         <v>368</v>
       </c>
-      <c r="F18" s="348"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="347"/>
+      <c r="F19" s="347"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B20" s="164" t="s">
+      <c r="B20" s="163" t="s">
         <v>332</v>
       </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+      <c r="E20" s="347"/>
+      <c r="F20" s="347"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
         <v>296</v>
       </c>
-      <c r="C21" s="165">
+      <c r="C21" s="164">
         <f>Market_Price</f>
         <v>7.9</v>
       </c>
@@ -15587,14 +15583,14 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="347"/>
+      <c r="F21" s="347"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
         <v>297</v>
       </c>
-      <c r="C22" s="165">
+      <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
         <v>9.111288498532895</v>
       </c>
@@ -15602,104 +15598,104 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="347"/>
+      <c r="F22" s="347"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B24" s="164" t="s">
+      <c r="B24" s="163" t="s">
         <v>120</v>
       </c>
-      <c r="E24" s="164" t="s">
+      <c r="E24" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F24" s="164"/>
+      <c r="F24" s="163"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="171">
+      <c r="C25" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
-      <c r="D25" s="168"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="D25" s="167"/>
+      <c r="E25" s="345"/>
+      <c r="F25" s="345"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C26" s="169">
+      <c r="C26" s="168">
         <v>0</v>
       </c>
-      <c r="D26" s="169"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="D26" s="168"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="165">
+      <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
         <v>9.1112884985328897</v>
       </c>
-      <c r="D27" s="165" t="str">
+      <c r="D27" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="345"/>
+      <c r="F27" s="345"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C28" s="170">
+      <c r="C28" s="169">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D28" s="170"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="D28" s="169"/>
+      <c r="E28" s="345"/>
+      <c r="F28" s="345"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B30" s="164" t="s">
+      <c r="B30" s="163" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="164" t="s">
+      <c r="E30" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F30" s="164"/>
+      <c r="F30" s="163"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C31" s="171">
+      <c r="C31" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
-      <c r="D31" s="168"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="D31" s="167"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C32" s="169">
+      <c r="C32" s="168">
         <v>-0.05</v>
       </c>
-      <c r="D32" s="169"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="D32" s="168"/>
+      <c r="E32" s="345"/>
+      <c r="F32" s="345"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="165">
+      <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
         <v>8.6191954792579697</v>
       </c>
@@ -15707,57 +15703,57 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="345"/>
+      <c r="F33" s="345"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C34" s="170">
+      <c r="C34" s="169">
         <v>0.2</v>
       </c>
-      <c r="D34" s="170"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="D34" s="169"/>
+      <c r="E34" s="345"/>
+      <c r="F34" s="345"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B36" s="164" t="s">
+      <c r="B36" s="163" t="s">
         <v>119</v>
       </c>
-      <c r="E36" s="164" t="s">
+      <c r="E36" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F36" s="164"/>
+      <c r="F36" s="163"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C37" s="171">
+      <c r="C37" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
-      <c r="D37" s="168"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="D37" s="167"/>
+      <c r="E37" s="345"/>
+      <c r="F37" s="345"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C38" s="169">
+      <c r="C38" s="168">
         <v>0.02</v>
       </c>
-      <c r="D38" s="169"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="D38" s="168"/>
+      <c r="E38" s="345"/>
+      <c r="F38" s="345"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="165">
+      <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
         <v>9.3427745886766083</v>
       </c>
@@ -15765,26 +15761,26 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="345"/>
+      <c r="F39" s="345"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C40" s="172">
+      <c r="C40" s="171">
         <f>1-C28-C34</f>
         <v>0.24999999999999994</v>
       </c>
-      <c r="D40" s="170"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="D40" s="169"/>
+      <c r="E40" s="345"/>
+      <c r="F40" s="345"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
         <v>125</v>
       </c>
-      <c r="C42" s="159">
+      <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
         <v>9.070741417213835</v>
       </c>
@@ -15818,47 +15814,47 @@
       <c r="F46" s="103"/>
     </row>
     <row r="47" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B47" s="164"/>
-      <c r="E47" s="164"/>
-      <c r="F47" s="164"/>
+      <c r="B47" s="163"/>
+      <c r="E47" s="163"/>
+      <c r="F47" s="163"/>
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B48" s="164" t="s">
+      <c r="B48" s="163" t="s">
         <v>170</v>
       </c>
-      <c r="E48" s="164" t="s">
+      <c r="E48" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F48" s="164"/>
+      <c r="F48" s="163"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C49" s="171">
+      <c r="C49" s="170">
         <f>C46</f>
         <v>15</v>
       </c>
-      <c r="D49" s="168"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="D49" s="167"/>
+      <c r="E49" s="345"/>
+      <c r="F49" s="345"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C50" s="169">
+      <c r="C50" s="168">
         <v>-0.2</v>
       </c>
-      <c r="D50" s="169"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="D50" s="168"/>
+      <c r="E50" s="345"/>
+      <c r="F50" s="345"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C51" s="165">
+      <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
         <v>7.2649269878396519</v>
       </c>
@@ -15866,57 +15862,57 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="345"/>
+      <c r="F51" s="345"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C52" s="170">
+      <c r="C52" s="169">
         <v>0.05</v>
       </c>
-      <c r="D52" s="170"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="D52" s="169"/>
+      <c r="E52" s="345"/>
+      <c r="F52" s="345"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B54" s="164" t="s">
+      <c r="B54" s="163" t="s">
         <v>350</v>
       </c>
-      <c r="E54" s="164" t="s">
+      <c r="E54" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F54" s="164"/>
+      <c r="F54" s="163"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C55" s="171">
+      <c r="C55" s="170">
         <f>C46</f>
         <v>15</v>
       </c>
-      <c r="D55" s="168"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="D55" s="167"/>
+      <c r="E55" s="345"/>
+      <c r="F55" s="345"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C56" s="169">
+      <c r="C56" s="168">
         <v>0.05</v>
       </c>
-      <c r="D56" s="169"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="D56" s="168"/>
+      <c r="E56" s="345"/>
+      <c r="F56" s="345"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C57" s="165">
+      <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
         <v>10.155837771544068</v>
       </c>
@@ -15924,25 +15920,25 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="345"/>
+      <c r="F57" s="345"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C58" s="170">
+      <c r="C58" s="169">
         <v>0.05</v>
       </c>
-      <c r="D58" s="170"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="D58" s="169"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="159">
+      <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
         <v>9.0347055134616365</v>
       </c>
@@ -15953,7 +15949,7 @@
       <c r="E60" s="103" t="s">
         <v>325</v>
       </c>
-      <c r="F60" s="321">
+      <c r="F60" s="319">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
@@ -15971,7 +15967,7 @@
       <c r="B63" s="112" t="s">
         <v>333</v>
       </c>
-      <c r="E63" s="290" t="s">
+      <c r="E63" s="288" t="s">
         <v>343</v>
       </c>
     </row>
@@ -15979,11 +15975,11 @@
       <c r="B64" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C64" s="171">
+      <c r="C64" s="170">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
-      <c r="E64" s="289" t="s">
+      <c r="E64" s="287" t="s">
         <v>344</v>
       </c>
     </row>
@@ -15995,7 +15991,7 @@
         <v>-7.3000000000000001E-3</v>
       </c>
       <c r="D65" s="155"/>
-      <c r="E65" s="289" t="s">
+      <c r="E65" s="287" t="s">
         <v>345</v>
       </c>
     </row>
@@ -16003,15 +15999,15 @@
       <c r="B66" s="103" t="s">
         <v>107</v>
       </c>
-      <c r="C66" s="165">
+      <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
         <v>9.0321281164495559</v>
       </c>
-      <c r="D66" s="165" t="str">
+      <c r="D66" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="289" t="s">
+      <c r="E66" s="287" t="s">
         <v>346</v>
       </c>
     </row>
@@ -16019,7 +16015,7 @@
       <c r="B68" s="112" t="s">
         <v>320</v>
       </c>
-      <c r="E68" s="290" t="s">
+      <c r="E68" s="288" t="s">
         <v>347</v>
       </c>
     </row>
@@ -16027,7 +16023,7 @@
       <c r="B69" s="103" t="s">
         <v>334</v>
       </c>
-      <c r="C69" s="281" t="str">
+      <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>Y</v>
       </c>
@@ -16037,11 +16033,11 @@
       <c r="B70" s="103" t="s">
         <v>322</v>
       </c>
-      <c r="C70" s="281" t="str">
+      <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
-      <c r="E70" s="289" t="s">
+      <c r="E70" s="287" t="s">
         <v>323</v>
       </c>
     </row>
@@ -16049,24 +16045,24 @@
       <c r="B71" s="103" t="s">
         <v>321</v>
       </c>
-      <c r="C71" s="281" t="str">
+      <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="289"/>
+      <c r="E71" s="287"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
         <v>312</v>
       </c>
-      <c r="C72" s="280" t="str">
+      <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
         <v>391</v>
       </c>
-      <c r="F72" s="349">
+      <c r="F72" s="337">
         <f>BS!D89/C60</f>
         <v>0.62612608991135499</v>
       </c>
@@ -16086,10 +16082,10 @@
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B76" s="283" t="s">
+      <c r="B76" s="281" t="s">
         <v>326</v>
       </c>
-      <c r="C76" s="282">
+      <c r="C76" s="280">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -16099,7 +16095,7 @@
       <c r="B77" s="103" t="s">
         <v>116</v>
       </c>
-      <c r="C77" s="178">
+      <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
         <v>0.57999999999999996</v>
       </c>
@@ -16117,7 +16113,7 @@
       <c r="B80" s="152" t="s">
         <v>328</v>
       </c>
-      <c r="C80" s="172">
+      <c r="C80" s="171">
         <f>Thesis!C121</f>
         <v>0.2</v>
       </c>
@@ -16159,9 +16155,9 @@
       <c r="E83" s="150" t="s">
         <v>131</v>
       </c>
-      <c r="F83" s="270">
-        <f>(C83/C60-1)</f>
-        <v>-0.28606673541699057</v>
+      <c r="F83" s="337">
+        <f>(1-C83/C60)</f>
+        <v>0.28606673541699057</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16176,7 +16172,7 @@
       <c r="B86" s="152" t="s">
         <v>329</v>
       </c>
-      <c r="C86" s="274">
+      <c r="C86" s="272">
         <f>Market_Price</f>
         <v>7.9</v>
       </c>
@@ -16189,7 +16185,7 @@
       <c r="B87" s="103" t="s">
         <v>327</v>
       </c>
-      <c r="C87" s="273">
+      <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.11614149089878545</v>
       </c>
@@ -16198,42 +16194,42 @@
       <c r="B88" s="103"/>
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="330" t="s">
+      <c r="E89" s="328" t="s">
         <v>362</v>
       </c>
-      <c r="F89" s="327"/>
+      <c r="F89" s="325"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="326"/>
+      <c r="H89" s="324"/>
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="323" t="s">
+      <c r="E90" s="321" t="s">
         <v>363</v>
       </c>
-      <c r="F90" s="328" t="s">
+      <c r="F90" s="326" t="s">
         <v>364</v>
       </c>
       <c r="G90" s="2"/>
-      <c r="H90" s="326"/>
+      <c r="H90" s="324"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="324" t="s">
+      <c r="E91" s="322" t="s">
         <v>363</v>
       </c>
-      <c r="F91" s="328" t="s">
+      <c r="F91" s="326" t="s">
         <v>365</v>
       </c>
       <c r="G91" s="2"/>
-      <c r="H91" s="326"/>
+      <c r="H91" s="324"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="325" t="s">
+      <c r="E92" s="323" t="s">
         <v>363</v>
       </c>
-      <c r="F92" s="329" t="s">
+      <c r="F92" s="327" t="s">
         <v>366</v>
       </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="326"/>
+      <c r="H92" s="324"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184A39BD-C96D-4D89-903D-B691DEBEED7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFA27D4-470F-4A46-99E2-A69A6F5D3E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -46,9 +46,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="392">
   <si>
     <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Reporting Currency:</t>
   </si>
   <si>
     <t>Exchange Rate:</t>
@@ -1570,10 +1567,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Categorize the investment</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asset Play</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1603,10 +1596,6 @@
   </si>
   <si>
     <t>Total Non-FCF Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Type of Investment</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1663,10 +1652,6 @@
   </si>
   <si>
     <t>Negative Growth</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Investment Type:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2006,6 +1991,22 @@
   </si>
   <si>
     <t>The Non-FCF Value is of the Expected Value, at</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reporting Currency:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Classification:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Classification</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type of Company</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3376,20 +3377,20 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3695,22 +3696,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C1" s="44">
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="290" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F1" s="291" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="253" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3734,24 +3735,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="50">
         <v>7.9</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -3767,7 +3768,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3777,7 +3778,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3803,24 +3804,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
-        <v>286</v>
-      </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="B12" s="339" t="s">
+        <v>285</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>335</v>
+        <v>389</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3830,17 +3831,17 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>388</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="50">
         <v>1</v>
@@ -3853,16 +3854,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C19" s="255">
         <v>0.2</v>
@@ -3879,7 +3880,7 @@
         <v>6.4501768017717804</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E20" s="320">
         <v>3</v>
@@ -3887,7 +3888,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
@@ -3902,7 +3903,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -3911,26 +3912,26 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
-        <v>236</v>
-      </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="B25" s="339" t="s">
+        <v>235</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
-        <v>382</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="B26" s="340" t="s">
+        <v>378</v>
+      </c>
+      <c r="C26" s="340"/>
+      <c r="D26" s="340"/>
+      <c r="E26" s="340"/>
+      <c r="F26" s="340"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
@@ -3938,17 +3939,17 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
-        <v>238</v>
-      </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="B29" s="338" t="s">
+        <v>237</v>
+      </c>
+      <c r="C29" s="338"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
@@ -3964,17 +3965,17 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
-        <v>240</v>
-      </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="B32" s="338" t="s">
+        <v>239</v>
+      </c>
+      <c r="C32" s="338"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="338"/>
+      <c r="F32" s="338"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
@@ -3987,7 +3988,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
@@ -3999,17 +4000,17 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
-        <v>243</v>
-      </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="B36" s="338" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36" s="338"/>
+      <c r="D36" s="338"/>
+      <c r="E36" s="338"/>
+      <c r="F36" s="338"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
@@ -4021,17 +4022,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
-        <v>247</v>
-      </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="B39" s="338" t="s">
+        <v>246</v>
+      </c>
+      <c r="C39" s="338"/>
+      <c r="D39" s="338"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C40" s="330">
         <f>Normalized_FCF!C48</f>
@@ -4046,7 +4047,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C41" s="330">
         <f>Normalized_FCF!C47</f>
@@ -4061,7 +4062,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
@@ -4074,12 +4075,12 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
@@ -4091,17 +4092,17 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
-        <v>248</v>
-      </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="B47" s="338" t="s">
+        <v>247</v>
+      </c>
+      <c r="C47" s="338"/>
+      <c r="D47" s="338"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
@@ -4113,17 +4114,17 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
-        <v>381</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="B50" s="338" t="s">
+        <v>377</v>
+      </c>
+      <c r="C50" s="342"/>
+      <c r="D50" s="342"/>
+      <c r="E50" s="342"/>
+      <c r="F50" s="342"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4135,26 +4136,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
-        <v>386</v>
-      </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="B53" s="339" t="s">
+        <v>382</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
-        <v>268</v>
-      </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="B54" s="339" t="s">
+        <v>267</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
@@ -4167,7 +4168,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B57" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
@@ -4180,7 +4181,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
@@ -4189,7 +4190,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
@@ -4198,7 +4199,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4211,31 +4212,31 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
-        <v>303</v>
-      </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="B63" s="338" t="s">
+        <v>302</v>
+      </c>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
-        <v>259</v>
-      </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="B64" s="340" t="s">
+        <v>258</v>
+      </c>
+      <c r="C64" s="340"/>
+      <c r="D64" s="340"/>
+      <c r="E64" s="340"/>
+      <c r="F64" s="340"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C67" s="318">
         <v>0.08</v>
@@ -4243,31 +4244,31 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D68" s="293" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="293" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C70" s="269">
         <f>SUM(C67:C69)</f>
@@ -4278,26 +4279,26 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="338" t="s">
-        <v>387</v>
-      </c>
-      <c r="C72" s="338"/>
-      <c r="D72" s="338"/>
-      <c r="E72" s="338"/>
-      <c r="F72" s="338"/>
+      <c r="B72" s="339" t="s">
+        <v>383</v>
+      </c>
+      <c r="C72" s="339"/>
+      <c r="D72" s="339"/>
+      <c r="E72" s="339"/>
+      <c r="F72" s="339"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
-        <v>388</v>
-      </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="B73" s="339" t="s">
+        <v>384</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C75" s="269">
         <v>0</v>
@@ -4305,7 +4306,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C76" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4318,7 +4319,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A78" s="253" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4330,36 +4331,36 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="338" t="s">
-        <v>261</v>
-      </c>
-      <c r="C80" s="338"/>
-      <c r="D80" s="338"/>
-      <c r="E80" s="338"/>
-      <c r="F80" s="338"/>
+      <c r="B80" s="339" t="s">
+        <v>260</v>
+      </c>
+      <c r="C80" s="339"/>
+      <c r="D80" s="339"/>
+      <c r="E80" s="339"/>
+      <c r="F80" s="339"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="338" t="s">
-        <v>389</v>
-      </c>
-      <c r="C84" s="338"/>
-      <c r="D84" s="338"/>
-      <c r="E84" s="338"/>
-      <c r="F84" s="338"/>
+      <c r="B84" s="339" t="s">
+        <v>385</v>
+      </c>
+      <c r="C84" s="339"/>
+      <c r="D84" s="339"/>
+      <c r="E84" s="339"/>
+      <c r="F84" s="339"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C85" s="191">
         <f>Valuation_Model!C7</f>
@@ -4372,7 +4373,7 @@
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C86" s="254">
         <f>C85*C28*Exchange_Rate/Common_Shares</f>
@@ -4385,12 +4386,12 @@
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="47" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C89" s="191">
         <f>BS!C66</f>
@@ -4403,7 +4404,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C90" s="191">
         <f>Valuation_Model!C8</f>
@@ -4416,7 +4417,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C91" s="254">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
@@ -4429,12 +4430,12 @@
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C94" s="191">
         <f>Valuation_Model!C9</f>
@@ -4447,7 +4448,7 @@
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C95" s="254">
         <f>C94*C28*Exchange_Rate/Common_Shares</f>
@@ -4459,17 +4460,17 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="338" t="s">
-        <v>267</v>
-      </c>
-      <c r="C97" s="338"/>
-      <c r="D97" s="338"/>
-      <c r="E97" s="338"/>
-      <c r="F97" s="338"/>
+      <c r="B97" s="339" t="s">
+        <v>266</v>
+      </c>
+      <c r="C97" s="339"/>
+      <c r="D97" s="339"/>
+      <c r="E97" s="339"/>
+      <c r="F97" s="339"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C99" s="254">
         <f>Valuation_Model!C12</f>
@@ -4482,7 +4483,7 @@
     </row>
     <row r="101" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A101" s="253" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B101" s="36"/>
       <c r="C101" s="36"/>
@@ -4491,29 +4492,29 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="340" t="s">
-        <v>369</v>
-      </c>
-      <c r="C103" s="340"/>
-      <c r="D103" s="340"/>
-      <c r="E103" s="340"/>
-      <c r="F103" s="340"/>
+      <c r="B103" s="338" t="s">
+        <v>365</v>
+      </c>
+      <c r="C103" s="338"/>
+      <c r="D103" s="338"/>
+      <c r="E103" s="338"/>
+      <c r="F103" s="338"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C105" s="266" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D105" s="266" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E105" s="266" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F105" s="266" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
@@ -4628,7 +4629,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B112" s="241" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C112" s="247">
         <f>Scenarios!C60</f>
@@ -4641,7 +4642,7 @@
     </row>
     <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="343" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C114" s="343"/>
       <c r="D114" s="343"/>
@@ -4650,7 +4651,7 @@
     </row>
     <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A116" s="253" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -4659,22 +4660,22 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="339" t="s">
-        <v>275</v>
-      </c>
-      <c r="C118" s="339"/>
-      <c r="D118" s="339"/>
-      <c r="E118" s="339"/>
-      <c r="F118" s="339"/>
+      <c r="B118" s="341" t="s">
+        <v>274</v>
+      </c>
+      <c r="C118" s="341"/>
+      <c r="D118" s="341"/>
+      <c r="E118" s="341"/>
+      <c r="F118" s="341"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B120" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C120" s="257">
         <f>E20</f>
@@ -4683,7 +4684,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C121" s="256">
         <f>C19</f>
@@ -4692,7 +4693,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="242" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C122" s="243">
         <f>Scenarios!C77</f>
@@ -4705,7 +4706,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B124" s="240" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
@@ -4730,7 +4731,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B127" s="82" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C127" s="245">
         <f>Scenarios!C83</f>
@@ -4743,7 +4744,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B128" s="244" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C128" s="94">
         <f>Scenarios!F83</f>
@@ -4752,12 +4753,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4773,6 +4768,12 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4856,7 +4857,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -4872,7 +4873,7 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="109">
         <v>1000000</v>
@@ -4880,7 +4881,7 @@
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B4" s="32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="193">
         <v>8765</v>
@@ -4900,7 +4901,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="193">
         <v>5344</v>
@@ -4920,7 +4921,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="193">
         <v>1084</v>
@@ -4940,7 +4941,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="194"/>
       <c r="D7" s="192"/>
@@ -4956,7 +4957,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" s="193"/>
       <c r="D8" s="184"/>
@@ -4972,7 +4973,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C9" s="193">
         <v>639</v>
@@ -4992,7 +4993,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C10" s="193"/>
       <c r="D10" s="184"/>
@@ -5008,7 +5009,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C11" s="193"/>
       <c r="D11" s="184"/>
@@ -5024,7 +5025,7 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="193">
         <v>43</v>
@@ -5044,7 +5045,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C13" s="193">
         <v>2340</v>
@@ -5064,7 +5065,7 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="193">
         <v>519</v>
@@ -5084,7 +5085,7 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="195">
         <v>4251</v>
@@ -5104,7 +5105,7 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="193">
         <v>-151</v>
@@ -5124,13 +5125,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" s="184">
         <v>160</v>
@@ -5150,7 +5151,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" s="184">
         <v>69</v>
@@ -5170,7 +5171,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" s="184">
         <v>910</v>
@@ -5211,13 +5212,13 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="186"/>
       <c r="D25" s="184">
@@ -5235,7 +5236,7 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="186"/>
       <c r="D26" s="184">
@@ -5253,7 +5254,7 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="185">
         <v>14028</v>
@@ -5273,7 +5274,7 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="185">
         <v>166316</v>
@@ -5293,7 +5294,7 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C29" s="184"/>
       <c r="D29" s="184"/>
@@ -5309,13 +5310,13 @@
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" s="9"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="184"/>
       <c r="D32" s="184"/>
@@ -5331,7 +5332,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -5347,12 +5348,12 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B36" s="32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
@@ -5401,7 +5402,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -5450,7 +5451,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
@@ -5499,7 +5500,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -5548,7 +5549,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="70" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -5597,7 +5598,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
@@ -5646,7 +5647,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -5695,7 +5696,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -5744,7 +5745,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -5793,7 +5794,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -5842,7 +5843,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -5891,7 +5892,7 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -5940,7 +5941,7 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -5989,12 +5990,12 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -6043,7 +6044,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6092,12 +6093,12 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="178" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6146,7 +6147,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C56" s="191">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6195,7 +6196,7 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C57" s="191">
         <f>IF(C$4="","",C11)</f>
@@ -6244,7 +6245,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -6293,13 +6294,13 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
@@ -6348,7 +6349,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
@@ -6397,7 +6398,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
@@ -6446,7 +6447,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C64" s="75">
         <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C22)</f>
@@ -6495,7 +6496,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="93" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -6750,7 +6751,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
@@ -6766,13 +6767,13 @@
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B74" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C74" s="9"/>
     </row>
     <row r="75" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B75" s="26" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75" s="78">
         <f>IF(C$4="","",C78+C79)</f>
@@ -6821,7 +6822,7 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="95" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
@@ -6855,7 +6856,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C77" s="74">
         <f t="shared" si="39"/>
@@ -6889,7 +6890,7 @@
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B78" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C78" s="58">
         <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
@@ -6938,7 +6939,7 @@
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C79" s="58">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C28)</f>
@@ -7030,7 +7031,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1" s="102">
         <v>45473</v>
@@ -7046,7 +7047,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7057,27 +7058,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="209" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="210" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="209" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" s="210" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>190</v>
-      </c>
       <c r="G3" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H3" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="19">
         <v>8029</v>
@@ -7087,7 +7088,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G4" s="19">
         <v>45665</v>
@@ -7098,7 +7099,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -7108,7 +7109,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="19">
         <v>2014</v>
@@ -7119,7 +7120,7 @@
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="19">
         <v>9844</v>
@@ -7129,7 +7130,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G6" s="19">
         <v>156</v>
@@ -7140,7 +7141,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" s="19">
         <v>5466</v>
@@ -7150,7 +7151,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -7161,7 +7162,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -7171,7 +7172,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -7182,7 +7183,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="19">
         <v>0</v>
@@ -7192,7 +7193,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -7203,7 +7204,7 @@
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="19">
         <v>10</v>
@@ -7215,7 +7216,7 @@
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="19">
         <v>0</v>
@@ -7227,7 +7228,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
@@ -7238,7 +7239,7 @@
         <v>13028</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
@@ -7256,27 +7257,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C14" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D14" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G14" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H14" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C15" s="19">
         <v>2757</v>
@@ -7285,7 +7286,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -7296,7 +7297,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -7305,7 +7306,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G16" s="19">
         <v>1373</v>
@@ -7316,7 +7317,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="19">
         <v>67668</v>
@@ -7325,7 +7326,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G17" s="19">
         <v>13024</v>
@@ -7336,7 +7337,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -7345,7 +7346,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G18" s="19">
         <v>23696</v>
@@ -7356,7 +7357,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" s="19">
         <v>1284</v>
@@ -7365,7 +7366,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -7376,7 +7377,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -7385,7 +7386,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -7396,7 +7397,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" s="19">
         <v>0</v>
@@ -7405,7 +7406,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -7416,7 +7417,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" s="19">
         <v>10</v>
@@ -7428,7 +7429,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" s="19">
         <v>0</v>
@@ -7440,7 +7441,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
@@ -7451,7 +7452,7 @@
         <v>41841</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
@@ -7464,30 +7465,30 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C26" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F26" s="211" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G26" s="212" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H26" s="213" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="19">
         <v>967</v>
       </c>
       <c r="F27" s="214" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
@@ -7500,13 +7501,13 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="19">
         <v>37</v>
       </c>
       <c r="F28" s="216" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G28" s="184">
         <v>519</v>
@@ -7515,13 +7516,13 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="19">
         <v>0</v>
       </c>
       <c r="F29" s="217" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -7534,13 +7535,13 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
       </c>
       <c r="F30" s="214" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
@@ -7550,14 +7551,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
         <v>1004</v>
       </c>
       <c r="F31" s="217" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G31" s="218">
         <f>C31+C40</f>
@@ -7567,14 +7568,14 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
         <v>8048</v>
       </c>
       <c r="F32" s="219" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G32" s="220">
         <f>G35+G40</f>
@@ -7587,7 +7588,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="85" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" s="86">
         <v>9052</v>
@@ -7600,24 +7601,24 @@
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="223" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G34" s="224" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H34" s="225" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C35" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F35" s="226" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G35" s="220">
         <f>C12+C24</f>
@@ -7630,13 +7631,13 @@
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C36" s="19">
         <v>832</v>
       </c>
       <c r="F36" s="217" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G36" s="218">
         <f>C4+C15</f>
@@ -7646,13 +7647,13 @@
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C37" s="19">
         <v>27</v>
       </c>
       <c r="F37" s="217" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G37" s="218">
         <f>C6</f>
@@ -7662,13 +7663,13 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C38" s="19">
         <v>1230</v>
       </c>
       <c r="F38" s="217" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G38" s="218">
         <f>C7+C17</f>
@@ -7678,13 +7679,13 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C39" s="19">
         <v>0</v>
       </c>
       <c r="F39" s="217" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
@@ -7697,14 +7698,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
         <v>2089</v>
       </c>
       <c r="F40" s="226" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G40" s="220">
         <f>G12+G24</f>
@@ -7717,14 +7718,14 @@
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
         <v>2748</v>
       </c>
       <c r="F41" s="217" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G41" s="218">
         <f>C70</f>
@@ -7737,13 +7738,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="86">
         <v>4837</v>
       </c>
       <c r="F42" s="228" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G42" s="229">
         <f>C82</f>
@@ -7756,7 +7757,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="81" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -7767,21 +7768,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C45" s="267" t="s">
+        <v>140</v>
+      </c>
+      <c r="D45" s="209" t="s">
         <v>287</v>
       </c>
-      <c r="C45" s="267" t="s">
-        <v>141</v>
-      </c>
-      <c r="D45" s="209" t="s">
-        <v>288</v>
-      </c>
       <c r="F45" s="294" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C46" s="191">
         <f>G29</f>
@@ -7813,20 +7814,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="161" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C49" s="268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D49" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="289"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
@@ -7840,7 +7841,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C51" s="208"/>
       <c r="D51" s="94">
@@ -7854,19 +7855,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="161" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C53" s="268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D53" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F53" s="289"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
@@ -7880,7 +7881,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
@@ -7897,19 +7898,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="161" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C57" s="268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D57" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F57" s="289"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C58" s="101"/>
       <c r="D58" s="23">
@@ -7920,7 +7921,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C59" s="101"/>
       <c r="D59" s="94">
@@ -7934,19 +7935,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="161" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C61" s="268" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D61" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F61" s="289"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -7957,12 +7958,12 @@
         <v>3.1154705020769802E-3</v>
       </c>
       <c r="F62" s="289" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="81" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -7973,21 +7974,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C65" s="267" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F65" s="294" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="108" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -7998,12 +7999,12 @@
         <v>41505.820259237436</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="108" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -8013,7 +8014,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -8023,7 +8024,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8033,7 +8034,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
@@ -8046,19 +8047,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="292" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C72" s="267" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D72" s="209" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F72" s="289"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
@@ -8071,7 +8072,7 @@
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="295" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C74" s="296">
         <f>-$C$66/C73</f>
@@ -8082,12 +8083,12 @@
         <v>92.682867505381196</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C75" s="300"/>
       <c r="D75" s="299">
@@ -8095,12 +8096,12 @@
         <v>6173.1797407625618</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="297" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C76" s="298"/>
       <c r="D76" s="335">
@@ -8108,7 +8109,7 @@
         <v>12</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8116,19 +8117,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C78" s="267" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D78" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F78" s="289"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8142,7 +8143,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8156,7 +8157,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8170,7 +8171,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
@@ -8184,7 +8185,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8195,15 +8196,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D85" s="276" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8220,7 +8221,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8237,7 +8238,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="274" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
@@ -8254,7 +8255,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
@@ -8302,7 +8303,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -8355,12 +8356,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -8378,7 +8379,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
@@ -8392,7 +8393,7 @@
     <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="196">
         <f>G4</f>
@@ -8449,7 +8450,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="197">
         <f>C25</f>
@@ -8504,7 +8505,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="187">
         <f>C4+C5</f>
@@ -8559,7 +8560,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="197">
         <f>C35</f>
@@ -8614,7 +8615,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8" s="198">
         <f>C6+C7</f>
@@ -8671,7 +8672,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
@@ -8726,7 +8727,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" s="197">
         <f>-C4*C78</f>
@@ -8781,7 +8782,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C11" s="199">
         <f>C63</f>
@@ -8838,7 +8839,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" s="197">
         <f>C50</f>
@@ -8893,7 +8894,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
@@ -8948,7 +8949,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -9003,7 +9004,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
@@ -9060,7 +9061,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
@@ -9117,7 +9118,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="197">
         <f>-C4*C85</f>
@@ -9125,7 +9126,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="308" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9143,14 +9144,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C18" s="197">
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="308" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9168,7 +9169,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
@@ -9244,12 +9245,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9267,7 +9268,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
@@ -9288,7 +9289,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C23" s="203">
         <f>-C4*C28</f>
@@ -9345,7 +9346,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" s="197">
         <f>-C4*C29</f>
@@ -9402,7 +9403,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="187">
         <f>C23+C24</f>
@@ -9463,14 +9464,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E27" s="309"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:H28)</f>
@@ -9478,7 +9479,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="307" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9538,7 +9539,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="307" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9589,7 +9590,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
@@ -9648,21 +9649,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E32" s="309"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C33" s="204">
         <f>AVERAGE(G33:H33)</f>
         <v>-1106.5</v>
       </c>
       <c r="E33" s="307" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9712,7 +9713,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
@@ -9720,7 +9721,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="307" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -9771,7 +9772,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" s="187">
         <f>C33+C34</f>
@@ -9832,7 +9833,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E37" s="309"/>
     </row>
@@ -9955,7 +9956,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
@@ -10014,21 +10015,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E42" s="309"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C43" s="303">
         <v>0.24</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="306" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10082,12 +10083,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10105,14 +10106,14 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E46" s="309"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
@@ -10167,7 +10168,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
@@ -10222,7 +10223,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="331" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C49" s="332">
         <f>BS!$C$66*C53</f>
@@ -10279,7 +10280,7 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10"/>
       <c r="B50" s="71" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
@@ -10338,23 +10339,23 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="73" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E52" s="309"/>
       <c r="G52" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C53" s="89">
         <v>0.03</v>
       </c>
       <c r="E53" s="306" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10374,14 +10375,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C54" s="84">
         <f>G54</f>
         <v>1.3902360168121564E-2</v>
       </c>
       <c r="E54" s="306" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10401,7 +10402,7 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -10460,17 +10461,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="65" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E57" s="309"/>
       <c r="G57" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C58" s="197">
         <f>BS!$C79*C66</f>
@@ -10525,7 +10526,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C59" s="197">
         <f>BS!$C68*C67</f>
@@ -10580,7 +10581,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C60" s="197">
         <f>BS!$C81*C68</f>
@@ -10635,7 +10636,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
@@ -10690,13 +10691,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C62" s="304">
         <v>0</v>
       </c>
       <c r="E62" s="307" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -10746,7 +10747,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C63" s="187">
         <f>C61+C62</f>
@@ -10805,17 +10806,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="99" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E65" s="309"/>
       <c r="G65" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C66" s="180">
         <f>G66</f>
@@ -10840,7 +10841,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C67" s="180">
         <f>G67</f>
@@ -10865,7 +10866,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="108" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C68" s="180">
         <f>G68</f>
@@ -10890,7 +10891,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C69" s="72">
         <f>C61/BS!C70</f>
@@ -10920,12 +10921,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -10943,7 +10944,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="73" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="27"/>
@@ -10964,7 +10965,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C73" s="79">
         <f>ABS(C5/C$4)</f>
@@ -11021,7 +11022,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C74" s="80">
         <f>ABS(C6/C$4)</f>
@@ -11078,7 +11079,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C75" s="79">
         <f>ABS(C7/C$4)</f>
@@ -11135,7 +11136,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C76" s="80">
         <f>ABS(C8/C$4)</f>
@@ -11192,7 +11193,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
@@ -11249,7 +11250,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C78" s="90">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -11257,7 +11258,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="307" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -11308,7 +11309,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C79" s="80">
         <f>ABS(C11/C$4)</f>
@@ -11365,7 +11366,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
@@ -11422,7 +11423,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
       <c r="B81" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
@@ -11479,7 +11480,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
@@ -11594,7 +11595,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
@@ -11651,7 +11652,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C85" s="305">
         <v>0</v>
@@ -11677,7 +11678,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C86" s="79">
         <v>0</v>
@@ -11701,7 +11702,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
@@ -11762,7 +11763,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
       <c r="B89" s="65" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E89" s="309"/>
     </row>
@@ -11881,7 +11882,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
@@ -11936,7 +11937,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -11995,7 +11996,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
       <c r="B95" s="161" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C95" s="63"/>
       <c r="D95" s="27"/>
@@ -12016,7 +12017,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C96" s="79">
         <f>C4/G4-1</f>
@@ -12073,7 +12074,7 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10"/>
       <c r="B97" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
@@ -12133,12 +12134,12 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C99" s="54"/>
       <c r="D99" s="56"/>
       <c r="E99" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="37"/>
@@ -12156,17 +12157,17 @@
     <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="10"/>
       <c r="B100" s="65" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E100" s="309"/>
       <c r="G100" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C101" s="205">
         <f>BS!G32</f>
@@ -12223,7 +12224,7 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="95" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C102" s="206">
         <f>BS!C4</f>
@@ -12280,7 +12281,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
       <c r="B103" s="95" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
@@ -12337,7 +12338,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C104" s="205">
         <f>BS!G30</f>
@@ -12394,7 +12395,7 @@
     <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C105" s="205">
         <f>BS!G27</f>
@@ -12455,14 +12456,14 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
       <c r="B107" s="93" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
       <c r="E107" s="310"/>
       <c r="F107" s="26"/>
       <c r="G107" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
@@ -12478,7 +12479,7 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
@@ -12535,7 +12536,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C109" s="97">
         <f>C103/C$4</f>
@@ -12592,7 +12593,7 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C110" s="97">
         <f>BS!$G$38/C$4</f>
@@ -12623,7 +12624,7 @@
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
       <c r="B112" s="93" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C112" s="55"/>
       <c r="D112" s="55"/>
@@ -12677,7 +12678,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C113" s="23">
         <f>C81</f>
@@ -12731,7 +12732,7 @@
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C114" s="42">
         <f>C4/C101</f>
@@ -12785,7 +12786,7 @@
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C115" s="15">
         <f>C101/C105</f>
@@ -12842,7 +12843,7 @@
     <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10"/>
       <c r="B116" s="71" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C116" s="105">
         <f>C8/C105</f>
@@ -12918,12 +12919,12 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A118" s="10"/>
       <c r="B118" s="54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C118" s="54"/>
       <c r="D118" s="56"/>
       <c r="E118" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F118" s="56"/>
       <c r="G118" s="37"/>
@@ -12941,7 +12942,7 @@
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10"/>
       <c r="B119" s="182" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C119" s="183"/>
       <c r="D119" s="27"/>
@@ -13020,7 +13021,7 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="10"/>
       <c r="B121" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13789,32 +13790,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="134" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="112" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H3" s="124"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="103" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
@@ -13825,7 +13826,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F4" s="138">
         <f>Thesis!C75</f>
@@ -13835,7 +13836,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="233" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5" s="234">
         <f>Thesis!C70</f>
@@ -13846,7 +13847,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="153" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -13857,14 +13858,14 @@
         <v>HKD</v>
       </c>
       <c r="E6" s="344" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F6" s="344"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C7" s="232">
         <f>BS!G31</f>
@@ -13880,7 +13881,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
@@ -13896,7 +13897,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="233" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C9" s="235">
         <f>BS!H42</f>
@@ -13912,7 +13913,7 @@
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
@@ -13926,7 +13927,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="236" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
@@ -13940,7 +13941,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
@@ -13957,7 +13958,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B14" s="36" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -13967,13 +13968,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B15" s="123" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="165">
         <f>Scenarios!C65</f>
@@ -13983,7 +13984,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17" s="166">
         <f>Scenarios!C64</f>
@@ -13993,7 +13994,7 @@
     </row>
     <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="157" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
@@ -14010,19 +14011,19 @@
     </row>
     <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="132" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="132" t="s">
         <v>112</v>
       </c>
-      <c r="C20" s="132" t="s">
+      <c r="D20" s="132" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" s="132" t="s">
         <v>113</v>
       </c>
-      <c r="D20" s="132" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" s="132" t="s">
+      <c r="F20" s="133" t="s">
         <v>114</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>115</v>
       </c>
       <c r="H20" s="124"/>
     </row>
@@ -14688,7 +14689,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B51" s="130" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -14711,7 +14712,7 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C52" s="118"/>
       <c r="E52" s="131" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
@@ -14725,7 +14726,7 @@
     </row>
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B54" s="123" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C54" s="140"/>
       <c r="D54" s="140"/>
@@ -14896,7 +14897,7 @@
     </row>
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B63" s="123" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C63" s="118"/>
       <c r="D63" s="118"/>
@@ -15115,19 +15116,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="175" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C73" s="175" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D73" s="175" t="s">
+        <v>116</v>
+      </c>
+      <c r="E73" s="176" t="s">
         <v>117</v>
       </c>
-      <c r="E73" s="176" t="s">
-        <v>118</v>
-      </c>
       <c r="F73" s="176" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -15252,20 +15253,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C80" s="159" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81" s="159" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82" s="159" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.35">
@@ -15317,20 +15318,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I2" s="284"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="163" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H3" s="282">
         <v>0</v>
@@ -15342,14 +15343,14 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="156" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="124">
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="159" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F4" s="159"/>
       <c r="H4" s="282">
@@ -15371,14 +15372,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="163" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="282">
@@ -15391,7 +15392,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15416,7 +15417,7 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="103" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
@@ -15438,7 +15439,7 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="103" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
@@ -15471,7 +15472,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="163" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E11" s="346"/>
       <c r="F11" s="346"/>
@@ -15485,7 +15486,7 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" s="162" t="e">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15504,7 +15505,7 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="152" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="162" t="e">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15522,7 +15523,7 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="103" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="162" t="e">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15533,7 +15534,7 @@
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -15542,21 +15543,21 @@
     </row>
     <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="112" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C18" s="154">
         <v>10</v>
       </c>
       <c r="E18" s="346" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F18" s="347"/>
     </row>
@@ -15566,14 +15567,14 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E20" s="347"/>
       <c r="F20" s="347"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
@@ -15588,7 +15589,7 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
@@ -15603,16 +15604,16 @@
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E24" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F24" s="163"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C25" s="170">
         <f>C18</f>
@@ -15624,7 +15625,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C26" s="168">
         <v>0</v>
@@ -15635,7 +15636,7 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
@@ -15650,7 +15651,7 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C28" s="169">
         <v>0.55000000000000004</v>
@@ -15661,16 +15662,16 @@
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E30" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F30" s="163"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C31" s="170">
         <f>C18</f>
@@ -15682,7 +15683,7 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C32" s="168">
         <v>-0.05</v>
@@ -15693,7 +15694,7 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
@@ -15708,7 +15709,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C34" s="169">
         <v>0.2</v>
@@ -15719,16 +15720,16 @@
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E36" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F36" s="163"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C37" s="170">
         <f>C18</f>
@@ -15740,7 +15741,7 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C38" s="168">
         <v>0.02</v>
@@ -15751,7 +15752,7 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
@@ -15766,7 +15767,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C40" s="171">
         <f>1-C28-C34</f>
@@ -15778,7 +15779,7 @@
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -15791,7 +15792,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B44" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -15800,12 +15801,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B45" s="112" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C46" s="154">
         <v>15</v>
@@ -15820,16 +15821,16 @@
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B48" s="163" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E48" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F48" s="163"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C49" s="170">
         <f>C46</f>
@@ -15841,7 +15842,7 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C50" s="168">
         <v>-0.2</v>
@@ -15852,7 +15853,7 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
@@ -15867,7 +15868,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C52" s="169">
         <v>0.05</v>
@@ -15878,16 +15879,16 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E54" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F54" s="163"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C55" s="170">
         <f>C46</f>
@@ -15899,7 +15900,7 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C56" s="168">
         <v>0.05</v>
@@ -15910,7 +15911,7 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
@@ -15925,7 +15926,7 @@
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C58" s="169">
         <v>0.05</v>
@@ -15936,7 +15937,7 @@
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -15947,7 +15948,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F60" s="319">
         <f>Thesis!E20</f>
@@ -15956,7 +15957,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>311</v>
+        <v>390</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -15965,39 +15966,39 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C64" s="170">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C65" s="155">
         <v>-7.3000000000000001E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
@@ -16008,20 +16009,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>320</v>
+        <v>391</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16031,19 +16032,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16053,14 +16054,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F72" s="337">
         <f>BS!D89/C60</f>
@@ -16069,7 +16070,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B74" s="36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -16078,12 +16079,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B75" s="112" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16093,7 +16094,7 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="103" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
@@ -16106,12 +16107,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C80" s="171">
         <f>Thesis!C121</f>
@@ -16120,7 +16121,7 @@
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -16132,7 +16133,7 @@
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
@@ -16142,7 +16143,7 @@
     </row>
     <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
@@ -16153,7 +16154,7 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="150" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F83" s="337">
         <f>(1-C83/C60)</f>
@@ -16165,12 +16166,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
@@ -16183,7 +16184,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -16195,7 +16196,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="328" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="F89" s="325"/>
       <c r="G89" s="2"/>
@@ -16203,30 +16204,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="321" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F90" s="326" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="324"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="322" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F91" s="326" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="324"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="323" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F92" s="327" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="324"/>

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFA27D4-470F-4A46-99E2-A69A6F5D3E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FBBDB9-106A-4663-A0E2-7E49C719F80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="40860" yWindow="3390" windowWidth="12690" windowHeight="7650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3341,9 +3341,6 @@
     <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3376,6 +3373,9 @@
     <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3882,7 +3882,7 @@
       <c r="D20" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E20" s="320">
+      <c r="E20" s="337">
         <v>3</v>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       <c r="B40" s="47" t="s">
         <v>379</v>
       </c>
-      <c r="C40" s="330">
+      <c r="C40" s="329">
         <f>Normalized_FCF!C48</f>
         <v>185.19539222287685</v>
       </c>
@@ -4042,14 +4042,14 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E40" s="329"/>
-      <c r="F40" s="329"/>
+      <c r="E40" s="328"/>
+      <c r="F40" s="328"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
         <v>380</v>
       </c>
-      <c r="C41" s="330">
+      <c r="C41" s="329">
         <f>Normalized_FCF!C47</f>
         <v>-43</v>
       </c>
@@ -4057,8 +4057,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E41" s="329"/>
-      <c r="F41" s="329"/>
+      <c r="E41" s="328"/>
+      <c r="F41" s="328"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
@@ -8104,7 +8104,7 @@
         <v>356</v>
       </c>
       <c r="C76" s="298"/>
-      <c r="D76" s="335">
+      <c r="D76" s="334">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,IF(D74&gt;36,12,6),2))</f>
         <v>12</v>
       </c>
@@ -10175,104 +10175,104 @@
         <v>185.19539222287685</v>
       </c>
       <c r="E48" s="309"/>
-      <c r="G48" s="336">
+      <c r="G48" s="335">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
         <v>302.96861497481899</v>
       </c>
-      <c r="H48" s="336">
+      <c r="H48" s="335">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
         <v>180.07798132735766</v>
       </c>
-      <c r="I48" s="336" t="str">
+      <c r="I48" s="335" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J48" s="336" t="str">
+      <c r="J48" s="335" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="K48" s="336" t="str">
+      <c r="K48" s="335" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="L48" s="336" t="str">
+      <c r="L48" s="335" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="336" t="str">
+      <c r="M48" s="335" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="336" t="str">
+      <c r="N48" s="335" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="336" t="str">
+      <c r="O48" s="335" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="336" t="str">
+      <c r="P48" s="335" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="336" t="str">
+      <c r="Q48" s="335" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
-      <c r="B49" s="331" t="s">
+      <c r="B49" s="330" t="s">
         <v>381</v>
       </c>
-      <c r="C49" s="332">
+      <c r="C49" s="331">
         <f>BS!$C$66*C53</f>
         <v>1430.37</v>
       </c>
-      <c r="D49" s="333"/>
-      <c r="E49" s="334"/>
-      <c r="F49" s="333"/>
-      <c r="G49" s="332">
+      <c r="D49" s="332"/>
+      <c r="E49" s="333"/>
+      <c r="F49" s="332"/>
+      <c r="G49" s="331">
         <f>Data!C52</f>
         <v>2340</v>
       </c>
-      <c r="H49" s="332">
+      <c r="H49" s="331">
         <f>Data!D52</f>
         <v>1390.845307</v>
       </c>
-      <c r="I49" s="332" t="str">
+      <c r="I49" s="331" t="str">
         <f>Data!E52</f>
         <v/>
       </c>
-      <c r="J49" s="332" t="str">
+      <c r="J49" s="331" t="str">
         <f>Data!F52</f>
         <v/>
       </c>
-      <c r="K49" s="332" t="str">
+      <c r="K49" s="331" t="str">
         <f>Data!G52</f>
         <v/>
       </c>
-      <c r="L49" s="332" t="str">
+      <c r="L49" s="331" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="332" t="str">
+      <c r="M49" s="331" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="332" t="str">
+      <c r="N49" s="331" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="332" t="str">
+      <c r="O49" s="331" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="332" t="str">
+      <c r="P49" s="331" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="332" t="str">
+      <c r="Q49" s="331" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -16063,7 +16063,7 @@
       <c r="E72" s="138" t="s">
         <v>387</v>
       </c>
-      <c r="F72" s="337">
+      <c r="F72" s="336">
         <f>BS!D89/C60</f>
         <v>0.62612608991135499</v>
       </c>
@@ -16156,7 +16156,7 @@
       <c r="E83" s="150" t="s">
         <v>130</v>
       </c>
-      <c r="F83" s="337">
+      <c r="F83" s="336">
         <f>(1-C83/C60)</f>
         <v>0.28606673541699057</v>
       </c>
@@ -16195,42 +16195,42 @@
       <c r="B88" s="103"/>
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="328" t="s">
+      <c r="E89" s="327" t="s">
         <v>358</v>
       </c>
-      <c r="F89" s="325"/>
+      <c r="F89" s="324"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="324"/>
+      <c r="H89" s="323"/>
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="321" t="s">
+      <c r="E90" s="320" t="s">
         <v>359</v>
       </c>
-      <c r="F90" s="326" t="s">
+      <c r="F90" s="325" t="s">
         <v>360</v>
       </c>
       <c r="G90" s="2"/>
-      <c r="H90" s="324"/>
+      <c r="H90" s="323"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="322" t="s">
+      <c r="E91" s="321" t="s">
         <v>359</v>
       </c>
-      <c r="F91" s="326" t="s">
+      <c r="F91" s="325" t="s">
         <v>361</v>
       </c>
       <c r="G91" s="2"/>
-      <c r="H91" s="324"/>
+      <c r="H91" s="323"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="323" t="s">
+      <c r="E92" s="322" t="s">
         <v>359</v>
       </c>
-      <c r="F92" s="327" t="s">
+      <c r="F92" s="326" t="s">
         <v>362</v>
       </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="324"/>
+      <c r="H92" s="323"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FBBDB9-106A-4663-A0E2-7E49C719F80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681BC566-16DA-4431-BF4D-9A24498F0CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="40860" yWindow="3390" windowWidth="12690" windowHeight="7650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="393">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1743,10 +1743,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1x for stable businesses, 2x for for volatile ones</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Operating Expenses Multiple (months)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2007,6 +2003,14 @@
   </si>
   <si>
     <t>Type of Company</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Variable + Fixed Costs &amp; Dividends</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1x for stable businesses, 2x for for volatile ones, 6x for cash hoarders</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3738,10 +3742,10 @@
         <v>344</v>
       </c>
       <c r="C5" s="48" t="s">
+        <v>366</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>367</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3821,7 +3825,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3831,7 +3835,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>42</v>
@@ -3877,7 +3881,7 @@
       </c>
       <c r="C20" s="258">
         <f>C127</f>
-        <v>6.4501768017717804</v>
+        <v>6.4883606756817951</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>335</v>
@@ -3892,7 +3896,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11614149089878545</v>
+        <v>0.1185224959199922</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3922,7 +3926,7 @@
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="340" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C26" s="340"/>
       <c r="D26" s="340"/>
@@ -4032,11 +4036,11 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C40" s="329">
         <f>Normalized_FCF!C48</f>
-        <v>185.19539222287685</v>
+        <v>163.69305155463843</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4047,7 +4051,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C41" s="329">
         <f>Normalized_FCF!C47</f>
@@ -4066,7 +4070,7 @@
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
-        <v>142.19539222287685</v>
+        <v>120.69305155463843</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4106,7 +4110,7 @@
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
-        <v>-809.52375635047554</v>
+        <v>-804.36319459009837</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4115,7 +4119,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="338" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C50" s="342"/>
       <c r="D50" s="342"/>
@@ -4137,7 +4141,7 @@
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="339" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C53" s="339"/>
       <c r="D53" s="339"/>
@@ -4159,7 +4163,7 @@
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
-        <v>2807.968614974819</v>
+        <v>2772.792068232593</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4172,7 +4176,7 @@
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
-        <v>2540.6221871727971</v>
+        <v>2524.2804082649359</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4185,7 +4189,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>3.9354193616452378E-2</v>
+        <v>3.9101059744590508E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4280,7 +4284,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="339" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C72" s="339"/>
       <c r="D72" s="339"/>
@@ -4289,7 +4293,7 @@
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="339" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C73" s="339"/>
       <c r="D73" s="339"/>
@@ -4310,7 +4314,7 @@
       </c>
       <c r="C76" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>3.4544236618885975</v>
+        <v>3.432204133136278</v>
       </c>
       <c r="D76" s="1" t="str">
         <f>Market_currency</f>
@@ -4351,7 +4355,7 @@
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="339" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C84" s="339"/>
       <c r="D84" s="339"/>
@@ -4408,7 +4412,7 @@
       </c>
       <c r="C90" s="191">
         <f>Valuation_Model!C8</f>
-        <v>41505.820259237436</v>
+        <v>42222.564948178719</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4421,7 +4425,7 @@
       </c>
       <c r="C91" s="254">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>5.0791030441342784</v>
+        <v>5.1668117102618574</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Market_currency</f>
@@ -4474,7 +4478,7 @@
       </c>
       <c r="C99" s="254">
         <f>Valuation_Model!C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4493,7 +4497,7 @@
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B103" s="338" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C103" s="338"/>
       <c r="D103" s="338"/>
@@ -4532,7 +4536,7 @@
       </c>
       <c r="E106" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>10.16 HKD</v>
+        <v>10.21 HKD</v>
       </c>
       <c r="F106" s="265">
         <f>Valuation_Model!F74</f>
@@ -4554,7 +4558,7 @@
       </c>
       <c r="E107" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>9.34 HKD</v>
+        <v>9.41 HKD</v>
       </c>
       <c r="F107" s="252">
         <f>Valuation_Model!F75</f>
@@ -4576,7 +4580,7 @@
       </c>
       <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>9.11 HKD</v>
+        <v>9.18 HKD</v>
       </c>
       <c r="F108" s="252">
         <f>Valuation_Model!F76</f>
@@ -4598,7 +4602,7 @@
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>8.62 HKD</v>
+        <v>8.69 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F77</f>
@@ -4620,7 +4624,7 @@
       </c>
       <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>7.26 HKD</v>
+        <v>7.34 HKD</v>
       </c>
       <c r="F110" s="252">
         <f>Valuation_Model!F78</f>
@@ -4633,7 +4637,7 @@
       </c>
       <c r="C112" s="247">
         <f>Scenarios!C60</f>
-        <v>9.0347055134616365</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="D112" s="242" t="str">
         <f>Market_currency</f>
@@ -4642,7 +4646,7 @@
     </row>
     <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="343" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C114" s="343"/>
       <c r="D114" s="343"/>
@@ -4726,7 +4730,7 @@
       </c>
       <c r="C126" s="246">
         <f>Scenarios!C82</f>
-        <v>5.2284175425125214</v>
+        <v>5.2666014164225361</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -4735,7 +4739,7 @@
       </c>
       <c r="C127" s="245">
         <f>Scenarios!C83</f>
-        <v>6.4501768017717804</v>
+        <v>6.4883606756817951</v>
       </c>
       <c r="D127" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4748,7 +4752,7 @@
       </c>
       <c r="C128" s="94">
         <f>Scenarios!F83</f>
-        <v>0.28606673541699057</v>
+        <v>0.28704717576043881</v>
       </c>
     </row>
   </sheetData>
@@ -7996,7 +8000,7 @@
       </c>
       <c r="D66" s="191">
         <f>C66-D75</f>
-        <v>41505.820259237436</v>
+        <v>42222.564948178719</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>230</v>
@@ -8062,25 +8066,28 @@
         <v>349</v>
       </c>
       <c r="C73" s="191">
-        <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
-        <v>-535.66666666666663</v>
+        <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
+        <v>-930.64086357333326</v>
       </c>
       <c r="D73" s="191">
-        <f>(Normalized_FCF!C25+Normalized_FCF!C35)/12</f>
-        <v>-514.43164506354685</v>
+        <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
+        <v>-909.4058419702136</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="295" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C74" s="296">
         <f>-$C$66/C73</f>
-        <v>89.008711885500944</v>
+        <v>51.232437631128107</v>
       </c>
       <c r="D74" s="296">
         <f>-$C$66/D73</f>
-        <v>92.682867505381196</v>
+        <v>52.428737313479523</v>
       </c>
       <c r="F74" s="289" t="s">
         <v>351</v>
@@ -8093,23 +8100,23 @@
       <c r="C75" s="300"/>
       <c r="D75" s="299">
         <f>MAX(-D73*D76,G5)</f>
-        <v>6173.1797407625618</v>
+        <v>5456.4350518212814</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="297" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C76" s="298"/>
       <c r="D76" s="334">
-        <f>IF(D74&lt;=3,1,IF(D74&gt;18,IF(D74&gt;36,12,6),2))</f>
-        <v>12</v>
+        <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
+        <v>6</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8225,11 +8232,11 @@
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>41505.820259237436</v>
+        <v>42222.564948178719</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>5.0791030441342784</v>
+        <v>5.1668117102618574</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8259,11 +8266,11 @@
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>46227.220259237438</v>
+        <v>46943.96494817872</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>5.6568648366442948</v>
+        <v>5.7445735027718738</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -8843,16 +8850,16 @@
       </c>
       <c r="C12" s="197">
         <f>C50</f>
-        <v>142.19539222287685</v>
+        <v>120.69305155463843</v>
       </c>
       <c r="E12" s="309"/>
       <c r="G12" s="197">
         <f>G50</f>
-        <v>259.96861497481899</v>
+        <v>224.79206823259295</v>
       </c>
       <c r="H12" s="197">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>139.30261332735768</v>
+        <v>118.39443599706225</v>
       </c>
       <c r="I12" s="197" t="str">
         <f t="shared" si="6"/>
@@ -8898,16 +8905,16 @@
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
-        <v>3373.015651460315</v>
+        <v>3351.5133107920765</v>
       </c>
       <c r="E13" s="309"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3326.968614974819</v>
+        <v>3291.792068232593</v>
       </c>
       <c r="H13" s="187">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>5416.3026133273579</v>
+        <v>5395.3944359970619</v>
       </c>
       <c r="I13" s="187" t="str">
         <f t="shared" si="7"/>
@@ -8953,7 +8960,7 @@
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-809.52375635047554</v>
+        <v>-804.36319459009837</v>
       </c>
       <c r="E14" s="309"/>
       <c r="G14" s="197">
@@ -9065,18 +9072,18 @@
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
-        <v>2540.6221871727971</v>
+        <v>2524.2804082649359</v>
       </c>
       <c r="D16" s="62"/>
       <c r="E16" s="317"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2807.968614974819</v>
+        <v>2772.792068232593</v>
       </c>
       <c r="H16" s="187">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>4524.4677853273579</v>
+        <v>4503.5596079970619</v>
       </c>
       <c r="I16" s="187" t="str">
         <f t="shared" si="8"/>
@@ -9126,7 +9133,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="308" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9151,7 +9158,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="308" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9173,18 +9180,18 @@
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
-        <v>2540.6221871727971</v>
+        <v>2524.2804082649359</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="306"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2807.968614974819</v>
+        <v>2772.792068232593</v>
       </c>
       <c r="H19" s="189">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>4524.4677853273579</v>
+        <v>4503.5596079970619</v>
       </c>
       <c r="I19" s="189" t="str">
         <f t="shared" si="9"/>
@@ -9479,7 +9486,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="307" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9539,7 +9546,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="307" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9663,7 +9670,7 @@
         <v>-1106.5</v>
       </c>
       <c r="E33" s="307" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9721,7 +9728,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="307" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -10029,16 +10036,16 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="306" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.16038474464748129</v>
+        <v>0.16214736506972799</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.16161958688679046</v>
+        <v>0.16225651803742283</v>
       </c>
       <c r="I43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10168,20 +10175,20 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
-        <v>185.19539222287685</v>
+        <v>163.69305155463843</v>
       </c>
       <c r="E48" s="309"/>
       <c r="G48" s="335">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>302.96861497481899</v>
+        <v>267.79206823259295</v>
       </c>
       <c r="H48" s="335">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>180.07798132735766</v>
+        <v>159.16980399706225</v>
       </c>
       <c r="I48" s="335" t="str">
         <f t="shared" si="19"/>
@@ -10223,7 +10230,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="330" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C49" s="331">
         <f>BS!$C$66*C53</f>
@@ -10284,16 +10291,16 @@
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
-        <v>142.19539222287685</v>
+        <v>120.69305155463843</v>
       </c>
       <c r="E50" s="309"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>259.96861497481899</v>
+        <v>224.79206823259295</v>
       </c>
       <c r="H50" s="187">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>139.30261332735768</v>
+        <v>118.39443599706225</v>
       </c>
       <c r="I50" s="187" t="str">
         <f t="shared" si="20"/>
@@ -10355,7 +10362,7 @@
         <v>0.03</v>
       </c>
       <c r="E53" s="306" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10382,7 +10389,7 @@
         <v>1.3902360168121564E-2</v>
       </c>
       <c r="E54" s="306" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10697,7 +10704,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="307" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -11258,7 +11265,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="307" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -11370,18 +11377,18 @@
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
-        <v>1.6223090955262618E-2</v>
+        <v>1.3769886087237698E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="306"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>2.9659853391308499E-2</v>
+        <v>2.5646556558196573E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1724822264738463E-2</v>
+        <v>9.9650228092805528E-3</v>
       </c>
       <c r="I80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -11427,18 +11434,18 @@
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
-        <v>0.3848277982270753</v>
+        <v>0.38237459335905039</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="306"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.37957428579290575</v>
+        <v>0.37556098895979384</v>
       </c>
       <c r="H81" s="66">
         <f t="shared" si="32"/>
-        <v>0.4558793547115022</v>
+        <v>0.45411955525604425</v>
       </c>
       <c r="I81" s="66" t="str">
         <f t="shared" si="32"/>
@@ -11484,7 +11491,7 @@
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
-        <v>9.2358671574498064E-2</v>
+        <v>9.1769902406172096E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="306"/>
@@ -11599,18 +11606,18 @@
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
-        <v>0.2898599186734509</v>
+        <v>0.28799548297375194</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="306"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.32036150769821098</v>
+        <v>0.31634821086509901</v>
       </c>
       <c r="H84" s="66">
         <f t="shared" si="35"/>
-        <v>0.38081540150890986</v>
+        <v>0.3790556020534519</v>
       </c>
       <c r="I84" s="66" t="str">
         <f t="shared" si="35"/>
@@ -11706,18 +11713,18 @@
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
-        <v>0.2898599186734509</v>
+        <v>0.28799548297375194</v>
       </c>
       <c r="D87" s="77"/>
       <c r="E87" s="306"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.32036150769821098</v>
+        <v>0.31634821086509901</v>
       </c>
       <c r="H87" s="66">
         <f t="shared" si="36"/>
-        <v>0.38081540150890986</v>
+        <v>0.3790556020534519</v>
       </c>
       <c r="I87" s="66" t="str">
         <f t="shared" si="36"/>
@@ -11886,16 +11893,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>1.8655628478763795</v>
+        <v>1.8776401969295582</v>
       </c>
       <c r="E92" s="309"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>1.6879427845465798</v>
+        <v>1.7093565785843898</v>
       </c>
       <c r="H92" s="174">
         <f t="shared" si="38"/>
-        <v>1.0475685954159291</v>
+        <v>1.0524320260941227</v>
       </c>
       <c r="I92" s="174" t="str">
         <f t="shared" si="38"/>
@@ -12078,14 +12085,14 @@
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>1.3840538284081383E-2</v>
+        <v>1.8142471128666626E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="306"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-0.38574912583568022</v>
+        <v>-0.38988852302060206</v>
       </c>
       <c r="H97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -12682,16 +12689,16 @@
       </c>
       <c r="C113" s="23">
         <f>C81</f>
-        <v>0.3848277982270753</v>
+        <v>0.38237459335905039</v>
       </c>
       <c r="E113" s="309"/>
       <c r="G113" s="23">
         <f t="shared" ref="G113:Q113" si="45">G81</f>
-        <v>0.37957428579290575</v>
+        <v>0.37556098895979384</v>
       </c>
       <c r="H113" s="23">
         <f t="shared" si="45"/>
-        <v>0.4558793547115022</v>
+        <v>0.45411955525604425</v>
       </c>
       <c r="I113" s="23" t="str">
         <f t="shared" si="45"/>
@@ -12968,18 +12975,18 @@
       </c>
       <c r="C120" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.31089812956997381</v>
+        <v>0.308898371982265</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="306"/>
       <c r="F120" s="27"/>
       <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.34361354265677985</v>
+        <v>0.33930895827500729</v>
       </c>
       <c r="H120" s="181">
         <f t="shared" si="49"/>
-        <v>0.55366302745045104</v>
+        <v>0.55110447574704324</v>
       </c>
       <c r="I120" s="181" t="str">
         <f t="shared" si="49"/>
@@ -13025,18 +13032,18 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.9354193616452378E-2</v>
+        <v>3.9101059744590508E-2</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="306"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>4.3495385146427826E-2</v>
+        <v>4.2950501047469274E-2</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>7.0083927525373541E-2</v>
+        <v>6.9760060221144712E-2</v>
       </c>
       <c r="I121" s="79" t="str">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
@@ -13819,7 +13826,7 @@
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
-        <v>2540.6221871727971</v>
+        <v>2524.2804082649359</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -13851,7 +13858,7 @@
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>28229.135413031079</v>
+        <v>28047.560091832624</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -13885,7 +13892,7 @@
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
-        <v>41505.820259237436</v>
+        <v>42222.564948178719</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -13917,7 +13924,7 @@
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
-        <v>74456.355672268517</v>
+        <v>74991.525040011329</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -13945,7 +13952,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -13998,7 +14005,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>9.0321281164495559</v>
+        <v>9.0981264288878361</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14033,7 +14040,7 @@
       </c>
       <c r="C21" s="127">
         <f>C4*(1+D21)</f>
-        <v>2522.0756452064356</v>
+        <v>2505.8531612846018</v>
       </c>
       <c r="D21" s="142">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14045,7 +14052,7 @@
       </c>
       <c r="F21" s="129">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2313.8308671618674</v>
+        <v>2298.947854389543</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -14055,7 +14062,7 @@
       </c>
       <c r="C22" s="127">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2503.6644929964286</v>
+        <v>2487.5604332072244</v>
       </c>
       <c r="D22" s="142">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14067,7 +14074,7 @@
       </c>
       <c r="F22" s="129">
         <f t="shared" si="1"/>
-        <v>2107.2843136069591</v>
+        <v>2093.7298486720174</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -14077,7 +14084,7 @@
       </c>
       <c r="C23" s="127">
         <f t="shared" si="2"/>
-        <v>2485.3877421975549</v>
+        <v>2469.4012420448116</v>
       </c>
       <c r="D23" s="142">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14089,7 +14096,7 @@
       </c>
       <c r="F23" s="129">
         <f t="shared" si="1"/>
-        <v>1919.1753560712189</v>
+        <v>1906.830844749277</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -14099,7 +14106,7 @@
       </c>
       <c r="C24" s="127">
         <f t="shared" si="2"/>
-        <v>2467.2444116795127</v>
+        <v>2451.3746129778847</v>
       </c>
       <c r="D24" s="142">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14111,7 +14118,7 @@
       </c>
       <c r="F24" s="129">
         <f t="shared" si="1"/>
-        <v>1747.8581430934851</v>
+        <v>1736.6155775987222</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -14121,7 +14128,7 @@
       </c>
       <c r="C25" s="127">
         <f t="shared" si="2"/>
-        <v>2449.2335274742522</v>
+        <v>2433.4795783031459</v>
       </c>
       <c r="D25" s="142">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14133,7 +14140,7 @@
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>1591.8337418797271</v>
+        <v>1581.5947558552762</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -14143,7 +14150,7 @@
       </c>
       <c r="C26" s="127">
         <f t="shared" si="2"/>
-        <v>2431.3541227236901</v>
+        <v>2415.7151773815331</v>
       </c>
       <c r="D26" s="142">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14155,7 +14162,7 @@
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>1449.7370234532154</v>
+        <v>1440.4120313188373</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -14165,7 +14172,7 @@
       </c>
       <c r="C27" s="127">
         <f t="shared" si="2"/>
-        <v>2413.6052376278076</v>
+        <v>2398.0804565866479</v>
       </c>
       <c r="D27" s="142">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -14177,7 +14184,7 @@
       </c>
       <c r="F27" s="129">
         <f t="shared" si="1"/>
-        <v>1320.3247185156031</v>
+        <v>1311.8321316423944</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -14187,7 +14194,7 @@
       </c>
       <c r="C28" s="127">
         <f t="shared" si="2"/>
-        <v>2395.9859193931243</v>
+        <v>2380.5744692535654</v>
       </c>
       <c r="D28" s="142">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -14199,7 +14206,7 @@
       </c>
       <c r="F28" s="129">
         <f t="shared" si="1"/>
-        <v>1202.464539514164</v>
+        <v>1194.7300523682613</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -14209,7 +14216,7 @@
       </c>
       <c r="C29" s="127">
         <f t="shared" si="2"/>
-        <v>2378.4952221815547</v>
+        <v>2363.1962756280145</v>
       </c>
       <c r="D29" s="142">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -14221,7 +14228,7 @@
       </c>
       <c r="F29" s="129">
         <f t="shared" si="1"/>
-        <v>1095.1252737391842</v>
+        <v>1088.0812137485991</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -14231,7 +14238,7 @@
       </c>
       <c r="C30" s="127">
         <f t="shared" si="2"/>
-        <v>2361.1322070596293</v>
+        <v>2345.9449428159301</v>
       </c>
       <c r="D30" s="142">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -14243,7 +14250,7 @@
       </c>
       <c r="F30" s="129">
         <f t="shared" si="1"/>
-        <v>997.36776077145691</v>
+        <v>990.95249622773781</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -14693,7 +14700,7 @@
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>28023.062724515952</v>
+        <v>27842.812903162245</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -14705,7 +14712,7 @@
       </c>
       <c r="F51" s="129">
         <f t="shared" si="1"/>
-        <v>11837.244537151286</v>
+        <v>11761.105064670463</v>
       </c>
       <c r="H51" s="124"/>
     </row>
@@ -14716,7 +14723,7 @@
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
-        <v>27582.246274958168</v>
+        <v>27404.831871241127</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -14737,7 +14744,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="137">
         <f>F52</f>
-        <v>27582.246274958168</v>
+        <v>27404.831871241127</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
@@ -14767,19 +14774,19 @@
       </c>
       <c r="B56" s="127">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>20193.592912324937</v>
+        <v>20063.703772414767</v>
       </c>
       <c r="C56" s="127">
-        <v>25999.545497513922</v>
+        <v>25832.311334807477</v>
       </c>
       <c r="D56" s="127">
-        <v>28229.135413031072</v>
+        <v>28047.560091832616</v>
       </c>
       <c r="E56" s="127">
-        <v>29169.388943080252</v>
+        <v>28981.765727242848</v>
       </c>
       <c r="F56" s="127">
-        <v>30635.527109280756</v>
+        <v>30438.473405950401</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -14788,19 +14795,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="127">
-        <v>16230.163670980823</v>
+        <v>16125.768083282397</v>
       </c>
       <c r="C57" s="127">
-        <v>24207.81034217267</v>
+        <v>24052.100970487048</v>
       </c>
       <c r="D57" s="127">
-        <v>28229.135413031065</v>
+        <v>28047.560091832609</v>
       </c>
       <c r="E57" s="127">
-        <v>30120.811948539595</v>
+        <v>29927.068993812412</v>
       </c>
       <c r="F57" s="127">
-        <v>33324.021051394309</v>
+        <v>33109.67442910144</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -14809,19 +14816,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="127">
-        <v>13140.890829194326</v>
+        <v>13056.366048742024</v>
       </c>
       <c r="C58" s="127">
-        <v>22409.643349910642</v>
+        <v>22265.500140079126</v>
       </c>
       <c r="D58" s="127">
-        <v>28229.135413031065</v>
+        <v>28047.560091832613</v>
       </c>
       <c r="E58" s="127">
-        <v>31246.686937184058</v>
+        <v>31045.702134284722</v>
       </c>
       <c r="F58" s="127">
-        <v>36765.0666593145</v>
+        <v>36528.586558529481</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -14830,19 +14837,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="127">
-        <v>11023.754834817611</v>
+        <v>10952.84788723816</v>
       </c>
       <c r="C59" s="127">
-        <v>20922.286661863869</v>
+        <v>20787.710421208605</v>
       </c>
       <c r="D59" s="127">
-        <v>28229.135413031061</v>
+        <v>28047.560091832613</v>
       </c>
       <c r="E59" s="127">
-        <v>32342.609628836006</v>
+        <v>32134.575636798087</v>
       </c>
       <c r="F59" s="127">
-        <v>40406.434113458046</v>
+        <v>40146.532024878717</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -14851,19 +14858,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="127">
-        <v>9624.4797447577112</v>
+        <v>9562.5732082856211</v>
       </c>
       <c r="C60" s="127">
-        <v>19795.345519715876</v>
+        <v>19668.01798494067</v>
       </c>
       <c r="D60" s="127">
-        <v>28229.135413031061</v>
+        <v>28047.560091832605</v>
       </c>
       <c r="E60" s="127">
-        <v>33316.212150828149</v>
+        <v>33101.915756911323</v>
       </c>
       <c r="F60" s="127">
-        <v>43938.451096733559</v>
+        <v>43655.830383979846</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -14872,19 +14879,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="127">
-        <v>8710.0885982663494</v>
+        <v>8654.0636045229312</v>
       </c>
       <c r="C61" s="127">
-        <v>18982.314945066366</v>
+        <v>18860.216981993442</v>
       </c>
       <c r="D61" s="127">
-        <v>28229.135413031065</v>
+        <v>28047.560091832605</v>
       </c>
       <c r="E61" s="127">
-        <v>34136.509865863532</v>
+        <v>33916.937156575856</v>
       </c>
       <c r="F61" s="127">
-        <v>47200.695522272283</v>
+        <v>46897.091415208801</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -14934,23 +14941,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -14961,23 +14968,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>8.1279722281473283</v>
+        <v>8.1997862481313746</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>8.8384516564624356</v>
+        <v>8.9056957337786056</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>9.1112884985328915</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>9.2263481344322198</v>
+        <v>9.2910971857212523</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>9.4057607270893442</v>
+        <v>9.4693557614854704</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -14988,23 +14995,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>7.6429639714934581</v>
+        <v>7.7178976594622748</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>8.6191954792579697</v>
+        <v>8.6878498551971095</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>9.3427745886766083</v>
+        <v>9.4067747622364397</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>9.7347540509229198</v>
+        <v>9.7962329359020277</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15015,23 +15022,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>7.2649269878396519</v>
+        <v>7.3422922836394369</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>8.3991522326189099</v>
+        <v>8.4692219697655933</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>9.480548882653272</v>
+        <v>9.5436628650026503</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>10.155837771544068</v>
+        <v>10.214608163659173</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15042,23 +15049,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>7.0058512291454997</v>
+        <v>7.0848829509059597</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>8.2171431111321347</v>
+        <v>8.2883835665530903</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>9.614657888198499</v>
+        <v>9.6769092551896243</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>10.601435049362856</v>
+        <v>10.65733927261868</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15069,23 +15076,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>6.8346207288177103</v>
+        <v>6.9147538386526222</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>8.0792383510311669</v>
+        <v>8.1513658368462085</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081488</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>9.7337984690216537</v>
+        <v>9.7952835004904841</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>11.03365101569341</v>
+        <v>11.086775141303123</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15095,23 +15102,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>6.7227258951132729</v>
+        <v>6.8035787344075898</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>7.97974709797594</v>
+        <v>8.0525145309932462</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081488</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>9.8341790083173546</v>
+        <v>9.8950183725208571</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>11.43285468132332</v>
+        <v>11.483411050862937</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15146,7 +15153,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.155837771544068</v>
+        <v>10.214608163659173</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15168,7 +15175,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>9.3427745886766083</v>
+        <v>9.4067747622364397</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15191,7 +15198,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15214,7 +15221,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>8.6191954792579697</v>
+        <v>8.6878498551971095</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15237,7 +15244,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.2649269878396519</v>
+        <v>7.3422922836394369</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15387,7 +15394,7 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>9.6147055134616366</v>
+        <v>9.6806872475781418</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15421,7 +15428,7 @@
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>2807.968614974819</v>
+        <v>2772.792068232593</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15443,7 +15450,7 @@
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
-        <v>2540.6221871727971</v>
+        <v>2524.2804082649359</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -15546,7 +15553,7 @@
         <v>155</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -15557,7 +15564,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="346" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F18" s="347"/>
     </row>
@@ -15593,7 +15600,7 @@
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15640,7 +15647,7 @@
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
@@ -15698,7 +15705,7 @@
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>8.6191954792579697</v>
+        <v>8.6878498551971095</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15756,7 +15763,7 @@
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>9.3427745886766083</v>
+        <v>9.4067747622364397</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15783,7 +15790,7 @@
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>9.070741417213835</v>
+        <v>9.1364913613480141</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15857,7 +15864,7 @@
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>7.2649269878396519</v>
+        <v>7.3422922836394369</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -15915,7 +15922,7 @@
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>10.155837771544068</v>
+        <v>10.214608163659173</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -15941,7 +15948,7 @@
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>9.0347055134616365</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -15957,7 +15964,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16002,7 +16009,7 @@
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>9.0321281164495559</v>
+        <v>9.0981264288878361</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
@@ -16014,7 +16021,7 @@
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E68" s="288" t="s">
         <v>343</v>
@@ -16061,11 +16068,11 @@
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F72" s="336">
         <f>BS!D89/C60</f>
-        <v>0.62612608991135499</v>
+        <v>0.63122414236360114</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16137,7 +16144,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>5.2284175425125214</v>
+        <v>5.2666014164225361</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16147,7 +16154,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>6.4501768017717804</v>
+        <v>6.4883606756817951</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16158,7 +16165,7 @@
       </c>
       <c r="F83" s="336">
         <f>(1-C83/C60)</f>
-        <v>0.28606673541699057</v>
+        <v>0.28704717576043881</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16188,7 +16195,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11614149089878545</v>
+        <v>0.1185224959199922</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
@@ -16196,7 +16203,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="327" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F89" s="324"/>
       <c r="G89" s="2"/>
@@ -16204,30 +16211,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="320" t="s">
+        <v>358</v>
+      </c>
+      <c r="F90" s="325" t="s">
         <v>359</v>
-      </c>
-      <c r="F90" s="325" t="s">
-        <v>360</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="323"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="321" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F91" s="325" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="323"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="322" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F92" s="326" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="323"/>

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681BC566-16DA-4431-BF4D-9A24498F0CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD1AEDB-C055-482C-BE1A-43998D996588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="392">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1707,15 +1707,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Status in Portfolio:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Snowball Scenario</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Held</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2011,6 +2003,10 @@
   </si>
   <si>
     <t>1x for stable businesses, 2x for for volatile ones, 6x for cash hoarders</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Selected:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3279,9 +3275,6 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3381,22 +3374,22 @@
     <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -3410,6 +3403,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3706,11 +3702,11 @@
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="290" t="s">
-        <v>345</v>
-      </c>
-      <c r="F1" s="291" t="s">
-        <v>347</v>
+      <c r="E1" s="347" t="s">
+        <v>391</v>
+      </c>
+      <c r="F1" s="290" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -3742,10 +3738,10 @@
         <v>344</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3808,13 +3804,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
+      <c r="B12" s="337" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="C12" s="337"/>
+      <c r="D12" s="337"/>
+      <c r="E12" s="337"/>
+      <c r="F12" s="337"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3825,7 +3821,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3835,7 +3831,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>42</v>
@@ -3861,7 +3857,7 @@
         <v>59</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -3886,7 +3882,7 @@
       <c r="D20" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E20" s="337">
+      <c r="E20" s="336">
         <v>3</v>
       </c>
     </row>
@@ -3916,22 +3912,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
+      <c r="B25" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="C25" s="337"/>
+      <c r="D25" s="337"/>
+      <c r="E25" s="337"/>
+      <c r="F25" s="337"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="340" t="s">
-        <v>377</v>
-      </c>
-      <c r="C26" s="340"/>
-      <c r="D26" s="340"/>
-      <c r="E26" s="340"/>
-      <c r="F26" s="340"/>
+      <c r="B26" s="341" t="s">
+        <v>375</v>
+      </c>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -3943,13 +3939,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="338" t="s">
+      <c r="B29" s="339" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="338"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3969,13 +3965,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="338" t="s">
+      <c r="B32" s="339" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="338"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="338"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4004,13 +4000,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="338" t="s">
+      <c r="B36" s="339" t="s">
         <v>242</v>
       </c>
-      <c r="C36" s="338"/>
-      <c r="D36" s="338"/>
-      <c r="E36" s="338"/>
-      <c r="F36" s="338"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4026,19 +4022,19 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="338" t="s">
+      <c r="B39" s="339" t="s">
         <v>246</v>
       </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>378</v>
-      </c>
-      <c r="C40" s="329">
+        <v>376</v>
+      </c>
+      <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
         <v>163.69305155463843</v>
       </c>
@@ -4046,14 +4042,14 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E40" s="328"/>
-      <c r="F40" s="328"/>
+      <c r="E40" s="327"/>
+      <c r="F40" s="327"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>379</v>
-      </c>
-      <c r="C41" s="329">
+        <v>377</v>
+      </c>
+      <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
         <v>-43</v>
       </c>
@@ -4061,8 +4057,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E41" s="328"/>
-      <c r="F41" s="328"/>
+      <c r="E41" s="327"/>
+      <c r="F41" s="327"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
@@ -4096,13 +4092,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="338" t="s">
+      <c r="B47" s="339" t="s">
         <v>247</v>
       </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4118,13 +4114,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="338" t="s">
-        <v>376</v>
-      </c>
-      <c r="C50" s="342"/>
-      <c r="D50" s="342"/>
-      <c r="E50" s="342"/>
-      <c r="F50" s="342"/>
+      <c r="B50" s="339" t="s">
+        <v>374</v>
+      </c>
+      <c r="C50" s="340"/>
+      <c r="D50" s="340"/>
+      <c r="E50" s="340"/>
+      <c r="F50" s="340"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4140,22 +4136,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
-        <v>381</v>
-      </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="B53" s="337" t="s">
+        <v>379</v>
+      </c>
+      <c r="C53" s="337"/>
+      <c r="D53" s="337"/>
+      <c r="E53" s="337"/>
+      <c r="F53" s="337"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
+      <c r="B54" s="337" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="C54" s="337"/>
+      <c r="D54" s="337"/>
+      <c r="E54" s="337"/>
+      <c r="F54" s="337"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4216,22 +4212,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="339" t="s">
         <v>302</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="340" t="s">
+      <c r="B64" s="341" t="s">
         <v>258</v>
       </c>
-      <c r="C64" s="340"/>
-      <c r="D64" s="340"/>
-      <c r="E64" s="340"/>
-      <c r="F64" s="340"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4242,7 +4238,7 @@
       <c r="B67" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C67" s="318">
+      <c r="C67" s="317">
         <v>0.08</v>
       </c>
     </row>
@@ -4254,7 +4250,7 @@
         <f>IF(D68="Y",1%,0)</f>
         <v>0.01</v>
       </c>
-      <c r="D68" s="293" t="s">
+      <c r="D68" s="292" t="s">
         <v>306</v>
       </c>
     </row>
@@ -4266,8 +4262,8 @@
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D69" s="293" t="s">
-        <v>353</v>
+      <c r="D69" s="292" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4283,22 +4279,22 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="339" t="s">
-        <v>382</v>
-      </c>
-      <c r="C72" s="339"/>
-      <c r="D72" s="339"/>
-      <c r="E72" s="339"/>
-      <c r="F72" s="339"/>
+      <c r="B72" s="337" t="s">
+        <v>380</v>
+      </c>
+      <c r="C72" s="337"/>
+      <c r="D72" s="337"/>
+      <c r="E72" s="337"/>
+      <c r="F72" s="337"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
-        <v>383</v>
-      </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="B73" s="337" t="s">
+        <v>381</v>
+      </c>
+      <c r="C73" s="337"/>
+      <c r="D73" s="337"/>
+      <c r="E73" s="337"/>
+      <c r="F73" s="337"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
@@ -4335,13 +4331,13 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="339" t="s">
+      <c r="B80" s="337" t="s">
         <v>260</v>
       </c>
-      <c r="C80" s="339"/>
-      <c r="D80" s="339"/>
-      <c r="E80" s="339"/>
-      <c r="F80" s="339"/>
+      <c r="C80" s="337"/>
+      <c r="D80" s="337"/>
+      <c r="E80" s="337"/>
+      <c r="F80" s="337"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4354,13 +4350,13 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="339" t="s">
-        <v>384</v>
-      </c>
-      <c r="C84" s="339"/>
-      <c r="D84" s="339"/>
-      <c r="E84" s="339"/>
-      <c r="F84" s="339"/>
+      <c r="B84" s="337" t="s">
+        <v>382</v>
+      </c>
+      <c r="C84" s="337"/>
+      <c r="D84" s="337"/>
+      <c r="E84" s="337"/>
+      <c r="F84" s="337"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
@@ -4464,13 +4460,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="339" t="s">
+      <c r="B97" s="337" t="s">
         <v>266</v>
       </c>
-      <c r="C97" s="339"/>
-      <c r="D97" s="339"/>
-      <c r="E97" s="339"/>
-      <c r="F97" s="339"/>
+      <c r="C97" s="337"/>
+      <c r="D97" s="337"/>
+      <c r="E97" s="337"/>
+      <c r="F97" s="337"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
@@ -4496,13 +4492,13 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="338" t="s">
-        <v>364</v>
-      </c>
-      <c r="C103" s="338"/>
-      <c r="D103" s="338"/>
-      <c r="E103" s="338"/>
-      <c r="F103" s="338"/>
+      <c r="B103" s="339" t="s">
+        <v>362</v>
+      </c>
+      <c r="C103" s="339"/>
+      <c r="D103" s="339"/>
+      <c r="E103" s="339"/>
+      <c r="F103" s="339"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
@@ -4645,13 +4641,13 @@
       </c>
     </row>
     <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="343" t="s">
-        <v>365</v>
-      </c>
-      <c r="C114" s="343"/>
-      <c r="D114" s="343"/>
-      <c r="E114" s="343"/>
-      <c r="F114" s="343"/>
+      <c r="B114" s="342" t="s">
+        <v>363</v>
+      </c>
+      <c r="C114" s="342"/>
+      <c r="D114" s="342"/>
+      <c r="E114" s="342"/>
+      <c r="F114" s="342"/>
     </row>
     <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A116" s="253" t="s">
@@ -4664,13 +4660,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="341" t="s">
+      <c r="B118" s="338" t="s">
         <v>274</v>
       </c>
-      <c r="C118" s="341"/>
-      <c r="D118" s="341"/>
-      <c r="E118" s="341"/>
-      <c r="F118" s="341"/>
+      <c r="C118" s="338"/>
+      <c r="D118" s="338"/>
+      <c r="E118" s="338"/>
+      <c r="F118" s="338"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
@@ -4757,6 +4753,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4772,12 +4774,6 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4785,7 +4781,7 @@
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
-      <formula1>"Not Held, Held"</formula1>
+      <formula1>"Y, N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
@@ -7087,7 +7083,7 @@
       <c r="C4" s="19">
         <v>8029</v>
       </c>
-      <c r="D4" s="301">
+      <c r="D4" s="300">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -7097,7 +7093,7 @@
       <c r="G4" s="19">
         <v>45665</v>
       </c>
-      <c r="H4" s="301">
+      <c r="H4" s="300">
         <v>0.9</v>
       </c>
     </row>
@@ -7108,7 +7104,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="301">
+      <c r="D5" s="300">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -7118,7 +7114,7 @@
       <c r="G5" s="19">
         <v>2014</v>
       </c>
-      <c r="H5" s="301">
+      <c r="H5" s="300">
         <v>0.7</v>
       </c>
     </row>
@@ -7129,7 +7125,7 @@
       <c r="C6" s="19">
         <v>9844</v>
       </c>
-      <c r="D6" s="301">
+      <c r="D6" s="300">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -7139,7 +7135,7 @@
       <c r="G6" s="19">
         <v>156</v>
       </c>
-      <c r="H6" s="301">
+      <c r="H6" s="300">
         <v>0.6</v>
       </c>
     </row>
@@ -7150,7 +7146,7 @@
       <c r="C7" s="19">
         <v>5466</v>
       </c>
-      <c r="D7" s="301">
+      <c r="D7" s="300">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -7160,7 +7156,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="301">
+      <c r="H7" s="300">
         <v>0.6</v>
       </c>
     </row>
@@ -7171,7 +7167,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="301">
+      <c r="D8" s="300">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -7181,7 +7177,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="301">
+      <c r="H8" s="300">
         <v>0.6</v>
       </c>
     </row>
@@ -7192,7 +7188,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="301">
+      <c r="D9" s="300">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -7202,7 +7198,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="301">
+      <c r="H9" s="300">
         <v>0.6</v>
       </c>
     </row>
@@ -7213,10 +7209,10 @@
       <c r="C10" s="19">
         <v>10</v>
       </c>
-      <c r="D10" s="301">
+      <c r="D10" s="300">
         <v>0.9</v>
       </c>
-      <c r="H10" s="302"/>
+      <c r="H10" s="301"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
@@ -7225,10 +7221,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="301">
+      <c r="D11" s="300">
         <v>0.05</v>
       </c>
-      <c r="H11" s="302"/>
+      <c r="H11" s="301"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
@@ -7286,7 +7282,7 @@
       <c r="C15" s="19">
         <v>2757</v>
       </c>
-      <c r="D15" s="301">
+      <c r="D15" s="300">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -7295,7 +7291,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="301">
+      <c r="H15" s="300">
         <v>0.8</v>
       </c>
     </row>
@@ -7306,7 +7302,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="301">
+      <c r="D16" s="300">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -7315,7 +7311,7 @@
       <c r="G16" s="19">
         <v>1373</v>
       </c>
-      <c r="H16" s="301">
+      <c r="H16" s="300">
         <v>0.6</v>
       </c>
     </row>
@@ -7326,7 +7322,7 @@
       <c r="C17" s="19">
         <v>67668</v>
       </c>
-      <c r="D17" s="301">
+      <c r="D17" s="300">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -7335,7 +7331,7 @@
       <c r="G17" s="19">
         <v>13024</v>
       </c>
-      <c r="H17" s="301">
+      <c r="H17" s="300">
         <v>0.6</v>
       </c>
     </row>
@@ -7346,7 +7342,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="301">
+      <c r="D18" s="300">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -7355,7 +7351,7 @@
       <c r="G18" s="19">
         <v>23696</v>
       </c>
-      <c r="H18" s="301">
+      <c r="H18" s="300">
         <v>0.1</v>
       </c>
     </row>
@@ -7366,7 +7362,7 @@
       <c r="C19" s="19">
         <v>1284</v>
       </c>
-      <c r="D19" s="301">
+      <c r="D19" s="300">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -7375,7 +7371,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="301">
+      <c r="H19" s="300">
         <v>0.1</v>
       </c>
     </row>
@@ -7386,7 +7382,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="301">
+      <c r="D20" s="300">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -7395,7 +7391,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="301">
+      <c r="H20" s="300">
         <v>0.2</v>
       </c>
     </row>
@@ -7406,7 +7402,7 @@
       <c r="C21" s="19">
         <v>0</v>
       </c>
-      <c r="D21" s="301">
+      <c r="D21" s="300">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -7415,7 +7411,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="301">
+      <c r="H21" s="300">
         <v>0.1</v>
       </c>
     </row>
@@ -7426,10 +7422,10 @@
       <c r="C22" s="19">
         <v>10</v>
       </c>
-      <c r="D22" s="301">
+      <c r="D22" s="300">
         <v>0.9</v>
       </c>
-      <c r="H22" s="302"/>
+      <c r="H22" s="301"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
@@ -7438,10 +7434,10 @@
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="301">
+      <c r="D23" s="300">
         <v>0</v>
       </c>
-      <c r="H23" s="302"/>
+      <c r="H23" s="301"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
@@ -7780,7 +7776,7 @@
       <c r="D45" s="209" t="s">
         <v>287</v>
       </c>
-      <c r="F45" s="294" t="s">
+      <c r="F45" s="293" t="s">
         <v>62</v>
       </c>
     </row>
@@ -7986,7 +7982,7 @@
       <c r="D65" s="210" t="s">
         <v>311</v>
       </c>
-      <c r="F65" s="294" t="s">
+      <c r="F65" s="293" t="s">
         <v>62</v>
       </c>
     </row>
@@ -8050,8 +8046,8 @@
       <c r="F71" s="289"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="292" t="s">
-        <v>350</v>
+      <c r="B72" s="291" t="s">
+        <v>348</v>
       </c>
       <c r="C72" s="267" t="s">
         <v>99</v>
@@ -8063,7 +8059,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8074,49 +8070,49 @@
         <v>-909.4058419702136</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="295" t="s">
-        <v>354</v>
-      </c>
-      <c r="C74" s="296">
+      <c r="B74" s="294" t="s">
+        <v>352</v>
+      </c>
+      <c r="C74" s="295">
         <f>-$C$66/C73</f>
         <v>51.232437631128107</v>
       </c>
-      <c r="D74" s="296">
+      <c r="D74" s="295">
         <f>-$C$66/D73</f>
         <v>52.428737313479523</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>352</v>
-      </c>
-      <c r="C75" s="300"/>
-      <c r="D75" s="299">
+        <v>350</v>
+      </c>
+      <c r="C75" s="299"/>
+      <c r="D75" s="298">
         <f>MAX(-D73*D76,G5)</f>
         <v>5456.4350518212814</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="297" t="s">
-        <v>355</v>
-      </c>
-      <c r="C76" s="298"/>
-      <c r="D76" s="334">
+      <c r="B76" s="296" t="s">
+        <v>353</v>
+      </c>
+      <c r="C76" s="297"/>
+      <c r="D76" s="333">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>6</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8393,7 +8389,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="309"/>
+      <c r="E3" s="308"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -8407,7 +8403,7 @@
         <v>8765</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="307"/>
+      <c r="E4" s="306"/>
       <c r="F4" s="57"/>
       <c r="G4" s="186">
         <f>Data!C36</f>
@@ -8463,7 +8459,7 @@
         <f>C25</f>
         <v>-5066.6797407625618</v>
       </c>
-      <c r="E5" s="309"/>
+      <c r="E5" s="308"/>
       <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-5344</v>
@@ -8518,7 +8514,7 @@
         <f>C4+C5</f>
         <v>3698.3202592374382</v>
       </c>
-      <c r="E6" s="309"/>
+      <c r="E6" s="308"/>
       <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
         <v>3421</v>
@@ -8573,7 +8569,7 @@
         <f>C35</f>
         <v>-1106.5</v>
       </c>
-      <c r="E7" s="309"/>
+      <c r="E7" s="308"/>
       <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-1084</v>
@@ -8629,7 +8625,7 @@
         <v>2591.8202592374382</v>
       </c>
       <c r="D8" s="60"/>
-      <c r="E8" s="315"/>
+      <c r="E8" s="314"/>
       <c r="F8" s="60"/>
       <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
@@ -8685,7 +8681,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>159.99999999999997</v>
       </c>
-      <c r="E9" s="309"/>
+      <c r="E9" s="308"/>
       <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>160</v>
@@ -8740,7 +8736,7 @@
         <f>-C4*C78</f>
         <v>-159.99999999999997</v>
       </c>
-      <c r="E10" s="309"/>
+      <c r="E10" s="308"/>
       <c r="G10" s="197">
         <f>Data!C62</f>
         <v>-69</v>
@@ -8796,7 +8792,7 @@
         <v>639</v>
       </c>
       <c r="D11" s="172"/>
-      <c r="E11" s="308"/>
+      <c r="E11" s="307"/>
       <c r="F11" s="172"/>
       <c r="G11" s="189">
         <f>G61</f>
@@ -8852,7 +8848,7 @@
         <f>C50</f>
         <v>120.69305155463843</v>
       </c>
-      <c r="E12" s="309"/>
+      <c r="E12" s="308"/>
       <c r="G12" s="197">
         <f>G50</f>
         <v>224.79206823259295</v>
@@ -8907,7 +8903,7 @@
         <f>SUM(C8:C12)</f>
         <v>3351.5133107920765</v>
       </c>
-      <c r="E13" s="309"/>
+      <c r="E13" s="308"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>3291.792068232593</v>
@@ -8962,7 +8958,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-804.36319459009837</v>
       </c>
-      <c r="E14" s="309"/>
+      <c r="E14" s="308"/>
       <c r="G14" s="197">
         <f>Data!C46</f>
         <v>-519</v>
@@ -9018,7 +9014,7 @@
         <v>-22.869707937042335</v>
       </c>
       <c r="D15" s="61"/>
-      <c r="E15" s="316"/>
+      <c r="E15" s="315"/>
       <c r="F15" s="61"/>
       <c r="G15" s="186">
         <f>Data!C48</f>
@@ -9075,7 +9071,7 @@
         <v>2524.2804082649359</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="317"/>
+      <c r="E16" s="316"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -9132,8 +9128,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="59"/>
-      <c r="E17" s="308" t="s">
-        <v>368</v>
+      <c r="E17" s="307" t="s">
+        <v>366</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9157,8 +9153,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
-      <c r="E18" s="308" t="s">
-        <v>369</v>
+      <c r="E18" s="307" t="s">
+        <v>367</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9183,7 +9179,7 @@
         <v>2524.2804082649359</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="306"/>
+      <c r="E19" s="305"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
@@ -9279,7 +9275,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="306"/>
+      <c r="E22" s="305"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -9303,7 +9299,7 @@
         <v>-5066.6797407625618</v>
       </c>
       <c r="D23" s="59"/>
-      <c r="E23" s="308"/>
+      <c r="E23" s="307"/>
       <c r="F23" s="59"/>
       <c r="G23" s="186">
         <f>Data!C37</f>
@@ -9360,7 +9356,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="306"/>
+      <c r="E24" s="305"/>
       <c r="F24" s="27"/>
       <c r="G24" s="186">
         <f>Data!C40</f>
@@ -9417,7 +9413,7 @@
         <v>-5066.6797407625618</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="314"/>
+      <c r="E25" s="313"/>
       <c r="F25" s="9"/>
       <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -9466,14 +9462,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
-      <c r="E26" s="309"/>
+      <c r="E26" s="308"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
         <v>210</v>
       </c>
-      <c r="E27" s="309"/>
+      <c r="E27" s="308"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
@@ -9485,8 +9481,8 @@
         <v>0.57805815639048053</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="307" t="s">
-        <v>370</v>
+      <c r="E28" s="306" t="s">
+        <v>368</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9545,8 +9541,8 @@
         <v>0</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="307" t="s">
-        <v>370</v>
+      <c r="E29" s="306" t="s">
+        <v>368</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9603,7 +9599,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.57805815639048053</v>
       </c>
-      <c r="E30" s="309"/>
+      <c r="E30" s="308"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.60969766115231028</v>
@@ -9651,14 +9647,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
-      <c r="E31" s="309"/>
+      <c r="E31" s="308"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="309"/>
+      <c r="E32" s="308"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
@@ -9669,8 +9665,8 @@
         <f>AVERAGE(G33:H33)</f>
         <v>-1106.5</v>
       </c>
-      <c r="E33" s="307" t="s">
-        <v>370</v>
+      <c r="E33" s="306" t="s">
+        <v>368</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9727,8 +9723,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="59"/>
-      <c r="E34" s="307" t="s">
-        <v>370</v>
+      <c r="E34" s="306" t="s">
+        <v>368</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -9786,7 +9782,7 @@
         <v>-1106.5</v>
       </c>
       <c r="D35" s="59"/>
-      <c r="E35" s="308"/>
+      <c r="E35" s="307"/>
       <c r="F35" s="59"/>
       <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -9835,14 +9831,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
-      <c r="E36" s="309"/>
+      <c r="E36" s="308"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="E37" s="309"/>
+      <c r="E37" s="308"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
@@ -9855,7 +9851,7 @@
         <v>0.1262407301768397</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="306"/>
+      <c r="E38" s="305"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -9913,7 +9909,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="306"/>
+      <c r="E39" s="305"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -9969,7 +9965,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.1262407301768397</v>
       </c>
-      <c r="E40" s="309"/>
+      <c r="E40" s="308"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.12367370222475756</v>
@@ -10017,26 +10013,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10"/>
-      <c r="E41" s="309"/>
+      <c r="E41" s="308"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="E42" s="309"/>
+      <c r="E42" s="308"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="C43" s="303">
+      <c r="C43" s="302">
         <v>0.24</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="306" t="s">
-        <v>371</v>
+      <c r="E43" s="305" t="s">
+        <v>369</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10115,7 +10111,7 @@
       <c r="B46" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="E46" s="309"/>
+      <c r="E46" s="308"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
@@ -10126,7 +10122,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-43</v>
       </c>
-      <c r="E47" s="309"/>
+      <c r="E47" s="308"/>
       <c r="G47" s="197">
         <f>Data!C51</f>
         <v>-43</v>
@@ -10175,111 +10171,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
         <v>163.69305155463843</v>
       </c>
-      <c r="E48" s="309"/>
-      <c r="G48" s="335">
+      <c r="E48" s="308"/>
+      <c r="G48" s="334">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
         <v>267.79206823259295</v>
       </c>
-      <c r="H48" s="335">
+      <c r="H48" s="334">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
         <v>159.16980399706225</v>
       </c>
-      <c r="I48" s="335" t="str">
+      <c r="I48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J48" s="335" t="str">
+      <c r="J48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="K48" s="335" t="str">
+      <c r="K48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="L48" s="335" t="str">
+      <c r="L48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="335" t="str">
+      <c r="M48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="335" t="str">
+      <c r="N48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="335" t="str">
+      <c r="O48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="335" t="str">
+      <c r="P48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="335" t="str">
+      <c r="Q48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
-      <c r="B49" s="330" t="s">
-        <v>380</v>
-      </c>
-      <c r="C49" s="331">
+      <c r="B49" s="329" t="s">
+        <v>378</v>
+      </c>
+      <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
         <v>1430.37</v>
       </c>
-      <c r="D49" s="332"/>
-      <c r="E49" s="333"/>
-      <c r="F49" s="332"/>
-      <c r="G49" s="331">
+      <c r="D49" s="331"/>
+      <c r="E49" s="332"/>
+      <c r="F49" s="331"/>
+      <c r="G49" s="330">
         <f>Data!C52</f>
         <v>2340</v>
       </c>
-      <c r="H49" s="331">
+      <c r="H49" s="330">
         <f>Data!D52</f>
         <v>1390.845307</v>
       </c>
-      <c r="I49" s="331" t="str">
+      <c r="I49" s="330" t="str">
         <f>Data!E52</f>
         <v/>
       </c>
-      <c r="J49" s="331" t="str">
+      <c r="J49" s="330" t="str">
         <f>Data!F52</f>
         <v/>
       </c>
-      <c r="K49" s="331" t="str">
+      <c r="K49" s="330" t="str">
         <f>Data!G52</f>
         <v/>
       </c>
-      <c r="L49" s="331" t="str">
+      <c r="L49" s="330" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="331" t="str">
+      <c r="M49" s="330" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="331" t="str">
+      <c r="N49" s="330" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="331" t="str">
+      <c r="O49" s="330" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="331" t="str">
+      <c r="P49" s="330" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="331" t="str">
+      <c r="Q49" s="330" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -10293,7 +10289,7 @@
         <f>C47+C48</f>
         <v>120.69305155463843</v>
       </c>
-      <c r="E50" s="309"/>
+      <c r="E50" s="308"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>224.79206823259295</v>
@@ -10341,14 +10337,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
-      <c r="E51" s="309"/>
+      <c r="E51" s="308"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="E52" s="309"/>
+      <c r="E52" s="308"/>
       <c r="G52" s="100" t="s">
         <v>223</v>
       </c>
@@ -10361,8 +10357,8 @@
       <c r="C53" s="89">
         <v>0.03</v>
       </c>
-      <c r="E53" s="306" t="s">
-        <v>372</v>
+      <c r="E53" s="305" t="s">
+        <v>370</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10388,8 +10384,8 @@
         <f>G54</f>
         <v>1.3902360168121564E-2</v>
       </c>
-      <c r="E54" s="306" t="s">
-        <v>373</v>
+      <c r="E54" s="305" t="s">
+        <v>371</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10415,7 +10411,7 @@
         <f>-C8/C47</f>
         <v>60.274889749707867</v>
       </c>
-      <c r="E55" s="309"/>
+      <c r="E55" s="308"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>54.348837209302324</v>
@@ -10463,14 +10459,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
-      <c r="E56" s="309"/>
+      <c r="E56" s="308"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="65" t="s">
         <v>172</v>
       </c>
-      <c r="E57" s="309"/>
+      <c r="E57" s="308"/>
       <c r="G57" s="100" t="s">
         <v>223</v>
       </c>
@@ -10484,7 +10480,7 @@
         <f>BS!$C79*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="309"/>
+      <c r="E58" s="308"/>
       <c r="G58" s="197">
         <f>Data!C56</f>
         <v>0</v>
@@ -10539,7 +10535,7 @@
         <f>BS!$C68*C67</f>
         <v>639</v>
       </c>
-      <c r="E59" s="309"/>
+      <c r="E59" s="308"/>
       <c r="G59" s="197">
         <f>Data!C55</f>
         <v>639</v>
@@ -10594,7 +10590,7 @@
         <f>BS!$C81*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="309"/>
+      <c r="E60" s="308"/>
       <c r="G60" s="197">
         <f>Data!C57</f>
         <v>0</v>
@@ -10649,7 +10645,7 @@
         <f>SUM(C58:C60)</f>
         <v>639</v>
       </c>
-      <c r="E61" s="309"/>
+      <c r="E61" s="308"/>
       <c r="G61" s="187">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>639</v>
@@ -10700,11 +10696,11 @@
       <c r="B62" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C62" s="304">
+      <c r="C62" s="303">
         <v>0</v>
       </c>
-      <c r="E62" s="307" t="s">
-        <v>374</v>
+      <c r="E62" s="306" t="s">
+        <v>372</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -10760,7 +10756,7 @@
         <f>C61+C62</f>
         <v>639</v>
       </c>
-      <c r="E63" s="309"/>
+      <c r="E63" s="308"/>
       <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>136</v>
@@ -10808,14 +10804,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
-      <c r="E64" s="309"/>
+      <c r="E64" s="308"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="99" t="s">
         <v>173</v>
       </c>
-      <c r="E65" s="309"/>
+      <c r="E65" s="308"/>
       <c r="G65" s="100" t="s">
         <v>223</v>
       </c>
@@ -10829,7 +10825,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="309"/>
+      <c r="E66" s="308"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -10854,7 +10850,7 @@
         <f>G67</f>
         <v>2.6966576637407157E-2</v>
       </c>
-      <c r="E67" s="309"/>
+      <c r="E67" s="308"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>2.6966576637407157E-2</v>
@@ -10879,7 +10875,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="309"/>
+      <c r="E68" s="308"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$81,0)</f>
         <v>0</v>
@@ -10905,7 +10901,7 @@
         <v>8.7649511686601553E-3</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="314"/>
+      <c r="E69" s="313"/>
       <c r="F69" s="9"/>
       <c r="G69" s="72">
         <f>G61/BS!C70</f>
@@ -10955,7 +10951,7 @@
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="306"/>
+      <c r="E72" s="305"/>
       <c r="F72" s="27"/>
       <c r="G72" s="100"/>
       <c r="H72" s="12"/>
@@ -10979,7 +10975,7 @@
         <v>0.57805815639048053</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="306"/>
+      <c r="E73" s="305"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -11036,7 +11032,7 @@
         <v>0.42194184360951947</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="306"/>
+      <c r="E74" s="305"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -11093,7 +11089,7 @@
         <v>0.1262407301768397</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="306"/>
+      <c r="E75" s="305"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -11150,7 +11146,7 @@
         <v>0.2957011134326798</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="306"/>
+      <c r="E76" s="305"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -11207,7 +11203,7 @@
         <v>1.8254420992584137E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="306"/>
+      <c r="E77" s="305"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -11264,8 +11260,8 @@
         <v>1.8254420992584137E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="307" t="s">
-        <v>375</v>
+      <c r="E78" s="306" t="s">
+        <v>373</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -11323,7 +11319,7 @@
         <v>7.2903593839132919E-2</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="306"/>
+      <c r="E79" s="305"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -11380,7 +11376,7 @@
         <v>1.3769886087237698E-2</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="306"/>
+      <c r="E80" s="305"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -11437,7 +11433,7 @@
         <v>0.38237459335905039</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="306"/>
+      <c r="E81" s="305"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -11494,7 +11490,7 @@
         <v>9.1769902406172096E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="306"/>
+      <c r="E82" s="305"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -11547,12 +11543,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="305">
+      <c r="C83" s="304">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>2.6092079791263361E-3</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="306"/>
+      <c r="E83" s="305"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -11609,7 +11605,7 @@
         <v>0.28799548297375194</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="306"/>
+      <c r="E84" s="305"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -11661,11 +11657,11 @@
       <c r="B85" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="C85" s="305">
+      <c r="C85" s="304">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="308" t="str">
+      <c r="E85" s="307" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
@@ -11690,7 +11686,7 @@
       <c r="C86" s="79">
         <v>0</v>
       </c>
-      <c r="E86" s="308" t="str">
+      <c r="E86" s="307" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -11716,7 +11712,7 @@
         <v>0.28799548297375194</v>
       </c>
       <c r="D87" s="77"/>
-      <c r="E87" s="306"/>
+      <c r="E87" s="305"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -11765,14 +11761,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
-      <c r="E88" s="309"/>
+      <c r="E88" s="308"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
       <c r="B89" s="65" t="s">
         <v>218</v>
       </c>
-      <c r="E89" s="309"/>
+      <c r="E89" s="308"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="10"/>
@@ -11784,7 +11780,7 @@
         <f>G90</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="E90" s="309"/>
+      <c r="E90" s="308"/>
       <c r="G90" s="116">
         <f>Data!C64</f>
         <v>0.57999999999999996</v>
@@ -11840,7 +11836,7 @@
         <f>C90*Common_Shares/$C$3</f>
         <v>4739.6903628800001</v>
       </c>
-      <c r="E91" s="309"/>
+      <c r="E91" s="308"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
         <v>4739.6903628800001</v>
@@ -11895,7 +11891,7 @@
         <f>C90/(C19*$C$3/Common_Shares)</f>
         <v>1.8776401969295582</v>
       </c>
-      <c r="E92" s="309"/>
+      <c r="E92" s="308"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
         <v>1.7093565785843898</v>
@@ -11950,7 +11946,7 @@
         <f>C90/Market_Price</f>
         <v>7.3417721518987331E-2</v>
       </c>
-      <c r="E93" s="309"/>
+      <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>7.3417721518987331E-2</v>
@@ -11998,7 +11994,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
-      <c r="E94" s="309"/>
+      <c r="E94" s="308"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
@@ -12007,7 +12003,7 @@
       </c>
       <c r="C95" s="63"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="306"/>
+      <c r="E95" s="305"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -12031,7 +12027,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="306"/>
+      <c r="E96" s="305"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -12088,7 +12084,7 @@
         <v>1.8142471128666626E-2</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="306"/>
+      <c r="E97" s="305"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -12166,7 +12162,7 @@
       <c r="B100" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="309"/>
+      <c r="E100" s="308"/>
       <c r="G100" s="100" t="s">
         <v>223</v>
       </c>
@@ -12181,7 +12177,7 @@
         <v>180996</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="310"/>
+      <c r="E101" s="309"/>
       <c r="F101" s="26"/>
       <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -12238,7 +12234,7 @@
         <v>8029</v>
       </c>
       <c r="D102" s="91"/>
-      <c r="E102" s="311"/>
+      <c r="E102" s="310"/>
       <c r="F102" s="91"/>
       <c r="G102" s="188">
         <f>IF(G$4="","",Data!D76)</f>
@@ -12295,7 +12291,7 @@
         <v>15310</v>
       </c>
       <c r="D103" s="91"/>
-      <c r="E103" s="311"/>
+      <c r="E103" s="310"/>
       <c r="F103" s="91"/>
       <c r="G103" s="188">
         <f>IF(G$4="","",Data!D77)</f>
@@ -12352,7 +12348,7 @@
         <v>13889</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="310"/>
+      <c r="E104" s="309"/>
       <c r="F104" s="26"/>
       <c r="G104" s="186">
         <f>Data!C78</f>
@@ -12409,7 +12405,7 @@
         <v>167107</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="310"/>
+      <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
         <f>Data!C79</f>
@@ -12458,7 +12454,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
-      <c r="E106" s="309"/>
+      <c r="E106" s="308"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
@@ -12467,7 +12463,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="310"/>
+      <c r="E107" s="309"/>
       <c r="F107" s="26"/>
       <c r="G107" s="100" t="s">
         <v>223</v>
@@ -12493,7 +12489,7 @@
         <v>0.91602966343411296</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="310"/>
+      <c r="E108" s="309"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -12550,7 +12546,7 @@
         <v>1.7467199087278951</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="310"/>
+      <c r="E109" s="309"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -12607,7 +12603,7 @@
         <v>8.343867655447804</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="310"/>
+      <c r="E110" s="309"/>
       <c r="F110" s="26"/>
       <c r="G110" s="97">
         <f>BS!$G$38/G$4</f>
@@ -12626,7 +12622,7 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
-      <c r="E111" s="309"/>
+      <c r="E111" s="308"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
@@ -12635,7 +12631,7 @@
       </c>
       <c r="C112" s="55"/>
       <c r="D112" s="55"/>
-      <c r="E112" s="312"/>
+      <c r="E112" s="311"/>
       <c r="F112" s="55"/>
       <c r="G112" s="23" t="str">
         <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
@@ -12691,7 +12687,7 @@
         <f>C81</f>
         <v>0.38237459335905039</v>
       </c>
-      <c r="E113" s="309"/>
+      <c r="E113" s="308"/>
       <c r="G113" s="23">
         <f t="shared" ref="G113:Q113" si="45">G81</f>
         <v>0.37556098895979384</v>
@@ -12745,7 +12741,7 @@
         <f>C4/C101</f>
         <v>4.8426484563194767E-2</v>
       </c>
-      <c r="E114" s="309"/>
+      <c r="E114" s="308"/>
       <c r="G114" s="42">
         <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
         <v>4.8601561460320276E-2</v>
@@ -12800,7 +12796,7 @@
         <v>1.0831144117242246</v>
       </c>
       <c r="D115" s="11"/>
-      <c r="E115" s="313"/>
+      <c r="E115" s="312"/>
       <c r="F115" s="11"/>
       <c r="G115" s="15">
         <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
@@ -12857,7 +12853,7 @@
         <v>1.5509944282629921E-2</v>
       </c>
       <c r="D116" s="106"/>
-      <c r="E116" s="312"/>
+      <c r="E116" s="311"/>
       <c r="F116" s="106"/>
       <c r="G116" s="105">
         <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
@@ -12953,7 +12949,7 @@
       </c>
       <c r="C119" s="183"/>
       <c r="D119" s="27"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="305"/>
       <c r="F119" s="27"/>
       <c r="G119" s="12"/>
       <c r="H119" s="12"/>
@@ -12978,7 +12974,7 @@
         <v>0.308898371982265</v>
       </c>
       <c r="D120" s="27"/>
-      <c r="E120" s="306"/>
+      <c r="E120" s="305"/>
       <c r="F120" s="27"/>
       <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -13035,7 +13031,7 @@
         <v>3.9101059744590508E-2</v>
       </c>
       <c r="D121" s="27"/>
-      <c r="E121" s="306"/>
+      <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
@@ -13864,10 +13860,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="344" t="s">
+      <c r="E6" s="343" t="s">
         <v>255</v>
       </c>
-      <c r="F6" s="344"/>
+      <c r="F6" s="343"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -13882,8 +13878,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="343"/>
+      <c r="F7" s="343"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -13898,8 +13894,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="343"/>
+      <c r="F8" s="343"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -13914,8 +13910,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="343"/>
+      <c r="F9" s="343"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15409,11 +15405,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="345" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15434,8 +15430,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15456,8 +15452,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15467,8 +15463,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="345"/>
+      <c r="F10" s="345"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15481,8 +15477,8 @@
       <c r="B11" s="163" t="s">
         <v>294</v>
       </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+      <c r="E11" s="345"/>
+      <c r="F11" s="345"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15500,8 +15496,8 @@
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="345"/>
+      <c r="F12" s="345"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -15518,8 +15514,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="345"/>
+      <c r="F13" s="345"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -15536,8 +15532,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="345"/>
+      <c r="F14" s="345"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15553,7 +15549,7 @@
         <v>155</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -15563,21 +15559,21 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>363</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="345" t="s">
+        <v>361</v>
+      </c>
+      <c r="F18" s="346"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="346"/>
+      <c r="F19" s="346"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
         <v>329</v>
       </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+      <c r="E20" s="346"/>
+      <c r="F20" s="346"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -15591,8 +15587,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="346"/>
+      <c r="F21" s="346"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -15606,8 +15602,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="346"/>
+      <c r="F22" s="346"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
@@ -15627,8 +15623,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="344"/>
+      <c r="F25" s="344"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -15638,8 +15634,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="344"/>
+      <c r="F26" s="344"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -15653,8 +15649,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="344"/>
+      <c r="F27" s="344"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -15664,8 +15660,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="344"/>
+      <c r="F28" s="344"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
@@ -15685,8 +15681,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="344"/>
+      <c r="F31" s="344"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -15696,8 +15692,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="344"/>
+      <c r="F32" s="344"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -15711,8 +15707,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="344"/>
+      <c r="F33" s="344"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -15722,8 +15718,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
@@ -15743,8 +15739,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -15754,8 +15750,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="344"/>
+      <c r="F38" s="344"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -15769,8 +15765,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="344"/>
+      <c r="F39" s="344"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -15781,8 +15777,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="344"/>
+      <c r="F40" s="344"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -15844,8 +15840,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="344"/>
+      <c r="F49" s="344"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -15855,8 +15851,8 @@
         <v>-0.2</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -15870,8 +15866,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="344"/>
+      <c r="F51" s="344"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -15881,12 +15877,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E54" s="163" t="s">
         <v>153</v>
@@ -15902,8 +15898,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="344"/>
+      <c r="F55" s="344"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -15913,8 +15909,8 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="344"/>
+      <c r="F56" s="344"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -15928,8 +15924,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="344"/>
+      <c r="F57" s="344"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -15939,8 +15935,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="344"/>
+      <c r="F58" s="344"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -15957,14 +15953,14 @@
       <c r="E60" s="103" t="s">
         <v>322</v>
       </c>
-      <c r="F60" s="319">
+      <c r="F60" s="318">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16021,7 +16017,7 @@
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E68" s="288" t="s">
         <v>343</v>
@@ -16068,9 +16064,9 @@
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>386</v>
-      </c>
-      <c r="F72" s="336">
+        <v>384</v>
+      </c>
+      <c r="F72" s="335">
         <f>BS!D89/C60</f>
         <v>0.63122414236360114</v>
       </c>
@@ -16163,7 +16159,7 @@
       <c r="E83" s="150" t="s">
         <v>130</v>
       </c>
-      <c r="F83" s="336">
+      <c r="F83" s="335">
         <f>(1-C83/C60)</f>
         <v>0.28704717576043881</v>
       </c>
@@ -16202,42 +16198,42 @@
       <c r="B88" s="103"/>
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="327" t="s">
+      <c r="E89" s="326" t="s">
+        <v>355</v>
+      </c>
+      <c r="F89" s="323"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="322"/>
+    </row>
+    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E90" s="319" t="s">
+        <v>356</v>
+      </c>
+      <c r="F90" s="324" t="s">
         <v>357</v>
       </c>
-      <c r="F89" s="324"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="323"/>
-    </row>
-    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="320" t="s">
+      <c r="G90" s="2"/>
+      <c r="H90" s="322"/>
+    </row>
+    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E91" s="320" t="s">
+        <v>356</v>
+      </c>
+      <c r="F91" s="324" t="s">
         <v>358</v>
       </c>
-      <c r="F90" s="325" t="s">
+      <c r="G91" s="2"/>
+      <c r="H91" s="322"/>
+    </row>
+    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E92" s="321" t="s">
+        <v>356</v>
+      </c>
+      <c r="F92" s="325" t="s">
         <v>359</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="323"/>
-    </row>
-    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="321" t="s">
-        <v>358</v>
-      </c>
-      <c r="F91" s="325" t="s">
-        <v>360</v>
-      </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="323"/>
-    </row>
-    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="322" t="s">
-        <v>358</v>
-      </c>
-      <c r="F92" s="326" t="s">
-        <v>361</v>
-      </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="323"/>
+      <c r="H92" s="322"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD1AEDB-C055-482C-BE1A-43998D996588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCCF1C3-025B-4CA0-AB4C-69872314C68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -1711,10 +1711,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>C0003</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Monthly Operating Expenses</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2007,6 +2003,10 @@
   </si>
   <si>
     <t>Selected:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3374,20 +3374,23 @@
     <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3403,9 +3406,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3689,7 +3689,7 @@
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.59765625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -3702,8 +3702,8 @@
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="347" t="s">
-        <v>391</v>
+      <c r="E1" s="337" t="s">
+        <v>390</v>
       </c>
       <c r="F1" s="290" t="s">
         <v>306</v>
@@ -3738,10 +3738,10 @@
         <v>344</v>
       </c>
       <c r="C5" s="48" t="s">
+        <v>363</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>364</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3804,13 +3804,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="337" t="s">
+      <c r="B12" s="339" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="337"/>
-      <c r="D12" s="337"/>
-      <c r="E12" s="337"/>
-      <c r="F12" s="337"/>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3821,7 +3821,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3831,7 +3831,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>42</v>
@@ -3857,7 +3857,7 @@
         <v>59</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>346</v>
+        <v>391</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -3912,22 +3912,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="337" t="s">
+      <c r="B25" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C25" s="337"/>
-      <c r="D25" s="337"/>
-      <c r="E25" s="337"/>
-      <c r="F25" s="337"/>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
-        <v>375</v>
-      </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="B26" s="340" t="s">
+        <v>374</v>
+      </c>
+      <c r="C26" s="340"/>
+      <c r="D26" s="340"/>
+      <c r="E26" s="340"/>
+      <c r="F26" s="340"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -3939,13 +3939,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="338" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="338"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3965,13 +3965,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="338" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="338"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="338"/>
+      <c r="F32" s="338"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4000,13 +4000,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="338" t="s">
         <v>242</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="338"/>
+      <c r="D36" s="338"/>
+      <c r="E36" s="338"/>
+      <c r="F36" s="338"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4022,17 +4022,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="338" t="s">
         <v>246</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="338"/>
+      <c r="D39" s="338"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
@@ -4092,13 +4092,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="338" t="s">
         <v>247</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="338"/>
+      <c r="D47" s="338"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4114,13 +4114,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
-        <v>374</v>
-      </c>
-      <c r="C50" s="340"/>
-      <c r="D50" s="340"/>
-      <c r="E50" s="340"/>
-      <c r="F50" s="340"/>
+      <c r="B50" s="338" t="s">
+        <v>373</v>
+      </c>
+      <c r="C50" s="342"/>
+      <c r="D50" s="342"/>
+      <c r="E50" s="342"/>
+      <c r="F50" s="342"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4136,22 +4136,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="337" t="s">
-        <v>379</v>
-      </c>
-      <c r="C53" s="337"/>
-      <c r="D53" s="337"/>
-      <c r="E53" s="337"/>
-      <c r="F53" s="337"/>
+      <c r="B53" s="339" t="s">
+        <v>378</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="337" t="s">
+      <c r="B54" s="339" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="337"/>
-      <c r="D54" s="337"/>
-      <c r="E54" s="337"/>
-      <c r="F54" s="337"/>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4212,22 +4212,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
+      <c r="B63" s="338" t="s">
         <v>302</v>
       </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="340" t="s">
         <v>258</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="340"/>
+      <c r="D64" s="340"/>
+      <c r="E64" s="340"/>
+      <c r="F64" s="340"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4263,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="292" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4279,22 +4279,22 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="337" t="s">
+      <c r="B72" s="339" t="s">
+        <v>379</v>
+      </c>
+      <c r="C72" s="339"/>
+      <c r="D72" s="339"/>
+      <c r="E72" s="339"/>
+      <c r="F72" s="339"/>
+    </row>
+    <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="339" t="s">
         <v>380</v>
       </c>
-      <c r="C72" s="337"/>
-      <c r="D72" s="337"/>
-      <c r="E72" s="337"/>
-      <c r="F72" s="337"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="337" t="s">
-        <v>381</v>
-      </c>
-      <c r="C73" s="337"/>
-      <c r="D73" s="337"/>
-      <c r="E73" s="337"/>
-      <c r="F73" s="337"/>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
@@ -4331,13 +4331,13 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="337" t="s">
+      <c r="B80" s="339" t="s">
         <v>260</v>
       </c>
-      <c r="C80" s="337"/>
-      <c r="D80" s="337"/>
-      <c r="E80" s="337"/>
-      <c r="F80" s="337"/>
+      <c r="C80" s="339"/>
+      <c r="D80" s="339"/>
+      <c r="E80" s="339"/>
+      <c r="F80" s="339"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4350,13 +4350,13 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="337" t="s">
-        <v>382</v>
-      </c>
-      <c r="C84" s="337"/>
-      <c r="D84" s="337"/>
-      <c r="E84" s="337"/>
-      <c r="F84" s="337"/>
+      <c r="B84" s="339" t="s">
+        <v>381</v>
+      </c>
+      <c r="C84" s="339"/>
+      <c r="D84" s="339"/>
+      <c r="E84" s="339"/>
+      <c r="F84" s="339"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
@@ -4460,13 +4460,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="337" t="s">
+      <c r="B97" s="339" t="s">
         <v>266</v>
       </c>
-      <c r="C97" s="337"/>
-      <c r="D97" s="337"/>
-      <c r="E97" s="337"/>
-      <c r="F97" s="337"/>
+      <c r="C97" s="339"/>
+      <c r="D97" s="339"/>
+      <c r="E97" s="339"/>
+      <c r="F97" s="339"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
@@ -4492,13 +4492,13 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="339" t="s">
-        <v>362</v>
-      </c>
-      <c r="C103" s="339"/>
-      <c r="D103" s="339"/>
-      <c r="E103" s="339"/>
-      <c r="F103" s="339"/>
+      <c r="B103" s="338" t="s">
+        <v>361</v>
+      </c>
+      <c r="C103" s="338"/>
+      <c r="D103" s="338"/>
+      <c r="E103" s="338"/>
+      <c r="F103" s="338"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
@@ -4641,13 +4641,13 @@
       </c>
     </row>
     <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="342" t="s">
-        <v>363</v>
-      </c>
-      <c r="C114" s="342"/>
-      <c r="D114" s="342"/>
-      <c r="E114" s="342"/>
-      <c r="F114" s="342"/>
+      <c r="B114" s="343" t="s">
+        <v>362</v>
+      </c>
+      <c r="C114" s="343"/>
+      <c r="D114" s="343"/>
+      <c r="E114" s="343"/>
+      <c r="F114" s="343"/>
     </row>
     <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A116" s="253" t="s">
@@ -4660,13 +4660,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="338" t="s">
+      <c r="B118" s="341" t="s">
         <v>274</v>
       </c>
-      <c r="C118" s="338"/>
-      <c r="D118" s="338"/>
-      <c r="E118" s="338"/>
-      <c r="F118" s="338"/>
+      <c r="C118" s="341"/>
+      <c r="D118" s="341"/>
+      <c r="E118" s="341"/>
+      <c r="F118" s="341"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
@@ -4753,12 +4753,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4774,6 +4768,12 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8047,7 +8047,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="291" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C72" s="267" t="s">
         <v>99</v>
@@ -8059,7 +8059,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8070,12 +8070,12 @@
         <v>-909.4058419702136</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="294" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
@@ -8086,12 +8086,12 @@
         <v>52.428737313479523</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C75" s="299"/>
       <c r="D75" s="298">
@@ -8099,12 +8099,12 @@
         <v>5456.4350518212814</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C76" s="297"/>
       <c r="D76" s="333">
@@ -8112,7 +8112,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="307" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="307" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9666,7 +9666,7 @@
         <v>-1106.5</v>
       </c>
       <c r="E33" s="306" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="305" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10171,7 +10171,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
@@ -10226,7 +10226,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="329" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
@@ -10358,7 +10358,7 @@
         <v>0.03</v>
       </c>
       <c r="E53" s="305" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10385,7 +10385,7 @@
         <v>1.3902360168121564E-2</v>
       </c>
       <c r="E54" s="305" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10700,7 +10700,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="306" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -11261,7 +11261,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -13860,10 +13860,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="343" t="s">
+      <c r="E6" s="344" t="s">
         <v>255</v>
       </c>
-      <c r="F6" s="343"/>
+      <c r="F6" s="344"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -13878,8 +13878,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="343"/>
-      <c r="F7" s="343"/>
+      <c r="E7" s="344"/>
+      <c r="F7" s="344"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -13894,8 +13894,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="343"/>
-      <c r="F8" s="343"/>
+      <c r="E8" s="344"/>
+      <c r="F8" s="344"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -13910,8 +13910,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="343"/>
-      <c r="F9" s="343"/>
+      <c r="E9" s="344"/>
+      <c r="F9" s="344"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15405,11 +15405,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="345" t="str">
+      <c r="E7" s="346" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="345"/>
+      <c r="F7" s="346"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15430,8 +15430,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="346"/>
+      <c r="F8" s="346"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15452,8 +15452,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="346"/>
+      <c r="F9" s="346"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15463,8 +15463,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="345"/>
-      <c r="F10" s="345"/>
+      <c r="E10" s="346"/>
+      <c r="F10" s="346"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15477,8 +15477,8 @@
       <c r="B11" s="163" t="s">
         <v>294</v>
       </c>
-      <c r="E11" s="345"/>
-      <c r="F11" s="345"/>
+      <c r="E11" s="346"/>
+      <c r="F11" s="346"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15496,8 +15496,8 @@
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="345"/>
-      <c r="F12" s="345"/>
+      <c r="E12" s="346"/>
+      <c r="F12" s="346"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -15514,8 +15514,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="345"/>
-      <c r="F13" s="345"/>
+      <c r="E13" s="346"/>
+      <c r="F13" s="346"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -15532,8 +15532,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="345"/>
-      <c r="F14" s="345"/>
+      <c r="E14" s="346"/>
+      <c r="F14" s="346"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15549,7 +15549,7 @@
         <v>155</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -15559,21 +15559,21 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="345" t="s">
-        <v>361</v>
-      </c>
-      <c r="F18" s="346"/>
+      <c r="E18" s="346" t="s">
+        <v>360</v>
+      </c>
+      <c r="F18" s="347"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="346"/>
-      <c r="F19" s="346"/>
+      <c r="E19" s="347"/>
+      <c r="F19" s="347"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
         <v>329</v>
       </c>
-      <c r="E20" s="346"/>
-      <c r="F20" s="346"/>
+      <c r="E20" s="347"/>
+      <c r="F20" s="347"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -15587,8 +15587,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="346"/>
-      <c r="F21" s="346"/>
+      <c r="E21" s="347"/>
+      <c r="F21" s="347"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -15602,8 +15602,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="346"/>
-      <c r="F22" s="346"/>
+      <c r="E22" s="347"/>
+      <c r="F22" s="347"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
@@ -15623,8 +15623,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="344"/>
-      <c r="F25" s="344"/>
+      <c r="E25" s="345"/>
+      <c r="F25" s="345"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -15634,8 +15634,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="344"/>
-      <c r="F26" s="344"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -15649,8 +15649,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="344"/>
-      <c r="F27" s="344"/>
+      <c r="E27" s="345"/>
+      <c r="F27" s="345"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -15660,8 +15660,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="344"/>
-      <c r="F28" s="344"/>
+      <c r="E28" s="345"/>
+      <c r="F28" s="345"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
@@ -15681,8 +15681,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="344"/>
-      <c r="F31" s="344"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -15692,8 +15692,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="344"/>
-      <c r="F32" s="344"/>
+      <c r="E32" s="345"/>
+      <c r="F32" s="345"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -15707,8 +15707,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="344"/>
-      <c r="F33" s="344"/>
+      <c r="E33" s="345"/>
+      <c r="F33" s="345"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -15718,8 +15718,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="E34" s="345"/>
+      <c r="F34" s="345"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
@@ -15739,8 +15739,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="E37" s="345"/>
+      <c r="F37" s="345"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -15750,8 +15750,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="344"/>
-      <c r="F38" s="344"/>
+      <c r="E38" s="345"/>
+      <c r="F38" s="345"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -15765,8 +15765,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="344"/>
-      <c r="F39" s="344"/>
+      <c r="E39" s="345"/>
+      <c r="F39" s="345"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -15777,8 +15777,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="344"/>
-      <c r="F40" s="344"/>
+      <c r="E40" s="345"/>
+      <c r="F40" s="345"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -15840,8 +15840,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="344"/>
-      <c r="F49" s="344"/>
+      <c r="E49" s="345"/>
+      <c r="F49" s="345"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -15851,8 +15851,8 @@
         <v>-0.2</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
+      <c r="E50" s="345"/>
+      <c r="F50" s="345"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -15866,8 +15866,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="344"/>
-      <c r="F51" s="344"/>
+      <c r="E51" s="345"/>
+      <c r="F51" s="345"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -15877,8 +15877,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="E52" s="345"/>
+      <c r="F52" s="345"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
@@ -15898,8 +15898,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="344"/>
-      <c r="F55" s="344"/>
+      <c r="E55" s="345"/>
+      <c r="F55" s="345"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -15909,8 +15909,8 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="344"/>
-      <c r="F56" s="344"/>
+      <c r="E56" s="345"/>
+      <c r="F56" s="345"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -15924,8 +15924,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="344"/>
-      <c r="F57" s="344"/>
+      <c r="E57" s="345"/>
+      <c r="F57" s="345"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -15935,8 +15935,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="344"/>
-      <c r="F58" s="344"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -15960,7 +15960,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16017,7 +16017,7 @@
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E68" s="288" t="s">
         <v>343</v>
@@ -16064,7 +16064,7 @@
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
@@ -16199,7 +16199,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="326" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F89" s="323"/>
       <c r="G89" s="2"/>
@@ -16207,30 +16207,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="319" t="s">
+        <v>355</v>
+      </c>
+      <c r="F90" s="324" t="s">
         <v>356</v>
-      </c>
-      <c r="F90" s="324" t="s">
-        <v>357</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="320" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F91" s="324" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="321" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F92" s="325" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="322"/>

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A14EA6B-785E-4172-BFDB-0F94DAF722D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20802F47-1D5C-4D80-A2D1-23D4EC2E0B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="411">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1353,10 +1353,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>FCFE/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Latest FCFE =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2172,6 +2168,149 @@
   </si>
   <si>
     <t>CFI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 6:  Risk Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key Risk Factors</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Sustainable Revenue &amp; Margins</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Capital Expenditures</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Working Capital</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Accuracy of Normalized FCFE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, which is affacted by uncertainties include:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- The extreme scenarios (“Snowball”, “Devil’s Advocate”) have low probabilities; if market conditions shift drastically, these might become more relevant than anticipated.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Appropriateness of Cost of Equity</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Reliability of Growth Scenarios</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Macroeconomic Sensitivity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Input Cost Volatility</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Intense Competition</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>External &amp; Company-Specific Risks</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normalized FCFE/Market Cap =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2839,7 +2978,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="351">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3560,6 +3699,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3849,7 +3994,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -3869,10 +4014,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="337" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F1" s="290" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -3901,13 +4046,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C5" s="48" t="s">
+        <v>368</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>369</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3934,7 +4079,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3971,7 +4116,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="339" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C12" s="339"/>
       <c r="D12" s="339"/>
@@ -3980,14 +4125,14 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3997,7 +4142,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>41</v>
@@ -4023,13 +4168,13 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C19" s="255">
         <v>0.2</v>
@@ -4046,7 +4191,7 @@
         <v>16.361242554197645</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E20" s="336">
         <v>3</v>
@@ -4054,7 +4199,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
@@ -4069,7 +4214,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4079,7 +4224,7 @@
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="339" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C25" s="339"/>
       <c r="D25" s="339"/>
@@ -4088,7 +4233,7 @@
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="341" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C26" s="341"/>
       <c r="D26" s="341"/>
@@ -4198,7 +4343,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
@@ -4213,7 +4358,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
@@ -4281,7 +4426,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="340" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C50" s="343"/>
       <c r="D50" s="343"/>
@@ -4303,7 +4448,7 @@
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="339" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C53" s="339"/>
       <c r="D53" s="339"/>
@@ -4312,7 +4457,7 @@
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="339" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C54" s="339"/>
       <c r="D54" s="339"/>
@@ -4321,7 +4466,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
@@ -4347,7 +4492,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>273</v>
+        <v>410</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
@@ -4356,7 +4501,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
@@ -4365,7 +4510,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4379,7 +4524,7 @@
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
       <c r="B63" s="339" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C63" s="339"/>
       <c r="D63" s="339"/>
@@ -4402,7 +4547,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C67" s="317">
         <v>0.08</v>
@@ -4410,26 +4555,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="292" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="292" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4446,13 +4591,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="338" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="339" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C73" s="339"/>
       <c r="D73" s="339"/>
@@ -4461,7 +4606,7 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="339" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C74" s="339"/>
       <c r="D74" s="339"/>
@@ -4478,7 +4623,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4491,7 +4636,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="253" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4504,7 +4649,7 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="339" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C81" s="339"/>
       <c r="D81" s="339"/>
@@ -4523,7 +4668,7 @@
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="339" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C85" s="339"/>
       <c r="D85" s="339"/>
@@ -4545,7 +4690,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C87" s="254">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4589,7 +4734,7 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C92" s="254">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
@@ -4620,7 +4765,7 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C96" s="254">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
@@ -4633,7 +4778,7 @@
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B98" s="339" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C98" s="339"/>
       <c r="D98" s="339"/>
@@ -4642,7 +4787,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
@@ -4655,7 +4800,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="253" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4665,7 +4810,7 @@
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="340" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C104" s="340"/>
       <c r="D104" s="340"/>
@@ -4814,7 +4959,7 @@
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="344" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C115" s="344"/>
       <c r="D115" s="344"/>
@@ -4823,7 +4968,7 @@
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4833,7 +4978,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="342" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C119" s="342"/>
       <c r="D119" s="342"/>
@@ -4842,7 +4987,7 @@
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B120" s="339" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C120" s="339"/>
       <c r="D120" s="339"/>
@@ -4865,7 +5010,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C123" s="256">
         <f>C19</f>
@@ -4910,7 +5055,7 @@
         <v>13.496427739382831</v>
       </c>
     </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B129" s="82" t="s">
         <v>262</v>
       </c>
@@ -4923,7 +5068,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B130" s="244" t="s">
         <v>264</v>
       </c>
@@ -4932,8 +5077,118 @@
         <v>0.29845794412101279</v>
       </c>
     </row>
+    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A132" s="253" t="s">
+        <v>394</v>
+      </c>
+      <c r="B132" s="36"/>
+      <c r="C132" s="36"/>
+      <c r="D132" s="36"/>
+      <c r="E132" s="36"/>
+      <c r="F132" s="36"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="346" t="s">
+        <v>396</v>
+      </c>
+      <c r="C134" s="339"/>
+      <c r="D134" s="339"/>
+      <c r="E134" s="339"/>
+      <c r="F134" s="339"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="240" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="343" t="s">
+        <v>400</v>
+      </c>
+      <c r="C137" s="343"/>
+      <c r="D137" s="343"/>
+      <c r="E137" s="343"/>
+      <c r="F137" s="343"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="244" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="244" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="244" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B143" s="340" t="s">
+        <v>401</v>
+      </c>
+      <c r="C143" s="340"/>
+      <c r="D143" s="340"/>
+      <c r="E143" s="340"/>
+      <c r="F143" s="340"/>
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B146" s="345" t="s">
+        <v>402</v>
+      </c>
+      <c r="C146" s="345"/>
+      <c r="D146" s="345"/>
+      <c r="E146" s="345"/>
+      <c r="F146" s="345"/>
+    </row>
+    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B147" s="345" t="s">
+        <v>403</v>
+      </c>
+      <c r="C147" s="345"/>
+      <c r="D147" s="345"/>
+      <c r="E147" s="345"/>
+      <c r="F147" s="345"/>
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="244" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="244" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="244" t="s">
+        <v>408</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B104:F104"/>
     <mergeCell ref="B73:F73"/>
@@ -4958,7 +5213,7 @@
     <mergeCell ref="B63:F63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5351,7 +5606,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C22" s="184"/>
       <c r="D22" s="184"/>
@@ -5367,7 +5622,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C23" s="184"/>
       <c r="D23" s="184"/>
@@ -5383,7 +5638,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C24" s="184"/>
       <c r="D24" s="184"/>
@@ -5532,47 +5787,47 @@
         <v>2</v>
       </c>
       <c r="C36" s="186">
-        <f>IF(C$4="","",C4)</f>
+        <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>15325962</v>
       </c>
       <c r="D36" s="186" t="str">
-        <f>IF(D$4="","",D4)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="E36" s="186" t="str">
-        <f>IF(E$4="","",E4)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F36" s="186" t="str">
-        <f>IF(F$4="","",F4)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G36" s="186" t="str">
-        <f>IF(G$4="","",G4)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="H36" s="186" t="str">
-        <f>IF(H$4="","",H4)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I36" s="186" t="str">
-        <f>IF(I$4="","",I4)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J36" s="186" t="str">
-        <f>IF(J$4="","",J4)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K36" s="186" t="str">
-        <f>IF(K$4="","",K4)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L36" s="186" t="str">
-        <f>IF(L$4="","",L4)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M36" s="186" t="str">
-        <f>IF(M$4="","",M4)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -5581,47 +5836,47 @@
         <v>44</v>
       </c>
       <c r="C37" s="186">
-        <f>IF(C$4="","",-C5)</f>
+        <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-11151623</v>
       </c>
       <c r="D37" s="186" t="str">
-        <f>IF(D$4="","",-D5)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="E37" s="186" t="str">
-        <f>IF(E$4="","",-E5)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="F37" s="186" t="str">
-        <f>IF(F$4="","",-F5)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="G37" s="186" t="str">
-        <f>IF(G$4="","",-G5)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="H37" s="186" t="str">
-        <f>IF(H$4="","",-H5)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I37" s="186" t="str">
-        <f>IF(I$4="","",-I5)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J37" s="186" t="str">
-        <f>IF(J$4="","",-J5)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K37" s="186" t="str">
-        <f>IF(K$4="","",-K5)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L37" s="186" t="str">
-        <f>IF(L$4="","",-L5)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="M37" s="186" t="str">
-        <f>IF(M$4="","",-M5)</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -5634,43 +5889,43 @@
         <v>4174339</v>
       </c>
       <c r="D38" s="187" t="str">
-        <f t="shared" ref="D38" si="1">IF(D36="","",D36+D37)</f>
+        <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v/>
       </c>
       <c r="E38" s="187" t="str">
-        <f t="shared" ref="E38" si="2">IF(E36="","",E36+E37)</f>
+        <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v/>
       </c>
       <c r="F38" s="187" t="str">
-        <f t="shared" ref="F38" si="3">IF(F36="","",F36+F37)</f>
+        <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v/>
       </c>
       <c r="G38" s="187" t="str">
-        <f t="shared" ref="G38" si="4">IF(G36="","",G36+G37)</f>
+        <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v/>
       </c>
       <c r="H38" s="187" t="str">
-        <f t="shared" ref="H38" si="5">IF(H36="","",H36+H37)</f>
+        <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v/>
       </c>
       <c r="I38" s="187" t="str">
-        <f t="shared" ref="I38" si="6">IF(I36="","",I36+I37)</f>
+        <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v/>
       </c>
       <c r="J38" s="187" t="str">
-        <f t="shared" ref="J38" si="7">IF(J36="","",J36+J37)</f>
+        <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v/>
       </c>
       <c r="K38" s="187" t="str">
-        <f t="shared" ref="K38" si="8">IF(K36="","",K36+K37)</f>
+        <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v/>
       </c>
       <c r="L38" s="187" t="str">
-        <f t="shared" ref="L38" si="9">IF(L36="","",L36+L37)</f>
+        <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v/>
       </c>
       <c r="M38" s="187" t="str">
-        <f t="shared" ref="M38" si="10">IF(M36="","",M36+M37)</f>
+        <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
     </row>
@@ -5679,47 +5934,47 @@
         <v>55</v>
       </c>
       <c r="C39" s="186">
-        <f>IF(C$4="","",-C6)</f>
+        <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-2297566</v>
       </c>
       <c r="D39" s="186" t="str">
-        <f>IF(D$4="","",-D6)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="E39" s="186" t="str">
-        <f>IF(E$4="","",-E6)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="F39" s="186" t="str">
-        <f>IF(F$4="","",-F6)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="G39" s="186" t="str">
-        <f>IF(G$4="","",-G6)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="H39" s="186" t="str">
-        <f>IF(H$4="","",-H6)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="I39" s="186" t="str">
-        <f>IF(I$4="","",-I6)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J39" s="186" t="str">
-        <f>IF(J$4="","",-J6)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K39" s="186" t="str">
-        <f>IF(K$4="","",-K6)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="L39" s="186" t="str">
-        <f>IF(L$4="","",-L6)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="M39" s="186" t="str">
-        <f>IF(M$4="","",-M6)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -5728,47 +5983,47 @@
         <v>62</v>
       </c>
       <c r="C40" s="188">
-        <f>IF(C$4="","",-C7)</f>
+        <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-2043459</v>
       </c>
       <c r="D40" s="188" t="str">
-        <f>IF(D$4="","",-D7)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="E40" s="188" t="str">
-        <f>IF(E$4="","",-E7)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="F40" s="188" t="str">
-        <f>IF(F$4="","",-F7)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G40" s="188" t="str">
-        <f>IF(G$4="","",-G7)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H40" s="188" t="str">
-        <f>IF(H$4="","",-H7)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="I40" s="188" t="str">
-        <f>IF(I$4="","",-I7)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J40" s="188" t="str">
-        <f>IF(J$4="","",-J7)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K40" s="188" t="str">
-        <f>IF(K$4="","",-K7)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="L40" s="188" t="str">
-        <f>IF(L$4="","",-L7)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="M40" s="188" t="str">
-        <f>IF(M$4="","",-M7)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -5781,43 +6036,43 @@
         <v>-254107</v>
       </c>
       <c r="D41" s="188" t="str">
-        <f t="shared" ref="D41:M41" si="11">IF(D$4="","",D39-D40)</f>
+        <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v/>
       </c>
       <c r="E41" s="188" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="F41" s="188" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="G41" s="188" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H41" s="188" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="I41" s="188" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J41" s="188" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K41" s="188" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="L41" s="188" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="M41" s="188" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -5826,47 +6081,47 @@
         <v>50</v>
       </c>
       <c r="C42" s="186">
-        <f>IF(C$4="","",-C8)</f>
+        <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>0</v>
       </c>
       <c r="D42" s="186" t="str">
-        <f>IF(D$4="","",-D8)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E42" s="186" t="str">
-        <f>IF(E$4="","",-E8)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="F42" s="186" t="str">
-        <f>IF(F$4="","",-F8)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="G42" s="186" t="str">
-        <f>IF(G$4="","",-G8)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H42" s="186" t="str">
-        <f>IF(H$4="","",-H8)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I42" s="186" t="str">
-        <f>IF(I$4="","",-I8)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J42" s="186" t="str">
-        <f>IF(J$4="","",-J8)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K42" s="186" t="str">
-        <f>IF(K$4="","",-K8)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L42" s="186" t="str">
-        <f>IF(L$4="","",-L8)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="M42" s="186" t="str">
-        <f>IF(M$4="","",-M8)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -5879,43 +6134,43 @@
         <v>1876773</v>
       </c>
       <c r="D43" s="189" t="str">
-        <f t="shared" ref="D43:M43" si="12">IF(D$4="","",D38+D39+D42)</f>
+        <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v/>
       </c>
       <c r="E43" s="189" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F43" s="189" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G43" s="189" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H43" s="189" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="I43" s="189" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J43" s="189" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K43" s="189" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="L43" s="189" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="M43" s="189" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -5924,47 +6179,47 @@
         <v>170</v>
       </c>
       <c r="C44" s="190">
-        <f t="shared" ref="C44:M44" si="13">IF(C$4="","",C47-C46-C45-C43)</f>
+        <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
         <v>248317</v>
       </c>
       <c r="D44" s="190" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="E44" s="190" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F44" s="190" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="G44" s="190" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H44" s="190" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I44" s="190" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J44" s="190" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K44" s="190" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="L44" s="190" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="M44" s="190" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -5973,47 +6228,47 @@
         <v>69</v>
       </c>
       <c r="C45" s="191">
-        <f t="shared" ref="C45:M45" si="14">IF(C$4="","",C51+C52)</f>
+        <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
         <v>-30619</v>
       </c>
       <c r="D45" s="191" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="E45" s="191" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F45" s="191" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G45" s="191" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H45" s="191" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I45" s="191" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J45" s="191" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K45" s="191" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="L45" s="191" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="M45" s="191" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6022,47 +6277,47 @@
         <v>51</v>
       </c>
       <c r="C46" s="186">
-        <f>IF(C$4="","",-C14)</f>
+        <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-327166</v>
       </c>
       <c r="D46" s="186" t="str">
-        <f>IF(D$4="","",-D14)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="E46" s="186" t="str">
-        <f>IF(E$4="","",-E14)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="F46" s="186" t="str">
-        <f>IF(F$4="","",-F14)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G46" s="186" t="str">
-        <f>IF(G$4="","",-G14)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H46" s="186" t="str">
-        <f>IF(H$4="","",-H14)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="I46" s="186" t="str">
-        <f>IF(I$4="","",-I14)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J46" s="186" t="str">
-        <f>IF(J$4="","",-J14)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="K46" s="186" t="str">
-        <f>IF(K$4="","",-K14)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="L46" s="186" t="str">
-        <f>IF(L$4="","",-L14)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="M46" s="186" t="str">
-        <f>IF(M$4="","",-M14)</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -6071,47 +6326,47 @@
         <v>43</v>
       </c>
       <c r="C47" s="189">
-        <f>IF(C$4="","",C15)</f>
+        <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>1767305</v>
       </c>
       <c r="D47" s="189" t="str">
-        <f>IF(D$4="","",D15)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="E47" s="189" t="str">
-        <f>IF(E$4="","",E15)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="F47" s="189" t="str">
-        <f>IF(F$4="","",F15)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="G47" s="189" t="str">
-        <f>IF(G$4="","",G15)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H47" s="189" t="str">
-        <f>IF(H$4="","",H15)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I47" s="189" t="str">
-        <f>IF(I$4="","",I15)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="J47" s="189" t="str">
-        <f>IF(J$4="","",J15)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K47" s="189" t="str">
-        <f>IF(K$4="","",K15)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="L47" s="189" t="str">
-        <f>IF(L$4="","",L15)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="M47" s="189" t="str">
-        <f>IF(M$4="","",M15)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -6120,47 +6375,47 @@
         <v>45</v>
       </c>
       <c r="C48" s="186">
-        <f>IF(C$4="","",MIN(-C16,0))</f>
+        <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>0</v>
       </c>
       <c r="D48" s="186" t="str">
-        <f>IF(D$4="","",MIN(-D16,0))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="E48" s="186" t="str">
-        <f>IF(E$4="","",MIN(-E16,0))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="F48" s="186" t="str">
-        <f>IF(F$4="","",MIN(-F16,0))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="G48" s="186" t="str">
-        <f>IF(G$4="","",MIN(-G16,0))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H48" s="186" t="str">
-        <f>IF(H$4="","",MIN(-H16,0))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I48" s="186" t="str">
-        <f>IF(I$4="","",MIN(-I16,0))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J48" s="186" t="str">
-        <f>IF(J$4="","",MIN(-J16,0))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="K48" s="186" t="str">
-        <f>IF(K$4="","",MIN(-K16,0))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L48" s="186" t="str">
-        <f>IF(L$4="","",MIN(-L16,0))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="M48" s="186" t="str">
-        <f>IF(M$4="","",MIN(-M16,0))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -6174,47 +6429,47 @@
         <v>39</v>
       </c>
       <c r="C51" s="186">
-        <f>IF(C$4="","",-C12)</f>
+        <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-59596</v>
       </c>
       <c r="D51" s="186" t="str">
-        <f>IF(D$4="","",-D12)</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="E51" s="186" t="str">
-        <f>IF(E$4="","",-E12)</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="F51" s="186" t="str">
-        <f>IF(F$4="","",-F12)</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="G51" s="186" t="str">
-        <f>IF(G$4="","",-G12)</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="H51" s="186" t="str">
-        <f>IF(H$4="","",-H12)</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="I51" s="186" t="str">
-        <f>IF(I$4="","",-I12)</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="J51" s="186" t="str">
-        <f>IF(J$4="","",-J12)</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K51" s="186" t="str">
-        <f>IF(K$4="","",-K12)</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="L51" s="186" t="str">
-        <f>IF(L$4="","",-L12)</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M51" s="186" t="str">
-        <f>IF(M$4="","",-M12)</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -6223,47 +6478,47 @@
         <v>68</v>
       </c>
       <c r="C52" s="186">
-        <f>IF(C$4="","",C13)</f>
+        <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>28977</v>
       </c>
       <c r="D52" s="186" t="str">
-        <f>IF(D$4="","",D13)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="E52" s="186" t="str">
-        <f>IF(E$4="","",E13)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="F52" s="186" t="str">
-        <f>IF(F$4="","",F13)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="G52" s="186" t="str">
-        <f>IF(G$4="","",G13)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H52" s="186" t="str">
-        <f>IF(H$4="","",H13)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="I52" s="186" t="str">
-        <f>IF(I$4="","",I13)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J52" s="186" t="str">
-        <f>IF(J$4="","",J13)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="K52" s="186" t="str">
-        <f>IF(K$4="","",K13)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L52" s="186" t="str">
-        <f>IF(L$4="","",L13)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="M52" s="186" t="str">
-        <f>IF(M$4="","",M13)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -6277,47 +6532,47 @@
         <v>161</v>
       </c>
       <c r="C55" s="191">
-        <f>IF(C$4="","",C9)</f>
+        <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
         <v>639</v>
       </c>
       <c r="D55" s="191" t="str">
-        <f>IF(D$4="","",D9)</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="E55" s="191" t="str">
-        <f>IF(E$4="","",E9)</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="F55" s="191" t="str">
-        <f>IF(F$4="","",F9)</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="G55" s="191" t="str">
-        <f>IF(G$4="","",G9)</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="H55" s="191" t="str">
-        <f>IF(H$4="","",H9)</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I55" s="191" t="str">
-        <f>IF(I$4="","",I9)</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="J55" s="191" t="str">
-        <f>IF(J$4="","",J9)</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K55" s="191" t="str">
-        <f>IF(K$4="","",K9)</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="L55" s="191" t="str">
-        <f>IF(L$4="","",L9)</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M55" s="191" t="str">
-        <f>IF(M$4="","",M9)</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -6326,47 +6581,47 @@
         <v>169</v>
       </c>
       <c r="C56" s="191">
-        <f>IF(C$4="","",C10)</f>
+        <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
         <v>0</v>
       </c>
       <c r="D56" s="191" t="str">
-        <f>IF(D$4="","",D10)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="E56" s="191" t="str">
-        <f>IF(E$4="","",E10)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="F56" s="191" t="str">
-        <f>IF(F$4="","",F10)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="G56" s="191" t="str">
-        <f>IF(G$4="","",G10)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="H56" s="191" t="str">
-        <f>IF(H$4="","",H10)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="I56" s="191" t="str">
-        <f>IF(I$4="","",I10)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J56" s="191" t="str">
-        <f>IF(J$4="","",J10)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="K56" s="191" t="str">
-        <f>IF(K$4="","",K10)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="L56" s="191" t="str">
-        <f>IF(L$4="","",L10)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="M56" s="191" t="str">
-        <f>IF(M$4="","",M10)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -6375,47 +6630,47 @@
         <v>160</v>
       </c>
       <c r="C57" s="191">
-        <f>IF(C$4="","",C11)</f>
+        <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
         <v>0</v>
       </c>
       <c r="D57" s="191" t="str">
-        <f>IF(D$4="","",D11)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="E57" s="191" t="str">
-        <f>IF(E$4="","",E11)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="F57" s="191" t="str">
-        <f>IF(F$4="","",F11)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="G57" s="191" t="str">
-        <f>IF(G$4="","",G11)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="H57" s="191" t="str">
-        <f>IF(H$4="","",H11)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="I57" s="191" t="str">
-        <f>IF(I$4="","",I11)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="J57" s="191" t="str">
-        <f>IF(J$4="","",J11)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K57" s="191" t="str">
-        <f>IF(K$4="","",K11)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="L57" s="191" t="str">
-        <f>IF(L$4="","",L11)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="M57" s="191" t="str">
-        <f>IF(M$4="","",M11)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
     </row>
@@ -6428,43 +6683,43 @@
         <v>247678</v>
       </c>
       <c r="D58" s="191" t="str">
-        <f t="shared" ref="D58:M58" si="15">IF(D$4="","",D44-D55-D56-D57)</f>
+        <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
         <v/>
       </c>
       <c r="E58" s="191" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="F58" s="191" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="G58" s="191" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="H58" s="191" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="I58" s="191" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J58" s="191" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="K58" s="191" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="L58" s="191" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="M58" s="191" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -6479,47 +6734,47 @@
         <v>48</v>
       </c>
       <c r="C61" s="186">
-        <f>IF(C$4="","",-C19)</f>
+        <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
         <v>-463424</v>
       </c>
       <c r="D61" s="186" t="str">
-        <f>IF(D$4="","",-D19)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="E61" s="186" t="str">
-        <f>IF(E$4="","",-E19)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="F61" s="186" t="str">
-        <f>IF(F$4="","",-F19)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="G61" s="186" t="str">
-        <f>IF(G$4="","",-G19)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="H61" s="186" t="str">
-        <f>IF(H$4="","",-H19)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="I61" s="186" t="str">
-        <f>IF(I$4="","",-I19)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J61" s="186" t="str">
-        <f>IF(J$4="","",-J19)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K61" s="186" t="str">
-        <f>IF(K$4="","",-K19)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="L61" s="186" t="str">
-        <f>IF(L$4="","",-L19)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="M61" s="186" t="str">
-        <f>IF(M$4="","",-M19)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -6528,47 +6783,47 @@
         <v>54</v>
       </c>
       <c r="C62" s="186">
-        <f>IF(C$4="","",-C20)</f>
+        <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
         <v>-676387</v>
       </c>
       <c r="D62" s="186" t="str">
-        <f>IF(D$4="","",-D20)</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="E62" s="186" t="str">
-        <f>IF(E$4="","",-E20)</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="F62" s="186" t="str">
-        <f>IF(F$4="","",-F20)</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="G62" s="186" t="str">
-        <f>IF(G$4="","",-G20)</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="H62" s="186" t="str">
-        <f>IF(H$4="","",-H20)</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="I62" s="186" t="str">
-        <f>IF(I$4="","",-I20)</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J62" s="186" t="str">
-        <f>IF(J$4="","",-J20)</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K62" s="186" t="str">
-        <f>IF(K$4="","",-K20)</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="L62" s="186" t="str">
-        <f>IF(L$4="","",-L20)</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="M62" s="186" t="str">
-        <f>IF(M$4="","",-M20)</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -6577,47 +6832,47 @@
         <v>53</v>
       </c>
       <c r="C63" s="186">
-        <f>IF(C$4="","",-C21)</f>
+        <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
         <v>-626583</v>
       </c>
       <c r="D63" s="186" t="str">
-        <f>IF(D$4="","",-D21)</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="E63" s="186" t="str">
-        <f>IF(E$4="","",-E21)</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="F63" s="186" t="str">
-        <f>IF(F$4="","",-F21)</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="G63" s="186" t="str">
-        <f>IF(G$4="","",-G21)</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="H63" s="186" t="str">
-        <f>IF(H$4="","",-H21)</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="I63" s="186" t="str">
-        <f>IF(I$4="","",-I21)</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="J63" s="186" t="str">
-        <f>IF(J$4="","",-J21)</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K63" s="186" t="str">
-        <f>IF(K$4="","",-K21)</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L63" s="186" t="str">
-        <f>IF(L$4="","",-L21)</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="M63" s="186" t="str">
-        <f>IF(M$4="","",-M21)</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -6626,47 +6881,47 @@
         <v>36</v>
       </c>
       <c r="C64" s="75">
-        <f>IF(C$4="","",C25)</f>
+        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C25)</f>
         <v>1.36</v>
       </c>
       <c r="D64" s="75" t="str">
-        <f>IF(D$4="","",D25)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="E64" s="75" t="str">
-        <f>IF(E$4="","",E25)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="F64" s="75" t="str">
-        <f>IF(F$4="","",F25)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="G64" s="75" t="str">
-        <f>IF(G$4="","",G25)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="H64" s="75" t="str">
-        <f>IF(H$4="","",H25)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="I64" s="75" t="str">
-        <f>IF(I$4="","",I25)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J64" s="75" t="str">
-        <f>IF(J$4="","",J25)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="K64" s="75" t="str">
-        <f>IF(K$4="","",K25)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="L64" s="75" t="str">
-        <f>IF(L$4="","",L25)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M64" s="75" t="str">
-        <f>IF(M$4="","",M25)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -6681,47 +6936,47 @@
         <v>Sales</v>
       </c>
       <c r="C67" s="94" t="str">
-        <f t="shared" ref="C67:M67" si="16">IF(D$36="","",C36/D36-1)</f>
+        <f t="shared" ref="C67:M67" si="33">IF(D$36="","",C36/D36-1)</f>
         <v/>
       </c>
       <c r="D67" s="94" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="E67" s="94" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="F67" s="94" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G67" s="94" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="H67" s="94" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="I67" s="94" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="J67" s="94" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K67" s="94" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L67" s="94" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M67" s="94" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
     </row>
@@ -6731,47 +6986,47 @@
         <v>Operating EBIT</v>
       </c>
       <c r="C68" s="104" t="str">
-        <f t="shared" ref="C68:M68" si="17">IF(D$36="","",C37/D37-1)</f>
+        <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C37/D37-1)</f>
         <v/>
       </c>
       <c r="D68" s="104" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="E68" s="104" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="F68" s="104" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="G68" s="104" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H68" s="104" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="I68" s="104" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J68" s="104" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="K68" s="104" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="L68" s="104" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M68" s="104" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
     </row>
@@ -6781,47 +7036,47 @@
         <v>Other Non-operating Income</v>
       </c>
       <c r="C69" s="94" t="str">
-        <f t="shared" ref="C69:M69" si="18">IF(D$36="","",C38/D38-1)</f>
+        <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C38/D38-1)</f>
         <v/>
       </c>
       <c r="D69" s="94" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="E69" s="94" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="F69" s="94" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="G69" s="94" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="H69" s="94" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I69" s="94" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="J69" s="94" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K69" s="94" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="L69" s="94" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="M69" s="94" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
     </row>
@@ -6831,47 +7086,47 @@
         <v>Reported Net Income</v>
       </c>
       <c r="C70" s="104" t="str">
-        <f t="shared" ref="C70:M70" si="19">IF(D$36="","",C39/D39-1)</f>
+        <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C39/D39-1)</f>
         <v/>
       </c>
       <c r="D70" s="104" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="E70" s="104" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="F70" s="104" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="G70" s="104" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="H70" s="104" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="I70" s="104" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J70" s="104" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K70" s="104" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="L70" s="104" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="M70" s="104" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -6885,43 +7140,43 @@
         <v/>
       </c>
       <c r="D71" s="94" t="str">
-        <f t="shared" ref="D71:M71" si="20">IF(E$36="","",D64/E64-1)</f>
+        <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D64/E64-1)</f>
         <v/>
       </c>
       <c r="E71" s="94" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="F71" s="94" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="G71" s="94" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="H71" s="94" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="I71" s="94" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="J71" s="94" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K71" s="94" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="L71" s="94" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="M71" s="94" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -6956,43 +7211,43 @@
         <v>16854064</v>
       </c>
       <c r="D75" s="78" t="str">
-        <f t="shared" ref="D75:M75" si="21">IF(D$4="","",D78+D79)</f>
+        <f t="shared" ref="D75:M75" si="38">IF(D$4="","",D78+D79)</f>
         <v/>
       </c>
       <c r="E75" s="78" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="F75" s="78" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="G75" s="78" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="H75" s="78" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="I75" s="78" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J75" s="78" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="K75" s="78" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="L75" s="78" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="M75" s="78" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -7001,27 +7256,27 @@
         <v>87</v>
       </c>
       <c r="C76" s="74">
-        <f t="shared" ref="C76:H77" si="22">IF(C$4="","",C28)</f>
+        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C28)</f>
         <v>0</v>
       </c>
       <c r="D76" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="E76" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="F76" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="G76" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="H76" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="I76" s="96"/>
@@ -7035,27 +7290,27 @@
         <v>88</v>
       </c>
       <c r="C77" s="74">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="D77" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="E77" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="F77" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="G77" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="H77" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="I77" s="96"/>
@@ -7069,47 +7324,47 @@
         <v>40</v>
       </c>
       <c r="C78" s="58">
-        <f t="shared" ref="C78:M78" si="23">IF(C$4="","",C30)</f>
+        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C30)</f>
         <v>3990166</v>
       </c>
       <c r="D78" s="58" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="E78" s="58" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="F78" s="58" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="G78" s="58" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="H78" s="58" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="I78" s="58" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J78" s="58" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="K78" s="58" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="L78" s="58" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="M78" s="58" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -7118,47 +7373,47 @@
         <v>30</v>
       </c>
       <c r="C79" s="58">
-        <f t="shared" ref="C79:M79" si="24">IF(C$4="","",C31)</f>
+        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C31)</f>
         <v>12863898</v>
       </c>
       <c r="D79" s="58" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="E79" s="58" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="F79" s="58" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="G79" s="58" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="H79" s="58" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="I79" s="58" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="J79" s="58" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K79" s="58" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="L79" s="58" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="M79" s="58" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
@@ -7944,13 +8199,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C45" s="267" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="209" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F45" s="293" t="s">
         <v>60</v>
@@ -7958,7 +8213,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C46" s="191">
         <f>G29</f>
@@ -8111,7 +8366,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="161" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C61" s="268" t="s">
         <v>139</v>
@@ -8134,7 +8389,7 @@
         <v>-2.0915594459950692E-3</v>
       </c>
       <c r="F62" s="289" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8156,7 +8411,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F65" s="293" t="s">
         <v>60</v>
@@ -8223,7 +8478,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="291" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C72" s="267" t="s">
         <v>97</v>
@@ -8235,7 +8490,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8246,12 +8501,12 @@
         <v>-1187304.6396666665</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="294" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
@@ -8262,12 +8517,12 @@
         <v>1.6829876118070222</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C75" s="299"/>
       <c r="D75" s="298">
@@ -8275,12 +8530,12 @@
         <v>1187304.6396666665</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C76" s="297"/>
       <c r="D76" s="333">
@@ -8288,7 +8543,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8364,7 +8619,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8375,15 +8630,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="D85" s="276" t="s">
         <v>301</v>
-      </c>
-      <c r="D85" s="276" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8400,7 +8655,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8434,7 +8689,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
@@ -9305,7 +9560,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="307" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9330,7 +9585,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="307" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9658,7 +9913,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9718,7 +9973,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9842,7 +10097,7 @@
         <v>-254107</v>
       </c>
       <c r="E33" s="306" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9900,7 +10155,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -10208,7 +10463,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="305" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10347,7 +10602,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
@@ -10402,7 +10657,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="329" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
@@ -10535,7 +10790,7 @@
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="E53" s="305" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10562,7 +10817,7 @@
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="E54" s="305" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10877,7 +11132,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="306" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -11438,7 +11693,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12117,7 +12372,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -14037,10 +14292,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="347" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="347"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14055,8 +14310,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="347"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14071,8 +14326,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14087,8 +14342,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15433,7 +15688,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C80" s="159" t="s">
         <v>107</v>
@@ -15505,7 +15760,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I2" s="284"/>
     </row>
@@ -15559,7 +15814,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="282">
@@ -15572,7 +15827,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15582,11 +15837,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="349" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 六福珠宝(0590.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
+      <c r="F7" s="349"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15607,8 +15862,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15629,8 +15884,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15640,8 +15895,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
+      <c r="E10" s="349"/>
+      <c r="F10" s="349"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15652,10 +15907,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="163" t="s">
-        <v>283</v>
-      </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
+        <v>282</v>
+      </c>
+      <c r="E11" s="349"/>
+      <c r="F11" s="349"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15673,8 +15928,8 @@
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
+      <c r="E12" s="349"/>
+      <c r="F12" s="349"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -15691,8 +15946,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
+      <c r="E13" s="349"/>
+      <c r="F13" s="349"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -15709,8 +15964,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="349"/>
+      <c r="F14" s="349"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15726,7 +15981,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -15736,25 +15991,25 @@
       <c r="C18" s="154">
         <v>5</v>
       </c>
-      <c r="E18" s="347" t="s">
-        <v>345</v>
-      </c>
-      <c r="F18" s="348"/>
+      <c r="E18" s="349" t="s">
+        <v>344</v>
+      </c>
+      <c r="F18" s="350"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="350"/>
+      <c r="F19" s="350"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>315</v>
-      </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+        <v>314</v>
+      </c>
+      <c r="E20" s="350"/>
+      <c r="F20" s="350"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
@@ -15764,12 +16019,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="350"/>
+      <c r="F21" s="350"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
@@ -15779,8 +16034,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="350"/>
+      <c r="F22" s="350"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
@@ -15800,8 +16055,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="E25" s="348"/>
+      <c r="F25" s="348"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -15811,8 +16066,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="E26" s="348"/>
+      <c r="F26" s="348"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -15826,8 +16081,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="348"/>
+      <c r="F27" s="348"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -15837,8 +16092,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="348"/>
+      <c r="F28" s="348"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
@@ -15858,8 +16113,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -15869,8 +16124,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="E32" s="348"/>
+      <c r="F32" s="348"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -15884,8 +16139,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="348"/>
+      <c r="F33" s="348"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -15895,8 +16150,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="E34" s="348"/>
+      <c r="F34" s="348"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
@@ -15916,8 +16171,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -15927,8 +16182,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="E38" s="348"/>
+      <c r="F38" s="348"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -15942,8 +16197,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="348"/>
+      <c r="F39" s="348"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -15954,8 +16209,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -16017,8 +16272,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="E49" s="348"/>
+      <c r="F49" s="348"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -16028,8 +16283,8 @@
         <v>-0.08</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -16043,8 +16298,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="348"/>
+      <c r="F51" s="348"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -16054,12 +16309,12 @@
         <v>0.02</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="E52" s="348"/>
+      <c r="F52" s="348"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E54" s="163" t="s">
         <v>151</v>
@@ -16075,8 +16330,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="E55" s="348"/>
+      <c r="F55" s="348"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -16086,8 +16341,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="E56" s="348"/>
+      <c r="F56" s="348"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -16101,8 +16356,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="348"/>
+      <c r="F57" s="348"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -16112,8 +16367,8 @@
         <v>0.02</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -16128,7 +16383,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F60" s="318">
         <f>Thesis!E20</f>
@@ -16137,7 +16392,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16146,10 +16401,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16161,7 +16416,7 @@
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16173,7 +16428,7 @@
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16189,20 +16444,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16212,19 +16467,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16234,14 +16489,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
@@ -16264,7 +16519,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16287,12 +16542,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C80" s="171">
         <f>Thesis!C123</f>
@@ -16346,12 +16601,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
@@ -16364,7 +16619,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -16376,7 +16631,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="326" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F89" s="323"/>
       <c r="G89" s="2"/>
@@ -16384,30 +16639,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="319" t="s">
+        <v>339</v>
+      </c>
+      <c r="F90" s="324" t="s">
         <v>340</v>
-      </c>
-      <c r="F90" s="324" t="s">
-        <v>341</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="320" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F91" s="324" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="321" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F92" s="325" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="322"/>

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20802F47-1D5C-4D80-A2D1-23D4EC2E0B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAAD931-CCEA-46A1-AC8B-04B64F444114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="415">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1805,14 +1805,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>六福珠宝</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0590.HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CNS_05</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2311,6 +2303,30 @@
   </si>
   <si>
     <t>Normalized FCFE/Market Cap =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0857.HK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国石油股份</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO/Net Income</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO/FCFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Change in Cash</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2338,7 +2354,7 @@
     <numFmt numFmtId="192" formatCode="0.0\x"/>
     <numFmt numFmtId="193" formatCode="0\x"/>
   </numFmts>
-  <fonts count="58" x14ac:knownFonts="1">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2771,6 +2787,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2978,7 +3001,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="351">
+  <cellXfs count="353">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3682,6 +3705,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4010,7 +4037,7 @@
         <v>42</v>
       </c>
       <c r="C1" s="44">
-        <v>45730</v>
+        <v>45754</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="337" t="s">
@@ -4037,22 +4064,22 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B4" s="45" t="str">
         <f>D5&amp;" Stock Information"</f>
-        <v>0590.HK Stock Information</v>
+        <v>0857.HK Stock Information</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C5" s="48" t="s">
-        <v>368</v>
+      <c r="C5" s="339" t="s">
+        <v>411</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>369</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4060,7 +4087,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>15.4</v>
+        <v>5.55</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4072,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="51">
-        <v>587107850</v>
+        <v>183020977818</v>
       </c>
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
@@ -4105,7 +4132,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>9041.4608900000003</v>
+        <v>1015766.4268899</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4115,13 +4142,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>379</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="341" t="s">
+        <v>377</v>
+      </c>
+      <c r="C12" s="341"/>
+      <c r="D12" s="341"/>
+      <c r="E12" s="341"/>
+      <c r="F12" s="341"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4136,7 +4163,7 @@
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
-        <v xml:space="preserve">Low Growth </v>
+        <v xml:space="preserve">Negative Growth </v>
       </c>
       <c r="E15" s="5"/>
     </row>
@@ -4145,7 +4172,7 @@
         <v>361</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>41</v>
+        <v>410</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4155,11 +4182,11 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1</v>
+        <v>0.94030000000000002</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>HKD</v>
+        <v>CNY/HKD</v>
       </c>
       <c r="E17" s="5"/>
     </row>
@@ -4168,7 +4195,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4188,7 +4215,7 @@
       </c>
       <c r="C20" s="258">
         <f>C129</f>
-        <v>16.361242554197645</v>
+        <v>6.9522077911095632</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4199,11 +4226,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22622690546409729</v>
+        <v>0.29981048955907563</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4214,7 +4241,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4223,22 +4250,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>380</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="B25" s="341" t="s">
+        <v>378</v>
+      </c>
+      <c r="C25" s="341"/>
+      <c r="D25" s="341"/>
+      <c r="E25" s="341"/>
+      <c r="F25" s="341"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="343" t="s">
         <v>353</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="343"/>
+      <c r="D26" s="343"/>
+      <c r="E26" s="343"/>
+      <c r="F26" s="343"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -4246,17 +4273,17 @@
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
-        <v>1000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="342" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="342"/>
+      <c r="D29" s="342"/>
+      <c r="E29" s="342"/>
+      <c r="F29" s="342"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4264,11 +4291,11 @@
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
-        <v>1876773</v>
+        <v>266372</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -4276,13 +4303,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="342" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="342"/>
+      <c r="D32" s="342"/>
+      <c r="E32" s="342"/>
+      <c r="F32" s="342"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4290,11 +4317,11 @@
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
-        <v>463424</v>
+        <v>229584</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
@@ -4303,21 +4330,21 @@
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
-        <v>-676387</v>
+        <v>-229584</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="342" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="342"/>
+      <c r="D36" s="342"/>
+      <c r="E36" s="342"/>
+      <c r="F36" s="342"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4325,21 +4352,21 @@
       </c>
       <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
-        <v>0</v>
+        <v>18538.000000000004</v>
       </c>
       <c r="D37" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="342" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="342"/>
+      <c r="D39" s="342"/>
+      <c r="E39" s="342"/>
+      <c r="F39" s="342"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4347,11 +4374,11 @@
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
-        <v>17217.595540639435</v>
+        <v>8177.2376941676157</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E40" s="327"/>
       <c r="F40" s="327"/>
@@ -4362,11 +4389,11 @@
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
-        <v>-59596</v>
+        <v>-24063</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E41" s="327"/>
       <c r="F41" s="327"/>
@@ -4377,11 +4404,11 @@
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
-        <v>-42378.404459360565</v>
+        <v>-15885.762305832384</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.35">
@@ -4395,21 +4422,21 @@
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
-        <v>0</v>
+        <v>-19147</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="342" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="342"/>
+      <c r="D47" s="342"/>
+      <c r="E47" s="342"/>
+      <c r="F47" s="342"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4417,21 +4444,21 @@
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
-        <v>-458598.64888515987</v>
+        <v>-67256.059423541898</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
+      <c r="B50" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C50" s="343"/>
-      <c r="D50" s="343"/>
-      <c r="E50" s="343"/>
-      <c r="F50" s="343"/>
+      <c r="C50" s="345"/>
+      <c r="D50" s="345"/>
+      <c r="E50" s="345"/>
+      <c r="F50" s="345"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4443,26 +4470,26 @@
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
+      <c r="B53" s="341" t="s">
         <v>357</v>
       </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="C53" s="341"/>
+      <c r="D53" s="341"/>
+      <c r="E53" s="341"/>
+      <c r="F53" s="341"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>381</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="341" t="s">
+        <v>379</v>
+      </c>
+      <c r="C54" s="341"/>
+      <c r="D54" s="341"/>
+      <c r="E54" s="341"/>
+      <c r="F54" s="341"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4470,11 +4497,11 @@
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
-        <v>1294904.5955406395</v>
+        <v>306997.23769416759</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
@@ -4483,20 +4510,20 @@
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
-        <v>1162832.9466554797</v>
+        <v>182621.17827062571</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C58" s="94">
-        <f>Normalized_FCF!C121</f>
-        <v>0.12861117918914977</v>
+        <f>Normalized_FCF!C125</f>
+        <v>0.16905332700711728</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4505,12 +4532,12 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>8.8311688311688313E-2</v>
+        <v>9.0061347106970835E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4523,22 +4550,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
-        <v>382</v>
-      </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="B63" s="341" t="s">
+        <v>380</v>
+      </c>
+      <c r="C63" s="341"/>
+      <c r="D63" s="341"/>
+      <c r="E63" s="341"/>
+      <c r="F63" s="341"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="343" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="343"/>
+      <c r="D64" s="343"/>
+      <c r="E64" s="343"/>
+      <c r="F64" s="343"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4591,27 +4618,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="338" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
-        <v>383</v>
-      </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="B73" s="341" t="s">
+        <v>381</v>
+      </c>
+      <c r="C73" s="341"/>
+      <c r="D73" s="341"/>
+      <c r="E73" s="341"/>
+      <c r="F73" s="341"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
-        <v>384</v>
-      </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="B74" s="341" t="s">
+        <v>382</v>
+      </c>
+      <c r="C74" s="341"/>
+      <c r="D74" s="341"/>
+      <c r="E74" s="341"/>
+      <c r="F74" s="341"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4627,7 +4654,7 @@
       </c>
       <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>24.757651993911335</v>
+        <v>11.728074561118762</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4636,7 +4663,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="253" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4648,13 +4675,13 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
-        <v>385</v>
-      </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="B81" s="341" t="s">
+        <v>383</v>
+      </c>
+      <c r="C81" s="341"/>
+      <c r="D81" s="341"/>
+      <c r="E81" s="341"/>
+      <c r="F81" s="341"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4667,13 +4694,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
+      <c r="B85" s="341" t="s">
         <v>358</v>
       </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="C85" s="341"/>
+      <c r="D85" s="341"/>
+      <c r="E85" s="341"/>
+      <c r="F85" s="341"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4681,11 +4708,11 @@
       </c>
       <c r="C86" s="191">
         <f>Valuation_Model!C7</f>
-        <v>2034922</v>
+        <v>245714</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
@@ -4694,7 +4721,7 @@
       </c>
       <c r="C87" s="254">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>3.4660105464438944</v>
+        <v>1.2623955841267334</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4712,11 +4739,11 @@
       </c>
       <c r="C90" s="191">
         <f>BS!C66</f>
-        <v>1998219</v>
+        <v>238880</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
@@ -4725,11 +4752,11 @@
       </c>
       <c r="C91" s="191">
         <f>Valuation_Model!C8</f>
-        <v>810914.36033333349</v>
+        <v>2536.5589373550902</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
@@ -4738,7 +4765,7 @@
       </c>
       <c r="C92" s="254">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.3812016997104255</v>
+        <v>1.3031983531236581E-2</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4756,11 +4783,11 @@
       </c>
       <c r="C95" s="191">
         <f>Valuation_Model!C9</f>
-        <v>92572.6</v>
+        <v>6352.8</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
@@ -4769,7 +4796,7 @@
       </c>
       <c r="C96" s="254">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.15767562978420405</v>
+        <v>3.2638541828468509E-2</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4777,13 +4804,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
-        <v>386</v>
-      </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
+      <c r="B98" s="341" t="s">
+        <v>384</v>
+      </c>
+      <c r="C98" s="341"/>
+      <c r="D98" s="341"/>
+      <c r="E98" s="341"/>
+      <c r="F98" s="341"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4791,7 +4818,7 @@
       </c>
       <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4800,7 +4827,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="253" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4809,13 +4836,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
-        <v>387</v>
-      </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
+      <c r="B104" s="342" t="s">
+        <v>385</v>
+      </c>
+      <c r="C104" s="342"/>
+      <c r="D104" s="342"/>
+      <c r="E104" s="342"/>
+      <c r="F104" s="342"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="266" t="s">
@@ -4849,11 +4876,11 @@
       </c>
       <c r="E107" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>28.13 HKD</v>
+        <v>13.02 HKD</v>
       </c>
       <c r="F107" s="265">
         <f>Valuation_Model!F74</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
@@ -4863,7 +4890,7 @@
       </c>
       <c r="C108" s="249">
         <f>Valuation_Model!C75</f>
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D108" s="250">
         <f>Valuation_Model!D75</f>
@@ -4871,11 +4898,11 @@
       </c>
       <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>24.87 HKD</v>
+        <v>10.89 HKD</v>
       </c>
       <c r="F108" s="252">
         <f>Valuation_Model!F75</f>
-        <v>0.192</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -4885,7 +4912,7 @@
       </c>
       <c r="C109" s="249">
         <f>Valuation_Model!C76</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D109" s="250">
         <f>Valuation_Model!D76</f>
@@ -4893,11 +4920,11 @@
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>23.63 HKD</v>
+        <v>10.51 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F76</f>
-        <v>0.57599999999999996</v>
+        <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
@@ -4907,7 +4934,7 @@
       </c>
       <c r="C110" s="249">
         <f>Valuation_Model!C77</f>
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="D110" s="250">
         <f>Valuation_Model!D77</f>
@@ -4915,11 +4942,11 @@
       </c>
       <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>20.93 HKD</v>
+        <v>8.77 HKD</v>
       </c>
       <c r="F110" s="252">
         <f>Valuation_Model!F77</f>
-        <v>0.192</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -4929,7 +4956,7 @@
       </c>
       <c r="C111" s="249">
         <f>Valuation_Model!C78</f>
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="D111" s="250">
         <f>Valuation_Model!D78</f>
@@ -4937,11 +4964,11 @@
       </c>
       <c r="E111" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>17.72 HKD</v>
+        <v>6.55 HKD</v>
       </c>
       <c r="F111" s="252">
         <f>Valuation_Model!F78</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
@@ -4950,7 +4977,7 @@
       </c>
       <c r="C113" s="247">
         <f>Scenarios!C60</f>
-        <v>23.321827133653532</v>
+        <v>10.1939957287823</v>
       </c>
       <c r="D113" s="242" t="str">
         <f>Market_currency</f>
@@ -4958,17 +4985,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="344" t="s">
-        <v>390</v>
-      </c>
-      <c r="C115" s="344"/>
-      <c r="D115" s="344"/>
-      <c r="E115" s="344"/>
-      <c r="F115" s="344"/>
+      <c r="B115" s="346" t="s">
+        <v>388</v>
+      </c>
+      <c r="C115" s="346"/>
+      <c r="D115" s="346"/>
+      <c r="E115" s="346"/>
+      <c r="F115" s="346"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4977,22 +5004,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="342" t="s">
-        <v>388</v>
-      </c>
-      <c r="C119" s="342"/>
-      <c r="D119" s="342"/>
-      <c r="E119" s="342"/>
-      <c r="F119" s="342"/>
+      <c r="B119" s="344" t="s">
+        <v>386</v>
+      </c>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
-        <v>389</v>
-      </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
+      <c r="B120" s="341" t="s">
+        <v>387</v>
+      </c>
+      <c r="C120" s="341"/>
+      <c r="D120" s="341"/>
+      <c r="E120" s="341"/>
+      <c r="F120" s="341"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
@@ -5023,7 +5050,7 @@
       </c>
       <c r="C124" s="243">
         <f>Scenarios!C77</f>
-        <v>1.36</v>
+        <v>0.49984047644368812</v>
       </c>
       <c r="D124" s="242" t="str">
         <f>Market_currency</f>
@@ -5042,7 +5069,7 @@
       </c>
       <c r="C127" s="246">
         <f>Scenarios!C81</f>
-        <v>2.8648148148148147</v>
+        <v>1.0529047073235096</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5052,7 +5079,7 @@
       </c>
       <c r="C128" s="246">
         <f>Scenarios!C82</f>
-        <v>13.496427739382831</v>
+        <v>5.8993030837860534</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5061,11 +5088,11 @@
       </c>
       <c r="C129" s="245">
         <f>Scenarios!C83</f>
-        <v>16.361242554197645</v>
+        <v>6.9522077911095632</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
@@ -5074,12 +5101,12 @@
       </c>
       <c r="C130" s="94">
         <f>Scenarios!F83</f>
-        <v>0.29845794412101279</v>
+        <v>0.31800954443405249</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A132" s="253" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
@@ -5088,98 +5115,98 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="346" t="s">
-        <v>396</v>
-      </c>
-      <c r="C134" s="339"/>
-      <c r="D134" s="339"/>
-      <c r="E134" s="339"/>
-      <c r="F134" s="339"/>
+      <c r="B134" s="348" t="s">
+        <v>394</v>
+      </c>
+      <c r="C134" s="341"/>
+      <c r="D134" s="341"/>
+      <c r="E134" s="341"/>
+      <c r="F134" s="341"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="240" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="343" t="s">
-        <v>400</v>
-      </c>
-      <c r="C137" s="343"/>
-      <c r="D137" s="343"/>
-      <c r="E137" s="343"/>
-      <c r="F137" s="343"/>
+      <c r="B137" s="345" t="s">
+        <v>398</v>
+      </c>
+      <c r="C137" s="345"/>
+      <c r="D137" s="345"/>
+      <c r="E137" s="345"/>
+      <c r="F137" s="345"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="244" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B139" s="244" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B140" s="244" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="340" t="s">
-        <v>401</v>
-      </c>
-      <c r="C143" s="340"/>
-      <c r="D143" s="340"/>
-      <c r="E143" s="340"/>
-      <c r="F143" s="340"/>
+      <c r="B143" s="342" t="s">
+        <v>399</v>
+      </c>
+      <c r="C143" s="342"/>
+      <c r="D143" s="342"/>
+      <c r="E143" s="342"/>
+      <c r="F143" s="342"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="345" t="s">
-        <v>402</v>
-      </c>
-      <c r="C146" s="345"/>
-      <c r="D146" s="345"/>
-      <c r="E146" s="345"/>
-      <c r="F146" s="345"/>
+      <c r="B146" s="347" t="s">
+        <v>400</v>
+      </c>
+      <c r="C146" s="347"/>
+      <c r="D146" s="347"/>
+      <c r="E146" s="347"/>
+      <c r="F146" s="347"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="345" t="s">
-        <v>403</v>
-      </c>
-      <c r="C147" s="345"/>
-      <c r="D147" s="345"/>
-      <c r="E147" s="345"/>
-      <c r="F147" s="345"/>
+      <c r="B147" s="347" t="s">
+        <v>401</v>
+      </c>
+      <c r="C147" s="347"/>
+      <c r="D147" s="347"/>
+      <c r="E147" s="347"/>
+      <c r="F147" s="347"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B150" s="244" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B151" s="244" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B152" s="244" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -5213,7 +5240,7 @@
     <mergeCell ref="B63:F63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5225,7 +5252,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="87" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5234,7 +5261,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M79"/>
+  <dimension ref="B1:M80"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
@@ -5246,50 +5273,50 @@
     <row r="1" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B1" s="92" t="str">
         <f>Thesis!C16</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="C1" s="107">
-        <v>45382</v>
+        <v>45291</v>
       </c>
       <c r="D1" s="38">
         <f>EOMONTH(EDATE(C1,-12),0)</f>
-        <v>45016</v>
+        <v>44926</v>
       </c>
       <c r="E1" s="38">
         <f t="shared" ref="E1:M1" si="0">EOMONTH(EDATE(D1,-12),0)</f>
-        <v>44651</v>
+        <v>44561</v>
       </c>
       <c r="F1" s="38">
         <f t="shared" si="0"/>
-        <v>44286</v>
+        <v>44196</v>
       </c>
       <c r="G1" s="38">
         <f t="shared" si="0"/>
-        <v>43921</v>
+        <v>43830</v>
       </c>
       <c r="H1" s="38">
         <f t="shared" si="0"/>
-        <v>43555</v>
+        <v>43465</v>
       </c>
       <c r="I1" s="38">
         <f t="shared" si="0"/>
-        <v>43190</v>
+        <v>43100</v>
       </c>
       <c r="J1" s="38">
         <f t="shared" si="0"/>
-        <v>42825</v>
+        <v>42735</v>
       </c>
       <c r="K1" s="38">
         <f t="shared" si="0"/>
-        <v>42460</v>
+        <v>42369</v>
       </c>
       <c r="L1" s="38">
         <f t="shared" si="0"/>
-        <v>42094</v>
+        <v>42004</v>
       </c>
       <c r="M1" s="38">
         <f t="shared" si="0"/>
-        <v>41729</v>
+        <v>41639</v>
       </c>
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
@@ -5313,7 +5340,7 @@
         <v>27</v>
       </c>
       <c r="C3" s="109">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
@@ -5321,7 +5348,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="193">
-        <v>15325962</v>
+        <v>3011012</v>
       </c>
       <c r="D4" s="184"/>
       <c r="E4" s="184"/>
@@ -5339,7 +5366,7 @@
         <v>44</v>
       </c>
       <c r="C5" s="193">
-        <v>11151623</v>
+        <v>2302385</v>
       </c>
       <c r="D5" s="184"/>
       <c r="E5" s="184"/>
@@ -5357,7 +5384,7 @@
         <v>55</v>
       </c>
       <c r="C6" s="193">
-        <v>2297566</v>
+        <v>420298</v>
       </c>
       <c r="D6" s="184"/>
       <c r="E6" s="184"/>
@@ -5375,7 +5402,7 @@
         <v>62</v>
       </c>
       <c r="C7" s="194">
-        <v>2043459</v>
+        <v>70260</v>
       </c>
       <c r="D7" s="192"/>
       <c r="E7" s="192"/>
@@ -5392,7 +5419,9 @@
       <c r="B8" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="193"/>
+      <c r="C8" s="193">
+        <v>21957</v>
+      </c>
       <c r="D8" s="184"/>
       <c r="E8" s="184"/>
       <c r="F8" s="184"/>
@@ -5409,7 +5438,7 @@
         <v>161</v>
       </c>
       <c r="C9" s="193">
-        <v>639</v>
+        <v>18538</v>
       </c>
       <c r="D9" s="184"/>
       <c r="E9" s="184"/>
@@ -5426,7 +5455,9 @@
       <c r="B10" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="193"/>
+      <c r="C10" s="184">
+        <v>0</v>
+      </c>
       <c r="D10" s="184"/>
       <c r="E10" s="184"/>
       <c r="F10" s="184"/>
@@ -5442,7 +5473,9 @@
       <c r="B11" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="193"/>
+      <c r="C11" s="193">
+        <v>0</v>
+      </c>
       <c r="D11" s="184"/>
       <c r="E11" s="184"/>
       <c r="F11" s="184"/>
@@ -5459,7 +5492,7 @@
         <v>39</v>
       </c>
       <c r="C12" s="193">
-        <v>59596</v>
+        <v>24063</v>
       </c>
       <c r="D12" s="184"/>
       <c r="E12" s="184"/>
@@ -5477,7 +5510,7 @@
         <v>68</v>
       </c>
       <c r="C13" s="193">
-        <v>28977</v>
+        <v>8265</v>
       </c>
       <c r="D13" s="184"/>
       <c r="E13" s="184"/>
@@ -5495,7 +5528,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="193">
-        <v>327166</v>
+        <v>57167</v>
       </c>
       <c r="D14" s="184"/>
       <c r="E14" s="184"/>
@@ -5513,7 +5546,7 @@
         <v>43</v>
       </c>
       <c r="C15" s="195">
-        <v>1767305</v>
+        <v>180291</v>
       </c>
       <c r="D15" s="185"/>
       <c r="E15" s="185"/>
@@ -5531,7 +5564,7 @@
         <v>45</v>
       </c>
       <c r="C16" s="193">
-        <v>-9467</v>
+        <v>19147</v>
       </c>
       <c r="D16" s="184"/>
       <c r="E16" s="184"/>
@@ -5555,7 +5588,7 @@
         <v>48</v>
       </c>
       <c r="C19" s="184">
-        <v>463424</v>
+        <v>229584</v>
       </c>
       <c r="D19" s="184"/>
       <c r="E19" s="184"/>
@@ -5573,7 +5606,7 @@
         <v>54</v>
       </c>
       <c r="C20" s="184">
-        <v>676387</v>
+        <v>115297</v>
       </c>
       <c r="D20" s="184"/>
       <c r="E20" s="184"/>
@@ -5591,7 +5624,7 @@
         <v>53</v>
       </c>
       <c r="C21" s="184">
-        <v>626583</v>
+        <v>31061</v>
       </c>
       <c r="D21" s="184"/>
       <c r="E21" s="184"/>
@@ -5606,9 +5639,11 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>391</v>
-      </c>
-      <c r="C22" s="184"/>
+        <v>389</v>
+      </c>
+      <c r="C22" s="184">
+        <v>456596</v>
+      </c>
       <c r="D22" s="184"/>
       <c r="E22" s="184"/>
       <c r="F22" s="184"/>
@@ -5622,9 +5657,11 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>393</v>
-      </c>
-      <c r="C23" s="184"/>
+        <v>391</v>
+      </c>
+      <c r="C23" s="184">
+        <v>-255789</v>
+      </c>
       <c r="D23" s="184"/>
       <c r="E23" s="184"/>
       <c r="F23" s="184"/>
@@ -5638,9 +5675,11 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>392</v>
-      </c>
-      <c r="C24" s="184"/>
+        <v>390</v>
+      </c>
+      <c r="C24" s="184">
+        <v>-146572</v>
+      </c>
       <c r="D24" s="184"/>
       <c r="E24" s="184"/>
       <c r="F24" s="184"/>
@@ -5658,7 +5697,8 @@
         <v>Dividend per share (HKD)</v>
       </c>
       <c r="C25" s="39">
-        <v>1.36</v>
+        <f>(0.25+0.22)/Exchange_Rate</f>
+        <v>0.49984047644368812</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -5681,7 +5721,10 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="186"/>
+      <c r="C28" s="184">
+        <f>68761+31090</f>
+        <v>99851</v>
+      </c>
       <c r="D28" s="184"/>
       <c r="E28" s="184"/>
       <c r="F28" s="184"/>
@@ -5697,7 +5740,9 @@
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="186"/>
+      <c r="C29" s="184">
+        <v>180533</v>
+      </c>
       <c r="D29" s="184"/>
       <c r="E29" s="184"/>
       <c r="F29" s="184"/>
@@ -5714,7 +5759,7 @@
         <v>40</v>
       </c>
       <c r="C30" s="185">
-        <v>3990166</v>
+        <v>1122089</v>
       </c>
       <c r="D30" s="185"/>
       <c r="E30" s="185"/>
@@ -5732,7 +5777,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="185">
-        <v>12863898</v>
+        <v>1630621</v>
       </c>
       <c r="D31" s="185"/>
       <c r="E31" s="185"/>
@@ -5749,7 +5794,9 @@
       <c r="B32" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="184"/>
+      <c r="C32" s="184">
+        <v>184211</v>
+      </c>
       <c r="D32" s="184"/>
       <c r="E32" s="184"/>
       <c r="F32" s="184"/>
@@ -5788,7 +5835,7 @@
       </c>
       <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
-        <v>15325962</v>
+        <v>3011012</v>
       </c>
       <c r="D36" s="186" t="str">
         <f t="shared" si="1"/>
@@ -5837,7 +5884,7 @@
       </c>
       <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
-        <v>-11151623</v>
+        <v>-2302385</v>
       </c>
       <c r="D37" s="186" t="str">
         <f t="shared" si="2"/>
@@ -5886,7 +5933,7 @@
       </c>
       <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
-        <v>4174339</v>
+        <v>708627</v>
       </c>
       <c r="D38" s="187" t="str">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
@@ -5935,7 +5982,7 @@
       </c>
       <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
-        <v>-2297566</v>
+        <v>-420298</v>
       </c>
       <c r="D39" s="186" t="str">
         <f t="shared" si="13"/>
@@ -5984,7 +6031,7 @@
       </c>
       <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
-        <v>-2043459</v>
+        <v>-70260</v>
       </c>
       <c r="D40" s="188" t="str">
         <f t="shared" si="14"/>
@@ -6033,7 +6080,7 @@
       </c>
       <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
-        <v>-254107</v>
+        <v>-350038</v>
       </c>
       <c r="D41" s="188" t="str">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
@@ -6082,7 +6129,7 @@
       </c>
       <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
-        <v>0</v>
+        <v>-21957</v>
       </c>
       <c r="D42" s="186" t="str">
         <f t="shared" si="16"/>
@@ -6131,7 +6178,7 @@
       </c>
       <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
-        <v>1876773</v>
+        <v>266372</v>
       </c>
       <c r="D43" s="189" t="str">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
@@ -6180,7 +6227,7 @@
       </c>
       <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
-        <v>248317</v>
+        <v>-13116</v>
       </c>
       <c r="D44" s="190" t="str">
         <f t="shared" si="18"/>
@@ -6229,7 +6276,7 @@
       </c>
       <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
-        <v>-30619</v>
+        <v>-15798</v>
       </c>
       <c r="D45" s="191" t="str">
         <f t="shared" si="19"/>
@@ -6278,7 +6325,7 @@
       </c>
       <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
-        <v>-327166</v>
+        <v>-57167</v>
       </c>
       <c r="D46" s="186" t="str">
         <f t="shared" si="20"/>
@@ -6327,7 +6374,7 @@
       </c>
       <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
-        <v>1767305</v>
+        <v>180291</v>
       </c>
       <c r="D47" s="189" t="str">
         <f t="shared" si="21"/>
@@ -6376,7 +6423,7 @@
       </c>
       <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
-        <v>0</v>
+        <v>-19147</v>
       </c>
       <c r="D48" s="186" t="str">
         <f t="shared" si="22"/>
@@ -6430,7 +6477,7 @@
       </c>
       <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
-        <v>-59596</v>
+        <v>-24063</v>
       </c>
       <c r="D51" s="186" t="str">
         <f t="shared" si="23"/>
@@ -6479,7 +6526,7 @@
       </c>
       <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
-        <v>28977</v>
+        <v>8265</v>
       </c>
       <c r="D52" s="186" t="str">
         <f t="shared" si="24"/>
@@ -6533,7 +6580,7 @@
       </c>
       <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
-        <v>639</v>
+        <v>18538</v>
       </c>
       <c r="D55" s="191" t="str">
         <f t="shared" si="25"/>
@@ -6680,7 +6727,7 @@
       </c>
       <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
-        <v>247678</v>
+        <v>-31654</v>
       </c>
       <c r="D58" s="191" t="str">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
@@ -6735,7 +6782,7 @@
       </c>
       <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
-        <v>-463424</v>
+        <v>-229584</v>
       </c>
       <c r="D61" s="186" t="str">
         <f t="shared" si="29"/>
@@ -6784,7 +6831,7 @@
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
-        <v>-676387</v>
+        <v>-115297</v>
       </c>
       <c r="D62" s="186" t="str">
         <f t="shared" si="30"/>
@@ -6833,7 +6880,7 @@
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
-        <v>-626583</v>
+        <v>-31061</v>
       </c>
       <c r="D63" s="186" t="str">
         <f t="shared" si="31"/>
@@ -6877,440 +6924,455 @@
       </c>
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B64" s="24" t="s">
+      <c r="B64" s="27" t="s">
+        <v>414</v>
+      </c>
+      <c r="C64" s="186">
+        <f>IF(C$4="","",C22+C23+C24)</f>
+        <v>54235</v>
+      </c>
+      <c r="D64" s="186" t="str">
+        <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
+        <v/>
+      </c>
+      <c r="E64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="F64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="G64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="H64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="I64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="J64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="K64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="L64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="M64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C64" s="75">
-        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C25)</f>
-        <v>1.36</v>
-      </c>
-      <c r="D64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="E64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="F64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="G64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="H64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="I64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="J64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="K64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="L64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B66" s="93" t="s">
+      <c r="C65" s="75">
+        <f t="shared" ref="C65:M65" si="33">IF(C$4="","",C25)</f>
+        <v>0.49984047644368812</v>
+      </c>
+      <c r="D65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="F65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="G65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="H65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="I65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="J65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="K65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="L65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="M65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B67" s="93" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B67" s="1" t="str">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
       </c>
-      <c r="C67" s="94" t="str">
-        <f t="shared" ref="C67:M67" si="33">IF(D$36="","",C36/D36-1)</f>
-        <v/>
-      </c>
-      <c r="D67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="E67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="F67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="G67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="H67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="I67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="J67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="K67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="L67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="M67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B68" s="82" t="str">
+      <c r="C68" s="94" t="str">
+        <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C36/D36-1)</f>
+        <v/>
+      </c>
+      <c r="D68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="E68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="F68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="G68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="H68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="I68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="J68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="K68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="L68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="M68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B69" s="82" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
       </c>
-      <c r="C68" s="104" t="str">
-        <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C37/D37-1)</f>
-        <v/>
-      </c>
-      <c r="D68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="E68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="F68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="G68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="H68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="I68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="J68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="K68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="L68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="M68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B69" s="1" t="str">
+      <c r="C69" s="104" t="str">
+        <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C37/D37-1)</f>
+        <v/>
+      </c>
+      <c r="D69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="E69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="F69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="G69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="H69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="I69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="J69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="K69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="L69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="M69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B70" s="1" t="str">
         <f>B58</f>
         <v>Other Non-operating Income</v>
       </c>
-      <c r="C69" s="94" t="str">
-        <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C38/D38-1)</f>
-        <v/>
-      </c>
-      <c r="D69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="E69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="F69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="G69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="H69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="I69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="J69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="L69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="M69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B70" s="82" t="str">
+      <c r="C70" s="94" t="str">
+        <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C38/D38-1)</f>
+        <v/>
+      </c>
+      <c r="D70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="E70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="F70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="G70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="H70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="I70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="J70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="K70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="L70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="M70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B71" s="82" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
       </c>
-      <c r="C70" s="104" t="str">
-        <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C39/D39-1)</f>
-        <v/>
-      </c>
-      <c r="D70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="E70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="F70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="G70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="H70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="I70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="J70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="K70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="L70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="M70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B71" s="1" t="str">
+      <c r="C71" s="104" t="str">
+        <f t="shared" ref="C71:M71" si="37">IF(D$36="","",C39/D39-1)</f>
+        <v/>
+      </c>
+      <c r="D71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="E71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="F71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="G71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="H71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="I71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="J71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="K71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="L71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="M71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B72" s="1" t="str">
         <f>B48</f>
         <v>Non-controling Interests</v>
       </c>
-      <c r="C71" s="94" t="str">
-        <f>IF(D$36="","",C64/D64-1)</f>
-        <v/>
-      </c>
-      <c r="D71" s="94" t="str">
-        <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D64/E64-1)</f>
-        <v/>
-      </c>
-      <c r="E71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="F71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="G71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="H71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="I71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="J71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="K71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="L71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="M71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="B73" s="36" t="s">
+      <c r="C72" s="94" t="str">
+        <f>IF(D$36="","",C65/D65-1)</f>
+        <v/>
+      </c>
+      <c r="D72" s="94" t="str">
+        <f t="shared" ref="D72:M72" si="38">IF(E$36="","",D65/E65-1)</f>
+        <v/>
+      </c>
+      <c r="E72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="F72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="G72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="H72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="I72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="J72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="K72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="L72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="M72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B74" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="37"/>
-      <c r="K73" s="37"/>
-      <c r="L73" s="37"/>
-      <c r="M73" s="37"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B74" s="16" t="s">
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="37"/>
+      <c r="I74" s="37"/>
+      <c r="J74" s="37"/>
+      <c r="K74" s="37"/>
+      <c r="L74" s="37"/>
+      <c r="M74" s="37"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C74" s="9"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B75" s="26" t="s">
+      <c r="C75" s="9"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C75" s="78">
-        <f>IF(C$4="","",C78+C79)</f>
-        <v>16854064</v>
-      </c>
-      <c r="D75" s="78" t="str">
-        <f t="shared" ref="D75:M75" si="38">IF(D$4="","",D78+D79)</f>
-        <v/>
-      </c>
-      <c r="E75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="F75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="G75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="H75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="I75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="J75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="L75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="M75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B76" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" s="74">
-        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C28)</f>
-        <v>0</v>
-      </c>
-      <c r="D76" s="74" t="str">
+      <c r="C76" s="78">
+        <f>IF(C$4="","",C79+C80)</f>
+        <v>2752710</v>
+      </c>
+      <c r="D76" s="78" t="str">
+        <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
+        <v/>
+      </c>
+      <c r="E76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="E76" s="74" t="str">
+      <c r="F76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="F76" s="74" t="str">
+      <c r="G76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="G76" s="74" t="str">
+      <c r="H76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="H76" s="74" t="str">
+      <c r="I76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="I76" s="96"/>
-      <c r="J76" s="96"/>
-      <c r="K76" s="96"/>
-      <c r="L76" s="96"/>
-      <c r="M76" s="96"/>
+      <c r="J76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="L76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="M76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C77" s="74">
-        <f t="shared" si="39"/>
-        <v>0</v>
+        <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
+        <v>99851</v>
       </c>
       <c r="D77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="E77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="F77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="G77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="H77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="I77" s="96"/>
@@ -7320,61 +7382,46 @@
       <c r="M77" s="96"/>
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B78" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C78" s="58">
-        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C30)</f>
-        <v>3990166</v>
-      </c>
-      <c r="D78" s="58" t="str">
+      <c r="B78" s="95" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" s="74">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="E78" s="58" t="str">
+        <v>180533</v>
+      </c>
+      <c r="D78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="F78" s="58" t="str">
+      <c r="E78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="G78" s="58" t="str">
+      <c r="F78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="H78" s="58" t="str">
+      <c r="G78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I78" s="58" t="str">
+      <c r="H78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="J78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="K78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="L78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="I78" s="96"/>
+      <c r="J78" s="96"/>
+      <c r="K78" s="96"/>
+      <c r="L78" s="96"/>
+      <c r="M78" s="96"/>
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C79" s="58">
-        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C31)</f>
-        <v>12863898</v>
+        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
+        <v>1122089</v>
       </c>
       <c r="D79" s="58" t="str">
         <f t="shared" si="41"/>
@@ -7417,9 +7464,58 @@
         <v/>
       </c>
     </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B80" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" s="58">
+        <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
+        <v>1630621</v>
+      </c>
+      <c r="D80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="E80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="F80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="G80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="H80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="I80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="J80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="K80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="L80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="M80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
+  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
     <cfRule type="expression" dxfId="5" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
@@ -7429,7 +7525,7 @@
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36:M37 C61:M64">
+  <conditionalFormatting sqref="C36:M37 C61:M65">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
@@ -7473,7 +7569,7 @@
       </c>
       <c r="H1" s="110">
         <f>Data!C3</f>
-        <v>1000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7512,7 +7608,8 @@
         <v>24</v>
       </c>
       <c r="C4" s="19">
-        <v>265773</v>
+        <f>90108+11142+41629</f>
+        <v>142879</v>
       </c>
       <c r="D4" s="300">
         <v>0.6</v>
@@ -7522,7 +7619,7 @@
         <v>79</v>
       </c>
       <c r="G4" s="19">
-        <v>1998219</v>
+        <v>238880</v>
       </c>
       <c r="H4" s="300">
         <v>0.9</v>
@@ -7533,7 +7630,7 @@
         <v>33</v>
       </c>
       <c r="C5" s="19">
-        <v>0</v>
+        <v>11851</v>
       </c>
       <c r="D5" s="300">
         <v>0.6</v>
@@ -7554,7 +7651,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="19">
-        <v>9672256</v>
+        <v>182674</v>
       </c>
       <c r="D6" s="300">
         <v>0.5</v>
@@ -7585,7 +7682,7 @@
         <v>180</v>
       </c>
       <c r="G7" s="19">
-        <v>0</v>
+        <v>9895</v>
       </c>
       <c r="H7" s="300">
         <v>0.6</v>
@@ -7617,7 +7714,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="19">
-        <v>366595</v>
+        <v>24847</v>
       </c>
       <c r="D9" s="300">
         <v>0.1</v>
@@ -7638,7 +7735,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="19">
-        <v>29465</v>
+        <v>0</v>
       </c>
       <c r="D10" s="300">
         <v>0.9</v>
@@ -7650,7 +7747,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="19">
-        <v>0</v>
+        <v>61345</v>
       </c>
       <c r="D11" s="300">
         <v>0.05</v>
@@ -7663,22 +7760,22 @@
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
-        <v>10334089</v>
+        <v>423596</v>
       </c>
       <c r="D12" s="20">
         <f>C4*D4+C5*D5+C9*D9+C6*D6+C8*D8+C7*D7+C10*D10+C11*D11</f>
-        <v>5058769.8</v>
+        <v>189726.95</v>
       </c>
       <c r="F12" s="82" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
-        <v>1998219</v>
+        <v>248775</v>
       </c>
       <c r="H12" s="20">
         <f>G4*H4+G5*H5+G6*H6+G7*H7+G8*H8+G9*H9</f>
-        <v>1798397.1</v>
+        <v>220929</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7711,7 +7808,7 @@
         <v>74</v>
       </c>
       <c r="C15" s="19">
-        <v>103050</v>
+        <v>0</v>
       </c>
       <c r="D15" s="300">
         <v>0.4</v>
@@ -7760,7 +7857,7 @@
         <v>180</v>
       </c>
       <c r="G17" s="19">
-        <v>0</v>
+        <v>693</v>
       </c>
       <c r="H17" s="300">
         <v>0.6</v>
@@ -7780,7 +7877,8 @@
         <v>183</v>
       </c>
       <c r="G18" s="19">
-        <v>0</v>
+        <f>292606</f>
+        <v>292606</v>
       </c>
       <c r="H18" s="300">
         <v>0.1</v>
@@ -7791,7 +7889,8 @@
         <v>26</v>
       </c>
       <c r="C19" s="19">
-        <v>2522337</v>
+        <f>458868+831001+201156+123479+13153</f>
+        <v>1627657</v>
       </c>
       <c r="D19" s="300">
         <v>0.1</v>
@@ -7831,7 +7930,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="19">
-        <v>538321</v>
+        <v>91529</v>
       </c>
       <c r="D21" s="300">
         <v>0.05</v>
@@ -7840,7 +7939,7 @@
         <v>182</v>
       </c>
       <c r="G21" s="19">
-        <v>925726</v>
+        <v>0</v>
       </c>
       <c r="H21" s="300">
         <v>0.1</v>
@@ -7851,7 +7950,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="19">
-        <v>154648</v>
+        <v>24707</v>
       </c>
       <c r="D22" s="300">
         <v>0.9</v>
@@ -7863,7 +7962,8 @@
         <v>21</v>
       </c>
       <c r="C23" s="19">
-        <v>277674</v>
+        <f>7476+51258</f>
+        <v>58734</v>
       </c>
       <c r="D23" s="300">
         <v>0</v>
@@ -7876,22 +7976,22 @@
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
-        <v>3596030</v>
+        <v>1802627</v>
       </c>
       <c r="D24" s="20">
         <f>C15*D15+C16*D16+C18*D18+C17*D17+C19*D19+C20*D20+C21*D21+C22*D22+C23*D23</f>
-        <v>459552.95</v>
+        <v>189578.45</v>
       </c>
       <c r="F24" s="82" t="s">
         <v>72</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
-        <v>925726</v>
+        <v>293299</v>
       </c>
       <c r="H24" s="20">
         <f>G15*H15+G16*H16+G17*H17+G18*H18+G19*H19+G20*H20+G21*H21</f>
-        <v>92572.6</v>
+        <v>29676.400000000001</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7916,18 +8016,18 @@
         <v>5</v>
       </c>
       <c r="C27" s="19">
-        <v>1427805</v>
+        <v>40594</v>
       </c>
       <c r="F27" s="214" t="s">
         <v>30</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
-        <v>12863898</v>
+        <v>1678153</v>
       </c>
       <c r="H27" s="215">
         <f>H32-G30</f>
-        <v>3419126.45</v>
+        <v>-460233.19999999995</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7935,13 +8035,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="19">
-        <v>287697</v>
+        <v>0</v>
       </c>
       <c r="F28" s="216" t="s">
         <v>246</v>
       </c>
       <c r="G28" s="184">
-        <v>-26962</v>
+        <v>188249</v>
       </c>
       <c r="H28" s="215"/>
     </row>
@@ -7957,11 +8057,11 @@
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
-        <v>12890860</v>
+        <v>1489904</v>
       </c>
       <c r="H29" s="215">
         <f>H27-G28</f>
-        <v>3446088.45</v>
+        <v>-648482.19999999995</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7969,14 +8069,15 @@
         <v>8</v>
       </c>
       <c r="C30" s="19">
-        <v>0</v>
+        <f>4685+7139</f>
+        <v>11824</v>
       </c>
       <c r="F30" s="214" t="s">
         <v>23</v>
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
-        <v>3990166</v>
+        <v>1090144</v>
       </c>
       <c r="H30" s="215"/>
     </row>
@@ -7986,14 +8087,14 @@
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
-        <v>1715502</v>
+        <v>52418</v>
       </c>
       <c r="F31" s="217" t="s">
         <v>78</v>
       </c>
       <c r="G31" s="218">
         <f>C31+C40</f>
-        <v>2034922</v>
+        <v>245714</v>
       </c>
       <c r="H31" s="215"/>
     </row>
@@ -8003,18 +8104,18 @@
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
-        <v>1801307</v>
+        <v>664223</v>
       </c>
       <c r="F32" s="219" t="s">
         <v>76</v>
       </c>
       <c r="G32" s="220">
         <f>G35+G40</f>
-        <v>16854064</v>
+        <v>2768297</v>
       </c>
       <c r="H32" s="215">
         <f>H35+H40</f>
-        <v>7409292.4500000002</v>
+        <v>629910.80000000005</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8022,7 +8123,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="86">
-        <v>3516809</v>
+        <v>716641</v>
       </c>
       <c r="F33" s="221"/>
       <c r="G33" s="2"/>
@@ -8053,11 +8154,11 @@
       </c>
       <c r="G35" s="220">
         <f>C12+C24</f>
-        <v>13930119</v>
+        <v>2226223</v>
       </c>
       <c r="H35" s="227">
         <f>D12+D24</f>
-        <v>5518322.75</v>
+        <v>379305.4</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8065,14 +8166,15 @@
         <v>13</v>
       </c>
       <c r="C36" s="19">
-        <v>0</v>
+        <f>70126+11000</f>
+        <v>81126</v>
       </c>
       <c r="F36" s="217" t="s">
         <v>199</v>
       </c>
       <c r="G36" s="218">
         <f>C4+C15</f>
-        <v>368823</v>
+        <v>142879</v>
       </c>
       <c r="H36" s="222"/>
     </row>
@@ -8081,14 +8183,14 @@
         <v>14</v>
       </c>
       <c r="C37" s="19">
-        <v>0</v>
+        <v>112170</v>
       </c>
       <c r="F37" s="217" t="s">
         <v>200</v>
       </c>
       <c r="G37" s="218">
         <f>C6</f>
-        <v>9672256</v>
+        <v>182674</v>
       </c>
       <c r="H37" s="222"/>
     </row>
@@ -8097,7 +8199,7 @@
         <v>15</v>
       </c>
       <c r="C38" s="19">
-        <v>319420</v>
+        <v>0</v>
       </c>
       <c r="F38" s="217" t="s">
         <v>201</v>
@@ -8120,11 +8222,11 @@
       </c>
       <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
-        <v>2522337</v>
+        <v>1627657</v>
       </c>
       <c r="H39" s="215">
         <f>C7*D7+C17*D17+C19*D19+C20*D20</f>
-        <v>252233.7</v>
+        <v>162765.70000000001</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8133,18 +8235,18 @@
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
-        <v>319420</v>
+        <v>193296</v>
       </c>
       <c r="F40" s="226" t="s">
         <v>140</v>
       </c>
       <c r="G40" s="220">
         <f>G12+G24</f>
-        <v>2923945</v>
+        <v>542074</v>
       </c>
       <c r="H40" s="227">
         <f>H12+H24</f>
-        <v>1890969.7000000002</v>
+        <v>250605.4</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8153,18 +8255,18 @@
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
-        <v>153937</v>
+        <v>180207</v>
       </c>
       <c r="F41" s="217" t="s">
         <v>193</v>
       </c>
       <c r="G41" s="218">
         <f>C70</f>
-        <v>1998219</v>
+        <v>531486</v>
       </c>
       <c r="H41" s="227">
         <f>H40-H42</f>
-        <v>1798397.1</v>
+        <v>244252.6</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8172,18 +8274,18 @@
         <v>22</v>
       </c>
       <c r="C42" s="86">
-        <v>473357</v>
+        <v>373503</v>
       </c>
       <c r="F42" s="228" t="s">
         <v>194</v>
       </c>
       <c r="G42" s="229">
         <f>C82</f>
-        <v>925726</v>
+        <v>10588</v>
       </c>
       <c r="H42" s="230">
         <f>D82</f>
-        <v>92572.6</v>
+        <v>6352.8</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8217,11 +8319,11 @@
       </c>
       <c r="C46" s="191">
         <f>G29</f>
-        <v>12890860</v>
+        <v>1489904</v>
       </c>
       <c r="D46" s="191">
         <f>H29</f>
-        <v>3446088.45</v>
+        <v>-648482.19999999995</v>
       </c>
       <c r="F46" s="289"/>
     </row>
@@ -8232,11 +8334,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.956545121990789</v>
+        <v>7.6546237917772562</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>5.8696003638854428</v>
+        <v>-3.3316826296620832</v>
       </c>
       <c r="F47" s="289"/>
     </row>
@@ -8262,11 +8364,11 @@
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
-        <v>1.0842664509772892</v>
+        <v>0.9224468037181085</v>
       </c>
       <c r="D50" s="98">
         <f>G31/Normalized_FCF!G8</f>
-        <v>1.0842664509772892</v>
+        <v>0.9224468037181085</v>
       </c>
       <c r="F50" s="289"/>
     </row>
@@ -8277,7 +8379,7 @@
       <c r="C51" s="208"/>
       <c r="D51" s="94">
         <f>G29/G32</f>
-        <v>0.76485172952944758</v>
+        <v>0.5382023677372767</v>
       </c>
       <c r="F51" s="289"/>
     </row>
@@ -8302,11 +8404,11 @@
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
-        <v>0.13472770763839131</v>
+        <v>0.11965198454961611</v>
       </c>
       <c r="D54" s="94">
         <f>Normalized_FCF!G8/G35</f>
-        <v>0.13472770763839131</v>
+        <v>0.11965198454961611</v>
       </c>
       <c r="F54" s="289"/>
     </row>
@@ -8316,11 +8418,11 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
-        <v>0</v>
+        <v>3.4198282891265773E-2</v>
       </c>
       <c r="D55" s="94">
         <f>Normalized_FCF!G11/G40</f>
-        <v>2.1854036242131779E-4</v>
+        <v>3.4198282891265766E-2</v>
       </c>
       <c r="F55" s="289"/>
     </row>
@@ -8346,7 +8448,7 @@
       <c r="C58" s="101"/>
       <c r="D58" s="23">
         <f>Normalized_FCF!G9/BS!$G$39</f>
-        <v>0.1837280268259158</v>
+        <v>0.14105183094472606</v>
       </c>
       <c r="F58" s="5"/>
     </row>
@@ -8357,7 +8459,7 @@
       <c r="C59" s="101"/>
       <c r="D59" s="94">
         <f>G39/G32</f>
-        <v>0.14965749507062509</v>
+        <v>0.58796328573126366</v>
       </c>
       <c r="F59" s="289"/>
     </row>
@@ -8382,11 +8484,11 @@
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
-        <v>0</v>
+        <v>0.12634975139337837</v>
       </c>
       <c r="D62" s="94">
         <f>G28/G29</f>
-        <v>-2.0915594459950692E-3</v>
+        <v>0.12634975139337837</v>
       </c>
       <c r="F62" s="289" t="s">
         <v>276</v>
@@ -8423,11 +8525,11 @@
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
-        <v>1998219</v>
+        <v>238880</v>
       </c>
       <c r="D66" s="191">
         <f>C66-D75</f>
-        <v>810914.36033333349</v>
+        <v>2536.5589373550902</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8449,7 +8551,7 @@
       </c>
       <c r="C68" s="20">
         <f>G18</f>
-        <v>0</v>
+        <v>292606</v>
       </c>
       <c r="F68" s="289"/>
     </row>
@@ -8469,7 +8571,7 @@
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
-        <v>1998219</v>
+        <v>531486</v>
       </c>
       <c r="F70" s="289"/>
     </row>
@@ -8494,11 +8596,11 @@
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-1187304.6396666665</v>
+        <v>-236343.44106264491</v>
       </c>
       <c r="D73" s="191">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-1187304.6396666665</v>
+        <v>-236343.44106264491</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>365</v>
@@ -8510,11 +8612,11 @@
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
-        <v>1.6829876118070222</v>
+        <v>1.0107325125078581</v>
       </c>
       <c r="D74" s="295">
         <f>-$C$66/D73</f>
-        <v>1.6829876118070222</v>
+        <v>1.0107325125078581</v>
       </c>
       <c r="F74" s="289" t="s">
         <v>332</v>
@@ -8527,7 +8629,7 @@
       <c r="C75" s="299"/>
       <c r="D75" s="298">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1187304.6396666665</v>
+        <v>236343.44106264491</v>
       </c>
       <c r="F75" s="289" t="s">
         <v>366</v>
@@ -8567,11 +8669,11 @@
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
-        <v>0</v>
+        <v>10588</v>
       </c>
       <c r="D79" s="191">
         <f>G7*H7+G17*H17</f>
-        <v>0</v>
+        <v>6352.8</v>
       </c>
       <c r="F79" s="289"/>
     </row>
@@ -8595,11 +8697,11 @@
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
-        <v>925726</v>
+        <v>0</v>
       </c>
       <c r="D81" s="191">
         <f>G9*H9+G21*H21</f>
-        <v>92572.6</v>
+        <v>0</v>
       </c>
       <c r="F81" s="289"/>
     </row>
@@ -8609,11 +8711,11 @@
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
-        <v>925726</v>
+        <v>10588</v>
       </c>
       <c r="D82" s="83">
         <f>SUM(D79:D81)</f>
-        <v>92572.6</v>
+        <v>6352.8</v>
       </c>
       <c r="F82" s="289"/>
     </row>
@@ -8642,11 +8744,11 @@
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2034922</v>
+        <v>-231044.87420000002</v>
       </c>
       <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-3.4660105464438944</v>
+        <v>-1.2623955841267334</v>
       </c>
       <c r="E86" s="275" t="str">
         <f>Market_currency</f>
@@ -8659,11 +8761,11 @@
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>810914.36033333349</v>
+        <v>2385.1263687949913</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.3812016997104255</v>
+        <v>1.3031983531236581E-2</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8676,11 +8778,11 @@
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>92572.6</v>
+        <v>5973.53784</v>
       </c>
       <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.15767562978420405</v>
+        <v>3.2638541828468509E-2</v>
       </c>
       <c r="E88" s="275" t="str">
         <f>Market_currency</f>
@@ -8693,11 +8795,11 @@
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>-1131435.0396666664</v>
+        <v>-222686.20999120502</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>-1.9271332169492648</v>
+        <v>-1.2167250587670282</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -8717,7 +8819,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q804"/>
+  <dimension ref="A1:Q808"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
@@ -8734,7 +8836,7 @@
       <c r="A1" s="3"/>
       <c r="B1" s="92" t="str">
         <f>Thesis!C16</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
         <v>58</v>
@@ -8744,47 +8846,47 @@
       <c r="F1" s="53"/>
       <c r="G1" s="38">
         <f>Data!C1</f>
-        <v>45382</v>
+        <v>45291</v>
       </c>
       <c r="H1" s="38">
         <f>EOMONTH(EDATE(G1,-12),0)</f>
-        <v>45016</v>
+        <v>44926</v>
       </c>
       <c r="I1" s="38">
         <f t="shared" ref="I1:Q1" si="0">EOMONTH(EDATE(H1,-12),0)</f>
-        <v>44651</v>
+        <v>44561</v>
       </c>
       <c r="J1" s="38">
         <f t="shared" si="0"/>
-        <v>44286</v>
+        <v>44196</v>
       </c>
       <c r="K1" s="38">
         <f t="shared" si="0"/>
-        <v>43921</v>
+        <v>43830</v>
       </c>
       <c r="L1" s="38">
         <f t="shared" si="0"/>
-        <v>43555</v>
+        <v>43465</v>
       </c>
       <c r="M1" s="38">
         <f t="shared" si="0"/>
-        <v>43190</v>
+        <v>43100</v>
       </c>
       <c r="N1" s="38">
         <f t="shared" si="0"/>
-        <v>42825</v>
+        <v>42735</v>
       </c>
       <c r="O1" s="38">
         <f t="shared" si="0"/>
-        <v>42460</v>
+        <v>42369</v>
       </c>
       <c r="P1" s="38">
         <f t="shared" si="0"/>
-        <v>42094</v>
+        <v>42004</v>
       </c>
       <c r="Q1" s="38">
         <f t="shared" si="0"/>
-        <v>41729</v>
+        <v>41639</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -8817,7 +8919,7 @@
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="308"/>
@@ -8831,14 +8933,14 @@
       </c>
       <c r="C4" s="196">
         <f>AVERAGE(G4:J4)</f>
-        <v>15325962</v>
+        <v>3011012</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="306"/>
       <c r="F4" s="57"/>
       <c r="G4" s="186">
         <f>Data!C36</f>
-        <v>15325962</v>
+        <v>3011012</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>Data!D36</f>
@@ -8888,12 +8990,12 @@
       </c>
       <c r="C5" s="197">
         <f>C25</f>
-        <v>-13195082</v>
+        <v>-2372645</v>
       </c>
       <c r="E5" s="308"/>
       <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
-        <v>-13195082</v>
+        <v>-2372645</v>
       </c>
       <c r="H5" s="186" t="str">
         <f t="shared" si="1"/>
@@ -8943,12 +9045,12 @@
       </c>
       <c r="C6" s="187">
         <f>C4+C5</f>
-        <v>2130880</v>
+        <v>638367</v>
       </c>
       <c r="E6" s="308"/>
       <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
-        <v>2130880</v>
+        <v>638367</v>
       </c>
       <c r="H6" s="187" t="str">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
@@ -8998,12 +9100,12 @@
       </c>
       <c r="C7" s="197">
         <f>C35</f>
-        <v>-254107</v>
+        <v>-371995</v>
       </c>
       <c r="E7" s="308"/>
       <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
-        <v>-254107</v>
+        <v>-371995</v>
       </c>
       <c r="H7" s="197" t="str">
         <f t="shared" si="3"/>
@@ -9053,14 +9155,14 @@
       </c>
       <c r="C8" s="198">
         <f>C6+C7</f>
-        <v>1876773</v>
+        <v>266372</v>
       </c>
       <c r="D8" s="60"/>
       <c r="E8" s="314"/>
       <c r="F8" s="60"/>
       <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
-        <v>1876773</v>
+        <v>266372</v>
       </c>
       <c r="H8" s="187" t="str">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
@@ -9110,12 +9212,12 @@
       </c>
       <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
-        <v>463424</v>
+        <v>229584</v>
       </c>
       <c r="E9" s="308"/>
       <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
-        <v>463424</v>
+        <v>229584</v>
       </c>
       <c r="H9" s="197" t="str">
         <f>IF(Data!D61="","",-Data!D61)</f>
@@ -9165,12 +9267,12 @@
       </c>
       <c r="C10" s="197">
         <f>-C4*C78</f>
-        <v>-676387</v>
+        <v>-229584</v>
       </c>
       <c r="E10" s="308"/>
       <c r="G10" s="197">
         <f>Data!C62</f>
-        <v>-676387</v>
+        <v>-115297</v>
       </c>
       <c r="H10" s="197" t="str">
         <f>Data!D62</f>
@@ -9220,14 +9322,14 @@
       </c>
       <c r="C11" s="199">
         <f>C63</f>
-        <v>0</v>
+        <v>18538.000000000004</v>
       </c>
       <c r="D11" s="172"/>
       <c r="E11" s="307"/>
       <c r="F11" s="172"/>
       <c r="G11" s="189">
         <f>G61</f>
-        <v>639</v>
+        <v>18538</v>
       </c>
       <c r="H11" s="189" t="str">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
@@ -9277,12 +9379,12 @@
       </c>
       <c r="C12" s="197">
         <f>C50</f>
-        <v>-42378.404459360565</v>
+        <v>-15885.762305832384</v>
       </c>
       <c r="E12" s="308"/>
       <c r="G12" s="197">
         <f>G50</f>
-        <v>-42378.404459360565</v>
+        <v>-15885.762305832384</v>
       </c>
       <c r="H12" s="197" t="str">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
@@ -9332,12 +9434,12 @@
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
-        <v>1621431.5955406395</v>
+        <v>269024.23769416759</v>
       </c>
       <c r="E13" s="308"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>1622070.5955406395</v>
+        <v>383311.23769416759</v>
       </c>
       <c r="H13" s="187" t="str">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
@@ -9387,12 +9489,12 @@
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-458598.64888515987</v>
+        <v>-67256.059423541898</v>
       </c>
       <c r="E14" s="308"/>
       <c r="G14" s="197">
         <f>Data!C46</f>
-        <v>-327166</v>
+        <v>-57167</v>
       </c>
       <c r="H14" s="197" t="str">
         <f>Data!D46</f>
@@ -9442,14 +9544,14 @@
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
-        <v>0</v>
+        <v>-19147</v>
       </c>
       <c r="D15" s="61"/>
       <c r="E15" s="315"/>
       <c r="F15" s="61"/>
       <c r="G15" s="186">
         <f>Data!C48</f>
-        <v>0</v>
+        <v>-19147</v>
       </c>
       <c r="H15" s="186" t="str">
         <f>Data!D48</f>
@@ -9499,14 +9601,14 @@
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
-        <v>1162832.9466554797</v>
+        <v>182621.17827062571</v>
       </c>
       <c r="D16" s="62"/>
       <c r="E16" s="316"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>1294904.5955406395</v>
+        <v>306997.23769416759</v>
       </c>
       <c r="H16" s="187" t="str">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
@@ -9607,14 +9709,14 @@
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
-        <v>1162832.9466554797</v>
+        <v>182621.17827062571</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="305"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>1294904.5955406395</v>
+        <v>306997.23769416759</v>
       </c>
       <c r="H19" s="189" t="str">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
@@ -9727,14 +9829,14 @@
       </c>
       <c r="C23" s="203">
         <f>-C4*C28</f>
-        <v>-11151623</v>
+        <v>-2302385</v>
       </c>
       <c r="D23" s="59"/>
       <c r="E23" s="307"/>
       <c r="F23" s="59"/>
       <c r="G23" s="186">
         <f>Data!C37</f>
-        <v>-11151623</v>
+        <v>-2302385</v>
       </c>
       <c r="H23" s="186" t="str">
         <f>Data!D37</f>
@@ -9784,14 +9886,14 @@
       </c>
       <c r="C24" s="197">
         <f>-C4*C29</f>
-        <v>-2043458.9999999998</v>
+        <v>-70260</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="305"/>
       <c r="F24" s="27"/>
       <c r="G24" s="186">
         <f>Data!C40</f>
-        <v>-2043459</v>
+        <v>-70260</v>
       </c>
       <c r="H24" s="186" t="str">
         <f>Data!D40</f>
@@ -9841,14 +9943,14 @@
       </c>
       <c r="C25" s="187">
         <f>C23+C24</f>
-        <v>-13195082</v>
+        <v>-2372645</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="313"/>
       <c r="F25" s="9"/>
       <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
-        <v>-13195082</v>
+        <v>-2372645</v>
       </c>
       <c r="H25" s="187" t="str">
         <f t="shared" si="10"/>
@@ -9909,7 +10011,7 @@
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:J28)</f>
-        <v>0.72762956087193742</v>
+        <v>0.76465487351096573</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
@@ -9918,7 +10020,7 @@
       <c r="F28" s="26"/>
       <c r="G28" s="13">
         <f t="shared" ref="G28:Q28" si="11">IF(G$4="","",ABS(G23/G$4))</f>
-        <v>0.72762956087193742</v>
+        <v>0.76465487351096573</v>
       </c>
       <c r="H28" s="13" t="str">
         <f t="shared" si="11"/>
@@ -9969,7 +10071,7 @@
       </c>
       <c r="C29" s="64">
         <f>AVERAGE(G29:J29)</f>
-        <v>0.13333316368656009</v>
+        <v>2.3334347388851324E-2</v>
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
@@ -9978,7 +10080,7 @@
       <c r="F29" s="26"/>
       <c r="G29" s="13">
         <f t="shared" ref="G29:Q29" si="12">IF(G$4="","",ABS(G24/G$4))</f>
-        <v>0.13333316368656009</v>
+        <v>2.3334347388851324E-2</v>
       </c>
       <c r="H29" s="13" t="str">
         <f t="shared" si="12"/>
@@ -10028,12 +10130,12 @@
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
-        <v>0.86096272455849754</v>
+        <v>0.78798922089981704</v>
       </c>
       <c r="E30" s="308"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
-        <v>0.86096272455849754</v>
+        <v>0.78798922089981704</v>
       </c>
       <c r="H30" s="30" t="str">
         <f t="shared" si="13"/>
@@ -10094,14 +10196,14 @@
       </c>
       <c r="C33" s="204">
         <f>AVERAGE(G33:J33)</f>
-        <v>-254107</v>
+        <v>-350038</v>
       </c>
       <c r="E33" s="306" t="s">
         <v>347</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
-        <v>-254107</v>
+        <v>-350038</v>
       </c>
       <c r="H33" s="197" t="str">
         <f>Data!D41</f>
@@ -10151,7 +10253,7 @@
       </c>
       <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
-        <v>0</v>
+        <v>-21957</v>
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
@@ -10160,7 +10262,7 @@
       <c r="F34" s="59"/>
       <c r="G34" s="186">
         <f>Data!C42</f>
-        <v>0</v>
+        <v>-21957</v>
       </c>
       <c r="H34" s="186" t="str">
         <f>Data!D42</f>
@@ -10210,14 +10312,14 @@
       </c>
       <c r="C35" s="187">
         <f>C33+C34</f>
-        <v>-254107</v>
+        <v>-371995</v>
       </c>
       <c r="D35" s="59"/>
       <c r="E35" s="307"/>
       <c r="F35" s="59"/>
       <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
-        <v>-254107</v>
+        <v>-371995</v>
       </c>
       <c r="H35" s="187" t="str">
         <f t="shared" si="14"/>
@@ -10279,14 +10381,14 @@
       </c>
       <c r="C38" s="23">
         <f>ABS(C33/$C$4)</f>
-        <v>1.6580166386945237E-2</v>
+        <v>0.1162526087574543</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="305"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
-        <v>1.6580166386945237E-2</v>
+        <v>0.1162526087574543</v>
       </c>
       <c r="H38" s="13" t="str">
         <f t="shared" si="15"/>
@@ -10337,14 +10439,14 @@
       </c>
       <c r="C39" s="23">
         <f>ABS(C34/$C$4)</f>
-        <v>0</v>
+        <v>7.2922326447055008E-3</v>
       </c>
       <c r="D39" s="27"/>
       <c r="E39" s="305"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
-        <v>0</v>
+        <v>7.2922326447055008E-3</v>
       </c>
       <c r="H39" s="13" t="str">
         <f t="shared" si="16"/>
@@ -10394,12 +10496,12 @@
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
-        <v>1.6580166386945237E-2</v>
+        <v>0.12354484140215981</v>
       </c>
       <c r="E40" s="308"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
-        <v>1.6580166386945237E-2</v>
+        <v>0.12354484140215981</v>
       </c>
       <c r="H40" s="30" t="str">
         <f t="shared" si="17"/>
@@ -10468,7 +10570,7 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.17828883394563139</v>
+        <v>0.21249758196504454</v>
       </c>
       <c r="H43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10551,12 +10653,12 @@
       </c>
       <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
-        <v>-59596</v>
+        <v>-24063</v>
       </c>
       <c r="E47" s="308"/>
       <c r="G47" s="197">
         <f>Data!C51</f>
-        <v>-59596</v>
+        <v>-24063</v>
       </c>
       <c r="H47" s="197" t="str">
         <f>Data!D51</f>
@@ -10606,12 +10708,12 @@
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
-        <v>17217.595540639435</v>
+        <v>8177.2376941676157</v>
       </c>
       <c r="E48" s="308"/>
       <c r="G48" s="334">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>17217.595540639435</v>
+        <v>8177.2376941676157</v>
       </c>
       <c r="H48" s="334" t="str">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
@@ -10661,14 +10763,14 @@
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
-        <v>28977</v>
+        <v>8265</v>
       </c>
       <c r="D49" s="331"/>
       <c r="E49" s="332"/>
       <c r="F49" s="331"/>
       <c r="G49" s="330">
         <f>Data!C52</f>
-        <v>28977</v>
+        <v>8265</v>
       </c>
       <c r="H49" s="330" t="str">
         <f>Data!D52</f>
@@ -10718,12 +10820,12 @@
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
-        <v>-42378.404459360565</v>
+        <v>-15885.762305832384</v>
       </c>
       <c r="E50" s="308"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-42378.404459360565</v>
+        <v>-15885.762305832384</v>
       </c>
       <c r="H50" s="187" t="str">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
@@ -10787,14 +10889,14 @@
       </c>
       <c r="C53" s="89">
         <f>G53</f>
-        <v>1.4501413508729523E-2</v>
+        <v>3.4598961821835229E-2</v>
       </c>
       <c r="E53" s="305" t="s">
         <v>349</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
-        <v>1.4501413508729523E-2</v>
+        <v>3.4598961821835229E-2</v>
       </c>
       <c r="H53" s="173"/>
       <c r="I53" s="173"/>
@@ -10814,14 +10916,14 @@
       </c>
       <c r="C54" s="84">
         <f>G54</f>
-        <v>2.9286626219579916E-2</v>
+        <v>9.7930927826660269E-2</v>
       </c>
       <c r="E54" s="305" t="s">
         <v>350</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
-        <v>2.9286626219579916E-2</v>
+        <v>9.7930927826660269E-2</v>
       </c>
       <c r="H54" s="173"/>
       <c r="I54" s="173"/>
@@ -10841,12 +10943,12 @@
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
-        <v>31.4915933955299</v>
+        <v>11.069775173502888</v>
       </c>
       <c r="E55" s="308"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
-        <v>31.4915933955299</v>
+        <v>11.069775173502888</v>
       </c>
       <c r="H55" s="42" t="str">
         <f t="shared" si="21"/>
@@ -10965,12 +11067,12 @@
       </c>
       <c r="C59" s="197">
         <f>BS!$C68*C67</f>
-        <v>0</v>
+        <v>18538.000000000004</v>
       </c>
       <c r="E59" s="308"/>
       <c r="G59" s="197">
         <f>Data!C55</f>
-        <v>639</v>
+        <v>18538</v>
       </c>
       <c r="H59" s="197" t="str">
         <f>Data!D55</f>
@@ -11075,12 +11177,12 @@
       </c>
       <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
-        <v>0</v>
+        <v>18538.000000000004</v>
       </c>
       <c r="E61" s="308"/>
       <c r="G61" s="187">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
-        <v>639</v>
+        <v>18538</v>
       </c>
       <c r="H61" s="187" t="str">
         <f t="shared" si="22"/>
@@ -11136,7 +11238,7 @@
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
-        <v>247678</v>
+        <v>-31654</v>
       </c>
       <c r="H62" s="197" t="str">
         <f>Data!D58</f>
@@ -11186,12 +11288,12 @@
       </c>
       <c r="C63" s="187">
         <f>C61+C62</f>
-        <v>0</v>
+        <v>18538.000000000004</v>
       </c>
       <c r="E63" s="308"/>
       <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
-        <v>248317</v>
+        <v>-13116</v>
       </c>
       <c r="H63" s="187" t="str">
         <f t="shared" si="23"/>
@@ -11280,12 +11382,12 @@
       </c>
       <c r="C67" s="180">
         <f>G67</f>
-        <v>0</v>
+        <v>6.3354818424775985E-2</v>
       </c>
       <c r="E67" s="308"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
-        <v>0</v>
+        <v>6.3354818424775985E-2</v>
       </c>
       <c r="H67" s="179"/>
       <c r="I67" s="179"/>
@@ -11330,14 +11432,14 @@
       </c>
       <c r="C69" s="72">
         <f>C61/BS!C70</f>
-        <v>0</v>
+        <v>3.4879564090117152E-2</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="313"/>
       <c r="F69" s="9"/>
       <c r="G69" s="72">
         <f>G61/BS!C70</f>
-        <v>3.197847683362034E-4</v>
+        <v>3.4879564090117145E-2</v>
       </c>
       <c r="H69" s="179"/>
       <c r="I69" s="179"/>
@@ -11404,14 +11506,14 @@
       </c>
       <c r="C73" s="79">
         <f>ABS(C5/C$4)</f>
-        <v>0.86096272455849754</v>
+        <v>0.78798922089981704</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="305"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
-        <v>0.86096272455849754</v>
+        <v>0.78798922089981704</v>
       </c>
       <c r="H73" s="6" t="str">
         <f t="shared" si="24"/>
@@ -11461,14 +11563,14 @@
       </c>
       <c r="C74" s="80">
         <f>ABS(C6/C$4)</f>
-        <v>0.13903727544150246</v>
+        <v>0.21201077910018293</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="305"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
-        <v>0.13903727544150246</v>
+        <v>0.21201077910018293</v>
       </c>
       <c r="H74" s="66" t="str">
         <f t="shared" si="25"/>
@@ -11518,14 +11620,14 @@
       </c>
       <c r="C75" s="79">
         <f>ABS(C7/C$4)</f>
-        <v>1.6580166386945237E-2</v>
+        <v>0.12354484140215981</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="305"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
-        <v>1.6580166386945237E-2</v>
+        <v>0.12354484140215981</v>
       </c>
       <c r="H75" s="6" t="str">
         <f t="shared" si="26"/>
@@ -11575,14 +11677,14 @@
       </c>
       <c r="C76" s="80">
         <f>ABS(C8/C$4)</f>
-        <v>0.12245710905455723</v>
+        <v>8.846593769802312E-2</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="305"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
-        <v>0.12245710905455723</v>
+        <v>8.846593769802312E-2</v>
       </c>
       <c r="H76" s="66" t="str">
         <f t="shared" si="27"/>
@@ -11632,14 +11734,14 @@
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
-        <v>3.0237840861147901E-2</v>
+        <v>7.6248118572758927E-2</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="305"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
-        <v>3.0237840861147901E-2</v>
+        <v>7.6248118572758927E-2</v>
       </c>
       <c r="H77" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11689,16 +11791,16 @@
       </c>
       <c r="C78" s="90">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
-        <v>4.413341231043115E-2</v>
+        <v>7.6248118572758927E-2</v>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
-        <v>4.413341231043115E-2</v>
+        <v>3.8291776983950913E-2</v>
       </c>
       <c r="H78" s="6" t="str">
         <f t="shared" si="29"/>
@@ -11748,14 +11850,14 @@
       </c>
       <c r="C79" s="80">
         <f>ABS(C11/C$4)</f>
-        <v>0</v>
+        <v>6.1567340150089087E-3</v>
       </c>
       <c r="D79" s="27"/>
       <c r="E79" s="305"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
-        <v>4.1693956960091643E-5</v>
+        <v>6.156734015008907E-3</v>
       </c>
       <c r="H79" s="66" t="str">
         <f t="shared" si="30"/>
@@ -11805,14 +11907,14 @@
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
-        <v>2.7651382966603051E-3</v>
+        <v>5.2758880754485149E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="305"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>2.7651382966603051E-3</v>
+        <v>5.2758880754485149E-3</v>
       </c>
       <c r="H80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -11862,14 +11964,14 @@
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
-        <v>0.10579639930861368</v>
+        <v>8.9346783637583513E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="305"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.10583809326557377</v>
+        <v>0.12730312522639153</v>
       </c>
       <c r="H81" s="66" t="str">
         <f t="shared" si="32"/>
@@ -11919,14 +12021,14 @@
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
-        <v>2.992299268947423E-2</v>
+        <v>2.2336695909395878E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="305"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>2.134717546604905E-2</v>
+        <v>1.89859754793405E-2</v>
       </c>
       <c r="H82" s="6" t="str">
         <f t="shared" si="33"/>
@@ -11977,14 +12079,14 @@
       </c>
       <c r="C83" s="304">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
-        <v>0</v>
+        <v>6.358991594852495E-3</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="305"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
-        <v>0</v>
+        <v>6.358991594852495E-3</v>
       </c>
       <c r="H83" s="6" t="str">
         <f t="shared" si="34"/>
@@ -12034,14 +12136,14 @@
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
-        <v>7.5873406619139452E-2</v>
+        <v>6.0651096133335143E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="305"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>8.4490917799524723E-2</v>
+        <v>0.10195815815219852</v>
       </c>
       <c r="H84" s="66" t="str">
         <f t="shared" si="35"/>
@@ -12141,14 +12243,14 @@
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
-        <v>7.5873406619139452E-2</v>
+        <v>6.0651096133335143E-2</v>
       </c>
       <c r="D87" s="77"/>
       <c r="E87" s="305"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>8.4490917799524723E-2</v>
+        <v>0.10195815815219852</v>
       </c>
       <c r="H87" s="66" t="str">
         <f t="shared" si="36"/>
@@ -12210,51 +12312,51 @@
       </c>
       <c r="C90" s="117">
         <f>G90</f>
-        <v>1.36</v>
+        <v>0.49984047644368812</v>
       </c>
       <c r="E90" s="308"/>
       <c r="G90" s="116">
-        <f>Data!C64</f>
-        <v>1.36</v>
+        <f>Data!C65</f>
+        <v>0.49984047644368812</v>
       </c>
       <c r="H90" s="116" t="str">
-        <f>Data!D64</f>
+        <f>Data!D65</f>
         <v/>
       </c>
       <c r="I90" s="116" t="str">
-        <f>Data!E64</f>
+        <f>Data!E65</f>
         <v/>
       </c>
       <c r="J90" s="116" t="str">
-        <f>Data!F64</f>
+        <f>Data!F65</f>
         <v/>
       </c>
       <c r="K90" s="116" t="str">
-        <f>Data!G64</f>
+        <f>Data!G65</f>
         <v/>
       </c>
       <c r="L90" s="116" t="str">
-        <f>Data!H64</f>
+        <f>Data!H65</f>
         <v/>
       </c>
       <c r="M90" s="116" t="str">
-        <f>Data!I64</f>
+        <f>Data!I65</f>
         <v/>
       </c>
       <c r="N90" s="116" t="str">
-        <f>Data!J64</f>
+        <f>Data!J65</f>
         <v/>
       </c>
       <c r="O90" s="116" t="str">
-        <f>Data!K64</f>
+        <f>Data!K65</f>
         <v/>
       </c>
       <c r="P90" s="116" t="str">
-        <f>Data!L64</f>
+        <f>Data!L65</f>
         <v/>
       </c>
       <c r="Q90" s="116" t="str">
-        <f>Data!M64</f>
+        <f>Data!M65</f>
         <v/>
       </c>
     </row>
@@ -12266,12 +12368,12 @@
       </c>
       <c r="C91" s="76">
         <f>C90*Common_Shares/$C$3</f>
-        <v>798466.67599999998</v>
+        <v>91481.292751738802</v>
       </c>
       <c r="E91" s="308"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>798466.67599999998</v>
+        <v>91481.292751738802</v>
       </c>
       <c r="H91" s="76" t="str">
         <f t="shared" si="37"/>
@@ -12321,12 +12423,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.68665639230169417</v>
+        <v>0.50093474162220653</v>
       </c>
       <c r="E92" s="308"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.61662201118888604</v>
+        <v>0.29798734815611916</v>
       </c>
       <c r="H92" s="174" t="str">
         <f t="shared" si="38"/>
@@ -12376,12 +12478,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>8.8311688311688313E-2</v>
+        <v>9.0061347106970835E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>8.8311688311688313E-2</v>
+        <v>9.0061347106970835E-2</v>
       </c>
       <c r="H93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12513,7 +12615,7 @@
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>-3.9394093065781011E-4</v>
+        <v>-0.29815718601807895</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="305"/>
@@ -12606,14 +12708,14 @@
       </c>
       <c r="C101" s="205">
         <f>BS!G32</f>
-        <v>16854064</v>
+        <v>2768297</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="309"/>
       <c r="F101" s="26"/>
       <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
-        <v>16854064</v>
+        <v>2752710</v>
       </c>
       <c r="H101" s="186" t="str">
         <f t="shared" si="42"/>
@@ -12663,53 +12765,53 @@
       </c>
       <c r="C102" s="206">
         <f>BS!C4</f>
-        <v>265773</v>
+        <v>142879</v>
       </c>
       <c r="D102" s="91"/>
       <c r="E102" s="310"/>
       <c r="F102" s="91"/>
       <c r="G102" s="188" t="str">
-        <f>IF(G$4="","",Data!D76)</f>
+        <f>IF(G$4="","",Data!D77)</f>
         <v/>
       </c>
       <c r="H102" s="188" t="str">
-        <f>IF(H$4="","",Data!E76)</f>
+        <f>IF(H$4="","",Data!E77)</f>
         <v/>
       </c>
       <c r="I102" s="188" t="str">
-        <f>IF(I$4="","",Data!F76)</f>
+        <f>IF(I$4="","",Data!F77)</f>
         <v/>
       </c>
       <c r="J102" s="188" t="str">
-        <f>IF(J$4="","",Data!G76)</f>
+        <f>IF(J$4="","",Data!G77)</f>
         <v/>
       </c>
       <c r="K102" s="188" t="str">
-        <f>IF(K$4="","",Data!H76)</f>
+        <f>IF(K$4="","",Data!H77)</f>
         <v/>
       </c>
       <c r="L102" s="188" t="str">
-        <f>IF(L$4="","",Data!I76)</f>
+        <f>IF(L$4="","",Data!I77)</f>
         <v/>
       </c>
       <c r="M102" s="188" t="str">
-        <f>IF(M$4="","",Data!J76)</f>
+        <f>IF(M$4="","",Data!J77)</f>
         <v/>
       </c>
       <c r="N102" s="188" t="str">
-        <f>IF(N$4="","",Data!K76)</f>
+        <f>IF(N$4="","",Data!K77)</f>
         <v/>
       </c>
       <c r="O102" s="188" t="str">
-        <f>IF(O$4="","",Data!L76)</f>
+        <f>IF(O$4="","",Data!L77)</f>
         <v/>
       </c>
       <c r="P102" s="188" t="str">
-        <f>IF(P$4="","",Data!M76)</f>
+        <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
       <c r="Q102" s="188" t="str">
-        <f>IF(Q$4="","",Data!N76)</f>
+        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
@@ -12720,53 +12822,53 @@
       </c>
       <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
-        <v>9672256</v>
+        <v>182674</v>
       </c>
       <c r="D103" s="91"/>
       <c r="E103" s="310"/>
       <c r="F103" s="91"/>
       <c r="G103" s="188" t="str">
-        <f>IF(G$4="","",Data!D77)</f>
+        <f>IF(G$4="","",Data!D78)</f>
         <v/>
       </c>
       <c r="H103" s="188" t="str">
-        <f>IF(H$4="","",Data!E77)</f>
+        <f>IF(H$4="","",Data!E78)</f>
         <v/>
       </c>
       <c r="I103" s="188" t="str">
-        <f>IF(I$4="","",Data!F77)</f>
+        <f>IF(I$4="","",Data!F78)</f>
         <v/>
       </c>
       <c r="J103" s="188" t="str">
-        <f>IF(J$4="","",Data!G77)</f>
+        <f>IF(J$4="","",Data!G78)</f>
         <v/>
       </c>
       <c r="K103" s="188" t="str">
-        <f>IF(K$4="","",Data!H77)</f>
+        <f>IF(K$4="","",Data!H78)</f>
         <v/>
       </c>
       <c r="L103" s="188" t="str">
-        <f>IF(L$4="","",Data!I77)</f>
+        <f>IF(L$4="","",Data!I78)</f>
         <v/>
       </c>
       <c r="M103" s="188" t="str">
-        <f>IF(M$4="","",Data!J77)</f>
+        <f>IF(M$4="","",Data!J78)</f>
         <v/>
       </c>
       <c r="N103" s="188" t="str">
-        <f>IF(N$4="","",Data!K77)</f>
+        <f>IF(N$4="","",Data!K78)</f>
         <v/>
       </c>
       <c r="O103" s="188" t="str">
-        <f>IF(O$4="","",Data!L77)</f>
+        <f>IF(O$4="","",Data!L78)</f>
         <v/>
       </c>
       <c r="P103" s="188" t="str">
-        <f>IF(P$4="","",Data!M77)</f>
+        <f>IF(P$4="","",Data!M78)</f>
         <v/>
       </c>
       <c r="Q103" s="188" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
+        <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
     </row>
@@ -12777,53 +12879,53 @@
       </c>
       <c r="C104" s="205">
         <f>BS!G30</f>
-        <v>3990166</v>
+        <v>1090144</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="309"/>
       <c r="F104" s="26"/>
       <c r="G104" s="186">
-        <f>Data!C78</f>
-        <v>3990166</v>
+        <f>Data!C79</f>
+        <v>1122089</v>
       </c>
       <c r="H104" s="186" t="str">
-        <f>Data!D78</f>
+        <f>Data!D79</f>
         <v/>
       </c>
       <c r="I104" s="186" t="str">
-        <f>Data!E78</f>
+        <f>Data!E79</f>
         <v/>
       </c>
       <c r="J104" s="186" t="str">
-        <f>Data!F78</f>
+        <f>Data!F79</f>
         <v/>
       </c>
       <c r="K104" s="186" t="str">
-        <f>Data!G78</f>
+        <f>Data!G79</f>
         <v/>
       </c>
       <c r="L104" s="186" t="str">
-        <f>Data!H78</f>
+        <f>Data!H79</f>
         <v/>
       </c>
       <c r="M104" s="186" t="str">
-        <f>Data!I78</f>
+        <f>Data!I79</f>
         <v/>
       </c>
       <c r="N104" s="186" t="str">
-        <f>Data!J78</f>
+        <f>Data!J79</f>
         <v/>
       </c>
       <c r="O104" s="186" t="str">
-        <f>Data!K78</f>
+        <f>Data!K79</f>
         <v/>
       </c>
       <c r="P104" s="186" t="str">
-        <f>Data!L78</f>
+        <f>Data!L79</f>
         <v/>
       </c>
       <c r="Q104" s="186" t="str">
-        <f>Data!M78</f>
+        <f>Data!M79</f>
         <v/>
       </c>
     </row>
@@ -12834,53 +12936,53 @@
       </c>
       <c r="C105" s="205">
         <f>BS!G27</f>
-        <v>12863898</v>
+        <v>1678153</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
-        <f>Data!C79</f>
-        <v>12863898</v>
+        <f>Data!C80</f>
+        <v>1630621</v>
       </c>
       <c r="H105" s="186" t="str">
-        <f>Data!D79</f>
+        <f>Data!D80</f>
         <v/>
       </c>
       <c r="I105" s="186" t="str">
-        <f>Data!E79</f>
+        <f>Data!E80</f>
         <v/>
       </c>
       <c r="J105" s="186" t="str">
-        <f>Data!F79</f>
+        <f>Data!F80</f>
         <v/>
       </c>
       <c r="K105" s="186" t="str">
-        <f>Data!G79</f>
+        <f>Data!G80</f>
         <v/>
       </c>
       <c r="L105" s="186" t="str">
-        <f>Data!H79</f>
+        <f>Data!H80</f>
         <v/>
       </c>
       <c r="M105" s="186" t="str">
-        <f>Data!I79</f>
+        <f>Data!I80</f>
         <v/>
       </c>
       <c r="N105" s="186" t="str">
-        <f>Data!J79</f>
+        <f>Data!J80</f>
         <v/>
       </c>
       <c r="O105" s="186" t="str">
-        <f>Data!K79</f>
+        <f>Data!K80</f>
         <v/>
       </c>
       <c r="P105" s="186" t="str">
-        <f>Data!L79</f>
+        <f>Data!L80</f>
         <v/>
       </c>
       <c r="Q105" s="186" t="str">
-        <f>Data!M79</f>
+        <f>Data!M80</f>
         <v/>
       </c>
     </row>
@@ -12918,7 +13020,7 @@
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
-        <v>1.7341358408692387E-2</v>
+        <v>4.7452152299625509E-2</v>
       </c>
       <c r="D108" s="26"/>
       <c r="E108" s="309"/>
@@ -12975,7 +13077,7 @@
       </c>
       <c r="C109" s="97">
         <f>C103/C$4</f>
-        <v>0.63110270011109249</v>
+        <v>6.0668638982508204E-2</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="309"/>
@@ -13058,462 +13160,573 @@
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
-      <c r="B112" s="93" t="s">
-        <v>38</v>
-      </c>
-      <c r="C112" s="55"/>
-      <c r="D112" s="55"/>
-      <c r="E112" s="311"/>
-      <c r="F112" s="55"/>
-      <c r="G112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H114*(1/#REF!)=H116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I114*(1/#REF!)=I116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J114*(1/#REF!)=J116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K114*(1/#REF!)=K116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L114*(1/#REF!)=L116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M114*(1/#REF!)=M116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N114*(1/#REF!)=N116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O114*(1/#REF!)=O116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P114*(1/#REF!)=P116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q114*(1/#REF!)=Q116,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="B112" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="E112" s="308"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
-      <c r="B113" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C113" s="23">
-        <f>C81</f>
-        <v>0.10579639930861368</v>
-      </c>
+      <c r="B113" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C113" s="173"/>
       <c r="E113" s="308"/>
-      <c r="G113" s="23">
-        <f t="shared" ref="G113:Q113" si="45">G81</f>
-        <v>0.10583809326557377</v>
-      </c>
-      <c r="H113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="I113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="J113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="K113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="L113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="M113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="N113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="O113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="P113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="Q113" s="23" t="str">
-        <f t="shared" si="45"/>
+      <c r="G113" s="340">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>2.5325501550271508</v>
+      </c>
+      <c r="H113" s="340" t="str">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v/>
+      </c>
+      <c r="I113" s="340" t="str">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v/>
+      </c>
+      <c r="J113" s="340" t="str">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v/>
+      </c>
+      <c r="K113" s="340" t="str">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v/>
+      </c>
+      <c r="L113" s="340" t="str">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v/>
+      </c>
+      <c r="M113" s="340" t="str">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v/>
+      </c>
+      <c r="N113" s="340" t="str">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v/>
+      </c>
+      <c r="O113" s="340" t="str">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v/>
+      </c>
+      <c r="P113" s="340" t="str">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v/>
+      </c>
+      <c r="Q113" s="340" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C114" s="42">
-        <f>C4/C101</f>
-        <v>0.90933332162498015</v>
-      </c>
+      <c r="A114" s="10"/>
+      <c r="B114" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C114" s="173"/>
       <c r="E114" s="308"/>
-      <c r="G114" s="42">
-        <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
-        <v>0.90933332162498015</v>
-      </c>
-      <c r="H114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="I114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="J114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="K114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="L114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="M114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="N114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="O114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="P114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="Q114" s="42" t="str">
-        <f t="shared" si="46"/>
+      <c r="G114" s="340">
+        <f>IF(G$4="","",Data!C$22/G19)</f>
+        <v>1.4872967699301045</v>
+      </c>
+      <c r="H114" s="340" t="str">
+        <f>IF(H$4="","",Data!D$22/H19)</f>
+        <v/>
+      </c>
+      <c r="I114" s="340" t="str">
+        <f>IF(I$4="","",Data!E$22/I19)</f>
+        <v/>
+      </c>
+      <c r="J114" s="340" t="str">
+        <f>IF(J$4="","",Data!F$22/J19)</f>
+        <v/>
+      </c>
+      <c r="K114" s="340" t="str">
+        <f>IF(K$4="","",Data!G$22/K19)</f>
+        <v/>
+      </c>
+      <c r="L114" s="340" t="str">
+        <f>IF(L$4="","",Data!H$22/L19)</f>
+        <v/>
+      </c>
+      <c r="M114" s="340" t="str">
+        <f>IF(M$4="","",Data!I$22/M19)</f>
+        <v/>
+      </c>
+      <c r="N114" s="340" t="str">
+        <f>IF(N$4="","",Data!J$22/N19)</f>
+        <v/>
+      </c>
+      <c r="O114" s="340" t="str">
+        <f>IF(O$4="","",Data!K$22/O19)</f>
+        <v/>
+      </c>
+      <c r="P114" s="340" t="str">
+        <f>IF(P$4="","",Data!L$22/P19)</f>
+        <v/>
+      </c>
+      <c r="Q114" s="340" t="str">
+        <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C115" s="15">
-        <f>C101/C105</f>
-        <v>1.3101832741522048</v>
-      </c>
-      <c r="D115" s="11"/>
-      <c r="E115" s="312"/>
-      <c r="F115" s="11"/>
-      <c r="G115" s="15">
-        <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
-        <v>1.3101832741522048</v>
-      </c>
-      <c r="H115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="I115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="J115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="K115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="L115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="M115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="N115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="O115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="P115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="Q115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
+      <c r="A115" s="10"/>
+      <c r="E115" s="308"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10"/>
-      <c r="B116" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="C116" s="105">
-        <f>C8/C105</f>
-        <v>0.14589458032083277</v>
-      </c>
-      <c r="D116" s="106"/>
+      <c r="B116" s="93" t="s">
+        <v>38</v>
+      </c>
+      <c r="C116" s="55"/>
+      <c r="D116" s="55"/>
       <c r="E116" s="311"/>
-      <c r="F116" s="106"/>
-      <c r="G116" s="105">
-        <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
-        <v>0.14589458032083277</v>
-      </c>
-      <c r="H116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="I116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="J116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="K116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="L116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="M116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="N116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="O116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="P116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="Q116" s="105" t="str">
-        <f t="shared" si="48"/>
+      <c r="F116" s="55"/>
+      <c r="G116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
         <v/>
       </c>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="10"/>
-      <c r="B117" s="27"/>
-      <c r="C117" s="63"/>
-      <c r="D117" s="27"/>
-      <c r="E117" s="68"/>
-      <c r="F117" s="27"/>
-      <c r="G117" s="12"/>
-      <c r="H117" s="12"/>
-      <c r="I117" s="12"/>
-      <c r="J117" s="12"/>
-      <c r="K117" s="12"/>
-      <c r="L117" s="12"/>
-      <c r="M117" s="12"/>
-      <c r="N117" s="12"/>
-      <c r="O117" s="12"/>
-      <c r="P117" s="12"/>
-      <c r="Q117" s="12"/>
-    </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A118" s="10"/>
-      <c r="B118" s="54" t="s">
-        <v>225</v>
-      </c>
-      <c r="C118" s="54"/>
-      <c r="D118" s="56"/>
-      <c r="E118" s="67" t="s">
-        <v>60</v>
-      </c>
-      <c r="F118" s="56"/>
-      <c r="G118" s="37"/>
-      <c r="H118" s="37"/>
-      <c r="I118" s="37"/>
-      <c r="J118" s="37"/>
-      <c r="K118" s="37"/>
-      <c r="L118" s="37"/>
-      <c r="M118" s="37"/>
-      <c r="N118" s="37"/>
-      <c r="O118" s="37"/>
-      <c r="P118" s="37"/>
-      <c r="Q118" s="37"/>
+      <c r="B117" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C117" s="23">
+        <f>C81</f>
+        <v>8.9346783637583513E-2</v>
+      </c>
+      <c r="E117" s="308"/>
+      <c r="G117" s="23">
+        <f t="shared" ref="G117:Q117" si="45">G81</f>
+        <v>0.12730312522639153</v>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C118" s="42">
+        <f>C4/C101</f>
+        <v>1.0876766474117481</v>
+      </c>
+      <c r="E118" s="308"/>
+      <c r="G118" s="42">
+        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
+        <v>1.0938355293510758</v>
+      </c>
+      <c r="H118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="I118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="J118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="K118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="L118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="M118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="N118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="O118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="P118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="Q118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="10"/>
-      <c r="B119" s="182" t="s">
-        <v>172</v>
-      </c>
-      <c r="C119" s="183"/>
-      <c r="D119" s="27"/>
-      <c r="E119" s="305"/>
-      <c r="F119" s="27"/>
-      <c r="G119" s="12"/>
-      <c r="H119" s="12"/>
-      <c r="I119" s="12"/>
-      <c r="J119" s="12"/>
-      <c r="K119" s="12"/>
-      <c r="L119" s="12"/>
-      <c r="M119" s="12"/>
-      <c r="N119" s="12"/>
-      <c r="O119" s="12"/>
-      <c r="P119" s="12"/>
-      <c r="Q119" s="12"/>
+      <c r="B119" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C119" s="15">
+        <f>C101/C105</f>
+        <v>1.6496094217869288</v>
+      </c>
+      <c r="D119" s="11"/>
+      <c r="E119" s="312"/>
+      <c r="F119" s="11"/>
+      <c r="G119" s="15">
+        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+        <v>1.6881359923611925</v>
+      </c>
+      <c r="H119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="I119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="J119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="K119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="L119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="M119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="N119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="O119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="P119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="Q119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
     </row>
     <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="10"/>
-      <c r="B120" s="27" t="str">
+      <c r="B120" s="71" t="s">
+        <v>224</v>
+      </c>
+      <c r="C120" s="105">
+        <f>C8/C105</f>
+        <v>0.1587292696196354</v>
+      </c>
+      <c r="D120" s="106"/>
+      <c r="E120" s="311"/>
+      <c r="F120" s="106"/>
+      <c r="G120" s="105">
+        <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
+        <v>0.16335616921406015</v>
+      </c>
+      <c r="H120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="I120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="J120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="K120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="L120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="M120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="N120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="O120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="P120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="Q120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="10"/>
+      <c r="B121" s="27"/>
+      <c r="C121" s="63"/>
+      <c r="D121" s="27"/>
+      <c r="E121" s="68"/>
+      <c r="F121" s="27"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="12"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="12"/>
+      <c r="K121" s="12"/>
+      <c r="L121" s="12"/>
+      <c r="M121" s="12"/>
+      <c r="N121" s="12"/>
+      <c r="O121" s="12"/>
+      <c r="P121" s="12"/>
+      <c r="Q121" s="12"/>
+    </row>
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A122" s="10"/>
+      <c r="B122" s="54" t="s">
+        <v>225</v>
+      </c>
+      <c r="C122" s="54"/>
+      <c r="D122" s="56"/>
+      <c r="E122" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="F122" s="56"/>
+      <c r="G122" s="37"/>
+      <c r="H122" s="37"/>
+      <c r="I122" s="37"/>
+      <c r="J122" s="37"/>
+      <c r="K122" s="37"/>
+      <c r="L122" s="37"/>
+      <c r="M122" s="37"/>
+      <c r="N122" s="37"/>
+      <c r="O122" s="37"/>
+      <c r="P122" s="37"/>
+      <c r="Q122" s="37"/>
+    </row>
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="10"/>
+      <c r="B123" s="182" t="s">
+        <v>172</v>
+      </c>
+      <c r="C123" s="183"/>
+      <c r="D123" s="27"/>
+      <c r="E123" s="305"/>
+      <c r="F123" s="27"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
+      <c r="L123" s="12"/>
+      <c r="M123" s="12"/>
+      <c r="N123" s="12"/>
+      <c r="O123" s="12"/>
+      <c r="P123" s="12"/>
+      <c r="Q123" s="12"/>
+    </row>
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="10"/>
+      <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
         <v>FCFE per share (HKD)</v>
       </c>
-      <c r="C120" s="181">
+      <c r="C124" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.9806121595129067</v>
-      </c>
-      <c r="D120" s="27"/>
-      <c r="E120" s="305"/>
-      <c r="F120" s="27"/>
-      <c r="G120" s="181">
-        <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.205565119833842</v>
-      </c>
-      <c r="H120" s="181" t="str">
+        <v>0.93824596488950096</v>
+      </c>
+      <c r="D124" s="27"/>
+      <c r="E124" s="305"/>
+      <c r="F124" s="27"/>
+      <c r="G124" s="181">
+        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>1.5772481714685458</v>
+      </c>
+      <c r="H124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="I120" s="181" t="str">
+      <c r="I124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="J120" s="181" t="str">
+      <c r="J124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="K120" s="181" t="str">
+      <c r="K124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="L120" s="181" t="str">
+      <c r="L124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="M120" s="181" t="str">
+      <c r="M124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="N120" s="181" t="str">
+      <c r="N124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="O120" s="181" t="str">
+      <c r="O124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="P120" s="181" t="str">
+      <c r="P124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="Q120" s="181" t="str">
+      <c r="Q124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27" t="s">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="10"/>
+      <c r="B125" s="27" t="s">
         <v>272</v>
       </c>
-      <c r="C121" s="79">
+      <c r="C125" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12861117918914977</v>
-      </c>
-      <c r="D121" s="27"/>
-      <c r="E121" s="305"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="79">
-        <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>0.1432185142749248</v>
-      </c>
-      <c r="H121" s="79" t="str">
-        <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="I121" s="79" t="str">
-        <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="J121" s="79" t="str">
-        <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="K121" s="79" t="str">
-        <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="L121" s="79" t="str">
-        <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="M121" s="79" t="str">
-        <f t="shared" ref="M121" si="56">IF(M$4="","",M120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="N121" s="79" t="str">
-        <f t="shared" ref="N121" si="57">IF(N$4="","",N120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="O121" s="79" t="str">
-        <f t="shared" ref="O121" si="58">IF(O$4="","",O120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="P121" s="79" t="str">
-        <f t="shared" ref="P121" si="59">IF(P$4="","",P120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="Q121" s="79" t="str">
-        <f t="shared" ref="Q121" si="60">IF(Q$4="","",Q120/Market_Price)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+        <v>0.16905332700711728</v>
+      </c>
+      <c r="D125" s="27"/>
+      <c r="E125" s="305"/>
+      <c r="F125" s="27"/>
+      <c r="G125" s="79">
+        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+        <v>0.28418885972406233</v>
+      </c>
+      <c r="H125" s="79" t="str">
+        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="I125" s="79" t="str">
+        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="J125" s="79" t="str">
+        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="K125" s="79" t="str">
+        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="L125" s="79" t="str">
+        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="M125" s="79" t="str">
+        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="N125" s="79" t="str">
+        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="O125" s="79" t="str">
+        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="P125" s="79" t="str">
+        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="Q125" s="79" t="str">
+        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+        <v/>
+      </c>
+    </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -14193,6 +14406,10 @@
     <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -14241,7 +14458,7 @@
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="E3" s="112" t="s">
         <v>126</v>
@@ -14254,11 +14471,11 @@
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
-        <v>1162832.9466554797</v>
+        <v>182621.17827062571</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E4" s="103" t="s">
         <v>252</v>
@@ -14286,16 +14503,16 @@
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>14535411.833193496</v>
+        <v>2282764.7283828212</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E6" s="347" t="s">
+        <v>CNY</v>
+      </c>
+      <c r="E6" s="349" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="347"/>
+      <c r="F6" s="349"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14304,14 +14521,14 @@
       </c>
       <c r="C7" s="232">
         <f>BS!G31</f>
-        <v>2034922</v>
+        <v>245714</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E7" s="347"/>
-      <c r="F7" s="347"/>
+        <v>CNY</v>
+      </c>
+      <c r="E7" s="349"/>
+      <c r="F7" s="349"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14320,14 +14537,14 @@
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
-        <v>810914.36033333349</v>
+        <v>2536.5589373550902</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+        <v>CNY</v>
+      </c>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14336,14 +14553,14 @@
       </c>
       <c r="C9" s="235">
         <f>BS!H42</f>
-        <v>92572.6</v>
+        <v>6352.8</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+        <v>CNY</v>
+      </c>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14352,11 +14569,11 @@
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
-        <v>13403976.793526828</v>
+        <v>2045940.0873201764</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="H10" s="124"/>
     </row>
@@ -14366,11 +14583,11 @@
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
-        <v>1</v>
+        <v>0.94030000000000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
-        <v>HKD</v>
+        <v>CNY/HKD</v>
       </c>
       <c r="H11" s="124"/>
     </row>
@@ -14380,7 +14597,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14413,7 +14630,7 @@
       </c>
       <c r="C16" s="165">
         <f>Scenarios!C65</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="H16" s="124"/>
     </row>
@@ -14433,7 +14650,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>23.325699825167451</v>
+        <v>10.189224696681462</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14468,11 +14685,11 @@
       </c>
       <c r="C21" s="127">
         <f>C4*(1+D21)</f>
-        <v>1170275.8082940446</v>
+        <v>180956.72859242809</v>
       </c>
       <c r="D21" s="142">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E21" s="128">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14480,7 +14697,7 @@
       </c>
       <c r="F21" s="129">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>1083588.7113833744</v>
+        <v>167552.52647447042</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -14490,11 +14707,11 @@
       </c>
       <c r="C22" s="127">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>1177766.3089245472</v>
+        <v>179307.44907553098</v>
       </c>
       <c r="D22" s="142">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E22" s="128">
         <f t="shared" si="0"/>
@@ -14502,7 +14719,7 @@
       </c>
       <c r="F22" s="129">
         <f t="shared" si="1"/>
-        <v>1009744.7778845568</v>
+        <v>153727.23686173779</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -14512,11 +14729,11 @@
       </c>
       <c r="C23" s="127">
         <f t="shared" si="2"/>
-        <v>1185304.7534664748</v>
+        <v>177673.20145573994</v>
       </c>
       <c r="D23" s="142">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E23" s="128">
         <f t="shared" si="0"/>
@@ -14524,7 +14741,7 @@
       </c>
       <c r="F23" s="129">
         <f t="shared" si="1"/>
-        <v>940933.12873615138</v>
+        <v>141042.7156808381</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -14534,11 +14751,11 @@
       </c>
       <c r="C24" s="127">
         <f t="shared" si="2"/>
-        <v>1192891.4487909905</v>
+        <v>176053.84872903093</v>
       </c>
       <c r="D24" s="142">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E24" s="128">
         <f t="shared" si="0"/>
@@ -14546,7 +14763,7 @@
       </c>
       <c r="F24" s="129">
         <f t="shared" si="1"/>
-        <v>876810.82600698969</v>
+        <v>129404.83451554866</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -14556,11 +14773,11 @@
       </c>
       <c r="C25" s="127">
         <f t="shared" si="2"/>
-        <v>1200526.7037334265</v>
+        <v>174449.25514006481</v>
       </c>
       <c r="D25" s="142">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E25" s="128">
         <f t="shared" si="0"/>
@@ -14568,7 +14785,7 @@
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>817058.30215128872</v>
+        <v>118727.23178338219</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -14578,11 +14795,11 @@
       </c>
       <c r="C26" s="127">
         <f t="shared" si="2"/>
-        <v>1208210.8291058543</v>
+        <v>172859.28617080644</v>
       </c>
       <c r="D26" s="142">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E26" s="128">
         <f t="shared" si="0"/>
@@ -14590,7 +14807,7 @@
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>761377.76737376256</v>
+        <v>108930.67186953689</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -14600,11 +14817,11 @@
       </c>
       <c r="C27" s="127">
         <f t="shared" si="2"/>
-        <v>1215944.137709738</v>
+        <v>171283.80852924779</v>
       </c>
       <c r="D27" s="142">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E27" s="128">
         <f t="shared" si="0"/>
@@ -14612,7 +14829,7 @@
       </c>
       <c r="F27" s="129">
         <f t="shared" si="1"/>
-        <v>709491.7255289295</v>
+        <v>99942.457140734448</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -14622,11 +14839,11 @@
       </c>
       <c r="C28" s="127">
         <f t="shared" si="2"/>
-        <v>1223726.9443486687</v>
+        <v>169722.69013823351</v>
       </c>
       <c r="D28" s="142">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E28" s="128">
         <f t="shared" si="0"/>
@@ -14634,7 +14851,7 @@
       </c>
       <c r="F28" s="129">
         <f t="shared" si="1"/>
-        <v>661141.59115826653</v>
+        <v>91695.888475657892</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -14644,11 +14861,11 @@
       </c>
       <c r="C29" s="127">
         <f t="shared" si="2"/>
-        <v>1231559.5658411772</v>
+        <v>168175.80012438865</v>
       </c>
       <c r="D29" s="142">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E29" s="128">
         <f t="shared" si="0"/>
@@ -14656,7 +14873,7 @@
       </c>
       <c r="F29" s="129">
         <f t="shared" si="1"/>
-        <v>616086.40077291708</v>
+        <v>84129.770308732128</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -14666,11 +14883,11 @@
       </c>
       <c r="C30" s="127">
         <f t="shared" si="2"/>
-        <v>1239442.3210336328</v>
+        <v>166643.00880714692</v>
       </c>
       <c r="D30" s="142">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E30" s="128">
         <f t="shared" si="0"/>
@@ -14678,7 +14895,7 @@
       </c>
       <c r="F30" s="129">
         <f t="shared" si="1"/>
-        <v>574101.61195934541</v>
+        <v>77187.956514309146</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -15128,7 +15345,7 @@
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>14628447.603675557</v>
+        <v>2261959.107405351</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -15140,7 +15357,7 @@
       </c>
       <c r="F51" s="129">
         <f t="shared" si="1"/>
-        <v>6775801.6708105225</v>
+        <v>1047724.7288640034</v>
       </c>
       <c r="H51" s="124"/>
     </row>
@@ -15151,7 +15368,7 @@
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
-        <v>14826136.513766104</v>
+        <v>2220066.018488951</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -15172,23 +15389,23 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="137">
         <f>F52</f>
-        <v>14826136.513766104</v>
+        <v>2220066.018488951</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="C55" s="135">
         <f>C77</f>
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="D55" s="135">
         <f>C76</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E55" s="135">
         <f>C75</f>
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F55" s="135">
         <f>C74</f>
@@ -15202,19 +15419,19 @@
       </c>
       <c r="B56" s="127">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>12788241.211071908</v>
+        <v>1791667.4501565206</v>
       </c>
       <c r="C56" s="127">
-        <v>13420515.524325915</v>
+        <v>1944399.2979690079</v>
       </c>
       <c r="D56" s="127">
-        <v>15004400.307915099</v>
+        <v>2282764.7283828212</v>
       </c>
       <c r="E56" s="127">
-        <v>15734411.148311835</v>
+        <v>2356418.6681816033</v>
       </c>
       <c r="F56" s="127">
-        <v>15985131.641699184</v>
+        <v>2510441.0600115755</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -15223,19 +15440,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="127">
-        <v>11535059.995283656</v>
+        <v>1512116.6840562024</v>
       </c>
       <c r="C57" s="127">
-        <v>12537042.701494243</v>
+        <v>1717259.7734446828</v>
       </c>
       <c r="D57" s="127">
-        <v>15473820.646910066</v>
+        <v>2282764.7283828203</v>
       </c>
       <c r="E57" s="127">
-        <v>17061254.876979411</v>
+        <v>2430140.4316197839</v>
       </c>
       <c r="F57" s="127">
-        <v>17644056.388321832</v>
+        <v>2770972.7148480518</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -15244,19 +15461,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="127">
-        <v>10298427.120539103</v>
+        <v>1267998.2938434205</v>
       </c>
       <c r="C58" s="127">
-        <v>11609617.700964648</v>
+        <v>1501500.7034384492</v>
       </c>
       <c r="D58" s="127">
-        <v>16054858.474479713</v>
+        <v>2282764.7283828198</v>
       </c>
       <c r="E58" s="127">
-        <v>18837634.59315075</v>
+        <v>2521391.5550040705</v>
       </c>
       <c r="F58" s="127">
-        <v>19925971.38051375</v>
+        <v>3129344.0576845901</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -15265,19 +15482,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="127">
-        <v>9284665.7634038813</v>
+        <v>1085590.6113440995</v>
       </c>
       <c r="C59" s="127">
-        <v>10806670.890222374</v>
+        <v>1330075.1609701074</v>
       </c>
       <c r="D59" s="127">
-        <v>16646842.841164071</v>
+        <v>2282764.7283828198</v>
       </c>
       <c r="E59" s="127">
-        <v>20805216.260669909</v>
+        <v>2614361.8160141576</v>
       </c>
       <c r="F59" s="127">
-        <v>22529016.1300468</v>
+        <v>3538148.349494644</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -15286,19 +15503,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="127">
-        <v>8517506.3067681082</v>
+        <v>956535.38724221883</v>
       </c>
       <c r="C60" s="127">
-        <v>10169747.747799639</v>
+        <v>1203526.2419221611</v>
       </c>
       <c r="D60" s="127">
-        <v>17197421.151398726</v>
+        <v>2282764.7283828198</v>
       </c>
       <c r="E60" s="127">
-        <v>22803257.715964336</v>
+        <v>2700829.317674215</v>
       </c>
       <c r="F60" s="127">
-        <v>25256927.882247664</v>
+        <v>3966562.8176588374</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -15307,19 +15524,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="127">
-        <v>7960756.9389042351</v>
+        <v>867219.36706202792</v>
       </c>
       <c r="C61" s="127">
-        <v>9688635.0268338043</v>
+        <v>1113428.7942805844</v>
       </c>
       <c r="D61" s="127">
-        <v>17683107.810972057</v>
+        <v>2282764.7283828198</v>
       </c>
       <c r="E61" s="127">
-        <v>24735455.482912373</v>
+        <v>2777105.6824751217</v>
       </c>
       <c r="F61" s="127">
-        <v>27984492.970261224</v>
+        <v>4394922.8427299513</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -15343,19 +15560,19 @@
     <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B64" s="136">
         <f>B55</f>
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="C64" s="136">
         <f>C55</f>
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="D64" s="136">
         <f>D55</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E64" s="136">
         <f>E55</f>
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F64" s="136">
         <f>F55</f>
@@ -15369,23 +15586,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15396,23 +15613,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>19.854624957586992</v>
+        <v>7.9882574709268273</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>20.931555394224837</v>
+        <v>8.7729421459311006</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>23.629330229954228</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>24.872731830523417</v>
+        <v>10.889758581018468</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>25.299775164022275</v>
+        <v>11.681073635524092</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15423,23 +15640,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>17.720125792249224</v>
+        <v>6.5520200051565114</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>19.426767436047015</v>
+        <v>7.605975946446522</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>24.428877262062496</v>
+        <v>10.511349502351729</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>27.132697744226626</v>
+        <v>11.268516114648602</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>28.125362910162355</v>
+        <v>13.019597328072329</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15450,23 +15667,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>15.613812829912655</v>
+        <v>5.2978221254722335</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>17.847117290797563</v>
+        <v>6.4974786804740496</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>25.418538407914397</v>
+        <v>10.511349502351727</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>30.158342378634668</v>
+        <v>11.737333582138968</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>32.012067869382236</v>
+        <v>14.860788308946084</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15477,23 +15694,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>13.887109027305996</v>
+        <v>4.3606730297840182</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>16.479486436019734</v>
+        <v>5.6167521129257443</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>26.426844406010588</v>
+        <v>10.511349502351727</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>33.509654522594523</v>
+        <v>12.214983398406025</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>36.445741766832334</v>
+        <v>16.961086756543974</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15504,23 +15721,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>12.580433504851692</v>
+        <v>3.6976308546751522</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>15.394637813364223</v>
+        <v>4.9665864871081711</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>27.364624935149575</v>
+        <v>10.511349502351727</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>36.912847743898624</v>
+        <v>12.659224232327279</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>41.092097205957991</v>
+        <v>19.162135670266764</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15530,23 +15747,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>11.63214203189</v>
+        <v>3.2387552941973317</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>14.575175561299575</v>
+        <v>4.5036962161272101</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>28.191877814792271</v>
+        <v>10.511349502351727</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>40.203891743647631</v>
+        <v>13.051106445379464</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>45.737862184255519</v>
+        <v>21.362904873756147</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15581,11 +15798,11 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>28.125362910162355</v>
+        <v>13.019597328072329</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
@@ -15595,7 +15812,7 @@
       </c>
       <c r="C75" s="146">
         <f>Scenarios!C38</f>
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D75" s="149">
         <f>Scenarios!C37</f>
@@ -15603,11 +15820,11 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>24.872731830523417</v>
+        <v>10.889758581018468</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
-        <v>0.192</v>
+        <v>0.18</v>
       </c>
       <c r="H75" s="124"/>
     </row>
@@ -15618,7 +15835,7 @@
       </c>
       <c r="C76" s="146">
         <f>Scenarios!C26</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D76" s="149">
         <f>Scenarios!C25</f>
@@ -15626,11 +15843,11 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.629330229954228</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
-        <v>0.57599999999999996</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="H76" s="124"/>
     </row>
@@ -15641,7 +15858,7 @@
       </c>
       <c r="C77" s="146">
         <f>Scenarios!C32</f>
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="D77" s="149">
         <f>Scenarios!C31</f>
@@ -15649,11 +15866,11 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>20.931555394224837</v>
+        <v>8.7729421459311006</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
-        <v>0.192</v>
+        <v>0.18</v>
       </c>
       <c r="H77" s="124"/>
     </row>
@@ -15664,7 +15881,7 @@
       </c>
       <c r="C78" s="146">
         <f>Scenarios!C50</f>
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="D78" s="149">
         <f>Scenarios!C49</f>
@@ -15672,11 +15889,11 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>17.720125792249224</v>
+        <v>6.5520200051565114</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
@@ -15773,7 +15990,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-15.4</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15793,7 +16010,7 @@
       </c>
       <c r="I4" s="270">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.36</v>
+        <v>0.49984047644368812</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -15802,7 +16019,7 @@
       </c>
       <c r="I5" s="270">
         <f t="shared" si="0"/>
-        <v>1.36</v>
+        <v>0.49984047644368812</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -15811,7 +16028,7 @@
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="E6" s="103" t="s">
         <v>285</v>
@@ -15822,7 +16039,7 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>24.681827133653531</v>
+        <v>10.693836205225988</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15831,17 +16048,17 @@
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
-        <v>1876773</v>
+        <v>266372</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E7" s="349" t="str">
+        <v>CNY</v>
+      </c>
+      <c r="E7" s="351" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
-        <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 六福珠宝(0590.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
-      </c>
-      <c r="F7" s="349"/>
+        <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国石油股份(0857.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
+      </c>
+      <c r="F7" s="351"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15856,14 +16073,14 @@
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>1294904.5955406395</v>
+        <v>306997.23769416759</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E8" s="349"/>
-      <c r="F8" s="349"/>
+        <v>CNY</v>
+      </c>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15878,14 +16095,14 @@
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
-        <v>1162832.9466554797</v>
+        <v>182621.17827062571</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E9" s="349"/>
-      <c r="F9" s="349"/>
+        <v>CNY</v>
+      </c>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15895,8 +16112,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="349"/>
-      <c r="F10" s="349"/>
+      <c r="E10" s="351"/>
+      <c r="F10" s="351"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15909,8 +16126,8 @@
       <c r="B11" s="163" t="s">
         <v>282</v>
       </c>
-      <c r="E11" s="349"/>
-      <c r="F11" s="349"/>
+      <c r="E11" s="351"/>
+      <c r="F11" s="351"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15928,8 +16145,8 @@
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="349"/>
-      <c r="F12" s="349"/>
+      <c r="E12" s="351"/>
+      <c r="F12" s="351"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -15946,8 +16163,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="349"/>
-      <c r="F13" s="349"/>
+      <c r="E13" s="351"/>
+      <c r="F13" s="351"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -15964,8 +16181,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="349"/>
-      <c r="F14" s="349"/>
+      <c r="E14" s="351"/>
+      <c r="F14" s="351"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15991,21 +16208,21 @@
       <c r="C18" s="154">
         <v>5</v>
       </c>
-      <c r="E18" s="349" t="s">
+      <c r="E18" s="351" t="s">
         <v>344</v>
       </c>
-      <c r="F18" s="350"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="350"/>
-      <c r="F19" s="350"/>
+      <c r="E19" s="352"/>
+      <c r="F19" s="352"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
         <v>314</v>
       </c>
-      <c r="E20" s="350"/>
-      <c r="F20" s="350"/>
+      <c r="E20" s="352"/>
+      <c r="F20" s="352"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -16013,14 +16230,14 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>15.4</v>
+        <v>5.55</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="350"/>
-      <c r="F21" s="350"/>
+      <c r="E21" s="352"/>
+      <c r="F21" s="352"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -16028,14 +16245,14 @@
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="350"/>
-      <c r="F22" s="350"/>
+      <c r="E22" s="352"/>
+      <c r="F22" s="352"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
@@ -16055,19 +16272,19 @@
         <v>5</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="348"/>
-      <c r="F25" s="348"/>
+      <c r="E25" s="350"/>
+      <c r="F25" s="350"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
         <v>136</v>
       </c>
       <c r="C26" s="168">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="348"/>
-      <c r="F26" s="348"/>
+      <c r="E26" s="350"/>
+      <c r="F26" s="350"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -16075,14 +16292,14 @@
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>23.629330229954228</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="348"/>
-      <c r="F27" s="348"/>
+      <c r="E27" s="350"/>
+      <c r="F27" s="350"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -16092,8 +16309,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="348"/>
-      <c r="F28" s="348"/>
+      <c r="E28" s="350"/>
+      <c r="F28" s="350"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
@@ -16113,19 +16330,19 @@
         <v>5</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="E31" s="350"/>
+      <c r="F31" s="350"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
         <v>136</v>
       </c>
       <c r="C32" s="168">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="348"/>
-      <c r="F32" s="348"/>
+      <c r="E32" s="350"/>
+      <c r="F32" s="350"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -16133,14 +16350,14 @@
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>20.931555394224837</v>
+        <v>8.7729421459311006</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="348"/>
-      <c r="F33" s="348"/>
+      <c r="E33" s="350"/>
+      <c r="F33" s="350"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -16150,8 +16367,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="348"/>
-      <c r="F34" s="348"/>
+      <c r="E34" s="350"/>
+      <c r="F34" s="350"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
@@ -16171,19 +16388,19 @@
         <v>5</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
         <v>136</v>
       </c>
       <c r="C38" s="168">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="348"/>
-      <c r="F38" s="348"/>
+      <c r="E38" s="350"/>
+      <c r="F38" s="350"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -16191,14 +16408,14 @@
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>24.872731830523417</v>
+        <v>10.889758581018468</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="348"/>
-      <c r="F39" s="348"/>
+      <c r="E39" s="350"/>
+      <c r="F39" s="350"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -16209,8 +16426,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -16218,7 +16435,7 @@
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>23.338455582922187</v>
+        <v>10.239349846800954</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16272,19 +16489,19 @@
         <v>10</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="348"/>
-      <c r="F49" s="348"/>
+      <c r="E49" s="350"/>
+      <c r="F49" s="350"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
         <v>136</v>
       </c>
       <c r="C50" s="168">
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -16292,25 +16509,25 @@
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>17.720125792249224</v>
+        <v>6.5520200051565114</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="348"/>
-      <c r="F51" s="348"/>
+      <c r="E51" s="350"/>
+      <c r="F51" s="350"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
         <v>149</v>
       </c>
       <c r="C52" s="169">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="348"/>
-      <c r="F52" s="348"/>
+      <c r="E52" s="350"/>
+      <c r="F52" s="350"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
@@ -16330,8 +16547,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="348"/>
-      <c r="F55" s="348"/>
+      <c r="E55" s="350"/>
+      <c r="F55" s="350"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -16341,8 +16558,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="348"/>
-      <c r="F56" s="348"/>
+      <c r="E56" s="350"/>
+      <c r="F56" s="350"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -16350,25 +16567,25 @@
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>28.125362910162355</v>
+        <v>13.019597328072329</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="348"/>
-      <c r="F57" s="348"/>
+      <c r="E57" s="350"/>
+      <c r="F57" s="350"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
         <v>149</v>
       </c>
       <c r="C58" s="169">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -16376,7 +16593,7 @@
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>23.321827133653532</v>
+        <v>10.1939957287823</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16641,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="155">
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
@@ -16437,7 +16654,7 @@
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>23.325699825167451</v>
+        <v>10.189224696681462</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
@@ -16461,7 +16678,7 @@
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E69" s="138"/>
     </row>
@@ -16471,7 +16688,7 @@
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E70" s="287" t="s">
         <v>305</v>
@@ -16500,7 +16717,7 @@
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
-        <v>-8.2632171394856124E-2</v>
+        <v>-0.11935703046565523</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16533,7 +16750,7 @@
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
-        <v>1.36</v>
+        <v>0.49984047644368812</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16560,7 +16777,7 @@
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.8648148148148147</v>
+        <v>1.0529047073235096</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
@@ -16572,7 +16789,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>13.496427739382831</v>
+        <v>5.8993030837860534</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16582,7 +16799,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>16.361242554197645</v>
+        <v>6.9522077911095632</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16593,7 +16810,7 @@
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.29845794412101279</v>
+        <v>0.31800954443405249</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16610,7 +16827,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>15.4</v>
+        <v>5.55</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16623,7 +16840,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22622690546409729</v>
+        <v>0.29981048955907563</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAAD931-CCEA-46A1-AC8B-04B64F444114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5D8BA2-09C5-4938-ACC4-F059F1A58587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="416">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2306,18 +2306,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>0857.HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CNY</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>中国石油股份</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CFO/Net Income</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2327,6 +2319,18 @@
   </si>
   <si>
     <t>Net Change in Cash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0168.HK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>青島啤酒股份</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Income/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3709,29 +3713,29 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4064,7 +4068,7 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B4" s="45" t="str">
         <f>D5&amp;" Stock Information"</f>
-        <v>0857.HK Stock Information</v>
+        <v>0168.HK Stock Information</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4076,10 +4080,10 @@
         <v>328</v>
       </c>
       <c r="C5" s="339" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4087,7 +4091,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>5.55</v>
+        <v>54.75</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4099,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="51">
-        <v>183020977818</v>
+        <v>1364196788</v>
       </c>
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
@@ -4132,7 +4136,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>1015766.4268899</v>
+        <v>74689.774143000002</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4142,13 +4146,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="341" t="s">
+      <c r="B12" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C12" s="341"/>
-      <c r="D12" s="341"/>
-      <c r="E12" s="341"/>
-      <c r="F12" s="341"/>
+      <c r="C12" s="343"/>
+      <c r="D12" s="343"/>
+      <c r="E12" s="343"/>
+      <c r="F12" s="343"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4163,7 +4167,7 @@
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
-        <v xml:space="preserve">Negative Growth </v>
+        <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="E15" s="5"/>
     </row>
@@ -4172,7 +4176,7 @@
         <v>361</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4182,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>0.94030000000000002</v>
+        <v>0.94020000000000004</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4215,7 +4219,7 @@
       </c>
       <c r="C20" s="258">
         <f>C129</f>
-        <v>6.9522077911095632</v>
+        <v>30.327492930578011</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4230,7 +4234,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.29981048955907563</v>
+        <v>-2.5075247395360156E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4250,22 +4254,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="341" t="s">
+      <c r="B25" s="343" t="s">
         <v>378</v>
       </c>
-      <c r="C25" s="341"/>
-      <c r="D25" s="341"/>
-      <c r="E25" s="341"/>
-      <c r="F25" s="341"/>
+      <c r="C25" s="343"/>
+      <c r="D25" s="343"/>
+      <c r="E25" s="343"/>
+      <c r="F25" s="343"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="343" t="s">
+      <c r="B26" s="346" t="s">
         <v>353</v>
       </c>
-      <c r="C26" s="343"/>
-      <c r="D26" s="343"/>
-      <c r="E26" s="343"/>
-      <c r="F26" s="343"/>
+      <c r="C26" s="346"/>
+      <c r="D26" s="346"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -4273,17 +4277,17 @@
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
-        <v>1000000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="342" t="s">
+      <c r="B29" s="344" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="342"/>
-      <c r="D29" s="342"/>
-      <c r="E29" s="342"/>
-      <c r="F29" s="342"/>
+      <c r="C29" s="344"/>
+      <c r="D29" s="344"/>
+      <c r="E29" s="344"/>
+      <c r="F29" s="344"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,7 +4295,7 @@
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
-        <v>266372</v>
+        <v>4487792577</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4303,13 +4307,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="342" t="s">
+      <c r="B32" s="344" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="342"/>
-      <c r="D32" s="342"/>
-      <c r="E32" s="342"/>
-      <c r="F32" s="342"/>
+      <c r="C32" s="344"/>
+      <c r="D32" s="344"/>
+      <c r="E32" s="344"/>
+      <c r="F32" s="344"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4317,7 +4321,7 @@
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
-        <v>229584</v>
+        <v>1191305772</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4330,7 +4334,7 @@
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
-        <v>-229584</v>
+        <v>-1191305772</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4338,13 +4342,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="342" t="s">
+      <c r="B36" s="344" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="342"/>
-      <c r="D36" s="342"/>
-      <c r="E36" s="342"/>
-      <c r="F36" s="342"/>
+      <c r="C36" s="344"/>
+      <c r="D36" s="344"/>
+      <c r="E36" s="344"/>
+      <c r="F36" s="344"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4352,7 +4356,7 @@
       </c>
       <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
-        <v>18538.000000000004</v>
+        <v>0</v>
       </c>
       <c r="D37" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4360,13 +4364,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="342" t="s">
+      <c r="B39" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="342"/>
-      <c r="D39" s="342"/>
-      <c r="E39" s="342"/>
-      <c r="F39" s="342"/>
+      <c r="C39" s="344"/>
+      <c r="D39" s="344"/>
+      <c r="E39" s="344"/>
+      <c r="F39" s="344"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4374,7 +4378,7 @@
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
-        <v>8177.2376941676157</v>
+        <v>176342732.47651258</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4389,7 +4393,7 @@
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
-        <v>-24063</v>
+        <v>-21837054</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4404,7 +4408,7 @@
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
-        <v>-15885.762305832384</v>
+        <v>154505678.47651258</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4422,7 +4426,7 @@
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
-        <v>-19147</v>
+        <v>-146792828</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4430,13 +4434,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="342" t="s">
+      <c r="B47" s="344" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="342"/>
-      <c r="D47" s="342"/>
-      <c r="E47" s="342"/>
-      <c r="F47" s="342"/>
+      <c r="C47" s="344"/>
+      <c r="D47" s="344"/>
+      <c r="E47" s="344"/>
+      <c r="F47" s="344"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4444,7 +4448,7 @@
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
-        <v>-67256.059423541898</v>
+        <v>-1160574563.8691282</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4452,7 +4456,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="342" t="s">
+      <c r="B50" s="344" t="s">
         <v>352</v>
       </c>
       <c r="C50" s="345"/>
@@ -4474,22 +4478,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="341" t="s">
+      <c r="B53" s="343" t="s">
         <v>357</v>
       </c>
-      <c r="C53" s="341"/>
-      <c r="D53" s="341"/>
-      <c r="E53" s="341"/>
-      <c r="F53" s="341"/>
+      <c r="C53" s="343"/>
+      <c r="D53" s="343"/>
+      <c r="E53" s="343"/>
+      <c r="F53" s="343"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="341" t="s">
+      <c r="B54" s="343" t="s">
         <v>379</v>
       </c>
-      <c r="C54" s="341"/>
-      <c r="D54" s="341"/>
-      <c r="E54" s="341"/>
-      <c r="F54" s="341"/>
+      <c r="C54" s="343"/>
+      <c r="D54" s="343"/>
+      <c r="E54" s="343"/>
+      <c r="F54" s="343"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4497,7 +4501,7 @@
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
-        <v>306997.23769416759</v>
+        <v>3154061396.4765129</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4510,7 +4514,7 @@
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
-        <v>182621.17827062571</v>
+        <v>3334930863.6073847</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4523,7 +4527,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C125</f>
-        <v>0.16905332700711728</v>
+        <v>4.1980338459190879E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4532,7 +4536,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>9.0061347106970835E-2</v>
+        <v>4.2738405022151121E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4550,22 +4554,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="341" t="s">
+      <c r="B63" s="343" t="s">
         <v>380</v>
       </c>
-      <c r="C63" s="341"/>
-      <c r="D63" s="341"/>
-      <c r="E63" s="341"/>
-      <c r="F63" s="341"/>
+      <c r="C63" s="343"/>
+      <c r="D63" s="343"/>
+      <c r="E63" s="343"/>
+      <c r="F63" s="343"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="343" t="s">
+      <c r="B64" s="346" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="343"/>
-      <c r="D64" s="343"/>
-      <c r="E64" s="343"/>
-      <c r="F64" s="343"/>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4623,22 +4627,22 @@
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="341" t="s">
+      <c r="B73" s="343" t="s">
         <v>381</v>
       </c>
-      <c r="C73" s="341"/>
-      <c r="D73" s="341"/>
-      <c r="E73" s="341"/>
-      <c r="F73" s="341"/>
+      <c r="C73" s="343"/>
+      <c r="D73" s="343"/>
+      <c r="E73" s="343"/>
+      <c r="F73" s="343"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="341" t="s">
+      <c r="B74" s="343" t="s">
         <v>382</v>
       </c>
-      <c r="C74" s="341"/>
-      <c r="D74" s="341"/>
-      <c r="E74" s="341"/>
-      <c r="F74" s="341"/>
+      <c r="C74" s="343"/>
+      <c r="D74" s="343"/>
+      <c r="E74" s="343"/>
+      <c r="F74" s="343"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4654,7 +4658,7 @@
       </c>
       <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>11.728074561118762</v>
+        <v>28.730294133008758</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4675,13 +4679,13 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="341" t="s">
+      <c r="B81" s="343" t="s">
         <v>383</v>
       </c>
-      <c r="C81" s="341"/>
-      <c r="D81" s="341"/>
-      <c r="E81" s="341"/>
-      <c r="F81" s="341"/>
+      <c r="C81" s="343"/>
+      <c r="D81" s="343"/>
+      <c r="E81" s="343"/>
+      <c r="F81" s="343"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4694,13 +4698,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="341" t="s">
+      <c r="B85" s="343" t="s">
         <v>358</v>
       </c>
-      <c r="C85" s="341"/>
-      <c r="D85" s="341"/>
-      <c r="E85" s="341"/>
-      <c r="F85" s="341"/>
+      <c r="C85" s="343"/>
+      <c r="D85" s="343"/>
+      <c r="E85" s="343"/>
+      <c r="F85" s="343"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4708,7 +4712,7 @@
       </c>
       <c r="C86" s="191">
         <f>Valuation_Model!C7</f>
-        <v>245714</v>
+        <v>285396383</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4721,7 +4725,7 @@
       </c>
       <c r="C87" s="254">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.2623955841267334</v>
+        <v>0.19669426116300168</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4739,7 +4743,7 @@
       </c>
       <c r="C90" s="191">
         <f>BS!C66</f>
-        <v>238880</v>
+        <v>17978772896</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4752,7 +4756,7 @@
       </c>
       <c r="C91" s="191">
         <f>Valuation_Model!C8</f>
-        <v>2536.5589373550902</v>
+        <v>12838413003.943913</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4765,7 +4769,7 @@
       </c>
       <c r="C92" s="254">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.3031983531236581E-2</v>
+        <v>8.8481925866461335</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4783,7 +4787,7 @@
       </c>
       <c r="C95" s="191">
         <f>Valuation_Model!C9</f>
-        <v>6352.8</v>
+        <v>2755411575.5</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4796,7 +4800,7 @@
       </c>
       <c r="C96" s="254">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>3.2638541828468509E-2</v>
+        <v>1.899020717592468</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4804,13 +4808,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="341" t="s">
+      <c r="B98" s="343" t="s">
         <v>384</v>
       </c>
-      <c r="C98" s="341"/>
-      <c r="D98" s="341"/>
-      <c r="E98" s="341"/>
-      <c r="F98" s="341"/>
+      <c r="C98" s="343"/>
+      <c r="D98" s="343"/>
+      <c r="E98" s="343"/>
+      <c r="F98" s="343"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4818,7 +4822,7 @@
       </c>
       <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
-        <v>10.511349502351733</v>
+        <v>39.280813176084358</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4836,13 +4840,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="342" t="s">
+      <c r="B104" s="344" t="s">
         <v>385</v>
       </c>
-      <c r="C104" s="342"/>
-      <c r="D104" s="342"/>
-      <c r="E104" s="342"/>
-      <c r="F104" s="342"/>
+      <c r="C104" s="344"/>
+      <c r="D104" s="344"/>
+      <c r="E104" s="344"/>
+      <c r="F104" s="344"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="266" t="s">
@@ -4868,15 +4872,15 @@
       </c>
       <c r="C107" s="262">
         <f>Valuation_Model!C74</f>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="D107" s="263">
         <f>Valuation_Model!D74</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E107" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>13.02 HKD</v>
+        <v>60.57 HKD</v>
       </c>
       <c r="F107" s="265">
         <f>Valuation_Model!F74</f>
@@ -4890,15 +4894,15 @@
       </c>
       <c r="C108" s="249">
         <f>Valuation_Model!C75</f>
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="D108" s="250">
         <f>Valuation_Model!D75</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>10.89 HKD</v>
+        <v>45.43 HKD</v>
       </c>
       <c r="F108" s="252">
         <f>Valuation_Model!F75</f>
@@ -4912,15 +4916,15 @@
       </c>
       <c r="C109" s="249">
         <f>Valuation_Model!C76</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D109" s="250">
         <f>Valuation_Model!D76</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>10.51 HKD</v>
+        <v>43.18 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F76</f>
@@ -4934,15 +4938,15 @@
       </c>
       <c r="C110" s="249">
         <f>Valuation_Model!C77</f>
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="D110" s="250">
         <f>Valuation_Model!D77</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>8.77 HKD</v>
+        <v>41.14 HKD</v>
       </c>
       <c r="F110" s="252">
         <f>Valuation_Model!F77</f>
@@ -4956,15 +4960,15 @@
       </c>
       <c r="C111" s="249">
         <f>Valuation_Model!C78</f>
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="D111" s="250">
         <f>Valuation_Model!D78</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E111" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>6.55 HKD</v>
+        <v>39.28 HKD</v>
       </c>
       <c r="F111" s="252">
         <f>Valuation_Model!F78</f>
@@ -4977,7 +4981,7 @@
       </c>
       <c r="C113" s="247">
         <f>Scenarios!C60</f>
-        <v>10.1939957287823</v>
+        <v>43.888571047174302</v>
       </c>
       <c r="D113" s="242" t="str">
         <f>Market_currency</f>
@@ -4985,13 +4989,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="346" t="s">
+      <c r="B115" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C115" s="346"/>
-      <c r="D115" s="346"/>
-      <c r="E115" s="346"/>
-      <c r="F115" s="346"/>
+      <c r="C115" s="347"/>
+      <c r="D115" s="347"/>
+      <c r="E115" s="347"/>
+      <c r="F115" s="347"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
@@ -5004,22 +5008,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="344" t="s">
+      <c r="B119" s="348" t="s">
         <v>386</v>
       </c>
-      <c r="C119" s="344"/>
-      <c r="D119" s="344"/>
-      <c r="E119" s="344"/>
-      <c r="F119" s="344"/>
+      <c r="C119" s="348"/>
+      <c r="D119" s="348"/>
+      <c r="E119" s="348"/>
+      <c r="F119" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="341" t="s">
+      <c r="B120" s="343" t="s">
         <v>387</v>
       </c>
-      <c r="C120" s="341"/>
-      <c r="D120" s="341"/>
-      <c r="E120" s="341"/>
-      <c r="F120" s="341"/>
+      <c r="C120" s="343"/>
+      <c r="D120" s="343"/>
+      <c r="E120" s="343"/>
+      <c r="F120" s="343"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
@@ -5050,7 +5054,7 @@
       </c>
       <c r="C124" s="243">
         <f>Scenarios!C77</f>
-        <v>0.49984047644368812</v>
+        <v>2.339927674962774</v>
       </c>
       <c r="D124" s="242" t="str">
         <f>Market_currency</f>
@@ -5069,7 +5073,7 @@
       </c>
       <c r="C127" s="246">
         <f>Scenarios!C81</f>
-        <v>1.0529047073235096</v>
+        <v>4.9290143153151025</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5079,7 +5083,7 @@
       </c>
       <c r="C128" s="246">
         <f>Scenarios!C82</f>
-        <v>5.8993030837860534</v>
+        <v>25.398478615262906</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5088,7 +5092,7 @@
       </c>
       <c r="C129" s="245">
         <f>Scenarios!C83</f>
-        <v>6.9522077911095632</v>
+        <v>30.327492930578011</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5101,7 +5105,7 @@
       </c>
       <c r="C130" s="94">
         <f>Scenarios!F83</f>
-        <v>0.31800954443405249</v>
+        <v>0.30898882768409019</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5115,13 +5119,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="348" t="s">
+      <c r="B134" s="342" t="s">
         <v>394</v>
       </c>
-      <c r="C134" s="341"/>
-      <c r="D134" s="341"/>
-      <c r="E134" s="341"/>
-      <c r="F134" s="341"/>
+      <c r="C134" s="343"/>
+      <c r="D134" s="343"/>
+      <c r="E134" s="343"/>
+      <c r="F134" s="343"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="240" t="s">
@@ -5158,13 +5162,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="342" t="s">
+      <c r="B143" s="344" t="s">
         <v>399</v>
       </c>
-      <c r="C143" s="342"/>
-      <c r="D143" s="342"/>
-      <c r="E143" s="342"/>
-      <c r="F143" s="342"/>
+      <c r="C143" s="344"/>
+      <c r="D143" s="344"/>
+      <c r="E143" s="344"/>
+      <c r="F143" s="344"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5172,22 +5176,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="347" t="s">
+      <c r="B146" s="341" t="s">
         <v>400</v>
       </c>
-      <c r="C146" s="347"/>
-      <c r="D146" s="347"/>
-      <c r="E146" s="347"/>
-      <c r="F146" s="347"/>
+      <c r="C146" s="341"/>
+      <c r="D146" s="341"/>
+      <c r="E146" s="341"/>
+      <c r="F146" s="341"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="347" t="s">
+      <c r="B147" s="341" t="s">
         <v>401</v>
       </c>
-      <c r="C147" s="347"/>
-      <c r="D147" s="347"/>
-      <c r="E147" s="347"/>
-      <c r="F147" s="347"/>
+      <c r="C147" s="341"/>
+      <c r="D147" s="341"/>
+      <c r="E147" s="341"/>
+      <c r="F147" s="341"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5211,17 +5215,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5238,6 +5231,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5276,47 +5280,47 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="107">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="D1" s="38">
         <f>EOMONTH(EDATE(C1,-12),0)</f>
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="E1" s="38">
         <f t="shared" ref="E1:M1" si="0">EOMONTH(EDATE(D1,-12),0)</f>
-        <v>44561</v>
+        <v>44926</v>
       </c>
       <c r="F1" s="38">
         <f t="shared" si="0"/>
-        <v>44196</v>
+        <v>44561</v>
       </c>
       <c r="G1" s="38">
         <f t="shared" si="0"/>
-        <v>43830</v>
+        <v>44196</v>
       </c>
       <c r="H1" s="38">
         <f t="shared" si="0"/>
-        <v>43465</v>
+        <v>43830</v>
       </c>
       <c r="I1" s="38">
         <f t="shared" si="0"/>
-        <v>43100</v>
+        <v>43465</v>
       </c>
       <c r="J1" s="38">
         <f t="shared" si="0"/>
-        <v>42735</v>
+        <v>43100</v>
       </c>
       <c r="K1" s="38">
         <f t="shared" si="0"/>
-        <v>42369</v>
+        <v>42735</v>
       </c>
       <c r="L1" s="38">
         <f t="shared" si="0"/>
-        <v>42004</v>
+        <v>42369</v>
       </c>
       <c r="M1" s="38">
         <f t="shared" si="0"/>
-        <v>41639</v>
+        <v>42004</v>
       </c>
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
@@ -5340,7 +5344,7 @@
         <v>27</v>
       </c>
       <c r="C3" s="109">
-        <v>1000000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
@@ -5348,7 +5352,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="193">
-        <v>3011012</v>
+        <v>32137830111</v>
       </c>
       <c r="D4" s="184"/>
       <c r="E4" s="184"/>
@@ -5366,7 +5370,8 @@
         <v>44</v>
       </c>
       <c r="C5" s="193">
-        <v>2302385</v>
+        <f>19209915823+2328256391</f>
+        <v>21538172214</v>
       </c>
       <c r="D5" s="184"/>
       <c r="E5" s="184"/>
@@ -5384,7 +5389,8 @@
         <v>55</v>
       </c>
       <c r="C6" s="193">
-        <v>420298</v>
+        <f>1406578781+C7</f>
+        <v>6009098645</v>
       </c>
       <c r="D6" s="184"/>
       <c r="E6" s="184"/>
@@ -5402,7 +5408,7 @@
         <v>62</v>
       </c>
       <c r="C7" s="194">
-        <v>70260</v>
+        <v>4602519864</v>
       </c>
       <c r="D7" s="192"/>
       <c r="E7" s="192"/>
@@ -5420,7 +5426,7 @@
         <v>50</v>
       </c>
       <c r="C8" s="193">
-        <v>21957</v>
+        <v>102766675</v>
       </c>
       <c r="D8" s="184"/>
       <c r="E8" s="184"/>
@@ -5438,7 +5444,7 @@
         <v>161</v>
       </c>
       <c r="C9" s="193">
-        <v>18538</v>
+        <v>48272283</v>
       </c>
       <c r="D9" s="184"/>
       <c r="E9" s="184"/>
@@ -5455,9 +5461,7 @@
       <c r="B10" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="184">
-        <v>0</v>
-      </c>
+      <c r="C10" s="184"/>
       <c r="D10" s="184"/>
       <c r="E10" s="184"/>
       <c r="F10" s="184"/>
@@ -5473,9 +5477,7 @@
       <c r="B11" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="193">
-        <v>0</v>
-      </c>
+      <c r="C11" s="193"/>
       <c r="D11" s="184"/>
       <c r="E11" s="184"/>
       <c r="F11" s="184"/>
@@ -5492,7 +5494,7 @@
         <v>39</v>
       </c>
       <c r="C12" s="193">
-        <v>24063</v>
+        <v>21837054</v>
       </c>
       <c r="D12" s="184"/>
       <c r="E12" s="184"/>
@@ -5510,7 +5512,7 @@
         <v>68</v>
       </c>
       <c r="C13" s="193">
-        <v>8265</v>
+        <v>616771200</v>
       </c>
       <c r="D13" s="184"/>
       <c r="E13" s="184"/>
@@ -5528,7 +5530,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="193">
-        <v>57167</v>
+        <v>1389716314</v>
       </c>
       <c r="D14" s="184"/>
       <c r="E14" s="184"/>
@@ -5546,7 +5548,7 @@
         <v>43</v>
       </c>
       <c r="C15" s="195">
-        <v>180291</v>
+        <v>4491776686</v>
       </c>
       <c r="D15" s="185"/>
       <c r="E15" s="185"/>
@@ -5564,7 +5566,7 @@
         <v>45</v>
       </c>
       <c r="C16" s="193">
-        <v>19147</v>
+        <v>146792828</v>
       </c>
       <c r="D16" s="184"/>
       <c r="E16" s="184"/>
@@ -5588,7 +5590,7 @@
         <v>48</v>
       </c>
       <c r="C19" s="184">
-        <v>229584</v>
+        <v>1191305772</v>
       </c>
       <c r="D19" s="184"/>
       <c r="E19" s="184"/>
@@ -5606,7 +5608,8 @@
         <v>54</v>
       </c>
       <c r="C20" s="184">
-        <v>115297</v>
+        <f>C19</f>
+        <v>1191305772</v>
       </c>
       <c r="D20" s="184"/>
       <c r="E20" s="184"/>
@@ -5624,7 +5627,7 @@
         <v>53</v>
       </c>
       <c r="C21" s="184">
-        <v>31061</v>
+        <v>583532518</v>
       </c>
       <c r="D21" s="184"/>
       <c r="E21" s="184"/>
@@ -5642,7 +5645,7 @@
         <v>389</v>
       </c>
       <c r="C22" s="184">
-        <v>456596</v>
+        <v>5154661132</v>
       </c>
       <c r="D22" s="184"/>
       <c r="E22" s="184"/>
@@ -5660,7 +5663,7 @@
         <v>391</v>
       </c>
       <c r="C23" s="184">
-        <v>-255789</v>
+        <v>-7421783375</v>
       </c>
       <c r="D23" s="184"/>
       <c r="E23" s="184"/>
@@ -5678,7 +5681,7 @@
         <v>390</v>
       </c>
       <c r="C24" s="184">
-        <v>-146572</v>
+        <v>-2983143705</v>
       </c>
       <c r="D24" s="184"/>
       <c r="E24" s="184"/>
@@ -5697,8 +5700,8 @@
         <v>Dividend per share (HKD)</v>
       </c>
       <c r="C25" s="39">
-        <f>(0.25+0.22)/Exchange_Rate</f>
-        <v>0.49984047644368812</v>
+        <f>2.2/Exchange_Rate</f>
+        <v>2.339927674962774</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -5715,15 +5718,17 @@
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="100" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="184">
-        <f>68761+31090</f>
-        <v>99851</v>
+      <c r="C28" s="186">
+        <f>BS!C4</f>
+        <v>185704725</v>
       </c>
       <c r="D28" s="184"/>
       <c r="E28" s="184"/>
@@ -5740,8 +5745,9 @@
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="184">
-        <v>180533</v>
+      <c r="C29" s="186">
+        <f>BS!C6</f>
+        <v>3576387537</v>
       </c>
       <c r="D29" s="184"/>
       <c r="E29" s="184"/>
@@ -5758,8 +5764,9 @@
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="185">
-        <v>1122089</v>
+      <c r="C30" s="189">
+        <f>BS!C33+BS!C42</f>
+        <v>21560843821</v>
       </c>
       <c r="D30" s="185"/>
       <c r="E30" s="185"/>
@@ -5776,8 +5783,9 @@
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="185">
-        <v>1630621</v>
+      <c r="C31" s="189">
+        <f>BS!G27</f>
+        <v>29859542011</v>
       </c>
       <c r="D31" s="185"/>
       <c r="E31" s="185"/>
@@ -5794,8 +5802,9 @@
       <c r="B32" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="184">
-        <v>184211</v>
+      <c r="C32" s="186">
+        <f>BS!G28</f>
+        <v>799157484</v>
       </c>
       <c r="D32" s="184"/>
       <c r="E32" s="184"/>
@@ -5835,7 +5844,7 @@
       </c>
       <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
-        <v>3011012</v>
+        <v>32137830111</v>
       </c>
       <c r="D36" s="186" t="str">
         <f t="shared" si="1"/>
@@ -5884,7 +5893,7 @@
       </c>
       <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
-        <v>-2302385</v>
+        <v>-21538172214</v>
       </c>
       <c r="D37" s="186" t="str">
         <f t="shared" si="2"/>
@@ -5933,7 +5942,7 @@
       </c>
       <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
-        <v>708627</v>
+        <v>10599657897</v>
       </c>
       <c r="D38" s="187" t="str">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
@@ -5982,7 +5991,7 @@
       </c>
       <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
-        <v>-420298</v>
+        <v>-6009098645</v>
       </c>
       <c r="D39" s="186" t="str">
         <f t="shared" si="13"/>
@@ -6031,7 +6040,7 @@
       </c>
       <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
-        <v>-70260</v>
+        <v>-4602519864</v>
       </c>
       <c r="D40" s="188" t="str">
         <f t="shared" si="14"/>
@@ -6080,7 +6089,7 @@
       </c>
       <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
-        <v>-350038</v>
+        <v>-1406578781</v>
       </c>
       <c r="D41" s="188" t="str">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
@@ -6129,7 +6138,7 @@
       </c>
       <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
-        <v>-21957</v>
+        <v>-102766675</v>
       </c>
       <c r="D42" s="186" t="str">
         <f t="shared" si="16"/>
@@ -6178,7 +6187,7 @@
       </c>
       <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
-        <v>266372</v>
+        <v>4487792577</v>
       </c>
       <c r="D43" s="189" t="str">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
@@ -6227,7 +6236,7 @@
       </c>
       <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
-        <v>-13116</v>
+        <v>798766277</v>
       </c>
       <c r="D44" s="190" t="str">
         <f t="shared" si="18"/>
@@ -6276,7 +6285,7 @@
       </c>
       <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
-        <v>-15798</v>
+        <v>594934146</v>
       </c>
       <c r="D45" s="191" t="str">
         <f t="shared" si="19"/>
@@ -6325,7 +6334,7 @@
       </c>
       <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
-        <v>-57167</v>
+        <v>-1389716314</v>
       </c>
       <c r="D46" s="186" t="str">
         <f t="shared" si="20"/>
@@ -6374,7 +6383,7 @@
       </c>
       <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
-        <v>180291</v>
+        <v>4491776686</v>
       </c>
       <c r="D47" s="189" t="str">
         <f t="shared" si="21"/>
@@ -6423,7 +6432,7 @@
       </c>
       <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
-        <v>-19147</v>
+        <v>-146792828</v>
       </c>
       <c r="D48" s="186" t="str">
         <f t="shared" si="22"/>
@@ -6477,7 +6486,7 @@
       </c>
       <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
-        <v>-24063</v>
+        <v>-21837054</v>
       </c>
       <c r="D51" s="186" t="str">
         <f t="shared" si="23"/>
@@ -6526,7 +6535,7 @@
       </c>
       <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
-        <v>8265</v>
+        <v>616771200</v>
       </c>
       <c r="D52" s="186" t="str">
         <f t="shared" si="24"/>
@@ -6580,7 +6589,7 @@
       </c>
       <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
-        <v>18538</v>
+        <v>48272283</v>
       </c>
       <c r="D55" s="191" t="str">
         <f t="shared" si="25"/>
@@ -6727,7 +6736,7 @@
       </c>
       <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
-        <v>-31654</v>
+        <v>750493994</v>
       </c>
       <c r="D58" s="191" t="str">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
@@ -6782,7 +6791,7 @@
       </c>
       <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
-        <v>-229584</v>
+        <v>-1191305772</v>
       </c>
       <c r="D61" s="186" t="str">
         <f t="shared" si="29"/>
@@ -6831,7 +6840,7 @@
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
-        <v>-115297</v>
+        <v>-1191305772</v>
       </c>
       <c r="D62" s="186" t="str">
         <f t="shared" si="30"/>
@@ -6880,7 +6889,7 @@
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
-        <v>-31061</v>
+        <v>-583532518</v>
       </c>
       <c r="D63" s="186" t="str">
         <f t="shared" si="31"/>
@@ -6925,11 +6934,11 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C64" s="186">
         <f>IF(C$4="","",C22+C23+C24)</f>
-        <v>54235</v>
+        <v>-5250265948</v>
       </c>
       <c r="D64" s="186" t="str">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
@@ -6978,7 +6987,7 @@
       </c>
       <c r="C65" s="75">
         <f t="shared" ref="C65:M65" si="33">IF(C$4="","",C25)</f>
-        <v>0.49984047644368812</v>
+        <v>2.339927674962774</v>
       </c>
       <c r="D65" s="75" t="str">
         <f t="shared" si="33"/>
@@ -7304,7 +7313,7 @@
       </c>
       <c r="C76" s="78">
         <f>IF(C$4="","",C79+C80)</f>
-        <v>2752710</v>
+        <v>51420385832</v>
       </c>
       <c r="D76" s="78" t="str">
         <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
@@ -7353,7 +7362,7 @@
       </c>
       <c r="C77" s="74">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
-        <v>99851</v>
+        <v>185704725</v>
       </c>
       <c r="D77" s="74" t="str">
         <f t="shared" si="40"/>
@@ -7387,7 +7396,7 @@
       </c>
       <c r="C78" s="74">
         <f t="shared" si="40"/>
-        <v>180533</v>
+        <v>3576387537</v>
       </c>
       <c r="D78" s="74" t="str">
         <f t="shared" si="40"/>
@@ -7421,7 +7430,7 @@
       </c>
       <c r="C79" s="58">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
-        <v>1122089</v>
+        <v>21560843821</v>
       </c>
       <c r="D79" s="58" t="str">
         <f t="shared" si="41"/>
@@ -7470,7 +7479,7 @@
       </c>
       <c r="C80" s="58">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
-        <v>1630621</v>
+        <v>29859542011</v>
       </c>
       <c r="D80" s="58" t="str">
         <f t="shared" si="42"/>
@@ -7530,7 +7539,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7569,7 +7578,7 @@
       </c>
       <c r="H1" s="110">
         <f>Data!C3</f>
-        <v>1000000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7608,8 +7617,8 @@
         <v>24</v>
       </c>
       <c r="C4" s="19">
-        <f>90108+11142+41629</f>
-        <v>142879</v>
+        <f>102420347+83284378</f>
+        <v>185704725</v>
       </c>
       <c r="D4" s="300">
         <v>0.6</v>
@@ -7619,7 +7628,7 @@
         <v>79</v>
       </c>
       <c r="G4" s="19">
-        <v>238880</v>
+        <v>17978772896</v>
       </c>
       <c r="H4" s="300">
         <v>0.9</v>
@@ -7630,7 +7639,7 @@
         <v>33</v>
       </c>
       <c r="C5" s="19">
-        <v>11851</v>
+        <v>0</v>
       </c>
       <c r="D5" s="300">
         <v>0.6</v>
@@ -7651,7 +7660,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="19">
-        <v>182674</v>
+        <v>3576387537</v>
       </c>
       <c r="D6" s="300">
         <v>0.5</v>
@@ -7682,7 +7691,7 @@
         <v>180</v>
       </c>
       <c r="G7" s="19">
-        <v>9895</v>
+        <v>2021804089</v>
       </c>
       <c r="H7" s="300">
         <v>0.6</v>
@@ -7714,7 +7723,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="19">
-        <v>24847</v>
+        <v>241896760</v>
       </c>
       <c r="D9" s="300">
         <v>0.1</v>
@@ -7747,7 +7756,8 @@
         <v>12</v>
       </c>
       <c r="C11" s="19">
-        <v>61345</v>
+        <f>51713930+1132635624</f>
+        <v>1184349554</v>
       </c>
       <c r="D11" s="300">
         <v>0.05</v>
@@ -7760,22 +7770,22 @@
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
-        <v>423596</v>
+        <v>5188338576</v>
       </c>
       <c r="D12" s="20">
         <f>C4*D4+C5*D5+C9*D9+C6*D6+C8*D8+C7*D7+C10*D10+C11*D11</f>
-        <v>189726.95</v>
+        <v>1983023757.2</v>
       </c>
       <c r="F12" s="82" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
-        <v>248775</v>
+        <v>20000576985</v>
       </c>
       <c r="H12" s="20">
         <f>G4*H4+G5*H5+G6*H6+G7*H7+G8*H8+G9*H9</f>
-        <v>220929</v>
+        <v>17393978059.799999</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7857,7 +7867,7 @@
         <v>180</v>
       </c>
       <c r="G17" s="19">
-        <v>693</v>
+        <v>2498379750</v>
       </c>
       <c r="H17" s="300">
         <v>0.6</v>
@@ -7877,8 +7887,7 @@
         <v>183</v>
       </c>
       <c r="G18" s="19">
-        <f>292606</f>
-        <v>292606</v>
+        <v>0</v>
       </c>
       <c r="H18" s="300">
         <v>0.1</v>
@@ -7889,8 +7898,8 @@
         <v>26</v>
       </c>
       <c r="C19" s="19">
-        <f>458868+831001+201156+123479+13153</f>
-        <v>1627657</v>
+        <f>11817650634+630874619+115672625+85702449</f>
+        <v>12649900327</v>
       </c>
       <c r="D19" s="300">
         <v>0.1</v>
@@ -7899,7 +7908,7 @@
         <v>184</v>
       </c>
       <c r="G19" s="19">
-        <v>0</v>
+        <v>391873803</v>
       </c>
       <c r="H19" s="300">
         <v>0.1</v>
@@ -7930,7 +7939,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="19">
-        <v>91529</v>
+        <v>2684120584</v>
       </c>
       <c r="D21" s="300">
         <v>0.05</v>
@@ -7939,7 +7948,7 @@
         <v>182</v>
       </c>
       <c r="G21" s="19">
-        <v>0</v>
+        <v>41138918</v>
       </c>
       <c r="H21" s="300">
         <v>0.1</v>
@@ -7950,7 +7959,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="19">
-        <v>24707</v>
+        <v>1930039528</v>
       </c>
       <c r="D22" s="300">
         <v>0.9</v>
@@ -7962,8 +7971,8 @@
         <v>21</v>
       </c>
       <c r="C23" s="19">
-        <f>7476+51258</f>
-        <v>58734</v>
+        <f>1307103982+4728913379</f>
+        <v>6036017361</v>
       </c>
       <c r="D23" s="300">
         <v>0</v>
@@ -7976,22 +7985,22 @@
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
-        <v>1802627</v>
+        <v>23300077800</v>
       </c>
       <c r="D24" s="20">
         <f>C15*D15+C16*D16+C18*D18+C17*D17+C19*D19+C20*D20+C21*D21+C22*D22+C23*D23</f>
-        <v>189578.45</v>
+        <v>3136231637.1000004</v>
       </c>
       <c r="F24" s="82" t="s">
         <v>72</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
-        <v>293299</v>
+        <v>2931392471</v>
       </c>
       <c r="H24" s="20">
         <f>G15*H15+G16*H16+G17*H17+G18*H18+G19*H19+G20*H20+G21*H21</f>
-        <v>29676.400000000001</v>
+        <v>1542329122.0999999</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8016,18 +8025,18 @@
         <v>5</v>
       </c>
       <c r="C27" s="19">
-        <v>40594</v>
+        <v>0</v>
       </c>
       <c r="F27" s="214" t="s">
         <v>30</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
-        <v>1678153</v>
+        <v>29859542011</v>
       </c>
       <c r="H27" s="215">
         <f>H32-G30</f>
-        <v>-460233.19999999995</v>
+        <v>2494718755.1999969</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8041,7 +8050,7 @@
         <v>246</v>
       </c>
       <c r="G28" s="184">
-        <v>188249</v>
+        <v>799157484</v>
       </c>
       <c r="H28" s="215"/>
     </row>
@@ -8057,11 +8066,11 @@
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
-        <v>1489904</v>
+        <v>29060384527</v>
       </c>
       <c r="H29" s="215">
         <f>H27-G28</f>
-        <v>-648482.19999999995</v>
+        <v>1695561271.1999969</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8069,15 +8078,14 @@
         <v>8</v>
       </c>
       <c r="C30" s="19">
-        <f>4685+7139</f>
-        <v>11824</v>
+        <v>217159673</v>
       </c>
       <c r="F30" s="214" t="s">
         <v>23</v>
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
-        <v>1090144</v>
+        <v>21560843821</v>
       </c>
       <c r="H30" s="215"/>
     </row>
@@ -8087,14 +8095,14 @@
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
-        <v>52418</v>
+        <v>217159673</v>
       </c>
       <c r="F31" s="217" t="s">
         <v>78</v>
       </c>
       <c r="G31" s="218">
         <f>C31+C40</f>
-        <v>245714</v>
+        <v>285396383</v>
       </c>
       <c r="H31" s="215"/>
     </row>
@@ -8104,18 +8112,18 @@
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
-        <v>664223</v>
+        <v>17305171626</v>
       </c>
       <c r="F32" s="219" t="s">
         <v>76</v>
       </c>
       <c r="G32" s="220">
         <f>G35+G40</f>
-        <v>2768297</v>
+        <v>51420385832</v>
       </c>
       <c r="H32" s="215">
         <f>H35+H40</f>
-        <v>629910.80000000005</v>
+        <v>24055562576.199997</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8123,7 +8131,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="86">
-        <v>716641</v>
+        <v>17522331299</v>
       </c>
       <c r="F33" s="221"/>
       <c r="G33" s="2"/>
@@ -8154,11 +8162,11 @@
       </c>
       <c r="G35" s="220">
         <f>C12+C24</f>
-        <v>2226223</v>
+        <v>28488416376</v>
       </c>
       <c r="H35" s="227">
         <f>D12+D24</f>
-        <v>379305.4</v>
+        <v>5119255394.3000002</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8166,15 +8174,14 @@
         <v>13</v>
       </c>
       <c r="C36" s="19">
-        <f>70126+11000</f>
-        <v>81126</v>
+        <v>0</v>
       </c>
       <c r="F36" s="217" t="s">
         <v>199</v>
       </c>
       <c r="G36" s="218">
         <f>C4+C15</f>
-        <v>142879</v>
+        <v>185704725</v>
       </c>
       <c r="H36" s="222"/>
     </row>
@@ -8183,14 +8190,14 @@
         <v>14</v>
       </c>
       <c r="C37" s="19">
-        <v>112170</v>
+        <v>68236710</v>
       </c>
       <c r="F37" s="217" t="s">
         <v>200</v>
       </c>
       <c r="G37" s="218">
         <f>C6</f>
-        <v>182674</v>
+        <v>3576387537</v>
       </c>
       <c r="H37" s="222"/>
     </row>
@@ -8222,11 +8229,11 @@
       </c>
       <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
-        <v>1627657</v>
+        <v>12649900327</v>
       </c>
       <c r="H39" s="215">
         <f>C7*D7+C17*D17+C19*D19+C20*D20</f>
-        <v>162765.70000000001</v>
+        <v>1264990032.7</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8235,18 +8242,18 @@
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
-        <v>193296</v>
+        <v>68236710</v>
       </c>
       <c r="F40" s="226" t="s">
         <v>140</v>
       </c>
       <c r="G40" s="220">
         <f>G12+G24</f>
-        <v>542074</v>
+        <v>22931969456</v>
       </c>
       <c r="H40" s="227">
         <f>H12+H24</f>
-        <v>250605.4</v>
+        <v>18936307181.899998</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8255,18 +8262,18 @@
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
-        <v>180207</v>
+        <v>3970275812</v>
       </c>
       <c r="F41" s="217" t="s">
         <v>193</v>
       </c>
       <c r="G41" s="218">
         <f>C70</f>
-        <v>531486</v>
+        <v>17978772896</v>
       </c>
       <c r="H41" s="227">
         <f>H40-H42</f>
-        <v>244252.6</v>
+        <v>16180895606.399998</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8274,18 +8281,18 @@
         <v>22</v>
       </c>
       <c r="C42" s="86">
-        <v>373503</v>
+        <v>4038512522</v>
       </c>
       <c r="F42" s="228" t="s">
         <v>194</v>
       </c>
       <c r="G42" s="229">
         <f>C82</f>
-        <v>10588</v>
+        <v>4953196560</v>
       </c>
       <c r="H42" s="230">
         <f>D82</f>
-        <v>6352.8</v>
+        <v>2755411575.5</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8319,11 +8326,11 @@
       </c>
       <c r="C46" s="191">
         <f>G29</f>
-        <v>1489904</v>
+        <v>29060384527</v>
       </c>
       <c r="D46" s="191">
         <f>H29</f>
-        <v>-648482.19999999995</v>
+        <v>1695561271.1999969</v>
       </c>
       <c r="F46" s="289"/>
     </row>
@@ -8334,11 +8341,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>7.6546237917772562</v>
+        <v>20.02832272632898</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.3316826296620832</v>
+        <v>1.1685753266721788</v>
       </c>
       <c r="F47" s="289"/>
     </row>
@@ -8364,11 +8371,11 @@
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
-        <v>0.9224468037181085</v>
+        <v>6.3593933566061064E-2</v>
       </c>
       <c r="D50" s="98">
         <f>G31/Normalized_FCF!G8</f>
-        <v>0.9224468037181085</v>
+        <v>6.3593933566061064E-2</v>
       </c>
       <c r="F50" s="289"/>
     </row>
@@ -8379,7 +8386,7 @@
       <c r="C51" s="208"/>
       <c r="D51" s="94">
         <f>G29/G32</f>
-        <v>0.5382023677372767</v>
+        <v>0.56515298469260233</v>
       </c>
       <c r="F51" s="289"/>
     </row>
@@ -8404,11 +8411,11 @@
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
-        <v>0.11965198454961611</v>
+        <v>0.15753043334415495</v>
       </c>
       <c r="D54" s="94">
         <f>Normalized_FCF!G8/G35</f>
-        <v>0.11965198454961611</v>
+        <v>0.15753043334415495</v>
       </c>
       <c r="F54" s="289"/>
     </row>
@@ -8418,11 +8425,11 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
-        <v>3.4198282891265773E-2</v>
+        <v>0</v>
       </c>
       <c r="D55" s="94">
         <f>Normalized_FCF!G11/G40</f>
-        <v>3.4198282891265766E-2</v>
+        <v>2.1050212495974641E-3</v>
       </c>
       <c r="F55" s="289"/>
     </row>
@@ -8448,7 +8455,7 @@
       <c r="C58" s="101"/>
       <c r="D58" s="23">
         <f>Normalized_FCF!G9/BS!$G$39</f>
-        <v>0.14105183094472606</v>
+        <v>9.4175111360938715E-2</v>
       </c>
       <c r="F58" s="5"/>
     </row>
@@ -8459,7 +8466,7 @@
       <c r="C59" s="101"/>
       <c r="D59" s="94">
         <f>G39/G32</f>
-        <v>0.58796328573126366</v>
+        <v>0.24600944007556819</v>
       </c>
       <c r="F59" s="289"/>
     </row>
@@ -8484,11 +8491,11 @@
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
-        <v>0.12634975139337837</v>
+        <v>2.749989365273205E-2</v>
       </c>
       <c r="D62" s="94">
         <f>G28/G29</f>
-        <v>0.12634975139337837</v>
+        <v>2.749989365273205E-2</v>
       </c>
       <c r="F62" s="289" t="s">
         <v>276</v>
@@ -8525,11 +8532,11 @@
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
-        <v>238880</v>
+        <v>17978772896</v>
       </c>
       <c r="D66" s="191">
         <f>C66-D75</f>
-        <v>2536.5589373550902</v>
+        <v>12838413003.943913</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8551,7 +8558,7 @@
       </c>
       <c r="C68" s="20">
         <f>G18</f>
-        <v>292606</v>
+        <v>0</v>
       </c>
       <c r="F68" s="289"/>
     </row>
@@ -8571,7 +8578,7 @@
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
-        <v>531486</v>
+        <v>17978772896</v>
       </c>
       <c r="F70" s="289"/>
     </row>
@@ -8596,11 +8603,11 @@
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-236343.44106264491</v>
+        <v>-2570179946.0280437</v>
       </c>
       <c r="D73" s="191">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-236343.44106264491</v>
+        <v>-2570179946.0280437</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>365</v>
@@ -8612,11 +8619,11 @@
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
-        <v>1.0107325125078581</v>
+        <v>6.9951416918431715</v>
       </c>
       <c r="D74" s="295">
         <f>-$C$66/D73</f>
-        <v>1.0107325125078581</v>
+        <v>6.9951416918431715</v>
       </c>
       <c r="F74" s="289" t="s">
         <v>332</v>
@@ -8629,7 +8636,7 @@
       <c r="C75" s="299"/>
       <c r="D75" s="298">
         <f>MAX(-D73*D76,G5)</f>
-        <v>236343.44106264491</v>
+        <v>5140359892.0560875</v>
       </c>
       <c r="F75" s="289" t="s">
         <v>366</v>
@@ -8642,7 +8649,7 @@
       <c r="C76" s="297"/>
       <c r="D76" s="333">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="289" t="s">
         <v>337</v>
@@ -8669,11 +8676,11 @@
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
-        <v>10588</v>
+        <v>4520183839</v>
       </c>
       <c r="D79" s="191">
         <f>G7*H7+G17*H17</f>
-        <v>6352.8</v>
+        <v>2712110303.3999996</v>
       </c>
       <c r="F79" s="289"/>
     </row>
@@ -8683,11 +8690,11 @@
       </c>
       <c r="C80" s="20">
         <f>G19</f>
-        <v>0</v>
+        <v>391873803</v>
       </c>
       <c r="D80" s="191">
         <f>G19*H19</f>
-        <v>0</v>
+        <v>39187380.300000004</v>
       </c>
       <c r="F80" s="289"/>
     </row>
@@ -8697,11 +8704,11 @@
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
-        <v>0</v>
+        <v>41138918</v>
       </c>
       <c r="D81" s="191">
         <f>G9*H9+G21*H21</f>
-        <v>0</v>
+        <v>4113891.8000000003</v>
       </c>
       <c r="F81" s="289"/>
     </row>
@@ -8711,11 +8718,11 @@
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
-        <v>10588</v>
+        <v>4953196560</v>
       </c>
       <c r="D82" s="83">
         <f>SUM(D79:D81)</f>
-        <v>6352.8</v>
+        <v>2755411575.5</v>
       </c>
       <c r="F82" s="289"/>
     </row>
@@ -8744,11 +8751,11 @@
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-231044.87420000002</v>
+        <v>-268329679.29660001</v>
       </c>
       <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-1.2623955841267334</v>
+        <v>-0.19669426116300168</v>
       </c>
       <c r="E86" s="275" t="str">
         <f>Market_currency</f>
@@ -8761,11 +8768,11 @@
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>2385.1263687949913</v>
+        <v>12070675906.308067</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.3031983531236581E-2</v>
+        <v>8.8481925866461335</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8778,11 +8785,11 @@
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>5973.53784</v>
+        <v>2590637963.2851</v>
       </c>
       <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
-        <v>3.2638541828468509E-2</v>
+        <v>1.899020717592468</v>
       </c>
       <c r="E88" s="275" t="str">
         <f>Market_currency</f>
@@ -8795,11 +8802,11 @@
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>-222686.20999120502</v>
+        <v>14392984190.296566</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>-1.2167250587670282</v>
+        <v>10.5505190430756</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -8846,47 +8853,47 @@
       <c r="F1" s="53"/>
       <c r="G1" s="38">
         <f>Data!C1</f>
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="H1" s="38">
         <f>EOMONTH(EDATE(G1,-12),0)</f>
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="I1" s="38">
         <f t="shared" ref="I1:Q1" si="0">EOMONTH(EDATE(H1,-12),0)</f>
-        <v>44561</v>
+        <v>44926</v>
       </c>
       <c r="J1" s="38">
         <f t="shared" si="0"/>
-        <v>44196</v>
+        <v>44561</v>
       </c>
       <c r="K1" s="38">
         <f t="shared" si="0"/>
-        <v>43830</v>
+        <v>44196</v>
       </c>
       <c r="L1" s="38">
         <f t="shared" si="0"/>
-        <v>43465</v>
+        <v>43830</v>
       </c>
       <c r="M1" s="38">
         <f t="shared" si="0"/>
-        <v>43100</v>
+        <v>43465</v>
       </c>
       <c r="N1" s="38">
         <f t="shared" si="0"/>
-        <v>42735</v>
+        <v>43100</v>
       </c>
       <c r="O1" s="38">
         <f t="shared" si="0"/>
-        <v>42369</v>
+        <v>42735</v>
       </c>
       <c r="P1" s="38">
         <f t="shared" si="0"/>
-        <v>42004</v>
+        <v>42369</v>
       </c>
       <c r="Q1" s="38">
         <f t="shared" si="0"/>
-        <v>41639</v>
+        <v>42004</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -8919,7 +8926,7 @@
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="308"/>
@@ -8933,14 +8940,14 @@
       </c>
       <c r="C4" s="196">
         <f>AVERAGE(G4:J4)</f>
-        <v>3011012</v>
+        <v>32137830111</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="306"/>
       <c r="F4" s="57"/>
       <c r="G4" s="186">
         <f>Data!C36</f>
-        <v>3011012</v>
+        <v>32137830111</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>Data!D36</f>
@@ -8990,12 +8997,12 @@
       </c>
       <c r="C5" s="197">
         <f>C25</f>
-        <v>-2372645</v>
+        <v>-26140692078</v>
       </c>
       <c r="E5" s="308"/>
       <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
-        <v>-2372645</v>
+        <v>-26140692078</v>
       </c>
       <c r="H5" s="186" t="str">
         <f t="shared" si="1"/>
@@ -9045,12 +9052,12 @@
       </c>
       <c r="C6" s="187">
         <f>C4+C5</f>
-        <v>638367</v>
+        <v>5997138033</v>
       </c>
       <c r="E6" s="308"/>
       <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
-        <v>638367</v>
+        <v>5997138033</v>
       </c>
       <c r="H6" s="187" t="str">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
@@ -9100,12 +9107,12 @@
       </c>
       <c r="C7" s="197">
         <f>C35</f>
-        <v>-371995</v>
+        <v>-1509345456</v>
       </c>
       <c r="E7" s="308"/>
       <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
-        <v>-371995</v>
+        <v>-1509345456</v>
       </c>
       <c r="H7" s="197" t="str">
         <f t="shared" si="3"/>
@@ -9155,14 +9162,14 @@
       </c>
       <c r="C8" s="198">
         <f>C6+C7</f>
-        <v>266372</v>
+        <v>4487792577</v>
       </c>
       <c r="D8" s="60"/>
       <c r="E8" s="314"/>
       <c r="F8" s="60"/>
       <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
-        <v>266372</v>
+        <v>4487792577</v>
       </c>
       <c r="H8" s="187" t="str">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
@@ -9212,12 +9219,12 @@
       </c>
       <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
-        <v>229584</v>
+        <v>1191305772</v>
       </c>
       <c r="E9" s="308"/>
       <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
-        <v>229584</v>
+        <v>1191305772</v>
       </c>
       <c r="H9" s="197" t="str">
         <f>IF(Data!D61="","",-Data!D61)</f>
@@ -9267,12 +9274,12 @@
       </c>
       <c r="C10" s="197">
         <f>-C4*C78</f>
-        <v>-229584</v>
+        <v>-1191305772</v>
       </c>
       <c r="E10" s="308"/>
       <c r="G10" s="197">
         <f>Data!C62</f>
-        <v>-115297</v>
+        <v>-1191305772</v>
       </c>
       <c r="H10" s="197" t="str">
         <f>Data!D62</f>
@@ -9322,14 +9329,14 @@
       </c>
       <c r="C11" s="199">
         <f>C63</f>
-        <v>18538.000000000004</v>
+        <v>0</v>
       </c>
       <c r="D11" s="172"/>
       <c r="E11" s="307"/>
       <c r="F11" s="172"/>
       <c r="G11" s="189">
         <f>G61</f>
-        <v>18538</v>
+        <v>48272283</v>
       </c>
       <c r="H11" s="189" t="str">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
@@ -9379,12 +9386,12 @@
       </c>
       <c r="C12" s="197">
         <f>C50</f>
-        <v>-15885.762305832384</v>
+        <v>154505678.47651258</v>
       </c>
       <c r="E12" s="308"/>
       <c r="G12" s="197">
         <f>G50</f>
-        <v>-15885.762305832384</v>
+        <v>154505678.47651258</v>
       </c>
       <c r="H12" s="197" t="str">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
@@ -9434,12 +9441,12 @@
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
-        <v>269024.23769416759</v>
+        <v>4642298255.4765129</v>
       </c>
       <c r="E13" s="308"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>383311.23769416759</v>
+        <v>4690570538.4765129</v>
       </c>
       <c r="H13" s="187" t="str">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
@@ -9489,12 +9496,12 @@
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-67256.059423541898</v>
+        <v>-1160574563.8691282</v>
       </c>
       <c r="E14" s="308"/>
       <c r="G14" s="197">
         <f>Data!C46</f>
-        <v>-57167</v>
+        <v>-1389716314</v>
       </c>
       <c r="H14" s="197" t="str">
         <f>Data!D46</f>
@@ -9544,14 +9551,14 @@
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
-        <v>-19147</v>
+        <v>-146792828</v>
       </c>
       <c r="D15" s="61"/>
       <c r="E15" s="315"/>
       <c r="F15" s="61"/>
       <c r="G15" s="186">
         <f>Data!C48</f>
-        <v>-19147</v>
+        <v>-146792828</v>
       </c>
       <c r="H15" s="186" t="str">
         <f>Data!D48</f>
@@ -9601,14 +9608,14 @@
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
-        <v>182621.17827062571</v>
+        <v>3334930863.6073847</v>
       </c>
       <c r="D16" s="62"/>
       <c r="E16" s="316"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>306997.23769416759</v>
+        <v>3154061396.4765129</v>
       </c>
       <c r="H16" s="187" t="str">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
@@ -9709,14 +9716,14 @@
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
-        <v>182621.17827062571</v>
+        <v>3334930863.6073847</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="305"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>306997.23769416759</v>
+        <v>3154061396.4765129</v>
       </c>
       <c r="H19" s="189" t="str">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
@@ -9829,14 +9836,14 @@
       </c>
       <c r="C23" s="203">
         <f>-C4*C28</f>
-        <v>-2302385</v>
+        <v>-21538172214</v>
       </c>
       <c r="D23" s="59"/>
       <c r="E23" s="307"/>
       <c r="F23" s="59"/>
       <c r="G23" s="186">
         <f>Data!C37</f>
-        <v>-2302385</v>
+        <v>-21538172214</v>
       </c>
       <c r="H23" s="186" t="str">
         <f>Data!D37</f>
@@ -9886,14 +9893,14 @@
       </c>
       <c r="C24" s="197">
         <f>-C4*C29</f>
-        <v>-70260</v>
+        <v>-4602519864</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="305"/>
       <c r="F24" s="27"/>
       <c r="G24" s="186">
         <f>Data!C40</f>
-        <v>-70260</v>
+        <v>-4602519864</v>
       </c>
       <c r="H24" s="186" t="str">
         <f>Data!D40</f>
@@ -9943,14 +9950,14 @@
       </c>
       <c r="C25" s="187">
         <f>C23+C24</f>
-        <v>-2372645</v>
+        <v>-26140692078</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="313"/>
       <c r="F25" s="9"/>
       <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
-        <v>-2372645</v>
+        <v>-26140692078</v>
       </c>
       <c r="H25" s="187" t="str">
         <f t="shared" si="10"/>
@@ -10011,7 +10018,7 @@
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:J28)</f>
-        <v>0.76465487351096573</v>
+        <v>0.67018128291828905</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
@@ -10020,7 +10027,7 @@
       <c r="F28" s="26"/>
       <c r="G28" s="13">
         <f t="shared" ref="G28:Q28" si="11">IF(G$4="","",ABS(G23/G$4))</f>
-        <v>0.76465487351096573</v>
+        <v>0.67018128291828905</v>
       </c>
       <c r="H28" s="13" t="str">
         <f t="shared" si="11"/>
@@ -10071,7 +10078,7 @@
       </c>
       <c r="C29" s="64">
         <f>AVERAGE(G29:J29)</f>
-        <v>2.3334347388851324E-2</v>
+        <v>0.14321190472734091</v>
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
@@ -10080,7 +10087,7 @@
       <c r="F29" s="26"/>
       <c r="G29" s="13">
         <f t="shared" ref="G29:Q29" si="12">IF(G$4="","",ABS(G24/G$4))</f>
-        <v>2.3334347388851324E-2</v>
+        <v>0.14321190472734091</v>
       </c>
       <c r="H29" s="13" t="str">
         <f t="shared" si="12"/>
@@ -10130,12 +10137,12 @@
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
-        <v>0.78798922089981704</v>
+        <v>0.81339318764562996</v>
       </c>
       <c r="E30" s="308"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
-        <v>0.78798922089981704</v>
+        <v>0.81339318764562996</v>
       </c>
       <c r="H30" s="30" t="str">
         <f t="shared" si="13"/>
@@ -10196,14 +10203,14 @@
       </c>
       <c r="C33" s="204">
         <f>AVERAGE(G33:J33)</f>
-        <v>-350038</v>
+        <v>-1406578781</v>
       </c>
       <c r="E33" s="306" t="s">
         <v>347</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
-        <v>-350038</v>
+        <v>-1406578781</v>
       </c>
       <c r="H33" s="197" t="str">
         <f>Data!D41</f>
@@ -10253,7 +10260,7 @@
       </c>
       <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
-        <v>-21957</v>
+        <v>-102766675</v>
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
@@ -10262,7 +10269,7 @@
       <c r="F34" s="59"/>
       <c r="G34" s="186">
         <f>Data!C42</f>
-        <v>-21957</v>
+        <v>-102766675</v>
       </c>
       <c r="H34" s="186" t="str">
         <f>Data!D42</f>
@@ -10312,14 +10319,14 @@
       </c>
       <c r="C35" s="187">
         <f>C33+C34</f>
-        <v>-371995</v>
+        <v>-1509345456</v>
       </c>
       <c r="D35" s="59"/>
       <c r="E35" s="307"/>
       <c r="F35" s="59"/>
       <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
-        <v>-371995</v>
+        <v>-1509345456</v>
       </c>
       <c r="H35" s="187" t="str">
         <f t="shared" si="14"/>
@@ -10381,14 +10388,14 @@
       </c>
       <c r="C38" s="23">
         <f>ABS(C33/$C$4)</f>
-        <v>0.1162526087574543</v>
+        <v>4.3767073761416211E-2</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="305"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
-        <v>0.1162526087574543</v>
+        <v>4.3767073761416211E-2</v>
       </c>
       <c r="H38" s="13" t="str">
         <f t="shared" si="15"/>
@@ -10439,14 +10446,14 @@
       </c>
       <c r="C39" s="23">
         <f>ABS(C34/$C$4)</f>
-        <v>7.2922326447055008E-3</v>
+        <v>3.1976855514220127E-3</v>
       </c>
       <c r="D39" s="27"/>
       <c r="E39" s="305"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
-        <v>7.2922326447055008E-3</v>
+        <v>3.1976855514220127E-3</v>
       </c>
       <c r="H39" s="13" t="str">
         <f t="shared" si="16"/>
@@ -10496,12 +10503,12 @@
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
-        <v>0.12354484140215981</v>
+        <v>4.6964759312838222E-2</v>
       </c>
       <c r="E40" s="308"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
-        <v>0.12354484140215981</v>
+        <v>4.6964759312838222E-2</v>
       </c>
       <c r="H40" s="30" t="str">
         <f t="shared" si="17"/>
@@ -10570,7 +10577,7 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.21249758196504454</v>
+        <v>0.29627873679762989</v>
       </c>
       <c r="H43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10653,12 +10660,12 @@
       </c>
       <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
-        <v>-24063</v>
+        <v>-21837054</v>
       </c>
       <c r="E47" s="308"/>
       <c r="G47" s="197">
         <f>Data!C51</f>
-        <v>-24063</v>
+        <v>-21837054</v>
       </c>
       <c r="H47" s="197" t="str">
         <f>Data!D51</f>
@@ -10708,12 +10715,12 @@
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
-        <v>8177.2376941676157</v>
+        <v>176342732.47651258</v>
       </c>
       <c r="E48" s="308"/>
       <c r="G48" s="334">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>8177.2376941676157</v>
+        <v>176342732.47651258</v>
       </c>
       <c r="H48" s="334" t="str">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
@@ -10763,14 +10770,14 @@
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
-        <v>8265</v>
+        <v>616771200</v>
       </c>
       <c r="D49" s="331"/>
       <c r="E49" s="332"/>
       <c r="F49" s="331"/>
       <c r="G49" s="330">
         <f>Data!C52</f>
-        <v>8265</v>
+        <v>616771200</v>
       </c>
       <c r="H49" s="330" t="str">
         <f>Data!D52</f>
@@ -10820,12 +10827,12 @@
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
-        <v>-15885.762305832384</v>
+        <v>154505678.47651258</v>
       </c>
       <c r="E50" s="308"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-15885.762305832384</v>
+        <v>154505678.47651258</v>
       </c>
       <c r="H50" s="187" t="str">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
@@ -10889,14 +10896,14 @@
       </c>
       <c r="C53" s="89">
         <f>G53</f>
-        <v>3.4598961821835229E-2</v>
+        <v>3.430552260533988E-2</v>
       </c>
       <c r="E53" s="305" t="s">
         <v>349</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
-        <v>3.4598961821835229E-2</v>
+        <v>3.430552260533988E-2</v>
       </c>
       <c r="H53" s="173"/>
       <c r="I53" s="173"/>
@@ -10916,14 +10923,14 @@
       </c>
       <c r="C54" s="84">
         <f>G54</f>
-        <v>9.7930927826660269E-2</v>
+        <v>7.6514823945754068E-2</v>
       </c>
       <c r="E54" s="305" t="s">
         <v>350</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
-        <v>9.7930927826660269E-2</v>
+        <v>7.6514823945754068E-2</v>
       </c>
       <c r="H54" s="173"/>
       <c r="I54" s="173"/>
@@ -10943,12 +10950,12 @@
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
-        <v>11.069775173502888</v>
+        <v>205.51272973909391</v>
       </c>
       <c r="E55" s="308"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
-        <v>11.069775173502888</v>
+        <v>205.51272973909391</v>
       </c>
       <c r="H55" s="42" t="str">
         <f t="shared" si="21"/>
@@ -11067,12 +11074,12 @@
       </c>
       <c r="C59" s="197">
         <f>BS!$C68*C67</f>
-        <v>18538.000000000004</v>
+        <v>0</v>
       </c>
       <c r="E59" s="308"/>
       <c r="G59" s="197">
         <f>Data!C55</f>
-        <v>18538</v>
+        <v>48272283</v>
       </c>
       <c r="H59" s="197" t="str">
         <f>Data!D55</f>
@@ -11177,12 +11184,12 @@
       </c>
       <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
-        <v>18538.000000000004</v>
+        <v>0</v>
       </c>
       <c r="E61" s="308"/>
       <c r="G61" s="187">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
-        <v>18538</v>
+        <v>48272283</v>
       </c>
       <c r="H61" s="187" t="str">
         <f t="shared" si="22"/>
@@ -11238,7 +11245,7 @@
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
-        <v>-31654</v>
+        <v>750493994</v>
       </c>
       <c r="H62" s="197" t="str">
         <f>Data!D58</f>
@@ -11288,12 +11295,12 @@
       </c>
       <c r="C63" s="187">
         <f>C61+C62</f>
-        <v>18538.000000000004</v>
+        <v>0</v>
       </c>
       <c r="E63" s="308"/>
       <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
-        <v>-13116</v>
+        <v>798766277</v>
       </c>
       <c r="H63" s="187" t="str">
         <f t="shared" si="23"/>
@@ -11382,12 +11389,12 @@
       </c>
       <c r="C67" s="180">
         <f>G67</f>
-        <v>6.3354818424775985E-2</v>
+        <v>0</v>
       </c>
       <c r="E67" s="308"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
-        <v>6.3354818424775985E-2</v>
+        <v>0</v>
       </c>
       <c r="H67" s="179"/>
       <c r="I67" s="179"/>
@@ -11432,14 +11439,14 @@
       </c>
       <c r="C69" s="72">
         <f>C61/BS!C70</f>
-        <v>3.4879564090117152E-2</v>
+        <v>0</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="313"/>
       <c r="F69" s="9"/>
       <c r="G69" s="72">
         <f>G61/BS!C70</f>
-        <v>3.4879564090117145E-2</v>
+        <v>2.684959828973636E-3</v>
       </c>
       <c r="H69" s="179"/>
       <c r="I69" s="179"/>
@@ -11506,14 +11513,14 @@
       </c>
       <c r="C73" s="79">
         <f>ABS(C5/C$4)</f>
-        <v>0.78798922089981704</v>
+        <v>0.81339318764562996</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="305"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
-        <v>0.78798922089981704</v>
+        <v>0.81339318764562996</v>
       </c>
       <c r="H73" s="6" t="str">
         <f t="shared" si="24"/>
@@ -11563,14 +11570,14 @@
       </c>
       <c r="C74" s="80">
         <f>ABS(C6/C$4)</f>
-        <v>0.21201077910018293</v>
+        <v>0.18660681235437004</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="305"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
-        <v>0.21201077910018293</v>
+        <v>0.18660681235437004</v>
       </c>
       <c r="H74" s="66" t="str">
         <f t="shared" si="25"/>
@@ -11620,14 +11627,14 @@
       </c>
       <c r="C75" s="79">
         <f>ABS(C7/C$4)</f>
-        <v>0.12354484140215981</v>
+        <v>4.6964759312838222E-2</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="305"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
-        <v>0.12354484140215981</v>
+        <v>4.6964759312838222E-2</v>
       </c>
       <c r="H75" s="6" t="str">
         <f t="shared" si="26"/>
@@ -11677,14 +11684,14 @@
       </c>
       <c r="C76" s="80">
         <f>ABS(C8/C$4)</f>
-        <v>8.846593769802312E-2</v>
+        <v>0.13964205304153179</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="305"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
-        <v>8.846593769802312E-2</v>
+        <v>0.13964205304153179</v>
       </c>
       <c r="H76" s="66" t="str">
         <f t="shared" si="27"/>
@@ -11734,14 +11741,14 @@
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
-        <v>7.6248118572758927E-2</v>
+        <v>3.7068643647856142E-2</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="305"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
-        <v>7.6248118572758927E-2</v>
+        <v>3.7068643647856142E-2</v>
       </c>
       <c r="H77" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11791,7 +11798,7 @@
       </c>
       <c r="C78" s="90">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
-        <v>7.6248118572758927E-2</v>
+        <v>3.7068643647856142E-2</v>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
@@ -11800,7 +11807,7 @@
       <c r="F78" s="27"/>
       <c r="G78" s="6">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
-        <v>3.8291776983950913E-2</v>
+        <v>3.7068643647856142E-2</v>
       </c>
       <c r="H78" s="6" t="str">
         <f t="shared" si="29"/>
@@ -11850,14 +11857,14 @@
       </c>
       <c r="C79" s="80">
         <f>ABS(C11/C$4)</f>
-        <v>6.1567340150089087E-3</v>
+        <v>0</v>
       </c>
       <c r="D79" s="27"/>
       <c r="E79" s="305"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
-        <v>6.156734015008907E-3</v>
+        <v>1.5020392737553731E-3</v>
       </c>
       <c r="H79" s="66" t="str">
         <f t="shared" si="30"/>
@@ -11907,14 +11914,14 @@
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
-        <v>5.2758880754485149E-3</v>
+        <v>4.8075952216708323E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="305"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>5.2758880754485149E-3</v>
+        <v>4.8075952216708323E-3</v>
       </c>
       <c r="H80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -11964,14 +11971,14 @@
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
-        <v>8.9346783637583513E-2</v>
+        <v>0.14444964826320264</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="305"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.12730312522639153</v>
+        <v>0.14595168753695803</v>
       </c>
       <c r="H81" s="66" t="str">
         <f t="shared" si="32"/>
@@ -12021,14 +12028,14 @@
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
-        <v>2.2336695909395878E-2</v>
+        <v>3.611241206580066E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="305"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>1.89859754793405E-2</v>
+        <v>4.3242381616932307E-2</v>
       </c>
       <c r="H82" s="6" t="str">
         <f t="shared" si="33"/>
@@ -12079,14 +12086,14 @@
       </c>
       <c r="C83" s="304">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
-        <v>6.358991594852495E-3</v>
+        <v>4.5676023394546593E-3</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="305"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
-        <v>6.358991594852495E-3</v>
+        <v>4.5676023394546593E-3</v>
       </c>
       <c r="H83" s="6" t="str">
         <f t="shared" si="34"/>
@@ -12136,14 +12143,14 @@
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
-        <v>6.0651096133335143E-2</v>
+        <v>0.10376963385794732</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="305"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.10195815815219852</v>
+        <v>9.8141703580571046E-2</v>
       </c>
       <c r="H84" s="66" t="str">
         <f t="shared" si="35"/>
@@ -12243,14 +12250,14 @@
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
-        <v>6.0651096133335143E-2</v>
+        <v>0.10376963385794732</v>
       </c>
       <c r="D87" s="77"/>
       <c r="E87" s="305"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.10195815815219852</v>
+        <v>9.8141703580571046E-2</v>
       </c>
       <c r="H87" s="66" t="str">
         <f t="shared" si="36"/>
@@ -12312,12 +12319,12 @@
       </c>
       <c r="C90" s="117">
         <f>G90</f>
-        <v>0.49984047644368812</v>
+        <v>2.339927674962774</v>
       </c>
       <c r="E90" s="308"/>
       <c r="G90" s="116">
         <f>Data!C65</f>
-        <v>0.49984047644368812</v>
+        <v>2.339927674962774</v>
       </c>
       <c r="H90" s="116" t="str">
         <f>Data!D65</f>
@@ -12368,12 +12375,12 @@
       </c>
       <c r="C91" s="76">
         <f>C90*Common_Shares/$C$3</f>
-        <v>91481.292751738802</v>
+        <v>3192121818.3365245</v>
       </c>
       <c r="E91" s="308"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>91481.292751738802</v>
+        <v>3192121818.3365245</v>
       </c>
       <c r="H91" s="76" t="str">
         <f t="shared" si="37"/>
@@ -12423,12 +12430,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.50093474162220653</v>
+        <v>0.95717780934253482</v>
       </c>
       <c r="E92" s="308"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.29798734815611916</v>
+        <v>1.0120671150861329</v>
       </c>
       <c r="H92" s="174" t="str">
         <f t="shared" si="38"/>
@@ -12478,12 +12485,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.0061347106970835E-2</v>
+        <v>4.2738405022151121E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.0061347106970835E-2</v>
+        <v>4.2738405022151121E-2</v>
       </c>
       <c r="H93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12615,7 +12622,7 @@
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>-0.29815718601807895</v>
+        <v>-1.0291345712429845E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="305"/>
@@ -12708,14 +12715,14 @@
       </c>
       <c r="C101" s="205">
         <f>BS!G32</f>
-        <v>2768297</v>
+        <v>51420385832</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="309"/>
       <c r="F101" s="26"/>
       <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
-        <v>2752710</v>
+        <v>51420385832</v>
       </c>
       <c r="H101" s="186" t="str">
         <f t="shared" si="42"/>
@@ -12765,7 +12772,7 @@
       </c>
       <c r="C102" s="206">
         <f>BS!C4</f>
-        <v>142879</v>
+        <v>185704725</v>
       </c>
       <c r="D102" s="91"/>
       <c r="E102" s="310"/>
@@ -12822,7 +12829,7 @@
       </c>
       <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
-        <v>182674</v>
+        <v>3576387537</v>
       </c>
       <c r="D103" s="91"/>
       <c r="E103" s="310"/>
@@ -12879,14 +12886,14 @@
       </c>
       <c r="C104" s="205">
         <f>BS!G30</f>
-        <v>1090144</v>
+        <v>21560843821</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="309"/>
       <c r="F104" s="26"/>
       <c r="G104" s="186">
         <f>Data!C79</f>
-        <v>1122089</v>
+        <v>21560843821</v>
       </c>
       <c r="H104" s="186" t="str">
         <f>Data!D79</f>
@@ -12936,14 +12943,14 @@
       </c>
       <c r="C105" s="205">
         <f>BS!G27</f>
-        <v>1678153</v>
+        <v>29859542011</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
         <f>Data!C80</f>
-        <v>1630621</v>
+        <v>29859542011</v>
       </c>
       <c r="H105" s="186" t="str">
         <f>Data!D80</f>
@@ -13020,7 +13027,7 @@
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
-        <v>4.7452152299625509E-2</v>
+        <v>5.7783840526444809E-3</v>
       </c>
       <c r="D108" s="26"/>
       <c r="E108" s="309"/>
@@ -13077,7 +13084,7 @@
       </c>
       <c r="C109" s="97">
         <f>C103/C$4</f>
-        <v>6.0668638982508204E-2</v>
+        <v>0.11128279428472955</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="309"/>
@@ -13168,13 +13175,13 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C113" s="173"/>
       <c r="E113" s="308"/>
       <c r="G113" s="340">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>2.5325501550271508</v>
+        <v>1.1475773379531717</v>
       </c>
       <c r="H113" s="340" t="str">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
@@ -13220,13 +13227,13 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C114" s="173"/>
       <c r="E114" s="308"/>
       <c r="G114" s="340">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.4872967699301045</v>
+        <v>1.6342932124778582</v>
       </c>
       <c r="H114" s="340" t="str">
         <f>IF(H$4="","",Data!D$22/H19)</f>
@@ -13334,12 +13341,12 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>8.9346783637583513E-2</v>
+        <v>0.14444964826320264</v>
       </c>
       <c r="E117" s="308"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.12730312522639153</v>
+        <v>0.14595168753695803</v>
       </c>
       <c r="H117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13388,12 +13395,12 @@
       </c>
       <c r="C118" s="42">
         <f>C4/C101</f>
-        <v>1.0876766474117481</v>
+        <v>0.62500173016982585</v>
       </c>
       <c r="E118" s="308"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
-        <v>1.0938355293510758</v>
+        <v>0.62500173016982585</v>
       </c>
       <c r="H118" s="42" t="str">
         <f t="shared" si="46"/>
@@ -13442,14 +13449,14 @@
       </c>
       <c r="C119" s="15">
         <f>C101/C105</f>
-        <v>1.6496094217869288</v>
+        <v>1.7220755031358876</v>
       </c>
       <c r="D119" s="11"/>
       <c r="E119" s="312"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
-        <v>1.6881359923611925</v>
+        <v>1.7220755031358876</v>
       </c>
       <c r="H119" s="15" t="str">
         <f t="shared" si="47"/>
@@ -13499,14 +13506,14 @@
       </c>
       <c r="C120" s="105">
         <f>C8/C105</f>
-        <v>0.1587292696196354</v>
+        <v>0.15029676528014849</v>
       </c>
       <c r="D120" s="106"/>
       <c r="E120" s="311"/>
       <c r="F120" s="106"/>
       <c r="G120" s="105">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
-        <v>0.16335616921406015</v>
+        <v>0.15029676528014849</v>
       </c>
       <c r="H120" s="105" t="str">
         <f t="shared" si="48"/>
@@ -13620,14 +13627,14 @@
       </c>
       <c r="C124" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.93824596488950096</v>
+        <v>2.2984235306407004</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="305"/>
       <c r="F124" s="27"/>
       <c r="G124" s="181">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.5772481714685458</v>
+        <v>2.1737688807453912</v>
       </c>
       <c r="H124" s="181" t="str">
         <f t="shared" si="49"/>
@@ -13677,14 +13684,14 @@
       </c>
       <c r="C125" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.16905332700711728</v>
+        <v>4.1980338459190879E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="305"/>
       <c r="F125" s="27"/>
       <c r="G125" s="79">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.28418885972406233</v>
+        <v>3.9703541200829064E-2</v>
       </c>
       <c r="H125" s="79" t="str">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
@@ -13727,7 +13734,56 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B126" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C126" s="173"/>
+      <c r="G126" s="23">
+        <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>6.0139111913768903E-2</v>
+      </c>
+      <c r="H126" s="23" t="str">
+        <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="I126" s="23" t="str">
+        <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="J126" s="23" t="str">
+        <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="K126" s="23" t="str">
+        <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="L126" s="23" t="str">
+        <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="M126" s="23" t="str">
+        <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="N126" s="23" t="str">
+        <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="O126" s="23" t="str">
+        <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="P126" s="23" t="str">
+        <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="Q126" s="23" t="str">
+        <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+    </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -14458,7 +14514,7 @@
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="E3" s="112" t="s">
         <v>126</v>
@@ -14471,7 +14527,7 @@
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
-        <v>182621.17827062571</v>
+        <v>3334930863.6073847</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14503,7 +14559,7 @@
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>2282764.7283828212</v>
+        <v>41686635795.092308</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14521,7 +14577,7 @@
       </c>
       <c r="C7" s="232">
         <f>BS!G31</f>
-        <v>245714</v>
+        <v>285396383</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
@@ -14537,7 +14593,7 @@
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
-        <v>2536.5589373550902</v>
+        <v>12838413003.943913</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14553,7 +14609,7 @@
       </c>
       <c r="C9" s="235">
         <f>BS!H42</f>
-        <v>6352.8</v>
+        <v>2755411575.5</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -14569,7 +14625,7 @@
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
-        <v>2045940.0873201764</v>
+        <v>56995063991.536224</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14583,7 +14639,7 @@
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
-        <v>0.94030000000000002</v>
+        <v>0.94020000000000004</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14597,7 +14653,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>10.511349502351733</v>
+        <v>39.280813176084358</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14630,7 +14686,7 @@
       </c>
       <c r="C16" s="165">
         <f>Scenarios!C65</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>4.6574870890079501E-2</v>
       </c>
       <c r="H16" s="124"/>
     </row>
@@ -14650,7 +14706,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>10.189224696681462</v>
+        <v>43.891569402079135</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14685,11 +14741,11 @@
       </c>
       <c r="C21" s="127">
         <f>C4*(1+D21)</f>
-        <v>180956.72859242809</v>
+        <v>3490254838.0072398</v>
       </c>
       <c r="D21" s="142">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>4.6574870890079501E-2</v>
       </c>
       <c r="E21" s="128">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14697,7 +14753,7 @@
       </c>
       <c r="F21" s="129">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>167552.52647447042</v>
+        <v>3231717442.5992956</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -14707,11 +14763,11 @@
       </c>
       <c r="C22" s="127">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>179307.44907553098</v>
+        <v>3652813006.4609022</v>
       </c>
       <c r="D22" s="142">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>4.6574870890079501E-2</v>
       </c>
       <c r="E22" s="128">
         <f t="shared" si="0"/>
@@ -14719,7 +14775,7 @@
       </c>
       <c r="F22" s="129">
         <f t="shared" si="1"/>
-        <v>153727.23686173779</v>
+        <v>3131698393.7421999</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -14729,11 +14785,11 @@
       </c>
       <c r="C23" s="127">
         <f t="shared" si="2"/>
-        <v>177673.20145573994</v>
+        <v>3822942300.6224222</v>
       </c>
       <c r="D23" s="142">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>4.6574870890079501E-2</v>
       </c>
       <c r="E23" s="128">
         <f t="shared" si="0"/>
@@ -14741,7 +14797,7 @@
       </c>
       <c r="F23" s="129">
         <f t="shared" si="1"/>
-        <v>141042.7156808381</v>
+        <v>3034774853.7939005</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -14751,11 +14807,11 @@
       </c>
       <c r="C24" s="127">
         <f t="shared" si="2"/>
-        <v>176053.84872903093</v>
+        <v>4000995344.6941352</v>
       </c>
       <c r="D24" s="142">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>4.6574870890079501E-2</v>
       </c>
       <c r="E24" s="128">
         <f t="shared" si="0"/>
@@ -14763,7 +14819,7 @@
       </c>
       <c r="F24" s="129">
         <f t="shared" si="1"/>
-        <v>129404.83451554866</v>
+        <v>2940851019.249825</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -14773,11 +14829,11 @@
       </c>
       <c r="C25" s="127">
         <f t="shared" si="2"/>
-        <v>174449.25514006481</v>
+        <v>4187341186.3050742</v>
       </c>
       <c r="D25" s="142">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>4.6574870890079501E-2</v>
       </c>
       <c r="E25" s="128">
         <f t="shared" si="0"/>
@@ -14785,7 +14841,7 @@
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>118727.23178338219</v>
+        <v>2849834051.6466155</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -14795,11 +14851,11 @@
       </c>
       <c r="C26" s="127">
         <f t="shared" si="2"/>
-        <v>172859.28617080644</v>
+        <v>4382366061.429945</v>
       </c>
       <c r="D26" s="142">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>4.6574870890079501E-2</v>
       </c>
       <c r="E26" s="128">
         <f t="shared" si="0"/>
@@ -14807,7 +14863,7 @@
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>108930.67186953689</v>
+        <v>2761633985.7964888</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -14817,11 +14873,11 @@
       </c>
       <c r="C27" s="127">
         <f t="shared" si="2"/>
-        <v>171283.80852924779</v>
+        <v>4586474194.9341116</v>
       </c>
       <c r="D27" s="142">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>4.6574870890079501E-2</v>
       </c>
       <c r="E27" s="128">
         <f t="shared" si="0"/>
@@ -14829,7 +14885,7 @@
       </c>
       <c r="F27" s="129">
         <f t="shared" si="1"/>
-        <v>99942.457140734448</v>
+        <v>2676163640.8616819</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -14839,11 +14895,11 @@
       </c>
       <c r="C28" s="127">
         <f t="shared" si="2"/>
-        <v>169722.69013823351</v>
+        <v>4800088638.4038496</v>
       </c>
       <c r="D28" s="142">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>4.6574870890079501E-2</v>
       </c>
       <c r="E28" s="128">
         <f t="shared" si="0"/>
@@ -14851,7 +14907,7 @@
       </c>
       <c r="F28" s="129">
         <f t="shared" si="1"/>
-        <v>91695.888475657892</v>
+        <v>2593338534.1810555</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -14861,11 +14917,11 @@
       </c>
       <c r="C29" s="127">
         <f t="shared" si="2"/>
-        <v>168175.80012438865</v>
+        <v>5023652146.9984465</v>
       </c>
       <c r="D29" s="142">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>4.6574870890079501E-2</v>
       </c>
       <c r="E29" s="128">
         <f t="shared" si="0"/>
@@ -14873,7 +14929,7 @@
       </c>
       <c r="F29" s="129">
         <f t="shared" si="1"/>
-        <v>84129.770308732128</v>
+        <v>2513076797.7637095</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -14883,11 +14939,11 @@
       </c>
       <c r="C30" s="127">
         <f t="shared" si="2"/>
-        <v>166643.00880714692</v>
+        <v>5257628097.1415701</v>
       </c>
       <c r="D30" s="142">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>-9.1142204532876307E-3</v>
+        <v>4.6574870890079501E-2</v>
       </c>
       <c r="E30" s="128">
         <f t="shared" si="0"/>
@@ -14895,7 +14951,7 @@
       </c>
       <c r="F30" s="129">
         <f t="shared" si="1"/>
-        <v>77187.956514309146</v>
+        <v>2435299097.3670449</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -15345,7 +15401,7 @@
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>2261959.107405351</v>
+        <v>43628185475.0905</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -15357,7 +15413,7 @@
       </c>
       <c r="F51" s="129">
         <f t="shared" si="1"/>
-        <v>1047724.7288640034</v>
+        <v>20208291409.012726</v>
       </c>
       <c r="H51" s="124"/>
     </row>
@@ -15368,7 +15424,7 @@
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
-        <v>2220066.018488951</v>
+        <v>48376679226.014542</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -15389,27 +15445,27 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="137">
         <f>F52</f>
-        <v>2220066.018488951</v>
+        <v>48376679226.014542</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="C55" s="135">
         <f>C77</f>
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="D55" s="135">
         <f>C76</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E55" s="135">
         <f>C75</f>
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F55" s="135">
         <f>C74</f>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H55" s="124"/>
     </row>
@@ -15419,19 +15475,19 @@
       </c>
       <c r="B56" s="127">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1791667.4501565206</v>
+        <v>41686635795.0923</v>
       </c>
       <c r="C56" s="127">
-        <v>1944399.2979690079</v>
+        <v>43031664884.200684</v>
       </c>
       <c r="D56" s="127">
-        <v>2282764.7283828212</v>
+        <v>44416977007.580719</v>
       </c>
       <c r="E56" s="127">
-        <v>2356418.6681816033</v>
+        <v>45844339914.909462</v>
       </c>
       <c r="F56" s="127">
-        <v>2510441.0600115755</v>
+        <v>48832563622.78038</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -15440,19 +15496,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="127">
-        <v>1512116.6840562024</v>
+        <v>41686635795.092293</v>
       </c>
       <c r="C57" s="127">
-        <v>1717259.7734446828</v>
+        <v>44377932532.552048</v>
       </c>
       <c r="D57" s="127">
-        <v>2282764.7283828203</v>
+        <v>47338970072.750206</v>
       </c>
       <c r="E57" s="127">
-        <v>2430140.4316197839</v>
+        <v>50602030478.99791</v>
       </c>
       <c r="F57" s="127">
-        <v>2770972.7148480518</v>
+        <v>58181752148.991631</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -15461,19 +15517,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="127">
-        <v>1267998.2938434205</v>
+        <v>41686635795.092293</v>
       </c>
       <c r="C58" s="127">
-        <v>1501500.7034384492</v>
+        <v>46044312032.426598</v>
       </c>
       <c r="D58" s="127">
-        <v>2282764.7283828198</v>
+        <v>51148158586.159439</v>
       </c>
       <c r="E58" s="127">
-        <v>2521391.5550040705</v>
+        <v>57146417407.040382</v>
       </c>
       <c r="F58" s="127">
-        <v>3129344.0576845901</v>
+        <v>72571194969.636124</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -15482,19 +15538,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="127">
-        <v>1085590.6113440995</v>
+        <v>41686635795.092293</v>
       </c>
       <c r="C59" s="127">
-        <v>1330075.1609701074</v>
+        <v>47742085509.611755</v>
       </c>
       <c r="D59" s="127">
-        <v>2282764.7283828198</v>
+        <v>55248087431.293556</v>
       </c>
       <c r="E59" s="127">
-        <v>2614361.8160141576</v>
+        <v>64611784035.615005</v>
       </c>
       <c r="F59" s="127">
-        <v>3538148.349494644</v>
+        <v>91162188864.467712</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -15503,19 +15559,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="127">
-        <v>956535.38724221883</v>
+        <v>41686635795.092293</v>
       </c>
       <c r="C60" s="127">
-        <v>1203526.2419221611</v>
+        <v>49321109052.860527</v>
       </c>
       <c r="D60" s="127">
-        <v>2282764.7283828198</v>
+        <v>59286656820.384186</v>
       </c>
       <c r="E60" s="127">
-        <v>2700829.317674215</v>
+        <v>72435261278.651276</v>
       </c>
       <c r="F60" s="127">
-        <v>3966562.8176588374</v>
+        <v>113458031789.94728</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -15524,19 +15580,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="127">
-        <v>867219.36706202792</v>
+        <v>41686635795.092293</v>
       </c>
       <c r="C61" s="127">
-        <v>1113428.7942805844</v>
+        <v>50714027473.096329</v>
       </c>
       <c r="D61" s="127">
-        <v>2282764.7283828198</v>
+        <v>63068812843.976898</v>
       </c>
       <c r="E61" s="127">
-        <v>2777105.6824751217</v>
+        <v>80257744310.867432</v>
       </c>
       <c r="F61" s="127">
-        <v>4394922.8427299513</v>
+        <v>139201902439.57507</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -15560,23 +15616,23 @@
     <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B64" s="136">
         <f>B55</f>
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="C64" s="136">
         <f>C55</f>
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="D64" s="136">
         <f>D55</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E64" s="136">
         <f>E55</f>
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F64" s="136">
         <f>F55</f>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H64" s="124"/>
     </row>
@@ -15586,23 +15642,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>10.511349502351733</v>
+        <v>39.280813176084358</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>10.511349502351733</v>
+        <v>39.280813176084358</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>10.511349502351733</v>
+        <v>39.280813176084358</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>10.511349502351733</v>
+        <v>39.280813176084358</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>10.511349502351733</v>
+        <v>39.280813176084358</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15613,23 +15669,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>7.9882574709268273</v>
+        <v>39.280813176084351</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>8.7729421459311006</v>
+        <v>40.207802860199997</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>10.511349502351733</v>
+        <v>41.162555480832843</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>10.889758581018468</v>
+        <v>42.146289365324655</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>11.681073635524092</v>
+        <v>44.205763449162056</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15640,23 +15696,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>6.5520200051565114</v>
+        <v>39.280813176084351</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>7.605975946446522</v>
+        <v>41.135646155327265</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>10.511349502351729</v>
+        <v>43.176383620613187</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>11.268516114648602</v>
+        <v>45.425274265233355</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>13.019597328072329</v>
+        <v>50.649193846935304</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15667,23 +15723,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>5.2978221254722335</v>
+        <v>39.280813176084351</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>6.4974786804740496</v>
+        <v>42.284109499885474</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>10.511349502351727</v>
+        <v>45.801663984715141</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>11.737333582138968</v>
+        <v>49.93564450204228</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>14.860788308946084</v>
+        <v>60.566351150761136</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15694,23 +15750,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>4.3606730297840182</v>
+        <v>39.280813176084351</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>5.6167521129257443</v>
+        <v>43.454209471744875</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>10.511349502351727</v>
+        <v>48.627321642102252</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>12.214983398406025</v>
+        <v>55.080750960235946</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>16.961086756543974</v>
+        <v>73.379203822512679</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15721,23 +15777,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>3.6976308546751522</v>
+        <v>39.280813176084351</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>4.9665864871081711</v>
+        <v>44.54246737443281</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>10.511349502351727</v>
+        <v>51.410690561471824</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>12.659224232327279</v>
+        <v>60.472666091986497</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>19.162135670266764</v>
+        <v>88.745426425388274</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15747,23 +15803,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>3.2387552941973317</v>
+        <v>39.280813176084351</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>4.5036962161272101</v>
+        <v>45.502462230179169</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>10.511349502351727</v>
+        <v>54.017340221302177</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>13.051106445379464</v>
+        <v>65.863896016865652</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>21.362904873756147</v>
+        <v>106.48801854823385</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15790,15 +15846,15 @@
       </c>
       <c r="C74" s="146">
         <f>Scenarios!C56</f>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="D74" s="149">
         <f>Scenarios!C55</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>13.019597328072329</v>
+        <v>60.566351150761136</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15812,15 +15868,15 @@
       </c>
       <c r="C75" s="146">
         <f>Scenarios!C38</f>
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="D75" s="149">
         <f>Scenarios!C37</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>10.889758581018468</v>
+        <v>45.425274265233355</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15835,15 +15891,15 @@
       </c>
       <c r="C76" s="146">
         <f>Scenarios!C26</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D76" s="149">
         <f>Scenarios!C25</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>10.511349502351733</v>
+        <v>43.176383620613187</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15858,15 +15914,15 @@
       </c>
       <c r="C77" s="146">
         <f>Scenarios!C32</f>
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="D77" s="149">
         <f>Scenarios!C31</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>8.7729421459311006</v>
+        <v>41.135646155327265</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15881,15 +15937,15 @@
       </c>
       <c r="C78" s="146">
         <f>Scenarios!C50</f>
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="D78" s="149">
         <f>Scenarios!C49</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>6.5520200051565114</v>
+        <v>39.280813176084351</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15990,7 +16046,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-5.55</v>
+        <v>-54.75</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16010,7 +16066,7 @@
       </c>
       <c r="I4" s="270">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.49984047644368812</v>
+        <v>2.339927674962774</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16019,7 +16075,7 @@
       </c>
       <c r="I5" s="270">
         <f t="shared" si="0"/>
-        <v>0.49984047644368812</v>
+        <v>2.339927674962774</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16028,7 +16084,7 @@
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="E6" s="103" t="s">
         <v>285</v>
@@ -16039,7 +16095,7 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>10.693836205225988</v>
+        <v>46.228498722137076</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16048,7 +16104,7 @@
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
-        <v>266372</v>
+        <v>4487792577</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
@@ -16056,7 +16112,7 @@
       </c>
       <c r="E7" s="351" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
-        <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国石油股份(0857.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
+        <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 青島啤酒股份(0168.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
       <c r="F7" s="351"/>
       <c r="H7" s="282">
@@ -16073,7 +16129,7 @@
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>306997.23769416759</v>
+        <v>3154061396.4765129</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16095,7 +16151,7 @@
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
-        <v>182621.17827062571</v>
+        <v>3334930863.6073847</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16206,7 +16262,7 @@
         <v>135</v>
       </c>
       <c r="C18" s="154">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E18" s="351" t="s">
         <v>344</v>
@@ -16230,7 +16286,7 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>5.55</v>
+        <v>54.75</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16245,7 +16301,7 @@
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>10.511349502351733</v>
+        <v>39.280813176084358</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16269,7 +16325,7 @@
       </c>
       <c r="C25" s="170">
         <f>C18</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D25" s="167"/>
       <c r="E25" s="350"/>
@@ -16280,7 +16336,7 @@
         <v>136</v>
       </c>
       <c r="C26" s="168">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D26" s="168"/>
       <c r="E26" s="350"/>
@@ -16292,7 +16348,7 @@
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>10.511349502351733</v>
+        <v>43.176383620613187</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
@@ -16327,7 +16383,7 @@
       </c>
       <c r="C31" s="170">
         <f>C18</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D31" s="167"/>
       <c r="E31" s="350"/>
@@ -16338,7 +16394,7 @@
         <v>136</v>
       </c>
       <c r="C32" s="168">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="D32" s="168"/>
       <c r="E32" s="350"/>
@@ -16350,7 +16406,7 @@
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>8.7729421459311006</v>
+        <v>41.135646155327265</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16385,7 +16441,7 @@
       </c>
       <c r="C37" s="170">
         <f>C18</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D37" s="167"/>
       <c r="E37" s="350"/>
@@ -16396,7 +16452,7 @@
         <v>136</v>
       </c>
       <c r="C38" s="168">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="D38" s="168"/>
       <c r="E38" s="350"/>
@@ -16408,7 +16464,7 @@
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>10.889758581018468</v>
+        <v>45.425274265233355</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16435,7 +16491,7 @@
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>10.239349846800954</v>
+        <v>43.218014256480032</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16461,7 +16517,7 @@
         <v>135</v>
       </c>
       <c r="C46" s="154">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E46" s="103"/>
       <c r="F46" s="103"/>
@@ -16486,7 +16542,7 @@
       </c>
       <c r="C49" s="170">
         <f>C46</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D49" s="167"/>
       <c r="E49" s="350"/>
@@ -16497,7 +16553,7 @@
         <v>136</v>
       </c>
       <c r="C50" s="168">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="D50" s="168"/>
       <c r="E50" s="350"/>
@@ -16509,7 +16565,7 @@
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>6.5520200051565114</v>
+        <v>39.280813176084351</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16544,7 +16600,7 @@
       </c>
       <c r="C55" s="170">
         <f>C46</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D55" s="167"/>
       <c r="E55" s="350"/>
@@ -16555,7 +16611,7 @@
         <v>136</v>
       </c>
       <c r="C56" s="168">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="D56" s="168"/>
       <c r="E56" s="350"/>
@@ -16567,7 +16623,7 @@
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>13.019597328072329</v>
+        <v>60.566351150761136</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16593,7 +16649,7 @@
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>10.1939957287823</v>
+        <v>43.888571047174302</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16641,7 +16697,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="155">
-        <v>-9.1142204532876307E-3</v>
+        <v>4.6574870890079501E-2</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
@@ -16654,7 +16710,7 @@
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>10.189224696681462</v>
+        <v>43.891569402079135</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
@@ -16678,7 +16734,7 @@
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E69" s="138"/>
     </row>
@@ -16688,7 +16744,7 @@
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E70" s="287" t="s">
         <v>305</v>
@@ -16717,7 +16773,7 @@
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
-        <v>-0.11935703046565523</v>
+        <v>0.24039331405288208</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16750,7 +16806,7 @@
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
-        <v>0.49984047644368812</v>
+        <v>2.339927674962774</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16777,7 +16833,7 @@
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.0529047073235096</v>
+        <v>4.9290143153151025</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
@@ -16789,7 +16845,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>5.8993030837860534</v>
+        <v>25.398478615262906</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16799,7 +16855,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>6.9522077911095632</v>
+        <v>30.327492930578011</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16810,7 +16866,7 @@
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.31800954443405249</v>
+        <v>0.30898882768409019</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16827,7 +16883,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>5.55</v>
+        <v>54.75</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16840,7 +16896,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.29981048955907563</v>
+        <v>-2.5075247395360156E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5D8BA2-09C5-4938-ACC4-F059F1A58587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5177FEE5-5464-48FC-A2E9-23BC9DF3BD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3713,29 +3713,29 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4146,13 +4146,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="343" t="s">
+      <c r="B12" s="341" t="s">
         <v>377</v>
       </c>
-      <c r="C12" s="343"/>
-      <c r="D12" s="343"/>
-      <c r="E12" s="343"/>
-      <c r="F12" s="343"/>
+      <c r="C12" s="341"/>
+      <c r="D12" s="341"/>
+      <c r="E12" s="341"/>
+      <c r="F12" s="341"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4254,22 +4254,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="343" t="s">
+      <c r="B25" s="341" t="s">
         <v>378</v>
       </c>
-      <c r="C25" s="343"/>
-      <c r="D25" s="343"/>
-      <c r="E25" s="343"/>
-      <c r="F25" s="343"/>
+      <c r="C25" s="341"/>
+      <c r="D25" s="341"/>
+      <c r="E25" s="341"/>
+      <c r="F25" s="341"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="346" t="s">
+      <c r="B26" s="343" t="s">
         <v>353</v>
       </c>
-      <c r="C26" s="346"/>
-      <c r="D26" s="346"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="C26" s="343"/>
+      <c r="D26" s="343"/>
+      <c r="E26" s="343"/>
+      <c r="F26" s="343"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -4281,13 +4281,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="344" t="s">
+      <c r="B29" s="342" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="344"/>
-      <c r="D29" s="344"/>
-      <c r="E29" s="344"/>
-      <c r="F29" s="344"/>
+      <c r="C29" s="342"/>
+      <c r="D29" s="342"/>
+      <c r="E29" s="342"/>
+      <c r="F29" s="342"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4307,13 +4307,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="344" t="s">
+      <c r="B32" s="342" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="344"/>
-      <c r="D32" s="344"/>
-      <c r="E32" s="344"/>
-      <c r="F32" s="344"/>
+      <c r="C32" s="342"/>
+      <c r="D32" s="342"/>
+      <c r="E32" s="342"/>
+      <c r="F32" s="342"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4342,13 +4342,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="344" t="s">
+      <c r="B36" s="342" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="344"/>
-      <c r="D36" s="344"/>
-      <c r="E36" s="344"/>
-      <c r="F36" s="344"/>
+      <c r="C36" s="342"/>
+      <c r="D36" s="342"/>
+      <c r="E36" s="342"/>
+      <c r="F36" s="342"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4364,13 +4364,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="344" t="s">
+      <c r="B39" s="342" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="344"/>
-      <c r="D39" s="344"/>
-      <c r="E39" s="344"/>
-      <c r="F39" s="344"/>
+      <c r="C39" s="342"/>
+      <c r="D39" s="342"/>
+      <c r="E39" s="342"/>
+      <c r="F39" s="342"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4434,13 +4434,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="344" t="s">
+      <c r="B47" s="342" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="344"/>
-      <c r="D47" s="344"/>
-      <c r="E47" s="344"/>
-      <c r="F47" s="344"/>
+      <c r="C47" s="342"/>
+      <c r="D47" s="342"/>
+      <c r="E47" s="342"/>
+      <c r="F47" s="342"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4456,7 +4456,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="344" t="s">
+      <c r="B50" s="342" t="s">
         <v>352</v>
       </c>
       <c r="C50" s="345"/>
@@ -4478,22 +4478,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="343" t="s">
+      <c r="B53" s="341" t="s">
         <v>357</v>
       </c>
-      <c r="C53" s="343"/>
-      <c r="D53" s="343"/>
-      <c r="E53" s="343"/>
-      <c r="F53" s="343"/>
+      <c r="C53" s="341"/>
+      <c r="D53" s="341"/>
+      <c r="E53" s="341"/>
+      <c r="F53" s="341"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="343" t="s">
+      <c r="B54" s="341" t="s">
         <v>379</v>
       </c>
-      <c r="C54" s="343"/>
-      <c r="D54" s="343"/>
-      <c r="E54" s="343"/>
-      <c r="F54" s="343"/>
+      <c r="C54" s="341"/>
+      <c r="D54" s="341"/>
+      <c r="E54" s="341"/>
+      <c r="F54" s="341"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4554,22 +4554,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="343" t="s">
+      <c r="B63" s="341" t="s">
         <v>380</v>
       </c>
-      <c r="C63" s="343"/>
-      <c r="D63" s="343"/>
-      <c r="E63" s="343"/>
-      <c r="F63" s="343"/>
+      <c r="C63" s="341"/>
+      <c r="D63" s="341"/>
+      <c r="E63" s="341"/>
+      <c r="F63" s="341"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="343" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="343"/>
+      <c r="D64" s="343"/>
+      <c r="E64" s="343"/>
+      <c r="F64" s="343"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4627,22 +4627,22 @@
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="343" t="s">
+      <c r="B73" s="341" t="s">
         <v>381</v>
       </c>
-      <c r="C73" s="343"/>
-      <c r="D73" s="343"/>
-      <c r="E73" s="343"/>
-      <c r="F73" s="343"/>
+      <c r="C73" s="341"/>
+      <c r="D73" s="341"/>
+      <c r="E73" s="341"/>
+      <c r="F73" s="341"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="343" t="s">
+      <c r="B74" s="341" t="s">
         <v>382</v>
       </c>
-      <c r="C74" s="343"/>
-      <c r="D74" s="343"/>
-      <c r="E74" s="343"/>
-      <c r="F74" s="343"/>
+      <c r="C74" s="341"/>
+      <c r="D74" s="341"/>
+      <c r="E74" s="341"/>
+      <c r="F74" s="341"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4679,13 +4679,13 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="343" t="s">
+      <c r="B81" s="341" t="s">
         <v>383</v>
       </c>
-      <c r="C81" s="343"/>
-      <c r="D81" s="343"/>
-      <c r="E81" s="343"/>
-      <c r="F81" s="343"/>
+      <c r="C81" s="341"/>
+      <c r="D81" s="341"/>
+      <c r="E81" s="341"/>
+      <c r="F81" s="341"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4698,13 +4698,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="343" t="s">
+      <c r="B85" s="341" t="s">
         <v>358</v>
       </c>
-      <c r="C85" s="343"/>
-      <c r="D85" s="343"/>
-      <c r="E85" s="343"/>
-      <c r="F85" s="343"/>
+      <c r="C85" s="341"/>
+      <c r="D85" s="341"/>
+      <c r="E85" s="341"/>
+      <c r="F85" s="341"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4808,13 +4808,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="343" t="s">
+      <c r="B98" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C98" s="343"/>
-      <c r="D98" s="343"/>
-      <c r="E98" s="343"/>
-      <c r="F98" s="343"/>
+      <c r="C98" s="341"/>
+      <c r="D98" s="341"/>
+      <c r="E98" s="341"/>
+      <c r="F98" s="341"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4840,13 +4840,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="344" t="s">
+      <c r="B104" s="342" t="s">
         <v>385</v>
       </c>
-      <c r="C104" s="344"/>
-      <c r="D104" s="344"/>
-      <c r="E104" s="344"/>
-      <c r="F104" s="344"/>
+      <c r="C104" s="342"/>
+      <c r="D104" s="342"/>
+      <c r="E104" s="342"/>
+      <c r="F104" s="342"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="266" t="s">
@@ -4989,13 +4989,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="347" t="s">
+      <c r="B115" s="346" t="s">
         <v>388</v>
       </c>
-      <c r="C115" s="347"/>
-      <c r="D115" s="347"/>
-      <c r="E115" s="347"/>
-      <c r="F115" s="347"/>
+      <c r="C115" s="346"/>
+      <c r="D115" s="346"/>
+      <c r="E115" s="346"/>
+      <c r="F115" s="346"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
@@ -5008,22 +5008,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="348" t="s">
+      <c r="B119" s="344" t="s">
         <v>386</v>
       </c>
-      <c r="C119" s="348"/>
-      <c r="D119" s="348"/>
-      <c r="E119" s="348"/>
-      <c r="F119" s="348"/>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="343" t="s">
+      <c r="B120" s="341" t="s">
         <v>387</v>
       </c>
-      <c r="C120" s="343"/>
-      <c r="D120" s="343"/>
-      <c r="E120" s="343"/>
-      <c r="F120" s="343"/>
+      <c r="C120" s="341"/>
+      <c r="D120" s="341"/>
+      <c r="E120" s="341"/>
+      <c r="F120" s="341"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
@@ -5119,13 +5119,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="342" t="s">
+      <c r="B134" s="348" t="s">
         <v>394</v>
       </c>
-      <c r="C134" s="343"/>
-      <c r="D134" s="343"/>
-      <c r="E134" s="343"/>
-      <c r="F134" s="343"/>
+      <c r="C134" s="341"/>
+      <c r="D134" s="341"/>
+      <c r="E134" s="341"/>
+      <c r="F134" s="341"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="240" t="s">
@@ -5162,13 +5162,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="344" t="s">
+      <c r="B143" s="342" t="s">
         <v>399</v>
       </c>
-      <c r="C143" s="344"/>
-      <c r="D143" s="344"/>
-      <c r="E143" s="344"/>
-      <c r="F143" s="344"/>
+      <c r="C143" s="342"/>
+      <c r="D143" s="342"/>
+      <c r="E143" s="342"/>
+      <c r="F143" s="342"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5176,22 +5176,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="341" t="s">
+      <c r="B146" s="347" t="s">
         <v>400</v>
       </c>
-      <c r="C146" s="341"/>
-      <c r="D146" s="341"/>
-      <c r="E146" s="341"/>
-      <c r="F146" s="341"/>
+      <c r="C146" s="347"/>
+      <c r="D146" s="347"/>
+      <c r="E146" s="347"/>
+      <c r="F146" s="347"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="341" t="s">
+      <c r="B147" s="347" t="s">
         <v>401</v>
       </c>
-      <c r="C147" s="341"/>
-      <c r="D147" s="341"/>
-      <c r="E147" s="341"/>
-      <c r="F147" s="341"/>
+      <c r="C147" s="347"/>
+      <c r="D147" s="347"/>
+      <c r="E147" s="347"/>
+      <c r="F147" s="347"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5215,6 +5215,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5231,17 +5242,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87AF323-0C9C-4011-B000-AB60336FEF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1080E3-DEBF-41D4-A6D6-E88645174401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -1557,10 +1557,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Always use 10yrs to identify the HGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Use Excel Goal Seek to find the HGR</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2331,6 +2327,10 @@
   </si>
   <si>
     <t>Net Income/Market Cap</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3697,30 +3697,31 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3733,7 +3734,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F1" s="284" t="s">
         <v>291</v>
@@ -4062,13 +4062,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4131,13 +4131,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="337" t="s">
-        <v>377</v>
-      </c>
-      <c r="C12" s="337"/>
-      <c r="D12" s="337"/>
-      <c r="E12" s="337"/>
-      <c r="F12" s="337"/>
+      <c r="B12" s="336" t="s">
+        <v>376</v>
+      </c>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4148,7 +4148,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4184,7 +4184,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4215,7 +4215,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4230,7 +4230,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4239,22 +4239,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="337" t="s">
-        <v>378</v>
-      </c>
-      <c r="C25" s="337"/>
-      <c r="D25" s="337"/>
-      <c r="E25" s="337"/>
-      <c r="F25" s="337"/>
+      <c r="B25" s="336" t="s">
+        <v>377</v>
+      </c>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="340" t="s">
-        <v>353</v>
-      </c>
-      <c r="C26" s="340"/>
-      <c r="D26" s="340"/>
-      <c r="E26" s="340"/>
-      <c r="F26" s="340"/>
+      <c r="B26" s="338" t="s">
+        <v>352</v>
+      </c>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4266,13 +4266,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="338" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="338"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4292,13 +4292,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="338" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="338"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="338"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="338" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="338"/>
-      <c r="D36" s="338"/>
-      <c r="E36" s="338"/>
-      <c r="F36" s="338"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4349,17 +4349,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="338" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4419,13 +4419,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="338" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4441,13 +4441,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="338" t="s">
-        <v>352</v>
-      </c>
-      <c r="C50" s="339"/>
-      <c r="D50" s="339"/>
-      <c r="E50" s="339"/>
-      <c r="F50" s="339"/>
+      <c r="B50" s="337" t="s">
+        <v>351</v>
+      </c>
+      <c r="C50" s="340"/>
+      <c r="D50" s="340"/>
+      <c r="E50" s="340"/>
+      <c r="F50" s="340"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4463,22 +4463,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="337" t="s">
-        <v>357</v>
-      </c>
-      <c r="C53" s="337"/>
-      <c r="D53" s="337"/>
-      <c r="E53" s="337"/>
-      <c r="F53" s="337"/>
+      <c r="B53" s="336" t="s">
+        <v>356</v>
+      </c>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="337" t="s">
-        <v>379</v>
-      </c>
-      <c r="C54" s="337"/>
-      <c r="D54" s="337"/>
-      <c r="E54" s="337"/>
-      <c r="F54" s="337"/>
+      <c r="B54" s="336" t="s">
+        <v>378</v>
+      </c>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4508,7 +4508,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4526,7 +4526,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4539,22 +4539,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="337" t="s">
-        <v>380</v>
-      </c>
-      <c r="C63" s="337"/>
-      <c r="D63" s="337"/>
-      <c r="E63" s="337"/>
-      <c r="F63" s="337"/>
+      <c r="B63" s="336" t="s">
+        <v>379</v>
+      </c>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="340" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="340"/>
-      <c r="D64" s="340"/>
-      <c r="E64" s="340"/>
-      <c r="F64" s="340"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -4590,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4607,27 +4607,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="337" t="s">
+      <c r="B73" s="336" t="s">
+        <v>380</v>
+      </c>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C73" s="337"/>
-      <c r="D73" s="337"/>
-      <c r="E73" s="337"/>
-      <c r="F73" s="337"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="337" t="s">
-        <v>382</v>
-      </c>
-      <c r="C74" s="337"/>
-      <c r="D74" s="337"/>
-      <c r="E74" s="337"/>
-      <c r="F74" s="337"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4652,7 +4652,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4664,13 +4664,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="337" t="s">
-        <v>383</v>
-      </c>
-      <c r="C81" s="337"/>
-      <c r="D81" s="337"/>
-      <c r="E81" s="337"/>
-      <c r="F81" s="337"/>
+      <c r="B81" s="336" t="s">
+        <v>382</v>
+      </c>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="337" t="s">
-        <v>358</v>
-      </c>
-      <c r="C85" s="337"/>
-      <c r="D85" s="337"/>
-      <c r="E85" s="337"/>
-      <c r="F85" s="337"/>
+      <c r="B85" s="336" t="s">
+        <v>357</v>
+      </c>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4793,13 +4793,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="337" t="s">
-        <v>384</v>
-      </c>
-      <c r="C98" s="337"/>
-      <c r="D98" s="337"/>
-      <c r="E98" s="337"/>
-      <c r="F98" s="337"/>
+      <c r="B98" s="336" t="s">
+        <v>383</v>
+      </c>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4816,7 +4816,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4825,13 +4825,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="338" t="s">
-        <v>385</v>
-      </c>
-      <c r="C104" s="338"/>
-      <c r="D104" s="338"/>
-      <c r="E104" s="338"/>
-      <c r="F104" s="338"/>
+      <c r="B104" s="337" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4975,7 +4975,7 @@
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="341" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C115" s="341"/>
       <c r="D115" s="341"/>
@@ -4984,7 +4984,7 @@
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4993,22 +4993,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="342" t="s">
+      <c r="B119" s="339" t="s">
+        <v>385</v>
+      </c>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
+    </row>
+    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="336" t="s">
         <v>386</v>
       </c>
-      <c r="C119" s="342"/>
-      <c r="D119" s="342"/>
-      <c r="E119" s="342"/>
-      <c r="F119" s="342"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="337" t="s">
-        <v>387</v>
-      </c>
-      <c r="C120" s="337"/>
-      <c r="D120" s="337"/>
-      <c r="E120" s="337"/>
-      <c r="F120" s="337"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5095,7 +5095,7 @@
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A132" s="247" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
@@ -5104,102 +5104,113 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="336" t="s">
-        <v>394</v>
-      </c>
-      <c r="C134" s="337"/>
-      <c r="D134" s="337"/>
-      <c r="E134" s="337"/>
-      <c r="F134" s="337"/>
+      <c r="B134" s="343" t="s">
+        <v>393</v>
+      </c>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="339" t="s">
-        <v>398</v>
-      </c>
-      <c r="C137" s="339"/>
-      <c r="D137" s="339"/>
-      <c r="E137" s="339"/>
-      <c r="F137" s="339"/>
+      <c r="B137" s="340" t="s">
+        <v>397</v>
+      </c>
+      <c r="C137" s="340"/>
+      <c r="D137" s="340"/>
+      <c r="E137" s="340"/>
+      <c r="F137" s="340"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="238" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B139" s="238" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B140" s="238" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="338" t="s">
-        <v>399</v>
-      </c>
-      <c r="C143" s="338"/>
-      <c r="D143" s="338"/>
-      <c r="E143" s="338"/>
-      <c r="F143" s="338"/>
+      <c r="B143" s="337" t="s">
+        <v>398</v>
+      </c>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="335" t="s">
+      <c r="B146" s="342" t="s">
+        <v>399</v>
+      </c>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
+    </row>
+    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B147" s="342" t="s">
         <v>400</v>
       </c>
-      <c r="C146" s="335"/>
-      <c r="D146" s="335"/>
-      <c r="E146" s="335"/>
-      <c r="F146" s="335"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="335" t="s">
-        <v>401</v>
-      </c>
-      <c r="C147" s="335"/>
-      <c r="D147" s="335"/>
-      <c r="E147" s="335"/>
-      <c r="F147" s="335"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B150" s="238" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B151" s="238" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B152" s="238" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5216,17 +5227,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5627,7 +5627,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C22" s="181">
         <v>5154661132</v>
@@ -5645,7 +5645,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C23" s="181">
         <v>-7421783375</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C24" s="181">
         <v>-2983143705</v>
@@ -6919,7 +6919,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7367,11 +7367,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I77" s="347"/>
-      <c r="J77" s="347"/>
-      <c r="K77" s="347"/>
-      <c r="L77" s="347"/>
-      <c r="M77" s="347"/>
+      <c r="I77" s="335"/>
+      <c r="J77" s="335"/>
+      <c r="K77" s="335"/>
+      <c r="L77" s="335"/>
+      <c r="M77" s="335"/>
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B78" s="93" t="s">
@@ -7401,11 +7401,11 @@
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I78" s="347"/>
-      <c r="J78" s="347"/>
-      <c r="K78" s="347"/>
-      <c r="L78" s="347"/>
-      <c r="M78" s="347"/>
+      <c r="I78" s="335"/>
+      <c r="J78" s="335"/>
+      <c r="K78" s="335"/>
+      <c r="L78" s="335"/>
+      <c r="M78" s="335"/>
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
@@ -8570,7 +8570,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8582,7 +8582,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8593,12 +8593,12 @@
         <v>-2570179946.0280437</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8609,12 +8609,12 @@
         <v>6.9951416918431715</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8622,12 +8622,12 @@
         <v>5140359892.0560875</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8635,7 +8635,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10189,7 +10189,7 @@
         <v>-1406578781</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10247,7 +10247,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10694,7 +10694,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10749,7 +10749,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -10882,7 +10882,7 @@
         <v>3.430552260533988E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10909,7 +10909,7 @@
         <v>7.6514823945754068E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -13158,7 +13158,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13210,7 +13210,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13719,7 +13719,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14548,10 +14548,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="343" t="s">
+      <c r="E6" s="344" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="343"/>
+      <c r="F6" s="344"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14566,8 +14566,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="343"/>
-      <c r="F7" s="343"/>
+      <c r="E7" s="344"/>
+      <c r="F7" s="344"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14582,8 +14582,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="343"/>
-      <c r="F8" s="343"/>
+      <c r="E8" s="344"/>
+      <c r="F8" s="344"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14598,8 +14598,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="343"/>
-      <c r="F9" s="343"/>
+      <c r="E9" s="344"/>
+      <c r="F9" s="344"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16093,11 +16093,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="345" t="str">
+      <c r="E7" s="346" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 青島啤酒股份(0168.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="345"/>
+      <c r="F7" s="346"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16118,8 +16118,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="346"/>
+      <c r="F8" s="346"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16140,8 +16140,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="346"/>
+      <c r="F9" s="346"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16151,8 +16151,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="345"/>
-      <c r="F10" s="345"/>
+      <c r="E10" s="346"/>
+      <c r="F10" s="346"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16165,8 +16165,8 @@
       <c r="B11" s="160" t="s">
         <v>282</v>
       </c>
-      <c r="E11" s="345"/>
-      <c r="F11" s="345"/>
+      <c r="E11" s="346"/>
+      <c r="F11" s="346"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16184,8 +16184,8 @@
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="345"/>
-      <c r="F12" s="345"/>
+      <c r="E12" s="346"/>
+      <c r="F12" s="346"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16202,8 +16202,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="345"/>
-      <c r="F13" s="345"/>
+      <c r="E13" s="346"/>
+      <c r="F13" s="346"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16220,8 +16220,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="345"/>
-      <c r="F14" s="345"/>
+      <c r="E14" s="346"/>
+      <c r="F14" s="346"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16237,7 +16237,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16247,21 +16247,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="345" t="s">
-        <v>344</v>
-      </c>
-      <c r="F18" s="346"/>
+      <c r="E18" s="346" t="s">
+        <v>343</v>
+      </c>
+      <c r="F18" s="347"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="346"/>
-      <c r="F19" s="346"/>
+      <c r="E19" s="347"/>
+      <c r="F19" s="347"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
         <v>314</v>
       </c>
-      <c r="E20" s="346"/>
-      <c r="F20" s="346"/>
+      <c r="E20" s="347"/>
+      <c r="F20" s="347"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
@@ -16275,8 +16275,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="346"/>
-      <c r="F21" s="346"/>
+      <c r="E21" s="347"/>
+      <c r="F21" s="347"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
@@ -16290,8 +16290,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="346"/>
-      <c r="F22" s="346"/>
+      <c r="E22" s="347"/>
+      <c r="F22" s="347"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16311,8 +16311,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="344"/>
-      <c r="F25" s="344"/>
+      <c r="E25" s="345"/>
+      <c r="F25" s="345"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16322,8 +16322,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="344"/>
-      <c r="F26" s="344"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16337,8 +16337,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="344"/>
-      <c r="F27" s="344"/>
+      <c r="E27" s="345"/>
+      <c r="F27" s="345"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16348,8 +16348,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="344"/>
-      <c r="F28" s="344"/>
+      <c r="E28" s="345"/>
+      <c r="F28" s="345"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16369,8 +16369,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="344"/>
-      <c r="F31" s="344"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16380,8 +16380,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="344"/>
-      <c r="F32" s="344"/>
+      <c r="E32" s="345"/>
+      <c r="F32" s="345"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16395,8 +16395,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="344"/>
-      <c r="F33" s="344"/>
+      <c r="E33" s="345"/>
+      <c r="F33" s="345"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16406,8 +16406,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="E34" s="345"/>
+      <c r="F34" s="345"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16427,8 +16427,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="E37" s="345"/>
+      <c r="F37" s="345"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16438,8 +16438,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="344"/>
-      <c r="F38" s="344"/>
+      <c r="E38" s="345"/>
+      <c r="F38" s="345"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16453,8 +16453,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="344"/>
-      <c r="F39" s="344"/>
+      <c r="E39" s="345"/>
+      <c r="F39" s="345"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16465,8 +16465,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="344"/>
-      <c r="F40" s="344"/>
+      <c r="E40" s="345"/>
+      <c r="F40" s="345"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16528,8 +16528,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="344"/>
-      <c r="F49" s="344"/>
+      <c r="E49" s="345"/>
+      <c r="F49" s="345"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16539,8 +16539,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
+      <c r="E50" s="345"/>
+      <c r="F50" s="345"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16554,8 +16554,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="344"/>
-      <c r="F51" s="344"/>
+      <c r="E51" s="345"/>
+      <c r="F51" s="345"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16565,12 +16565,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="E52" s="345"/>
+      <c r="F52" s="345"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16586,8 +16586,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="344"/>
-      <c r="F55" s="344"/>
+      <c r="E55" s="345"/>
+      <c r="F55" s="345"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16597,8 +16597,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="344"/>
-      <c r="F56" s="344"/>
+      <c r="E56" s="345"/>
+      <c r="F56" s="345"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16612,8 +16612,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="344"/>
-      <c r="F57" s="344"/>
+      <c r="E57" s="345"/>
+      <c r="F57" s="345"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16623,8 +16623,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="344"/>
-      <c r="F58" s="344"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16648,7 +16648,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16668,11 +16668,12 @@
         <v>135</v>
       </c>
       <c r="C64" s="167">
+        <f>C18</f>
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16684,7 +16685,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16700,15 +16701,15 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
@@ -16752,7 +16753,7 @@
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16887,7 +16888,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="320" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F89" s="317"/>
       <c r="G89" s="2"/>
@@ -16895,30 +16896,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="313" t="s">
+        <v>338</v>
+      </c>
+      <c r="F90" s="318" t="s">
         <v>339</v>
-      </c>
-      <c r="F90" s="318" t="s">
-        <v>340</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="316"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="314" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F91" s="318" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="316"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="315" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F92" s="319" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="316"/>

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1080E3-DEBF-41D4-A6D6-E88645174401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9D8ECB-1899-4602-A76F-BF866ADF449E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3154061396.4765129</v>
+        <v>3105789113.4765129</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5428,9 +5428,7 @@
       <c r="B9" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C9" s="181">
-        <v>48272283</v>
-      </c>
+      <c r="C9" s="181"/>
       <c r="D9" s="181"/>
       <c r="E9" s="181"/>
       <c r="F9" s="181"/>
@@ -6574,7 +6572,7 @@
       </c>
       <c r="C55" s="188">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
-        <v>48272283</v>
+        <v>0</v>
       </c>
       <c r="D55" s="188" t="str">
         <f t="shared" si="25"/>
@@ -6721,7 +6719,7 @@
       </c>
       <c r="C58" s="188">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
-        <v>750493994</v>
+        <v>798766277</v>
       </c>
       <c r="D58" s="188" t="str">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
@@ -8412,7 +8410,7 @@
       </c>
       <c r="D55" s="92">
         <f>Normalized_FCF!G11/G40</f>
-        <v>2.1050212495974641E-3</v>
+        <v>0</v>
       </c>
       <c r="F55" s="283"/>
     </row>
@@ -9319,7 +9317,7 @@
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
-        <v>48272283</v>
+        <v>0</v>
       </c>
       <c r="H11" s="186" t="str">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
@@ -9429,7 +9427,7 @@
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4690570538.4765129</v>
+        <v>4642298255.4765129</v>
       </c>
       <c r="H13" s="184" t="str">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
@@ -9598,7 +9596,7 @@
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3154061396.4765129</v>
+        <v>3105789113.4765129</v>
       </c>
       <c r="H16" s="184" t="str">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
@@ -9706,7 +9704,7 @@
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3154061396.4765129</v>
+        <v>3105789113.4765129</v>
       </c>
       <c r="H19" s="186" t="str">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
@@ -10560,7 +10558,7 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29627873679762989</v>
+        <v>0.29935954941295589</v>
       </c>
       <c r="H43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10702,11 +10700,11 @@
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
-        <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
+        <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>176342732.47651258</v>
       </c>
       <c r="H48" s="328" t="str">
-        <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
+        <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v/>
       </c>
       <c r="I48" s="328" t="str">
@@ -11001,7 +10999,7 @@
         <v>169</v>
       </c>
       <c r="C58" s="191">
-        <f>BS!$C79*C66</f>
+        <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="302"/>
@@ -11062,7 +11060,7 @@
       <c r="E59" s="302"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
-        <v>48272283</v>
+        <v>0</v>
       </c>
       <c r="H59" s="191" t="str">
         <f>Data!D55</f>
@@ -11111,7 +11109,7 @@
         <v>160</v>
       </c>
       <c r="C60" s="191">
-        <f>BS!$C81*C68</f>
+        <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="302"/>
@@ -11172,7 +11170,7 @@
       <c r="E61" s="302"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
-        <v>48272283</v>
+        <v>0</v>
       </c>
       <c r="H61" s="184" t="str">
         <f t="shared" si="22"/>
@@ -11228,7 +11226,7 @@
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
-        <v>750493994</v>
+        <v>798766277</v>
       </c>
       <c r="H62" s="191" t="str">
         <f>Data!D58</f>
@@ -11401,7 +11399,7 @@
       </c>
       <c r="E68" s="302"/>
       <c r="G68" s="23">
-        <f>IFERROR(G60/BS!$C$81,0)</f>
+        <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
       </c>
       <c r="H68" s="176"/>
@@ -11429,7 +11427,7 @@
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
-        <v>2.684959828973636E-3</v>
+        <v>0</v>
       </c>
       <c r="H69" s="176"/>
       <c r="I69" s="176"/>
@@ -11847,7 +11845,7 @@
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
-        <v>1.5020392737553731E-3</v>
+        <v>0</v>
       </c>
       <c r="H79" s="65" t="str">
         <f t="shared" si="30"/>
@@ -11961,7 +11959,7 @@
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14595168753695803</v>
+        <v>0.14444964826320264</v>
       </c>
       <c r="H81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12133,7 +12131,7 @@
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.8141703580571046E-2</v>
+        <v>9.6639664306815684E-2</v>
       </c>
       <c r="H84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12240,7 +12238,7 @@
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.8141703580571046E-2</v>
+        <v>9.6639664306815684E-2</v>
       </c>
       <c r="H87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12418,7 +12416,7 @@
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>1.0120671150861329</v>
+        <v>1.0277973493066221</v>
       </c>
       <c r="H92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12605,7 +12603,7 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-1.0291345712429845E-2</v>
+        <v>0</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
@@ -13216,7 +13214,7 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6342932124778582</v>
+        <v>1.6596945071489579</v>
       </c>
       <c r="H114" s="334" t="str">
         <f>IF(H$4="","",Data!D$22/H19)</f>
@@ -13329,7 +13327,7 @@
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14595168753695803</v>
+        <v>0.14444964826320264</v>
       </c>
       <c r="H117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13617,7 +13615,7 @@
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.1737688807453912</v>
+        <v>2.1404997799266314</v>
       </c>
       <c r="H124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13674,7 +13672,7 @@
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.9703541200829064E-2</v>
+        <v>3.9095886391354001E-2</v>
       </c>
       <c r="H125" s="77" t="str">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
@@ -16112,7 +16110,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>3154061396.4765129</v>
+        <v>3105789113.4765129</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9D8ECB-1899-4602-A76F-BF866ADF449E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9474C67-4A32-4056-BE35-9615ADC615E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1321,10 +1321,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1829,14 +1825,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Implied Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2331,6 +2319,45 @@
   </si>
   <si>
     <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>in contrast to a cash yield of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>Sell Price Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Cash Yield</t>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3005,7 +3032,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3698,6 +3725,9 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4010,7 +4040,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4030,15 +4060,15 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="247" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4062,13 +4092,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4095,7 +4125,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4105,7 +4135,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4131,24 +4161,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
-        <v>376</v>
-      </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="B12" s="337" t="s">
+        <v>373</v>
+      </c>
+      <c r="C12" s="337"/>
+      <c r="D12" s="337"/>
+      <c r="E12" s="337"/>
+      <c r="F12" s="337"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4158,10 +4188,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4184,18 +4214,23 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C19" s="249">
-        <v>0.2</v>
-      </c>
-      <c r="E19" s="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E19" s="336">
+        <v>3.4500000000000003E-2</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="str">
@@ -4204,10 +4239,10 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>30.327492930578011</v>
+        <v>27.038487197680578</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4215,7 +4250,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>375</v>
+        <v>418</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4230,7 +4265,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4239,22 +4274,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
-        <v>377</v>
-      </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="B25" s="337" t="s">
+        <v>374</v>
+      </c>
+      <c r="C25" s="337"/>
+      <c r="D25" s="337"/>
+      <c r="E25" s="337"/>
+      <c r="F25" s="337"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
-        <v>352</v>
-      </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="B26" s="339" t="s">
+        <v>351</v>
+      </c>
+      <c r="C26" s="339"/>
+      <c r="D26" s="339"/>
+      <c r="E26" s="339"/>
+      <c r="F26" s="339"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4266,13 +4301,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="338" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="338"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4292,13 +4327,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="338" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="338"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="338"/>
+      <c r="F32" s="338"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4327,13 +4362,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="338" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="338"/>
+      <c r="D36" s="338"/>
+      <c r="E36" s="338"/>
+      <c r="F36" s="338"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4349,17 +4384,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="338" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="338"/>
+      <c r="D39" s="338"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4374,7 +4409,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4407,7 +4442,7 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4419,13 +4454,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="338" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="338"/>
+      <c r="D47" s="338"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4441,13 +4476,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
-        <v>351</v>
-      </c>
-      <c r="C50" s="340"/>
-      <c r="D50" s="340"/>
-      <c r="E50" s="340"/>
-      <c r="F50" s="340"/>
+      <c r="B50" s="338" t="s">
+        <v>350</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4463,26 +4498,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
-        <v>356</v>
-      </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="B53" s="337" t="s">
+        <v>355</v>
+      </c>
+      <c r="C53" s="337"/>
+      <c r="D53" s="337"/>
+      <c r="E53" s="337"/>
+      <c r="F53" s="337"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
-        <v>378</v>
-      </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="B54" s="337" t="s">
+        <v>375</v>
+      </c>
+      <c r="C54" s="337"/>
+      <c r="D54" s="337"/>
+      <c r="E54" s="337"/>
+      <c r="F54" s="337"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4508,7 +4543,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4517,7 +4552,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4526,7 +4561,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4539,22 +4574,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
-        <v>379</v>
-      </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="B63" s="337" t="s">
+        <v>376</v>
+      </c>
+      <c r="C63" s="337"/>
+      <c r="D63" s="337"/>
+      <c r="E63" s="337"/>
+      <c r="F63" s="337"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="339" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="339"/>
+      <c r="D64" s="339"/>
+      <c r="E64" s="339"/>
+      <c r="F64" s="339"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4563,7 +4598,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4571,26 +4606,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4607,27 +4642,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
-        <v>380</v>
-      </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="B73" s="337" t="s">
+        <v>377</v>
+      </c>
+      <c r="C73" s="337"/>
+      <c r="D73" s="337"/>
+      <c r="E73" s="337"/>
+      <c r="F73" s="337"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
-        <v>381</v>
-      </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="B74" s="337" t="s">
+        <v>378</v>
+      </c>
+      <c r="C74" s="337"/>
+      <c r="D74" s="337"/>
+      <c r="E74" s="337"/>
+      <c r="F74" s="337"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4639,7 +4674,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4652,7 +4687,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4664,13 +4699,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
-        <v>382</v>
-      </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="B81" s="337" t="s">
+        <v>379</v>
+      </c>
+      <c r="C81" s="337"/>
+      <c r="D81" s="337"/>
+      <c r="E81" s="337"/>
+      <c r="F81" s="337"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4683,13 +4718,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
-        <v>357</v>
-      </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="B85" s="337" t="s">
+        <v>356</v>
+      </c>
+      <c r="C85" s="337"/>
+      <c r="D85" s="337"/>
+      <c r="E85" s="337"/>
+      <c r="F85" s="337"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4706,7 +4741,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4724,7 +4759,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C90" s="188">
         <f>BS!C66</f>
@@ -4737,7 +4772,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
@@ -4750,7 +4785,7 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
@@ -4781,7 +4816,7 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
@@ -4793,17 +4828,17 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
-        <v>383</v>
-      </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="B98" s="337" t="s">
+        <v>380</v>
+      </c>
+      <c r="C98" s="337"/>
+      <c r="D98" s="337"/>
+      <c r="E98" s="337"/>
+      <c r="F98" s="337"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
@@ -4816,7 +4851,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4825,13 +4860,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
-        <v>384</v>
-      </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="B104" s="338" t="s">
+        <v>381</v>
+      </c>
+      <c r="C104" s="338"/>
+      <c r="D104" s="338"/>
+      <c r="E104" s="338"/>
+      <c r="F104" s="338"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4974,17 +5009,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
-        <v>387</v>
-      </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="B115" s="342" t="s">
+        <v>384</v>
+      </c>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4993,22 +5028,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
-        <v>385</v>
-      </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="B119" s="340" t="s">
+        <v>382</v>
+      </c>
+      <c r="C119" s="340"/>
+      <c r="D119" s="340"/>
+      <c r="E119" s="340"/>
+      <c r="F119" s="340"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
-        <v>386</v>
-      </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="B120" s="337" t="s">
+        <v>383</v>
+      </c>
+      <c r="C120" s="337"/>
+      <c r="D120" s="337"/>
+      <c r="E120" s="337"/>
+      <c r="F120" s="337"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5017,7 +5052,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C122" s="251">
         <f>E20</f>
@@ -5026,11 +5061,11 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C123" s="250">
         <f>C19</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
@@ -5048,7 +5083,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B126" s="234" t="s">
-        <v>265</v>
+        <v>419</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -5058,7 +5093,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>4.9290143153151025</v>
+        <v>4.5675388215273349</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5068,7 +5103,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>25.398478615262906</v>
+        <v>22.470948376153242</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5077,7 +5112,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>30.327492930578011</v>
+        <v>27.038487197680578</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5090,121 +5125,168 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.30898882768409019</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A132" s="247" t="s">
+        <v>0.38392874152549084</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="234" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="236" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C133" s="240">
+        <f>Scenarios!C91</f>
+        <v>6.5618942447874584</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C134" s="240">
+        <f>Scenarios!C92</f>
+        <v>39.642401523537714</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B135" s="80" t="s">
+        <v>421</v>
+      </c>
+      <c r="C135" s="239">
+        <f>Scenarios!C93</f>
+        <v>46.204295768325174</v>
+      </c>
+      <c r="D135" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="238" t="s">
+        <v>264</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!F93</f>
+        <v>-5.2763730189843372E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A138" s="247" t="s">
+        <v>388</v>
+      </c>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36"/>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="344" t="s">
+        <v>390</v>
+      </c>
+      <c r="C140" s="337"/>
+      <c r="D140" s="337"/>
+      <c r="E140" s="337"/>
+      <c r="F140" s="337"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="234" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B143" s="341" t="s">
+        <v>394</v>
+      </c>
+      <c r="C143" s="341"/>
+      <c r="D143" s="341"/>
+      <c r="E143" s="341"/>
+      <c r="F143" s="341"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="238" t="s">
         <v>391</v>
       </c>
-      <c r="B132" s="36"/>
-      <c r="C132" s="36"/>
-      <c r="D132" s="36"/>
-      <c r="E132" s="36"/>
-      <c r="F132" s="36"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="238" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="238" t="s">
         <v>393</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="234" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="340" t="s">
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="338" t="s">
+        <v>395</v>
+      </c>
+      <c r="C149" s="338"/>
+      <c r="D149" s="338"/>
+      <c r="E149" s="338"/>
+      <c r="F149" s="338"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="343" t="s">
+        <v>396</v>
+      </c>
+      <c r="C152" s="343"/>
+      <c r="D152" s="343"/>
+      <c r="E152" s="343"/>
+      <c r="F152" s="343"/>
+    </row>
+    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="343" t="s">
         <v>397</v>
       </c>
-      <c r="C137" s="340"/>
-      <c r="D137" s="340"/>
-      <c r="E137" s="340"/>
-      <c r="F137" s="340"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B138" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B139" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="238" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="1" t="s">
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B155" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B156" s="238" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B157" s="238" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
-        <v>398</v>
-      </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="1" t="s">
+    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B158" s="238" t="s">
         <v>402</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
-        <v>399</v>
-      </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
-        <v>400</v>
-      </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="238" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="238" t="s">
-        <v>405</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B149:F149"/>
     <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B104:F104"/>
     <mergeCell ref="B73:F73"/>
@@ -5229,7 +5311,7 @@
     <mergeCell ref="B63:F63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5625,7 +5707,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C22" s="181">
         <v>5154661132</v>
@@ -5643,7 +5725,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C23" s="181">
         <v>-7421783375</v>
@@ -5661,7 +5743,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C24" s="181">
         <v>-2983143705</v>
@@ -6917,7 +6999,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8289,13 +8371,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C45" s="261" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8303,7 +8385,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8456,7 +8538,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8479,7 +8561,7 @@
         <v>2.749989365273205E-2</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8501,7 +8583,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8568,7 +8650,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8580,7 +8662,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8591,12 +8673,12 @@
         <v>-2570179946.0280437</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8607,12 +8689,12 @@
         <v>6.9951416918431715</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8620,12 +8702,12 @@
         <v>5140359892.0560875</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8633,7 +8715,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8709,7 +8791,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8720,15 +8802,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>300</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8745,7 +8827,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8779,7 +8861,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9650,7 +9732,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9675,7 +9757,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10003,7 +10085,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10063,7 +10145,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10187,7 +10269,7 @@
         <v>-1406578781</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10245,7 +10327,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10553,7 +10635,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10692,7 +10774,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10747,7 +10829,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -10880,7 +10962,7 @@
         <v>3.430552260533988E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10907,7 +10989,7 @@
         <v>7.6514823945754068E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11222,7 +11304,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11783,7 +11865,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12462,7 +12544,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13156,7 +13238,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13208,7 +13290,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13661,7 +13743,7 @@
     <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13717,7 +13799,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14546,10 +14628,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="344" t="s">
+      <c r="E6" s="345" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="344"/>
+      <c r="F6" s="345"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14564,8 +14646,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14580,8 +14662,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14596,8 +14678,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15942,7 +16024,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -15994,7 +16076,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I92"/>
+  <dimension ref="B2:I98"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16014,7 +16096,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16068,7 +16150,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16081,7 +16163,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16091,11 +16173,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 青島啤酒股份(0168.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16116,8 +16198,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16138,8 +16220,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16149,8 +16231,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16161,10 +16243,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>281</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16182,8 +16264,8 @@
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16200,8 +16282,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16218,8 +16300,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16235,7 +16317,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16245,25 +16327,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>343</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>342</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>314</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>313</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16273,12 +16355,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16288,8 +16370,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16309,8 +16391,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16320,8 +16402,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16335,8 +16417,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16346,8 +16428,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16367,8 +16449,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16378,8 +16460,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16393,8 +16475,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16404,8 +16486,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16425,8 +16507,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16436,8 +16518,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16451,8 +16533,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16463,8 +16545,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16526,8 +16608,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16537,8 +16619,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16552,8 +16634,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16563,12 +16645,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16584,8 +16666,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16595,8 +16677,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16610,8 +16692,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16621,8 +16703,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16637,7 +16719,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16646,7 +16728,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16655,10 +16737,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16671,7 +16753,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16683,7 +16765,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16699,20 +16781,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16722,19 +16804,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16744,14 +16826,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16774,7 +16856,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -16797,16 +16879,16 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C123</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
@@ -16815,7 +16897,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.9290143153151025</v>
+        <v>4.5675388215273349</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -16827,7 +16909,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>25.398478615262906</v>
+        <v>22.470948376153242</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -16837,7 +16919,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>30.327492930578011</v>
+        <v>27.038487197680578</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16848,7 +16930,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.30898882768409019</v>
+        <v>0.38392874152549084</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16856,12 +16938,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -16874,7 +16956,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -16884,43 +16966,99 @@
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="320" t="s">
+    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B89" s="109" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B90" s="149" t="s">
+        <v>416</v>
+      </c>
+      <c r="C90" s="135">
+        <f>Thesis!E19</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B91" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C91" s="117">
+        <f>PV(C90, C76, -C77, 0)</f>
+        <v>6.5618942447874584</v>
+      </c>
+      <c r="D91" s="117"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B92" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C92" s="117">
+        <f>C60/(1+C90)^C76</f>
+        <v>39.642401523537714</v>
+      </c>
+      <c r="D92" s="117"/>
+    </row>
+    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B93" s="111" t="s">
+        <v>417</v>
+      </c>
+      <c r="C93" s="112">
+        <f>C91+C92</f>
+        <v>46.204295768325174</v>
+      </c>
+      <c r="D93" t="s">
+        <v>414</v>
+      </c>
+      <c r="E93" s="147" t="s">
+        <v>128</v>
+      </c>
+      <c r="F93" s="329">
+        <f>(1-C93/C60)</f>
+        <v>-5.2763730189843372E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="100"/>
+    </row>
+    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E95" s="320" t="s">
+        <v>336</v>
+      </c>
+      <c r="F95" s="317"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="316"/>
+    </row>
+    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E96" s="313" t="s">
         <v>337</v>
       </c>
-      <c r="F89" s="317"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="316"/>
-    </row>
-    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="313" t="s">
+      <c r="F96" s="318" t="s">
         <v>338</v>
       </c>
-      <c r="F90" s="318" t="s">
+      <c r="G96" s="2"/>
+      <c r="H96" s="316"/>
+    </row>
+    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E97" s="314" t="s">
+        <v>337</v>
+      </c>
+      <c r="F97" s="318" t="s">
         <v>339</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="316"/>
-    </row>
-    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="314" t="s">
-        <v>338</v>
-      </c>
-      <c r="F91" s="318" t="s">
+      <c r="G97" s="2"/>
+      <c r="H97" s="316"/>
+    </row>
+    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E98" s="315" t="s">
+        <v>337</v>
+      </c>
+      <c r="F98" s="319" t="s">
         <v>340</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="316"/>
-    </row>
-    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="315" t="s">
-        <v>338</v>
-      </c>
-      <c r="F92" s="319" t="s">
-        <v>341</v>
-      </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="316"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="316"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9474C67-4A32-4056-BE35-9615ADC615E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0F31F3-8395-41CB-B4BB-96CB4EFA2EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="426">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1357,10 +1357,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Stress Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rough Estimate only</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2333,31 +2329,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>@Cash Yield</t>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Sell Above</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Implied Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Sell)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sell Above:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 5: Determining the Investment Decision</t>
+    <t>Liabilities to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debt to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Est. Realizable Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt to EBIT Ratio = </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3032,7 +3044,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="352">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3764,6 +3776,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4040,7 +4057,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4060,10 +4077,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4092,13 +4109,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4125,7 +4142,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4162,7 +4179,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="337" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C12" s="337"/>
       <c r="D12" s="337"/>
@@ -4171,14 +4188,14 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4188,10 +4205,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4214,19 +4231,19 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
@@ -4238,11 +4255,11 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="252">
-        <f>C129</f>
+        <f>C133</f>
         <v>27.038487197680578</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4250,7 +4267,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4265,7 +4282,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4275,7 +4292,7 @@
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="337" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C25" s="337"/>
       <c r="D25" s="337"/>
@@ -4284,7 +4301,7 @@
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="339" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C26" s="339"/>
       <c r="D26" s="339"/>
@@ -4394,7 +4411,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4409,7 +4426,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4477,7 +4494,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="338" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C50" s="341"/>
       <c r="D50" s="341"/>
@@ -4499,7 +4516,7 @@
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="337" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C53" s="337"/>
       <c r="D53" s="337"/>
@@ -4508,7 +4525,7 @@
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="337" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C54" s="337"/>
       <c r="D54" s="337"/>
@@ -4543,7 +4560,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4552,7 +4569,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4561,7 +4578,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4575,7 +4592,7 @@
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
       <c r="B63" s="337" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C63" s="337"/>
       <c r="D63" s="337"/>
@@ -4598,7 +4615,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4606,26 +4623,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4642,13 +4659,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="337" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C73" s="337"/>
       <c r="D73" s="337"/>
@@ -4657,7 +4674,7 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="337" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C74" s="337"/>
       <c r="D74" s="337"/>
@@ -4674,7 +4691,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4687,7 +4704,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4700,7 +4717,7 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="337" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C81" s="337"/>
       <c r="D81" s="337"/>
@@ -4719,7 +4736,7 @@
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="337" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C85" s="337"/>
       <c r="D85" s="337"/>
@@ -4741,7 +4758,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4752,548 +4769,588 @@
         <v>HKD</v>
       </c>
     </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B88" s="349" t="s">
+        <v>422</v>
+      </c>
+      <c r="C88" s="350">
+        <f>BS!G30/BS!G27</f>
+        <v>0.72207550313588764</v>
+      </c>
+    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="349" t="s">
+        <v>423</v>
+      </c>
+      <c r="C89" s="350">
+        <f>BS!G31/BS!G27</f>
+        <v>9.5579625064196368E-3</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B90" s="349" t="s">
+        <v>425</v>
+      </c>
+      <c r="C90" s="351">
+        <f>BS!C50</f>
+        <v>6.3593933566061064E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="47" t="s">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B93" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C90" s="188">
+      <c r="C93" s="188">
         <f>BS!C66</f>
         <v>17978772896</v>
       </c>
-      <c r="D90" s="1" t="str">
+      <c r="D93" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B91" s="47" t="s">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B94" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
         <v>12838413003.943913</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B92" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*C28*Exchange_Rate/Common_Shares</f>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C95" s="248">
+        <f>C94*C28*Exchange_Rate/Common_Shares</f>
         <v>8.8481925866461335</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D95" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B98" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="C95" s="188">
+      <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
         <v>2755411575.5</v>
       </c>
-      <c r="D95" s="1" t="str">
+      <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B96" s="47" t="s">
-        <v>289</v>
-      </c>
-      <c r="C96" s="248">
-        <f>C95*C28*Exchange_Rate/Common_Shares</f>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B99" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C99" s="248">
+        <f>C98*C28*Exchange_Rate/Common_Shares</f>
         <v>1.899020717592468</v>
       </c>
-      <c r="D96" s="1" t="str">
+      <c r="D99" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="337" t="s">
-        <v>380</v>
-      </c>
-      <c r="C98" s="337"/>
-      <c r="D98" s="337"/>
-      <c r="E98" s="337"/>
-      <c r="F98" s="337"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B100" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C100" s="248">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="337" t="s">
+        <v>379</v>
+      </c>
+      <c r="C101" s="337"/>
+      <c r="D101" s="337"/>
+      <c r="E101" s="337"/>
+      <c r="F101" s="337"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B103" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
         <v>39.280813176084358</v>
       </c>
-      <c r="D100" s="1" t="str">
+      <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A102" s="247" t="s">
-        <v>372</v>
-      </c>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="36"/>
-      <c r="E102" s="36"/>
-      <c r="F102" s="36"/>
-    </row>
-    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="338" t="s">
-        <v>381</v>
-      </c>
-      <c r="C104" s="338"/>
-      <c r="D104" s="338"/>
-      <c r="E104" s="338"/>
-      <c r="F104" s="338"/>
-    </row>
-    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B106" s="260" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B104" s="349" t="s">
+        <v>424</v>
+      </c>
+      <c r="C104" s="248">
+        <f>BS!D47</f>
+        <v>1.1685753266721788</v>
+      </c>
+      <c r="D104" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A106" s="247" t="s">
+        <v>371</v>
+      </c>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+    </row>
+    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="338" t="s">
+        <v>380</v>
+      </c>
+      <c r="C108" s="338"/>
+      <c r="D108" s="338"/>
+      <c r="E108" s="338"/>
+      <c r="F108" s="338"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B110" s="260" t="s">
         <v>119</v>
       </c>
-      <c r="C106" s="260" t="s">
+      <c r="C110" s="260" t="s">
         <v>134</v>
       </c>
-      <c r="D106" s="260" t="s">
+      <c r="D110" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="E106" s="260" t="s">
+      <c r="E110" s="260" t="s">
         <v>261</v>
       </c>
-      <c r="F106" s="260" t="s">
+      <c r="F110" s="260" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="255" t="str">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C107" s="256">
+      <c r="C111" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D107" s="257">
+      <c r="D111" s="257">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E107" s="258" t="str">
+      <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>60.57 HKD</v>
       </c>
-      <c r="F107" s="259">
+      <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="242" t="str">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C108" s="243">
+      <c r="C112" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D108" s="244">
+      <c r="D112" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E108" s="245" t="str">
+      <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>45.43 HKD</v>
       </c>
-      <c r="F108" s="246">
+      <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="242" t="str">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C109" s="243">
+      <c r="C113" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.04</v>
       </c>
-      <c r="D109" s="244">
+      <c r="D113" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E109" s="245" t="str">
+      <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>43.18 HKD</v>
       </c>
-      <c r="F109" s="246">
+      <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="242" t="str">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C110" s="243">
+      <c r="C114" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D110" s="244">
+      <c r="D114" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E110" s="245" t="str">
+      <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>41.14 HKD</v>
       </c>
-      <c r="F110" s="246">
+      <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B111" s="242" t="str">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C111" s="243">
+      <c r="C115" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D111" s="244">
+      <c r="D115" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E111" s="245" t="str">
+      <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>39.28 HKD</v>
       </c>
-      <c r="F111" s="246">
+      <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B113" s="235" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B117" s="235" t="s">
         <v>260</v>
       </c>
-      <c r="C113" s="241">
+      <c r="C117" s="241">
         <f>Scenarios!C60</f>
         <v>43.888571047174302</v>
       </c>
-      <c r="D113" s="236" t="str">
+      <c r="D117" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
-        <v>384</v>
-      </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
-    </row>
-    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A117" s="247" t="s">
-        <v>422</v>
-      </c>
-      <c r="B117" s="36"/>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="340" t="s">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="342" t="s">
+        <v>383</v>
+      </c>
+      <c r="C119" s="342"/>
+      <c r="D119" s="342"/>
+      <c r="E119" s="342"/>
+      <c r="F119" s="342"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A121" s="247" t="s">
+        <v>420</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="340" t="s">
+        <v>381</v>
+      </c>
+      <c r="C123" s="340"/>
+      <c r="D123" s="340"/>
+      <c r="E123" s="340"/>
+      <c r="F123" s="340"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="337" t="s">
         <v>382</v>
       </c>
-      <c r="C119" s="340"/>
-      <c r="D119" s="340"/>
-      <c r="E119" s="340"/>
-      <c r="F119" s="340"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="337" t="s">
-        <v>383</v>
-      </c>
-      <c r="C120" s="337"/>
-      <c r="D120" s="337"/>
-      <c r="E120" s="337"/>
-      <c r="F120" s="337"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="234" t="s">
+      <c r="C124" s="337"/>
+      <c r="D124" s="337"/>
+      <c r="E124" s="337"/>
+      <c r="F124" s="337"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B125" s="234" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="1" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C122" s="251">
+      <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C123" s="250">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="236" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="236" t="s">
         <v>263</v>
       </c>
-      <c r="C124" s="237">
+      <c r="C128" s="237">
         <f>Scenarios!C77</f>
         <v>2.339927674962774</v>
       </c>
-      <c r="D124" s="236" t="str">
+      <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="234" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B130" s="234" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B131" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C127" s="240">
+      <c r="C131" s="240">
         <f>Scenarios!C81</f>
         <v>4.5675388215273349</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C128" s="240">
+      <c r="C132" s="240">
         <f>Scenarios!C82</f>
         <v>22.470948376153242</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B129" s="80" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="80" t="s">
         <v>262</v>
       </c>
-      <c r="C129" s="239">
+      <c r="C133" s="239">
         <f>Scenarios!C83</f>
         <v>27.038487197680578</v>
       </c>
-      <c r="D129" s="47" t="str">
+      <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B130" s="238" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C130" s="92">
+      <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.38392874152549084</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B132" s="234" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B133" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="234" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C133" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>6.5618942447874584</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>6.2866148239914477</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C134" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>39.642401523537714</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B135" s="80" t="s">
-        <v>421</v>
-      </c>
-      <c r="C135" s="239">
+        <v>37.137986975177412</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="80" t="s">
+        <v>419</v>
+      </c>
+      <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>46.204295768325174</v>
-      </c>
-      <c r="D135" s="101" t="str">
+        <v>43.424601799168862</v>
+      </c>
+      <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="238" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="92">
+      <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>-5.2763730189843372E-2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A138" s="247" t="s">
+        <v>1.0571527778991396E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A142" s="247" t="s">
+        <v>387</v>
+      </c>
+      <c r="B142" s="36"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="36"/>
+      <c r="E142" s="36"/>
+      <c r="F142" s="36"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="344" t="s">
+        <v>389</v>
+      </c>
+      <c r="C144" s="337"/>
+      <c r="D144" s="337"/>
+      <c r="E144" s="337"/>
+      <c r="F144" s="337"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="234" t="s">
         <v>388</v>
       </c>
-      <c r="B138" s="36"/>
-      <c r="C138" s="36"/>
-      <c r="D138" s="36"/>
-      <c r="E138" s="36"/>
-      <c r="F138" s="36"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="344" t="s">
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B147" s="341" t="s">
+        <v>393</v>
+      </c>
+      <c r="C147" s="341"/>
+      <c r="D147" s="341"/>
+      <c r="E147" s="341"/>
+      <c r="F147" s="341"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C140" s="337"/>
-      <c r="D140" s="337"/>
-      <c r="E140" s="337"/>
-      <c r="F140" s="337"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="234" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B143" s="341" t="s">
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="238" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="238" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="338" t="s">
         <v>394</v>
       </c>
-      <c r="C143" s="341"/>
-      <c r="D143" s="341"/>
-      <c r="E143" s="341"/>
-      <c r="F143" s="341"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="238" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="238" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B146" s="238" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B148" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="338" t="s">
-        <v>395</v>
-      </c>
-      <c r="C149" s="338"/>
-      <c r="D149" s="338"/>
-      <c r="E149" s="338"/>
-      <c r="F149" s="338"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="343" t="s">
-        <v>396</v>
-      </c>
-      <c r="C152" s="343"/>
-      <c r="D152" s="343"/>
-      <c r="E152" s="343"/>
-      <c r="F152" s="343"/>
-    </row>
-    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="343" t="s">
-        <v>397</v>
-      </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
+      <c r="C153" s="338"/>
+      <c r="D153" s="338"/>
+      <c r="E153" s="338"/>
+      <c r="F153" s="338"/>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B156" s="238" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B156" s="343" t="s">
+        <v>395</v>
+      </c>
+      <c r="C156" s="343"/>
+      <c r="D156" s="343"/>
+      <c r="E156" s="343"/>
+      <c r="F156" s="343"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="343" t="s">
+        <v>396</v>
+      </c>
+      <c r="C157" s="343"/>
+      <c r="D157" s="343"/>
+      <c r="E157" s="343"/>
+      <c r="F157" s="343"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B159" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B160" s="238" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B161" s="238" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B162" s="238" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B158" s="238" t="s">
-        <v>402</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
     <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B147:F147"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B25:F25"/>
@@ -5302,8 +5359,8 @@
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B123:F123"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
@@ -5707,7 +5764,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C22" s="181">
         <v>5154661132</v>
@@ -5725,7 +5782,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C23" s="181">
         <v>-7421783375</v>
@@ -5743,7 +5800,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C24" s="181">
         <v>-2983143705</v>
@@ -6999,7 +7056,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8377,7 +8434,7 @@
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>274</v>
+        <v>424</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8385,7 +8442,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8538,7 +8595,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8561,7 +8618,7 @@
         <v>2.749989365273205E-2</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8583,7 +8640,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8650,7 +8707,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8662,7 +8719,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8673,12 +8730,12 @@
         <v>-2570179946.0280437</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8689,12 +8746,12 @@
         <v>6.9951416918431715</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8702,12 +8759,12 @@
         <v>5140359892.0560875</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8715,7 +8772,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8791,7 +8848,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8802,15 +8859,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>299</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8827,7 +8884,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8861,7 +8918,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9732,7 +9789,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9757,7 +9814,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10085,7 +10142,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10145,7 +10202,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10269,7 +10326,7 @@
         <v>-1406578781</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10327,7 +10384,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10635,7 +10692,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10774,7 +10831,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10829,7 +10886,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -10962,7 +11019,7 @@
         <v>3.430552260533988E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10989,7 +11046,7 @@
         <v>7.6514823945754068E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11304,7 +11361,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11865,7 +11922,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12544,7 +12601,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13238,7 +13295,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13290,7 +13347,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13799,7 +13856,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -16024,7 +16081,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16096,7 +16153,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16150,7 +16207,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16163,7 +16220,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16243,7 +16300,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E11" s="347"/>
       <c r="F11" s="347"/>
@@ -16317,7 +16374,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16328,7 +16385,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="347" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F18" s="348"/>
     </row>
@@ -16338,14 +16395,14 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E20" s="348"/>
       <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16360,7 +16417,7 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16650,7 +16707,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16719,7 +16776,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16728,7 +16785,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16737,10 +16794,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16753,7 +16810,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16765,7 +16822,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16781,20 +16838,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16804,19 +16861,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16826,14 +16883,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16856,7 +16913,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -16879,15 +16936,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C123</f>
+        <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
@@ -16938,12 +16995,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -16956,7 +17013,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -16968,16 +17025,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B89" s="109" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B90" s="149" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C90" s="135">
-        <f>Thesis!E19</f>
-        <v>3.4500000000000003E-2</v>
+        <f>(Thesis!E19+Thesis!C67)/2</f>
+        <v>5.7250000000000002E-2</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.35">
@@ -16986,7 +17043,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>6.5618942447874584</v>
+        <v>6.2866148239914477</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -16996,27 +17053,27 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>39.642401523537714</v>
+        <v>37.137986975177412</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B93" s="111" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>46.204295768325174</v>
+        <v>43.424601799168862</v>
       </c>
       <c r="D93" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>128</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>-5.2763730189843372E-2</v>
+        <v>1.0571527778991396E-2</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.35">
@@ -17024,7 +17081,7 @@
     </row>
     <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E95" s="320" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
@@ -17032,30 +17089,30 @@
     </row>
     <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E96" s="313" t="s">
+        <v>336</v>
+      </c>
+      <c r="F96" s="318" t="s">
         <v>337</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>338</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
     <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E97" s="314" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
     <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E98" s="315" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/templates/Valuation_v2.1.xlsx
+++ b/financial_models/templates/Valuation_v2.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0F31F3-8395-41CB-B4BB-96CB4EFA2EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64005932-9CA8-462B-9D44-6D7A00EF2413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,6 +28,7 @@
     <definedName name="Market_currency">Thesis!$D$6</definedName>
     <definedName name="Market_Price">Thesis!$C$6</definedName>
     <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="428">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2372,32 +2373,38 @@
     <t xml:space="preserve">Debt to EBIT Ratio = </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Implied Return</t>
+  </si>
+  <si>
+    <t>Target Return</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="18">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="178" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.00\x"/>
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="181" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="182" formatCode="#,##0_ "/>
-    <numFmt numFmtId="183" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="184" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="185" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="186" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="187" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="188" formatCode="0.000_ "/>
-    <numFmt numFmtId="189" formatCode="#,##0_);\(#,##0\)"/>
-    <numFmt numFmtId="190" formatCode="#,##0.00_);\(#,##0.00\)"/>
-    <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="192" formatCode="0.0\x"/>
-    <numFmt numFmtId="193" formatCode="0\x"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0_);\(#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="180" formatCode="0.0\x"/>
+    <numFmt numFmtId="181" formatCode="0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3072,7 +3079,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3114,23 +3121,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3139,13 +3146,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3216,10 +3223,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3230,7 +3237,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3268,7 +3275,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3278,7 +3285,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3289,29 +3296,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="185" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3327,7 +3334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3341,38 +3348,38 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="39" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="186" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="187" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3392,17 +3399,17 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3417,11 +3424,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3430,51 +3437,51 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3490,7 +3497,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -3524,21 +3531,21 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3547,7 +3554,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3557,13 +3564,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3574,7 +3581,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3593,9 +3600,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3604,23 +3611,23 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="190" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="191" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3638,13 +3645,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="192" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3652,7 +3659,7 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3689,7 +3696,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3711,21 +3718,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="193" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3736,33 +3743,38 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3776,11 +3788,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4058,7 +4065,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
@@ -4068,7 +4075,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>42</v>
       </c>
@@ -4083,7 +4090,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="247" t="s">
         <v>269</v>
       </c>
@@ -4097,7 +4104,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="str">
         <f>D5&amp;" Stock Information"</f>
         <v>0168.HK Stock Information</v>
@@ -4107,7 +4114,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>325</v>
       </c>
@@ -4118,7 +4125,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>96</v>
       </c>
@@ -4130,7 +4137,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="B7" s="4" t="s">
         <v>0</v>
       </c>
@@ -4140,7 +4147,7 @@
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="B8" s="2" t="s">
         <v>316</v>
       </c>
@@ -4150,7 +4157,7 @@
       <c r="D8" s="5"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="B9" s="1" t="s">
         <v>270</v>
       </c>
@@ -4161,7 +4168,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="B10" s="4" t="str">
         <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
         <v>Capitalization (HKD):</v>
@@ -4173,27 +4180,27 @@
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="337" t="s">
+    <row r="12" spans="1:10" ht="24.4" customHeight="1">
+      <c r="B12" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C12" s="337"/>
-      <c r="D12" s="337"/>
-      <c r="E12" s="337"/>
-      <c r="F12" s="337"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
         <v>315</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="B15" s="2" t="s">
         <v>359</v>
       </c>
@@ -4203,7 +4210,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>358</v>
       </c>
@@ -4213,12 +4220,12 @@
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6">
       <c r="B17" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>0.94020000000000004</v>
+        <v>1.07</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4226,7 +4233,7 @@
       </c>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6">
       <c r="B18" s="2" t="s">
         <v>57</v>
       </c>
@@ -4235,7 +4242,7 @@
       </c>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
         <v>278</v>
       </c>
@@ -4249,14 +4256,14 @@
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6">
       <c r="B20" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>27.038487197680578</v>
+        <v>29.602894893931072</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>317</v>
@@ -4265,22 +4272,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
         <v>416</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>-2.5075247395360156E-2</v>
+        <v>8.761949902906796E-3</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6">
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="13.9">
       <c r="A23" s="247" t="s">
         <v>367</v>
       </c>
@@ -4290,43 +4297,43 @@
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
     </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="337" t="s">
+    <row r="25" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B25" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C25" s="337"/>
-      <c r="D25" s="337"/>
-      <c r="E25" s="337"/>
-      <c r="F25" s="337"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="339" t="s">
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
+    </row>
+    <row r="26" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B26" s="345" t="s">
         <v>350</v>
       </c>
-      <c r="C26" s="339"/>
-      <c r="D26" s="339"/>
-      <c r="E26" s="339"/>
-      <c r="F26" s="339"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
+    </row>
+    <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
         <v>232</v>
       </c>
       <c r="C28" s="108">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="338" t="s">
+    <row r="29" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B29" s="343" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="338"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
+    </row>
+    <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
         <v>234</v>
       </c>
@@ -4339,20 +4346,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6">
       <c r="B31" s="47"/>
       <c r="C31" s="76"/>
     </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="338" t="s">
+    <row r="32" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B32" s="343" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="338"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="338"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
+    </row>
+    <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
         <v>236</v>
       </c>
@@ -4365,7 +4372,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="52" t="s">
         <v>237</v>
       </c>
@@ -4378,16 +4385,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="338" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="343" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="338"/>
-      <c r="D36" s="338"/>
-      <c r="E36" s="338"/>
-      <c r="F36" s="338"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
         <v>239</v>
       </c>
@@ -4400,22 +4407,22 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="338" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
+    </row>
+    <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
         <v>351</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>176342732.47651258</v>
+        <v>174128704.21260402</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4424,7 +4431,7 @@
       <c r="E40" s="321"/>
       <c r="F40" s="321"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6">
       <c r="B41" s="47" t="s">
         <v>352</v>
       </c>
@@ -4439,25 +4446,25 @@
       <c r="E41" s="321"/>
       <c r="F41" s="321"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
         <v>240</v>
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>154505678.47651258</v>
+        <v>152291650.21260402</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6">
       <c r="B44" s="1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
         <v>267</v>
       </c>
@@ -4470,38 +4477,38 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="338" t="s">
+    <row r="47" spans="2:6">
+      <c r="B47" s="343" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
+    </row>
+    <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
         <v>241</v>
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-1160574563.8691282</v>
+        <v>-1160021056.8031509</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="338" t="s">
+    <row r="50" spans="1:6">
+      <c r="B50" s="343" t="s">
         <v>349</v>
       </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C50" s="344"/>
+      <c r="D50" s="344"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
+    </row>
+    <row r="51" spans="1:6">
       <c r="B51" s="47" t="s">
         <v>244</v>
       </c>
@@ -4514,69 +4521,69 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="337" t="s">
+    <row r="53" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B53" s="342" t="s">
         <v>354</v>
       </c>
-      <c r="C53" s="337"/>
-      <c r="D53" s="337"/>
-      <c r="E53" s="337"/>
-      <c r="F53" s="337"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="337" t="s">
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
+    </row>
+    <row r="54" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B54" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C54" s="337"/>
-      <c r="D54" s="337"/>
-      <c r="E54" s="337"/>
-      <c r="F54" s="337"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
+    </row>
+    <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
         <v>272</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3105789113.4765129</v>
+        <v>3103575085.2126045</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6">
       <c r="B57" s="47" t="s">
         <v>250</v>
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>3334930863.6073847</v>
+        <v>3333270342.4094524</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6">
       <c r="B58" s="254" t="s">
         <v>403</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.1980338459190879E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+        <v>4.7752176349463223E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="B59" s="254" t="s">
         <v>318</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.2738405022151121E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+        <v>3.755387701105279E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="13.9">
       <c r="A61" s="247" t="s">
         <v>368</v>
       </c>
@@ -4586,34 +4593,34 @@
       <c r="E61" s="36"/>
       <c r="F61" s="36"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6">
       <c r="A62" s="233"/>
     </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="337" t="s">
+      <c r="B63" s="342" t="s">
         <v>375</v>
       </c>
-      <c r="C63" s="337"/>
-      <c r="D63" s="337"/>
-      <c r="E63" s="337"/>
-      <c r="F63" s="337"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="339" t="s">
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="B64" s="345" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="339"/>
-      <c r="D64" s="339"/>
-      <c r="E64" s="339"/>
-      <c r="F64" s="339"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
+    </row>
+    <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6">
       <c r="B67" s="1" t="s">
         <v>290</v>
       </c>
@@ -4621,7 +4628,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6">
       <c r="B68" s="1" t="s">
         <v>292</v>
       </c>
@@ -4633,7 +4640,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6">
       <c r="B69" s="1" t="s">
         <v>291</v>
       </c>
@@ -4645,7 +4652,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6">
       <c r="B70" s="80" t="s">
         <v>249</v>
       </c>
@@ -4654,34 +4661,34 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6">
       <c r="C71" s="122"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6">
       <c r="B72" s="332" t="s">
         <v>369</v>
       </c>
       <c r="C72" s="122"/>
     </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="337" t="s">
+    <row r="73" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B73" s="342" t="s">
         <v>376</v>
       </c>
-      <c r="C73" s="337"/>
-      <c r="D73" s="337"/>
-      <c r="E73" s="337"/>
-      <c r="F73" s="337"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="337" t="s">
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B74" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C74" s="337"/>
-      <c r="D74" s="337"/>
-      <c r="E74" s="337"/>
-      <c r="F74" s="337"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
         <v>253</v>
       </c>
@@ -4689,20 +4696,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6">
       <c r="B77" s="47" t="s">
         <v>285</v>
       </c>
       <c r="C77" s="248">
-        <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>28.730294133008758</v>
+        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>32.680395689163895</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:6" ht="13.9">
       <c r="A79" s="247" t="s">
         <v>370</v>
       </c>
@@ -4712,38 +4719,38 @@
       <c r="E79" s="36"/>
       <c r="F79" s="36"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6">
       <c r="A80" s="233"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="337" t="s">
+    <row r="81" spans="2:6">
+      <c r="B81" s="342" t="s">
         <v>378</v>
       </c>
-      <c r="C81" s="337"/>
-      <c r="D81" s="337"/>
-      <c r="E81" s="337"/>
-      <c r="F81" s="337"/>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
+    </row>
+    <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:6">
       <c r="B84" s="234" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="337" t="s">
+    <row r="85" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B85" s="342" t="s">
         <v>355</v>
       </c>
-      <c r="C85" s="337"/>
-      <c r="D85" s="337"/>
-      <c r="E85" s="337"/>
-      <c r="F85" s="337"/>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
+    </row>
+    <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
         <v>257</v>
       </c>
@@ -4756,52 +4763,52 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:6">
       <c r="B87" s="47" t="s">
         <v>286</v>
       </c>
       <c r="C87" s="248">
-        <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.19669426116300168</v>
+        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.22384903152989977</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B88" s="349" t="s">
+    <row r="88" spans="2:6">
+      <c r="B88" s="337" t="s">
         <v>422</v>
       </c>
-      <c r="C88" s="350">
+      <c r="C88" s="338">
         <f>BS!G30/BS!G27</f>
         <v>0.72207550313588764</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="349" t="s">
+    <row r="89" spans="2:6">
+      <c r="B89" s="337" t="s">
         <v>423</v>
       </c>
-      <c r="C89" s="350">
+      <c r="C89" s="338">
         <f>BS!G31/BS!G27</f>
         <v>9.5579625064196368E-3</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="349" t="s">
+    <row r="90" spans="2:6">
+      <c r="B90" s="337" t="s">
         <v>425</v>
       </c>
-      <c r="C90" s="351">
+      <c r="C90" s="339">
         <f>BS!C50</f>
         <v>6.3593933566061064E-2</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:6">
       <c r="B92" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:6">
       <c r="B93" s="47" t="s">
         <v>266</v>
       </c>
@@ -4814,38 +4821,38 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:6">
       <c r="B94" s="47" t="s">
         <v>268</v>
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>12838413003.943913</v>
+        <v>12902951541.641745</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:6">
       <c r="B95" s="47" t="s">
         <v>287</v>
       </c>
       <c r="C95" s="248">
-        <f>C94*C28*Exchange_Rate/Common_Shares</f>
-        <v>8.8481925866461335</v>
+        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>10.120356733721225</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6">
       <c r="B97" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6">
       <c r="B98" s="47" t="s">
         <v>259</v>
       </c>
@@ -4858,55 +4865,55 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
         <v>288</v>
       </c>
       <c r="C99" s="248">
-        <f>C98*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.899020717592468</v>
+        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.161191414405383</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="337" t="s">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B101" s="342" t="s">
         <v>379</v>
       </c>
-      <c r="C101" s="337"/>
-      <c r="D101" s="337"/>
-      <c r="E101" s="337"/>
-      <c r="F101" s="337"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
+    </row>
+    <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
         <v>284</v>
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>39.280813176084358</v>
+        <v>44.738094805760603</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B104" s="349" t="s">
+    <row r="104" spans="1:6">
+      <c r="B104" s="337" t="s">
         <v>424</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>1.1685753266721788</v>
+        <v>1.3299038497545537</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:6" ht="13.9">
       <c r="A106" s="247" t="s">
         <v>371</v>
       </c>
@@ -4916,16 +4923,16 @@
       <c r="E106" s="36"/>
       <c r="F106" s="36"/>
     </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="338" t="s">
+    <row r="108" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B108" s="343" t="s">
         <v>380</v>
       </c>
-      <c r="C108" s="338"/>
-      <c r="D108" s="338"/>
-      <c r="E108" s="338"/>
-      <c r="F108" s="338"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
         <v>119</v>
       </c>
@@ -4942,7 +4949,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6">
       <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
@@ -4957,14 +4964,14 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>60.57 HKD</v>
+        <v>68.95 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6">
       <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
@@ -4979,14 +4986,14 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>45.43 HKD</v>
+        <v>51.73 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6">
       <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
@@ -5001,14 +5008,14 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>43.18 HKD</v>
+        <v>49.17 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6">
       <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
@@ -5023,14 +5030,14 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>41.14 HKD</v>
+        <v>46.85 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6">
       <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
@@ -5045,36 +5052,36 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>39.28 HKD</v>
+        <v>44.74 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6">
       <c r="B117" s="235" t="s">
         <v>260</v>
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>43.888571047174302</v>
+        <v>49.979369042980153</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="342" t="s">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B119" s="346" t="s">
         <v>383</v>
       </c>
-      <c r="C119" s="342"/>
-      <c r="D119" s="342"/>
-      <c r="E119" s="342"/>
-      <c r="F119" s="342"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
         <v>420</v>
       </c>
@@ -5084,30 +5091,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="340" t="s">
+    <row r="123" spans="1:6">
+      <c r="B123" s="347" t="s">
         <v>381</v>
       </c>
-      <c r="C123" s="340"/>
-      <c r="D123" s="340"/>
-      <c r="E123" s="340"/>
-      <c r="F123" s="340"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="337" t="s">
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="342" t="s">
         <v>382</v>
       </c>
-      <c r="C124" s="337"/>
-      <c r="D124" s="337"/>
-      <c r="E124" s="337"/>
-      <c r="F124" s="337"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
+    </row>
+    <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6">
       <c r="B126" s="1" t="s">
         <v>265</v>
       </c>
@@ -5116,7 +5123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6">
       <c r="B127" s="1" t="s">
         <v>279</v>
       </c>
@@ -5125,114 +5132,128 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6">
       <c r="B128" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>2.339927674962774</v>
+        <v>2.0560747663551404</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C130" s="338">
+        <f>C19</f>
+        <v>0.25</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>4.5675388215273349</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+        <v>4.0134579439252347</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>22.470948376153242</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+        <v>25.589436950005837</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
       <c r="B133" s="80" t="s">
         <v>262</v>
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>27.038487197680578</v>
+        <v>29.602894893931072</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6">
       <c r="B134" s="238" t="s">
         <v>264</v>
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.38392874152549084</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0.40769770685832729</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C136" s="92">
+        <f>Scenarios!C90</f>
+        <v>0.06</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>6.2866148239914477</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+        <v>5.4959124194538393</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>37.137986975177412</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+        <v>41.963642002273808</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
         <v>419</v>
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>43.424601799168862</v>
+        <v>47.459554421727645</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6">
       <c r="B140" s="238" t="s">
         <v>264</v>
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>1.0571527778991396E-2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+        <v>5.0417095483649921E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9">
       <c r="A142" s="247" t="s">
         <v>387</v>
       </c>
@@ -5242,114 +5263,103 @@
       <c r="E142" s="36"/>
       <c r="F142" s="36"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="344" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C144" s="337"/>
-      <c r="D144" s="337"/>
-      <c r="E144" s="337"/>
-      <c r="F144" s="337"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
+    </row>
+    <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B147" s="341" t="s">
+    <row r="147" spans="2:6">
+      <c r="B147" s="344" t="s">
         <v>393</v>
       </c>
-      <c r="C147" s="341"/>
-      <c r="D147" s="341"/>
-      <c r="E147" s="341"/>
-      <c r="F147" s="341"/>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C147" s="344"/>
+      <c r="D147" s="344"/>
+      <c r="E147" s="344"/>
+      <c r="F147" s="344"/>
+    </row>
+    <row r="148" spans="2:6">
       <c r="B148" s="238" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:6">
       <c r="B149" s="238" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:6">
       <c r="B150" s="238" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:6">
       <c r="B152" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="338" t="s">
+    <row r="153" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B153" s="343" t="s">
         <v>394</v>
       </c>
-      <c r="C153" s="338"/>
-      <c r="D153" s="338"/>
-      <c r="E153" s="338"/>
-      <c r="F153" s="338"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
+    </row>
+    <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B156" s="343" t="s">
+    <row r="156" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B156" s="340" t="s">
         <v>395</v>
       </c>
-      <c r="C156" s="343"/>
-      <c r="D156" s="343"/>
-      <c r="E156" s="343"/>
-      <c r="F156" s="343"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="343" t="s">
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B157" s="340" t="s">
         <v>396</v>
       </c>
-      <c r="C157" s="343"/>
-      <c r="D157" s="343"/>
-      <c r="E157" s="343"/>
-      <c r="F157" s="343"/>
-    </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
+    </row>
+    <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:6">
       <c r="B160" s="238" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="161" spans="2:2">
       <c r="B161" s="238" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="162" spans="2:2">
       <c r="B162" s="238" t="s">
         <v>401</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5366,6 +5376,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5390,7 +5411,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
@@ -5398,7 +5419,7 @@
     <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
         <v>CNY</v>
@@ -5447,7 +5468,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>99</v>
       </c>
@@ -5463,7 +5484,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5471,7 +5492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5489,7 +5510,7 @@
       <c r="L4" s="181"/>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>44</v>
       </c>
@@ -5508,7 +5529,7 @@
       <c r="L5" s="181"/>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>55</v>
       </c>
@@ -5527,7 +5548,7 @@
       <c r="L6" s="181"/>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>62</v>
       </c>
@@ -5545,7 +5566,7 @@
       <c r="L7" s="189"/>
       <c r="M7" s="189"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>50</v>
       </c>
@@ -5563,7 +5584,7 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>161</v>
       </c>
@@ -5579,7 +5600,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>169</v>
       </c>
@@ -5595,7 +5616,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>160</v>
       </c>
@@ -5611,7 +5632,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -5629,7 +5650,7 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>68</v>
       </c>
@@ -5647,7 +5668,7 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>51</v>
       </c>
@@ -5665,7 +5686,7 @@
       <c r="L14" s="181"/>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>43</v>
       </c>
@@ -5683,7 +5704,7 @@
       <c r="L15" s="182"/>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>45</v>
       </c>
@@ -5701,13 +5722,13 @@
       <c r="L16" s="181"/>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>48</v>
       </c>
@@ -5725,7 +5746,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>54</v>
       </c>
@@ -5744,7 +5765,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>53</v>
       </c>
@@ -5762,7 +5783,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>384</v>
       </c>
@@ -5780,7 +5801,7 @@
       <c r="L22" s="181"/>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>386</v>
       </c>
@@ -5798,7 +5819,7 @@
       <c r="L23" s="181"/>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>385</v>
       </c>
@@ -5816,14 +5837,14 @@
       <c r="L24" s="181"/>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.339927674962774</v>
+        <v>2.0560747663551404</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -5836,7 +5857,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -5844,7 +5865,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -5863,7 +5884,7 @@
       <c r="L28" s="181"/>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -5882,7 +5903,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -5901,7 +5922,7 @@
       <c r="L30" s="182"/>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -5920,7 +5941,7 @@
       <c r="L31" s="182"/>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>174</v>
       </c>
@@ -5939,7 +5960,7 @@
       <c r="L32" s="182"/>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>83</v>
       </c>
@@ -5955,12 +5976,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6009,7 +6030,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>44</v>
       </c>
@@ -6058,7 +6079,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>59</v>
       </c>
@@ -6107,7 +6128,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>55</v>
       </c>
@@ -6156,7 +6177,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>62</v>
       </c>
@@ -6205,7 +6226,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>65</v>
       </c>
@@ -6254,7 +6275,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>50</v>
       </c>
@@ -6303,7 +6324,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>154</v>
       </c>
@@ -6352,7 +6373,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>170</v>
       </c>
@@ -6401,7 +6422,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>69</v>
       </c>
@@ -6450,7 +6471,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>51</v>
       </c>
@@ -6499,7 +6520,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>43</v>
       </c>
@@ -6548,7 +6569,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>45</v>
       </c>
@@ -6597,12 +6618,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -6651,7 +6672,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>68</v>
       </c>
@@ -6700,12 +6721,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>161</v>
       </c>
@@ -6754,7 +6775,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>169</v>
       </c>
@@ -6803,7 +6824,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>160</v>
       </c>
@@ -6852,7 +6873,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>162</v>
       </c>
@@ -6901,13 +6922,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>52</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>48</v>
       </c>
@@ -6956,7 +6977,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>54</v>
       </c>
@@ -7005,7 +7026,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>53</v>
       </c>
@@ -7054,7 +7075,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>407</v>
       </c>
@@ -7103,13 +7124,13 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.339927674962774</v>
+        <v>2.0560747663551404</v>
       </c>
       <c r="D65" s="73" t="str">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -7152,12 +7173,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7207,7 +7228,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>59</v>
       </c>
@@ -7256,7 +7277,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -7306,7 +7327,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>170</v>
       </c>
@@ -7355,7 +7376,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -7405,7 +7426,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>84</v>
       </c>
@@ -7421,13 +7442,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -7476,7 +7497,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>87</v>
       </c>
@@ -7510,7 +7531,7 @@
       <c r="L77" s="335"/>
       <c r="M77" s="335"/>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>88</v>
       </c>
@@ -7544,7 +7565,7 @@
       <c r="L78" s="335"/>
       <c r="M78" s="335"/>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -7593,7 +7614,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -7674,7 +7695,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -7685,7 +7706,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -7697,11 +7718,11 @@
         <v>Quarter Report</v>
       </c>
       <c r="H1" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>158</v>
       </c>
@@ -7712,7 +7733,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>186</v>
       </c>
@@ -7732,7 +7753,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -7754,7 +7775,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -7775,7 +7796,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -7796,7 +7817,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>70</v>
       </c>
@@ -7817,7 +7838,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>175</v>
       </c>
@@ -7838,7 +7859,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -7859,7 +7880,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -7871,7 +7892,7 @@
       </c>
       <c r="H10" s="295"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7884,7 +7905,7 @@
       </c>
       <c r="H11" s="295"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>73</v>
       </c>
@@ -7908,12 +7929,12 @@
         <v>17393978059.799999</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>185</v>
       </c>
@@ -7933,7 +7954,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>74</v>
       </c>
@@ -7953,7 +7974,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -7973,7 +7994,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>70</v>
       </c>
@@ -7993,7 +8014,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>175</v>
       </c>
@@ -8013,7 +8034,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8034,7 +8055,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8054,7 +8075,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8074,7 +8095,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8086,7 +8107,7 @@
       </c>
       <c r="H22" s="295"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8099,7 +8120,7 @@
       </c>
       <c r="H23" s="295"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>75</v>
       </c>
@@ -8123,7 +8144,7 @@
         <v>1542329122.0999999</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>202</v>
       </c>
@@ -8140,7 +8161,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8159,7 +8180,7 @@
         <v>2494718755.1999969</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8174,7 +8195,7 @@
       </c>
       <c r="H28" s="209"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8193,7 +8214,7 @@
         <v>1695561271.1999969</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8209,7 +8230,7 @@
       </c>
       <c r="H30" s="209"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>205</v>
       </c>
@@ -8226,7 +8247,7 @@
       </c>
       <c r="H31" s="209"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -8246,7 +8267,7 @@
         <v>24055562576.199997</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -8257,7 +8278,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="216"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="217" t="s">
@@ -8270,7 +8291,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>203</v>
       </c>
@@ -8289,7 +8310,7 @@
         <v>5119255394.3000002</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -8305,7 +8326,7 @@
       </c>
       <c r="H36" s="216"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -8321,7 +8342,7 @@
       </c>
       <c r="H37" s="216"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -8337,7 +8358,7 @@
       </c>
       <c r="H38" s="216"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -8356,7 +8377,7 @@
         <v>1264990032.7</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>206</v>
       </c>
@@ -8376,7 +8397,7 @@
         <v>18936307181.899998</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -8396,7 +8417,7 @@
         <v>16180895606.399998</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -8415,7 +8436,7 @@
         <v>2755411575.5</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>98</v>
       </c>
@@ -8426,7 +8447,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>273</v>
       </c>
@@ -8440,7 +8461,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>275</v>
       </c>
@@ -8454,25 +8475,25 @@
       </c>
       <c r="F46" s="283"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>20.02832272632898</v>
+        <v>22.793347497523943</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.1685753266721788</v>
+        <v>1.3299038497545537</v>
       </c>
       <c r="F47" s="283"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="283"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>145</v>
       </c>
@@ -8485,7 +8506,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="283"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>95</v>
       </c>
@@ -8499,7 +8520,7 @@
       </c>
       <c r="F50" s="283"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>178</v>
       </c>
@@ -8510,10 +8531,10 @@
       </c>
       <c r="F51" s="283"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="283"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>144</v>
       </c>
@@ -8525,7 +8546,7 @@
       </c>
       <c r="F53" s="283"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>141</v>
       </c>
@@ -8539,7 +8560,7 @@
       </c>
       <c r="F54" s="283"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>143</v>
       </c>
@@ -8553,10 +8574,10 @@
       </c>
       <c r="F55" s="283"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="283"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>177</v>
       </c>
@@ -8568,7 +8589,7 @@
       </c>
       <c r="F57" s="283"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>91</v>
       </c>
@@ -8579,7 +8600,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>94</v>
       </c>
@@ -8590,10 +8611,10 @@
       </c>
       <c r="F59" s="283"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="283"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>276</v>
       </c>
@@ -8605,7 +8626,7 @@
       </c>
       <c r="F61" s="283"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>247</v>
       </c>
@@ -8621,7 +8642,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>195</v>
       </c>
@@ -8632,7 +8653,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>190</v>
       </c>
@@ -8646,7 +8667,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>189</v>
       </c>
@@ -8656,13 +8677,13 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>12838413003.943913</v>
+        <v>12902951541.641745</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>179</v>
       </c>
@@ -8672,7 +8693,7 @@
       </c>
       <c r="F67" s="283"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>183</v>
       </c>
@@ -8682,7 +8703,7 @@
       </c>
       <c r="F68" s="283"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>181</v>
       </c>
@@ -8692,7 +8713,7 @@
       </c>
       <c r="F69" s="283"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>190</v>
       </c>
@@ -8702,10 +8723,10 @@
       </c>
       <c r="F70" s="283"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="283"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="285" t="s">
         <v>328</v>
       </c>
@@ -8717,52 +8738,52 @@
       </c>
       <c r="F72" s="283"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>327</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2570179946.0280437</v>
+        <v>-2537910677.1791277</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2570179946.0280437</v>
+        <v>-2537910677.1791277</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="288" t="s">
         <v>332</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>6.9951416918431715</v>
+        <v>7.0840841869120847</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.9951416918431715</v>
+        <v>7.0840841869120847</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>330</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5140359892.0560875</v>
+        <v>5075821354.3582554</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="290" t="s">
         <v>333</v>
       </c>
@@ -8775,10 +8796,10 @@
         <v>334</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="283"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>191</v>
       </c>
@@ -8790,7 +8811,7 @@
       </c>
       <c r="F78" s="283"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>180</v>
       </c>
@@ -8804,7 +8825,7 @@
       </c>
       <c r="F79" s="283"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>184</v>
       </c>
@@ -8818,7 +8839,7 @@
       </c>
       <c r="F80" s="283"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>182</v>
       </c>
@@ -8832,7 +8853,7 @@
       </c>
       <c r="F81" s="283"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>191</v>
       </c>
@@ -8846,7 +8867,7 @@
       </c>
       <c r="F82" s="283"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>297</v>
       </c>
@@ -8857,7 +8878,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>298</v>
       </c>
@@ -8865,68 +8886,68 @@
         <v>299</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="267" t="s">
         <v>295</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-268329679.29660001</v>
+        <v>-305374129.81</v>
       </c>
       <c r="D86" s="248">
-        <f>C86*$H$1/Common_Shares</f>
-        <v>-0.19669426116300168</v>
+        <f>C86*scaling_factor/Common_Shares</f>
+        <v>-0.22384903152989977</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="267" t="s">
         <v>296</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>12070675906.308067</v>
+        <v>13806158149.556667</v>
       </c>
       <c r="D87" s="248">
-        <f>C87*$H$1/Common_Shares</f>
-        <v>8.8481925866461335</v>
+        <f>C87*scaling_factor/Common_Shares</f>
+        <v>10.120356733721225</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="268" t="s">
         <v>191</v>
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2590637963.2851</v>
+        <v>2948290385.7850003</v>
       </c>
       <c r="D88" s="248">
-        <f>C88*$H$1/Common_Shares</f>
-        <v>1.899020717592468</v>
+        <f>C88*scaling_factor/Common_Shares</f>
+        <v>2.161191414405383</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>300</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>14392984190.296566</v>
+        <v>16449074405.531668</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>10.5505190430756</v>
+        <v>12.057699116596709</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -8947,7 +8968,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
@@ -8959,7 +8980,7 @@
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
@@ -9016,7 +9037,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>101</v>
@@ -9039,13 +9060,13 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>67</v>
       </c>
       <c r="C3" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="D3" s="9"/>
@@ -9053,7 +9074,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9110,7 +9131,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>47</v>
@@ -9165,7 +9186,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>49</v>
@@ -9220,7 +9241,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>46</v>
@@ -9275,7 +9296,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>154</v>
@@ -9332,7 +9353,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>66</v>
@@ -9387,7 +9408,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>82</v>
@@ -9442,7 +9463,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>196</v>
@@ -9499,19 +9520,19 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>154505678.47651258</v>
+        <v>152291650.21260402</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>154505678.47651258</v>
+        <v>152291650.21260405</v>
       </c>
       <c r="H12" s="191" t="str">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
@@ -9554,19 +9575,19 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>166</v>
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>4642298255.4765129</v>
+        <v>4640084227.2126036</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4642298255.4765129</v>
+        <v>4640084227.2126045</v>
       </c>
       <c r="H13" s="184" t="str">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
@@ -9609,14 +9630,14 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1160574563.8691282</v>
+        <v>-1160021056.8031509</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9664,7 +9685,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>245</v>
@@ -9721,21 +9742,21 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>156</v>
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>3334930863.6073847</v>
+        <v>3333270342.4094524</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3105789113.4765129</v>
+        <v>3103575085.2126045</v>
       </c>
       <c r="H16" s="184" t="str">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
@@ -9778,7 +9799,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>53</v>
@@ -9804,7 +9825,7 @@
       <c r="P17" s="195"/>
       <c r="Q17" s="195"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>100</v>
@@ -9829,21 +9850,21 @@
       <c r="P18" s="196"/>
       <c r="Q18" s="196"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>67</v>
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>3334930863.6073847</v>
+        <v>3333270342.4094524</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3105789113.4765129</v>
+        <v>3103575085.2126045</v>
       </c>
       <c r="H19" s="186" t="str">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
@@ -9886,7 +9907,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -9905,7 +9926,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>207</v>
@@ -9928,7 +9949,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>47</v>
@@ -9949,7 +9970,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>44</v>
@@ -10006,7 +10027,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>63</v>
@@ -10063,7 +10084,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>47</v>
@@ -10120,18 +10141,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="302"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E27" s="302"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>44</v>
@@ -10190,7 +10211,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -10250,7 +10271,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>47</v>
@@ -10305,18 +10326,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="302"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>46</v>
       </c>
       <c r="E32" s="302"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>176</v>
@@ -10373,7 +10394,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>50</v>
@@ -10432,7 +10453,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>46</v>
@@ -10489,18 +10510,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="302"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E37" s="302"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -10558,7 +10579,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -10616,7 +10637,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>46</v>
@@ -10671,18 +10692,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="302"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>210</v>
       </c>
       <c r="E42" s="302"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>173</v>
@@ -10697,7 +10718,7 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29935954941295589</v>
+        <v>0.2995023896009818</v>
       </c>
       <c r="H43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10740,10 +10761,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>211</v>
@@ -10766,14 +10787,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>61</v>
       </c>
       <c r="E46" s="302"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -10828,19 +10849,19 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>356</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>176342732.47651258</v>
+        <v>174128704.21260402</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>176342732.47651258</v>
+        <v>174128704.21260405</v>
       </c>
       <c r="H48" s="328" t="str">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
@@ -10883,7 +10904,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
         <v>353</v>
@@ -10940,19 +10961,19 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>69</v>
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>154505678.47651258</v>
+        <v>152291650.21260402</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>154505678.47651258</v>
+        <v>152291650.21260405</v>
       </c>
       <c r="H50" s="184" t="str">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
@@ -10995,11 +11016,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="302"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>157</v>
@@ -11009,7 +11030,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>90</v>
@@ -11036,7 +11057,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>89</v>
@@ -11063,7 +11084,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>92</v>
@@ -11118,11 +11139,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="302"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>170</v>
@@ -11132,7 +11153,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>169</v>
@@ -11187,7 +11208,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>161</v>
@@ -11242,7 +11263,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>160</v>
@@ -11297,7 +11318,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>196</v>
@@ -11352,7 +11373,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>162</v>
@@ -11408,7 +11429,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>197</v>
@@ -11463,11 +11484,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="302"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>171</v>
@@ -11477,7 +11498,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>169</v>
@@ -11502,7 +11523,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>159</v>
@@ -11527,7 +11548,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>160</v>
@@ -11552,7 +11573,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>196</v>
@@ -11579,10 +11600,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>214</v>
@@ -11605,7 +11626,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>218</v>
@@ -11626,7 +11647,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>47</v>
@@ -11683,7 +11704,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>49</v>
@@ -11740,7 +11761,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>46</v>
@@ -11797,7 +11818,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>154</v>
@@ -11854,7 +11875,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>66</v>
@@ -11911,7 +11932,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>82</v>
@@ -11970,7 +11991,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>155</v>
@@ -12027,21 +12048,21 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.8075952216708323E-3</v>
+        <v>4.7387035679324931E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.8075952216708323E-3</v>
+        <v>4.7387035679324939E-3</v>
       </c>
       <c r="H80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12084,21 +12105,21 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>166</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.14444964826320264</v>
+        <v>0.14438075660946428</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14444964826320264</v>
+        <v>0.14438075660946431</v>
       </c>
       <c r="H81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12141,14 +12162,14 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.611241206580066E-2</v>
+        <v>3.6095189152366071E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12198,7 +12219,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -12256,21 +12277,21 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>156</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>0.10376963385794732</v>
+        <v>0.10371796511764354</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.6639664306815684E-2</v>
+        <v>9.6570772653077341E-2</v>
       </c>
       <c r="H84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12313,7 +12334,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>53</v>
@@ -12339,7 +12360,7 @@
       <c r="P85" s="253"/>
       <c r="Q85" s="253"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>100</v>
@@ -12363,21 +12384,21 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>142</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>0.10376963385794732</v>
+        <v>0.10371796511764354</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.6639664306815684E-2</v>
+        <v>9.6570772653077341E-2</v>
       </c>
       <c r="H87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12420,18 +12441,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="302"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>216</v>
       </c>
       <c r="E89" s="302"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -12439,12 +12460,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.339927674962774</v>
+        <v>2.0560747663551404</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.339927674962774</v>
+        <v>2.0560747663551404</v>
       </c>
       <c r="H90" s="113" t="str">
         <f>Data!D65</f>
@@ -12487,177 +12508,177 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
         <v>Dividend (HKD)</v>
       </c>
       <c r="C91" s="74">
-        <f>C90*Common_Shares/$C$3</f>
-        <v>3192121818.3365245</v>
+        <f>C90*Common_Shares/scaling_factor</f>
+        <v>2804890592.1495328</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
-        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>3192121818.3365245</v>
+        <f>IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
+        <v>2804890592.1495328</v>
       </c>
       <c r="H91" s="74" t="str">
-        <f t="shared" si="37"/>
+        <f>IF(H$4="","",H90*Common_Shares/scaling_factor)</f>
         <v/>
       </c>
       <c r="I91" s="74" t="str">
-        <f t="shared" si="37"/>
+        <f>IF(I$4="","",I90*Common_Shares/scaling_factor)</f>
         <v/>
       </c>
       <c r="J91" s="74" t="str">
-        <f t="shared" si="37"/>
+        <f>IF(J$4="","",J90*Common_Shares/scaling_factor)</f>
         <v/>
       </c>
       <c r="K91" s="74" t="str">
-        <f t="shared" si="37"/>
+        <f>IF(K$4="","",K90*Common_Shares/scaling_factor)</f>
         <v/>
       </c>
       <c r="L91" s="74" t="str">
-        <f t="shared" si="37"/>
+        <f>IF(L$4="","",L90*Common_Shares/scaling_factor)</f>
         <v/>
       </c>
       <c r="M91" s="74" t="str">
-        <f t="shared" si="37"/>
+        <f>IF(M$4="","",M90*Common_Shares/scaling_factor)</f>
         <v/>
       </c>
       <c r="N91" s="74" t="str">
-        <f t="shared" si="37"/>
+        <f>IF(N$4="","",N90*Common_Shares/scaling_factor)</f>
         <v/>
       </c>
       <c r="O91" s="74" t="str">
-        <f t="shared" si="37"/>
+        <f>IF(O$4="","",O90*Common_Shares/scaling_factor)</f>
         <v/>
       </c>
       <c r="P91" s="74" t="str">
-        <f t="shared" si="37"/>
+        <f>IF(P$4="","",P90*Common_Shares/scaling_factor)</f>
         <v/>
       </c>
       <c r="Q91" s="74" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f>IF(Q$4="","",Q90*Common_Shares/scaling_factor)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>215</v>
       </c>
       <c r="C92" s="23">
-        <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.95717780934253482</v>
+        <f>C90/(C19*scaling_factor/Common_Shares)</f>
+        <v>0.84148307938384004</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
-        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>1.0277973493066221</v>
+        <f>IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
+        <v>0.9037611512973559</v>
       </c>
       <c r="H92" s="171" t="str">
-        <f t="shared" si="38"/>
+        <f>IF(H$4="","",H90/(H19*scaling_factor/Common_Shares))</f>
         <v/>
       </c>
       <c r="I92" s="171" t="str">
-        <f t="shared" si="38"/>
+        <f>IF(I$4="","",I90/(I19*scaling_factor/Common_Shares))</f>
         <v/>
       </c>
       <c r="J92" s="171" t="str">
-        <f t="shared" si="38"/>
+        <f>IF(J$4="","",J90/(J19*scaling_factor/Common_Shares))</f>
         <v/>
       </c>
       <c r="K92" s="171" t="str">
-        <f t="shared" si="38"/>
+        <f>IF(K$4="","",K90/(K19*scaling_factor/Common_Shares))</f>
         <v/>
       </c>
       <c r="L92" s="171" t="str">
-        <f t="shared" si="38"/>
+        <f>IF(L$4="","",L90/(L19*scaling_factor/Common_Shares))</f>
         <v/>
       </c>
       <c r="M92" s="171" t="str">
-        <f t="shared" si="38"/>
+        <f>IF(M$4="","",M90/(M19*scaling_factor/Common_Shares))</f>
         <v/>
       </c>
       <c r="N92" s="171" t="str">
-        <f t="shared" si="38"/>
+        <f>IF(N$4="","",N90/(N19*scaling_factor/Common_Shares))</f>
         <v/>
       </c>
       <c r="O92" s="171" t="str">
-        <f t="shared" si="38"/>
+        <f>IF(O$4="","",O90/(O19*scaling_factor/Common_Shares))</f>
         <v/>
       </c>
       <c r="P92" s="171" t="str">
-        <f t="shared" si="38"/>
+        <f>IF(P$4="","",P90/(P19*scaling_factor/Common_Shares))</f>
         <v/>
       </c>
       <c r="Q92" s="171" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f>IF(Q$4="","",Q90/(Q19*scaling_factor/Common_Shares))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>319</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.2738405022151121E-2</v>
+        <v>3.755387701105279E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.2738405022151121E-2</v>
+        <f t="shared" ref="G93:Q93" si="37">IF(G$4="","",G90/Market_Price)</f>
+        <v>3.755387701105279E-2</v>
       </c>
       <c r="H93" s="23" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="I93" s="23" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="J93" s="23" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K93" s="23" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="L93" s="23" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="M93" s="23" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N93" s="23" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="O93" s="23" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="P93" s="23" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="Q93" s="23" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="302"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>86</v>
@@ -12678,7 +12699,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>146</v>
@@ -12691,51 +12712,51 @@
       <c r="E96" s="299"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6" t="str">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
+        <f t="shared" ref="G96:Q96" si="38">IF(H4="","",G4/H4-1)</f>
         <v/>
       </c>
       <c r="H96" s="6" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="I96" s="6" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J96" s="6" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="K96" s="6" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="L96" s="6" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="M96" s="6" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="N96" s="6" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O96" s="6" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-    </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>166</v>
@@ -12748,54 +12769,54 @@
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6" t="str">
-        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G97:Q97" si="39">IF(H5="","",G13/H13-1)</f>
         <v/>
       </c>
       <c r="H97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="I97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="J97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="L97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="M97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="O97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Q97" s="6" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>217</v>
@@ -12818,7 +12839,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -12828,7 +12849,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -12841,51 +12862,51 @@
       <c r="E101" s="303"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
-        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
+        <f t="shared" ref="G101:Q101" si="40">IF(G$4="","",G105+G104)</f>
         <v>51420385832</v>
       </c>
       <c r="H101" s="183" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="I101" s="183" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J101" s="183" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="K101" s="183" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="L101" s="183" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="M101" s="183" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="N101" s="183" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="O101" s="183" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="P101" s="183" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="Q101" s="183" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>212</v>
@@ -12942,7 +12963,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>213</v>
@@ -12999,7 +13020,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13056,7 +13077,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13113,11 +13134,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="302"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>222</v>
@@ -13140,7 +13161,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>219</v>
@@ -13153,51 +13174,51 @@
       <c r="E108" s="303"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94" t="e">
-        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
+        <f t="shared" ref="G108:Q108" si="41">IF(G$4="","",G102/G$4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="H108" s="94" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="I108" s="94" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="J108" s="94" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K108" s="94" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="L108" s="94" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="M108" s="94" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="N108" s="94" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="O108" s="94" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="P108" s="94" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="Q108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>220</v>
@@ -13210,51 +13231,51 @@
       <c r="E109" s="303"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94" t="e">
-        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
+        <f t="shared" ref="G109:Q109" si="42">IF(G$4="","",G103/G$4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="H109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="I109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="K109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="L109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="M109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="N109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="O109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="P109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="Q109" s="94" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-    </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>70</v>
@@ -13281,18 +13302,18 @@
       <c r="P110" s="225"/>
       <c r="Q110" s="225"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="302"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>52</v>
       </c>
       <c r="E112" s="302"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>405</v>
@@ -13344,7 +13365,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>406</v>
@@ -13353,7 +13374,7 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6596945071489579</v>
+        <v>1.6608784999467443</v>
       </c>
       <c r="H114" s="334" t="str">
         <f>IF(H$4="","",Data!D$22/H19)</f>
@@ -13396,11 +13417,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="302"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -13454,62 +13475,62 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>223</v>
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.14444964826320264</v>
+        <v>0.14438075660946428</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14444964826320264</v>
+        <f t="shared" ref="G117:Q117" si="43">G81</f>
+        <v>0.14438075660946431</v>
       </c>
       <c r="H117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="I117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="J117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="L117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="M117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="N117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="O117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="P117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Q117" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>85</v>
       </c>
@@ -13519,51 +13540,51 @@
       </c>
       <c r="E118" s="302"/>
       <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
+        <f t="shared" ref="G118:Q118" si="44">IF(G4="","",G4/G101)</f>
         <v>0.62500173016982585</v>
       </c>
       <c r="H118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="I118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="K118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="L118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="M118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="N118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="O118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="P118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="Q118" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-    </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>93</v>
       </c>
@@ -13575,51 +13596,51 @@
       <c r="E119" s="306"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+        <f t="shared" ref="G119:Q119" si="45">IF(G$4="","",G101/G105)</f>
         <v>1.7220755031358876</v>
       </c>
       <c r="H119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="L119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="M119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="N119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="O119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="P119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Q119" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-    </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>224</v>
@@ -13632,51 +13653,51 @@
       <c r="E120" s="305"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
-        <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
+        <f t="shared" ref="G120:Q120" si="46">IF(G$4="","",G8/G105)</f>
         <v>0.15029676528014849</v>
       </c>
       <c r="H120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="I120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="K120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="L120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="M120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="N120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="O120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="P120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="Q120" s="102" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -13695,7 +13716,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>225</v>
@@ -13718,7 +13739,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>172</v>
@@ -13739,7 +13760,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -13747,114 +13768,114 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.2984235306407004</v>
+        <v>2.6144316551331115</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.1404997799266314</v>
+        <f t="shared" ref="G124:Q124" si="47">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>2.4342714851616312</v>
       </c>
       <c r="H124" s="178" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="I124" s="178" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="J124" s="178" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K124" s="178" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="L124" s="178" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="M124" s="178" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="N124" s="178" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="O124" s="178" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="P124" s="178" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="Q124" s="178" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>271</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1980338459190879E-2</v>
+        <v>4.7752176349463223E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.9095886391354001E-2</v>
+        <f t="shared" ref="G125" si="48">IF(G$4="","",G124/Market_Price)</f>
+        <v>4.4461579637655367E-2</v>
       </c>
       <c r="H125" s="77" t="str">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+        <f t="shared" ref="H125" si="49">IF(H$4="","",H124/Market_Price)</f>
         <v/>
       </c>
       <c r="I125" s="77" t="str">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+        <f t="shared" ref="I125" si="50">IF(I$4="","",I124/Market_Price)</f>
         <v/>
       </c>
       <c r="J125" s="77" t="str">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+        <f t="shared" ref="J125" si="51">IF(J$4="","",J124/Market_Price)</f>
         <v/>
       </c>
       <c r="K125" s="77" t="str">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+        <f t="shared" ref="K125" si="52">IF(K$4="","",K124/Market_Price)</f>
         <v/>
       </c>
       <c r="L125" s="77" t="str">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+        <f t="shared" ref="L125" si="53">IF(L$4="","",L124/Market_Price)</f>
         <v/>
       </c>
       <c r="M125" s="77" t="str">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+        <f t="shared" ref="M125" si="54">IF(M$4="","",M124/Market_Price)</f>
         <v/>
       </c>
       <c r="N125" s="77" t="str">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+        <f t="shared" ref="N125" si="55">IF(N$4="","",N124/Market_Price)</f>
         <v/>
       </c>
       <c r="O125" s="77" t="str">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+        <f t="shared" ref="O125" si="56">IF(O$4="","",O124/Market_Price)</f>
         <v/>
       </c>
       <c r="P125" s="77" t="str">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+        <f t="shared" ref="P125" si="57">IF(P$4="","",P124/Market_Price)</f>
         <v/>
       </c>
       <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="Q125" si="58">IF(Q$4="","",Q124/Market_Price)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>410</v>
       </c>
@@ -13904,688 +13925,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3